--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="404">
   <si>
     <t>Id</t>
   </si>
@@ -1076,6 +1076,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserXPixelSizeCalibrationViewModel</t>
+  </si>
+  <si>
+    <t>Focus Shift</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Laser.LaserFocusShiftCalibrationViewModel</t>
+  </si>
+  <si>
+    <t>RTFC</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Laser.LaserRtfcCalibrationViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -2030,7 +2042,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2072,6 +2084,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2587,525 +2605,525 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="18">
         <v>1</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="18">
         <v>666666</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="19">
         <v>1</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="19" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="19">
         <v>666666</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="20" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="17">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="19">
         <v>1</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="20" t="s">
+      <c r="E4" s="19"/>
+      <c r="F4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="19">
         <v>111111</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3140,172 +3158,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="18">
         <v>1</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17">
-        <v>2</v>
-      </c>
-      <c r="C3" s="17">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19">
+        <v>2</v>
+      </c>
+      <c r="C3" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="17">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="19">
         <v>3</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3335,172 +3353,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="18">
         <v>1</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17">
-        <v>2</v>
-      </c>
-      <c r="C3" s="17">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19">
+        <v>2</v>
+      </c>
+      <c r="C3" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="17">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="19">
         <v>3</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3539,340 +3557,340 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="18">
         <v>-1</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="18">
         <v>0</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="18">
         <v>1</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="19">
         <v>-1</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="19">
         <v>1</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="19">
         <v>3</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="17">
+      <c r="A4" s="19">
         <v>21</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="17">
-        <v>2</v>
-      </c>
-      <c r="D4" s="17">
+      <c r="C4" s="19">
+        <v>2</v>
+      </c>
+      <c r="D4" s="19">
         <v>21</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="19">
         <v>3</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="17">
+      <c r="A5" s="19">
         <v>211</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="19">
         <v>21</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="19">
         <v>211</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="19">
         <v>1</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="17">
+      <c r="A6" s="19">
         <v>212</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="19">
         <v>21</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="19">
         <v>212</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="19">
         <v>3</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="19" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="17">
+      <c r="A7" s="19">
         <v>22</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="17">
-        <v>2</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="C7" s="19">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19">
         <v>22</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="19">
         <v>3</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="17">
+      <c r="A8" s="19">
         <v>221</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="19">
         <v>22</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <v>221</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <v>3</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="19" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="17">
+      <c r="A9" s="19">
         <v>222</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="19">
         <v>22</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="19">
         <v>222</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="19">
         <v>3</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="19" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3908,234 +3926,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="18">
         <v>0</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="16">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="18">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4173,234 +4191,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="18">
         <v>0</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="16">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="18">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4430,154 +4448,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4607,10 +4625,10 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="18">
         <v>2</v>
       </c>
       <c r="C2" s="5">
@@ -4618,10 +4636,10 @@
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18">
         <v>2</v>
       </c>
       <c r="C3" s="5">
@@ -4629,10 +4647,10 @@
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="16">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="18">
         <v>2</v>
       </c>
       <c r="C4" s="5">
@@ -4640,10 +4658,10 @@
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="16">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="18">
         <v>2</v>
       </c>
       <c r="C5" s="5">
@@ -4651,10 +4669,10 @@
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="18">
         <v>2</v>
       </c>
       <c r="C6" s="5">
@@ -4662,10 +4680,10 @@
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="16">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="18">
         <v>2</v>
       </c>
       <c r="C7" s="5">
@@ -4673,10 +4691,10 @@
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="16">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="18">
         <v>2</v>
       </c>
       <c r="C8" s="5">
@@ -4684,10 +4702,10 @@
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="18">
         <v>2</v>
       </c>
       <c r="C9" s="5">
@@ -4695,10 +4713,10 @@
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="16">
+      <c r="A10" s="18">
         <v>9</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="18">
         <v>2</v>
       </c>
       <c r="C10" s="5">
@@ -4706,10 +4724,10 @@
       </c>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="16">
+      <c r="A11" s="18">
         <v>10</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="18">
         <v>2</v>
       </c>
       <c r="C11" s="5">
@@ -4717,10 +4735,10 @@
       </c>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="18">
         <v>2</v>
       </c>
       <c r="C12" s="5">
@@ -4728,10 +4746,10 @@
       </c>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="16">
+      <c r="A13" s="18">
         <v>12</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="18">
         <v>2</v>
       </c>
       <c r="C13" s="5">
@@ -4739,10 +4757,10 @@
       </c>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="16">
+      <c r="A14" s="18">
         <v>13</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="18">
         <v>2</v>
       </c>
       <c r="C14" s="5">
@@ -4750,10 +4768,10 @@
       </c>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="18">
         <v>2</v>
       </c>
       <c r="C15" s="5">
@@ -4761,10 +4779,10 @@
       </c>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="16">
+      <c r="A16" s="18">
         <v>15</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="18">
         <v>2</v>
       </c>
       <c r="C16" s="5">
@@ -4772,10 +4790,10 @@
       </c>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="16">
+      <c r="A17" s="18">
         <v>16</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="18">
         <v>2</v>
       </c>
       <c r="C17" s="5">
@@ -4783,10 +4801,10 @@
       </c>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="18">
         <v>2</v>
       </c>
       <c r="C18" s="5">
@@ -4794,10 +4812,10 @@
       </c>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="16">
+      <c r="A19" s="18">
         <v>18</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="18">
         <v>2</v>
       </c>
       <c r="C19" s="5">
@@ -4805,10 +4823,10 @@
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="16">
+      <c r="A20" s="18">
         <v>19</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="18">
         <v>2</v>
       </c>
       <c r="C20" s="5">
@@ -4816,10 +4834,10 @@
       </c>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17">
+      <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="18">
         <v>2</v>
       </c>
       <c r="C21" s="5">
@@ -4827,10 +4845,10 @@
       </c>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="16">
+      <c r="A22" s="18">
         <v>21</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="18">
         <v>2</v>
       </c>
       <c r="C22" s="5">
@@ -4838,10 +4856,10 @@
       </c>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="16">
+      <c r="A23" s="18">
         <v>22</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="18">
         <v>2</v>
       </c>
       <c r="C23" s="5">
@@ -4849,10 +4867,10 @@
       </c>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17">
+      <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="18">
         <v>2</v>
       </c>
       <c r="C24" s="5">
@@ -4860,10 +4878,10 @@
       </c>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="16">
+      <c r="A25" s="18">
         <v>24</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="18">
         <v>2</v>
       </c>
       <c r="C25" s="5">
@@ -4871,10 +4889,10 @@
       </c>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="16">
+      <c r="A26" s="18">
         <v>25</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="18">
         <v>2</v>
       </c>
       <c r="C26" s="5">
@@ -4882,10 +4900,10 @@
       </c>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17">
+      <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="18">
         <v>2</v>
       </c>
       <c r="C27" s="5">
@@ -4893,10 +4911,10 @@
       </c>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="16">
+      <c r="A28" s="18">
         <v>27</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="18">
         <v>2</v>
       </c>
       <c r="C28" s="5">
@@ -4904,10 +4922,10 @@
       </c>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="16">
+      <c r="A29" s="18">
         <v>28</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="18">
         <v>2</v>
       </c>
       <c r="C29" s="5">
@@ -4915,10 +4933,10 @@
       </c>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17">
+      <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="18">
         <v>2</v>
       </c>
       <c r="C30" s="5">
@@ -4926,10 +4944,10 @@
       </c>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="16">
+      <c r="A31" s="18">
         <v>30</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="18">
         <v>2</v>
       </c>
       <c r="C31" s="5">
@@ -4937,10 +4955,10 @@
       </c>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A32" s="16">
+      <c r="A32" s="18">
         <v>31</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="18">
         <v>2</v>
       </c>
       <c r="C32" s="5">
@@ -4948,10 +4966,10 @@
       </c>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A33" s="17">
+      <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="18">
         <v>2</v>
       </c>
       <c r="C33" s="5">
@@ -4959,10 +4977,10 @@
       </c>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A34" s="16">
+      <c r="A34" s="18">
         <v>33</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="18">
         <v>2</v>
       </c>
       <c r="C34" s="5">
@@ -4970,10 +4988,10 @@
       </c>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A35" s="16">
+      <c r="A35" s="18">
         <v>34</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="18">
         <v>2</v>
       </c>
       <c r="C35" s="5">
@@ -4981,10 +4999,10 @@
       </c>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A36" s="17">
+      <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="18">
         <v>2</v>
       </c>
       <c r="C36" s="5">
@@ -4992,10 +5010,10 @@
       </c>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A37" s="16">
+      <c r="A37" s="18">
         <v>36</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="18">
         <v>2</v>
       </c>
       <c r="C37" s="5">
@@ -5003,10 +5021,10 @@
       </c>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A38" s="16">
+      <c r="A38" s="18">
         <v>37</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="18">
         <v>2</v>
       </c>
       <c r="C38" s="5">
@@ -5014,10 +5032,10 @@
       </c>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A39" s="17">
+      <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="18">
         <v>2</v>
       </c>
       <c r="C39" s="5">
@@ -5025,10 +5043,10 @@
       </c>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A40" s="16">
+      <c r="A40" s="18">
         <v>39</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="18">
         <v>2</v>
       </c>
       <c r="C40" s="5">
@@ -5036,10 +5054,10 @@
       </c>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A41" s="16">
+      <c r="A41" s="18">
         <v>40</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="18">
         <v>2</v>
       </c>
       <c r="C41" s="5">
@@ -5047,10 +5065,10 @@
       </c>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A42" s="17">
+      <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="18">
         <v>2</v>
       </c>
       <c r="C42" s="5">
@@ -5058,10 +5076,10 @@
       </c>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A43" s="16">
+      <c r="A43" s="18">
         <v>42</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="18">
         <v>2</v>
       </c>
       <c r="C43" s="5">
@@ -5069,10 +5087,10 @@
       </c>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A44" s="16">
+      <c r="A44" s="18">
         <v>43</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="18">
         <v>2</v>
       </c>
       <c r="C44" s="5">
@@ -5080,10 +5098,10 @@
       </c>
     </row>
     <row r="45" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A45" s="17">
+      <c r="A45" s="19">
         <v>44</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="18">
         <v>2</v>
       </c>
       <c r="C45" s="5">
@@ -5091,10 +5109,10 @@
       </c>
     </row>
     <row r="46" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A46" s="16">
+      <c r="A46" s="18">
         <v>45</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="18">
         <v>2</v>
       </c>
       <c r="C46" s="5">
@@ -5102,10 +5120,10 @@
       </c>
     </row>
     <row r="47" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A47" s="16">
+      <c r="A47" s="18">
         <v>46</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="18">
         <v>2</v>
       </c>
       <c r="C47" s="5">
@@ -5113,10 +5131,10 @@
       </c>
     </row>
     <row r="48" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A48" s="17">
+      <c r="A48" s="19">
         <v>47</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="18">
         <v>2</v>
       </c>
       <c r="C48" s="5">
@@ -5124,10 +5142,10 @@
       </c>
     </row>
     <row r="49" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A49" s="16">
+      <c r="A49" s="18">
         <v>48</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="18">
         <v>2</v>
       </c>
       <c r="C49" s="5">
@@ -5135,10 +5153,10 @@
       </c>
     </row>
     <row r="50" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A50" s="16">
+      <c r="A50" s="18">
         <v>49</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="18">
         <v>2</v>
       </c>
       <c r="C50" s="5">
@@ -5146,10 +5164,10 @@
       </c>
     </row>
     <row r="51" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A51" s="17">
+      <c r="A51" s="19">
         <v>50</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="18">
         <v>2</v>
       </c>
       <c r="C51" s="5">
@@ -5157,10 +5175,10 @@
       </c>
     </row>
     <row r="52" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A52" s="16">
+      <c r="A52" s="18">
         <v>51</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="18">
         <v>2</v>
       </c>
       <c r="C52" s="5">
@@ -5168,10 +5186,10 @@
       </c>
     </row>
     <row r="53" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A53" s="16">
+      <c r="A53" s="18">
         <v>52</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="18">
         <v>2</v>
       </c>
       <c r="C53" s="5">
@@ -5179,10 +5197,10 @@
       </c>
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A54" s="17">
+      <c r="A54" s="19">
         <v>53</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="18">
         <v>2</v>
       </c>
       <c r="C54" s="5">
@@ -5190,10 +5208,10 @@
       </c>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A55" s="16">
+      <c r="A55" s="18">
         <v>54</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="18">
         <v>2</v>
       </c>
       <c r="C55" s="5">
@@ -5201,10 +5219,10 @@
       </c>
     </row>
     <row r="56" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A56" s="16">
+      <c r="A56" s="18">
         <v>55</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="18">
         <v>2</v>
       </c>
       <c r="C56" s="5">
@@ -5212,10 +5230,10 @@
       </c>
     </row>
     <row r="57" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A57" s="17">
+      <c r="A57" s="19">
         <v>56</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="18">
         <v>2</v>
       </c>
       <c r="C57" s="5">
@@ -5223,10 +5241,10 @@
       </c>
     </row>
     <row r="58" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A58" s="16">
+      <c r="A58" s="18">
         <v>57</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="18">
         <v>2</v>
       </c>
       <c r="C58" s="5">
@@ -5234,10 +5252,10 @@
       </c>
     </row>
     <row r="59" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A59" s="16">
-        <v>58</v>
-      </c>
-      <c r="B59" s="16">
+      <c r="A59" s="18">
+        <v>58</v>
+      </c>
+      <c r="B59" s="18">
         <v>2</v>
       </c>
       <c r="C59" s="5">
@@ -5245,10 +5263,10 @@
       </c>
     </row>
     <row r="60" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A60" s="16">
+      <c r="A60" s="18">
         <v>59</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="18">
         <v>2</v>
       </c>
       <c r="C60" s="5">
@@ -5256,10 +5274,10 @@
       </c>
     </row>
     <row r="61" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A61" s="16">
+      <c r="A61" s="18">
         <v>60</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="18">
         <v>2</v>
       </c>
       <c r="C61" s="5">
@@ -5267,10 +5285,10 @@
       </c>
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A62" s="16">
+      <c r="A62" s="18">
         <v>61</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="18">
         <v>2</v>
       </c>
       <c r="C62" s="5">
@@ -5278,10 +5296,10 @@
       </c>
     </row>
     <row r="63" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A63" s="16">
+      <c r="A63" s="18">
         <v>62</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="18">
         <v>2</v>
       </c>
       <c r="C63" s="5">
@@ -5289,10 +5307,10 @@
       </c>
     </row>
     <row r="64" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A64" s="16">
+      <c r="A64" s="18">
         <v>63</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="18">
         <v>2</v>
       </c>
       <c r="C64" s="5">
@@ -5300,10 +5318,10 @@
       </c>
     </row>
     <row r="65" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A65" s="16">
+      <c r="A65" s="18">
         <v>64</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="18">
         <v>2</v>
       </c>
       <c r="C65" s="5">
@@ -5311,10 +5329,10 @@
       </c>
     </row>
     <row r="66" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A66" s="16">
+      <c r="A66" s="18">
         <v>65</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="18">
         <v>2</v>
       </c>
       <c r="C66" s="5">
@@ -5322,10 +5340,10 @@
       </c>
     </row>
     <row r="67" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A67" s="16">
+      <c r="A67" s="18">
         <v>66</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="18">
         <v>2</v>
       </c>
       <c r="C67" s="5">
@@ -5333,10 +5351,10 @@
       </c>
     </row>
     <row r="68" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A68" s="16">
+      <c r="A68" s="18">
         <v>67</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="18">
         <v>2</v>
       </c>
       <c r="C68" s="5">
@@ -5344,10 +5362,10 @@
       </c>
     </row>
     <row r="69" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A69" s="16">
+      <c r="A69" s="18">
         <v>68</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="18">
         <v>2</v>
       </c>
       <c r="C69" s="5">
@@ -5355,10 +5373,10 @@
       </c>
     </row>
     <row r="70" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A70" s="16">
+      <c r="A70" s="18">
         <v>69</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="18">
         <v>2</v>
       </c>
       <c r="C70" s="5">
@@ -5366,10 +5384,10 @@
       </c>
     </row>
     <row r="71" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A71" s="16">
+      <c r="A71" s="18">
         <v>70</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="18">
         <v>2</v>
       </c>
       <c r="C71" s="5">
@@ -5377,10 +5395,10 @@
       </c>
     </row>
     <row r="72" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A72" s="16">
+      <c r="A72" s="18">
         <v>71</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="18">
         <v>2</v>
       </c>
       <c r="C72" s="5">
@@ -5388,10 +5406,10 @@
       </c>
     </row>
     <row r="73" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A73" s="16">
+      <c r="A73" s="18">
         <v>72</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="18">
         <v>2</v>
       </c>
       <c r="C73" s="5">
@@ -5399,10 +5417,10 @@
       </c>
     </row>
     <row r="74" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A74" s="16">
+      <c r="A74" s="18">
         <v>73</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="18">
         <v>2</v>
       </c>
       <c r="C74" s="5">
@@ -5410,10 +5428,10 @@
       </c>
     </row>
     <row r="75" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A75" s="16">
+      <c r="A75" s="18">
         <v>74</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="18">
         <v>2</v>
       </c>
       <c r="C75" s="5">
@@ -5421,10 +5439,10 @@
       </c>
     </row>
     <row r="76" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A76" s="16">
+      <c r="A76" s="18">
         <v>75</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="18">
         <v>2</v>
       </c>
       <c r="C76" s="5">
@@ -5432,10 +5450,10 @@
       </c>
     </row>
     <row r="77" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A77" s="16">
+      <c r="A77" s="18">
         <v>76</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="18">
         <v>2</v>
       </c>
       <c r="C77" s="5">
@@ -5443,10 +5461,10 @@
       </c>
     </row>
     <row r="78" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A78" s="16">
+      <c r="A78" s="18">
         <v>77</v>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="18">
         <v>2</v>
       </c>
       <c r="C78" s="5">
@@ -5454,10 +5472,10 @@
       </c>
     </row>
     <row r="79" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A79" s="16">
+      <c r="A79" s="18">
         <v>78</v>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="18">
         <v>2</v>
       </c>
       <c r="C79" s="5">
@@ -5465,10 +5483,10 @@
       </c>
     </row>
     <row r="80" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A80" s="16">
+      <c r="A80" s="18">
         <v>79</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="18">
         <v>2</v>
       </c>
       <c r="C80" s="5">
@@ -5476,10 +5494,10 @@
       </c>
     </row>
     <row r="81" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A81" s="16">
+      <c r="A81" s="18">
         <v>80</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="18">
         <v>2</v>
       </c>
       <c r="C81" s="5">
@@ -5487,10 +5505,10 @@
       </c>
     </row>
     <row r="82" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A82" s="16">
+      <c r="A82" s="18">
         <v>81</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="18">
         <v>2</v>
       </c>
       <c r="C82" s="5">
@@ -5498,10 +5516,10 @@
       </c>
     </row>
     <row r="83" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A83" s="16">
+      <c r="A83" s="18">
         <v>82</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="18">
         <v>2</v>
       </c>
       <c r="C83" s="5">
@@ -5509,10 +5527,10 @@
       </c>
     </row>
     <row r="84" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A84" s="16">
+      <c r="A84" s="18">
         <v>83</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="18">
         <v>2</v>
       </c>
       <c r="C84" s="5">
@@ -5520,10 +5538,10 @@
       </c>
     </row>
     <row r="85" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A85" s="16">
+      <c r="A85" s="18">
         <v>84</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="18">
         <v>2</v>
       </c>
       <c r="C85" s="5">
@@ -5531,10 +5549,10 @@
       </c>
     </row>
     <row r="86" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A86" s="16">
+      <c r="A86" s="18">
         <v>85</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="18">
         <v>2</v>
       </c>
       <c r="C86" s="5">
@@ -5542,10 +5560,10 @@
       </c>
     </row>
     <row r="87" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A87" s="16">
+      <c r="A87" s="18">
         <v>86</v>
       </c>
-      <c r="B87" s="16">
+      <c r="B87" s="18">
         <v>2</v>
       </c>
       <c r="C87" s="5">
@@ -5553,10 +5571,10 @@
       </c>
     </row>
     <row r="88" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A88" s="16">
+      <c r="A88" s="18">
         <v>87</v>
       </c>
-      <c r="B88" s="16">
+      <c r="B88" s="18">
         <v>2</v>
       </c>
       <c r="C88" s="5">
@@ -5564,10 +5582,10 @@
       </c>
     </row>
     <row r="89" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A89" s="16">
+      <c r="A89" s="18">
         <v>88</v>
       </c>
-      <c r="B89" s="16">
+      <c r="B89" s="18">
         <v>2</v>
       </c>
       <c r="C89" s="5">
@@ -5575,10 +5593,10 @@
       </c>
     </row>
     <row r="90" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A90" s="16">
+      <c r="A90" s="18">
         <v>89</v>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="18">
         <v>2</v>
       </c>
       <c r="C90" s="5">
@@ -5586,10 +5604,10 @@
       </c>
     </row>
     <row r="91" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A91" s="16">
+      <c r="A91" s="18">
         <v>90</v>
       </c>
-      <c r="B91" s="16">
+      <c r="B91" s="18">
         <v>2</v>
       </c>
       <c r="C91" s="5">
@@ -5597,10 +5615,10 @@
       </c>
     </row>
     <row r="92" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A92" s="16">
+      <c r="A92" s="18">
         <v>91</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B92" s="18">
         <v>2</v>
       </c>
       <c r="C92" s="5">
@@ -5608,10 +5626,10 @@
       </c>
     </row>
     <row r="93" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A93" s="16">
+      <c r="A93" s="18">
         <v>92</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B93" s="18">
         <v>2</v>
       </c>
       <c r="C93" s="5">
@@ -5619,10 +5637,10 @@
       </c>
     </row>
     <row r="94" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A94" s="16">
+      <c r="A94" s="18">
         <v>93</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B94" s="18">
         <v>2</v>
       </c>
       <c r="C94" s="5">
@@ -5630,10 +5648,10 @@
       </c>
     </row>
     <row r="95" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A95" s="16">
+      <c r="A95" s="18">
         <v>94</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B95" s="18">
         <v>2</v>
       </c>
       <c r="C95" s="5">
@@ -5641,10 +5659,10 @@
       </c>
     </row>
     <row r="96" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A96" s="16">
+      <c r="A96" s="18">
         <v>95</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B96" s="18">
         <v>2</v>
       </c>
       <c r="C96" s="5">
@@ -5652,10 +5670,10 @@
       </c>
     </row>
     <row r="97" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A97" s="16">
+      <c r="A97" s="18">
         <v>96</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B97" s="18">
         <v>2</v>
       </c>
       <c r="C97" s="5">
@@ -5663,10 +5681,10 @@
       </c>
     </row>
     <row r="98" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A98" s="16">
+      <c r="A98" s="18">
         <v>97</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B98" s="18">
         <v>2</v>
       </c>
       <c r="C98" s="5">
@@ -5674,10 +5692,10 @@
       </c>
     </row>
     <row r="99" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A99" s="16">
+      <c r="A99" s="18">
         <v>98</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="18">
         <v>2</v>
       </c>
       <c r="C99" s="5">
@@ -5685,10 +5703,10 @@
       </c>
     </row>
     <row r="100" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A100" s="16">
+      <c r="A100" s="18">
         <v>99</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B100" s="18">
         <v>2</v>
       </c>
       <c r="C100" s="5">
@@ -5696,10 +5714,10 @@
       </c>
     </row>
     <row r="101" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A101" s="16">
+      <c r="A101" s="18">
         <v>100</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B101" s="18">
         <v>2</v>
       </c>
       <c r="C101" s="5">
@@ -5707,10 +5725,10 @@
       </c>
     </row>
     <row r="102" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A102" s="16">
+      <c r="A102" s="18">
         <v>101</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B102" s="18">
         <v>2</v>
       </c>
       <c r="C102" s="5">
@@ -5718,10 +5736,10 @@
       </c>
     </row>
     <row r="103" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A103" s="16">
+      <c r="A103" s="18">
         <v>102</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B103" s="18">
         <v>2</v>
       </c>
       <c r="C103" s="5">
@@ -5729,10 +5747,10 @@
       </c>
     </row>
     <row r="104" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A104" s="16">
+      <c r="A104" s="18">
         <v>103</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B104" s="18">
         <v>2</v>
       </c>
       <c r="C104" s="5">
@@ -5740,10 +5758,10 @@
       </c>
     </row>
     <row r="105" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A105" s="16">
+      <c r="A105" s="18">
         <v>104</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B105" s="18">
         <v>2</v>
       </c>
       <c r="C105" s="5">
@@ -5751,10 +5769,10 @@
       </c>
     </row>
     <row r="106" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A106" s="16">
+      <c r="A106" s="18">
         <v>105</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B106" s="18">
         <v>2</v>
       </c>
       <c r="C106" s="5">
@@ -5762,10 +5780,10 @@
       </c>
     </row>
     <row r="107" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A107" s="16">
+      <c r="A107" s="18">
         <v>106</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B107" s="18">
         <v>2</v>
       </c>
       <c r="C107" s="5">
@@ -5773,10 +5791,10 @@
       </c>
     </row>
     <row r="108" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A108" s="16">
+      <c r="A108" s="18">
         <v>107</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B108" s="18">
         <v>2</v>
       </c>
       <c r="C108" s="5">
@@ -5784,10 +5802,10 @@
       </c>
     </row>
     <row r="109" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A109" s="16">
+      <c r="A109" s="18">
         <v>108</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B109" s="18">
         <v>2</v>
       </c>
       <c r="C109" s="5">
@@ -5795,10 +5813,10 @@
       </c>
     </row>
     <row r="110" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A110" s="16">
+      <c r="A110" s="18">
         <v>109</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B110" s="18">
         <v>2</v>
       </c>
       <c r="C110" s="5">
@@ -5806,10 +5824,10 @@
       </c>
     </row>
     <row r="111" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A111" s="16">
+      <c r="A111" s="18">
         <v>110</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="18">
         <v>2</v>
       </c>
       <c r="C111" s="5">
@@ -5817,10 +5835,10 @@
       </c>
     </row>
     <row r="112" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A112" s="16">
+      <c r="A112" s="18">
         <v>111</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B112" s="18">
         <v>2</v>
       </c>
       <c r="C112" s="5">
@@ -5828,10 +5846,10 @@
       </c>
     </row>
     <row r="113" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A113" s="16">
+      <c r="A113" s="18">
         <v>112</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="18">
         <v>2</v>
       </c>
       <c r="C113" s="5">
@@ -5839,10 +5857,10 @@
       </c>
     </row>
     <row r="114" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A114" s="16">
+      <c r="A114" s="18">
         <v>113</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="18">
         <v>2</v>
       </c>
       <c r="C114" s="5">
@@ -5850,10 +5868,10 @@
       </c>
     </row>
     <row r="115" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A115" s="16">
+      <c r="A115" s="18">
         <v>114</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="18">
         <v>2</v>
       </c>
       <c r="C115" s="5">
@@ -5861,10 +5879,10 @@
       </c>
     </row>
     <row r="116" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A116" s="16">
+      <c r="A116" s="18">
         <v>115</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B116" s="18">
         <v>2</v>
       </c>
       <c r="C116" s="5">
@@ -5872,10 +5890,10 @@
       </c>
     </row>
     <row r="117" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A117" s="16">
+      <c r="A117" s="18">
         <v>116</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B117" s="18">
         <v>2</v>
       </c>
       <c r="C117" s="5">
@@ -5883,10 +5901,10 @@
       </c>
     </row>
     <row r="118" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A118" s="16">
+      <c r="A118" s="18">
         <v>117</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B118" s="18">
         <v>2</v>
       </c>
       <c r="C118" s="5">
@@ -5894,10 +5912,10 @@
       </c>
     </row>
     <row r="119" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A119" s="16">
+      <c r="A119" s="18">
         <v>118</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B119" s="18">
         <v>2</v>
       </c>
       <c r="C119" s="5">
@@ -5905,10 +5923,10 @@
       </c>
     </row>
     <row r="120" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A120" s="16">
+      <c r="A120" s="18">
         <v>119</v>
       </c>
-      <c r="B120" s="16">
+      <c r="B120" s="18">
         <v>2</v>
       </c>
       <c r="C120" s="5">
@@ -5916,10 +5934,10 @@
       </c>
     </row>
     <row r="121" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A121" s="16">
+      <c r="A121" s="18">
         <v>120</v>
       </c>
-      <c r="B121" s="16">
+      <c r="B121" s="18">
         <v>2</v>
       </c>
       <c r="C121" s="5">
@@ -5927,10 +5945,10 @@
       </c>
     </row>
     <row r="122" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A122" s="16">
+      <c r="A122" s="18">
         <v>121</v>
       </c>
-      <c r="B122" s="16">
+      <c r="B122" s="18">
         <v>2</v>
       </c>
       <c r="C122" s="5">
@@ -5938,10 +5956,10 @@
       </c>
     </row>
     <row r="123" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A123" s="16">
+      <c r="A123" s="18">
         <v>122</v>
       </c>
-      <c r="B123" s="16">
+      <c r="B123" s="18">
         <v>2</v>
       </c>
       <c r="C123" s="5">
@@ -5949,10 +5967,10 @@
       </c>
     </row>
     <row r="124" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A124" s="16">
+      <c r="A124" s="18">
         <v>123</v>
       </c>
-      <c r="B124" s="16">
+      <c r="B124" s="18">
         <v>2</v>
       </c>
       <c r="C124" s="5">
@@ -5960,10 +5978,10 @@
       </c>
     </row>
     <row r="125" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A125" s="16">
+      <c r="A125" s="18">
         <v>124</v>
       </c>
-      <c r="B125" s="16">
+      <c r="B125" s="18">
         <v>2</v>
       </c>
       <c r="C125" s="5">
@@ -5971,10 +5989,10 @@
       </c>
     </row>
     <row r="126" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A126" s="16">
+      <c r="A126" s="18">
         <v>125</v>
       </c>
-      <c r="B126" s="16">
+      <c r="B126" s="18">
         <v>2</v>
       </c>
       <c r="C126" s="5">
@@ -5982,10 +6000,10 @@
       </c>
     </row>
     <row r="127" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A127" s="16">
+      <c r="A127" s="18">
         <v>126</v>
       </c>
-      <c r="B127" s="16">
+      <c r="B127" s="18">
         <v>2</v>
       </c>
       <c r="C127" s="5">
@@ -5993,10 +6011,10 @@
       </c>
     </row>
     <row r="128" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A128" s="16">
+      <c r="A128" s="18">
         <v>127</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="18">
         <v>2</v>
       </c>
       <c r="C128" s="5">
@@ -6004,10 +6022,10 @@
       </c>
     </row>
     <row r="129" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A129" s="16">
+      <c r="A129" s="18">
         <v>128</v>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="18">
         <v>2</v>
       </c>
       <c r="C129" s="5">
@@ -6015,10 +6033,10 @@
       </c>
     </row>
     <row r="130" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A130" s="16">
+      <c r="A130" s="18">
         <v>129</v>
       </c>
-      <c r="B130" s="16">
+      <c r="B130" s="18">
         <v>2</v>
       </c>
       <c r="C130" s="5">
@@ -6026,10 +6044,10 @@
       </c>
     </row>
     <row r="131" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A131" s="16">
+      <c r="A131" s="18">
         <v>130</v>
       </c>
-      <c r="B131" s="16">
+      <c r="B131" s="18">
         <v>2</v>
       </c>
       <c r="C131" s="5">
@@ -6037,10 +6055,10 @@
       </c>
     </row>
     <row r="132" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A132" s="16">
+      <c r="A132" s="18">
         <v>131</v>
       </c>
-      <c r="B132" s="16">
+      <c r="B132" s="18">
         <v>2</v>
       </c>
       <c r="C132" s="5">
@@ -6048,10 +6066,10 @@
       </c>
     </row>
     <row r="133" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A133" s="16">
+      <c r="A133" s="18">
         <v>132</v>
       </c>
-      <c r="B133" s="16">
+      <c r="B133" s="18">
         <v>2</v>
       </c>
       <c r="C133" s="5">
@@ -6059,10 +6077,10 @@
       </c>
     </row>
     <row r="134" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A134" s="16">
+      <c r="A134" s="18">
         <v>133</v>
       </c>
-      <c r="B134" s="16">
+      <c r="B134" s="18">
         <v>2</v>
       </c>
       <c r="C134" s="5">
@@ -6070,10 +6088,10 @@
       </c>
     </row>
     <row r="135" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A135" s="16">
+      <c r="A135" s="18">
         <v>134</v>
       </c>
-      <c r="B135" s="16">
+      <c r="B135" s="18">
         <v>2</v>
       </c>
       <c r="C135" s="5">
@@ -6081,10 +6099,10 @@
       </c>
     </row>
     <row r="136" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A136" s="16">
+      <c r="A136" s="18">
         <v>135</v>
       </c>
-      <c r="B136" s="16">
+      <c r="B136" s="18">
         <v>2</v>
       </c>
       <c r="C136" s="5">
@@ -6092,10 +6110,10 @@
       </c>
     </row>
     <row r="137" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A137" s="16">
+      <c r="A137" s="18">
         <v>136</v>
       </c>
-      <c r="B137" s="16">
+      <c r="B137" s="18">
         <v>2</v>
       </c>
       <c r="C137" s="5">
@@ -6103,10 +6121,10 @@
       </c>
     </row>
     <row r="138" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A138" s="16">
+      <c r="A138" s="18">
         <v>137</v>
       </c>
-      <c r="B138" s="16">
+      <c r="B138" s="18">
         <v>2</v>
       </c>
       <c r="C138" s="5">
@@ -6114,10 +6132,10 @@
       </c>
     </row>
     <row r="139" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A139" s="16">
+      <c r="A139" s="18">
         <v>138</v>
       </c>
-      <c r="B139" s="16">
+      <c r="B139" s="18">
         <v>2</v>
       </c>
       <c r="C139" s="5">
@@ -6125,10 +6143,10 @@
       </c>
     </row>
     <row r="140" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A140" s="16">
+      <c r="A140" s="18">
         <v>139</v>
       </c>
-      <c r="B140" s="16">
+      <c r="B140" s="18">
         <v>2</v>
       </c>
       <c r="C140" s="5">
@@ -6136,10 +6154,10 @@
       </c>
     </row>
     <row r="141" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A141" s="16">
+      <c r="A141" s="18">
         <v>140</v>
       </c>
-      <c r="B141" s="16">
+      <c r="B141" s="18">
         <v>2</v>
       </c>
       <c r="C141" s="5">
@@ -6147,10 +6165,10 @@
       </c>
     </row>
     <row r="142" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A142" s="16">
+      <c r="A142" s="18">
         <v>141</v>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="18">
         <v>2</v>
       </c>
       <c r="C142" s="5">
@@ -6158,10 +6176,10 @@
       </c>
     </row>
     <row r="143" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A143" s="16">
+      <c r="A143" s="18">
         <v>142</v>
       </c>
-      <c r="B143" s="16">
+      <c r="B143" s="18">
         <v>2</v>
       </c>
       <c r="C143" s="5">
@@ -6169,10 +6187,10 @@
       </c>
     </row>
     <row r="144" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A144" s="16">
+      <c r="A144" s="18">
         <v>122</v>
       </c>
-      <c r="B144" s="16">
+      <c r="B144" s="18">
         <v>2</v>
       </c>
       <c r="C144" s="5">
@@ -6180,10 +6198,10 @@
       </c>
     </row>
     <row r="145" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A145" s="16">
+      <c r="A145" s="18">
         <v>123</v>
       </c>
-      <c r="B145" s="16">
+      <c r="B145" s="18">
         <v>2</v>
       </c>
       <c r="C145" s="5">
@@ -6191,10 +6209,10 @@
       </c>
     </row>
     <row r="146" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A146" s="16">
+      <c r="A146" s="18">
         <v>124</v>
       </c>
-      <c r="B146" s="16">
+      <c r="B146" s="18">
         <v>2</v>
       </c>
       <c r="C146" s="5">
@@ -6202,10 +6220,10 @@
       </c>
     </row>
     <row r="147" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A147" s="16">
+      <c r="A147" s="18">
         <v>125</v>
       </c>
-      <c r="B147" s="16">
+      <c r="B147" s="18">
         <v>2</v>
       </c>
       <c r="C147" s="5">
@@ -6213,10 +6231,10 @@
       </c>
     </row>
     <row r="148" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A148" s="16">
+      <c r="A148" s="18">
         <v>126</v>
       </c>
-      <c r="B148" s="16">
+      <c r="B148" s="18">
         <v>2</v>
       </c>
       <c r="C148" s="5">
@@ -6224,10 +6242,10 @@
       </c>
     </row>
     <row r="149" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A149" s="16">
+      <c r="A149" s="18">
         <v>127</v>
       </c>
-      <c r="B149" s="16">
+      <c r="B149" s="18">
         <v>2</v>
       </c>
       <c r="C149" s="5">
@@ -6235,10 +6253,10 @@
       </c>
     </row>
     <row r="150" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A150" s="16">
+      <c r="A150" s="18">
         <v>128</v>
       </c>
-      <c r="B150" s="16">
+      <c r="B150" s="18">
         <v>2</v>
       </c>
       <c r="C150" s="5">
@@ -6246,10 +6264,10 @@
       </c>
     </row>
     <row r="151" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A151" s="16">
+      <c r="A151" s="18">
         <v>129</v>
       </c>
-      <c r="B151" s="16">
+      <c r="B151" s="18">
         <v>2</v>
       </c>
       <c r="C151" s="5">
@@ -6257,10 +6275,10 @@
       </c>
     </row>
     <row r="152" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A152" s="16">
+      <c r="A152" s="18">
         <v>130</v>
       </c>
-      <c r="B152" s="16">
+      <c r="B152" s="18">
         <v>2</v>
       </c>
       <c r="C152" s="5">
@@ -6268,10 +6286,10 @@
       </c>
     </row>
     <row r="153" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A153" s="16">
+      <c r="A153" s="18">
         <v>131</v>
       </c>
-      <c r="B153" s="16">
+      <c r="B153" s="18">
         <v>2</v>
       </c>
       <c r="C153" s="5">
@@ -6279,10 +6297,10 @@
       </c>
     </row>
     <row r="154" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A154" s="16">
+      <c r="A154" s="18">
         <v>132</v>
       </c>
-      <c r="B154" s="16">
+      <c r="B154" s="18">
         <v>2</v>
       </c>
       <c r="C154" s="5">
@@ -6290,10 +6308,10 @@
       </c>
     </row>
     <row r="155" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A155" s="16">
+      <c r="A155" s="18">
         <v>133</v>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="18">
         <v>2</v>
       </c>
       <c r="C155" s="5">
@@ -6301,10 +6319,10 @@
       </c>
     </row>
     <row r="156" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A156" s="16">
+      <c r="A156" s="18">
         <v>134</v>
       </c>
-      <c r="B156" s="16">
+      <c r="B156" s="18">
         <v>2</v>
       </c>
       <c r="C156" s="5">
@@ -6312,10 +6330,10 @@
       </c>
     </row>
     <row r="157" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A157" s="16">
+      <c r="A157" s="18">
         <v>135</v>
       </c>
-      <c r="B157" s="16">
+      <c r="B157" s="18">
         <v>2</v>
       </c>
       <c r="C157" s="5">
@@ -6323,10 +6341,10 @@
       </c>
     </row>
     <row r="158" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A158" s="16">
+      <c r="A158" s="18">
         <v>136</v>
       </c>
-      <c r="B158" s="16">
+      <c r="B158" s="18">
         <v>2</v>
       </c>
       <c r="C158" s="5">
@@ -6334,10 +6352,10 @@
       </c>
     </row>
     <row r="159" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A159" s="16">
+      <c r="A159" s="18">
         <v>137</v>
       </c>
-      <c r="B159" s="16">
+      <c r="B159" s="18">
         <v>2</v>
       </c>
       <c r="C159" s="5">
@@ -6345,10 +6363,10 @@
       </c>
     </row>
     <row r="160" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A160" s="16">
+      <c r="A160" s="18">
         <v>138</v>
       </c>
-      <c r="B160" s="16">
+      <c r="B160" s="18">
         <v>2</v>
       </c>
       <c r="C160" s="5">
@@ -6356,10 +6374,10 @@
       </c>
     </row>
     <row r="161" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A161" s="16">
+      <c r="A161" s="18">
         <v>139</v>
       </c>
-      <c r="B161" s="16">
+      <c r="B161" s="18">
         <v>2</v>
       </c>
       <c r="C161" s="5">
@@ -6367,10 +6385,10 @@
       </c>
     </row>
     <row r="162" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A162" s="16">
+      <c r="A162" s="18">
         <v>140</v>
       </c>
-      <c r="B162" s="16">
+      <c r="B162" s="18">
         <v>2</v>
       </c>
       <c r="C162" s="5">
@@ -6378,10 +6396,10 @@
       </c>
     </row>
     <row r="163" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A163" s="16">
+      <c r="A163" s="18">
         <v>141</v>
       </c>
-      <c r="B163" s="16">
+      <c r="B163" s="18">
         <v>2</v>
       </c>
       <c r="C163" s="5">
@@ -6389,10 +6407,10 @@
       </c>
     </row>
     <row r="164" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A164" s="16">
+      <c r="A164" s="18">
         <v>142</v>
       </c>
-      <c r="B164" s="16">
+      <c r="B164" s="18">
         <v>2</v>
       </c>
       <c r="C164" s="5">
@@ -6400,10 +6418,10 @@
       </c>
     </row>
     <row r="165" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A165" s="16">
+      <c r="A165" s="18">
         <v>143</v>
       </c>
-      <c r="B165" s="16">
+      <c r="B165" s="18">
         <v>2</v>
       </c>
       <c r="C165" s="5">
@@ -6411,10 +6429,10 @@
       </c>
     </row>
     <row r="166" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A166" s="16">
+      <c r="A166" s="18">
         <v>144</v>
       </c>
-      <c r="B166" s="16">
+      <c r="B166" s="18">
         <v>2</v>
       </c>
       <c r="C166" s="5">
@@ -6422,10 +6440,10 @@
       </c>
     </row>
     <row r="167" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A167" s="16">
+      <c r="A167" s="18">
         <v>145</v>
       </c>
-      <c r="B167" s="16">
+      <c r="B167" s="18">
         <v>2</v>
       </c>
       <c r="C167" s="5">
@@ -6433,10 +6451,10 @@
       </c>
     </row>
     <row r="168" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A168" s="16">
+      <c r="A168" s="18">
         <v>146</v>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="18">
         <v>2</v>
       </c>
       <c r="C168" s="5">
@@ -6444,10 +6462,10 @@
       </c>
     </row>
     <row r="169" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A169" s="16">
+      <c r="A169" s="18">
         <v>147</v>
       </c>
-      <c r="B169" s="16">
+      <c r="B169" s="18">
         <v>2</v>
       </c>
       <c r="C169" s="5">
@@ -6455,10 +6473,10 @@
       </c>
     </row>
     <row r="170" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A170" s="16">
+      <c r="A170" s="18">
         <v>148</v>
       </c>
-      <c r="B170" s="16">
+      <c r="B170" s="18">
         <v>2</v>
       </c>
       <c r="C170" s="5">
@@ -6466,10 +6484,10 @@
       </c>
     </row>
     <row r="171" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A171" s="16">
+      <c r="A171" s="18">
         <v>149</v>
       </c>
-      <c r="B171" s="16">
+      <c r="B171" s="18">
         <v>2</v>
       </c>
       <c r="C171" s="5">
@@ -6477,10 +6495,10 @@
       </c>
     </row>
     <row r="172" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A172" s="16">
+      <c r="A172" s="18">
         <v>150</v>
       </c>
-      <c r="B172" s="16">
+      <c r="B172" s="18">
         <v>2</v>
       </c>
       <c r="C172" s="5">
@@ -6488,10 +6506,10 @@
       </c>
     </row>
     <row r="173" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A173" s="16">
+      <c r="A173" s="18">
         <v>151</v>
       </c>
-      <c r="B173" s="16">
+      <c r="B173" s="18">
         <v>2</v>
       </c>
       <c r="C173" s="5">
@@ -6499,10 +6517,10 @@
       </c>
     </row>
     <row r="174" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A174" s="16">
+      <c r="A174" s="18">
         <v>152</v>
       </c>
-      <c r="B174" s="16">
+      <c r="B174" s="18">
         <v>2</v>
       </c>
       <c r="C174" s="5">
@@ -6510,10 +6528,10 @@
       </c>
     </row>
     <row r="175" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A175" s="16">
+      <c r="A175" s="18">
         <v>153</v>
       </c>
-      <c r="B175" s="16">
+      <c r="B175" s="18">
         <v>2</v>
       </c>
       <c r="C175" s="5">
@@ -6521,10 +6539,10 @@
       </c>
     </row>
     <row r="176" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A176" s="16">
+      <c r="A176" s="18">
         <v>154</v>
       </c>
-      <c r="B176" s="16">
+      <c r="B176" s="18">
         <v>2</v>
       </c>
       <c r="C176" s="5">
@@ -6532,10 +6550,10 @@
       </c>
     </row>
     <row r="177" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A177" s="16">
+      <c r="A177" s="18">
         <v>155</v>
       </c>
-      <c r="B177" s="16">
+      <c r="B177" s="18">
         <v>2</v>
       </c>
       <c r="C177" s="5">
@@ -6543,10 +6561,10 @@
       </c>
     </row>
     <row r="178" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A178" s="16">
+      <c r="A178" s="18">
         <v>156</v>
       </c>
-      <c r="B178" s="16">
+      <c r="B178" s="18">
         <v>2</v>
       </c>
       <c r="C178" s="5">
@@ -6554,10 +6572,10 @@
       </c>
     </row>
     <row r="179" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A179" s="16">
+      <c r="A179" s="18">
         <v>157</v>
       </c>
-      <c r="B179" s="16">
+      <c r="B179" s="18">
         <v>2</v>
       </c>
       <c r="C179" s="5">
@@ -6565,10 +6583,10 @@
       </c>
     </row>
     <row r="180" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A180" s="16">
+      <c r="A180" s="18">
         <v>158</v>
       </c>
-      <c r="B180" s="16">
+      <c r="B180" s="18">
         <v>2</v>
       </c>
       <c r="C180" s="5">
@@ -6576,10 +6594,10 @@
       </c>
     </row>
     <row r="181" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A181" s="16">
+      <c r="A181" s="18">
         <v>159</v>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="18">
         <v>2</v>
       </c>
       <c r="C181" s="5">
@@ -6587,10 +6605,10 @@
       </c>
     </row>
     <row r="182" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A182" s="16">
+      <c r="A182" s="18">
         <v>160</v>
       </c>
-      <c r="B182" s="16">
+      <c r="B182" s="18">
         <v>2</v>
       </c>
       <c r="C182" s="5">
@@ -6598,10 +6616,10 @@
       </c>
     </row>
     <row r="183" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A183" s="16">
+      <c r="A183" s="18">
         <v>161</v>
       </c>
-      <c r="B183" s="16">
+      <c r="B183" s="18">
         <v>2</v>
       </c>
       <c r="C183" s="5">
@@ -6609,10 +6627,10 @@
       </c>
     </row>
     <row r="184" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A184" s="16">
+      <c r="A184" s="18">
         <v>162</v>
       </c>
-      <c r="B184" s="16">
+      <c r="B184" s="18">
         <v>2</v>
       </c>
       <c r="C184" s="5">
@@ -6620,10 +6638,10 @@
       </c>
     </row>
     <row r="185" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A185" s="16">
+      <c r="A185" s="18">
         <v>163</v>
       </c>
-      <c r="B185" s="16">
+      <c r="B185" s="18">
         <v>2</v>
       </c>
       <c r="C185" s="5">
@@ -6631,10 +6649,10 @@
       </c>
     </row>
     <row r="186" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A186" s="16">
+      <c r="A186" s="18">
         <v>164</v>
       </c>
-      <c r="B186" s="16">
+      <c r="B186" s="18">
         <v>2</v>
       </c>
       <c r="C186" s="5">
@@ -6642,10 +6660,10 @@
       </c>
     </row>
     <row r="187" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A187" s="16">
+      <c r="A187" s="18">
         <v>165</v>
       </c>
-      <c r="B187" s="16">
+      <c r="B187" s="18">
         <v>2</v>
       </c>
       <c r="C187" s="5">
@@ -6653,10 +6671,10 @@
       </c>
     </row>
     <row r="188" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A188" s="16">
+      <c r="A188" s="18">
         <v>166</v>
       </c>
-      <c r="B188" s="16">
+      <c r="B188" s="18">
         <v>2</v>
       </c>
       <c r="C188" s="5">
@@ -6664,10 +6682,10 @@
       </c>
     </row>
     <row r="189" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A189" s="16">
+      <c r="A189" s="18">
         <v>167</v>
       </c>
-      <c r="B189" s="16">
+      <c r="B189" s="18">
         <v>2</v>
       </c>
       <c r="C189" s="5">
@@ -6675,10 +6693,10 @@
       </c>
     </row>
     <row r="190" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A190" s="16">
+      <c r="A190" s="18">
         <v>168</v>
       </c>
-      <c r="B190" s="16">
+      <c r="B190" s="18">
         <v>2</v>
       </c>
       <c r="C190" s="5">
@@ -6686,10 +6704,10 @@
       </c>
     </row>
     <row r="191" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A191" s="16">
+      <c r="A191" s="18">
         <v>169</v>
       </c>
-      <c r="B191" s="16">
+      <c r="B191" s="18">
         <v>2</v>
       </c>
       <c r="C191" s="5">
@@ -6697,10 +6715,10 @@
       </c>
     </row>
     <row r="192" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A192" s="16">
+      <c r="A192" s="18">
         <v>170</v>
       </c>
-      <c r="B192" s="16">
+      <c r="B192" s="18">
         <v>2</v>
       </c>
       <c r="C192" s="5">
@@ -6708,10 +6726,10 @@
       </c>
     </row>
     <row r="193" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A193" s="16">
+      <c r="A193" s="18">
         <v>171</v>
       </c>
-      <c r="B193" s="16">
+      <c r="B193" s="18">
         <v>2</v>
       </c>
       <c r="C193" s="5">
@@ -6719,10 +6737,10 @@
       </c>
     </row>
     <row r="194" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A194" s="16">
+      <c r="A194" s="18">
         <v>172</v>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="18">
         <v>2</v>
       </c>
       <c r="C194" s="5">
@@ -6730,10 +6748,10 @@
       </c>
     </row>
     <row r="195" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A195" s="16">
+      <c r="A195" s="18">
         <v>173</v>
       </c>
-      <c r="B195" s="16">
+      <c r="B195" s="18">
         <v>2</v>
       </c>
       <c r="C195" s="5">
@@ -6741,10 +6759,10 @@
       </c>
     </row>
     <row r="196" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A196" s="16">
+      <c r="A196" s="18">
         <v>174</v>
       </c>
-      <c r="B196" s="16">
+      <c r="B196" s="18">
         <v>2</v>
       </c>
       <c r="C196" s="5">
@@ -6752,10 +6770,10 @@
       </c>
     </row>
     <row r="197" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A197" s="16">
+      <c r="A197" s="18">
         <v>175</v>
       </c>
-      <c r="B197" s="16">
+      <c r="B197" s="18">
         <v>2</v>
       </c>
       <c r="C197" s="5">
@@ -6763,10 +6781,10 @@
       </c>
     </row>
     <row r="198" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A198" s="16">
+      <c r="A198" s="18">
         <v>176</v>
       </c>
-      <c r="B198" s="16">
+      <c r="B198" s="18">
         <v>2</v>
       </c>
       <c r="C198" s="5">
@@ -6774,10 +6792,10 @@
       </c>
     </row>
     <row r="199" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A199" s="16">
+      <c r="A199" s="18">
         <v>177</v>
       </c>
-      <c r="B199" s="16">
+      <c r="B199" s="18">
         <v>2</v>
       </c>
       <c r="C199" s="5">
@@ -6785,10 +6803,10 @@
       </c>
     </row>
     <row r="200" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A200" s="16">
+      <c r="A200" s="18">
         <v>178</v>
       </c>
-      <c r="B200" s="16">
+      <c r="B200" s="18">
         <v>2</v>
       </c>
       <c r="C200" s="5">
@@ -6796,10 +6814,10 @@
       </c>
     </row>
     <row r="201" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A201" s="16">
+      <c r="A201" s="18">
         <v>179</v>
       </c>
-      <c r="B201" s="16">
+      <c r="B201" s="18">
         <v>2</v>
       </c>
       <c r="C201" s="5">
@@ -6807,10 +6825,10 @@
       </c>
     </row>
     <row r="202" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A202" s="16">
+      <c r="A202" s="18">
         <v>180</v>
       </c>
-      <c r="B202" s="16">
+      <c r="B202" s="18">
         <v>2</v>
       </c>
       <c r="C202" s="5">
@@ -6818,10 +6836,10 @@
       </c>
     </row>
     <row r="203" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A203" s="16">
+      <c r="A203" s="18">
         <v>181</v>
       </c>
-      <c r="B203" s="16">
+      <c r="B203" s="18">
         <v>2</v>
       </c>
       <c r="C203" s="5">
@@ -6829,10 +6847,10 @@
       </c>
     </row>
     <row r="204" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A204" s="16">
+      <c r="A204" s="18">
         <v>182</v>
       </c>
-      <c r="B204" s="16">
+      <c r="B204" s="18">
         <v>2</v>
       </c>
       <c r="C204" s="5">
@@ -6840,10 +6858,10 @@
       </c>
     </row>
     <row r="205" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A205" s="16">
+      <c r="A205" s="18">
         <v>183</v>
       </c>
-      <c r="B205" s="16">
+      <c r="B205" s="18">
         <v>2</v>
       </c>
       <c r="C205" s="5">
@@ -6851,10 +6869,10 @@
       </c>
     </row>
     <row r="206" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A206" s="16">
+      <c r="A206" s="18">
         <v>184</v>
       </c>
-      <c r="B206" s="16">
+      <c r="B206" s="18">
         <v>2</v>
       </c>
       <c r="C206" s="5">
@@ -6862,10 +6880,10 @@
       </c>
     </row>
     <row r="207" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A207" s="16">
+      <c r="A207" s="18">
         <v>185</v>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="18">
         <v>2</v>
       </c>
       <c r="C207" s="5">
@@ -6873,10 +6891,10 @@
       </c>
     </row>
     <row r="208" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A208" s="16">
+      <c r="A208" s="18">
         <v>186</v>
       </c>
-      <c r="B208" s="16">
+      <c r="B208" s="18">
         <v>2</v>
       </c>
       <c r="C208" s="5">
@@ -6884,10 +6902,10 @@
       </c>
     </row>
     <row r="209" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A209" s="16">
+      <c r="A209" s="18">
         <v>187</v>
       </c>
-      <c r="B209" s="16">
+      <c r="B209" s="18">
         <v>2</v>
       </c>
       <c r="C209" s="5">
@@ -6895,10 +6913,10 @@
       </c>
     </row>
     <row r="210" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A210" s="16">
+      <c r="A210" s="18">
         <v>188</v>
       </c>
-      <c r="B210" s="16">
+      <c r="B210" s="18">
         <v>2</v>
       </c>
       <c r="C210" s="5">
@@ -6906,10 +6924,10 @@
       </c>
     </row>
     <row r="211" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A211" s="16">
+      <c r="A211" s="18">
         <v>189</v>
       </c>
-      <c r="B211" s="16">
+      <c r="B211" s="18">
         <v>2</v>
       </c>
       <c r="C211" s="5">
@@ -6917,10 +6935,10 @@
       </c>
     </row>
     <row r="212" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A212" s="16">
+      <c r="A212" s="18">
         <v>190</v>
       </c>
-      <c r="B212" s="16">
+      <c r="B212" s="18">
         <v>2</v>
       </c>
       <c r="C212" s="5">
@@ -6928,10 +6946,10 @@
       </c>
     </row>
     <row r="213" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A213" s="16">
+      <c r="A213" s="18">
         <v>191</v>
       </c>
-      <c r="B213" s="16">
+      <c r="B213" s="18">
         <v>2</v>
       </c>
       <c r="C213" s="5">
@@ -6939,10 +6957,10 @@
       </c>
     </row>
     <row r="214" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A214" s="16">
+      <c r="A214" s="18">
         <v>192</v>
       </c>
-      <c r="B214" s="16">
+      <c r="B214" s="18">
         <v>2</v>
       </c>
       <c r="C214" s="5">
@@ -6950,10 +6968,10 @@
       </c>
     </row>
     <row r="215" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A215" s="16">
+      <c r="A215" s="18">
         <v>193</v>
       </c>
-      <c r="B215" s="16">
+      <c r="B215" s="18">
         <v>2</v>
       </c>
       <c r="C215" s="5">
@@ -6961,10 +6979,10 @@
       </c>
     </row>
     <row r="216" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A216" s="16">
+      <c r="A216" s="18">
         <v>194</v>
       </c>
-      <c r="B216" s="16">
+      <c r="B216" s="18">
         <v>2</v>
       </c>
       <c r="C216" s="5">
@@ -6972,10 +6990,10 @@
       </c>
     </row>
     <row r="217" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A217" s="16">
+      <c r="A217" s="18">
         <v>195</v>
       </c>
-      <c r="B217" s="16">
+      <c r="B217" s="18">
         <v>2</v>
       </c>
       <c r="C217" s="5">
@@ -6983,10 +7001,10 @@
       </c>
     </row>
     <row r="218" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A218" s="16">
+      <c r="A218" s="18">
         <v>196</v>
       </c>
-      <c r="B218" s="16">
+      <c r="B218" s="18">
         <v>2</v>
       </c>
       <c r="C218" s="5">
@@ -6994,10 +7012,10 @@
       </c>
     </row>
     <row r="219" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A219" s="16">
+      <c r="A219" s="18">
         <v>197</v>
       </c>
-      <c r="B219" s="16">
+      <c r="B219" s="18">
         <v>2</v>
       </c>
       <c r="C219" s="5">
@@ -7005,10 +7023,10 @@
       </c>
     </row>
     <row r="220" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A220" s="16">
+      <c r="A220" s="18">
         <v>198</v>
       </c>
-      <c r="B220" s="16">
+      <c r="B220" s="18">
         <v>2</v>
       </c>
       <c r="C220" s="5">
@@ -7016,10 +7034,10 @@
       </c>
     </row>
     <row r="221" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A221" s="16">
+      <c r="A221" s="18">
         <v>199</v>
       </c>
-      <c r="B221" s="16">
+      <c r="B221" s="18">
         <v>2</v>
       </c>
       <c r="C221" s="5">
@@ -7027,10 +7045,10 @@
       </c>
     </row>
     <row r="222" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A222" s="16">
+      <c r="A222" s="18">
         <v>200</v>
       </c>
-      <c r="B222" s="16">
+      <c r="B222" s="18">
         <v>2</v>
       </c>
       <c r="C222" s="5">
@@ -7038,10 +7056,10 @@
       </c>
     </row>
     <row r="223" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A223" s="16">
+      <c r="A223" s="18">
         <v>201</v>
       </c>
-      <c r="B223" s="16">
+      <c r="B223" s="18">
         <v>2</v>
       </c>
       <c r="C223" s="5">
@@ -7049,10 +7067,10 @@
       </c>
     </row>
     <row r="224" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A224" s="16">
+      <c r="A224" s="18">
         <v>202</v>
       </c>
-      <c r="B224" s="16">
+      <c r="B224" s="18">
         <v>2</v>
       </c>
       <c r="C224" s="5">
@@ -7060,10 +7078,10 @@
       </c>
     </row>
     <row r="225" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A225" s="16">
+      <c r="A225" s="18">
         <v>203</v>
       </c>
-      <c r="B225" s="16">
+      <c r="B225" s="18">
         <v>2</v>
       </c>
       <c r="C225" s="5">
@@ -7071,10 +7089,10 @@
       </c>
     </row>
     <row r="226" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A226" s="16">
+      <c r="A226" s="18">
         <v>204</v>
       </c>
-      <c r="B226" s="16">
+      <c r="B226" s="18">
         <v>2</v>
       </c>
       <c r="C226" s="5">
@@ -7082,10 +7100,10 @@
       </c>
     </row>
     <row r="227" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A227" s="16">
+      <c r="A227" s="18">
         <v>205</v>
       </c>
-      <c r="B227" s="16">
+      <c r="B227" s="18">
         <v>2</v>
       </c>
       <c r="C227" s="5">
@@ -7093,10 +7111,10 @@
       </c>
     </row>
     <row r="228" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A228" s="16">
+      <c r="A228" s="18">
         <v>206</v>
       </c>
-      <c r="B228" s="16">
+      <c r="B228" s="18">
         <v>2</v>
       </c>
       <c r="C228" s="5">
@@ -7104,10 +7122,10 @@
       </c>
     </row>
     <row r="229" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A229" s="16">
+      <c r="A229" s="18">
         <v>207</v>
       </c>
-      <c r="B229" s="16">
+      <c r="B229" s="18">
         <v>2</v>
       </c>
       <c r="C229" s="5">
@@ -7115,10 +7133,10 @@
       </c>
     </row>
     <row r="230" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A230" s="16">
+      <c r="A230" s="18">
         <v>208</v>
       </c>
-      <c r="B230" s="16">
+      <c r="B230" s="18">
         <v>2</v>
       </c>
       <c r="C230" s="5">
@@ -7126,10 +7144,10 @@
       </c>
     </row>
     <row r="231" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A231" s="16">
+      <c r="A231" s="18">
         <v>209</v>
       </c>
-      <c r="B231" s="16">
+      <c r="B231" s="18">
         <v>2</v>
       </c>
       <c r="C231" s="5">
@@ -7137,10 +7155,10 @@
       </c>
     </row>
     <row r="232" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A232" s="16">
+      <c r="A232" s="18">
         <v>210</v>
       </c>
-      <c r="B232" s="16">
+      <c r="B232" s="18">
         <v>2</v>
       </c>
       <c r="C232" s="5">
@@ -7148,10 +7166,10 @@
       </c>
     </row>
     <row r="233" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A233" s="16">
+      <c r="A233" s="18">
         <v>211</v>
       </c>
-      <c r="B233" s="16">
+      <c r="B233" s="18">
         <v>2</v>
       </c>
       <c r="C233" s="5">
@@ -7159,10 +7177,10 @@
       </c>
     </row>
     <row r="234" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A234" s="16">
+      <c r="A234" s="18">
         <v>212</v>
       </c>
-      <c r="B234" s="16">
+      <c r="B234" s="18">
         <v>2</v>
       </c>
       <c r="C234" s="5">
@@ -7170,10 +7188,10 @@
       </c>
     </row>
     <row r="235" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A235" s="16">
+      <c r="A235" s="18">
         <v>213</v>
       </c>
-      <c r="B235" s="16">
+      <c r="B235" s="18">
         <v>2</v>
       </c>
       <c r="C235" s="5">
@@ -7181,10 +7199,10 @@
       </c>
     </row>
     <row r="236" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A236" s="16">
+      <c r="A236" s="18">
         <v>214</v>
       </c>
-      <c r="B236" s="16">
+      <c r="B236" s="18">
         <v>2</v>
       </c>
       <c r="C236" s="5">
@@ -7192,10 +7210,10 @@
       </c>
     </row>
     <row r="237" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A237" s="16">
+      <c r="A237" s="18">
         <v>215</v>
       </c>
-      <c r="B237" s="16">
+      <c r="B237" s="18">
         <v>2</v>
       </c>
       <c r="C237" s="5">
@@ -7203,10 +7221,10 @@
       </c>
     </row>
     <row r="238" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A238" s="16">
+      <c r="A238" s="18">
         <v>216</v>
       </c>
-      <c r="B238" s="16">
+      <c r="B238" s="18">
         <v>2</v>
       </c>
       <c r="C238" s="5">
@@ -7214,10 +7232,10 @@
       </c>
     </row>
     <row r="239" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A239" s="16">
+      <c r="A239" s="18">
         <v>217</v>
       </c>
-      <c r="B239" s="16">
+      <c r="B239" s="18">
         <v>2</v>
       </c>
       <c r="C239" s="5">
@@ -7225,10 +7243,10 @@
       </c>
     </row>
     <row r="240" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A240" s="16">
+      <c r="A240" s="18">
         <v>218</v>
       </c>
-      <c r="B240" s="16">
+      <c r="B240" s="18">
         <v>2</v>
       </c>
       <c r="C240" s="5">
@@ -7236,10 +7254,10 @@
       </c>
     </row>
     <row r="241" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A241" s="16">
+      <c r="A241" s="18">
         <v>219</v>
       </c>
-      <c r="B241" s="16">
+      <c r="B241" s="18">
         <v>2</v>
       </c>
       <c r="C241" s="5">
@@ -7247,10 +7265,10 @@
       </c>
     </row>
     <row r="242" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A242" s="16">
+      <c r="A242" s="18">
         <v>220</v>
       </c>
-      <c r="B242" s="16">
+      <c r="B242" s="18">
         <v>2</v>
       </c>
       <c r="C242" s="5">
@@ -7258,10 +7276,10 @@
       </c>
     </row>
     <row r="243" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A243" s="16">
+      <c r="A243" s="18">
         <v>221</v>
       </c>
-      <c r="B243" s="16">
+      <c r="B243" s="18">
         <v>2</v>
       </c>
       <c r="C243" s="5">
@@ -7269,10 +7287,10 @@
       </c>
     </row>
     <row r="244" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A244" s="16">
+      <c r="A244" s="18">
         <v>222</v>
       </c>
-      <c r="B244" s="16">
+      <c r="B244" s="18">
         <v>2</v>
       </c>
       <c r="C244" s="5">
@@ -7280,10 +7298,10 @@
       </c>
     </row>
     <row r="245" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A245" s="16">
+      <c r="A245" s="18">
         <v>223</v>
       </c>
-      <c r="B245" s="16">
+      <c r="B245" s="18">
         <v>2</v>
       </c>
       <c r="C245" s="5">
@@ -7291,10 +7309,10 @@
       </c>
     </row>
     <row r="246" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A246" s="16">
+      <c r="A246" s="18">
         <v>224</v>
       </c>
-      <c r="B246" s="16">
+      <c r="B246" s="18">
         <v>2</v>
       </c>
       <c r="C246" s="5">
@@ -7302,10 +7320,10 @@
       </c>
     </row>
     <row r="247" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A247" s="16">
+      <c r="A247" s="18">
         <v>225</v>
       </c>
-      <c r="B247" s="16">
+      <c r="B247" s="18">
         <v>2</v>
       </c>
       <c r="C247" s="5">
@@ -7313,10 +7331,10 @@
       </c>
     </row>
     <row r="248" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A248" s="16">
+      <c r="A248" s="18">
         <v>226</v>
       </c>
-      <c r="B248" s="16">
+      <c r="B248" s="18">
         <v>2</v>
       </c>
       <c r="C248" s="5">
@@ -7324,10 +7342,10 @@
       </c>
     </row>
     <row r="249" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A249" s="16">
+      <c r="A249" s="18">
         <v>227</v>
       </c>
-      <c r="B249" s="16">
+      <c r="B249" s="18">
         <v>2</v>
       </c>
       <c r="C249" s="5">
@@ -7335,10 +7353,10 @@
       </c>
     </row>
     <row r="250" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A250" s="16">
+      <c r="A250" s="18">
         <v>228</v>
       </c>
-      <c r="B250" s="16">
+      <c r="B250" s="18">
         <v>2</v>
       </c>
       <c r="C250" s="5">
@@ -7346,10 +7364,10 @@
       </c>
     </row>
     <row r="251" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A251" s="16">
+      <c r="A251" s="18">
         <v>229</v>
       </c>
-      <c r="B251" s="16">
+      <c r="B251" s="18">
         <v>2</v>
       </c>
       <c r="C251" s="5">
@@ -7357,10 +7375,10 @@
       </c>
     </row>
     <row r="252" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A252" s="16">
+      <c r="A252" s="18">
         <v>230</v>
       </c>
-      <c r="B252" s="16">
+      <c r="B252" s="18">
         <v>2</v>
       </c>
       <c r="C252" s="5">
@@ -7368,10 +7386,10 @@
       </c>
     </row>
     <row r="253" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A253" s="16">
+      <c r="A253" s="18">
         <v>231</v>
       </c>
-      <c r="B253" s="16">
+      <c r="B253" s="18">
         <v>2</v>
       </c>
       <c r="C253" s="5">
@@ -7379,10 +7397,10 @@
       </c>
     </row>
     <row r="254" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A254" s="16">
+      <c r="A254" s="18">
         <v>232</v>
       </c>
-      <c r="B254" s="16">
+      <c r="B254" s="18">
         <v>2</v>
       </c>
       <c r="C254" s="5">
@@ -7390,10 +7408,10 @@
       </c>
     </row>
     <row r="255" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A255" s="16">
+      <c r="A255" s="18">
         <v>233</v>
       </c>
-      <c r="B255" s="16">
+      <c r="B255" s="18">
         <v>2</v>
       </c>
       <c r="C255" s="5">
@@ -7401,10 +7419,10 @@
       </c>
     </row>
     <row r="256" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A256" s="16">
+      <c r="A256" s="18">
         <v>234</v>
       </c>
-      <c r="B256" s="16">
+      <c r="B256" s="18">
         <v>2</v>
       </c>
       <c r="C256" s="5">
@@ -7412,10 +7430,10 @@
       </c>
     </row>
     <row r="257" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A257" s="16">
+      <c r="A257" s="18">
         <v>235</v>
       </c>
-      <c r="B257" s="16">
+      <c r="B257" s="18">
         <v>2</v>
       </c>
       <c r="C257" s="5">
@@ -7423,10 +7441,10 @@
       </c>
     </row>
     <row r="258" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A258" s="16">
+      <c r="A258" s="18">
         <v>236</v>
       </c>
-      <c r="B258" s="16">
+      <c r="B258" s="18">
         <v>2</v>
       </c>
       <c r="C258" s="5">
@@ -7434,10 +7452,10 @@
       </c>
     </row>
     <row r="259" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A259" s="16">
+      <c r="A259" s="18">
         <v>237</v>
       </c>
-      <c r="B259" s="16">
+      <c r="B259" s="18">
         <v>2</v>
       </c>
       <c r="C259" s="5">
@@ -7445,10 +7463,10 @@
       </c>
     </row>
     <row r="260" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A260" s="16">
+      <c r="A260" s="18">
         <v>238</v>
       </c>
-      <c r="B260" s="16">
+      <c r="B260" s="18">
         <v>2</v>
       </c>
       <c r="C260" s="5">
@@ -7456,10 +7474,10 @@
       </c>
     </row>
     <row r="261" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A261" s="16">
+      <c r="A261" s="18">
         <v>239</v>
       </c>
-      <c r="B261" s="16">
+      <c r="B261" s="18">
         <v>2</v>
       </c>
       <c r="C261" s="5">
@@ -7467,10 +7485,10 @@
       </c>
     </row>
     <row r="262" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A262" s="16">
+      <c r="A262" s="18">
         <v>240</v>
       </c>
-      <c r="B262" s="16">
+      <c r="B262" s="18">
         <v>2</v>
       </c>
       <c r="C262" s="5">
@@ -7478,10 +7496,10 @@
       </c>
     </row>
     <row r="263" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A263" s="16">
+      <c r="A263" s="18">
         <v>241</v>
       </c>
-      <c r="B263" s="16">
+      <c r="B263" s="18">
         <v>2</v>
       </c>
       <c r="C263" s="5">
@@ -7489,10 +7507,10 @@
       </c>
     </row>
     <row r="264" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A264" s="16">
+      <c r="A264" s="18">
         <v>242</v>
       </c>
-      <c r="B264" s="16">
+      <c r="B264" s="18">
         <v>2</v>
       </c>
       <c r="C264" s="5">
@@ -7500,10 +7518,10 @@
       </c>
     </row>
     <row r="265" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A265" s="16">
+      <c r="A265" s="18">
         <v>243</v>
       </c>
-      <c r="B265" s="16">
+      <c r="B265" s="18">
         <v>2</v>
       </c>
       <c r="C265" s="5">
@@ -7511,10 +7529,10 @@
       </c>
     </row>
     <row r="266" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A266" s="16">
+      <c r="A266" s="18">
         <v>244</v>
       </c>
-      <c r="B266" s="16">
+      <c r="B266" s="18">
         <v>2</v>
       </c>
       <c r="C266" s="5">
@@ -7522,10 +7540,10 @@
       </c>
     </row>
     <row r="267" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A267" s="16">
+      <c r="A267" s="18">
         <v>245</v>
       </c>
-      <c r="B267" s="16">
+      <c r="B267" s="18">
         <v>2</v>
       </c>
       <c r="C267" s="5">
@@ -7533,10 +7551,10 @@
       </c>
     </row>
     <row r="268" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A268" s="16">
+      <c r="A268" s="18">
         <v>246</v>
       </c>
-      <c r="B268" s="16">
+      <c r="B268" s="18">
         <v>2</v>
       </c>
       <c r="C268" s="5">
@@ -7544,10 +7562,10 @@
       </c>
     </row>
     <row r="269" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A269" s="16">
+      <c r="A269" s="18">
         <v>247</v>
       </c>
-      <c r="B269" s="16">
+      <c r="B269" s="18">
         <v>2</v>
       </c>
       <c r="C269" s="5">
@@ -7555,10 +7573,10 @@
       </c>
     </row>
     <row r="270" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A270" s="16">
+      <c r="A270" s="18">
         <v>248</v>
       </c>
-      <c r="B270" s="16">
+      <c r="B270" s="18">
         <v>2</v>
       </c>
       <c r="C270" s="5">
@@ -7566,10 +7584,10 @@
       </c>
     </row>
     <row r="271" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A271" s="16">
+      <c r="A271" s="18">
         <v>249</v>
       </c>
-      <c r="B271" s="16">
+      <c r="B271" s="18">
         <v>2</v>
       </c>
       <c r="C271" s="5">
@@ -7577,10 +7595,10 @@
       </c>
     </row>
     <row r="272" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A272" s="16">
+      <c r="A272" s="18">
         <v>250</v>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="18">
         <v>2</v>
       </c>
       <c r="C272" s="5">
@@ -7588,10 +7606,10 @@
       </c>
     </row>
     <row r="273" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A273" s="16">
+      <c r="A273" s="18">
         <v>251</v>
       </c>
-      <c r="B273" s="16">
+      <c r="B273" s="18">
         <v>2</v>
       </c>
       <c r="C273" s="5">
@@ -7599,10 +7617,10 @@
       </c>
     </row>
     <row r="274" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A274" s="16">
+      <c r="A274" s="18">
         <v>252</v>
       </c>
-      <c r="B274" s="16">
+      <c r="B274" s="18">
         <v>2</v>
       </c>
       <c r="C274" s="5">
@@ -7610,10 +7628,10 @@
       </c>
     </row>
     <row r="275" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A275" s="16">
+      <c r="A275" s="18">
         <v>253</v>
       </c>
-      <c r="B275" s="16">
+      <c r="B275" s="18">
         <v>2</v>
       </c>
       <c r="C275" s="5">
@@ -7621,10 +7639,10 @@
       </c>
     </row>
     <row r="276" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A276" s="16">
+      <c r="A276" s="18">
         <v>254</v>
       </c>
-      <c r="B276" s="16">
+      <c r="B276" s="18">
         <v>2</v>
       </c>
       <c r="C276" s="5">
@@ -7632,10 +7650,10 @@
       </c>
     </row>
     <row r="277" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A277" s="16">
+      <c r="A277" s="18">
         <v>255</v>
       </c>
-      <c r="B277" s="16">
+      <c r="B277" s="18">
         <v>2</v>
       </c>
       <c r="C277" s="5">
@@ -7643,10 +7661,10 @@
       </c>
     </row>
     <row r="278" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A278" s="16">
+      <c r="A278" s="18">
         <v>256</v>
       </c>
-      <c r="B278" s="16">
+      <c r="B278" s="18">
         <v>2</v>
       </c>
       <c r="C278" s="5">
@@ -7654,10 +7672,10 @@
       </c>
     </row>
     <row r="279" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A279" s="16">
+      <c r="A279" s="18">
         <v>257</v>
       </c>
-      <c r="B279" s="16">
+      <c r="B279" s="18">
         <v>2</v>
       </c>
       <c r="C279" s="5">
@@ -7665,10 +7683,10 @@
       </c>
     </row>
     <row r="280" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A280" s="16">
+      <c r="A280" s="18">
         <v>258</v>
       </c>
-      <c r="B280" s="16">
+      <c r="B280" s="18">
         <v>2</v>
       </c>
       <c r="C280" s="5">
@@ -7676,10 +7694,10 @@
       </c>
     </row>
     <row r="281" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A281" s="16">
+      <c r="A281" s="18">
         <v>259</v>
       </c>
-      <c r="B281" s="16">
+      <c r="B281" s="18">
         <v>2</v>
       </c>
       <c r="C281" s="5">
@@ -7687,10 +7705,10 @@
       </c>
     </row>
     <row r="282" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A282" s="16">
+      <c r="A282" s="18">
         <v>260</v>
       </c>
-      <c r="B282" s="16">
+      <c r="B282" s="18">
         <v>2</v>
       </c>
       <c r="C282" s="5">
@@ -7698,10 +7716,10 @@
       </c>
     </row>
     <row r="283" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A283" s="16">
+      <c r="A283" s="18">
         <v>261</v>
       </c>
-      <c r="B283" s="16">
+      <c r="B283" s="18">
         <v>2</v>
       </c>
       <c r="C283" s="5">
@@ -7709,10 +7727,10 @@
       </c>
     </row>
     <row r="284" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A284" s="16">
+      <c r="A284" s="18">
         <v>262</v>
       </c>
-      <c r="B284" s="16">
+      <c r="B284" s="18">
         <v>2</v>
       </c>
       <c r="C284" s="5">
@@ -7720,10 +7738,10 @@
       </c>
     </row>
     <row r="285" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A285" s="16">
+      <c r="A285" s="18">
         <v>263</v>
       </c>
-      <c r="B285" s="16">
+      <c r="B285" s="18">
         <v>2</v>
       </c>
       <c r="C285" s="5">
@@ -7731,10 +7749,10 @@
       </c>
     </row>
     <row r="286" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A286" s="16">
+      <c r="A286" s="18">
         <v>264</v>
       </c>
-      <c r="B286" s="16">
+      <c r="B286" s="18">
         <v>2</v>
       </c>
       <c r="C286" s="5">
@@ -7742,10 +7760,10 @@
       </c>
     </row>
     <row r="287" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A287" s="16">
+      <c r="A287" s="18">
         <v>265</v>
       </c>
-      <c r="B287" s="16">
+      <c r="B287" s="18">
         <v>2</v>
       </c>
       <c r="C287" s="5">
@@ -7753,10 +7771,10 @@
       </c>
     </row>
     <row r="288" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A288" s="16">
+      <c r="A288" s="18">
         <v>266</v>
       </c>
-      <c r="B288" s="16">
+      <c r="B288" s="18">
         <v>2</v>
       </c>
       <c r="C288" s="5">
@@ -7764,10 +7782,10 @@
       </c>
     </row>
     <row r="289" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A289" s="16">
+      <c r="A289" s="18">
         <v>267</v>
       </c>
-      <c r="B289" s="16">
+      <c r="B289" s="18">
         <v>2</v>
       </c>
       <c r="C289" s="5">
@@ -7775,10 +7793,10 @@
       </c>
     </row>
     <row r="290" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A290" s="16">
+      <c r="A290" s="18">
         <v>268</v>
       </c>
-      <c r="B290" s="16">
+      <c r="B290" s="18">
         <v>2</v>
       </c>
       <c r="C290" s="5">
@@ -7786,10 +7804,10 @@
       </c>
     </row>
     <row r="291" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A291" s="16">
+      <c r="A291" s="18">
         <v>269</v>
       </c>
-      <c r="B291" s="16">
+      <c r="B291" s="18">
         <v>2</v>
       </c>
       <c r="C291" s="5">
@@ -7797,10 +7815,10 @@
       </c>
     </row>
     <row r="292" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A292" s="16">
+      <c r="A292" s="18">
         <v>270</v>
       </c>
-      <c r="B292" s="16">
+      <c r="B292" s="18">
         <v>2</v>
       </c>
       <c r="C292" s="5">
@@ -7808,10 +7826,10 @@
       </c>
     </row>
     <row r="293" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A293" s="16">
+      <c r="A293" s="18">
         <v>271</v>
       </c>
-      <c r="B293" s="16">
+      <c r="B293" s="18">
         <v>2</v>
       </c>
       <c r="C293" s="5">
@@ -7819,10 +7837,10 @@
       </c>
     </row>
     <row r="294" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A294" s="16">
+      <c r="A294" s="18">
         <v>272</v>
       </c>
-      <c r="B294" s="16">
+      <c r="B294" s="18">
         <v>2</v>
       </c>
       <c r="C294" s="5">
@@ -7830,10 +7848,10 @@
       </c>
     </row>
     <row r="295" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A295" s="16">
+      <c r="A295" s="18">
         <v>273</v>
       </c>
-      <c r="B295" s="16">
+      <c r="B295" s="18">
         <v>2</v>
       </c>
       <c r="C295" s="5">
@@ -7841,10 +7859,10 @@
       </c>
     </row>
     <row r="296" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A296" s="16">
+      <c r="A296" s="18">
         <v>274</v>
       </c>
-      <c r="B296" s="16">
+      <c r="B296" s="18">
         <v>2</v>
       </c>
       <c r="C296" s="5">
@@ -7852,10 +7870,10 @@
       </c>
     </row>
     <row r="297" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A297" s="16">
+      <c r="A297" s="18">
         <v>275</v>
       </c>
-      <c r="B297" s="16">
+      <c r="B297" s="18">
         <v>2</v>
       </c>
       <c r="C297" s="5">
@@ -7863,10 +7881,10 @@
       </c>
     </row>
     <row r="298" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A298" s="16">
+      <c r="A298" s="18">
         <v>276</v>
       </c>
-      <c r="B298" s="16">
+      <c r="B298" s="18">
         <v>2</v>
       </c>
       <c r="C298" s="5">
@@ -7874,10 +7892,10 @@
       </c>
     </row>
     <row r="299" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A299" s="16">
+      <c r="A299" s="18">
         <v>277</v>
       </c>
-      <c r="B299" s="16">
+      <c r="B299" s="18">
         <v>2</v>
       </c>
       <c r="C299" s="5">
@@ -7885,10 +7903,10 @@
       </c>
     </row>
     <row r="300" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A300" s="16">
+      <c r="A300" s="18">
         <v>278</v>
       </c>
-      <c r="B300" s="16">
+      <c r="B300" s="18">
         <v>2</v>
       </c>
       <c r="C300" s="5">
@@ -7896,10 +7914,10 @@
       </c>
     </row>
     <row r="301" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A301" s="16">
+      <c r="A301" s="18">
         <v>279</v>
       </c>
-      <c r="B301" s="16">
+      <c r="B301" s="18">
         <v>2</v>
       </c>
       <c r="C301" s="5">
@@ -7907,10 +7925,10 @@
       </c>
     </row>
     <row r="302" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A302" s="16">
+      <c r="A302" s="18">
         <v>280</v>
       </c>
-      <c r="B302" s="16">
+      <c r="B302" s="18">
         <v>2</v>
       </c>
       <c r="C302" s="5">
@@ -7918,10 +7936,10 @@
       </c>
     </row>
     <row r="303" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A303" s="16">
+      <c r="A303" s="18">
         <v>281</v>
       </c>
-      <c r="B303" s="16">
+      <c r="B303" s="18">
         <v>2</v>
       </c>
       <c r="C303" s="5">
@@ -7929,10 +7947,10 @@
       </c>
     </row>
     <row r="304" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A304" s="16">
+      <c r="A304" s="18">
         <v>282</v>
       </c>
-      <c r="B304" s="16">
+      <c r="B304" s="18">
         <v>2</v>
       </c>
       <c r="C304" s="5">
@@ -7940,10 +7958,10 @@
       </c>
     </row>
     <row r="305" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A305" s="16">
+      <c r="A305" s="18">
         <v>283</v>
       </c>
-      <c r="B305" s="16">
+      <c r="B305" s="18">
         <v>2</v>
       </c>
       <c r="C305" s="5">
@@ -7951,10 +7969,10 @@
       </c>
     </row>
     <row r="306" ht="15.5" spans="1:3">
-      <c r="A306" s="16">
+      <c r="A306" s="18">
         <v>284</v>
       </c>
-      <c r="B306" s="16">
+      <c r="B306" s="18">
         <v>2</v>
       </c>
       <c r="C306" s="5">
@@ -7962,10 +7980,10 @@
       </c>
     </row>
     <row r="307" ht="15.5" spans="1:3">
-      <c r="A307" s="16">
+      <c r="A307" s="18">
         <v>285</v>
       </c>
-      <c r="B307" s="16">
+      <c r="B307" s="18">
         <v>2</v>
       </c>
       <c r="C307" s="5">
@@ -7973,10 +7991,10 @@
       </c>
     </row>
     <row r="308" ht="15.5" spans="1:3">
-      <c r="A308" s="16">
+      <c r="A308" s="18">
         <v>286</v>
       </c>
-      <c r="B308" s="16">
+      <c r="B308" s="18">
         <v>2</v>
       </c>
       <c r="C308" s="5">
@@ -7984,10 +8002,10 @@
       </c>
     </row>
     <row r="309" ht="15.5" spans="1:3">
-      <c r="A309" s="16">
+      <c r="A309" s="18">
         <v>287</v>
       </c>
-      <c r="B309" s="16">
+      <c r="B309" s="18">
         <v>2</v>
       </c>
       <c r="C309" s="5">
@@ -7995,10 +8013,10 @@
       </c>
     </row>
     <row r="310" ht="15.5" spans="1:3">
-      <c r="A310" s="16">
+      <c r="A310" s="18">
         <v>288</v>
       </c>
-      <c r="B310" s="16">
+      <c r="B310" s="18">
         <v>2</v>
       </c>
       <c r="C310" s="5">
@@ -8006,10 +8024,10 @@
       </c>
     </row>
     <row r="311" ht="15.5" spans="1:3">
-      <c r="A311" s="16">
+      <c r="A311" s="18">
         <v>289</v>
       </c>
-      <c r="B311" s="16">
+      <c r="B311" s="18">
         <v>2</v>
       </c>
       <c r="C311" s="5">
@@ -8017,10 +8035,10 @@
       </c>
     </row>
     <row r="312" ht="15.5" spans="1:3">
-      <c r="A312" s="16">
+      <c r="A312" s="18">
         <v>290</v>
       </c>
-      <c r="B312" s="16">
+      <c r="B312" s="18">
         <v>2</v>
       </c>
       <c r="C312" s="5">
@@ -8028,10 +8046,10 @@
       </c>
     </row>
     <row r="313" ht="15.5" spans="1:3">
-      <c r="A313" s="16">
+      <c r="A313" s="18">
         <v>291</v>
       </c>
-      <c r="B313" s="16">
+      <c r="B313" s="18">
         <v>2</v>
       </c>
       <c r="C313" s="5">
@@ -8048,7 +8066,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J344"/>
+  <dimension ref="A1:J346"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.6333333333333" style="3" customWidth="1"/>
@@ -16018,7 +16036,7 @@
       <c r="F289" s="11"/>
       <c r="G289" s="10"/>
       <c r="H289" s="10"/>
-      <c r="I289" s="14"/>
+      <c r="I289" s="16"/>
       <c r="J289" s="6"/>
     </row>
     <row r="290" ht="20.1" customHeight="1" spans="1:10">
@@ -16678,127 +16696,129 @@
       </c>
       <c r="J313" s="6"/>
     </row>
-    <row r="314" spans="10:10">
+    <row r="314" customFormat="1" spans="1:10">
+      <c r="A314" s="5">
+        <v>1606</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C314" s="5">
+        <v>16</v>
+      </c>
+      <c r="D314" s="5">
+        <v>1606</v>
+      </c>
+      <c r="E314" s="5"/>
+      <c r="F314" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G314" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="H314" s="2"/>
+      <c r="I314" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="J314" s="6"/>
     </row>
-    <row r="315" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A315" s="5">
-        <v>2</v>
-      </c>
-      <c r="B315" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C315" s="5">
-        <v>-1</v>
-      </c>
-      <c r="D315" s="5">
-        <v>2</v>
-      </c>
-      <c r="E315" s="5"/>
-      <c r="F315" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G315" s="6"/>
-      <c r="H315" s="6"/>
-      <c r="I315" s="6" t="s">
-        <v>347</v>
+    <row r="315" customFormat="1" spans="1:10">
+      <c r="A315" s="14">
+        <v>1607</v>
+      </c>
+      <c r="B315" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="C315" s="14">
+        <v>16</v>
+      </c>
+      <c r="D315" s="14">
+        <v>1607</v>
+      </c>
+      <c r="E315" s="14"/>
+      <c r="F315" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G315" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H315" s="15"/>
+      <c r="I315" s="15" t="s">
+        <v>349</v>
       </c>
       <c r="J315" s="6"/>
     </row>
-    <row r="316" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A316" s="5">
-        <v>21</v>
-      </c>
-      <c r="B316" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C316" s="5">
-        <v>2</v>
-      </c>
-      <c r="D316" s="5">
-        <v>21</v>
-      </c>
-      <c r="E316" s="5"/>
-      <c r="F316" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G316" s="6"/>
-      <c r="H316" s="6"/>
-      <c r="I316" s="6" t="s">
-        <v>348</v>
-      </c>
+    <row r="316" spans="10:10">
       <c r="J316" s="6"/>
     </row>
     <row r="317" ht="20.1" customHeight="1" spans="1:10">
       <c r="A317" s="5">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C317" s="5">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D317" s="5">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="E317" s="5"/>
       <c r="F317" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G317" s="6" t="s">
-        <v>350</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G317" s="6"/>
       <c r="H317" s="6"/>
       <c r="I317" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J317" s="6"/>
     </row>
     <row r="318" ht="20.1" customHeight="1" spans="1:10">
       <c r="A318" s="5">
-        <v>2111</v>
+        <v>21</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C318" s="5">
+        <v>2</v>
+      </c>
+      <c r="D318" s="5">
         <v>21</v>
-      </c>
-      <c r="D318" s="5">
-        <v>2111</v>
       </c>
       <c r="E318" s="5"/>
       <c r="F318" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G318" s="6" t="s">
-        <v>352</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G318" s="6"/>
       <c r="H318" s="6"/>
       <c r="I318" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J318" s="6"/>
     </row>
     <row r="319" ht="20.1" customHeight="1" spans="1:10">
       <c r="A319" s="5">
-        <v>22</v>
+        <v>2110</v>
       </c>
       <c r="B319" s="6" t="s">
         <v>353</v>
       </c>
       <c r="C319" s="5">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D319" s="5">
-        <v>22</v>
+        <v>2110</v>
       </c>
       <c r="E319" s="5"/>
       <c r="F319" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G319" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G319" s="6" t="s">
+        <v>354</v>
+      </c>
       <c r="H319" s="6"/>
       <c r="I319" s="6" t="s">
         <v>353</v>
@@ -16807,59 +16827,57 @@
     </row>
     <row r="320" ht="20.1" customHeight="1" spans="1:10">
       <c r="A320" s="5">
-        <v>2201</v>
+        <v>2111</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C320" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D320" s="5">
-        <v>2201</v>
+        <v>2111</v>
       </c>
       <c r="E320" s="5"/>
       <c r="F320" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G320" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H320" s="6"/>
       <c r="I320" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J320" s="6"/>
     </row>
     <row r="321" ht="20.1" customHeight="1" spans="1:10">
       <c r="A321" s="5">
-        <v>2202</v>
+        <v>22</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C321" s="5">
+        <v>2</v>
+      </c>
+      <c r="D321" s="5">
         <v>22</v>
-      </c>
-      <c r="D321" s="5">
-        <v>2202</v>
       </c>
       <c r="E321" s="5"/>
       <c r="F321" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G321" s="6" t="s">
-        <v>357</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G321" s="6"/>
       <c r="H321" s="6"/>
       <c r="I321" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J321" s="6"/>
     </row>
     <row r="322" ht="20.1" customHeight="1" spans="1:10">
       <c r="A322" s="5">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B322" s="6" t="s">
         <v>358</v>
@@ -16868,7 +16886,7 @@
         <v>22</v>
       </c>
       <c r="D322" s="5">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E322" s="5"/>
       <c r="F322" s="5" t="s">
@@ -16885,22 +16903,24 @@
     </row>
     <row r="323" ht="20.1" customHeight="1" spans="1:10">
       <c r="A323" s="5">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="B323" s="6" t="s">
         <v>360</v>
       </c>
       <c r="C323" s="5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D323" s="5">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="E323" s="5"/>
       <c r="F323" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G323" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G323" s="6" t="s">
+        <v>361</v>
+      </c>
       <c r="H323" s="6"/>
       <c r="I323" s="6" t="s">
         <v>360</v>
@@ -16909,185 +16929,183 @@
     </row>
     <row r="324" ht="20.1" customHeight="1" spans="1:10">
       <c r="A324" s="5">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C324" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D324" s="5">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="E324" s="5"/>
       <c r="F324" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G324" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H324" s="6"/>
       <c r="I324" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J324" s="6"/>
     </row>
     <row r="325" ht="20.1" customHeight="1" spans="1:10">
       <c r="A325" s="5">
-        <v>2302</v>
-      </c>
-      <c r="B325" s="15" t="s">
-        <v>363</v>
+        <v>23</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>364</v>
       </c>
       <c r="C325" s="5">
+        <v>2</v>
+      </c>
+      <c r="D325" s="5">
         <v>23</v>
-      </c>
-      <c r="D325" s="5">
-        <v>2302</v>
       </c>
       <c r="E325" s="5"/>
       <c r="F325" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G325" s="15"/>
+      <c r="G325" s="6"/>
       <c r="H325" s="6"/>
       <c r="I325" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J325" s="6"/>
     </row>
     <row r="326" ht="20.1" customHeight="1" spans="1:10">
       <c r="A326" s="5">
-        <v>23021</v>
-      </c>
-      <c r="B326" s="15" t="s">
-        <v>364</v>
+        <v>2301</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>365</v>
       </c>
       <c r="C326" s="5">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D326" s="5">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="E326" s="5"/>
       <c r="F326" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G326" s="15" t="s">
-        <v>365</v>
+      <c r="G326" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="H326" s="6"/>
       <c r="I326" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J326" s="6"/>
     </row>
     <row r="327" ht="20.1" customHeight="1" spans="1:10">
       <c r="A327" s="5">
-        <v>23022</v>
-      </c>
-      <c r="B327" s="15" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B327" s="17" t="s">
         <v>367</v>
       </c>
       <c r="C327" s="5">
+        <v>23</v>
+      </c>
+      <c r="D327" s="5">
         <v>2302</v>
-      </c>
-      <c r="D327" s="5">
-        <v>23022</v>
       </c>
       <c r="E327" s="5"/>
       <c r="F327" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G327" s="15" t="s">
-        <v>368</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G327" s="17"/>
       <c r="H327" s="6"/>
       <c r="I327" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J327" s="6"/>
     </row>
     <row r="328" ht="20.1" customHeight="1" spans="1:10">
       <c r="A328" s="5">
-        <v>2303</v>
-      </c>
-      <c r="B328" s="6" t="s">
-        <v>305</v>
+        <v>23021</v>
+      </c>
+      <c r="B328" s="17" t="s">
+        <v>368</v>
       </c>
       <c r="C328" s="5">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D328" s="5">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="E328" s="5"/>
       <c r="F328" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G328" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G328" s="17" t="s">
+        <v>369</v>
+      </c>
       <c r="H328" s="6"/>
       <c r="I328" s="6" t="s">
-        <v>305</v>
+        <v>370</v>
       </c>
       <c r="J328" s="6"/>
     </row>
     <row r="329" ht="20.1" customHeight="1" spans="1:10">
       <c r="A329" s="5">
-        <v>23031</v>
-      </c>
-      <c r="B329" s="6" t="s">
-        <v>370</v>
+        <v>23022</v>
+      </c>
+      <c r="B329" s="17" t="s">
+        <v>371</v>
       </c>
       <c r="C329" s="5">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="D329" s="5">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="E329" s="5"/>
       <c r="F329" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G329" s="6" t="s">
-        <v>371</v>
+      <c r="G329" s="17" t="s">
+        <v>372</v>
       </c>
       <c r="H329" s="6"/>
       <c r="I329" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J329" s="6"/>
     </row>
     <row r="330" ht="20.1" customHeight="1" spans="1:10">
       <c r="A330" s="5">
-        <v>23032</v>
+        <v>2303</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>372</v>
+        <v>305</v>
       </c>
       <c r="C330" s="5">
+        <v>23</v>
+      </c>
+      <c r="D330" s="5">
         <v>2303</v>
-      </c>
-      <c r="D330" s="5">
-        <v>23031</v>
       </c>
       <c r="E330" s="5"/>
       <c r="F330" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G330" s="6" t="s">
-        <v>373</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G330" s="6"/>
       <c r="H330" s="6"/>
       <c r="I330" s="6" t="s">
-        <v>372</v>
+        <v>305</v>
       </c>
       <c r="J330" s="6"/>
     </row>
     <row r="331" ht="20.1" customHeight="1" spans="1:10">
       <c r="A331" s="5">
-        <v>23033</v>
+        <v>23031</v>
       </c>
       <c r="B331" s="6" t="s">
         <v>374</v>
@@ -17096,7 +17114,7 @@
         <v>2303</v>
       </c>
       <c r="D331" s="5">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="E331" s="5"/>
       <c r="F331" s="5" t="s">
@@ -17111,24 +17129,26 @@
       </c>
       <c r="J331" s="6"/>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" ht="20.1" customHeight="1" spans="1:10">
       <c r="A332" s="5">
-        <v>2304</v>
+        <v>23032</v>
       </c>
       <c r="B332" s="6" t="s">
         <v>376</v>
       </c>
       <c r="C332" s="5">
-        <v>23</v>
+        <v>2303</v>
       </c>
       <c r="D332" s="5">
-        <v>2304</v>
+        <v>23031</v>
       </c>
       <c r="E332" s="5"/>
       <c r="F332" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G332" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G332" s="6" t="s">
+        <v>377</v>
+      </c>
       <c r="H332" s="6"/>
       <c r="I332" s="6" t="s">
         <v>376</v>
@@ -17137,59 +17157,57 @@
     </row>
     <row r="333" ht="20.1" customHeight="1" spans="1:10">
       <c r="A333" s="5">
-        <v>23041</v>
+        <v>23033</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C333" s="5">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D333" s="5">
-        <v>23041</v>
+        <v>23032</v>
       </c>
       <c r="E333" s="5"/>
       <c r="F333" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G333" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H333" s="6"/>
       <c r="I333" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J333" s="6"/>
     </row>
     <row r="334" spans="1:10">
       <c r="A334" s="5">
-        <v>23042</v>
+        <v>2304</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C334" s="5">
+        <v>23</v>
+      </c>
+      <c r="D334" s="5">
         <v>2304</v>
-      </c>
-      <c r="D334" s="5">
-        <v>23042</v>
       </c>
       <c r="E334" s="5"/>
       <c r="F334" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G334" s="6" t="s">
-        <v>380</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G334" s="6"/>
       <c r="H334" s="6"/>
       <c r="I334" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J334" s="6"/>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" ht="20.1" customHeight="1" spans="1:10">
       <c r="A335" s="5">
-        <v>23043</v>
+        <v>23041</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>381</v>
@@ -17198,7 +17216,7 @@
         <v>2304</v>
       </c>
       <c r="D335" s="5">
-        <v>23043</v>
+        <v>23041</v>
       </c>
       <c r="E335" s="5"/>
       <c r="F335" s="5" t="s">
@@ -17209,72 +17227,74 @@
       </c>
       <c r="H335" s="6"/>
       <c r="I335" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="J335" s="6"/>
+    </row>
+    <row r="336" spans="1:10">
+      <c r="A336" s="5">
+        <v>23042</v>
+      </c>
+      <c r="B336" s="6" t="s">
         <v>383</v>
-      </c>
-      <c r="J335" s="6"/>
-    </row>
-    <row r="336" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A336" s="5">
-        <v>23044</v>
-      </c>
-      <c r="B336" s="6" t="s">
-        <v>384</v>
       </c>
       <c r="C336" s="5">
         <v>2304</v>
       </c>
       <c r="D336" s="5">
-        <v>23044</v>
+        <v>23042</v>
       </c>
       <c r="E336" s="5"/>
       <c r="F336" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G336" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H336" s="6"/>
       <c r="I336" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J336" s="6"/>
     </row>
     <row r="337" spans="1:10">
       <c r="A337" s="5">
-        <v>2305</v>
+        <v>23043</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C337" s="5">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D337" s="5">
-        <v>2305</v>
+        <v>23043</v>
       </c>
       <c r="E337" s="5"/>
       <c r="F337" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G337" s="5"/>
-      <c r="H337" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G337" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="H337" s="6"/>
       <c r="I337" s="6" t="s">
         <v>387</v>
       </c>
       <c r="J337" s="6"/>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" ht="20.1" customHeight="1" spans="1:10">
       <c r="A338" s="5">
-        <v>23051</v>
+        <v>23044</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>388</v>
       </c>
       <c r="C338" s="5">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D338" s="5">
-        <v>23051</v>
+        <v>23044</v>
       </c>
       <c r="E338" s="5"/>
       <c r="F338" s="5" t="s">
@@ -17283,57 +17303,57 @@
       <c r="G338" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="H338" s="5"/>
+      <c r="H338" s="6"/>
       <c r="I338" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J338" s="6"/>
     </row>
     <row r="339" spans="1:10">
       <c r="A339" s="5">
-        <v>23052</v>
+        <v>2305</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C339" s="5">
+        <v>23</v>
+      </c>
+      <c r="D339" s="5">
         <v>2305</v>
-      </c>
-      <c r="D339" s="5">
-        <v>23052</v>
       </c>
       <c r="E339" s="5"/>
       <c r="F339" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G339" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G339" s="5"/>
+      <c r="H339" s="5"/>
+      <c r="I339" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H339" s="6"/>
-      <c r="I339" s="6" t="s">
-        <v>390</v>
       </c>
       <c r="J339" s="6"/>
     </row>
     <row r="340" spans="1:10">
       <c r="A340" s="5">
-        <v>24</v>
+        <v>23051</v>
       </c>
       <c r="B340" s="6" t="s">
         <v>392</v>
       </c>
       <c r="C340" s="5">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D340" s="5">
-        <v>24</v>
+        <v>23051</v>
       </c>
       <c r="E340" s="5"/>
       <c r="F340" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G340" s="6"/>
-      <c r="H340" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G340" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="H340" s="5"/>
       <c r="I340" s="6" t="s">
         <v>392</v>
       </c>
@@ -17341,48 +17361,48 @@
     </row>
     <row r="341" spans="1:10">
       <c r="A341" s="5">
-        <v>25</v>
+        <v>23052</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C341" s="5">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D341" s="5">
-        <v>25</v>
-      </c>
-      <c r="E341" s="6"/>
+        <v>23052</v>
+      </c>
+      <c r="E341" s="5"/>
       <c r="F341" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G341" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G341" s="6" t="s">
+        <v>395</v>
+      </c>
       <c r="H341" s="6"/>
       <c r="I341" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J341" s="6"/>
     </row>
     <row r="342" spans="1:10">
       <c r="A342" s="5">
-        <v>2501</v>
+        <v>24</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C342" s="5">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D342" s="5">
-        <v>2501</v>
-      </c>
-      <c r="E342" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="E342" s="5"/>
       <c r="F342" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G342" s="6" t="s">
-        <v>395</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G342" s="6"/>
       <c r="H342" s="6"/>
       <c r="I342" s="6" t="s">
         <v>396</v>
@@ -17391,52 +17411,102 @@
     </row>
     <row r="343" spans="1:10">
       <c r="A343" s="5">
-        <v>2502</v>
+        <v>25</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>397</v>
       </c>
       <c r="C343" s="5">
+        <v>2</v>
+      </c>
+      <c r="D343" s="5">
         <v>25</v>
       </c>
-      <c r="D343" s="5">
-        <v>2502</v>
-      </c>
-      <c r="E343" s="5"/>
+      <c r="E343" s="6"/>
       <c r="F343" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G343" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="H343" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G343" s="6"/>
+      <c r="H343" s="6"/>
       <c r="I343" s="6" t="s">
         <v>397</v>
       </c>
       <c r="J343" s="6"/>
     </row>
-    <row r="344" s="2" customFormat="1" spans="1:10">
+    <row r="344" spans="1:10">
       <c r="A344" s="5">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C344" s="5">
         <v>25</v>
       </c>
       <c r="D344" s="5">
-        <v>2503</v>
-      </c>
-      <c r="E344" s="5"/>
+        <v>2501</v>
+      </c>
+      <c r="E344" s="6"/>
       <c r="F344" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G344" s="6"/>
-      <c r="I344" s="2" t="s">
+      <c r="G344" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="J344" s="2" t="b">
+      <c r="H344" s="6"/>
+      <c r="I344" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="J344" s="6"/>
+    </row>
+    <row r="345" spans="1:10">
+      <c r="A345" s="5">
+        <v>2502</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C345" s="5">
+        <v>25</v>
+      </c>
+      <c r="D345" s="5">
+        <v>2502</v>
+      </c>
+      <c r="E345" s="5"/>
+      <c r="F345" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G345" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="H345" s="5"/>
+      <c r="I345" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="J345" s="6"/>
+    </row>
+    <row r="346" s="2" customFormat="1" spans="1:10">
+      <c r="A346" s="5">
+        <v>2503</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C346" s="5">
+        <v>25</v>
+      </c>
+      <c r="D346" s="5">
+        <v>2503</v>
+      </c>
+      <c r="E346" s="5"/>
+      <c r="F346" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G346" s="6"/>
+      <c r="I346" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="J346" s="2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800" tabRatio="500" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="17655" tabRatio="500" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="406">
   <si>
     <t>Id</t>
   </si>
@@ -1221,6 +1221,12 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AodGenerateWaveFileTrainingChirpWindowViewModel</t>
+  </si>
+  <si>
+    <t>Generate Wave File Training2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AodGenerateWaveFileTrainingChirp2WindowViewModel</t>
   </si>
   <si>
     <t>Power Uniformity</t>
@@ -2042,7 +2048,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2084,12 +2090,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2568,14 +2568,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="20.6333333333333" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" ht="23.25" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2605,525 +2605,525 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="21" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="16">
         <v>666666</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="19">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="17">
         <v>1</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="E3" s="17"/>
+      <c r="F3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="17">
         <v>666666</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="17">
         <v>1</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="22" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="17">
         <v>111111</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="23"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A44" s="23"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3141,12 +3141,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3158,172 +3158,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="16">
         <v>1</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="19">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19">
-        <v>2</v>
-      </c>
-      <c r="C3" s="19">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
+        <v>2</v>
+      </c>
+      <c r="C3" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="17">
         <v>3</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3336,12 +3336,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3353,172 +3353,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="16">
         <v>1</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="19">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19">
-        <v>2</v>
-      </c>
-      <c r="C3" s="19">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
+        <v>2</v>
+      </c>
+      <c r="C3" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="17">
         <v>3</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3531,12 +3531,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:6">
+    <row r="1" ht="23.25" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3557,340 +3557,340 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="16">
         <v>-1</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="16">
         <v>0</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="16">
         <v>1</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="19">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="17">
         <v>-1</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="17">
         <v>1</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="17">
         <v>3</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="18" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>21</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="19">
-        <v>2</v>
-      </c>
-      <c r="D4" s="19">
+      <c r="C4" s="17">
+        <v>2</v>
+      </c>
+      <c r="D4" s="17">
         <v>21</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="17">
         <v>3</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>211</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="17">
         <v>21</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <v>211</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="17">
         <v>1</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>212</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="17">
         <v>21</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="17">
         <v>212</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="17">
         <v>3</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <v>22</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="19">
-        <v>2</v>
-      </c>
-      <c r="D7" s="19">
+      <c r="C7" s="17">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17">
         <v>22</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="17">
         <v>3</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <v>221</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="17">
         <v>22</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="17">
         <v>221</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="17">
         <v>3</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="17" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>222</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="17">
         <v>22</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="17">
         <v>222</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="17">
         <v>3</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3903,12 +3903,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3926,234 +3926,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="16">
         <v>0</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="16">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4166,14 +4166,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="20.6333333333333" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
     <col min="4" max="5" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4191,234 +4191,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="16">
         <v>0</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="16">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4431,12 +4431,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4448,154 +4448,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4608,12 +4608,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C313"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4625,10 +4625,10 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="16">
         <v>2</v>
       </c>
       <c r="C2" s="5">
@@ -4636,10 +4636,10 @@
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="19">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16">
         <v>2</v>
       </c>
       <c r="C3" s="5">
@@ -4647,10 +4647,10 @@
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="18">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="16">
         <v>2</v>
       </c>
       <c r="C4" s="5">
@@ -4658,10 +4658,10 @@
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="18">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="16">
         <v>2</v>
       </c>
       <c r="C5" s="5">
@@ -4669,10 +4669,10 @@
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="16">
         <v>2</v>
       </c>
       <c r="C6" s="5">
@@ -4680,10 +4680,10 @@
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="18">
+      <c r="A7" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="16">
         <v>2</v>
       </c>
       <c r="C7" s="5">
@@ -4691,10 +4691,10 @@
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="18">
+      <c r="A8" s="16">
         <v>7</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="16">
         <v>2</v>
       </c>
       <c r="C8" s="5">
@@ -4702,10 +4702,10 @@
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>8</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="16">
         <v>2</v>
       </c>
       <c r="C9" s="5">
@@ -4713,10 +4713,10 @@
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="18">
+      <c r="A10" s="16">
         <v>9</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="16">
         <v>2</v>
       </c>
       <c r="C10" s="5">
@@ -4724,10 +4724,10 @@
       </c>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="18">
+      <c r="A11" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="16">
         <v>2</v>
       </c>
       <c r="C11" s="5">
@@ -4735,10 +4735,10 @@
       </c>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="19">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="16">
         <v>2</v>
       </c>
       <c r="C12" s="5">
@@ -4746,10 +4746,10 @@
       </c>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="18">
+      <c r="A13" s="16">
         <v>12</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="16">
         <v>2</v>
       </c>
       <c r="C13" s="5">
@@ -4757,10 +4757,10 @@
       </c>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="18">
+      <c r="A14" s="16">
         <v>13</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="16">
         <v>2</v>
       </c>
       <c r="C14" s="5">
@@ -4768,10 +4768,10 @@
       </c>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="19">
+      <c r="A15" s="17">
         <v>14</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="16">
         <v>2</v>
       </c>
       <c r="C15" s="5">
@@ -4779,10 +4779,10 @@
       </c>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="18">
+      <c r="A16" s="16">
         <v>15</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="16">
         <v>2</v>
       </c>
       <c r="C16" s="5">
@@ -4790,10 +4790,10 @@
       </c>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="18">
+      <c r="A17" s="16">
         <v>16</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="16">
         <v>2</v>
       </c>
       <c r="C17" s="5">
@@ -4801,10 +4801,10 @@
       </c>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="19">
+      <c r="A18" s="17">
         <v>17</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="16">
         <v>2</v>
       </c>
       <c r="C18" s="5">
@@ -4812,10 +4812,10 @@
       </c>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="18">
+      <c r="A19" s="16">
         <v>18</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="16">
         <v>2</v>
       </c>
       <c r="C19" s="5">
@@ -4823,10 +4823,10 @@
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="18">
+      <c r="A20" s="16">
         <v>19</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="16">
         <v>2</v>
       </c>
       <c r="C20" s="5">
@@ -4834,10 +4834,10 @@
       </c>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="19">
+      <c r="A21" s="17">
         <v>20</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="16">
         <v>2</v>
       </c>
       <c r="C21" s="5">
@@ -4845,10 +4845,10 @@
       </c>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="18">
+      <c r="A22" s="16">
         <v>21</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="16">
         <v>2</v>
       </c>
       <c r="C22" s="5">
@@ -4856,10 +4856,10 @@
       </c>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="18">
+      <c r="A23" s="16">
         <v>22</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="16">
         <v>2</v>
       </c>
       <c r="C23" s="5">
@@ -4867,10 +4867,10 @@
       </c>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="19">
+      <c r="A24" s="17">
         <v>23</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="16">
         <v>2</v>
       </c>
       <c r="C24" s="5">
@@ -4878,10 +4878,10 @@
       </c>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="18">
+      <c r="A25" s="16">
         <v>24</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="16">
         <v>2</v>
       </c>
       <c r="C25" s="5">
@@ -4889,10 +4889,10 @@
       </c>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="18">
+      <c r="A26" s="16">
         <v>25</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="16">
         <v>2</v>
       </c>
       <c r="C26" s="5">
@@ -4900,10 +4900,10 @@
       </c>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="19">
+      <c r="A27" s="17">
         <v>26</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="16">
         <v>2</v>
       </c>
       <c r="C27" s="5">
@@ -4911,10 +4911,10 @@
       </c>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="18">
+      <c r="A28" s="16">
         <v>27</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="16">
         <v>2</v>
       </c>
       <c r="C28" s="5">
@@ -4922,10 +4922,10 @@
       </c>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="18">
+      <c r="A29" s="16">
         <v>28</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="16">
         <v>2</v>
       </c>
       <c r="C29" s="5">
@@ -4933,10 +4933,10 @@
       </c>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="19">
+      <c r="A30" s="17">
         <v>29</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="16">
         <v>2</v>
       </c>
       <c r="C30" s="5">
@@ -4944,10 +4944,10 @@
       </c>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="18">
+      <c r="A31" s="16">
         <v>30</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="16">
         <v>2</v>
       </c>
       <c r="C31" s="5">
@@ -4955,10 +4955,10 @@
       </c>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A32" s="18">
+      <c r="A32" s="16">
         <v>31</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="16">
         <v>2</v>
       </c>
       <c r="C32" s="5">
@@ -4966,10 +4966,10 @@
       </c>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A33" s="19">
+      <c r="A33" s="17">
         <v>32</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="16">
         <v>2</v>
       </c>
       <c r="C33" s="5">
@@ -4977,10 +4977,10 @@
       </c>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A34" s="18">
+      <c r="A34" s="16">
         <v>33</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="16">
         <v>2</v>
       </c>
       <c r="C34" s="5">
@@ -4988,10 +4988,10 @@
       </c>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A35" s="18">
+      <c r="A35" s="16">
         <v>34</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="16">
         <v>2</v>
       </c>
       <c r="C35" s="5">
@@ -4999,10 +4999,10 @@
       </c>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A36" s="19">
+      <c r="A36" s="17">
         <v>35</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="16">
         <v>2</v>
       </c>
       <c r="C36" s="5">
@@ -5010,10 +5010,10 @@
       </c>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A37" s="18">
+      <c r="A37" s="16">
         <v>36</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <v>2</v>
       </c>
       <c r="C37" s="5">
@@ -5021,10 +5021,10 @@
       </c>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A38" s="18">
+      <c r="A38" s="16">
         <v>37</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <v>2</v>
       </c>
       <c r="C38" s="5">
@@ -5032,10 +5032,10 @@
       </c>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A39" s="19">
+      <c r="A39" s="17">
         <v>38</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <v>2</v>
       </c>
       <c r="C39" s="5">
@@ -5043,10 +5043,10 @@
       </c>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A40" s="18">
+      <c r="A40" s="16">
         <v>39</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="16">
         <v>2</v>
       </c>
       <c r="C40" s="5">
@@ -5054,10 +5054,10 @@
       </c>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A41" s="18">
+      <c r="A41" s="16">
         <v>40</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="16">
         <v>2</v>
       </c>
       <c r="C41" s="5">
@@ -5065,10 +5065,10 @@
       </c>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A42" s="19">
+      <c r="A42" s="17">
         <v>41</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="16">
         <v>2</v>
       </c>
       <c r="C42" s="5">
@@ -5076,10 +5076,10 @@
       </c>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A43" s="18">
+      <c r="A43" s="16">
         <v>42</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="16">
         <v>2</v>
       </c>
       <c r="C43" s="5">
@@ -5087,10 +5087,10 @@
       </c>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A44" s="18">
+      <c r="A44" s="16">
         <v>43</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="16">
         <v>2</v>
       </c>
       <c r="C44" s="5">
@@ -5098,10 +5098,10 @@
       </c>
     </row>
     <row r="45" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A45" s="19">
+      <c r="A45" s="17">
         <v>44</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="16">
         <v>2</v>
       </c>
       <c r="C45" s="5">
@@ -5109,10 +5109,10 @@
       </c>
     </row>
     <row r="46" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A46" s="18">
+      <c r="A46" s="16">
         <v>45</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="16">
         <v>2</v>
       </c>
       <c r="C46" s="5">
@@ -5120,10 +5120,10 @@
       </c>
     </row>
     <row r="47" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A47" s="18">
+      <c r="A47" s="16">
         <v>46</v>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="16">
         <v>2</v>
       </c>
       <c r="C47" s="5">
@@ -5131,10 +5131,10 @@
       </c>
     </row>
     <row r="48" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A48" s="19">
+      <c r="A48" s="17">
         <v>47</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="16">
         <v>2</v>
       </c>
       <c r="C48" s="5">
@@ -5142,10 +5142,10 @@
       </c>
     </row>
     <row r="49" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A49" s="18">
+      <c r="A49" s="16">
         <v>48</v>
       </c>
-      <c r="B49" s="18">
+      <c r="B49" s="16">
         <v>2</v>
       </c>
       <c r="C49" s="5">
@@ -5153,10 +5153,10 @@
       </c>
     </row>
     <row r="50" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A50" s="18">
+      <c r="A50" s="16">
         <v>49</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="16">
         <v>2</v>
       </c>
       <c r="C50" s="5">
@@ -5164,10 +5164,10 @@
       </c>
     </row>
     <row r="51" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A51" s="19">
+      <c r="A51" s="17">
         <v>50</v>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="16">
         <v>2</v>
       </c>
       <c r="C51" s="5">
@@ -5175,10 +5175,10 @@
       </c>
     </row>
     <row r="52" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A52" s="18">
+      <c r="A52" s="16">
         <v>51</v>
       </c>
-      <c r="B52" s="18">
+      <c r="B52" s="16">
         <v>2</v>
       </c>
       <c r="C52" s="5">
@@ -5186,10 +5186,10 @@
       </c>
     </row>
     <row r="53" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A53" s="18">
+      <c r="A53" s="16">
         <v>52</v>
       </c>
-      <c r="B53" s="18">
+      <c r="B53" s="16">
         <v>2</v>
       </c>
       <c r="C53" s="5">
@@ -5197,10 +5197,10 @@
       </c>
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A54" s="19">
+      <c r="A54" s="17">
         <v>53</v>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="16">
         <v>2</v>
       </c>
       <c r="C54" s="5">
@@ -5208,10 +5208,10 @@
       </c>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A55" s="18">
+      <c r="A55" s="16">
         <v>54</v>
       </c>
-      <c r="B55" s="18">
+      <c r="B55" s="16">
         <v>2</v>
       </c>
       <c r="C55" s="5">
@@ -5219,10 +5219,10 @@
       </c>
     </row>
     <row r="56" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A56" s="18">
+      <c r="A56" s="16">
         <v>55</v>
       </c>
-      <c r="B56" s="18">
+      <c r="B56" s="16">
         <v>2</v>
       </c>
       <c r="C56" s="5">
@@ -5230,10 +5230,10 @@
       </c>
     </row>
     <row r="57" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A57" s="19">
+      <c r="A57" s="17">
         <v>56</v>
       </c>
-      <c r="B57" s="18">
+      <c r="B57" s="16">
         <v>2</v>
       </c>
       <c r="C57" s="5">
@@ -5241,10 +5241,10 @@
       </c>
     </row>
     <row r="58" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A58" s="18">
+      <c r="A58" s="16">
         <v>57</v>
       </c>
-      <c r="B58" s="18">
+      <c r="B58" s="16">
         <v>2</v>
       </c>
       <c r="C58" s="5">
@@ -5252,10 +5252,10 @@
       </c>
     </row>
     <row r="59" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A59" s="18">
-        <v>58</v>
-      </c>
-      <c r="B59" s="18">
+      <c r="A59" s="16">
+        <v>58</v>
+      </c>
+      <c r="B59" s="16">
         <v>2</v>
       </c>
       <c r="C59" s="5">
@@ -5263,10 +5263,10 @@
       </c>
     </row>
     <row r="60" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A60" s="18">
+      <c r="A60" s="16">
         <v>59</v>
       </c>
-      <c r="B60" s="18">
+      <c r="B60" s="16">
         <v>2</v>
       </c>
       <c r="C60" s="5">
@@ -5274,10 +5274,10 @@
       </c>
     </row>
     <row r="61" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A61" s="18">
+      <c r="A61" s="16">
         <v>60</v>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="16">
         <v>2</v>
       </c>
       <c r="C61" s="5">
@@ -5285,10 +5285,10 @@
       </c>
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A62" s="18">
+      <c r="A62" s="16">
         <v>61</v>
       </c>
-      <c r="B62" s="18">
+      <c r="B62" s="16">
         <v>2</v>
       </c>
       <c r="C62" s="5">
@@ -5296,10 +5296,10 @@
       </c>
     </row>
     <row r="63" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A63" s="18">
+      <c r="A63" s="16">
         <v>62</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="16">
         <v>2</v>
       </c>
       <c r="C63" s="5">
@@ -5307,10 +5307,10 @@
       </c>
     </row>
     <row r="64" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A64" s="18">
+      <c r="A64" s="16">
         <v>63</v>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="16">
         <v>2</v>
       </c>
       <c r="C64" s="5">
@@ -5318,10 +5318,10 @@
       </c>
     </row>
     <row r="65" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A65" s="18">
+      <c r="A65" s="16">
         <v>64</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="16">
         <v>2</v>
       </c>
       <c r="C65" s="5">
@@ -5329,10 +5329,10 @@
       </c>
     </row>
     <row r="66" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A66" s="18">
+      <c r="A66" s="16">
         <v>65</v>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="16">
         <v>2</v>
       </c>
       <c r="C66" s="5">
@@ -5340,10 +5340,10 @@
       </c>
     </row>
     <row r="67" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A67" s="18">
+      <c r="A67" s="16">
         <v>66</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="16">
         <v>2</v>
       </c>
       <c r="C67" s="5">
@@ -5351,10 +5351,10 @@
       </c>
     </row>
     <row r="68" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A68" s="18">
+      <c r="A68" s="16">
         <v>67</v>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="16">
         <v>2</v>
       </c>
       <c r="C68" s="5">
@@ -5362,10 +5362,10 @@
       </c>
     </row>
     <row r="69" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A69" s="18">
+      <c r="A69" s="16">
         <v>68</v>
       </c>
-      <c r="B69" s="18">
+      <c r="B69" s="16">
         <v>2</v>
       </c>
       <c r="C69" s="5">
@@ -5373,10 +5373,10 @@
       </c>
     </row>
     <row r="70" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A70" s="18">
+      <c r="A70" s="16">
         <v>69</v>
       </c>
-      <c r="B70" s="18">
+      <c r="B70" s="16">
         <v>2</v>
       </c>
       <c r="C70" s="5">
@@ -5384,10 +5384,10 @@
       </c>
     </row>
     <row r="71" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A71" s="18">
+      <c r="A71" s="16">
         <v>70</v>
       </c>
-      <c r="B71" s="18">
+      <c r="B71" s="16">
         <v>2</v>
       </c>
       <c r="C71" s="5">
@@ -5395,10 +5395,10 @@
       </c>
     </row>
     <row r="72" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A72" s="18">
+      <c r="A72" s="16">
         <v>71</v>
       </c>
-      <c r="B72" s="18">
+      <c r="B72" s="16">
         <v>2</v>
       </c>
       <c r="C72" s="5">
@@ -5406,10 +5406,10 @@
       </c>
     </row>
     <row r="73" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A73" s="18">
+      <c r="A73" s="16">
         <v>72</v>
       </c>
-      <c r="B73" s="18">
+      <c r="B73" s="16">
         <v>2</v>
       </c>
       <c r="C73" s="5">
@@ -5417,10 +5417,10 @@
       </c>
     </row>
     <row r="74" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A74" s="18">
+      <c r="A74" s="16">
         <v>73</v>
       </c>
-      <c r="B74" s="18">
+      <c r="B74" s="16">
         <v>2</v>
       </c>
       <c r="C74" s="5">
@@ -5428,10 +5428,10 @@
       </c>
     </row>
     <row r="75" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A75" s="18">
+      <c r="A75" s="16">
         <v>74</v>
       </c>
-      <c r="B75" s="18">
+      <c r="B75" s="16">
         <v>2</v>
       </c>
       <c r="C75" s="5">
@@ -5439,10 +5439,10 @@
       </c>
     </row>
     <row r="76" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A76" s="18">
+      <c r="A76" s="16">
         <v>75</v>
       </c>
-      <c r="B76" s="18">
+      <c r="B76" s="16">
         <v>2</v>
       </c>
       <c r="C76" s="5">
@@ -5450,10 +5450,10 @@
       </c>
     </row>
     <row r="77" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A77" s="18">
+      <c r="A77" s="16">
         <v>76</v>
       </c>
-      <c r="B77" s="18">
+      <c r="B77" s="16">
         <v>2</v>
       </c>
       <c r="C77" s="5">
@@ -5461,10 +5461,10 @@
       </c>
     </row>
     <row r="78" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A78" s="18">
+      <c r="A78" s="16">
         <v>77</v>
       </c>
-      <c r="B78" s="18">
+      <c r="B78" s="16">
         <v>2</v>
       </c>
       <c r="C78" s="5">
@@ -5472,10 +5472,10 @@
       </c>
     </row>
     <row r="79" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A79" s="18">
+      <c r="A79" s="16">
         <v>78</v>
       </c>
-      <c r="B79" s="18">
+      <c r="B79" s="16">
         <v>2</v>
       </c>
       <c r="C79" s="5">
@@ -5483,10 +5483,10 @@
       </c>
     </row>
     <row r="80" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A80" s="18">
+      <c r="A80" s="16">
         <v>79</v>
       </c>
-      <c r="B80" s="18">
+      <c r="B80" s="16">
         <v>2</v>
       </c>
       <c r="C80" s="5">
@@ -5494,10 +5494,10 @@
       </c>
     </row>
     <row r="81" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A81" s="18">
+      <c r="A81" s="16">
         <v>80</v>
       </c>
-      <c r="B81" s="18">
+      <c r="B81" s="16">
         <v>2</v>
       </c>
       <c r="C81" s="5">
@@ -5505,10 +5505,10 @@
       </c>
     </row>
     <row r="82" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A82" s="18">
+      <c r="A82" s="16">
         <v>81</v>
       </c>
-      <c r="B82" s="18">
+      <c r="B82" s="16">
         <v>2</v>
       </c>
       <c r="C82" s="5">
@@ -5516,10 +5516,10 @@
       </c>
     </row>
     <row r="83" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A83" s="18">
+      <c r="A83" s="16">
         <v>82</v>
       </c>
-      <c r="B83" s="18">
+      <c r="B83" s="16">
         <v>2</v>
       </c>
       <c r="C83" s="5">
@@ -5527,10 +5527,10 @@
       </c>
     </row>
     <row r="84" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A84" s="18">
+      <c r="A84" s="16">
         <v>83</v>
       </c>
-      <c r="B84" s="18">
+      <c r="B84" s="16">
         <v>2</v>
       </c>
       <c r="C84" s="5">
@@ -5538,10 +5538,10 @@
       </c>
     </row>
     <row r="85" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A85" s="18">
+      <c r="A85" s="16">
         <v>84</v>
       </c>
-      <c r="B85" s="18">
+      <c r="B85" s="16">
         <v>2</v>
       </c>
       <c r="C85" s="5">
@@ -5549,10 +5549,10 @@
       </c>
     </row>
     <row r="86" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A86" s="18">
+      <c r="A86" s="16">
         <v>85</v>
       </c>
-      <c r="B86" s="18">
+      <c r="B86" s="16">
         <v>2</v>
       </c>
       <c r="C86" s="5">
@@ -5560,10 +5560,10 @@
       </c>
     </row>
     <row r="87" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A87" s="18">
+      <c r="A87" s="16">
         <v>86</v>
       </c>
-      <c r="B87" s="18">
+      <c r="B87" s="16">
         <v>2</v>
       </c>
       <c r="C87" s="5">
@@ -5571,10 +5571,10 @@
       </c>
     </row>
     <row r="88" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A88" s="18">
+      <c r="A88" s="16">
         <v>87</v>
       </c>
-      <c r="B88" s="18">
+      <c r="B88" s="16">
         <v>2</v>
       </c>
       <c r="C88" s="5">
@@ -5582,10 +5582,10 @@
       </c>
     </row>
     <row r="89" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A89" s="18">
+      <c r="A89" s="16">
         <v>88</v>
       </c>
-      <c r="B89" s="18">
+      <c r="B89" s="16">
         <v>2</v>
       </c>
       <c r="C89" s="5">
@@ -5593,10 +5593,10 @@
       </c>
     </row>
     <row r="90" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A90" s="18">
+      <c r="A90" s="16">
         <v>89</v>
       </c>
-      <c r="B90" s="18">
+      <c r="B90" s="16">
         <v>2</v>
       </c>
       <c r="C90" s="5">
@@ -5604,10 +5604,10 @@
       </c>
     </row>
     <row r="91" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A91" s="18">
+      <c r="A91" s="16">
         <v>90</v>
       </c>
-      <c r="B91" s="18">
+      <c r="B91" s="16">
         <v>2</v>
       </c>
       <c r="C91" s="5">
@@ -5615,10 +5615,10 @@
       </c>
     </row>
     <row r="92" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A92" s="18">
+      <c r="A92" s="16">
         <v>91</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="16">
         <v>2</v>
       </c>
       <c r="C92" s="5">
@@ -5626,10 +5626,10 @@
       </c>
     </row>
     <row r="93" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A93" s="18">
+      <c r="A93" s="16">
         <v>92</v>
       </c>
-      <c r="B93" s="18">
+      <c r="B93" s="16">
         <v>2</v>
       </c>
       <c r="C93" s="5">
@@ -5637,10 +5637,10 @@
       </c>
     </row>
     <row r="94" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A94" s="18">
+      <c r="A94" s="16">
         <v>93</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="16">
         <v>2</v>
       </c>
       <c r="C94" s="5">
@@ -5648,10 +5648,10 @@
       </c>
     </row>
     <row r="95" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A95" s="18">
+      <c r="A95" s="16">
         <v>94</v>
       </c>
-      <c r="B95" s="18">
+      <c r="B95" s="16">
         <v>2</v>
       </c>
       <c r="C95" s="5">
@@ -5659,10 +5659,10 @@
       </c>
     </row>
     <row r="96" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A96" s="18">
+      <c r="A96" s="16">
         <v>95</v>
       </c>
-      <c r="B96" s="18">
+      <c r="B96" s="16">
         <v>2</v>
       </c>
       <c r="C96" s="5">
@@ -5670,10 +5670,10 @@
       </c>
     </row>
     <row r="97" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A97" s="18">
+      <c r="A97" s="16">
         <v>96</v>
       </c>
-      <c r="B97" s="18">
+      <c r="B97" s="16">
         <v>2</v>
       </c>
       <c r="C97" s="5">
@@ -5681,10 +5681,10 @@
       </c>
     </row>
     <row r="98" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A98" s="18">
+      <c r="A98" s="16">
         <v>97</v>
       </c>
-      <c r="B98" s="18">
+      <c r="B98" s="16">
         <v>2</v>
       </c>
       <c r="C98" s="5">
@@ -5692,10 +5692,10 @@
       </c>
     </row>
     <row r="99" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A99" s="18">
+      <c r="A99" s="16">
         <v>98</v>
       </c>
-      <c r="B99" s="18">
+      <c r="B99" s="16">
         <v>2</v>
       </c>
       <c r="C99" s="5">
@@ -5703,10 +5703,10 @@
       </c>
     </row>
     <row r="100" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A100" s="18">
+      <c r="A100" s="16">
         <v>99</v>
       </c>
-      <c r="B100" s="18">
+      <c r="B100" s="16">
         <v>2</v>
       </c>
       <c r="C100" s="5">
@@ -5714,10 +5714,10 @@
       </c>
     </row>
     <row r="101" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A101" s="18">
+      <c r="A101" s="16">
         <v>100</v>
       </c>
-      <c r="B101" s="18">
+      <c r="B101" s="16">
         <v>2</v>
       </c>
       <c r="C101" s="5">
@@ -5725,10 +5725,10 @@
       </c>
     </row>
     <row r="102" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A102" s="18">
+      <c r="A102" s="16">
         <v>101</v>
       </c>
-      <c r="B102" s="18">
+      <c r="B102" s="16">
         <v>2</v>
       </c>
       <c r="C102" s="5">
@@ -5736,10 +5736,10 @@
       </c>
     </row>
     <row r="103" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A103" s="18">
+      <c r="A103" s="16">
         <v>102</v>
       </c>
-      <c r="B103" s="18">
+      <c r="B103" s="16">
         <v>2</v>
       </c>
       <c r="C103" s="5">
@@ -5747,10 +5747,10 @@
       </c>
     </row>
     <row r="104" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A104" s="18">
+      <c r="A104" s="16">
         <v>103</v>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" s="16">
         <v>2</v>
       </c>
       <c r="C104" s="5">
@@ -5758,10 +5758,10 @@
       </c>
     </row>
     <row r="105" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A105" s="18">
+      <c r="A105" s="16">
         <v>104</v>
       </c>
-      <c r="B105" s="18">
+      <c r="B105" s="16">
         <v>2</v>
       </c>
       <c r="C105" s="5">
@@ -5769,10 +5769,10 @@
       </c>
     </row>
     <row r="106" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A106" s="18">
+      <c r="A106" s="16">
         <v>105</v>
       </c>
-      <c r="B106" s="18">
+      <c r="B106" s="16">
         <v>2</v>
       </c>
       <c r="C106" s="5">
@@ -5780,10 +5780,10 @@
       </c>
     </row>
     <row r="107" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A107" s="18">
+      <c r="A107" s="16">
         <v>106</v>
       </c>
-      <c r="B107" s="18">
+      <c r="B107" s="16">
         <v>2</v>
       </c>
       <c r="C107" s="5">
@@ -5791,10 +5791,10 @@
       </c>
     </row>
     <row r="108" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A108" s="18">
+      <c r="A108" s="16">
         <v>107</v>
       </c>
-      <c r="B108" s="18">
+      <c r="B108" s="16">
         <v>2</v>
       </c>
       <c r="C108" s="5">
@@ -5802,10 +5802,10 @@
       </c>
     </row>
     <row r="109" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A109" s="18">
+      <c r="A109" s="16">
         <v>108</v>
       </c>
-      <c r="B109" s="18">
+      <c r="B109" s="16">
         <v>2</v>
       </c>
       <c r="C109" s="5">
@@ -5813,10 +5813,10 @@
       </c>
     </row>
     <row r="110" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A110" s="18">
+      <c r="A110" s="16">
         <v>109</v>
       </c>
-      <c r="B110" s="18">
+      <c r="B110" s="16">
         <v>2</v>
       </c>
       <c r="C110" s="5">
@@ -5824,10 +5824,10 @@
       </c>
     </row>
     <row r="111" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A111" s="18">
+      <c r="A111" s="16">
         <v>110</v>
       </c>
-      <c r="B111" s="18">
+      <c r="B111" s="16">
         <v>2</v>
       </c>
       <c r="C111" s="5">
@@ -5835,10 +5835,10 @@
       </c>
     </row>
     <row r="112" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A112" s="18">
+      <c r="A112" s="16">
         <v>111</v>
       </c>
-      <c r="B112" s="18">
+      <c r="B112" s="16">
         <v>2</v>
       </c>
       <c r="C112" s="5">
@@ -5846,10 +5846,10 @@
       </c>
     </row>
     <row r="113" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A113" s="18">
+      <c r="A113" s="16">
         <v>112</v>
       </c>
-      <c r="B113" s="18">
+      <c r="B113" s="16">
         <v>2</v>
       </c>
       <c r="C113" s="5">
@@ -5857,10 +5857,10 @@
       </c>
     </row>
     <row r="114" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A114" s="18">
+      <c r="A114" s="16">
         <v>113</v>
       </c>
-      <c r="B114" s="18">
+      <c r="B114" s="16">
         <v>2</v>
       </c>
       <c r="C114" s="5">
@@ -5868,10 +5868,10 @@
       </c>
     </row>
     <row r="115" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A115" s="18">
+      <c r="A115" s="16">
         <v>114</v>
       </c>
-      <c r="B115" s="18">
+      <c r="B115" s="16">
         <v>2</v>
       </c>
       <c r="C115" s="5">
@@ -5879,10 +5879,10 @@
       </c>
     </row>
     <row r="116" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A116" s="18">
+      <c r="A116" s="16">
         <v>115</v>
       </c>
-      <c r="B116" s="18">
+      <c r="B116" s="16">
         <v>2</v>
       </c>
       <c r="C116" s="5">
@@ -5890,10 +5890,10 @@
       </c>
     </row>
     <row r="117" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A117" s="18">
+      <c r="A117" s="16">
         <v>116</v>
       </c>
-      <c r="B117" s="18">
+      <c r="B117" s="16">
         <v>2</v>
       </c>
       <c r="C117" s="5">
@@ -5901,10 +5901,10 @@
       </c>
     </row>
     <row r="118" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A118" s="18">
+      <c r="A118" s="16">
         <v>117</v>
       </c>
-      <c r="B118" s="18">
+      <c r="B118" s="16">
         <v>2</v>
       </c>
       <c r="C118" s="5">
@@ -5912,10 +5912,10 @@
       </c>
     </row>
     <row r="119" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A119" s="18">
+      <c r="A119" s="16">
         <v>118</v>
       </c>
-      <c r="B119" s="18">
+      <c r="B119" s="16">
         <v>2</v>
       </c>
       <c r="C119" s="5">
@@ -5923,10 +5923,10 @@
       </c>
     </row>
     <row r="120" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A120" s="18">
+      <c r="A120" s="16">
         <v>119</v>
       </c>
-      <c r="B120" s="18">
+      <c r="B120" s="16">
         <v>2</v>
       </c>
       <c r="C120" s="5">
@@ -5934,10 +5934,10 @@
       </c>
     </row>
     <row r="121" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A121" s="18">
+      <c r="A121" s="16">
         <v>120</v>
       </c>
-      <c r="B121" s="18">
+      <c r="B121" s="16">
         <v>2</v>
       </c>
       <c r="C121" s="5">
@@ -5945,10 +5945,10 @@
       </c>
     </row>
     <row r="122" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A122" s="18">
+      <c r="A122" s="16">
         <v>121</v>
       </c>
-      <c r="B122" s="18">
+      <c r="B122" s="16">
         <v>2</v>
       </c>
       <c r="C122" s="5">
@@ -5956,10 +5956,10 @@
       </c>
     </row>
     <row r="123" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A123" s="18">
+      <c r="A123" s="16">
         <v>122</v>
       </c>
-      <c r="B123" s="18">
+      <c r="B123" s="16">
         <v>2</v>
       </c>
       <c r="C123" s="5">
@@ -5967,10 +5967,10 @@
       </c>
     </row>
     <row r="124" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A124" s="18">
+      <c r="A124" s="16">
         <v>123</v>
       </c>
-      <c r="B124" s="18">
+      <c r="B124" s="16">
         <v>2</v>
       </c>
       <c r="C124" s="5">
@@ -5978,10 +5978,10 @@
       </c>
     </row>
     <row r="125" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A125" s="18">
+      <c r="A125" s="16">
         <v>124</v>
       </c>
-      <c r="B125" s="18">
+      <c r="B125" s="16">
         <v>2</v>
       </c>
       <c r="C125" s="5">
@@ -5989,10 +5989,10 @@
       </c>
     </row>
     <row r="126" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A126" s="18">
+      <c r="A126" s="16">
         <v>125</v>
       </c>
-      <c r="B126" s="18">
+      <c r="B126" s="16">
         <v>2</v>
       </c>
       <c r="C126" s="5">
@@ -6000,10 +6000,10 @@
       </c>
     </row>
     <row r="127" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A127" s="18">
+      <c r="A127" s="16">
         <v>126</v>
       </c>
-      <c r="B127" s="18">
+      <c r="B127" s="16">
         <v>2</v>
       </c>
       <c r="C127" s="5">
@@ -6011,10 +6011,10 @@
       </c>
     </row>
     <row r="128" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A128" s="18">
+      <c r="A128" s="16">
         <v>127</v>
       </c>
-      <c r="B128" s="18">
+      <c r="B128" s="16">
         <v>2</v>
       </c>
       <c r="C128" s="5">
@@ -6022,10 +6022,10 @@
       </c>
     </row>
     <row r="129" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A129" s="18">
+      <c r="A129" s="16">
         <v>128</v>
       </c>
-      <c r="B129" s="18">
+      <c r="B129" s="16">
         <v>2</v>
       </c>
       <c r="C129" s="5">
@@ -6033,10 +6033,10 @@
       </c>
     </row>
     <row r="130" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A130" s="18">
+      <c r="A130" s="16">
         <v>129</v>
       </c>
-      <c r="B130" s="18">
+      <c r="B130" s="16">
         <v>2</v>
       </c>
       <c r="C130" s="5">
@@ -6044,10 +6044,10 @@
       </c>
     </row>
     <row r="131" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A131" s="18">
+      <c r="A131" s="16">
         <v>130</v>
       </c>
-      <c r="B131" s="18">
+      <c r="B131" s="16">
         <v>2</v>
       </c>
       <c r="C131" s="5">
@@ -6055,10 +6055,10 @@
       </c>
     </row>
     <row r="132" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A132" s="18">
+      <c r="A132" s="16">
         <v>131</v>
       </c>
-      <c r="B132" s="18">
+      <c r="B132" s="16">
         <v>2</v>
       </c>
       <c r="C132" s="5">
@@ -6066,10 +6066,10 @@
       </c>
     </row>
     <row r="133" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A133" s="18">
+      <c r="A133" s="16">
         <v>132</v>
       </c>
-      <c r="B133" s="18">
+      <c r="B133" s="16">
         <v>2</v>
       </c>
       <c r="C133" s="5">
@@ -6077,10 +6077,10 @@
       </c>
     </row>
     <row r="134" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A134" s="18">
+      <c r="A134" s="16">
         <v>133</v>
       </c>
-      <c r="B134" s="18">
+      <c r="B134" s="16">
         <v>2</v>
       </c>
       <c r="C134" s="5">
@@ -6088,10 +6088,10 @@
       </c>
     </row>
     <row r="135" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A135" s="18">
+      <c r="A135" s="16">
         <v>134</v>
       </c>
-      <c r="B135" s="18">
+      <c r="B135" s="16">
         <v>2</v>
       </c>
       <c r="C135" s="5">
@@ -6099,10 +6099,10 @@
       </c>
     </row>
     <row r="136" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A136" s="18">
+      <c r="A136" s="16">
         <v>135</v>
       </c>
-      <c r="B136" s="18">
+      <c r="B136" s="16">
         <v>2</v>
       </c>
       <c r="C136" s="5">
@@ -6110,10 +6110,10 @@
       </c>
     </row>
     <row r="137" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A137" s="18">
+      <c r="A137" s="16">
         <v>136</v>
       </c>
-      <c r="B137" s="18">
+      <c r="B137" s="16">
         <v>2</v>
       </c>
       <c r="C137" s="5">
@@ -6121,10 +6121,10 @@
       </c>
     </row>
     <row r="138" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A138" s="18">
+      <c r="A138" s="16">
         <v>137</v>
       </c>
-      <c r="B138" s="18">
+      <c r="B138" s="16">
         <v>2</v>
       </c>
       <c r="C138" s="5">
@@ -6132,10 +6132,10 @@
       </c>
     </row>
     <row r="139" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A139" s="18">
+      <c r="A139" s="16">
         <v>138</v>
       </c>
-      <c r="B139" s="18">
+      <c r="B139" s="16">
         <v>2</v>
       </c>
       <c r="C139" s="5">
@@ -6143,10 +6143,10 @@
       </c>
     </row>
     <row r="140" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A140" s="18">
+      <c r="A140" s="16">
         <v>139</v>
       </c>
-      <c r="B140" s="18">
+      <c r="B140" s="16">
         <v>2</v>
       </c>
       <c r="C140" s="5">
@@ -6154,10 +6154,10 @@
       </c>
     </row>
     <row r="141" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A141" s="18">
+      <c r="A141" s="16">
         <v>140</v>
       </c>
-      <c r="B141" s="18">
+      <c r="B141" s="16">
         <v>2</v>
       </c>
       <c r="C141" s="5">
@@ -6165,10 +6165,10 @@
       </c>
     </row>
     <row r="142" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A142" s="18">
+      <c r="A142" s="16">
         <v>141</v>
       </c>
-      <c r="B142" s="18">
+      <c r="B142" s="16">
         <v>2</v>
       </c>
       <c r="C142" s="5">
@@ -6176,10 +6176,10 @@
       </c>
     </row>
     <row r="143" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A143" s="18">
+      <c r="A143" s="16">
         <v>142</v>
       </c>
-      <c r="B143" s="18">
+      <c r="B143" s="16">
         <v>2</v>
       </c>
       <c r="C143" s="5">
@@ -6187,10 +6187,10 @@
       </c>
     </row>
     <row r="144" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A144" s="18">
+      <c r="A144" s="16">
         <v>122</v>
       </c>
-      <c r="B144" s="18">
+      <c r="B144" s="16">
         <v>2</v>
       </c>
       <c r="C144" s="5">
@@ -6198,10 +6198,10 @@
       </c>
     </row>
     <row r="145" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A145" s="18">
+      <c r="A145" s="16">
         <v>123</v>
       </c>
-      <c r="B145" s="18">
+      <c r="B145" s="16">
         <v>2</v>
       </c>
       <c r="C145" s="5">
@@ -6209,10 +6209,10 @@
       </c>
     </row>
     <row r="146" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A146" s="18">
+      <c r="A146" s="16">
         <v>124</v>
       </c>
-      <c r="B146" s="18">
+      <c r="B146" s="16">
         <v>2</v>
       </c>
       <c r="C146" s="5">
@@ -6220,10 +6220,10 @@
       </c>
     </row>
     <row r="147" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A147" s="18">
+      <c r="A147" s="16">
         <v>125</v>
       </c>
-      <c r="B147" s="18">
+      <c r="B147" s="16">
         <v>2</v>
       </c>
       <c r="C147" s="5">
@@ -6231,10 +6231,10 @@
       </c>
     </row>
     <row r="148" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A148" s="18">
+      <c r="A148" s="16">
         <v>126</v>
       </c>
-      <c r="B148" s="18">
+      <c r="B148" s="16">
         <v>2</v>
       </c>
       <c r="C148" s="5">
@@ -6242,10 +6242,10 @@
       </c>
     </row>
     <row r="149" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A149" s="18">
+      <c r="A149" s="16">
         <v>127</v>
       </c>
-      <c r="B149" s="18">
+      <c r="B149" s="16">
         <v>2</v>
       </c>
       <c r="C149" s="5">
@@ -6253,10 +6253,10 @@
       </c>
     </row>
     <row r="150" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A150" s="18">
+      <c r="A150" s="16">
         <v>128</v>
       </c>
-      <c r="B150" s="18">
+      <c r="B150" s="16">
         <v>2</v>
       </c>
       <c r="C150" s="5">
@@ -6264,10 +6264,10 @@
       </c>
     </row>
     <row r="151" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A151" s="18">
+      <c r="A151" s="16">
         <v>129</v>
       </c>
-      <c r="B151" s="18">
+      <c r="B151" s="16">
         <v>2</v>
       </c>
       <c r="C151" s="5">
@@ -6275,10 +6275,10 @@
       </c>
     </row>
     <row r="152" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A152" s="18">
+      <c r="A152" s="16">
         <v>130</v>
       </c>
-      <c r="B152" s="18">
+      <c r="B152" s="16">
         <v>2</v>
       </c>
       <c r="C152" s="5">
@@ -6286,10 +6286,10 @@
       </c>
     </row>
     <row r="153" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A153" s="18">
+      <c r="A153" s="16">
         <v>131</v>
       </c>
-      <c r="B153" s="18">
+      <c r="B153" s="16">
         <v>2</v>
       </c>
       <c r="C153" s="5">
@@ -6297,10 +6297,10 @@
       </c>
     </row>
     <row r="154" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A154" s="18">
+      <c r="A154" s="16">
         <v>132</v>
       </c>
-      <c r="B154" s="18">
+      <c r="B154" s="16">
         <v>2</v>
       </c>
       <c r="C154" s="5">
@@ -6308,10 +6308,10 @@
       </c>
     </row>
     <row r="155" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A155" s="18">
+      <c r="A155" s="16">
         <v>133</v>
       </c>
-      <c r="B155" s="18">
+      <c r="B155" s="16">
         <v>2</v>
       </c>
       <c r="C155" s="5">
@@ -6319,10 +6319,10 @@
       </c>
     </row>
     <row r="156" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A156" s="18">
+      <c r="A156" s="16">
         <v>134</v>
       </c>
-      <c r="B156" s="18">
+      <c r="B156" s="16">
         <v>2</v>
       </c>
       <c r="C156" s="5">
@@ -6330,10 +6330,10 @@
       </c>
     </row>
     <row r="157" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A157" s="18">
+      <c r="A157" s="16">
         <v>135</v>
       </c>
-      <c r="B157" s="18">
+      <c r="B157" s="16">
         <v>2</v>
       </c>
       <c r="C157" s="5">
@@ -6341,10 +6341,10 @@
       </c>
     </row>
     <row r="158" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A158" s="18">
+      <c r="A158" s="16">
         <v>136</v>
       </c>
-      <c r="B158" s="18">
+      <c r="B158" s="16">
         <v>2</v>
       </c>
       <c r="C158" s="5">
@@ -6352,10 +6352,10 @@
       </c>
     </row>
     <row r="159" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A159" s="18">
+      <c r="A159" s="16">
         <v>137</v>
       </c>
-      <c r="B159" s="18">
+      <c r="B159" s="16">
         <v>2</v>
       </c>
       <c r="C159" s="5">
@@ -6363,10 +6363,10 @@
       </c>
     </row>
     <row r="160" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A160" s="18">
+      <c r="A160" s="16">
         <v>138</v>
       </c>
-      <c r="B160" s="18">
+      <c r="B160" s="16">
         <v>2</v>
       </c>
       <c r="C160" s="5">
@@ -6374,10 +6374,10 @@
       </c>
     </row>
     <row r="161" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A161" s="18">
+      <c r="A161" s="16">
         <v>139</v>
       </c>
-      <c r="B161" s="18">
+      <c r="B161" s="16">
         <v>2</v>
       </c>
       <c r="C161" s="5">
@@ -6385,10 +6385,10 @@
       </c>
     </row>
     <row r="162" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A162" s="18">
+      <c r="A162" s="16">
         <v>140</v>
       </c>
-      <c r="B162" s="18">
+      <c r="B162" s="16">
         <v>2</v>
       </c>
       <c r="C162" s="5">
@@ -6396,10 +6396,10 @@
       </c>
     </row>
     <row r="163" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A163" s="18">
+      <c r="A163" s="16">
         <v>141</v>
       </c>
-      <c r="B163" s="18">
+      <c r="B163" s="16">
         <v>2</v>
       </c>
       <c r="C163" s="5">
@@ -6407,10 +6407,10 @@
       </c>
     </row>
     <row r="164" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A164" s="18">
+      <c r="A164" s="16">
         <v>142</v>
       </c>
-      <c r="B164" s="18">
+      <c r="B164" s="16">
         <v>2</v>
       </c>
       <c r="C164" s="5">
@@ -6418,10 +6418,10 @@
       </c>
     </row>
     <row r="165" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A165" s="18">
+      <c r="A165" s="16">
         <v>143</v>
       </c>
-      <c r="B165" s="18">
+      <c r="B165" s="16">
         <v>2</v>
       </c>
       <c r="C165" s="5">
@@ -6429,10 +6429,10 @@
       </c>
     </row>
     <row r="166" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A166" s="18">
+      <c r="A166" s="16">
         <v>144</v>
       </c>
-      <c r="B166" s="18">
+      <c r="B166" s="16">
         <v>2</v>
       </c>
       <c r="C166" s="5">
@@ -6440,10 +6440,10 @@
       </c>
     </row>
     <row r="167" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A167" s="18">
+      <c r="A167" s="16">
         <v>145</v>
       </c>
-      <c r="B167" s="18">
+      <c r="B167" s="16">
         <v>2</v>
       </c>
       <c r="C167" s="5">
@@ -6451,10 +6451,10 @@
       </c>
     </row>
     <row r="168" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A168" s="18">
+      <c r="A168" s="16">
         <v>146</v>
       </c>
-      <c r="B168" s="18">
+      <c r="B168" s="16">
         <v>2</v>
       </c>
       <c r="C168" s="5">
@@ -6462,10 +6462,10 @@
       </c>
     </row>
     <row r="169" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A169" s="18">
+      <c r="A169" s="16">
         <v>147</v>
       </c>
-      <c r="B169" s="18">
+      <c r="B169" s="16">
         <v>2</v>
       </c>
       <c r="C169" s="5">
@@ -6473,10 +6473,10 @@
       </c>
     </row>
     <row r="170" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A170" s="18">
+      <c r="A170" s="16">
         <v>148</v>
       </c>
-      <c r="B170" s="18">
+      <c r="B170" s="16">
         <v>2</v>
       </c>
       <c r="C170" s="5">
@@ -6484,10 +6484,10 @@
       </c>
     </row>
     <row r="171" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A171" s="18">
+      <c r="A171" s="16">
         <v>149</v>
       </c>
-      <c r="B171" s="18">
+      <c r="B171" s="16">
         <v>2</v>
       </c>
       <c r="C171" s="5">
@@ -6495,10 +6495,10 @@
       </c>
     </row>
     <row r="172" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A172" s="18">
+      <c r="A172" s="16">
         <v>150</v>
       </c>
-      <c r="B172" s="18">
+      <c r="B172" s="16">
         <v>2</v>
       </c>
       <c r="C172" s="5">
@@ -6506,10 +6506,10 @@
       </c>
     </row>
     <row r="173" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A173" s="18">
+      <c r="A173" s="16">
         <v>151</v>
       </c>
-      <c r="B173" s="18">
+      <c r="B173" s="16">
         <v>2</v>
       </c>
       <c r="C173" s="5">
@@ -6517,10 +6517,10 @@
       </c>
     </row>
     <row r="174" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A174" s="18">
+      <c r="A174" s="16">
         <v>152</v>
       </c>
-      <c r="B174" s="18">
+      <c r="B174" s="16">
         <v>2</v>
       </c>
       <c r="C174" s="5">
@@ -6528,10 +6528,10 @@
       </c>
     </row>
     <row r="175" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A175" s="18">
+      <c r="A175" s="16">
         <v>153</v>
       </c>
-      <c r="B175" s="18">
+      <c r="B175" s="16">
         <v>2</v>
       </c>
       <c r="C175" s="5">
@@ -6539,10 +6539,10 @@
       </c>
     </row>
     <row r="176" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A176" s="18">
+      <c r="A176" s="16">
         <v>154</v>
       </c>
-      <c r="B176" s="18">
+      <c r="B176" s="16">
         <v>2</v>
       </c>
       <c r="C176" s="5">
@@ -6550,10 +6550,10 @@
       </c>
     </row>
     <row r="177" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A177" s="18">
+      <c r="A177" s="16">
         <v>155</v>
       </c>
-      <c r="B177" s="18">
+      <c r="B177" s="16">
         <v>2</v>
       </c>
       <c r="C177" s="5">
@@ -6561,10 +6561,10 @@
       </c>
     </row>
     <row r="178" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A178" s="18">
+      <c r="A178" s="16">
         <v>156</v>
       </c>
-      <c r="B178" s="18">
+      <c r="B178" s="16">
         <v>2</v>
       </c>
       <c r="C178" s="5">
@@ -6572,10 +6572,10 @@
       </c>
     </row>
     <row r="179" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A179" s="18">
+      <c r="A179" s="16">
         <v>157</v>
       </c>
-      <c r="B179" s="18">
+      <c r="B179" s="16">
         <v>2</v>
       </c>
       <c r="C179" s="5">
@@ -6583,10 +6583,10 @@
       </c>
     </row>
     <row r="180" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A180" s="18">
+      <c r="A180" s="16">
         <v>158</v>
       </c>
-      <c r="B180" s="18">
+      <c r="B180" s="16">
         <v>2</v>
       </c>
       <c r="C180" s="5">
@@ -6594,10 +6594,10 @@
       </c>
     </row>
     <row r="181" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A181" s="18">
+      <c r="A181" s="16">
         <v>159</v>
       </c>
-      <c r="B181" s="18">
+      <c r="B181" s="16">
         <v>2</v>
       </c>
       <c r="C181" s="5">
@@ -6605,10 +6605,10 @@
       </c>
     </row>
     <row r="182" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A182" s="18">
+      <c r="A182" s="16">
         <v>160</v>
       </c>
-      <c r="B182" s="18">
+      <c r="B182" s="16">
         <v>2</v>
       </c>
       <c r="C182" s="5">
@@ -6616,10 +6616,10 @@
       </c>
     </row>
     <row r="183" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A183" s="18">
+      <c r="A183" s="16">
         <v>161</v>
       </c>
-      <c r="B183" s="18">
+      <c r="B183" s="16">
         <v>2</v>
       </c>
       <c r="C183" s="5">
@@ -6627,10 +6627,10 @@
       </c>
     </row>
     <row r="184" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A184" s="18">
+      <c r="A184" s="16">
         <v>162</v>
       </c>
-      <c r="B184" s="18">
+      <c r="B184" s="16">
         <v>2</v>
       </c>
       <c r="C184" s="5">
@@ -6638,10 +6638,10 @@
       </c>
     </row>
     <row r="185" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A185" s="18">
+      <c r="A185" s="16">
         <v>163</v>
       </c>
-      <c r="B185" s="18">
+      <c r="B185" s="16">
         <v>2</v>
       </c>
       <c r="C185" s="5">
@@ -6649,10 +6649,10 @@
       </c>
     </row>
     <row r="186" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A186" s="18">
+      <c r="A186" s="16">
         <v>164</v>
       </c>
-      <c r="B186" s="18">
+      <c r="B186" s="16">
         <v>2</v>
       </c>
       <c r="C186" s="5">
@@ -6660,10 +6660,10 @@
       </c>
     </row>
     <row r="187" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A187" s="18">
+      <c r="A187" s="16">
         <v>165</v>
       </c>
-      <c r="B187" s="18">
+      <c r="B187" s="16">
         <v>2</v>
       </c>
       <c r="C187" s="5">
@@ -6671,10 +6671,10 @@
       </c>
     </row>
     <row r="188" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A188" s="18">
+      <c r="A188" s="16">
         <v>166</v>
       </c>
-      <c r="B188" s="18">
+      <c r="B188" s="16">
         <v>2</v>
       </c>
       <c r="C188" s="5">
@@ -6682,10 +6682,10 @@
       </c>
     </row>
     <row r="189" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A189" s="18">
+      <c r="A189" s="16">
         <v>167</v>
       </c>
-      <c r="B189" s="18">
+      <c r="B189" s="16">
         <v>2</v>
       </c>
       <c r="C189" s="5">
@@ -6693,10 +6693,10 @@
       </c>
     </row>
     <row r="190" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A190" s="18">
+      <c r="A190" s="16">
         <v>168</v>
       </c>
-      <c r="B190" s="18">
+      <c r="B190" s="16">
         <v>2</v>
       </c>
       <c r="C190" s="5">
@@ -6704,10 +6704,10 @@
       </c>
     </row>
     <row r="191" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A191" s="18">
+      <c r="A191" s="16">
         <v>169</v>
       </c>
-      <c r="B191" s="18">
+      <c r="B191" s="16">
         <v>2</v>
       </c>
       <c r="C191" s="5">
@@ -6715,10 +6715,10 @@
       </c>
     </row>
     <row r="192" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A192" s="18">
+      <c r="A192" s="16">
         <v>170</v>
       </c>
-      <c r="B192" s="18">
+      <c r="B192" s="16">
         <v>2</v>
       </c>
       <c r="C192" s="5">
@@ -6726,10 +6726,10 @@
       </c>
     </row>
     <row r="193" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A193" s="18">
+      <c r="A193" s="16">
         <v>171</v>
       </c>
-      <c r="B193" s="18">
+      <c r="B193" s="16">
         <v>2</v>
       </c>
       <c r="C193" s="5">
@@ -6737,10 +6737,10 @@
       </c>
     </row>
     <row r="194" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A194" s="18">
+      <c r="A194" s="16">
         <v>172</v>
       </c>
-      <c r="B194" s="18">
+      <c r="B194" s="16">
         <v>2</v>
       </c>
       <c r="C194" s="5">
@@ -6748,10 +6748,10 @@
       </c>
     </row>
     <row r="195" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A195" s="18">
+      <c r="A195" s="16">
         <v>173</v>
       </c>
-      <c r="B195" s="18">
+      <c r="B195" s="16">
         <v>2</v>
       </c>
       <c r="C195" s="5">
@@ -6759,10 +6759,10 @@
       </c>
     </row>
     <row r="196" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A196" s="18">
+      <c r="A196" s="16">
         <v>174</v>
       </c>
-      <c r="B196" s="18">
+      <c r="B196" s="16">
         <v>2</v>
       </c>
       <c r="C196" s="5">
@@ -6770,10 +6770,10 @@
       </c>
     </row>
     <row r="197" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A197" s="18">
+      <c r="A197" s="16">
         <v>175</v>
       </c>
-      <c r="B197" s="18">
+      <c r="B197" s="16">
         <v>2</v>
       </c>
       <c r="C197" s="5">
@@ -6781,10 +6781,10 @@
       </c>
     </row>
     <row r="198" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A198" s="18">
+      <c r="A198" s="16">
         <v>176</v>
       </c>
-      <c r="B198" s="18">
+      <c r="B198" s="16">
         <v>2</v>
       </c>
       <c r="C198" s="5">
@@ -6792,10 +6792,10 @@
       </c>
     </row>
     <row r="199" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A199" s="18">
+      <c r="A199" s="16">
         <v>177</v>
       </c>
-      <c r="B199" s="18">
+      <c r="B199" s="16">
         <v>2</v>
       </c>
       <c r="C199" s="5">
@@ -6803,10 +6803,10 @@
       </c>
     </row>
     <row r="200" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A200" s="18">
+      <c r="A200" s="16">
         <v>178</v>
       </c>
-      <c r="B200" s="18">
+      <c r="B200" s="16">
         <v>2</v>
       </c>
       <c r="C200" s="5">
@@ -6814,10 +6814,10 @@
       </c>
     </row>
     <row r="201" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A201" s="18">
+      <c r="A201" s="16">
         <v>179</v>
       </c>
-      <c r="B201" s="18">
+      <c r="B201" s="16">
         <v>2</v>
       </c>
       <c r="C201" s="5">
@@ -6825,10 +6825,10 @@
       </c>
     </row>
     <row r="202" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A202" s="18">
+      <c r="A202" s="16">
         <v>180</v>
       </c>
-      <c r="B202" s="18">
+      <c r="B202" s="16">
         <v>2</v>
       </c>
       <c r="C202" s="5">
@@ -6836,10 +6836,10 @@
       </c>
     </row>
     <row r="203" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A203" s="18">
+      <c r="A203" s="16">
         <v>181</v>
       </c>
-      <c r="B203" s="18">
+      <c r="B203" s="16">
         <v>2</v>
       </c>
       <c r="C203" s="5">
@@ -6847,10 +6847,10 @@
       </c>
     </row>
     <row r="204" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A204" s="18">
+      <c r="A204" s="16">
         <v>182</v>
       </c>
-      <c r="B204" s="18">
+      <c r="B204" s="16">
         <v>2</v>
       </c>
       <c r="C204" s="5">
@@ -6858,10 +6858,10 @@
       </c>
     </row>
     <row r="205" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A205" s="18">
+      <c r="A205" s="16">
         <v>183</v>
       </c>
-      <c r="B205" s="18">
+      <c r="B205" s="16">
         <v>2</v>
       </c>
       <c r="C205" s="5">
@@ -6869,10 +6869,10 @@
       </c>
     </row>
     <row r="206" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A206" s="18">
+      <c r="A206" s="16">
         <v>184</v>
       </c>
-      <c r="B206" s="18">
+      <c r="B206" s="16">
         <v>2</v>
       </c>
       <c r="C206" s="5">
@@ -6880,10 +6880,10 @@
       </c>
     </row>
     <row r="207" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A207" s="18">
+      <c r="A207" s="16">
         <v>185</v>
       </c>
-      <c r="B207" s="18">
+      <c r="B207" s="16">
         <v>2</v>
       </c>
       <c r="C207" s="5">
@@ -6891,10 +6891,10 @@
       </c>
     </row>
     <row r="208" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A208" s="18">
+      <c r="A208" s="16">
         <v>186</v>
       </c>
-      <c r="B208" s="18">
+      <c r="B208" s="16">
         <v>2</v>
       </c>
       <c r="C208" s="5">
@@ -6902,10 +6902,10 @@
       </c>
     </row>
     <row r="209" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A209" s="18">
+      <c r="A209" s="16">
         <v>187</v>
       </c>
-      <c r="B209" s="18">
+      <c r="B209" s="16">
         <v>2</v>
       </c>
       <c r="C209" s="5">
@@ -6913,10 +6913,10 @@
       </c>
     </row>
     <row r="210" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A210" s="18">
+      <c r="A210" s="16">
         <v>188</v>
       </c>
-      <c r="B210" s="18">
+      <c r="B210" s="16">
         <v>2</v>
       </c>
       <c r="C210" s="5">
@@ -6924,10 +6924,10 @@
       </c>
     </row>
     <row r="211" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A211" s="18">
+      <c r="A211" s="16">
         <v>189</v>
       </c>
-      <c r="B211" s="18">
+      <c r="B211" s="16">
         <v>2</v>
       </c>
       <c r="C211" s="5">
@@ -6935,10 +6935,10 @@
       </c>
     </row>
     <row r="212" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A212" s="18">
+      <c r="A212" s="16">
         <v>190</v>
       </c>
-      <c r="B212" s="18">
+      <c r="B212" s="16">
         <v>2</v>
       </c>
       <c r="C212" s="5">
@@ -6946,10 +6946,10 @@
       </c>
     </row>
     <row r="213" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A213" s="18">
+      <c r="A213" s="16">
         <v>191</v>
       </c>
-      <c r="B213" s="18">
+      <c r="B213" s="16">
         <v>2</v>
       </c>
       <c r="C213" s="5">
@@ -6957,10 +6957,10 @@
       </c>
     </row>
     <row r="214" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A214" s="18">
+      <c r="A214" s="16">
         <v>192</v>
       </c>
-      <c r="B214" s="18">
+      <c r="B214" s="16">
         <v>2</v>
       </c>
       <c r="C214" s="5">
@@ -6968,10 +6968,10 @@
       </c>
     </row>
     <row r="215" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A215" s="18">
+      <c r="A215" s="16">
         <v>193</v>
       </c>
-      <c r="B215" s="18">
+      <c r="B215" s="16">
         <v>2</v>
       </c>
       <c r="C215" s="5">
@@ -6979,10 +6979,10 @@
       </c>
     </row>
     <row r="216" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A216" s="18">
+      <c r="A216" s="16">
         <v>194</v>
       </c>
-      <c r="B216" s="18">
+      <c r="B216" s="16">
         <v>2</v>
       </c>
       <c r="C216" s="5">
@@ -6990,10 +6990,10 @@
       </c>
     </row>
     <row r="217" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A217" s="18">
+      <c r="A217" s="16">
         <v>195</v>
       </c>
-      <c r="B217" s="18">
+      <c r="B217" s="16">
         <v>2</v>
       </c>
       <c r="C217" s="5">
@@ -7001,10 +7001,10 @@
       </c>
     </row>
     <row r="218" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A218" s="18">
+      <c r="A218" s="16">
         <v>196</v>
       </c>
-      <c r="B218" s="18">
+      <c r="B218" s="16">
         <v>2</v>
       </c>
       <c r="C218" s="5">
@@ -7012,10 +7012,10 @@
       </c>
     </row>
     <row r="219" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A219" s="18">
+      <c r="A219" s="16">
         <v>197</v>
       </c>
-      <c r="B219" s="18">
+      <c r="B219" s="16">
         <v>2</v>
       </c>
       <c r="C219" s="5">
@@ -7023,10 +7023,10 @@
       </c>
     </row>
     <row r="220" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A220" s="18">
+      <c r="A220" s="16">
         <v>198</v>
       </c>
-      <c r="B220" s="18">
+      <c r="B220" s="16">
         <v>2</v>
       </c>
       <c r="C220" s="5">
@@ -7034,10 +7034,10 @@
       </c>
     </row>
     <row r="221" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A221" s="18">
+      <c r="A221" s="16">
         <v>199</v>
       </c>
-      <c r="B221" s="18">
+      <c r="B221" s="16">
         <v>2</v>
       </c>
       <c r="C221" s="5">
@@ -7045,10 +7045,10 @@
       </c>
     </row>
     <row r="222" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A222" s="18">
+      <c r="A222" s="16">
         <v>200</v>
       </c>
-      <c r="B222" s="18">
+      <c r="B222" s="16">
         <v>2</v>
       </c>
       <c r="C222" s="5">
@@ -7056,10 +7056,10 @@
       </c>
     </row>
     <row r="223" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A223" s="18">
+      <c r="A223" s="16">
         <v>201</v>
       </c>
-      <c r="B223" s="18">
+      <c r="B223" s="16">
         <v>2</v>
       </c>
       <c r="C223" s="5">
@@ -7067,10 +7067,10 @@
       </c>
     </row>
     <row r="224" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A224" s="18">
+      <c r="A224" s="16">
         <v>202</v>
       </c>
-      <c r="B224" s="18">
+      <c r="B224" s="16">
         <v>2</v>
       </c>
       <c r="C224" s="5">
@@ -7078,10 +7078,10 @@
       </c>
     </row>
     <row r="225" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A225" s="18">
+      <c r="A225" s="16">
         <v>203</v>
       </c>
-      <c r="B225" s="18">
+      <c r="B225" s="16">
         <v>2</v>
       </c>
       <c r="C225" s="5">
@@ -7089,10 +7089,10 @@
       </c>
     </row>
     <row r="226" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A226" s="18">
+      <c r="A226" s="16">
         <v>204</v>
       </c>
-      <c r="B226" s="18">
+      <c r="B226" s="16">
         <v>2</v>
       </c>
       <c r="C226" s="5">
@@ -7100,10 +7100,10 @@
       </c>
     </row>
     <row r="227" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A227" s="18">
+      <c r="A227" s="16">
         <v>205</v>
       </c>
-      <c r="B227" s="18">
+      <c r="B227" s="16">
         <v>2</v>
       </c>
       <c r="C227" s="5">
@@ -7111,10 +7111,10 @@
       </c>
     </row>
     <row r="228" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A228" s="18">
+      <c r="A228" s="16">
         <v>206</v>
       </c>
-      <c r="B228" s="18">
+      <c r="B228" s="16">
         <v>2</v>
       </c>
       <c r="C228" s="5">
@@ -7122,10 +7122,10 @@
       </c>
     </row>
     <row r="229" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A229" s="18">
+      <c r="A229" s="16">
         <v>207</v>
       </c>
-      <c r="B229" s="18">
+      <c r="B229" s="16">
         <v>2</v>
       </c>
       <c r="C229" s="5">
@@ -7133,10 +7133,10 @@
       </c>
     </row>
     <row r="230" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A230" s="18">
+      <c r="A230" s="16">
         <v>208</v>
       </c>
-      <c r="B230" s="18">
+      <c r="B230" s="16">
         <v>2</v>
       </c>
       <c r="C230" s="5">
@@ -7144,10 +7144,10 @@
       </c>
     </row>
     <row r="231" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A231" s="18">
+      <c r="A231" s="16">
         <v>209</v>
       </c>
-      <c r="B231" s="18">
+      <c r="B231" s="16">
         <v>2</v>
       </c>
       <c r="C231" s="5">
@@ -7155,10 +7155,10 @@
       </c>
     </row>
     <row r="232" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A232" s="18">
+      <c r="A232" s="16">
         <v>210</v>
       </c>
-      <c r="B232" s="18">
+      <c r="B232" s="16">
         <v>2</v>
       </c>
       <c r="C232" s="5">
@@ -7166,10 +7166,10 @@
       </c>
     </row>
     <row r="233" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A233" s="18">
+      <c r="A233" s="16">
         <v>211</v>
       </c>
-      <c r="B233" s="18">
+      <c r="B233" s="16">
         <v>2</v>
       </c>
       <c r="C233" s="5">
@@ -7177,10 +7177,10 @@
       </c>
     </row>
     <row r="234" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A234" s="18">
+      <c r="A234" s="16">
         <v>212</v>
       </c>
-      <c r="B234" s="18">
+      <c r="B234" s="16">
         <v>2</v>
       </c>
       <c r="C234" s="5">
@@ -7188,10 +7188,10 @@
       </c>
     </row>
     <row r="235" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A235" s="18">
+      <c r="A235" s="16">
         <v>213</v>
       </c>
-      <c r="B235" s="18">
+      <c r="B235" s="16">
         <v>2</v>
       </c>
       <c r="C235" s="5">
@@ -7199,10 +7199,10 @@
       </c>
     </row>
     <row r="236" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A236" s="18">
+      <c r="A236" s="16">
         <v>214</v>
       </c>
-      <c r="B236" s="18">
+      <c r="B236" s="16">
         <v>2</v>
       </c>
       <c r="C236" s="5">
@@ -7210,10 +7210,10 @@
       </c>
     </row>
     <row r="237" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A237" s="18">
+      <c r="A237" s="16">
         <v>215</v>
       </c>
-      <c r="B237" s="18">
+      <c r="B237" s="16">
         <v>2</v>
       </c>
       <c r="C237" s="5">
@@ -7221,10 +7221,10 @@
       </c>
     </row>
     <row r="238" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A238" s="18">
+      <c r="A238" s="16">
         <v>216</v>
       </c>
-      <c r="B238" s="18">
+      <c r="B238" s="16">
         <v>2</v>
       </c>
       <c r="C238" s="5">
@@ -7232,10 +7232,10 @@
       </c>
     </row>
     <row r="239" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A239" s="18">
+      <c r="A239" s="16">
         <v>217</v>
       </c>
-      <c r="B239" s="18">
+      <c r="B239" s="16">
         <v>2</v>
       </c>
       <c r="C239" s="5">
@@ -7243,10 +7243,10 @@
       </c>
     </row>
     <row r="240" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A240" s="18">
+      <c r="A240" s="16">
         <v>218</v>
       </c>
-      <c r="B240" s="18">
+      <c r="B240" s="16">
         <v>2</v>
       </c>
       <c r="C240" s="5">
@@ -7254,10 +7254,10 @@
       </c>
     </row>
     <row r="241" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A241" s="18">
+      <c r="A241" s="16">
         <v>219</v>
       </c>
-      <c r="B241" s="18">
+      <c r="B241" s="16">
         <v>2</v>
       </c>
       <c r="C241" s="5">
@@ -7265,10 +7265,10 @@
       </c>
     </row>
     <row r="242" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A242" s="18">
+      <c r="A242" s="16">
         <v>220</v>
       </c>
-      <c r="B242" s="18">
+      <c r="B242" s="16">
         <v>2</v>
       </c>
       <c r="C242" s="5">
@@ -7276,10 +7276,10 @@
       </c>
     </row>
     <row r="243" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A243" s="18">
+      <c r="A243" s="16">
         <v>221</v>
       </c>
-      <c r="B243" s="18">
+      <c r="B243" s="16">
         <v>2</v>
       </c>
       <c r="C243" s="5">
@@ -7287,10 +7287,10 @@
       </c>
     </row>
     <row r="244" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A244" s="18">
+      <c r="A244" s="16">
         <v>222</v>
       </c>
-      <c r="B244" s="18">
+      <c r="B244" s="16">
         <v>2</v>
       </c>
       <c r="C244" s="5">
@@ -7298,10 +7298,10 @@
       </c>
     </row>
     <row r="245" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A245" s="18">
+      <c r="A245" s="16">
         <v>223</v>
       </c>
-      <c r="B245" s="18">
+      <c r="B245" s="16">
         <v>2</v>
       </c>
       <c r="C245" s="5">
@@ -7309,10 +7309,10 @@
       </c>
     </row>
     <row r="246" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A246" s="18">
+      <c r="A246" s="16">
         <v>224</v>
       </c>
-      <c r="B246" s="18">
+      <c r="B246" s="16">
         <v>2</v>
       </c>
       <c r="C246" s="5">
@@ -7320,10 +7320,10 @@
       </c>
     </row>
     <row r="247" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A247" s="18">
+      <c r="A247" s="16">
         <v>225</v>
       </c>
-      <c r="B247" s="18">
+      <c r="B247" s="16">
         <v>2</v>
       </c>
       <c r="C247" s="5">
@@ -7331,10 +7331,10 @@
       </c>
     </row>
     <row r="248" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A248" s="18">
+      <c r="A248" s="16">
         <v>226</v>
       </c>
-      <c r="B248" s="18">
+      <c r="B248" s="16">
         <v>2</v>
       </c>
       <c r="C248" s="5">
@@ -7342,10 +7342,10 @@
       </c>
     </row>
     <row r="249" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A249" s="18">
+      <c r="A249" s="16">
         <v>227</v>
       </c>
-      <c r="B249" s="18">
+      <c r="B249" s="16">
         <v>2</v>
       </c>
       <c r="C249" s="5">
@@ -7353,10 +7353,10 @@
       </c>
     </row>
     <row r="250" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A250" s="18">
+      <c r="A250" s="16">
         <v>228</v>
       </c>
-      <c r="B250" s="18">
+      <c r="B250" s="16">
         <v>2</v>
       </c>
       <c r="C250" s="5">
@@ -7364,10 +7364,10 @@
       </c>
     </row>
     <row r="251" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A251" s="18">
+      <c r="A251" s="16">
         <v>229</v>
       </c>
-      <c r="B251" s="18">
+      <c r="B251" s="16">
         <v>2</v>
       </c>
       <c r="C251" s="5">
@@ -7375,10 +7375,10 @@
       </c>
     </row>
     <row r="252" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A252" s="18">
+      <c r="A252" s="16">
         <v>230</v>
       </c>
-      <c r="B252" s="18">
+      <c r="B252" s="16">
         <v>2</v>
       </c>
       <c r="C252" s="5">
@@ -7386,10 +7386,10 @@
       </c>
     </row>
     <row r="253" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A253" s="18">
+      <c r="A253" s="16">
         <v>231</v>
       </c>
-      <c r="B253" s="18">
+      <c r="B253" s="16">
         <v>2</v>
       </c>
       <c r="C253" s="5">
@@ -7397,10 +7397,10 @@
       </c>
     </row>
     <row r="254" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A254" s="18">
+      <c r="A254" s="16">
         <v>232</v>
       </c>
-      <c r="B254" s="18">
+      <c r="B254" s="16">
         <v>2</v>
       </c>
       <c r="C254" s="5">
@@ -7408,10 +7408,10 @@
       </c>
     </row>
     <row r="255" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A255" s="18">
+      <c r="A255" s="16">
         <v>233</v>
       </c>
-      <c r="B255" s="18">
+      <c r="B255" s="16">
         <v>2</v>
       </c>
       <c r="C255" s="5">
@@ -7419,10 +7419,10 @@
       </c>
     </row>
     <row r="256" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A256" s="18">
+      <c r="A256" s="16">
         <v>234</v>
       </c>
-      <c r="B256" s="18">
+      <c r="B256" s="16">
         <v>2</v>
       </c>
       <c r="C256" s="5">
@@ -7430,10 +7430,10 @@
       </c>
     </row>
     <row r="257" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A257" s="18">
+      <c r="A257" s="16">
         <v>235</v>
       </c>
-      <c r="B257" s="18">
+      <c r="B257" s="16">
         <v>2</v>
       </c>
       <c r="C257" s="5">
@@ -7441,10 +7441,10 @@
       </c>
     </row>
     <row r="258" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A258" s="18">
+      <c r="A258" s="16">
         <v>236</v>
       </c>
-      <c r="B258" s="18">
+      <c r="B258" s="16">
         <v>2</v>
       </c>
       <c r="C258" s="5">
@@ -7452,10 +7452,10 @@
       </c>
     </row>
     <row r="259" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A259" s="18">
+      <c r="A259" s="16">
         <v>237</v>
       </c>
-      <c r="B259" s="18">
+      <c r="B259" s="16">
         <v>2</v>
       </c>
       <c r="C259" s="5">
@@ -7463,10 +7463,10 @@
       </c>
     </row>
     <row r="260" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A260" s="18">
+      <c r="A260" s="16">
         <v>238</v>
       </c>
-      <c r="B260" s="18">
+      <c r="B260" s="16">
         <v>2</v>
       </c>
       <c r="C260" s="5">
@@ -7474,10 +7474,10 @@
       </c>
     </row>
     <row r="261" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A261" s="18">
+      <c r="A261" s="16">
         <v>239</v>
       </c>
-      <c r="B261" s="18">
+      <c r="B261" s="16">
         <v>2</v>
       </c>
       <c r="C261" s="5">
@@ -7485,10 +7485,10 @@
       </c>
     </row>
     <row r="262" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A262" s="18">
+      <c r="A262" s="16">
         <v>240</v>
       </c>
-      <c r="B262" s="18">
+      <c r="B262" s="16">
         <v>2</v>
       </c>
       <c r="C262" s="5">
@@ -7496,10 +7496,10 @@
       </c>
     </row>
     <row r="263" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A263" s="18">
+      <c r="A263" s="16">
         <v>241</v>
       </c>
-      <c r="B263" s="18">
+      <c r="B263" s="16">
         <v>2</v>
       </c>
       <c r="C263" s="5">
@@ -7507,10 +7507,10 @@
       </c>
     </row>
     <row r="264" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A264" s="18">
+      <c r="A264" s="16">
         <v>242</v>
       </c>
-      <c r="B264" s="18">
+      <c r="B264" s="16">
         <v>2</v>
       </c>
       <c r="C264" s="5">
@@ -7518,10 +7518,10 @@
       </c>
     </row>
     <row r="265" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A265" s="18">
+      <c r="A265" s="16">
         <v>243</v>
       </c>
-      <c r="B265" s="18">
+      <c r="B265" s="16">
         <v>2</v>
       </c>
       <c r="C265" s="5">
@@ -7529,10 +7529,10 @@
       </c>
     </row>
     <row r="266" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A266" s="18">
+      <c r="A266" s="16">
         <v>244</v>
       </c>
-      <c r="B266" s="18">
+      <c r="B266" s="16">
         <v>2</v>
       </c>
       <c r="C266" s="5">
@@ -7540,10 +7540,10 @@
       </c>
     </row>
     <row r="267" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A267" s="18">
+      <c r="A267" s="16">
         <v>245</v>
       </c>
-      <c r="B267" s="18">
+      <c r="B267" s="16">
         <v>2</v>
       </c>
       <c r="C267" s="5">
@@ -7551,10 +7551,10 @@
       </c>
     </row>
     <row r="268" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A268" s="18">
+      <c r="A268" s="16">
         <v>246</v>
       </c>
-      <c r="B268" s="18">
+      <c r="B268" s="16">
         <v>2</v>
       </c>
       <c r="C268" s="5">
@@ -7562,10 +7562,10 @@
       </c>
     </row>
     <row r="269" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A269" s="18">
+      <c r="A269" s="16">
         <v>247</v>
       </c>
-      <c r="B269" s="18">
+      <c r="B269" s="16">
         <v>2</v>
       </c>
       <c r="C269" s="5">
@@ -7573,10 +7573,10 @@
       </c>
     </row>
     <row r="270" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A270" s="18">
+      <c r="A270" s="16">
         <v>248</v>
       </c>
-      <c r="B270" s="18">
+      <c r="B270" s="16">
         <v>2</v>
       </c>
       <c r="C270" s="5">
@@ -7584,10 +7584,10 @@
       </c>
     </row>
     <row r="271" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A271" s="18">
+      <c r="A271" s="16">
         <v>249</v>
       </c>
-      <c r="B271" s="18">
+      <c r="B271" s="16">
         <v>2</v>
       </c>
       <c r="C271" s="5">
@@ -7595,10 +7595,10 @@
       </c>
     </row>
     <row r="272" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A272" s="18">
+      <c r="A272" s="16">
         <v>250</v>
       </c>
-      <c r="B272" s="18">
+      <c r="B272" s="16">
         <v>2</v>
       </c>
       <c r="C272" s="5">
@@ -7606,10 +7606,10 @@
       </c>
     </row>
     <row r="273" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A273" s="18">
+      <c r="A273" s="16">
         <v>251</v>
       </c>
-      <c r="B273" s="18">
+      <c r="B273" s="16">
         <v>2</v>
       </c>
       <c r="C273" s="5">
@@ -7617,10 +7617,10 @@
       </c>
     </row>
     <row r="274" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A274" s="18">
+      <c r="A274" s="16">
         <v>252</v>
       </c>
-      <c r="B274" s="18">
+      <c r="B274" s="16">
         <v>2</v>
       </c>
       <c r="C274" s="5">
@@ -7628,10 +7628,10 @@
       </c>
     </row>
     <row r="275" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A275" s="18">
+      <c r="A275" s="16">
         <v>253</v>
       </c>
-      <c r="B275" s="18">
+      <c r="B275" s="16">
         <v>2</v>
       </c>
       <c r="C275" s="5">
@@ -7639,10 +7639,10 @@
       </c>
     </row>
     <row r="276" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A276" s="18">
+      <c r="A276" s="16">
         <v>254</v>
       </c>
-      <c r="B276" s="18">
+      <c r="B276" s="16">
         <v>2</v>
       </c>
       <c r="C276" s="5">
@@ -7650,10 +7650,10 @@
       </c>
     </row>
     <row r="277" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A277" s="18">
+      <c r="A277" s="16">
         <v>255</v>
       </c>
-      <c r="B277" s="18">
+      <c r="B277" s="16">
         <v>2</v>
       </c>
       <c r="C277" s="5">
@@ -7661,10 +7661,10 @@
       </c>
     </row>
     <row r="278" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A278" s="18">
+      <c r="A278" s="16">
         <v>256</v>
       </c>
-      <c r="B278" s="18">
+      <c r="B278" s="16">
         <v>2</v>
       </c>
       <c r="C278" s="5">
@@ -7672,10 +7672,10 @@
       </c>
     </row>
     <row r="279" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A279" s="18">
+      <c r="A279" s="16">
         <v>257</v>
       </c>
-      <c r="B279" s="18">
+      <c r="B279" s="16">
         <v>2</v>
       </c>
       <c r="C279" s="5">
@@ -7683,10 +7683,10 @@
       </c>
     </row>
     <row r="280" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A280" s="18">
+      <c r="A280" s="16">
         <v>258</v>
       </c>
-      <c r="B280" s="18">
+      <c r="B280" s="16">
         <v>2</v>
       </c>
       <c r="C280" s="5">
@@ -7694,10 +7694,10 @@
       </c>
     </row>
     <row r="281" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A281" s="18">
+      <c r="A281" s="16">
         <v>259</v>
       </c>
-      <c r="B281" s="18">
+      <c r="B281" s="16">
         <v>2</v>
       </c>
       <c r="C281" s="5">
@@ -7705,10 +7705,10 @@
       </c>
     </row>
     <row r="282" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A282" s="18">
+      <c r="A282" s="16">
         <v>260</v>
       </c>
-      <c r="B282" s="18">
+      <c r="B282" s="16">
         <v>2</v>
       </c>
       <c r="C282" s="5">
@@ -7716,10 +7716,10 @@
       </c>
     </row>
     <row r="283" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A283" s="18">
+      <c r="A283" s="16">
         <v>261</v>
       </c>
-      <c r="B283" s="18">
+      <c r="B283" s="16">
         <v>2</v>
       </c>
       <c r="C283" s="5">
@@ -7727,10 +7727,10 @@
       </c>
     </row>
     <row r="284" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A284" s="18">
+      <c r="A284" s="16">
         <v>262</v>
       </c>
-      <c r="B284" s="18">
+      <c r="B284" s="16">
         <v>2</v>
       </c>
       <c r="C284" s="5">
@@ -7738,10 +7738,10 @@
       </c>
     </row>
     <row r="285" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A285" s="18">
+      <c r="A285" s="16">
         <v>263</v>
       </c>
-      <c r="B285" s="18">
+      <c r="B285" s="16">
         <v>2</v>
       </c>
       <c r="C285" s="5">
@@ -7749,10 +7749,10 @@
       </c>
     </row>
     <row r="286" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A286" s="18">
+      <c r="A286" s="16">
         <v>264</v>
       </c>
-      <c r="B286" s="18">
+      <c r="B286" s="16">
         <v>2</v>
       </c>
       <c r="C286" s="5">
@@ -7760,10 +7760,10 @@
       </c>
     </row>
     <row r="287" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A287" s="18">
+      <c r="A287" s="16">
         <v>265</v>
       </c>
-      <c r="B287" s="18">
+      <c r="B287" s="16">
         <v>2</v>
       </c>
       <c r="C287" s="5">
@@ -7771,10 +7771,10 @@
       </c>
     </row>
     <row r="288" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A288" s="18">
+      <c r="A288" s="16">
         <v>266</v>
       </c>
-      <c r="B288" s="18">
+      <c r="B288" s="16">
         <v>2</v>
       </c>
       <c r="C288" s="5">
@@ -7782,10 +7782,10 @@
       </c>
     </row>
     <row r="289" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A289" s="18">
+      <c r="A289" s="16">
         <v>267</v>
       </c>
-      <c r="B289" s="18">
+      <c r="B289" s="16">
         <v>2</v>
       </c>
       <c r="C289" s="5">
@@ -7793,10 +7793,10 @@
       </c>
     </row>
     <row r="290" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A290" s="18">
+      <c r="A290" s="16">
         <v>268</v>
       </c>
-      <c r="B290" s="18">
+      <c r="B290" s="16">
         <v>2</v>
       </c>
       <c r="C290" s="5">
@@ -7804,10 +7804,10 @@
       </c>
     </row>
     <row r="291" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A291" s="18">
+      <c r="A291" s="16">
         <v>269</v>
       </c>
-      <c r="B291" s="18">
+      <c r="B291" s="16">
         <v>2</v>
       </c>
       <c r="C291" s="5">
@@ -7815,10 +7815,10 @@
       </c>
     </row>
     <row r="292" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A292" s="18">
+      <c r="A292" s="16">
         <v>270</v>
       </c>
-      <c r="B292" s="18">
+      <c r="B292" s="16">
         <v>2</v>
       </c>
       <c r="C292" s="5">
@@ -7826,10 +7826,10 @@
       </c>
     </row>
     <row r="293" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A293" s="18">
+      <c r="A293" s="16">
         <v>271</v>
       </c>
-      <c r="B293" s="18">
+      <c r="B293" s="16">
         <v>2</v>
       </c>
       <c r="C293" s="5">
@@ -7837,10 +7837,10 @@
       </c>
     </row>
     <row r="294" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A294" s="18">
+      <c r="A294" s="16">
         <v>272</v>
       </c>
-      <c r="B294" s="18">
+      <c r="B294" s="16">
         <v>2</v>
       </c>
       <c r="C294" s="5">
@@ -7848,10 +7848,10 @@
       </c>
     </row>
     <row r="295" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A295" s="18">
+      <c r="A295" s="16">
         <v>273</v>
       </c>
-      <c r="B295" s="18">
+      <c r="B295" s="16">
         <v>2</v>
       </c>
       <c r="C295" s="5">
@@ -7859,10 +7859,10 @@
       </c>
     </row>
     <row r="296" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A296" s="18">
+      <c r="A296" s="16">
         <v>274</v>
       </c>
-      <c r="B296" s="18">
+      <c r="B296" s="16">
         <v>2</v>
       </c>
       <c r="C296" s="5">
@@ -7870,10 +7870,10 @@
       </c>
     </row>
     <row r="297" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A297" s="18">
+      <c r="A297" s="16">
         <v>275</v>
       </c>
-      <c r="B297" s="18">
+      <c r="B297" s="16">
         <v>2</v>
       </c>
       <c r="C297" s="5">
@@ -7881,10 +7881,10 @@
       </c>
     </row>
     <row r="298" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A298" s="18">
+      <c r="A298" s="16">
         <v>276</v>
       </c>
-      <c r="B298" s="18">
+      <c r="B298" s="16">
         <v>2</v>
       </c>
       <c r="C298" s="5">
@@ -7892,10 +7892,10 @@
       </c>
     </row>
     <row r="299" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A299" s="18">
+      <c r="A299" s="16">
         <v>277</v>
       </c>
-      <c r="B299" s="18">
+      <c r="B299" s="16">
         <v>2</v>
       </c>
       <c r="C299" s="5">
@@ -7903,10 +7903,10 @@
       </c>
     </row>
     <row r="300" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A300" s="18">
+      <c r="A300" s="16">
         <v>278</v>
       </c>
-      <c r="B300" s="18">
+      <c r="B300" s="16">
         <v>2</v>
       </c>
       <c r="C300" s="5">
@@ -7914,10 +7914,10 @@
       </c>
     </row>
     <row r="301" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A301" s="18">
+      <c r="A301" s="16">
         <v>279</v>
       </c>
-      <c r="B301" s="18">
+      <c r="B301" s="16">
         <v>2</v>
       </c>
       <c r="C301" s="5">
@@ -7925,10 +7925,10 @@
       </c>
     </row>
     <row r="302" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A302" s="18">
+      <c r="A302" s="16">
         <v>280</v>
       </c>
-      <c r="B302" s="18">
+      <c r="B302" s="16">
         <v>2</v>
       </c>
       <c r="C302" s="5">
@@ -7936,10 +7936,10 @@
       </c>
     </row>
     <row r="303" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A303" s="18">
+      <c r="A303" s="16">
         <v>281</v>
       </c>
-      <c r="B303" s="18">
+      <c r="B303" s="16">
         <v>2</v>
       </c>
       <c r="C303" s="5">
@@ -7947,10 +7947,10 @@
       </c>
     </row>
     <row r="304" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A304" s="18">
+      <c r="A304" s="16">
         <v>282</v>
       </c>
-      <c r="B304" s="18">
+      <c r="B304" s="16">
         <v>2</v>
       </c>
       <c r="C304" s="5">
@@ -7958,98 +7958,98 @@
       </c>
     </row>
     <row r="305" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A305" s="18">
+      <c r="A305" s="16">
         <v>283</v>
       </c>
-      <c r="B305" s="18">
+      <c r="B305" s="16">
         <v>2</v>
       </c>
       <c r="C305" s="5">
         <v>2111</v>
       </c>
     </row>
-    <row r="306" ht="15.5" spans="1:3">
-      <c r="A306" s="18">
+    <row r="306" ht="15.75" spans="1:3">
+      <c r="A306" s="16">
         <v>284</v>
       </c>
-      <c r="B306" s="18">
+      <c r="B306" s="16">
         <v>2</v>
       </c>
       <c r="C306" s="5">
         <v>22</v>
       </c>
     </row>
-    <row r="307" ht="15.5" spans="1:3">
-      <c r="A307" s="18">
+    <row r="307" ht="15.75" spans="1:3">
+      <c r="A307" s="16">
         <v>285</v>
       </c>
-      <c r="B307" s="18">
+      <c r="B307" s="16">
         <v>2</v>
       </c>
       <c r="C307" s="5">
         <v>2201</v>
       </c>
     </row>
-    <row r="308" ht="15.5" spans="1:3">
-      <c r="A308" s="18">
+    <row r="308" ht="15.75" spans="1:3">
+      <c r="A308" s="16">
         <v>286</v>
       </c>
-      <c r="B308" s="18">
+      <c r="B308" s="16">
         <v>2</v>
       </c>
       <c r="C308" s="5">
         <v>2202</v>
       </c>
     </row>
-    <row r="309" ht="15.5" spans="1:3">
-      <c r="A309" s="18">
+    <row r="309" ht="15.75" spans="1:3">
+      <c r="A309" s="16">
         <v>287</v>
       </c>
-      <c r="B309" s="18">
+      <c r="B309" s="16">
         <v>2</v>
       </c>
       <c r="C309" s="5">
         <v>23</v>
       </c>
     </row>
-    <row r="310" ht="15.5" spans="1:3">
-      <c r="A310" s="18">
+    <row r="310" ht="15.75" spans="1:3">
+      <c r="A310" s="16">
         <v>288</v>
       </c>
-      <c r="B310" s="18">
+      <c r="B310" s="16">
         <v>2</v>
       </c>
       <c r="C310" s="5">
         <v>2301</v>
       </c>
     </row>
-    <row r="311" ht="15.5" spans="1:3">
-      <c r="A311" s="18">
+    <row r="311" ht="15.75" spans="1:3">
+      <c r="A311" s="16">
         <v>289</v>
       </c>
-      <c r="B311" s="18">
+      <c r="B311" s="16">
         <v>2</v>
       </c>
       <c r="C311" s="5">
         <v>2302</v>
       </c>
     </row>
-    <row r="312" ht="15.5" spans="1:3">
-      <c r="A312" s="18">
+    <row r="312" ht="15.75" spans="1:3">
+      <c r="A312" s="16">
         <v>290</v>
       </c>
-      <c r="B312" s="18">
+      <c r="B312" s="16">
         <v>2</v>
       </c>
       <c r="C312" s="5">
         <v>2303</v>
       </c>
     </row>
-    <row r="313" ht="15.5" spans="1:3">
-      <c r="A313" s="18">
+    <row r="313" ht="15.75" spans="1:3">
+      <c r="A313" s="16">
         <v>291</v>
       </c>
-      <c r="B313" s="18">
+      <c r="B313" s="16">
         <v>2</v>
       </c>
       <c r="C313" s="5">
@@ -8066,8 +8066,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J346"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:J347"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.6333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -8079,7 +8079,7 @@
     <col min="10" max="10" width="17.825" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:10">
+    <row r="1" ht="23.25" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -16036,7 +16036,7 @@
       <c r="F289" s="11"/>
       <c r="G289" s="10"/>
       <c r="H289" s="10"/>
-      <c r="I289" s="16"/>
+      <c r="I289" s="14"/>
       <c r="J289" s="6"/>
     </row>
     <row r="290" ht="20.1" customHeight="1" spans="1:10">
@@ -16723,27 +16723,27 @@
       <c r="J314" s="6"/>
     </row>
     <row r="315" customFormat="1" spans="1:10">
-      <c r="A315" s="14">
+      <c r="A315" s="5">
         <v>1607</v>
       </c>
-      <c r="B315" s="15" t="s">
+      <c r="B315" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C315" s="14">
+      <c r="C315" s="5">
         <v>16</v>
       </c>
-      <c r="D315" s="14">
+      <c r="D315" s="5">
         <v>1607</v>
       </c>
-      <c r="E315" s="14"/>
-      <c r="F315" s="14" t="s">
+      <c r="E315" s="5"/>
+      <c r="F315" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G315" s="15" t="s">
+      <c r="G315" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="H315" s="15"/>
-      <c r="I315" s="15" t="s">
+      <c r="H315" s="2"/>
+      <c r="I315" s="2" t="s">
         <v>349</v>
       </c>
       <c r="J315" s="6"/>
@@ -17007,7 +17007,7 @@
       <c r="A327" s="5">
         <v>2302</v>
       </c>
-      <c r="B327" s="17" t="s">
+      <c r="B327" s="15" t="s">
         <v>367</v>
       </c>
       <c r="C327" s="5">
@@ -17020,7 +17020,7 @@
       <c r="F327" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G327" s="17"/>
+      <c r="G327" s="15"/>
       <c r="H327" s="6"/>
       <c r="I327" s="6" t="s">
         <v>367</v>
@@ -17031,7 +17031,7 @@
       <c r="A328" s="5">
         <v>23021</v>
       </c>
-      <c r="B328" s="17" t="s">
+      <c r="B328" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C328" s="5">
@@ -17044,7 +17044,7 @@
       <c r="F328" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G328" s="17" t="s">
+      <c r="G328" s="15" t="s">
         <v>369</v>
       </c>
       <c r="H328" s="6"/>
@@ -17057,7 +17057,7 @@
       <c r="A329" s="5">
         <v>23022</v>
       </c>
-      <c r="B329" s="17" t="s">
+      <c r="B329" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C329" s="5">
@@ -17070,7 +17070,7 @@
       <c r="F329" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G329" s="17" t="s">
+      <c r="G329" s="15" t="s">
         <v>372</v>
       </c>
       <c r="H329" s="6"/>
@@ -17140,7 +17140,7 @@
         <v>2303</v>
       </c>
       <c r="D332" s="5">
-        <v>23031</v>
+        <v>23032</v>
       </c>
       <c r="E332" s="5"/>
       <c r="F332" s="5" t="s">
@@ -17166,7 +17166,7 @@
         <v>2303</v>
       </c>
       <c r="D333" s="5">
-        <v>23032</v>
+        <v>23033</v>
       </c>
       <c r="E333" s="5"/>
       <c r="F333" s="5" t="s">
@@ -17181,59 +17181,59 @@
       </c>
       <c r="J333" s="6"/>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" ht="20.1" customHeight="1" spans="1:10">
       <c r="A334" s="5">
-        <v>2304</v>
+        <v>23034</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>380</v>
       </c>
       <c r="C334" s="5">
-        <v>23</v>
+        <v>2303</v>
       </c>
       <c r="D334" s="5">
-        <v>2304</v>
+        <v>23034</v>
       </c>
       <c r="E334" s="5"/>
       <c r="F334" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G334" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G334" s="6" t="s">
+        <v>381</v>
+      </c>
       <c r="H334" s="6"/>
       <c r="I334" s="6" t="s">
         <v>380</v>
       </c>
       <c r="J334" s="6"/>
     </row>
-    <row r="335" ht="20.1" customHeight="1" spans="1:10">
+    <row r="335" spans="1:10">
       <c r="A335" s="5">
-        <v>23041</v>
+        <v>2304</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C335" s="5">
+        <v>23</v>
+      </c>
+      <c r="D335" s="5">
         <v>2304</v>
-      </c>
-      <c r="D335" s="5">
-        <v>23041</v>
       </c>
       <c r="E335" s="5"/>
       <c r="F335" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G335" s="6" t="s">
-        <v>382</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G335" s="6"/>
       <c r="H335" s="6"/>
       <c r="I335" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J335" s="6"/>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" ht="20.1" customHeight="1" spans="1:10">
       <c r="A336" s="5">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>383</v>
@@ -17242,7 +17242,7 @@
         <v>2304</v>
       </c>
       <c r="D336" s="5">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="E336" s="5"/>
       <c r="F336" s="5" t="s">
@@ -17259,7 +17259,7 @@
     </row>
     <row r="337" spans="1:10">
       <c r="A337" s="5">
-        <v>23043</v>
+        <v>23042</v>
       </c>
       <c r="B337" s="6" t="s">
         <v>385</v>
@@ -17268,7 +17268,7 @@
         <v>2304</v>
       </c>
       <c r="D337" s="5">
-        <v>23043</v>
+        <v>23042</v>
       </c>
       <c r="E337" s="5"/>
       <c r="F337" s="5" t="s">
@@ -17279,89 +17279,89 @@
       </c>
       <c r="H337" s="6"/>
       <c r="I337" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="J337" s="6"/>
+    </row>
+    <row r="338" spans="1:10">
+      <c r="A338" s="5">
+        <v>23043</v>
+      </c>
+      <c r="B338" s="6" t="s">
         <v>387</v>
-      </c>
-      <c r="J337" s="6"/>
-    </row>
-    <row r="338" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A338" s="5">
-        <v>23044</v>
-      </c>
-      <c r="B338" s="6" t="s">
-        <v>388</v>
       </c>
       <c r="C338" s="5">
         <v>2304</v>
       </c>
       <c r="D338" s="5">
-        <v>23044</v>
+        <v>23043</v>
       </c>
       <c r="E338" s="5"/>
       <c r="F338" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G338" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H338" s="6"/>
       <c r="I338" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J338" s="6"/>
+    </row>
+    <row r="339" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A339" s="5">
+        <v>23044</v>
+      </c>
+      <c r="B339" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="J338" s="6"/>
-    </row>
-    <row r="339" spans="1:10">
-      <c r="A339" s="5">
-        <v>2305</v>
-      </c>
-      <c r="B339" s="6" t="s">
-        <v>391</v>
-      </c>
       <c r="C339" s="5">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D339" s="5">
-        <v>2305</v>
+        <v>23044</v>
       </c>
       <c r="E339" s="5"/>
       <c r="F339" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G339" s="5"/>
-      <c r="H339" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G339" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="H339" s="6"/>
       <c r="I339" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J339" s="6"/>
     </row>
     <row r="340" spans="1:10">
       <c r="A340" s="5">
-        <v>23051</v>
+        <v>2305</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C340" s="5">
+        <v>23</v>
+      </c>
+      <c r="D340" s="5">
         <v>2305</v>
-      </c>
-      <c r="D340" s="5">
-        <v>23051</v>
       </c>
       <c r="E340" s="5"/>
       <c r="F340" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G340" s="6" t="s">
-        <v>393</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G340" s="5"/>
       <c r="H340" s="5"/>
       <c r="I340" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J340" s="6"/>
     </row>
     <row r="341" spans="1:10">
       <c r="A341" s="5">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>394</v>
@@ -17370,7 +17370,7 @@
         <v>2305</v>
       </c>
       <c r="D341" s="5">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="E341" s="5"/>
       <c r="F341" s="5" t="s">
@@ -17379,7 +17379,7 @@
       <c r="G341" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="H341" s="6"/>
+      <c r="H341" s="5"/>
       <c r="I341" s="6" t="s">
         <v>394</v>
       </c>
@@ -17387,22 +17387,24 @@
     </row>
     <row r="342" spans="1:10">
       <c r="A342" s="5">
-        <v>24</v>
+        <v>23052</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>396</v>
       </c>
       <c r="C342" s="5">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D342" s="5">
-        <v>24</v>
+        <v>23052</v>
       </c>
       <c r="E342" s="5"/>
       <c r="F342" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G342" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G342" s="6" t="s">
+        <v>397</v>
+      </c>
       <c r="H342" s="6"/>
       <c r="I342" s="6" t="s">
         <v>396</v>
@@ -17411,83 +17413,81 @@
     </row>
     <row r="343" spans="1:10">
       <c r="A343" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C343" s="5">
         <v>2</v>
       </c>
       <c r="D343" s="5">
-        <v>25</v>
-      </c>
-      <c r="E343" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="E343" s="5"/>
       <c r="F343" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
       <c r="I343" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J343" s="6"/>
     </row>
     <row r="344" spans="1:10">
       <c r="A344" s="5">
-        <v>2501</v>
+        <v>25</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C344" s="5">
+        <v>2</v>
+      </c>
+      <c r="D344" s="5">
         <v>25</v>
-      </c>
-      <c r="D344" s="5">
-        <v>2501</v>
       </c>
       <c r="E344" s="6"/>
       <c r="F344" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G344" s="6" t="s">
-        <v>399</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G344" s="6"/>
       <c r="H344" s="6"/>
       <c r="I344" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J344" s="6"/>
     </row>
     <row r="345" spans="1:10">
       <c r="A345" s="5">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C345" s="5">
         <v>25</v>
       </c>
       <c r="D345" s="5">
-        <v>2502</v>
-      </c>
-      <c r="E345" s="5"/>
+        <v>2501</v>
+      </c>
+      <c r="E345" s="6"/>
       <c r="F345" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G345" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="H345" s="6"/>
+      <c r="I345" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="H345" s="5"/>
-      <c r="I345" s="6" t="s">
-        <v>401</v>
-      </c>
       <c r="J345" s="6"/>
     </row>
-    <row r="346" s="2" customFormat="1" spans="1:10">
+    <row r="346" spans="1:10">
       <c r="A346" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>403</v>
@@ -17496,17 +17496,43 @@
         <v>25</v>
       </c>
       <c r="D346" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="E346" s="5"/>
       <c r="F346" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G346" s="6"/>
-      <c r="I346" s="2" t="s">
+      <c r="G346" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="H346" s="5"/>
+      <c r="I346" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="J346" s="2" t="b">
+      <c r="J346" s="6"/>
+    </row>
+    <row r="347" s="2" customFormat="1" spans="1:10">
+      <c r="A347" s="5">
+        <v>2503</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C347" s="5">
+        <v>25</v>
+      </c>
+      <c r="D347" s="5">
+        <v>2503</v>
+      </c>
+      <c r="E347" s="5"/>
+      <c r="F347" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G347" s="6"/>
+      <c r="I347" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J347" s="2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="408">
   <si>
     <t>Id</t>
   </si>
@@ -1088,6 +1088,12 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserRtfcCalibrationViewModel</t>
+  </si>
+  <si>
+    <t>Pmt Agc Delay</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Laser.LaserPmtAgcDelayCalibrationViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -16748,7 +16754,30 @@
       </c>
       <c r="J315" s="6"/>
     </row>
-    <row r="316" spans="10:10">
+    <row r="316" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A316" s="5">
+        <v>1608</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C316" s="5">
+        <v>16</v>
+      </c>
+      <c r="D316" s="5">
+        <v>1608</v>
+      </c>
+      <c r="E316" s="5"/>
+      <c r="F316" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G316" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H316" s="6"/>
+      <c r="I316" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="J316" s="6"/>
     </row>
     <row r="317" ht="20.1" customHeight="1" spans="1:10">
@@ -16756,7 +16785,7 @@
         <v>2</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C317" s="5">
         <v>-1</v>
@@ -16771,7 +16800,7 @@
       <c r="G317" s="6"/>
       <c r="H317" s="6"/>
       <c r="I317" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J317" s="6"/>
     </row>
@@ -16780,7 +16809,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C318" s="5">
         <v>2</v>
@@ -16795,7 +16824,7 @@
       <c r="G318" s="6"/>
       <c r="H318" s="6"/>
       <c r="I318" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J318" s="6"/>
     </row>
@@ -16804,7 +16833,7 @@
         <v>2110</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C319" s="5">
         <v>21</v>
@@ -16817,11 +16846,11 @@
         <v>55</v>
       </c>
       <c r="G319" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H319" s="6"/>
       <c r="I319" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J319" s="6"/>
     </row>
@@ -16830,7 +16859,7 @@
         <v>2111</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C320" s="5">
         <v>21</v>
@@ -16843,11 +16872,11 @@
         <v>55</v>
       </c>
       <c r="G320" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H320" s="6"/>
       <c r="I320" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J320" s="6"/>
     </row>
@@ -16856,7 +16885,7 @@
         <v>22</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C321" s="5">
         <v>2</v>
@@ -16871,7 +16900,7 @@
       <c r="G321" s="6"/>
       <c r="H321" s="6"/>
       <c r="I321" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J321" s="6"/>
     </row>
@@ -16880,7 +16909,7 @@
         <v>2201</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C322" s="5">
         <v>22</v>
@@ -16893,11 +16922,11 @@
         <v>55</v>
       </c>
       <c r="G322" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H322" s="6"/>
       <c r="I322" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J322" s="6"/>
     </row>
@@ -16906,7 +16935,7 @@
         <v>2202</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C323" s="5">
         <v>22</v>
@@ -16919,11 +16948,11 @@
         <v>55</v>
       </c>
       <c r="G323" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H323" s="6"/>
       <c r="I323" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J323" s="6"/>
     </row>
@@ -16932,7 +16961,7 @@
         <v>2203</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C324" s="5">
         <v>22</v>
@@ -16945,11 +16974,11 @@
         <v>55</v>
       </c>
       <c r="G324" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H324" s="6"/>
       <c r="I324" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J324" s="6"/>
     </row>
@@ -16958,7 +16987,7 @@
         <v>23</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C325" s="5">
         <v>2</v>
@@ -16973,7 +17002,7 @@
       <c r="G325" s="6"/>
       <c r="H325" s="6"/>
       <c r="I325" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J325" s="6"/>
     </row>
@@ -16982,7 +17011,7 @@
         <v>2301</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C326" s="5">
         <v>23</v>
@@ -16995,11 +17024,11 @@
         <v>55</v>
       </c>
       <c r="G326" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H326" s="6"/>
       <c r="I326" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J326" s="6"/>
     </row>
@@ -17008,7 +17037,7 @@
         <v>2302</v>
       </c>
       <c r="B327" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C327" s="5">
         <v>23</v>
@@ -17023,7 +17052,7 @@
       <c r="G327" s="15"/>
       <c r="H327" s="6"/>
       <c r="I327" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J327" s="6"/>
     </row>
@@ -17032,7 +17061,7 @@
         <v>23021</v>
       </c>
       <c r="B328" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C328" s="5">
         <v>2302</v>
@@ -17045,11 +17074,11 @@
         <v>55</v>
       </c>
       <c r="G328" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H328" s="6"/>
       <c r="I328" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J328" s="6"/>
     </row>
@@ -17058,7 +17087,7 @@
         <v>23022</v>
       </c>
       <c r="B329" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C329" s="5">
         <v>2302</v>
@@ -17071,11 +17100,11 @@
         <v>55</v>
       </c>
       <c r="G329" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H329" s="6"/>
       <c r="I329" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J329" s="6"/>
     </row>
@@ -17108,7 +17137,7 @@
         <v>23031</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C331" s="5">
         <v>2303</v>
@@ -17121,11 +17150,11 @@
         <v>55</v>
       </c>
       <c r="G331" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H331" s="6"/>
       <c r="I331" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J331" s="6"/>
     </row>
@@ -17134,7 +17163,7 @@
         <v>23032</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C332" s="5">
         <v>2303</v>
@@ -17147,11 +17176,11 @@
         <v>55</v>
       </c>
       <c r="G332" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H332" s="6"/>
       <c r="I332" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J332" s="6"/>
     </row>
@@ -17160,7 +17189,7 @@
         <v>23033</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C333" s="5">
         <v>2303</v>
@@ -17173,11 +17202,11 @@
         <v>55</v>
       </c>
       <c r="G333" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H333" s="6"/>
       <c r="I333" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J333" s="6"/>
     </row>
@@ -17186,7 +17215,7 @@
         <v>23034</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C334" s="5">
         <v>2303</v>
@@ -17199,11 +17228,11 @@
         <v>55</v>
       </c>
       <c r="G334" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H334" s="6"/>
       <c r="I334" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J334" s="6"/>
     </row>
@@ -17212,7 +17241,7 @@
         <v>2304</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C335" s="5">
         <v>23</v>
@@ -17227,7 +17256,7 @@
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
       <c r="I335" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J335" s="6"/>
     </row>
@@ -17236,7 +17265,7 @@
         <v>23041</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C336" s="5">
         <v>2304</v>
@@ -17249,11 +17278,11 @@
         <v>55</v>
       </c>
       <c r="G336" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H336" s="6"/>
       <c r="I336" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J336" s="6"/>
     </row>
@@ -17262,7 +17291,7 @@
         <v>23042</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C337" s="5">
         <v>2304</v>
@@ -17275,11 +17304,11 @@
         <v>55</v>
       </c>
       <c r="G337" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H337" s="6"/>
       <c r="I337" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J337" s="6"/>
     </row>
@@ -17288,7 +17317,7 @@
         <v>23043</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C338" s="5">
         <v>2304</v>
@@ -17301,11 +17330,11 @@
         <v>55</v>
       </c>
       <c r="G338" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H338" s="6"/>
       <c r="I338" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J338" s="6"/>
     </row>
@@ -17314,7 +17343,7 @@
         <v>23044</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C339" s="5">
         <v>2304</v>
@@ -17327,11 +17356,11 @@
         <v>55</v>
       </c>
       <c r="G339" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H339" s="6"/>
       <c r="I339" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J339" s="6"/>
     </row>
@@ -17340,7 +17369,7 @@
         <v>2305</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C340" s="5">
         <v>23</v>
@@ -17355,7 +17384,7 @@
       <c r="G340" s="5"/>
       <c r="H340" s="5"/>
       <c r="I340" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J340" s="6"/>
     </row>
@@ -17364,7 +17393,7 @@
         <v>23051</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C341" s="5">
         <v>2305</v>
@@ -17377,11 +17406,11 @@
         <v>55</v>
       </c>
       <c r="G341" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H341" s="5"/>
       <c r="I341" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J341" s="6"/>
     </row>
@@ -17390,7 +17419,7 @@
         <v>23052</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C342" s="5">
         <v>2305</v>
@@ -17403,11 +17432,11 @@
         <v>55</v>
       </c>
       <c r="G342" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H342" s="6"/>
       <c r="I342" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J342" s="6"/>
     </row>
@@ -17416,7 +17445,7 @@
         <v>24</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C343" s="5">
         <v>2</v>
@@ -17431,7 +17460,7 @@
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
       <c r="I343" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J343" s="6"/>
     </row>
@@ -17440,7 +17469,7 @@
         <v>25</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C344" s="5">
         <v>2</v>
@@ -17455,7 +17484,7 @@
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
       <c r="I344" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J344" s="6"/>
     </row>
@@ -17464,7 +17493,7 @@
         <v>2501</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C345" s="5">
         <v>25</v>
@@ -17477,11 +17506,11 @@
         <v>55</v>
       </c>
       <c r="G345" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H345" s="6"/>
       <c r="I345" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J345" s="6"/>
     </row>
@@ -17490,7 +17519,7 @@
         <v>2502</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C346" s="5">
         <v>25</v>
@@ -17503,11 +17532,11 @@
         <v>55</v>
       </c>
       <c r="G346" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H346" s="5"/>
       <c r="I346" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J346" s="6"/>
     </row>
@@ -17516,7 +17545,7 @@
         <v>2503</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C347" s="5">
         <v>25</v>
@@ -17530,7 +17559,7 @@
       </c>
       <c r="G347" s="6"/>
       <c r="I347" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J347" s="2" t="b">
         <v>1</v>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1066,6 +1066,12 @@
     <t>CugaCalibration.Views.Laser.LineCentricity.Children.Review</t>
   </si>
   <si>
+    <t>Pmt Agc Delay</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Laser.LaserPmtAgcDelayCalibrationViewModel</t>
+  </si>
+  <si>
     <t>Pmt Gain</t>
   </si>
   <si>
@@ -1088,12 +1094,6 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserRtfcCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>Pmt Agc Delay</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserPmtAgcDelayCalibrationViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -16652,59 +16652,60 @@
       <c r="J311" s="6"/>
     </row>
     <row r="312" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A312" s="7">
+      <c r="A312" s="5">
+        <v>1608</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C312" s="5">
+        <v>16</v>
+      </c>
+      <c r="D312" s="5">
+        <v>1608</v>
+      </c>
+      <c r="E312" s="5"/>
+      <c r="F312" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G312" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="H312" s="6"/>
+      <c r="I312" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="J312" s="6"/>
+    </row>
+    <row r="313" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A313" s="7">
         <v>1604</v>
       </c>
-      <c r="B312" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C312" s="7">
+      <c r="B313" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C313" s="7">
         <v>16</v>
       </c>
-      <c r="D312" s="7">
+      <c r="D313" s="7">
         <v>1604</v>
       </c>
-      <c r="E312" s="7"/>
-      <c r="F312" s="7" t="s">
+      <c r="E313" s="7"/>
+      <c r="F313" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G312" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="H312" s="8"/>
-      <c r="I312" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="J312" s="6"/>
-    </row>
-    <row r="313" s="2" customFormat="1" spans="1:10">
-      <c r="A313" s="5">
+      <c r="G313" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="H313" s="8"/>
+      <c r="I313" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="J313" s="6"/>
+    </row>
+    <row r="314" s="2" customFormat="1" spans="1:10">
+      <c r="A314" s="5">
         <v>1605</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C313" s="5">
-        <v>16</v>
-      </c>
-      <c r="D313" s="5">
-        <v>1605</v>
-      </c>
-      <c r="E313" s="5"/>
-      <c r="F313" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G313" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="I313" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="J313" s="6"/>
-    </row>
-    <row r="314" customFormat="1" spans="1:10">
-      <c r="A314" s="5">
-        <v>1606</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>347</v>
@@ -16713,16 +16714,15 @@
         <v>16</v>
       </c>
       <c r="D314" s="5">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E314" s="5"/>
       <c r="F314" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G314" s="2" t="s">
+      <c r="G314" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="H314" s="2"/>
       <c r="I314" s="2" t="s">
         <v>347</v>
       </c>
@@ -16730,7 +16730,7 @@
     </row>
     <row r="315" customFormat="1" spans="1:10">
       <c r="A315" s="5">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>349</v>
@@ -16739,7 +16739,7 @@
         <v>16</v>
       </c>
       <c r="D315" s="5">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E315" s="5"/>
       <c r="F315" s="5" t="s">
@@ -16754,28 +16754,28 @@
       </c>
       <c r="J315" s="6"/>
     </row>
-    <row r="316" ht="20.1" customHeight="1" spans="1:10">
+    <row r="316" customFormat="1" spans="1:10">
       <c r="A316" s="5">
-        <v>1608</v>
-      </c>
-      <c r="B316" s="6" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>351</v>
       </c>
       <c r="C316" s="5">
         <v>16</v>
       </c>
       <c r="D316" s="5">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="E316" s="5"/>
       <c r="F316" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G316" s="6" t="s">
+      <c r="G316" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="H316" s="6"/>
-      <c r="I316" s="6" t="s">
+      <c r="H316" s="2"/>
+      <c r="I316" s="2" t="s">
         <v>351</v>
       </c>
       <c r="J316" s="6"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="17800" tabRatio="500" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="410">
   <si>
     <t>Id</t>
   </si>
@@ -824,6 +824,12 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Chuck.ChuckAutoFocusCalibrationViewModel</t>
+  </si>
+  <si>
+    <t>Stage Map</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Chuck.ChuckStageMapCalibrationViewModel</t>
   </si>
   <si>
     <t>Laser</t>
@@ -2574,14 +2580,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="5" width="20.6333333333333" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:9">
+    <row r="1" ht="22.5" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3147,12 +3153,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:3">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3342,12 +3348,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:3">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3537,12 +3543,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:6">
+    <row r="1" ht="22.5" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3909,12 +3915,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:5">
+    <row r="1" ht="22.5" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4172,14 +4178,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="20.6333333333333" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
     <col min="4" max="5" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:5">
+    <row r="1" ht="22.5" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4437,12 +4443,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:3">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4614,12 +4620,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C313"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:3">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7974,7 +7980,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="306" ht="15.75" spans="1:3">
+    <row r="306" ht="15.5" spans="1:3">
       <c r="A306" s="16">
         <v>284</v>
       </c>
@@ -7985,7 +7991,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="307" ht="15.75" spans="1:3">
+    <row r="307" ht="15.5" spans="1:3">
       <c r="A307" s="16">
         <v>285</v>
       </c>
@@ -7996,7 +8002,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="308" ht="15.75" spans="1:3">
+    <row r="308" ht="15.5" spans="1:3">
       <c r="A308" s="16">
         <v>286</v>
       </c>
@@ -8007,7 +8013,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="309" ht="15.75" spans="1:3">
+    <row r="309" ht="15.5" spans="1:3">
       <c r="A309" s="16">
         <v>287</v>
       </c>
@@ -8018,7 +8024,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" ht="15.75" spans="1:3">
+    <row r="310" ht="15.5" spans="1:3">
       <c r="A310" s="16">
         <v>288</v>
       </c>
@@ -8029,7 +8035,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="311" ht="15.75" spans="1:3">
+    <row r="311" ht="15.5" spans="1:3">
       <c r="A311" s="16">
         <v>289</v>
       </c>
@@ -8040,7 +8046,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="312" ht="15.75" spans="1:3">
+    <row r="312" ht="15.5" spans="1:3">
       <c r="A312" s="16">
         <v>290</v>
       </c>
@@ -8051,7 +8057,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="313" ht="15.75" spans="1:3">
+    <row r="313" ht="15.5" spans="1:3">
       <c r="A313" s="16">
         <v>291</v>
       </c>
@@ -8072,8 +8078,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J347"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:J348"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.6333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -8085,7 +8091,7 @@
     <col min="10" max="10" width="17.825" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:10">
+    <row r="1" ht="22.5" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -14259,118 +14265,116 @@
       </c>
       <c r="J222" s="6"/>
     </row>
-    <row r="223" spans="10:10">
+    <row r="223" customFormat="1" spans="1:10">
+      <c r="A223" s="5">
+        <v>1309</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C223" s="5">
+        <v>13</v>
+      </c>
+      <c r="D223" s="5">
+        <v>1309</v>
+      </c>
+      <c r="E223" s="5"/>
+      <c r="F223" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2" t="s">
+        <v>263</v>
+      </c>
       <c r="J223" s="6"/>
     </row>
-    <row r="224" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A224" s="5">
-        <v>14</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C224" s="5">
-        <v>1</v>
-      </c>
-      <c r="D224" s="5">
-        <v>14</v>
-      </c>
-      <c r="E224" s="5"/>
-      <c r="F224" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G224" s="6"/>
-      <c r="H224" s="6"/>
-      <c r="I224" s="6" t="s">
-        <v>263</v>
-      </c>
+    <row r="224" spans="10:10">
       <c r="J224" s="6"/>
     </row>
     <row r="225" ht="20.1" customHeight="1" spans="1:10">
       <c r="A225" s="5">
-        <v>1401</v>
+        <v>14</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C225" s="5">
+        <v>1</v>
+      </c>
+      <c r="D225" s="5">
         <v>14</v>
-      </c>
-      <c r="D225" s="5">
-        <v>1401</v>
       </c>
       <c r="E225" s="5"/>
       <c r="F225" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G225" s="6" t="s">
-        <v>265</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G225" s="6"/>
       <c r="H225" s="6"/>
       <c r="I225" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J225" s="6"/>
     </row>
     <row r="226" ht="20.1" customHeight="1" spans="1:10">
       <c r="A226" s="5">
-        <v>140101</v>
+        <v>1401</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>266</v>
       </c>
       <c r="C226" s="5">
+        <v>14</v>
+      </c>
+      <c r="D226" s="5">
         <v>1401</v>
-      </c>
-      <c r="D226" s="5">
-        <v>140101</v>
       </c>
       <c r="E226" s="5"/>
       <c r="F226" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G226" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="H226" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="H226" s="6"/>
       <c r="I226" s="6" t="s">
-        <v>60</v>
+        <v>266</v>
       </c>
       <c r="J226" s="6"/>
     </row>
     <row r="227" ht="20.1" customHeight="1" spans="1:10">
       <c r="A227" s="5">
-        <v>140102</v>
+        <v>140101</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C227" s="5">
         <v>1401</v>
       </c>
       <c r="D227" s="5">
-        <v>140102</v>
+        <v>140101</v>
       </c>
       <c r="E227" s="5"/>
       <c r="F227" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G227" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H227" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J227" s="6"/>
     </row>
     <row r="228" ht="20.1" customHeight="1" spans="1:10">
       <c r="A228" s="5">
-        <v>140103</v>
+        <v>140102</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>268</v>
@@ -14379,360 +14383,360 @@
         <v>1401</v>
       </c>
       <c r="D228" s="5">
-        <v>140103</v>
+        <v>140102</v>
       </c>
       <c r="E228" s="5"/>
       <c r="F228" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G228" s="6" t="s">
         <v>269</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>270</v>
+        <v>61</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>270</v>
+        <v>61</v>
       </c>
       <c r="J228" s="6"/>
     </row>
     <row r="229" ht="20.1" customHeight="1" spans="1:10">
       <c r="A229" s="5">
-        <v>140104</v>
+        <v>140103</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C229" s="5">
         <v>1401</v>
       </c>
       <c r="D229" s="5">
-        <v>140104</v>
+        <v>140103</v>
       </c>
       <c r="E229" s="5"/>
       <c r="F229" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G229" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H229" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J229" s="6"/>
     </row>
     <row r="230" ht="20.1" customHeight="1" spans="1:10">
       <c r="A230" s="5">
-        <v>140105</v>
+        <v>140104</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C230" s="5">
         <v>1401</v>
       </c>
       <c r="D230" s="5">
-        <v>140105</v>
+        <v>140104</v>
       </c>
       <c r="E230" s="5"/>
       <c r="F230" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J230" s="6"/>
     </row>
     <row r="231" ht="20.1" customHeight="1" spans="1:10">
       <c r="A231" s="5">
-        <v>140106</v>
+        <v>140105</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C231" s="5">
         <v>1401</v>
       </c>
       <c r="D231" s="5">
-        <v>140106</v>
+        <v>140105</v>
       </c>
       <c r="E231" s="5"/>
       <c r="F231" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G231" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H231" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J231" s="6"/>
     </row>
     <row r="232" ht="20.1" customHeight="1" spans="1:10">
       <c r="A232" s="5">
-        <v>140107</v>
+        <v>140106</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C232" s="5">
         <v>1401</v>
       </c>
       <c r="D232" s="5">
-        <v>140107</v>
+        <v>140106</v>
       </c>
       <c r="E232" s="5"/>
       <c r="F232" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J232" s="6"/>
     </row>
     <row r="233" ht="20.1" customHeight="1" spans="1:10">
       <c r="A233" s="5">
-        <v>140108</v>
+        <v>140107</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C233" s="5">
         <v>1401</v>
       </c>
       <c r="D233" s="5">
-        <v>140108</v>
+        <v>140107</v>
       </c>
       <c r="E233" s="5"/>
       <c r="F233" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G233" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H233" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J233" s="6"/>
     </row>
     <row r="234" ht="20.1" customHeight="1" spans="1:10">
       <c r="A234" s="5">
-        <v>140109</v>
+        <v>140108</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C234" s="5">
         <v>1401</v>
       </c>
       <c r="D234" s="5">
-        <v>140109</v>
+        <v>140108</v>
       </c>
       <c r="E234" s="5"/>
       <c r="F234" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J234" s="6"/>
     </row>
     <row r="235" ht="20.1" customHeight="1" spans="1:10">
       <c r="A235" s="5">
-        <v>140110</v>
+        <v>140109</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C235" s="5">
         <v>1401</v>
       </c>
       <c r="D235" s="5">
-        <v>140110</v>
+        <v>140109</v>
       </c>
       <c r="E235" s="5"/>
       <c r="F235" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G235" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>64</v>
+        <v>278</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>64</v>
+        <v>278</v>
       </c>
       <c r="J235" s="6"/>
     </row>
     <row r="236" ht="20.1" customHeight="1" spans="1:10">
       <c r="A236" s="5">
-        <v>140111</v>
+        <v>140110</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C236" s="5">
         <v>1401</v>
       </c>
       <c r="D236" s="5">
-        <v>140111</v>
+        <v>140110</v>
       </c>
       <c r="E236" s="5"/>
       <c r="F236" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J236" s="6"/>
     </row>
     <row r="237" ht="20.1" customHeight="1" spans="1:10">
       <c r="A237" s="5">
-        <v>140112</v>
+        <v>140111</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C237" s="5">
         <v>1401</v>
       </c>
       <c r="D237" s="5">
-        <v>140112</v>
+        <v>140111</v>
       </c>
       <c r="E237" s="5"/>
       <c r="F237" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G237" s="6" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="H237" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J237" s="6"/>
     </row>
     <row r="238" ht="20.1" customHeight="1" spans="1:10">
       <c r="A238" s="5">
-        <v>140113</v>
+        <v>140112</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C238" s="5">
         <v>1401</v>
       </c>
       <c r="D238" s="5">
-        <v>140113</v>
+        <v>140112</v>
       </c>
       <c r="E238" s="5"/>
       <c r="F238" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G238" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H238" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I238" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J238" s="6"/>
     </row>
     <row r="239" ht="20.1" customHeight="1" spans="1:10">
       <c r="A239" s="5">
-        <v>1402</v>
+        <v>140113</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>279</v>
       </c>
       <c r="C239" s="5">
-        <v>14</v>
+        <v>1401</v>
       </c>
       <c r="D239" s="5">
-        <v>1402</v>
+        <v>140113</v>
       </c>
       <c r="E239" s="5"/>
       <c r="F239" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G239" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="H239" s="6"/>
+      <c r="H239" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I239" s="6" t="s">
-        <v>279</v>
+        <v>65</v>
       </c>
       <c r="J239" s="6"/>
     </row>
     <row r="240" ht="20.1" customHeight="1" spans="1:10">
       <c r="A240" s="5">
-        <v>140201</v>
+        <v>1402</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>281</v>
       </c>
       <c r="C240" s="5">
+        <v>14</v>
+      </c>
+      <c r="D240" s="5">
         <v>1402</v>
-      </c>
-      <c r="D240" s="5">
-        <v>140201</v>
       </c>
       <c r="E240" s="5"/>
       <c r="F240" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G240" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="H240" s="6" t="s">
-        <v>90</v>
-      </c>
+      <c r="H240" s="6"/>
       <c r="I240" s="6" t="s">
-        <v>90</v>
+        <v>281</v>
       </c>
       <c r="J240" s="6"/>
     </row>
     <row r="241" ht="20.1" customHeight="1" spans="1:10">
       <c r="A241" s="5">
-        <v>140202</v>
+        <v>140201</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>283</v>
@@ -14741,7 +14745,7 @@
         <v>1402</v>
       </c>
       <c r="D241" s="5">
-        <v>140202</v>
+        <v>140201</v>
       </c>
       <c r="E241" s="5"/>
       <c r="F241" s="5" t="s">
@@ -14751,72 +14755,72 @@
         <v>284</v>
       </c>
       <c r="H241" s="6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J241" s="6"/>
     </row>
     <row r="242" ht="20.1" customHeight="1" spans="1:10">
       <c r="A242" s="5">
-        <v>140203</v>
+        <v>140202</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C242" s="5">
         <v>1402</v>
       </c>
       <c r="D242" s="5">
-        <v>140203</v>
+        <v>140202</v>
       </c>
       <c r="E242" s="5"/>
       <c r="F242" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G242" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H242" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J242" s="6"/>
     </row>
     <row r="243" ht="20.1" customHeight="1" spans="1:10">
       <c r="A243" s="5">
-        <v>140204</v>
+        <v>140203</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C243" s="5">
         <v>1402</v>
       </c>
       <c r="D243" s="5">
-        <v>140204</v>
+        <v>140203</v>
       </c>
       <c r="E243" s="5"/>
       <c r="F243" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G243" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H243" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J243" s="6"/>
     </row>
     <row r="244" ht="20.1" customHeight="1" spans="1:10">
       <c r="A244" s="5">
-        <v>140205</v>
+        <v>140204</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>285</v>
@@ -14825,192 +14829,192 @@
         <v>1402</v>
       </c>
       <c r="D244" s="5">
-        <v>140205</v>
+        <v>140204</v>
       </c>
       <c r="E244" s="5"/>
       <c r="F244" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G244" s="6" t="s">
         <v>286</v>
       </c>
       <c r="H244" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I244" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J244" s="6"/>
     </row>
     <row r="245" ht="20.1" customHeight="1" spans="1:10">
       <c r="A245" s="5">
-        <v>140206</v>
+        <v>140205</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C245" s="5">
         <v>1402</v>
       </c>
       <c r="D245" s="5">
-        <v>140206</v>
+        <v>140205</v>
       </c>
       <c r="E245" s="5"/>
       <c r="F245" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G245" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H245" s="6" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I245" s="6" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="J245" s="6"/>
     </row>
     <row r="246" ht="20.1" customHeight="1" spans="1:10">
       <c r="A246" s="5">
-        <v>140207</v>
+        <v>140206</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C246" s="5">
         <v>1402</v>
       </c>
       <c r="D246" s="5">
-        <v>140207</v>
+        <v>140206</v>
       </c>
       <c r="E246" s="5"/>
       <c r="F246" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H246" s="6" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="I246" s="6" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="J246" s="6"/>
     </row>
     <row r="247" ht="20.1" customHeight="1" spans="1:10">
       <c r="A247" s="5">
-        <v>140208</v>
+        <v>140207</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C247" s="5">
         <v>1402</v>
       </c>
       <c r="D247" s="5">
-        <v>140208</v>
+        <v>140207</v>
       </c>
       <c r="E247" s="5"/>
       <c r="F247" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G247" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H247" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I247" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J247" s="6"/>
     </row>
     <row r="248" ht="20.1" customHeight="1" spans="1:10">
       <c r="A248" s="5">
-        <v>1403</v>
+        <v>140208</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>287</v>
       </c>
       <c r="C248" s="5">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="D248" s="5">
-        <v>1403</v>
+        <v>140208</v>
       </c>
       <c r="E248" s="5"/>
       <c r="F248" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G248" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="H248" s="6"/>
+      <c r="H248" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I248" s="6" t="s">
-        <v>287</v>
+        <v>65</v>
       </c>
       <c r="J248" s="6"/>
     </row>
     <row r="249" ht="20.1" customHeight="1" spans="1:10">
       <c r="A249" s="5">
-        <v>140301</v>
+        <v>1403</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>289</v>
       </c>
       <c r="C249" s="5">
+        <v>14</v>
+      </c>
+      <c r="D249" s="5">
         <v>1403</v>
-      </c>
-      <c r="D249" s="5">
-        <v>140301</v>
       </c>
       <c r="E249" s="5"/>
       <c r="F249" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G249" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="H249" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="H249" s="6"/>
       <c r="I249" s="6" t="s">
-        <v>60</v>
+        <v>289</v>
       </c>
       <c r="J249" s="6"/>
     </row>
     <row r="250" ht="20.1" customHeight="1" spans="1:10">
       <c r="A250" s="5">
-        <v>140302</v>
+        <v>140301</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C250" s="5">
         <v>1403</v>
       </c>
       <c r="D250" s="5">
-        <v>140302</v>
+        <v>140301</v>
       </c>
       <c r="E250" s="5"/>
       <c r="F250" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G250" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I250" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J250" s="6"/>
     </row>
     <row r="251" ht="20.1" customHeight="1" spans="1:10">
       <c r="A251" s="5">
-        <v>140303</v>
+        <v>140302</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>291</v>
@@ -15019,472 +15023,472 @@
         <v>1403</v>
       </c>
       <c r="D251" s="5">
-        <v>140303</v>
+        <v>140302</v>
       </c>
       <c r="E251" s="5"/>
       <c r="F251" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G251" s="6" t="s">
         <v>292</v>
       </c>
       <c r="H251" s="6" t="s">
-        <v>293</v>
+        <v>61</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>293</v>
+        <v>61</v>
       </c>
       <c r="J251" s="6"/>
     </row>
     <row r="252" ht="20.1" customHeight="1" spans="1:10">
       <c r="A252" s="5">
-        <v>140304</v>
+        <v>140303</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C252" s="5">
         <v>1403</v>
       </c>
       <c r="D252" s="5">
-        <v>140304</v>
+        <v>140303</v>
       </c>
       <c r="E252" s="5"/>
       <c r="F252" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G252" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H252" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I252" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J252" s="6"/>
     </row>
     <row r="253" ht="20.1" customHeight="1" spans="1:10">
       <c r="A253" s="5">
-        <v>140305</v>
+        <v>140304</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C253" s="5">
         <v>1403</v>
       </c>
       <c r="D253" s="5">
-        <v>140305</v>
+        <v>140304</v>
       </c>
       <c r="E253" s="5"/>
       <c r="F253" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G253" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H253" s="6" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="J253" s="6"/>
     </row>
     <row r="254" ht="20.1" customHeight="1" spans="1:10">
       <c r="A254" s="5">
-        <v>140306</v>
+        <v>140305</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C254" s="5">
         <v>1403</v>
       </c>
       <c r="D254" s="5">
-        <v>140306</v>
+        <v>140305</v>
       </c>
       <c r="E254" s="5"/>
       <c r="F254" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H254" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J254" s="6"/>
     </row>
     <row r="255" ht="20.1" customHeight="1" spans="1:10">
       <c r="A255" s="5">
-        <v>140307</v>
+        <v>140306</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C255" s="5">
         <v>1403</v>
       </c>
       <c r="D255" s="5">
-        <v>140307</v>
+        <v>140306</v>
       </c>
       <c r="E255" s="5"/>
       <c r="F255" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G255" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H255" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I255" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J255" s="6"/>
     </row>
     <row r="256" ht="20.1" customHeight="1" spans="1:10">
       <c r="A256" s="5">
-        <v>140308</v>
+        <v>140307</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C256" s="5">
         <v>1403</v>
       </c>
       <c r="D256" s="5">
-        <v>140308</v>
+        <v>140307</v>
       </c>
       <c r="E256" s="5"/>
       <c r="F256" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H256" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I256" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J256" s="6"/>
     </row>
     <row r="257" ht="20.1" customHeight="1" spans="1:10">
       <c r="A257" s="5">
-        <v>140309</v>
+        <v>140308</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C257" s="5">
         <v>1403</v>
       </c>
       <c r="D257" s="5">
-        <v>140309</v>
+        <v>140308</v>
       </c>
       <c r="E257" s="5"/>
       <c r="F257" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G257" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H257" s="6" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="I257" s="6" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="J257" s="6"/>
     </row>
     <row r="258" ht="20.1" customHeight="1" spans="1:10">
       <c r="A258" s="5">
-        <v>140310</v>
+        <v>140309</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C258" s="5">
         <v>1403</v>
       </c>
       <c r="D258" s="5">
-        <v>140310</v>
+        <v>140309</v>
       </c>
       <c r="E258" s="5"/>
       <c r="F258" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G258" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H258" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I258" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J258" s="6"/>
     </row>
     <row r="259" ht="20.1" customHeight="1" spans="1:10">
       <c r="A259" s="5">
-        <v>140311</v>
+        <v>140310</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C259" s="5">
         <v>1403</v>
       </c>
       <c r="D259" s="5">
-        <v>140311</v>
+        <v>140310</v>
       </c>
       <c r="E259" s="5"/>
       <c r="F259" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G259" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H259" s="6" t="s">
-        <v>64</v>
+        <v>298</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>64</v>
+        <v>298</v>
       </c>
       <c r="J259" s="6"/>
     </row>
     <row r="260" ht="20.1" customHeight="1" spans="1:10">
       <c r="A260" s="5">
-        <v>140312</v>
+        <v>140311</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C260" s="5">
         <v>1403</v>
       </c>
       <c r="D260" s="5">
-        <v>140312</v>
+        <v>140311</v>
       </c>
       <c r="E260" s="5"/>
       <c r="F260" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H260" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J260" s="6"/>
     </row>
     <row r="261" ht="20.1" customHeight="1" spans="1:10">
       <c r="A261" s="5">
-        <v>140313</v>
+        <v>140312</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C261" s="5">
         <v>1403</v>
       </c>
       <c r="D261" s="5">
-        <v>140313</v>
+        <v>140312</v>
       </c>
       <c r="E261" s="5"/>
       <c r="F261" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G261" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H261" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I261" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J261" s="6"/>
     </row>
     <row r="262" ht="20.1" customHeight="1" spans="1:10">
       <c r="A262" s="5">
-        <v>140314</v>
+        <v>140313</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C262" s="5">
         <v>1403</v>
       </c>
       <c r="D262" s="5">
-        <v>140314</v>
+        <v>140313</v>
       </c>
       <c r="E262" s="5"/>
       <c r="F262" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H262" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I262" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J262" s="6"/>
     </row>
     <row r="263" ht="20.1" customHeight="1" spans="1:10">
       <c r="A263" s="5">
-        <v>140315</v>
+        <v>140314</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C263" s="5">
         <v>1403</v>
       </c>
       <c r="D263" s="5">
-        <v>140315</v>
+        <v>140314</v>
       </c>
       <c r="E263" s="5"/>
       <c r="F263" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G263" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H263" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I263" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J263" s="6"/>
     </row>
     <row r="264" ht="20.1" customHeight="1" spans="1:10">
       <c r="A264" s="5">
-        <v>1404</v>
+        <v>140315</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>299</v>
       </c>
       <c r="C264" s="5">
-        <v>14</v>
+        <v>1403</v>
       </c>
       <c r="D264" s="5">
-        <v>1404</v>
+        <v>140315</v>
       </c>
       <c r="E264" s="5"/>
       <c r="F264" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G264" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="H264" s="6"/>
+      <c r="H264" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I264" s="6" t="s">
-        <v>299</v>
+        <v>65</v>
       </c>
       <c r="J264" s="6"/>
     </row>
     <row r="265" ht="20.1" customHeight="1" spans="1:10">
       <c r="A265" s="5">
-        <v>140401</v>
+        <v>1404</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>301</v>
       </c>
       <c r="C265" s="5">
+        <v>14</v>
+      </c>
+      <c r="D265" s="5">
         <v>1404</v>
-      </c>
-      <c r="D265" s="5">
-        <v>140401</v>
       </c>
       <c r="E265" s="5"/>
       <c r="F265" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G265" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="H265" s="6" t="s">
-        <v>90</v>
-      </c>
+      <c r="H265" s="6"/>
       <c r="I265" s="6" t="s">
-        <v>90</v>
+        <v>301</v>
       </c>
       <c r="J265" s="6"/>
     </row>
     <row r="266" ht="20.1" customHeight="1" spans="1:10">
       <c r="A266" s="5">
-        <v>140402</v>
+        <v>140401</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C266" s="5">
         <v>1404</v>
       </c>
       <c r="D266" s="5">
-        <v>140402</v>
+        <v>140401</v>
       </c>
       <c r="E266" s="5"/>
       <c r="F266" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H266" s="6" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="J266" s="6"/>
     </row>
     <row r="267" ht="20.1" customHeight="1" spans="1:10">
       <c r="A267" s="5">
-        <v>140403</v>
+        <v>140402</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C267" s="5">
         <v>1404</v>
       </c>
       <c r="D267" s="5">
-        <v>140403</v>
+        <v>140402</v>
       </c>
       <c r="E267" s="5"/>
       <c r="F267" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G267" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H267" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J267" s="6"/>
     </row>
     <row r="268" ht="20.1" customHeight="1" spans="1:10">
       <c r="A268" s="5">
-        <v>140404</v>
+        <v>140403</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>303</v>
@@ -15493,7 +15497,7 @@
         <v>1404</v>
       </c>
       <c r="D268" s="5">
-        <v>140404</v>
+        <v>140403</v>
       </c>
       <c r="E268" s="5"/>
       <c r="F268" s="5" t="s">
@@ -15503,153 +15507,153 @@
         <v>304</v>
       </c>
       <c r="H268" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J268" s="6"/>
     </row>
     <row r="269" ht="20.1" customHeight="1" spans="1:10">
       <c r="A269" s="5">
-        <v>140405</v>
+        <v>140404</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C269" s="5">
         <v>1404</v>
       </c>
       <c r="D269" s="5">
-        <v>140405</v>
+        <v>140404</v>
       </c>
       <c r="E269" s="5"/>
       <c r="F269" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G269" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H269" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I269" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J269" s="6"/>
+    </row>
+    <row r="270" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A270" s="5">
+        <v>140405</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C270" s="5">
+        <v>1404</v>
+      </c>
+      <c r="D270" s="5">
+        <v>140405</v>
+      </c>
+      <c r="E270" s="5"/>
+      <c r="F270" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G270" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="H270" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="I269" s="6" t="s">
+      <c r="I270" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J269" s="6"/>
-    </row>
-    <row r="270" spans="10:10">
       <c r="J270" s="6"/>
     </row>
-    <row r="271" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A271" s="5">
-        <v>15</v>
-      </c>
-      <c r="B271" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C271" s="5">
-        <v>1</v>
-      </c>
-      <c r="D271" s="5">
-        <v>15</v>
-      </c>
-      <c r="E271" s="5"/>
-      <c r="F271" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G271" s="6"/>
-      <c r="H271" s="6"/>
-      <c r="I271" s="6" t="s">
-        <v>305</v>
-      </c>
+    <row r="271" spans="10:10">
       <c r="J271" s="6"/>
     </row>
     <row r="272" ht="20.1" customHeight="1" spans="1:10">
       <c r="A272" s="5">
-        <v>1501</v>
+        <v>15</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C272" s="5">
+        <v>1</v>
+      </c>
+      <c r="D272" s="5">
         <v>15</v>
-      </c>
-      <c r="D272" s="5">
-        <v>1501</v>
       </c>
       <c r="E272" s="5"/>
       <c r="F272" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G272" s="6" t="s">
-        <v>307</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G272" s="6"/>
       <c r="H272" s="6"/>
       <c r="I272" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J272" s="6"/>
     </row>
     <row r="273" ht="20.1" customHeight="1" spans="1:10">
       <c r="A273" s="5">
-        <v>150101</v>
+        <v>1501</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>308</v>
       </c>
       <c r="C273" s="5">
+        <v>15</v>
+      </c>
+      <c r="D273" s="5">
         <v>1501</v>
-      </c>
-      <c r="D273" s="5">
-        <v>150101</v>
       </c>
       <c r="E273" s="5"/>
       <c r="F273" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G273" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="H273" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="H273" s="6"/>
       <c r="I273" s="6" t="s">
-        <v>60</v>
+        <v>308</v>
       </c>
       <c r="J273" s="6"/>
     </row>
     <row r="274" ht="20.1" customHeight="1" spans="1:10">
       <c r="A274" s="5">
-        <v>150102</v>
+        <v>150101</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C274" s="5">
         <v>1501</v>
       </c>
       <c r="D274" s="5">
-        <v>150102</v>
+        <v>150101</v>
       </c>
       <c r="E274" s="5"/>
       <c r="F274" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H274" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J274" s="6"/>
     </row>
     <row r="275" ht="20.1" customHeight="1" spans="1:10">
       <c r="A275" s="5">
-        <v>150103</v>
+        <v>150102</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>310</v>
@@ -15658,332 +15662,334 @@
         <v>1501</v>
       </c>
       <c r="D275" s="5">
-        <v>150103</v>
+        <v>150102</v>
       </c>
       <c r="E275" s="5"/>
       <c r="F275" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G275" s="6" t="s">
         <v>311</v>
       </c>
       <c r="H275" s="6" t="s">
-        <v>295</v>
+        <v>61</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>295</v>
+        <v>61</v>
       </c>
       <c r="J275" s="6"/>
     </row>
     <row r="276" ht="20.1" customHeight="1" spans="1:10">
       <c r="A276" s="5">
-        <v>150104</v>
+        <v>150103</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C276" s="5">
         <v>1501</v>
       </c>
       <c r="D276" s="5">
-        <v>150104</v>
+        <v>150103</v>
       </c>
       <c r="E276" s="5"/>
       <c r="F276" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H276" s="6" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="J276" s="6"/>
     </row>
     <row r="277" ht="20.1" customHeight="1" spans="1:10">
       <c r="A277" s="5">
-        <v>150105</v>
+        <v>150104</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C277" s="5">
         <v>1501</v>
       </c>
       <c r="D277" s="5">
-        <v>150105</v>
+        <v>150104</v>
       </c>
       <c r="E277" s="5"/>
       <c r="F277" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G277" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H277" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J277" s="6"/>
     </row>
     <row r="278" ht="20.1" customHeight="1" spans="1:10">
       <c r="A278" s="5">
-        <v>150106</v>
+        <v>150105</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C278" s="5">
         <v>1501</v>
       </c>
       <c r="D278" s="5">
-        <v>150106</v>
+        <v>150105</v>
       </c>
       <c r="E278" s="5"/>
       <c r="F278" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H278" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J278" s="6"/>
     </row>
     <row r="279" ht="20.1" customHeight="1" spans="1:10">
       <c r="A279" s="5">
-        <v>150107</v>
+        <v>150106</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C279" s="5">
         <v>1501</v>
       </c>
       <c r="D279" s="5">
-        <v>150107</v>
+        <v>150106</v>
       </c>
       <c r="E279" s="5"/>
       <c r="F279" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G279" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H279" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J279" s="6"/>
     </row>
     <row r="280" ht="20.1" customHeight="1" spans="1:10">
       <c r="A280" s="5">
-        <v>150108</v>
+        <v>150107</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C280" s="5">
         <v>1501</v>
       </c>
       <c r="D280" s="5">
-        <v>150108</v>
+        <v>150107</v>
       </c>
       <c r="E280" s="5"/>
       <c r="F280" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J280" s="6"/>
     </row>
     <row r="281" ht="20.1" customHeight="1" spans="1:10">
       <c r="A281" s="5">
-        <v>150109</v>
+        <v>150108</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C281" s="5">
         <v>1501</v>
       </c>
       <c r="D281" s="5">
-        <v>150109</v>
+        <v>150108</v>
       </c>
       <c r="E281" s="5"/>
       <c r="F281" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G281" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H281" s="6" t="s">
-        <v>64</v>
+        <v>318</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>64</v>
+        <v>318</v>
       </c>
       <c r="J281" s="6"/>
     </row>
     <row r="282" ht="20.1" customHeight="1" spans="1:10">
       <c r="A282" s="5">
-        <v>150110</v>
+        <v>150109</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C282" s="5">
         <v>1501</v>
       </c>
       <c r="D282" s="5">
-        <v>150110</v>
+        <v>150109</v>
       </c>
       <c r="E282" s="5"/>
       <c r="F282" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G282" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J282" s="6"/>
     </row>
     <row r="283" ht="20.1" customHeight="1" spans="1:10">
       <c r="A283" s="5">
-        <v>150111</v>
+        <v>150110</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C283" s="5">
         <v>1501</v>
       </c>
       <c r="D283" s="5">
-        <v>150111</v>
+        <v>150110</v>
       </c>
       <c r="E283" s="5"/>
       <c r="F283" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G283" s="6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H283" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J283" s="6"/>
     </row>
     <row r="284" ht="20.1" customHeight="1" spans="1:10">
       <c r="A284" s="5">
-        <v>150112</v>
+        <v>150111</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C284" s="5">
         <v>1501</v>
       </c>
       <c r="D284" s="5">
-        <v>150112</v>
+        <v>150111</v>
       </c>
       <c r="E284" s="5"/>
       <c r="F284" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J284" s="6"/>
     </row>
     <row r="285" ht="20.1" customHeight="1" spans="1:10">
       <c r="A285" s="5">
-        <v>150113</v>
+        <v>150112</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C285" s="5">
         <v>1501</v>
       </c>
       <c r="D285" s="5">
-        <v>150113</v>
+        <v>150112</v>
       </c>
       <c r="E285" s="5"/>
       <c r="F285" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G285" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H285" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J285" s="6"/>
     </row>
     <row r="286" ht="20.1" customHeight="1" spans="1:10">
       <c r="A286" s="5">
-        <v>1502</v>
+        <v>150113</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>319</v>
       </c>
       <c r="C286" s="5">
-        <v>15</v>
+        <v>1501</v>
       </c>
       <c r="D286" s="5">
-        <v>1502</v>
+        <v>150113</v>
       </c>
       <c r="E286" s="5"/>
       <c r="F286" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G286" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="H286" s="6"/>
+      <c r="H286" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I286" s="6" t="s">
-        <v>319</v>
+        <v>65</v>
       </c>
       <c r="J286" s="6"/>
     </row>
     <row r="287" ht="20.1" customHeight="1" spans="1:10">
       <c r="A287" s="5">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
@@ -15992,7 +15998,7 @@
         <v>15</v>
       </c>
       <c r="D287" s="5">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E287" s="5"/>
       <c r="F287" s="5" t="s">
@@ -16008,150 +16014,148 @@
       <c r="J287" s="6"/>
     </row>
     <row r="288" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A288" s="7">
+      <c r="A288" s="5">
+        <v>1503</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C288" s="5">
+        <v>15</v>
+      </c>
+      <c r="D288" s="5">
+        <v>1503</v>
+      </c>
+      <c r="E288" s="5"/>
+      <c r="F288" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G288" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H288" s="6"/>
+      <c r="I288" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="J288" s="6"/>
+    </row>
+    <row r="289" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A289" s="7">
         <v>1504</v>
       </c>
-      <c r="B288" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="C288" s="7">
+      <c r="B289" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C289" s="7">
         <v>15</v>
       </c>
-      <c r="D288" s="7">
+      <c r="D289" s="7">
         <v>1504</v>
       </c>
-      <c r="E288" s="7"/>
-      <c r="F288" s="7" t="s">
+      <c r="E289" s="7"/>
+      <c r="F289" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G288" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="H288" s="8"/>
-      <c r="I288" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="J288" s="6"/>
-    </row>
-    <row r="289" s="1" customFormat="1" ht="11" customHeight="1" spans="1:10">
-      <c r="A289" s="9"/>
-      <c r="B289" s="10"/>
-      <c r="C289" s="11"/>
-      <c r="D289" s="11"/>
-      <c r="E289" s="11"/>
-      <c r="F289" s="11"/>
-      <c r="G289" s="10"/>
-      <c r="H289" s="10"/>
-      <c r="I289" s="14"/>
+      <c r="G289" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H289" s="8"/>
+      <c r="I289" s="8" t="s">
+        <v>325</v>
+      </c>
       <c r="J289" s="6"/>
     </row>
-    <row r="290" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A290" s="12">
+    <row r="290" s="1" customFormat="1" ht="11" customHeight="1" spans="1:10">
+      <c r="A290" s="9"/>
+      <c r="B290" s="10"/>
+      <c r="C290" s="11"/>
+      <c r="D290" s="11"/>
+      <c r="E290" s="11"/>
+      <c r="F290" s="11"/>
+      <c r="G290" s="10"/>
+      <c r="H290" s="10"/>
+      <c r="I290" s="14"/>
+      <c r="J290" s="6"/>
+    </row>
+    <row r="291" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A291" s="12">
         <v>16</v>
       </c>
-      <c r="B290" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="C290" s="12">
+      <c r="B291" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C291" s="12">
         <v>1</v>
       </c>
-      <c r="D290" s="12">
+      <c r="D291" s="12">
         <v>16</v>
       </c>
-      <c r="E290" s="12"/>
-      <c r="F290" s="12" t="s">
+      <c r="E291" s="12"/>
+      <c r="F291" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G290" s="13"/>
-      <c r="H290" s="13"/>
-      <c r="I290" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="J290" s="6"/>
-    </row>
-    <row r="291" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A291" s="5">
-        <v>1601</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C291" s="5">
-        <v>16</v>
-      </c>
-      <c r="D291" s="5">
-        <v>1601</v>
-      </c>
-      <c r="E291" s="5"/>
-      <c r="F291" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G291" s="6" t="s">
+      <c r="G291" s="13"/>
+      <c r="H291" s="13"/>
+      <c r="I291" s="13" t="s">
         <v>327</v>
-      </c>
-      <c r="H291" s="6"/>
-      <c r="I291" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="J291" s="6"/>
     </row>
     <row r="292" ht="20.1" customHeight="1" spans="1:10">
       <c r="A292" s="5">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>144</v>
+        <v>328</v>
       </c>
       <c r="C292" s="5">
         <v>16</v>
       </c>
       <c r="D292" s="5">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="E292" s="5"/>
       <c r="F292" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G292" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H292" s="6"/>
       <c r="I292" s="6" t="s">
-        <v>144</v>
+        <v>328</v>
       </c>
       <c r="J292" s="6"/>
     </row>
     <row r="293" ht="20.1" customHeight="1" spans="1:10">
       <c r="A293" s="5">
-        <v>160201</v>
+        <v>1602</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C293" s="5">
+        <v>16</v>
+      </c>
+      <c r="D293" s="5">
         <v>1602</v>
-      </c>
-      <c r="D293" s="5">
-        <v>160201</v>
       </c>
       <c r="E293" s="5"/>
       <c r="F293" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G293" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="H293" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="H293" s="6"/>
       <c r="I293" s="6" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="J293" s="6"/>
     </row>
     <row r="294" ht="20.1" customHeight="1" spans="1:10">
       <c r="A294" s="5">
-        <v>160202</v>
+        <v>160201</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>146</v>
@@ -16160,54 +16164,54 @@
         <v>1602</v>
       </c>
       <c r="D294" s="5">
-        <v>160202</v>
+        <v>160201</v>
       </c>
       <c r="E294" s="5"/>
       <c r="F294" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G294" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H294" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J294" s="6"/>
     </row>
     <row r="295" ht="20.1" customHeight="1" spans="1:10">
       <c r="A295" s="5">
-        <v>160203</v>
+        <v>160202</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C295" s="5">
         <v>1602</v>
       </c>
       <c r="D295" s="5">
-        <v>160203</v>
+        <v>160202</v>
       </c>
       <c r="E295" s="5"/>
       <c r="F295" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G295" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H295" s="6" t="s">
-        <v>331</v>
+        <v>61</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>331</v>
+        <v>61</v>
       </c>
       <c r="J295" s="6"/>
     </row>
     <row r="296" ht="20.1" customHeight="1" spans="1:10">
       <c r="A296" s="5">
-        <v>160204</v>
+        <v>160203</v>
       </c>
       <c r="B296" s="6" t="s">
         <v>148</v>
@@ -16216,26 +16220,26 @@
         <v>1602</v>
       </c>
       <c r="D296" s="5">
-        <v>160204</v>
+        <v>160203</v>
       </c>
       <c r="E296" s="5"/>
       <c r="F296" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G296" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H296" s="6" t="s">
-        <v>64</v>
+        <v>333</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>64</v>
+        <v>333</v>
       </c>
       <c r="J296" s="6"/>
     </row>
     <row r="297" ht="20.1" customHeight="1" spans="1:10">
       <c r="A297" s="5">
-        <v>160205</v>
+        <v>160204</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>148</v>
@@ -16244,54 +16248,54 @@
         <v>1602</v>
       </c>
       <c r="D297" s="5">
-        <v>160205</v>
+        <v>160204</v>
       </c>
       <c r="E297" s="5"/>
       <c r="F297" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G297" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H297" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I297" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J297" s="6"/>
     </row>
     <row r="298" ht="20.1" customHeight="1" spans="1:10">
       <c r="A298" s="5">
-        <v>160206</v>
+        <v>160205</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C298" s="5">
         <v>1602</v>
       </c>
       <c r="D298" s="5">
-        <v>160206</v>
+        <v>160205</v>
       </c>
       <c r="E298" s="5"/>
       <c r="F298" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G298" s="6" t="s">
         <v>332</v>
       </c>
       <c r="H298" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J298" s="6"/>
     </row>
     <row r="299" ht="20.1" customHeight="1" spans="1:10">
       <c r="A299" s="5">
-        <v>160207</v>
+        <v>160206</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>150</v>
@@ -16300,26 +16304,26 @@
         <v>1602</v>
       </c>
       <c r="D299" s="5">
-        <v>160207</v>
+        <v>160206</v>
       </c>
       <c r="E299" s="5"/>
       <c r="F299" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G299" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H299" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J299" s="6"/>
     </row>
     <row r="300" ht="20.1" customHeight="1" spans="1:10">
       <c r="A300" s="5">
-        <v>160208</v>
+        <v>160207</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>150</v>
@@ -16328,136 +16332,136 @@
         <v>1602</v>
       </c>
       <c r="D300" s="5">
-        <v>160208</v>
+        <v>160207</v>
       </c>
       <c r="E300" s="5"/>
       <c r="F300" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G300" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H300" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I300" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J300" s="6"/>
     </row>
     <row r="301" ht="20.1" customHeight="1" spans="1:10">
       <c r="A301" s="5">
-        <v>1603</v>
+        <v>160208</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>333</v>
+        <v>150</v>
       </c>
       <c r="C301" s="5">
-        <v>16</v>
+        <v>1602</v>
       </c>
       <c r="D301" s="5">
-        <v>1603</v>
+        <v>160208</v>
       </c>
       <c r="E301" s="5"/>
       <c r="F301" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G301" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="H301" s="6"/>
+      <c r="H301" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I301" s="6" t="s">
-        <v>333</v>
+        <v>65</v>
       </c>
       <c r="J301" s="6"/>
     </row>
     <row r="302" ht="20.1" customHeight="1" spans="1:10">
       <c r="A302" s="5">
-        <v>160301</v>
+        <v>1603</v>
       </c>
       <c r="B302" s="6" t="s">
         <v>335</v>
       </c>
       <c r="C302" s="5">
+        <v>16</v>
+      </c>
+      <c r="D302" s="5">
         <v>1603</v>
-      </c>
-      <c r="D302" s="5">
-        <v>160301</v>
       </c>
       <c r="E302" s="5"/>
       <c r="F302" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G302" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="H302" s="6" t="s">
-        <v>156</v>
-      </c>
+      <c r="H302" s="6"/>
       <c r="I302" s="6" t="s">
-        <v>156</v>
+        <v>335</v>
       </c>
       <c r="J302" s="6"/>
     </row>
     <row r="303" ht="20.1" customHeight="1" spans="1:10">
       <c r="A303" s="5">
-        <v>160302</v>
+        <v>160301</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C303" s="5">
         <v>1603</v>
       </c>
       <c r="D303" s="5">
-        <v>160302</v>
+        <v>160301</v>
       </c>
       <c r="E303" s="5"/>
       <c r="F303" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G303" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H303" s="6" t="s">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="J303" s="6"/>
     </row>
     <row r="304" ht="20.1" customHeight="1" spans="1:10">
       <c r="A304" s="5">
-        <v>160303</v>
+        <v>160302</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C304" s="5">
         <v>1603</v>
       </c>
       <c r="D304" s="5">
-        <v>160303</v>
+        <v>160302</v>
       </c>
       <c r="E304" s="5"/>
       <c r="F304" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G304" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H304" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I304" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J304" s="6"/>
     </row>
     <row r="305" ht="20.1" customHeight="1" spans="1:10">
       <c r="A305" s="5">
-        <v>160304</v>
+        <v>160303</v>
       </c>
       <c r="B305" s="6" t="s">
         <v>337</v>
@@ -16466,7 +16470,7 @@
         <v>1603</v>
       </c>
       <c r="D305" s="5">
-        <v>160304</v>
+        <v>160303</v>
       </c>
       <c r="E305" s="5"/>
       <c r="F305" s="5" t="s">
@@ -16476,261 +16480,264 @@
         <v>338</v>
       </c>
       <c r="H305" s="6" t="s">
-        <v>339</v>
+        <v>61</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>339</v>
+        <v>61</v>
       </c>
       <c r="J305" s="6"/>
     </row>
     <row r="306" ht="20.1" customHeight="1" spans="1:10">
       <c r="A306" s="5">
-        <v>160305</v>
+        <v>160304</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C306" s="5">
         <v>1603</v>
       </c>
       <c r="D306" s="5">
-        <v>160305</v>
+        <v>160304</v>
       </c>
       <c r="E306" s="5"/>
       <c r="F306" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G306" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H306" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J306" s="6"/>
     </row>
     <row r="307" ht="20.1" customHeight="1" spans="1:10">
       <c r="A307" s="5">
-        <v>160306</v>
+        <v>160305</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C307" s="5">
         <v>1603</v>
       </c>
       <c r="D307" s="5">
-        <v>160306</v>
+        <v>160305</v>
       </c>
       <c r="E307" s="5"/>
       <c r="F307" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G307" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H307" s="6" t="s">
-        <v>64</v>
+        <v>342</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>64</v>
+        <v>342</v>
       </c>
       <c r="J307" s="6"/>
     </row>
     <row r="308" ht="20.1" customHeight="1" spans="1:10">
       <c r="A308" s="5">
-        <v>160307</v>
+        <v>160306</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C308" s="5">
         <v>1603</v>
       </c>
       <c r="D308" s="5">
-        <v>160307</v>
+        <v>160306</v>
       </c>
       <c r="E308" s="5"/>
       <c r="F308" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G308" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H308" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I308" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J308" s="6"/>
     </row>
     <row r="309" ht="20.1" customHeight="1" spans="1:10">
       <c r="A309" s="5">
-        <v>160308</v>
+        <v>160307</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C309" s="5">
         <v>1603</v>
       </c>
       <c r="D309" s="5">
-        <v>160308</v>
+        <v>160307</v>
       </c>
       <c r="E309" s="5"/>
       <c r="F309" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G309" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H309" s="6" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="I309" s="6" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="J309" s="6"/>
     </row>
     <row r="310" ht="20.1" customHeight="1" spans="1:10">
       <c r="A310" s="5">
-        <v>160309</v>
+        <v>160308</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C310" s="5">
         <v>1603</v>
       </c>
       <c r="D310" s="5">
-        <v>160309</v>
+        <v>160308</v>
       </c>
       <c r="E310" s="5"/>
       <c r="F310" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G310" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H310" s="6" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="J310" s="6"/>
     </row>
     <row r="311" ht="20.1" customHeight="1" spans="1:10">
       <c r="A311" s="5">
-        <v>160310</v>
+        <v>160309</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C311" s="5">
         <v>1603</v>
       </c>
       <c r="D311" s="5">
-        <v>160310</v>
+        <v>160309</v>
       </c>
       <c r="E311" s="5"/>
       <c r="F311" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G311" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H311" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J311" s="6"/>
     </row>
     <row r="312" ht="20.1" customHeight="1" spans="1:10">
       <c r="A312" s="5">
-        <v>1608</v>
+        <v>160310</v>
       </c>
       <c r="B312" s="6" t="s">
         <v>343</v>
       </c>
       <c r="C312" s="5">
-        <v>16</v>
+        <v>1603</v>
       </c>
       <c r="D312" s="5">
-        <v>1608</v>
+        <v>160310</v>
       </c>
       <c r="E312" s="5"/>
       <c r="F312" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G312" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="H312" s="6"/>
+      <c r="H312" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I312" s="6" t="s">
-        <v>343</v>
+        <v>65</v>
       </c>
       <c r="J312" s="6"/>
     </row>
     <row r="313" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A313" s="7">
+      <c r="A313" s="5">
+        <v>1608</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C313" s="5">
+        <v>16</v>
+      </c>
+      <c r="D313" s="5">
+        <v>1608</v>
+      </c>
+      <c r="E313" s="5"/>
+      <c r="F313" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G313" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="H313" s="6"/>
+      <c r="I313" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="J313" s="6"/>
+    </row>
+    <row r="314" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A314" s="7">
         <v>1604</v>
       </c>
-      <c r="B313" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="C313" s="7">
+      <c r="B314" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C314" s="7">
         <v>16</v>
       </c>
-      <c r="D313" s="7">
+      <c r="D314" s="7">
         <v>1604</v>
       </c>
-      <c r="E313" s="7"/>
-      <c r="F313" s="7" t="s">
+      <c r="E314" s="7"/>
+      <c r="F314" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G313" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="H313" s="8"/>
-      <c r="I313" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="J313" s="6"/>
-    </row>
-    <row r="314" s="2" customFormat="1" spans="1:10">
-      <c r="A314" s="5">
+      <c r="G314" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="H314" s="8"/>
+      <c r="I314" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="J314" s="6"/>
+    </row>
+    <row r="315" s="2" customFormat="1" spans="1:10">
+      <c r="A315" s="5">
         <v>1605</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C314" s="5">
-        <v>16</v>
-      </c>
-      <c r="D314" s="5">
-        <v>1605</v>
-      </c>
-      <c r="E314" s="5"/>
-      <c r="F314" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G314" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="I314" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="J314" s="6"/>
-    </row>
-    <row r="315" customFormat="1" spans="1:10">
-      <c r="A315" s="5">
-        <v>1606</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>349</v>
@@ -16739,16 +16746,15 @@
         <v>16</v>
       </c>
       <c r="D315" s="5">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E315" s="5"/>
       <c r="F315" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G315" s="2" t="s">
+      <c r="G315" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="H315" s="2"/>
       <c r="I315" s="2" t="s">
         <v>349</v>
       </c>
@@ -16756,7 +16762,7 @@
     </row>
     <row r="316" customFormat="1" spans="1:10">
       <c r="A316" s="5">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>351</v>
@@ -16765,7 +16771,7 @@
         <v>16</v>
       </c>
       <c r="D316" s="5">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E316" s="5"/>
       <c r="F316" s="5" t="s">
@@ -16780,42 +16786,44 @@
       </c>
       <c r="J316" s="6"/>
     </row>
-    <row r="317" ht="20.1" customHeight="1" spans="1:10">
+    <row r="317" customFormat="1" spans="1:10">
       <c r="A317" s="5">
-        <v>2</v>
-      </c>
-      <c r="B317" s="6" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>353</v>
       </c>
       <c r="C317" s="5">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="D317" s="5">
-        <v>2</v>
+        <v>1607</v>
       </c>
       <c r="E317" s="5"/>
       <c r="F317" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G317" s="6"/>
-      <c r="H317" s="6"/>
-      <c r="I317" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G317" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H317" s="2"/>
+      <c r="I317" s="2" t="s">
         <v>353</v>
       </c>
       <c r="J317" s="6"/>
     </row>
     <row r="318" ht="20.1" customHeight="1" spans="1:10">
       <c r="A318" s="5">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C318" s="5">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D318" s="5">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E318" s="5"/>
       <c r="F318" s="5" t="s">
@@ -16824,39 +16832,37 @@
       <c r="G318" s="6"/>
       <c r="H318" s="6"/>
       <c r="I318" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J318" s="6"/>
     </row>
     <row r="319" ht="20.1" customHeight="1" spans="1:10">
       <c r="A319" s="5">
-        <v>2110</v>
+        <v>21</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C319" s="5">
+        <v>2</v>
+      </c>
+      <c r="D319" s="5">
         <v>21</v>
-      </c>
-      <c r="D319" s="5">
-        <v>2110</v>
       </c>
       <c r="E319" s="5"/>
       <c r="F319" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G319" s="6" t="s">
-        <v>356</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G319" s="6"/>
       <c r="H319" s="6"/>
       <c r="I319" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J319" s="6"/>
     </row>
     <row r="320" ht="20.1" customHeight="1" spans="1:10">
       <c r="A320" s="5">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B320" s="6" t="s">
         <v>357</v>
@@ -16865,7 +16871,7 @@
         <v>21</v>
       </c>
       <c r="D320" s="5">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="E320" s="5"/>
       <c r="F320" s="5" t="s">
@@ -16882,22 +16888,24 @@
     </row>
     <row r="321" ht="20.1" customHeight="1" spans="1:10">
       <c r="A321" s="5">
-        <v>22</v>
+        <v>2111</v>
       </c>
       <c r="B321" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C321" s="5">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D321" s="5">
-        <v>22</v>
+        <v>2111</v>
       </c>
       <c r="E321" s="5"/>
       <c r="F321" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G321" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G321" s="6" t="s">
+        <v>360</v>
+      </c>
       <c r="H321" s="6"/>
       <c r="I321" s="6" t="s">
         <v>359</v>
@@ -16906,33 +16914,31 @@
     </row>
     <row r="322" ht="20.1" customHeight="1" spans="1:10">
       <c r="A322" s="5">
-        <v>2201</v>
+        <v>22</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C322" s="5">
+        <v>2</v>
+      </c>
+      <c r="D322" s="5">
         <v>22</v>
-      </c>
-      <c r="D322" s="5">
-        <v>2201</v>
       </c>
       <c r="E322" s="5"/>
       <c r="F322" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G322" s="6" t="s">
-        <v>361</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G322" s="6"/>
       <c r="H322" s="6"/>
       <c r="I322" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J322" s="6"/>
     </row>
     <row r="323" ht="20.1" customHeight="1" spans="1:10">
       <c r="A323" s="5">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B323" s="6" t="s">
         <v>362</v>
@@ -16941,7 +16947,7 @@
         <v>22</v>
       </c>
       <c r="D323" s="5">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="E323" s="5"/>
       <c r="F323" s="5" t="s">
@@ -16958,7 +16964,7 @@
     </row>
     <row r="324" ht="20.1" customHeight="1" spans="1:10">
       <c r="A324" s="5">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B324" s="6" t="s">
         <v>364</v>
@@ -16967,7 +16973,7 @@
         <v>22</v>
       </c>
       <c r="D324" s="5">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="E324" s="5"/>
       <c r="F324" s="5" t="s">
@@ -16984,22 +16990,24 @@
     </row>
     <row r="325" ht="20.1" customHeight="1" spans="1:10">
       <c r="A325" s="5">
-        <v>23</v>
+        <v>2203</v>
       </c>
       <c r="B325" s="6" t="s">
         <v>366</v>
       </c>
       <c r="C325" s="5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D325" s="5">
-        <v>23</v>
+        <v>2203</v>
       </c>
       <c r="E325" s="5"/>
       <c r="F325" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G325" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G325" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="H325" s="6"/>
       <c r="I325" s="6" t="s">
         <v>366</v>
@@ -17008,48 +17016,48 @@
     </row>
     <row r="326" ht="20.1" customHeight="1" spans="1:10">
       <c r="A326" s="5">
-        <v>2301</v>
+        <v>23</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C326" s="5">
+        <v>2</v>
+      </c>
+      <c r="D326" s="5">
         <v>23</v>
-      </c>
-      <c r="D326" s="5">
-        <v>2301</v>
       </c>
       <c r="E326" s="5"/>
       <c r="F326" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G326" s="6" t="s">
-        <v>368</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G326" s="6"/>
       <c r="H326" s="6"/>
       <c r="I326" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J326" s="6"/>
     </row>
     <row r="327" ht="20.1" customHeight="1" spans="1:10">
       <c r="A327" s="5">
-        <v>2302</v>
-      </c>
-      <c r="B327" s="15" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B327" s="6" t="s">
         <v>369</v>
       </c>
       <c r="C327" s="5">
         <v>23</v>
       </c>
       <c r="D327" s="5">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="E327" s="5"/>
       <c r="F327" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G327" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="G327" s="6" t="s">
+        <v>370</v>
+      </c>
       <c r="H327" s="6"/>
       <c r="I327" s="6" t="s">
         <v>369</v>
@@ -17058,109 +17066,107 @@
     </row>
     <row r="328" ht="20.1" customHeight="1" spans="1:10">
       <c r="A328" s="5">
-        <v>23021</v>
+        <v>2302</v>
       </c>
       <c r="B328" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C328" s="5">
+        <v>23</v>
+      </c>
+      <c r="D328" s="5">
         <v>2302</v>
-      </c>
-      <c r="D328" s="5">
-        <v>23021</v>
       </c>
       <c r="E328" s="5"/>
       <c r="F328" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G328" s="15" t="s">
-        <v>371</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G328" s="15"/>
       <c r="H328" s="6"/>
       <c r="I328" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J328" s="6"/>
     </row>
     <row r="329" ht="20.1" customHeight="1" spans="1:10">
       <c r="A329" s="5">
-        <v>23022</v>
+        <v>23021</v>
       </c>
       <c r="B329" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C329" s="5">
         <v>2302</v>
       </c>
       <c r="D329" s="5">
-        <v>23022</v>
+        <v>23021</v>
       </c>
       <c r="E329" s="5"/>
       <c r="F329" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G329" s="15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H329" s="6"/>
       <c r="I329" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J329" s="6"/>
     </row>
     <row r="330" ht="20.1" customHeight="1" spans="1:10">
       <c r="A330" s="5">
-        <v>2303</v>
-      </c>
-      <c r="B330" s="6" t="s">
-        <v>305</v>
+        <v>23022</v>
+      </c>
+      <c r="B330" s="15" t="s">
+        <v>375</v>
       </c>
       <c r="C330" s="5">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D330" s="5">
-        <v>2303</v>
+        <v>23022</v>
       </c>
       <c r="E330" s="5"/>
       <c r="F330" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G330" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G330" s="15" t="s">
+        <v>376</v>
+      </c>
       <c r="H330" s="6"/>
       <c r="I330" s="6" t="s">
-        <v>305</v>
+        <v>377</v>
       </c>
       <c r="J330" s="6"/>
     </row>
     <row r="331" ht="20.1" customHeight="1" spans="1:10">
       <c r="A331" s="5">
-        <v>23031</v>
+        <v>2303</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>376</v>
+        <v>307</v>
       </c>
       <c r="C331" s="5">
+        <v>23</v>
+      </c>
+      <c r="D331" s="5">
         <v>2303</v>
-      </c>
-      <c r="D331" s="5">
-        <v>23031</v>
       </c>
       <c r="E331" s="5"/>
       <c r="F331" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G331" s="6" t="s">
-        <v>377</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G331" s="6"/>
       <c r="H331" s="6"/>
       <c r="I331" s="6" t="s">
-        <v>376</v>
+        <v>307</v>
       </c>
       <c r="J331" s="6"/>
     </row>
     <row r="332" ht="20.1" customHeight="1" spans="1:10">
       <c r="A332" s="5">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B332" s="6" t="s">
         <v>378</v>
@@ -17169,7 +17175,7 @@
         <v>2303</v>
       </c>
       <c r="D332" s="5">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="E332" s="5"/>
       <c r="F332" s="5" t="s">
@@ -17186,7 +17192,7 @@
     </row>
     <row r="333" ht="20.1" customHeight="1" spans="1:10">
       <c r="A333" s="5">
-        <v>23033</v>
+        <v>23032</v>
       </c>
       <c r="B333" s="6" t="s">
         <v>380</v>
@@ -17195,7 +17201,7 @@
         <v>2303</v>
       </c>
       <c r="D333" s="5">
-        <v>23033</v>
+        <v>23032</v>
       </c>
       <c r="E333" s="5"/>
       <c r="F333" s="5" t="s">
@@ -17212,7 +17218,7 @@
     </row>
     <row r="334" ht="20.1" customHeight="1" spans="1:10">
       <c r="A334" s="5">
-        <v>23034</v>
+        <v>23033</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>382</v>
@@ -17221,7 +17227,7 @@
         <v>2303</v>
       </c>
       <c r="D334" s="5">
-        <v>23034</v>
+        <v>23033</v>
       </c>
       <c r="E334" s="5"/>
       <c r="F334" s="5" t="s">
@@ -17236,59 +17242,59 @@
       </c>
       <c r="J334" s="6"/>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" ht="20.1" customHeight="1" spans="1:10">
       <c r="A335" s="5">
-        <v>2304</v>
+        <v>23034</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>384</v>
       </c>
       <c r="C335" s="5">
-        <v>23</v>
+        <v>2303</v>
       </c>
       <c r="D335" s="5">
-        <v>2304</v>
+        <v>23034</v>
       </c>
       <c r="E335" s="5"/>
       <c r="F335" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G335" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G335" s="6" t="s">
+        <v>385</v>
+      </c>
       <c r="H335" s="6"/>
       <c r="I335" s="6" t="s">
         <v>384</v>
       </c>
       <c r="J335" s="6"/>
     </row>
-    <row r="336" ht="20.1" customHeight="1" spans="1:10">
+    <row r="336" spans="1:10">
       <c r="A336" s="5">
-        <v>23041</v>
+        <v>2304</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C336" s="5">
+        <v>23</v>
+      </c>
+      <c r="D336" s="5">
         <v>2304</v>
-      </c>
-      <c r="D336" s="5">
-        <v>23041</v>
       </c>
       <c r="E336" s="5"/>
       <c r="F336" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G336" s="6" t="s">
-        <v>386</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G336" s="6"/>
       <c r="H336" s="6"/>
       <c r="I336" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J336" s="6"/>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" ht="20.1" customHeight="1" spans="1:10">
       <c r="A337" s="5">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="B337" s="6" t="s">
         <v>387</v>
@@ -17297,7 +17303,7 @@
         <v>2304</v>
       </c>
       <c r="D337" s="5">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="E337" s="5"/>
       <c r="F337" s="5" t="s">
@@ -17314,7 +17320,7 @@
     </row>
     <row r="338" spans="1:10">
       <c r="A338" s="5">
-        <v>23043</v>
+        <v>23042</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>389</v>
@@ -17323,7 +17329,7 @@
         <v>2304</v>
       </c>
       <c r="D338" s="5">
-        <v>23043</v>
+        <v>23042</v>
       </c>
       <c r="E338" s="5"/>
       <c r="F338" s="5" t="s">
@@ -17334,89 +17340,89 @@
       </c>
       <c r="H338" s="6"/>
       <c r="I338" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J338" s="6"/>
+    </row>
+    <row r="339" spans="1:10">
+      <c r="A339" s="5">
+        <v>23043</v>
+      </c>
+      <c r="B339" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="J338" s="6"/>
-    </row>
-    <row r="339" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A339" s="5">
-        <v>23044</v>
-      </c>
-      <c r="B339" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="C339" s="5">
         <v>2304</v>
       </c>
       <c r="D339" s="5">
-        <v>23044</v>
+        <v>23043</v>
       </c>
       <c r="E339" s="5"/>
       <c r="F339" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G339" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H339" s="6"/>
       <c r="I339" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="J339" s="6"/>
+    </row>
+    <row r="340" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A340" s="5">
+        <v>23044</v>
+      </c>
+      <c r="B340" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="J339" s="6"/>
-    </row>
-    <row r="340" spans="1:10">
-      <c r="A340" s="5">
-        <v>2305</v>
-      </c>
-      <c r="B340" s="6" t="s">
-        <v>395</v>
-      </c>
       <c r="C340" s="5">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D340" s="5">
-        <v>2305</v>
+        <v>23044</v>
       </c>
       <c r="E340" s="5"/>
       <c r="F340" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G340" s="5"/>
-      <c r="H340" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G340" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="H340" s="6"/>
       <c r="I340" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J340" s="6"/>
     </row>
     <row r="341" spans="1:10">
       <c r="A341" s="5">
-        <v>23051</v>
+        <v>2305</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C341" s="5">
+        <v>23</v>
+      </c>
+      <c r="D341" s="5">
         <v>2305</v>
-      </c>
-      <c r="D341" s="5">
-        <v>23051</v>
       </c>
       <c r="E341" s="5"/>
       <c r="F341" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G341" s="6" t="s">
-        <v>397</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G341" s="5"/>
       <c r="H341" s="5"/>
       <c r="I341" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J341" s="6"/>
     </row>
     <row r="342" spans="1:10">
       <c r="A342" s="5">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>398</v>
@@ -17425,7 +17431,7 @@
         <v>2305</v>
       </c>
       <c r="D342" s="5">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="E342" s="5"/>
       <c r="F342" s="5" t="s">
@@ -17434,7 +17440,7 @@
       <c r="G342" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="H342" s="6"/>
+      <c r="H342" s="5"/>
       <c r="I342" s="6" t="s">
         <v>398</v>
       </c>
@@ -17442,22 +17448,24 @@
     </row>
     <row r="343" spans="1:10">
       <c r="A343" s="5">
-        <v>24</v>
+        <v>23052</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>400</v>
       </c>
       <c r="C343" s="5">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D343" s="5">
-        <v>24</v>
+        <v>23052</v>
       </c>
       <c r="E343" s="5"/>
       <c r="F343" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G343" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G343" s="6" t="s">
+        <v>401</v>
+      </c>
       <c r="H343" s="6"/>
       <c r="I343" s="6" t="s">
         <v>400</v>
@@ -17466,83 +17474,81 @@
     </row>
     <row r="344" spans="1:10">
       <c r="A344" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C344" s="5">
         <v>2</v>
       </c>
       <c r="D344" s="5">
-        <v>25</v>
-      </c>
-      <c r="E344" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="E344" s="5"/>
       <c r="F344" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
       <c r="I344" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J344" s="6"/>
     </row>
     <row r="345" spans="1:10">
       <c r="A345" s="5">
-        <v>2501</v>
+        <v>25</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C345" s="5">
+        <v>2</v>
+      </c>
+      <c r="D345" s="5">
         <v>25</v>
-      </c>
-      <c r="D345" s="5">
-        <v>2501</v>
       </c>
       <c r="E345" s="6"/>
       <c r="F345" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G345" s="6" t="s">
-        <v>403</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G345" s="6"/>
       <c r="H345" s="6"/>
       <c r="I345" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J345" s="6"/>
     </row>
     <row r="346" spans="1:10">
       <c r="A346" s="5">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C346" s="5">
         <v>25</v>
       </c>
       <c r="D346" s="5">
-        <v>2502</v>
-      </c>
-      <c r="E346" s="5"/>
+        <v>2501</v>
+      </c>
+      <c r="E346" s="6"/>
       <c r="F346" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G346" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="H346" s="6"/>
+      <c r="I346" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="H346" s="5"/>
-      <c r="I346" s="6" t="s">
-        <v>405</v>
-      </c>
       <c r="J346" s="6"/>
     </row>
-    <row r="347" s="2" customFormat="1" spans="1:10">
+    <row r="347" spans="1:10">
       <c r="A347" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B347" s="6" t="s">
         <v>407</v>
@@ -17551,17 +17557,43 @@
         <v>25</v>
       </c>
       <c r="D347" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="E347" s="5"/>
       <c r="F347" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G347" s="6"/>
-      <c r="I347" s="2" t="s">
+      <c r="G347" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="H347" s="5"/>
+      <c r="I347" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="J347" s="2" t="b">
+      <c r="J347" s="6"/>
+    </row>
+    <row r="348" s="2" customFormat="1" spans="1:10">
+      <c r="A348" s="5">
+        <v>2503</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C348" s="5">
+        <v>25</v>
+      </c>
+      <c r="D348" s="5">
+        <v>2503</v>
+      </c>
+      <c r="E348" s="5"/>
+      <c r="F348" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G348" s="6"/>
+      <c r="I348" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J348" s="2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800" tabRatio="500" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="17775" tabRatio="500" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="412">
   <si>
     <t>Id</t>
   </si>
@@ -956,6 +956,12 @@
   </si>
   <si>
     <t>CugaCalibration.Views.Laser.Attenuator.Children.Review</t>
+  </si>
+  <si>
+    <t>DOE Angle</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Laser.LaserDOEAngleCalibrationViewModel</t>
   </si>
   <si>
     <t>AOD</t>
@@ -1714,7 +1720,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1785,6 +1791,15 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1933,7 +1948,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1945,34 +1960,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2056,11 +2071,11 @@
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2104,6 +2119,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2580,14 +2598,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="20.6333333333333" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" ht="23.25" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2617,525 +2635,525 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="17">
         <v>1</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="17">
         <v>666666</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="18">
         <v>1</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="19" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="18">
         <v>666666</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="17">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <v>1</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="20" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="18">
         <v>111111</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3153,12 +3171,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3170,172 +3188,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="17">
         <v>1</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17">
-        <v>2</v>
-      </c>
-      <c r="C3" s="17">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="17">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="18">
         <v>3</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3348,12 +3366,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3365,172 +3383,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="17">
         <v>1</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17">
-        <v>2</v>
-      </c>
-      <c r="C3" s="17">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="17">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="18">
         <v>3</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3543,12 +3561,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:6">
+    <row r="1" ht="23.25" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3569,340 +3587,340 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="17">
         <v>-1</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="17">
         <v>0</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="17">
         <v>1</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="18">
         <v>-1</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="18">
         <v>1</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="18">
         <v>3</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="17">
+      <c r="A4" s="18">
         <v>21</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="17">
-        <v>2</v>
-      </c>
-      <c r="D4" s="17">
+      <c r="C4" s="18">
+        <v>2</v>
+      </c>
+      <c r="D4" s="18">
         <v>21</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="18">
         <v>3</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="17">
+      <c r="A5" s="18">
         <v>211</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <v>21</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <v>211</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <v>1</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="17">
+      <c r="A6" s="18">
         <v>212</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <v>21</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <v>212</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <v>3</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="17">
+      <c r="A7" s="18">
         <v>22</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="17">
-        <v>2</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="C7" s="18">
+        <v>2</v>
+      </c>
+      <c r="D7" s="18">
         <v>22</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <v>3</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="17">
+      <c r="A8" s="18">
         <v>221</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <v>22</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <v>221</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <v>3</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="18" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="17">
+      <c r="A9" s="18">
         <v>222</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <v>22</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <v>222</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <v>3</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="18" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3915,12 +3933,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3938,234 +3956,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="17">
         <v>0</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="16">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="17">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4178,14 +4196,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="20.6333333333333" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
     <col min="4" max="5" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4203,234 +4221,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="17">
         <v>0</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="16">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="17">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4443,12 +4461,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4460,154 +4478,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4620,12 +4638,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C313"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4637,10 +4655,10 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="17">
         <v>2</v>
       </c>
       <c r="C2" s="5">
@@ -4648,10 +4666,10 @@
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
         <v>2</v>
       </c>
       <c r="C3" s="5">
@@ -4659,10 +4677,10 @@
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="16">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="17">
         <v>2</v>
       </c>
       <c r="C4" s="5">
@@ -4670,10 +4688,10 @@
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="16">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="17">
         <v>2</v>
       </c>
       <c r="C5" s="5">
@@ -4681,10 +4699,10 @@
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="17">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="17">
         <v>2</v>
       </c>
       <c r="C6" s="5">
@@ -4692,10 +4710,10 @@
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="16">
+      <c r="A7" s="17">
         <v>6</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="17">
         <v>2</v>
       </c>
       <c r="C7" s="5">
@@ -4703,10 +4721,10 @@
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="16">
+      <c r="A8" s="17">
         <v>7</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="17">
         <v>2</v>
       </c>
       <c r="C8" s="5">
@@ -4714,10 +4732,10 @@
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="17">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="17">
         <v>2</v>
       </c>
       <c r="C9" s="5">
@@ -4725,10 +4743,10 @@
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="16">
+      <c r="A10" s="17">
         <v>9</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="17">
         <v>2</v>
       </c>
       <c r="C10" s="5">
@@ -4736,10 +4754,10 @@
       </c>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="16">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="17">
         <v>2</v>
       </c>
       <c r="C11" s="5">
@@ -4747,10 +4765,10 @@
       </c>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="17">
+      <c r="A12" s="18">
         <v>11</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="17">
         <v>2</v>
       </c>
       <c r="C12" s="5">
@@ -4758,10 +4776,10 @@
       </c>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="16">
+      <c r="A13" s="17">
         <v>12</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="17">
         <v>2</v>
       </c>
       <c r="C13" s="5">
@@ -4769,10 +4787,10 @@
       </c>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="16">
+      <c r="A14" s="17">
         <v>13</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="17">
         <v>2</v>
       </c>
       <c r="C14" s="5">
@@ -4780,10 +4798,10 @@
       </c>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="17">
+      <c r="A15" s="18">
         <v>14</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="17">
         <v>2</v>
       </c>
       <c r="C15" s="5">
@@ -4791,10 +4809,10 @@
       </c>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="16">
+      <c r="A16" s="17">
         <v>15</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <v>2</v>
       </c>
       <c r="C16" s="5">
@@ -4802,10 +4820,10 @@
       </c>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="16">
+      <c r="A17" s="17">
         <v>16</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <v>2</v>
       </c>
       <c r="C17" s="5">
@@ -4813,10 +4831,10 @@
       </c>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="17">
+      <c r="A18" s="18">
         <v>17</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <v>2</v>
       </c>
       <c r="C18" s="5">
@@ -4824,10 +4842,10 @@
       </c>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="16">
+      <c r="A19" s="17">
         <v>18</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="17">
         <v>2</v>
       </c>
       <c r="C19" s="5">
@@ -4835,10 +4853,10 @@
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="16">
+      <c r="A20" s="17">
         <v>19</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <v>2</v>
       </c>
       <c r="C20" s="5">
@@ -4846,10 +4864,10 @@
       </c>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="17">
+      <c r="A21" s="18">
         <v>20</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="17">
         <v>2</v>
       </c>
       <c r="C21" s="5">
@@ -4857,10 +4875,10 @@
       </c>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="16">
+      <c r="A22" s="17">
         <v>21</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <v>2</v>
       </c>
       <c r="C22" s="5">
@@ -4868,10 +4886,10 @@
       </c>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="16">
+      <c r="A23" s="17">
         <v>22</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="17">
         <v>2</v>
       </c>
       <c r="C23" s="5">
@@ -4879,10 +4897,10 @@
       </c>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="17">
+      <c r="A24" s="18">
         <v>23</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <v>2</v>
       </c>
       <c r="C24" s="5">
@@ -4890,10 +4908,10 @@
       </c>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="16">
+      <c r="A25" s="17">
         <v>24</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <v>2</v>
       </c>
       <c r="C25" s="5">
@@ -4901,10 +4919,10 @@
       </c>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="16">
+      <c r="A26" s="17">
         <v>25</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>2</v>
       </c>
       <c r="C26" s="5">
@@ -4912,10 +4930,10 @@
       </c>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="17">
+      <c r="A27" s="18">
         <v>26</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <v>2</v>
       </c>
       <c r="C27" s="5">
@@ -4923,10 +4941,10 @@
       </c>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="16">
+      <c r="A28" s="17">
         <v>27</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <v>2</v>
       </c>
       <c r="C28" s="5">
@@ -4934,10 +4952,10 @@
       </c>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="16">
+      <c r="A29" s="17">
         <v>28</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <v>2</v>
       </c>
       <c r="C29" s="5">
@@ -4945,10 +4963,10 @@
       </c>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="17">
+      <c r="A30" s="18">
         <v>29</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="17">
         <v>2</v>
       </c>
       <c r="C30" s="5">
@@ -4956,10 +4974,10 @@
       </c>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="16">
+      <c r="A31" s="17">
         <v>30</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <v>2</v>
       </c>
       <c r="C31" s="5">
@@ -4967,10 +4985,10 @@
       </c>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A32" s="16">
+      <c r="A32" s="17">
         <v>31</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>2</v>
       </c>
       <c r="C32" s="5">
@@ -4978,10 +4996,10 @@
       </c>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A33" s="17">
+      <c r="A33" s="18">
         <v>32</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>2</v>
       </c>
       <c r="C33" s="5">
@@ -4989,10 +5007,10 @@
       </c>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A34" s="16">
+      <c r="A34" s="17">
         <v>33</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <v>2</v>
       </c>
       <c r="C34" s="5">
@@ -5000,10 +5018,10 @@
       </c>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A35" s="16">
+      <c r="A35" s="17">
         <v>34</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="17">
         <v>2</v>
       </c>
       <c r="C35" s="5">
@@ -5011,10 +5029,10 @@
       </c>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A36" s="17">
+      <c r="A36" s="18">
         <v>35</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <v>2</v>
       </c>
       <c r="C36" s="5">
@@ -5022,10 +5040,10 @@
       </c>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A37" s="16">
+      <c r="A37" s="17">
         <v>36</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <v>2</v>
       </c>
       <c r="C37" s="5">
@@ -5033,10 +5051,10 @@
       </c>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A38" s="16">
+      <c r="A38" s="17">
         <v>37</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="17">
         <v>2</v>
       </c>
       <c r="C38" s="5">
@@ -5044,10 +5062,10 @@
       </c>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A39" s="17">
+      <c r="A39" s="18">
         <v>38</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>2</v>
       </c>
       <c r="C39" s="5">
@@ -5055,10 +5073,10 @@
       </c>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A40" s="16">
+      <c r="A40" s="17">
         <v>39</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="17">
         <v>2</v>
       </c>
       <c r="C40" s="5">
@@ -5066,10 +5084,10 @@
       </c>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A41" s="16">
+      <c r="A41" s="17">
         <v>40</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="17">
         <v>2</v>
       </c>
       <c r="C41" s="5">
@@ -5077,10 +5095,10 @@
       </c>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A42" s="17">
+      <c r="A42" s="18">
         <v>41</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="17">
         <v>2</v>
       </c>
       <c r="C42" s="5">
@@ -5088,10 +5106,10 @@
       </c>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A43" s="16">
+      <c r="A43" s="17">
         <v>42</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="17">
         <v>2</v>
       </c>
       <c r="C43" s="5">
@@ -5099,10 +5117,10 @@
       </c>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A44" s="16">
+      <c r="A44" s="17">
         <v>43</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <v>2</v>
       </c>
       <c r="C44" s="5">
@@ -5110,10 +5128,10 @@
       </c>
     </row>
     <row r="45" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A45" s="17">
+      <c r="A45" s="18">
         <v>44</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="17">
         <v>2</v>
       </c>
       <c r="C45" s="5">
@@ -5121,10 +5139,10 @@
       </c>
     </row>
     <row r="46" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A46" s="16">
+      <c r="A46" s="17">
         <v>45</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="17">
         <v>2</v>
       </c>
       <c r="C46" s="5">
@@ -5132,10 +5150,10 @@
       </c>
     </row>
     <row r="47" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A47" s="16">
+      <c r="A47" s="17">
         <v>46</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="17">
         <v>2</v>
       </c>
       <c r="C47" s="5">
@@ -5143,10 +5161,10 @@
       </c>
     </row>
     <row r="48" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A48" s="17">
+      <c r="A48" s="18">
         <v>47</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <v>2</v>
       </c>
       <c r="C48" s="5">
@@ -5154,10 +5172,10 @@
       </c>
     </row>
     <row r="49" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A49" s="16">
+      <c r="A49" s="17">
         <v>48</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="17">
         <v>2</v>
       </c>
       <c r="C49" s="5">
@@ -5165,10 +5183,10 @@
       </c>
     </row>
     <row r="50" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A50" s="16">
+      <c r="A50" s="17">
         <v>49</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="17">
         <v>2</v>
       </c>
       <c r="C50" s="5">
@@ -5176,10 +5194,10 @@
       </c>
     </row>
     <row r="51" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A51" s="17">
+      <c r="A51" s="18">
         <v>50</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="17">
         <v>2</v>
       </c>
       <c r="C51" s="5">
@@ -5187,10 +5205,10 @@
       </c>
     </row>
     <row r="52" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A52" s="16">
+      <c r="A52" s="17">
         <v>51</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="17">
         <v>2</v>
       </c>
       <c r="C52" s="5">
@@ -5198,10 +5216,10 @@
       </c>
     </row>
     <row r="53" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A53" s="16">
+      <c r="A53" s="17">
         <v>52</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <v>2</v>
       </c>
       <c r="C53" s="5">
@@ -5209,10 +5227,10 @@
       </c>
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A54" s="17">
+      <c r="A54" s="18">
         <v>53</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="17">
         <v>2</v>
       </c>
       <c r="C54" s="5">
@@ -5220,10 +5238,10 @@
       </c>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A55" s="16">
+      <c r="A55" s="17">
         <v>54</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="17">
         <v>2</v>
       </c>
       <c r="C55" s="5">
@@ -5231,10 +5249,10 @@
       </c>
     </row>
     <row r="56" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A56" s="16">
+      <c r="A56" s="17">
         <v>55</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="17">
         <v>2</v>
       </c>
       <c r="C56" s="5">
@@ -5242,10 +5260,10 @@
       </c>
     </row>
     <row r="57" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A57" s="17">
+      <c r="A57" s="18">
         <v>56</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="17">
         <v>2</v>
       </c>
       <c r="C57" s="5">
@@ -5253,10 +5271,10 @@
       </c>
     </row>
     <row r="58" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A58" s="16">
+      <c r="A58" s="17">
         <v>57</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="17">
         <v>2</v>
       </c>
       <c r="C58" s="5">
@@ -5264,10 +5282,10 @@
       </c>
     </row>
     <row r="59" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A59" s="16">
-        <v>58</v>
-      </c>
-      <c r="B59" s="16">
+      <c r="A59" s="17">
+        <v>58</v>
+      </c>
+      <c r="B59" s="17">
         <v>2</v>
       </c>
       <c r="C59" s="5">
@@ -5275,10 +5293,10 @@
       </c>
     </row>
     <row r="60" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A60" s="16">
+      <c r="A60" s="17">
         <v>59</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="17">
         <v>2</v>
       </c>
       <c r="C60" s="5">
@@ -5286,10 +5304,10 @@
       </c>
     </row>
     <row r="61" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A61" s="16">
+      <c r="A61" s="17">
         <v>60</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="17">
         <v>2</v>
       </c>
       <c r="C61" s="5">
@@ -5297,10 +5315,10 @@
       </c>
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A62" s="16">
+      <c r="A62" s="17">
         <v>61</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="17">
         <v>2</v>
       </c>
       <c r="C62" s="5">
@@ -5308,10 +5326,10 @@
       </c>
     </row>
     <row r="63" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A63" s="16">
+      <c r="A63" s="17">
         <v>62</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <v>2</v>
       </c>
       <c r="C63" s="5">
@@ -5319,10 +5337,10 @@
       </c>
     </row>
     <row r="64" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A64" s="16">
+      <c r="A64" s="17">
         <v>63</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="17">
         <v>2</v>
       </c>
       <c r="C64" s="5">
@@ -5330,10 +5348,10 @@
       </c>
     </row>
     <row r="65" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A65" s="16">
+      <c r="A65" s="17">
         <v>64</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="17">
         <v>2</v>
       </c>
       <c r="C65" s="5">
@@ -5341,10 +5359,10 @@
       </c>
     </row>
     <row r="66" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A66" s="16">
+      <c r="A66" s="17">
         <v>65</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="17">
         <v>2</v>
       </c>
       <c r="C66" s="5">
@@ -5352,10 +5370,10 @@
       </c>
     </row>
     <row r="67" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A67" s="16">
+      <c r="A67" s="17">
         <v>66</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="17">
         <v>2</v>
       </c>
       <c r="C67" s="5">
@@ -5363,10 +5381,10 @@
       </c>
     </row>
     <row r="68" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A68" s="16">
+      <c r="A68" s="17">
         <v>67</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="17">
         <v>2</v>
       </c>
       <c r="C68" s="5">
@@ -5374,10 +5392,10 @@
       </c>
     </row>
     <row r="69" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A69" s="16">
+      <c r="A69" s="17">
         <v>68</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="17">
         <v>2</v>
       </c>
       <c r="C69" s="5">
@@ -5385,10 +5403,10 @@
       </c>
     </row>
     <row r="70" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A70" s="16">
+      <c r="A70" s="17">
         <v>69</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="17">
         <v>2</v>
       </c>
       <c r="C70" s="5">
@@ -5396,10 +5414,10 @@
       </c>
     </row>
     <row r="71" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A71" s="16">
+      <c r="A71" s="17">
         <v>70</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="17">
         <v>2</v>
       </c>
       <c r="C71" s="5">
@@ -5407,10 +5425,10 @@
       </c>
     </row>
     <row r="72" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A72" s="16">
+      <c r="A72" s="17">
         <v>71</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="17">
         <v>2</v>
       </c>
       <c r="C72" s="5">
@@ -5418,10 +5436,10 @@
       </c>
     </row>
     <row r="73" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A73" s="16">
+      <c r="A73" s="17">
         <v>72</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="17">
         <v>2</v>
       </c>
       <c r="C73" s="5">
@@ -5429,10 +5447,10 @@
       </c>
     </row>
     <row r="74" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A74" s="16">
+      <c r="A74" s="17">
         <v>73</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="17">
         <v>2</v>
       </c>
       <c r="C74" s="5">
@@ -5440,10 +5458,10 @@
       </c>
     </row>
     <row r="75" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A75" s="16">
+      <c r="A75" s="17">
         <v>74</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="17">
         <v>2</v>
       </c>
       <c r="C75" s="5">
@@ -5451,10 +5469,10 @@
       </c>
     </row>
     <row r="76" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A76" s="16">
+      <c r="A76" s="17">
         <v>75</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="17">
         <v>2</v>
       </c>
       <c r="C76" s="5">
@@ -5462,10 +5480,10 @@
       </c>
     </row>
     <row r="77" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A77" s="16">
+      <c r="A77" s="17">
         <v>76</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="17">
         <v>2</v>
       </c>
       <c r="C77" s="5">
@@ -5473,10 +5491,10 @@
       </c>
     </row>
     <row r="78" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A78" s="16">
+      <c r="A78" s="17">
         <v>77</v>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="17">
         <v>2</v>
       </c>
       <c r="C78" s="5">
@@ -5484,10 +5502,10 @@
       </c>
     </row>
     <row r="79" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A79" s="16">
+      <c r="A79" s="17">
         <v>78</v>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="17">
         <v>2</v>
       </c>
       <c r="C79" s="5">
@@ -5495,10 +5513,10 @@
       </c>
     </row>
     <row r="80" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A80" s="16">
+      <c r="A80" s="17">
         <v>79</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="17">
         <v>2</v>
       </c>
       <c r="C80" s="5">
@@ -5506,10 +5524,10 @@
       </c>
     </row>
     <row r="81" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A81" s="16">
+      <c r="A81" s="17">
         <v>80</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="17">
         <v>2</v>
       </c>
       <c r="C81" s="5">
@@ -5517,10 +5535,10 @@
       </c>
     </row>
     <row r="82" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A82" s="16">
+      <c r="A82" s="17">
         <v>81</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="17">
         <v>2</v>
       </c>
       <c r="C82" s="5">
@@ -5528,10 +5546,10 @@
       </c>
     </row>
     <row r="83" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A83" s="16">
+      <c r="A83" s="17">
         <v>82</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="17">
         <v>2</v>
       </c>
       <c r="C83" s="5">
@@ -5539,10 +5557,10 @@
       </c>
     </row>
     <row r="84" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A84" s="16">
+      <c r="A84" s="17">
         <v>83</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="17">
         <v>2</v>
       </c>
       <c r="C84" s="5">
@@ -5550,10 +5568,10 @@
       </c>
     </row>
     <row r="85" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A85" s="16">
+      <c r="A85" s="17">
         <v>84</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="17">
         <v>2</v>
       </c>
       <c r="C85" s="5">
@@ -5561,10 +5579,10 @@
       </c>
     </row>
     <row r="86" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A86" s="16">
+      <c r="A86" s="17">
         <v>85</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="17">
         <v>2</v>
       </c>
       <c r="C86" s="5">
@@ -5572,10 +5590,10 @@
       </c>
     </row>
     <row r="87" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A87" s="16">
+      <c r="A87" s="17">
         <v>86</v>
       </c>
-      <c r="B87" s="16">
+      <c r="B87" s="17">
         <v>2</v>
       </c>
       <c r="C87" s="5">
@@ -5583,10 +5601,10 @@
       </c>
     </row>
     <row r="88" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A88" s="16">
+      <c r="A88" s="17">
         <v>87</v>
       </c>
-      <c r="B88" s="16">
+      <c r="B88" s="17">
         <v>2</v>
       </c>
       <c r="C88" s="5">
@@ -5594,10 +5612,10 @@
       </c>
     </row>
     <row r="89" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A89" s="16">
+      <c r="A89" s="17">
         <v>88</v>
       </c>
-      <c r="B89" s="16">
+      <c r="B89" s="17">
         <v>2</v>
       </c>
       <c r="C89" s="5">
@@ -5605,10 +5623,10 @@
       </c>
     </row>
     <row r="90" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A90" s="16">
+      <c r="A90" s="17">
         <v>89</v>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="17">
         <v>2</v>
       </c>
       <c r="C90" s="5">
@@ -5616,10 +5634,10 @@
       </c>
     </row>
     <row r="91" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A91" s="16">
+      <c r="A91" s="17">
         <v>90</v>
       </c>
-      <c r="B91" s="16">
+      <c r="B91" s="17">
         <v>2</v>
       </c>
       <c r="C91" s="5">
@@ -5627,10 +5645,10 @@
       </c>
     </row>
     <row r="92" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A92" s="16">
+      <c r="A92" s="17">
         <v>91</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B92" s="17">
         <v>2</v>
       </c>
       <c r="C92" s="5">
@@ -5638,10 +5656,10 @@
       </c>
     </row>
     <row r="93" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A93" s="16">
+      <c r="A93" s="17">
         <v>92</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B93" s="17">
         <v>2</v>
       </c>
       <c r="C93" s="5">
@@ -5649,10 +5667,10 @@
       </c>
     </row>
     <row r="94" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A94" s="16">
+      <c r="A94" s="17">
         <v>93</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B94" s="17">
         <v>2</v>
       </c>
       <c r="C94" s="5">
@@ -5660,10 +5678,10 @@
       </c>
     </row>
     <row r="95" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A95" s="16">
+      <c r="A95" s="17">
         <v>94</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B95" s="17">
         <v>2</v>
       </c>
       <c r="C95" s="5">
@@ -5671,10 +5689,10 @@
       </c>
     </row>
     <row r="96" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A96" s="16">
+      <c r="A96" s="17">
         <v>95</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B96" s="17">
         <v>2</v>
       </c>
       <c r="C96" s="5">
@@ -5682,10 +5700,10 @@
       </c>
     </row>
     <row r="97" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A97" s="16">
+      <c r="A97" s="17">
         <v>96</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B97" s="17">
         <v>2</v>
       </c>
       <c r="C97" s="5">
@@ -5693,10 +5711,10 @@
       </c>
     </row>
     <row r="98" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A98" s="16">
+      <c r="A98" s="17">
         <v>97</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B98" s="17">
         <v>2</v>
       </c>
       <c r="C98" s="5">
@@ -5704,10 +5722,10 @@
       </c>
     </row>
     <row r="99" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A99" s="16">
+      <c r="A99" s="17">
         <v>98</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="17">
         <v>2</v>
       </c>
       <c r="C99" s="5">
@@ -5715,10 +5733,10 @@
       </c>
     </row>
     <row r="100" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A100" s="16">
+      <c r="A100" s="17">
         <v>99</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B100" s="17">
         <v>2</v>
       </c>
       <c r="C100" s="5">
@@ -5726,10 +5744,10 @@
       </c>
     </row>
     <row r="101" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A101" s="16">
+      <c r="A101" s="17">
         <v>100</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B101" s="17">
         <v>2</v>
       </c>
       <c r="C101" s="5">
@@ -5737,10 +5755,10 @@
       </c>
     </row>
     <row r="102" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A102" s="16">
+      <c r="A102" s="17">
         <v>101</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B102" s="17">
         <v>2</v>
       </c>
       <c r="C102" s="5">
@@ -5748,10 +5766,10 @@
       </c>
     </row>
     <row r="103" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A103" s="16">
+      <c r="A103" s="17">
         <v>102</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B103" s="17">
         <v>2</v>
       </c>
       <c r="C103" s="5">
@@ -5759,10 +5777,10 @@
       </c>
     </row>
     <row r="104" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A104" s="16">
+      <c r="A104" s="17">
         <v>103</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B104" s="17">
         <v>2</v>
       </c>
       <c r="C104" s="5">
@@ -5770,10 +5788,10 @@
       </c>
     </row>
     <row r="105" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A105" s="16">
+      <c r="A105" s="17">
         <v>104</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B105" s="17">
         <v>2</v>
       </c>
       <c r="C105" s="5">
@@ -5781,10 +5799,10 @@
       </c>
     </row>
     <row r="106" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A106" s="16">
+      <c r="A106" s="17">
         <v>105</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B106" s="17">
         <v>2</v>
       </c>
       <c r="C106" s="5">
@@ -5792,10 +5810,10 @@
       </c>
     </row>
     <row r="107" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A107" s="16">
+      <c r="A107" s="17">
         <v>106</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B107" s="17">
         <v>2</v>
       </c>
       <c r="C107" s="5">
@@ -5803,10 +5821,10 @@
       </c>
     </row>
     <row r="108" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A108" s="16">
+      <c r="A108" s="17">
         <v>107</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B108" s="17">
         <v>2</v>
       </c>
       <c r="C108" s="5">
@@ -5814,10 +5832,10 @@
       </c>
     </row>
     <row r="109" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A109" s="16">
+      <c r="A109" s="17">
         <v>108</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B109" s="17">
         <v>2</v>
       </c>
       <c r="C109" s="5">
@@ -5825,10 +5843,10 @@
       </c>
     </row>
     <row r="110" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A110" s="16">
+      <c r="A110" s="17">
         <v>109</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B110" s="17">
         <v>2</v>
       </c>
       <c r="C110" s="5">
@@ -5836,10 +5854,10 @@
       </c>
     </row>
     <row r="111" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A111" s="16">
+      <c r="A111" s="17">
         <v>110</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="17">
         <v>2</v>
       </c>
       <c r="C111" s="5">
@@ -5847,10 +5865,10 @@
       </c>
     </row>
     <row r="112" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A112" s="16">
+      <c r="A112" s="17">
         <v>111</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B112" s="17">
         <v>2</v>
       </c>
       <c r="C112" s="5">
@@ -5858,10 +5876,10 @@
       </c>
     </row>
     <row r="113" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A113" s="16">
+      <c r="A113" s="17">
         <v>112</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="17">
         <v>2</v>
       </c>
       <c r="C113" s="5">
@@ -5869,10 +5887,10 @@
       </c>
     </row>
     <row r="114" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A114" s="16">
+      <c r="A114" s="17">
         <v>113</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="17">
         <v>2</v>
       </c>
       <c r="C114" s="5">
@@ -5880,10 +5898,10 @@
       </c>
     </row>
     <row r="115" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A115" s="16">
+      <c r="A115" s="17">
         <v>114</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <v>2</v>
       </c>
       <c r="C115" s="5">
@@ -5891,10 +5909,10 @@
       </c>
     </row>
     <row r="116" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A116" s="16">
+      <c r="A116" s="17">
         <v>115</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B116" s="17">
         <v>2</v>
       </c>
       <c r="C116" s="5">
@@ -5902,10 +5920,10 @@
       </c>
     </row>
     <row r="117" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A117" s="16">
+      <c r="A117" s="17">
         <v>116</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B117" s="17">
         <v>2</v>
       </c>
       <c r="C117" s="5">
@@ -5913,10 +5931,10 @@
       </c>
     </row>
     <row r="118" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A118" s="16">
+      <c r="A118" s="17">
         <v>117</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B118" s="17">
         <v>2</v>
       </c>
       <c r="C118" s="5">
@@ -5924,10 +5942,10 @@
       </c>
     </row>
     <row r="119" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A119" s="16">
+      <c r="A119" s="17">
         <v>118</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B119" s="17">
         <v>2</v>
       </c>
       <c r="C119" s="5">
@@ -5935,10 +5953,10 @@
       </c>
     </row>
     <row r="120" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A120" s="16">
+      <c r="A120" s="17">
         <v>119</v>
       </c>
-      <c r="B120" s="16">
+      <c r="B120" s="17">
         <v>2</v>
       </c>
       <c r="C120" s="5">
@@ -5946,10 +5964,10 @@
       </c>
     </row>
     <row r="121" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A121" s="16">
+      <c r="A121" s="17">
         <v>120</v>
       </c>
-      <c r="B121" s="16">
+      <c r="B121" s="17">
         <v>2</v>
       </c>
       <c r="C121" s="5">
@@ -5957,10 +5975,10 @@
       </c>
     </row>
     <row r="122" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A122" s="16">
+      <c r="A122" s="17">
         <v>121</v>
       </c>
-      <c r="B122" s="16">
+      <c r="B122" s="17">
         <v>2</v>
       </c>
       <c r="C122" s="5">
@@ -5968,10 +5986,10 @@
       </c>
     </row>
     <row r="123" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A123" s="16">
+      <c r="A123" s="17">
         <v>122</v>
       </c>
-      <c r="B123" s="16">
+      <c r="B123" s="17">
         <v>2</v>
       </c>
       <c r="C123" s="5">
@@ -5979,10 +5997,10 @@
       </c>
     </row>
     <row r="124" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A124" s="16">
+      <c r="A124" s="17">
         <v>123</v>
       </c>
-      <c r="B124" s="16">
+      <c r="B124" s="17">
         <v>2</v>
       </c>
       <c r="C124" s="5">
@@ -5990,10 +6008,10 @@
       </c>
     </row>
     <row r="125" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A125" s="16">
+      <c r="A125" s="17">
         <v>124</v>
       </c>
-      <c r="B125" s="16">
+      <c r="B125" s="17">
         <v>2</v>
       </c>
       <c r="C125" s="5">
@@ -6001,10 +6019,10 @@
       </c>
     </row>
     <row r="126" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A126" s="16">
+      <c r="A126" s="17">
         <v>125</v>
       </c>
-      <c r="B126" s="16">
+      <c r="B126" s="17">
         <v>2</v>
       </c>
       <c r="C126" s="5">
@@ -6012,10 +6030,10 @@
       </c>
     </row>
     <row r="127" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A127" s="16">
+      <c r="A127" s="17">
         <v>126</v>
       </c>
-      <c r="B127" s="16">
+      <c r="B127" s="17">
         <v>2</v>
       </c>
       <c r="C127" s="5">
@@ -6023,10 +6041,10 @@
       </c>
     </row>
     <row r="128" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A128" s="16">
+      <c r="A128" s="17">
         <v>127</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="17">
         <v>2</v>
       </c>
       <c r="C128" s="5">
@@ -6034,10 +6052,10 @@
       </c>
     </row>
     <row r="129" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A129" s="16">
+      <c r="A129" s="17">
         <v>128</v>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="17">
         <v>2</v>
       </c>
       <c r="C129" s="5">
@@ -6045,10 +6063,10 @@
       </c>
     </row>
     <row r="130" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A130" s="16">
+      <c r="A130" s="17">
         <v>129</v>
       </c>
-      <c r="B130" s="16">
+      <c r="B130" s="17">
         <v>2</v>
       </c>
       <c r="C130" s="5">
@@ -6056,10 +6074,10 @@
       </c>
     </row>
     <row r="131" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A131" s="16">
+      <c r="A131" s="17">
         <v>130</v>
       </c>
-      <c r="B131" s="16">
+      <c r="B131" s="17">
         <v>2</v>
       </c>
       <c r="C131" s="5">
@@ -6067,10 +6085,10 @@
       </c>
     </row>
     <row r="132" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A132" s="16">
+      <c r="A132" s="17">
         <v>131</v>
       </c>
-      <c r="B132" s="16">
+      <c r="B132" s="17">
         <v>2</v>
       </c>
       <c r="C132" s="5">
@@ -6078,10 +6096,10 @@
       </c>
     </row>
     <row r="133" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A133" s="16">
+      <c r="A133" s="17">
         <v>132</v>
       </c>
-      <c r="B133" s="16">
+      <c r="B133" s="17">
         <v>2</v>
       </c>
       <c r="C133" s="5">
@@ -6089,10 +6107,10 @@
       </c>
     </row>
     <row r="134" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A134" s="16">
+      <c r="A134" s="17">
         <v>133</v>
       </c>
-      <c r="B134" s="16">
+      <c r="B134" s="17">
         <v>2</v>
       </c>
       <c r="C134" s="5">
@@ -6100,10 +6118,10 @@
       </c>
     </row>
     <row r="135" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A135" s="16">
+      <c r="A135" s="17">
         <v>134</v>
       </c>
-      <c r="B135" s="16">
+      <c r="B135" s="17">
         <v>2</v>
       </c>
       <c r="C135" s="5">
@@ -6111,10 +6129,10 @@
       </c>
     </row>
     <row r="136" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A136" s="16">
+      <c r="A136" s="17">
         <v>135</v>
       </c>
-      <c r="B136" s="16">
+      <c r="B136" s="17">
         <v>2</v>
       </c>
       <c r="C136" s="5">
@@ -6122,10 +6140,10 @@
       </c>
     </row>
     <row r="137" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A137" s="16">
+      <c r="A137" s="17">
         <v>136</v>
       </c>
-      <c r="B137" s="16">
+      <c r="B137" s="17">
         <v>2</v>
       </c>
       <c r="C137" s="5">
@@ -6133,10 +6151,10 @@
       </c>
     </row>
     <row r="138" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A138" s="16">
+      <c r="A138" s="17">
         <v>137</v>
       </c>
-      <c r="B138" s="16">
+      <c r="B138" s="17">
         <v>2</v>
       </c>
       <c r="C138" s="5">
@@ -6144,10 +6162,10 @@
       </c>
     </row>
     <row r="139" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A139" s="16">
+      <c r="A139" s="17">
         <v>138</v>
       </c>
-      <c r="B139" s="16">
+      <c r="B139" s="17">
         <v>2</v>
       </c>
       <c r="C139" s="5">
@@ -6155,10 +6173,10 @@
       </c>
     </row>
     <row r="140" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A140" s="16">
+      <c r="A140" s="17">
         <v>139</v>
       </c>
-      <c r="B140" s="16">
+      <c r="B140" s="17">
         <v>2</v>
       </c>
       <c r="C140" s="5">
@@ -6166,10 +6184,10 @@
       </c>
     </row>
     <row r="141" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A141" s="16">
+      <c r="A141" s="17">
         <v>140</v>
       </c>
-      <c r="B141" s="16">
+      <c r="B141" s="17">
         <v>2</v>
       </c>
       <c r="C141" s="5">
@@ -6177,10 +6195,10 @@
       </c>
     </row>
     <row r="142" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A142" s="16">
+      <c r="A142" s="17">
         <v>141</v>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="17">
         <v>2</v>
       </c>
       <c r="C142" s="5">
@@ -6188,10 +6206,10 @@
       </c>
     </row>
     <row r="143" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A143" s="16">
+      <c r="A143" s="17">
         <v>142</v>
       </c>
-      <c r="B143" s="16">
+      <c r="B143" s="17">
         <v>2</v>
       </c>
       <c r="C143" s="5">
@@ -6199,10 +6217,10 @@
       </c>
     </row>
     <row r="144" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A144" s="16">
+      <c r="A144" s="17">
         <v>122</v>
       </c>
-      <c r="B144" s="16">
+      <c r="B144" s="17">
         <v>2</v>
       </c>
       <c r="C144" s="5">
@@ -6210,10 +6228,10 @@
       </c>
     </row>
     <row r="145" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A145" s="16">
+      <c r="A145" s="17">
         <v>123</v>
       </c>
-      <c r="B145" s="16">
+      <c r="B145" s="17">
         <v>2</v>
       </c>
       <c r="C145" s="5">
@@ -6221,10 +6239,10 @@
       </c>
     </row>
     <row r="146" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A146" s="16">
+      <c r="A146" s="17">
         <v>124</v>
       </c>
-      <c r="B146" s="16">
+      <c r="B146" s="17">
         <v>2</v>
       </c>
       <c r="C146" s="5">
@@ -6232,10 +6250,10 @@
       </c>
     </row>
     <row r="147" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A147" s="16">
+      <c r="A147" s="17">
         <v>125</v>
       </c>
-      <c r="B147" s="16">
+      <c r="B147" s="17">
         <v>2</v>
       </c>
       <c r="C147" s="5">
@@ -6243,10 +6261,10 @@
       </c>
     </row>
     <row r="148" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A148" s="16">
+      <c r="A148" s="17">
         <v>126</v>
       </c>
-      <c r="B148" s="16">
+      <c r="B148" s="17">
         <v>2</v>
       </c>
       <c r="C148" s="5">
@@ -6254,10 +6272,10 @@
       </c>
     </row>
     <row r="149" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A149" s="16">
+      <c r="A149" s="17">
         <v>127</v>
       </c>
-      <c r="B149" s="16">
+      <c r="B149" s="17">
         <v>2</v>
       </c>
       <c r="C149" s="5">
@@ -6265,10 +6283,10 @@
       </c>
     </row>
     <row r="150" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A150" s="16">
+      <c r="A150" s="17">
         <v>128</v>
       </c>
-      <c r="B150" s="16">
+      <c r="B150" s="17">
         <v>2</v>
       </c>
       <c r="C150" s="5">
@@ -6276,10 +6294,10 @@
       </c>
     </row>
     <row r="151" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A151" s="16">
+      <c r="A151" s="17">
         <v>129</v>
       </c>
-      <c r="B151" s="16">
+      <c r="B151" s="17">
         <v>2</v>
       </c>
       <c r="C151" s="5">
@@ -6287,10 +6305,10 @@
       </c>
     </row>
     <row r="152" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A152" s="16">
+      <c r="A152" s="17">
         <v>130</v>
       </c>
-      <c r="B152" s="16">
+      <c r="B152" s="17">
         <v>2</v>
       </c>
       <c r="C152" s="5">
@@ -6298,10 +6316,10 @@
       </c>
     </row>
     <row r="153" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A153" s="16">
+      <c r="A153" s="17">
         <v>131</v>
       </c>
-      <c r="B153" s="16">
+      <c r="B153" s="17">
         <v>2</v>
       </c>
       <c r="C153" s="5">
@@ -6309,10 +6327,10 @@
       </c>
     </row>
     <row r="154" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A154" s="16">
+      <c r="A154" s="17">
         <v>132</v>
       </c>
-      <c r="B154" s="16">
+      <c r="B154" s="17">
         <v>2</v>
       </c>
       <c r="C154" s="5">
@@ -6320,10 +6338,10 @@
       </c>
     </row>
     <row r="155" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A155" s="16">
+      <c r="A155" s="17">
         <v>133</v>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="17">
         <v>2</v>
       </c>
       <c r="C155" s="5">
@@ -6331,10 +6349,10 @@
       </c>
     </row>
     <row r="156" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A156" s="16">
+      <c r="A156" s="17">
         <v>134</v>
       </c>
-      <c r="B156" s="16">
+      <c r="B156" s="17">
         <v>2</v>
       </c>
       <c r="C156" s="5">
@@ -6342,10 +6360,10 @@
       </c>
     </row>
     <row r="157" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A157" s="16">
+      <c r="A157" s="17">
         <v>135</v>
       </c>
-      <c r="B157" s="16">
+      <c r="B157" s="17">
         <v>2</v>
       </c>
       <c r="C157" s="5">
@@ -6353,10 +6371,10 @@
       </c>
     </row>
     <row r="158" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A158" s="16">
+      <c r="A158" s="17">
         <v>136</v>
       </c>
-      <c r="B158" s="16">
+      <c r="B158" s="17">
         <v>2</v>
       </c>
       <c r="C158" s="5">
@@ -6364,10 +6382,10 @@
       </c>
     </row>
     <row r="159" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A159" s="16">
+      <c r="A159" s="17">
         <v>137</v>
       </c>
-      <c r="B159" s="16">
+      <c r="B159" s="17">
         <v>2</v>
       </c>
       <c r="C159" s="5">
@@ -6375,10 +6393,10 @@
       </c>
     </row>
     <row r="160" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A160" s="16">
+      <c r="A160" s="17">
         <v>138</v>
       </c>
-      <c r="B160" s="16">
+      <c r="B160" s="17">
         <v>2</v>
       </c>
       <c r="C160" s="5">
@@ -6386,10 +6404,10 @@
       </c>
     </row>
     <row r="161" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A161" s="16">
+      <c r="A161" s="17">
         <v>139</v>
       </c>
-      <c r="B161" s="16">
+      <c r="B161" s="17">
         <v>2</v>
       </c>
       <c r="C161" s="5">
@@ -6397,10 +6415,10 @@
       </c>
     </row>
     <row r="162" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A162" s="16">
+      <c r="A162" s="17">
         <v>140</v>
       </c>
-      <c r="B162" s="16">
+      <c r="B162" s="17">
         <v>2</v>
       </c>
       <c r="C162" s="5">
@@ -6408,10 +6426,10 @@
       </c>
     </row>
     <row r="163" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A163" s="16">
+      <c r="A163" s="17">
         <v>141</v>
       </c>
-      <c r="B163" s="16">
+      <c r="B163" s="17">
         <v>2</v>
       </c>
       <c r="C163" s="5">
@@ -6419,10 +6437,10 @@
       </c>
     </row>
     <row r="164" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A164" s="16">
+      <c r="A164" s="17">
         <v>142</v>
       </c>
-      <c r="B164" s="16">
+      <c r="B164" s="17">
         <v>2</v>
       </c>
       <c r="C164" s="5">
@@ -6430,10 +6448,10 @@
       </c>
     </row>
     <row r="165" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A165" s="16">
+      <c r="A165" s="17">
         <v>143</v>
       </c>
-      <c r="B165" s="16">
+      <c r="B165" s="17">
         <v>2</v>
       </c>
       <c r="C165" s="5">
@@ -6441,10 +6459,10 @@
       </c>
     </row>
     <row r="166" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A166" s="16">
+      <c r="A166" s="17">
         <v>144</v>
       </c>
-      <c r="B166" s="16">
+      <c r="B166" s="17">
         <v>2</v>
       </c>
       <c r="C166" s="5">
@@ -6452,10 +6470,10 @@
       </c>
     </row>
     <row r="167" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A167" s="16">
+      <c r="A167" s="17">
         <v>145</v>
       </c>
-      <c r="B167" s="16">
+      <c r="B167" s="17">
         <v>2</v>
       </c>
       <c r="C167" s="5">
@@ -6463,10 +6481,10 @@
       </c>
     </row>
     <row r="168" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A168" s="16">
+      <c r="A168" s="17">
         <v>146</v>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="17">
         <v>2</v>
       </c>
       <c r="C168" s="5">
@@ -6474,10 +6492,10 @@
       </c>
     </row>
     <row r="169" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A169" s="16">
+      <c r="A169" s="17">
         <v>147</v>
       </c>
-      <c r="B169" s="16">
+      <c r="B169" s="17">
         <v>2</v>
       </c>
       <c r="C169" s="5">
@@ -6485,10 +6503,10 @@
       </c>
     </row>
     <row r="170" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A170" s="16">
+      <c r="A170" s="17">
         <v>148</v>
       </c>
-      <c r="B170" s="16">
+      <c r="B170" s="17">
         <v>2</v>
       </c>
       <c r="C170" s="5">
@@ -6496,10 +6514,10 @@
       </c>
     </row>
     <row r="171" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A171" s="16">
+      <c r="A171" s="17">
         <v>149</v>
       </c>
-      <c r="B171" s="16">
+      <c r="B171" s="17">
         <v>2</v>
       </c>
       <c r="C171" s="5">
@@ -6507,10 +6525,10 @@
       </c>
     </row>
     <row r="172" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A172" s="16">
+      <c r="A172" s="17">
         <v>150</v>
       </c>
-      <c r="B172" s="16">
+      <c r="B172" s="17">
         <v>2</v>
       </c>
       <c r="C172" s="5">
@@ -6518,10 +6536,10 @@
       </c>
     </row>
     <row r="173" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A173" s="16">
+      <c r="A173" s="17">
         <v>151</v>
       </c>
-      <c r="B173" s="16">
+      <c r="B173" s="17">
         <v>2</v>
       </c>
       <c r="C173" s="5">
@@ -6529,10 +6547,10 @@
       </c>
     </row>
     <row r="174" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A174" s="16">
+      <c r="A174" s="17">
         <v>152</v>
       </c>
-      <c r="B174" s="16">
+      <c r="B174" s="17">
         <v>2</v>
       </c>
       <c r="C174" s="5">
@@ -6540,10 +6558,10 @@
       </c>
     </row>
     <row r="175" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A175" s="16">
+      <c r="A175" s="17">
         <v>153</v>
       </c>
-      <c r="B175" s="16">
+      <c r="B175" s="17">
         <v>2</v>
       </c>
       <c r="C175" s="5">
@@ -6551,10 +6569,10 @@
       </c>
     </row>
     <row r="176" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A176" s="16">
+      <c r="A176" s="17">
         <v>154</v>
       </c>
-      <c r="B176" s="16">
+      <c r="B176" s="17">
         <v>2</v>
       </c>
       <c r="C176" s="5">
@@ -6562,10 +6580,10 @@
       </c>
     </row>
     <row r="177" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A177" s="16">
+      <c r="A177" s="17">
         <v>155</v>
       </c>
-      <c r="B177" s="16">
+      <c r="B177" s="17">
         <v>2</v>
       </c>
       <c r="C177" s="5">
@@ -6573,10 +6591,10 @@
       </c>
     </row>
     <row r="178" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A178" s="16">
+      <c r="A178" s="17">
         <v>156</v>
       </c>
-      <c r="B178" s="16">
+      <c r="B178" s="17">
         <v>2</v>
       </c>
       <c r="C178" s="5">
@@ -6584,10 +6602,10 @@
       </c>
     </row>
     <row r="179" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A179" s="16">
+      <c r="A179" s="17">
         <v>157</v>
       </c>
-      <c r="B179" s="16">
+      <c r="B179" s="17">
         <v>2</v>
       </c>
       <c r="C179" s="5">
@@ -6595,10 +6613,10 @@
       </c>
     </row>
     <row r="180" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A180" s="16">
+      <c r="A180" s="17">
         <v>158</v>
       </c>
-      <c r="B180" s="16">
+      <c r="B180" s="17">
         <v>2</v>
       </c>
       <c r="C180" s="5">
@@ -6606,10 +6624,10 @@
       </c>
     </row>
     <row r="181" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A181" s="16">
+      <c r="A181" s="17">
         <v>159</v>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="17">
         <v>2</v>
       </c>
       <c r="C181" s="5">
@@ -6617,10 +6635,10 @@
       </c>
     </row>
     <row r="182" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A182" s="16">
+      <c r="A182" s="17">
         <v>160</v>
       </c>
-      <c r="B182" s="16">
+      <c r="B182" s="17">
         <v>2</v>
       </c>
       <c r="C182" s="5">
@@ -6628,10 +6646,10 @@
       </c>
     </row>
     <row r="183" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A183" s="16">
+      <c r="A183" s="17">
         <v>161</v>
       </c>
-      <c r="B183" s="16">
+      <c r="B183" s="17">
         <v>2</v>
       </c>
       <c r="C183" s="5">
@@ -6639,10 +6657,10 @@
       </c>
     </row>
     <row r="184" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A184" s="16">
+      <c r="A184" s="17">
         <v>162</v>
       </c>
-      <c r="B184" s="16">
+      <c r="B184" s="17">
         <v>2</v>
       </c>
       <c r="C184" s="5">
@@ -6650,10 +6668,10 @@
       </c>
     </row>
     <row r="185" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A185" s="16">
+      <c r="A185" s="17">
         <v>163</v>
       </c>
-      <c r="B185" s="16">
+      <c r="B185" s="17">
         <v>2</v>
       </c>
       <c r="C185" s="5">
@@ -6661,10 +6679,10 @@
       </c>
     </row>
     <row r="186" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A186" s="16">
+      <c r="A186" s="17">
         <v>164</v>
       </c>
-      <c r="B186" s="16">
+      <c r="B186" s="17">
         <v>2</v>
       </c>
       <c r="C186" s="5">
@@ -6672,10 +6690,10 @@
       </c>
     </row>
     <row r="187" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A187" s="16">
+      <c r="A187" s="17">
         <v>165</v>
       </c>
-      <c r="B187" s="16">
+      <c r="B187" s="17">
         <v>2</v>
       </c>
       <c r="C187" s="5">
@@ -6683,10 +6701,10 @@
       </c>
     </row>
     <row r="188" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A188" s="16">
+      <c r="A188" s="17">
         <v>166</v>
       </c>
-      <c r="B188" s="16">
+      <c r="B188" s="17">
         <v>2</v>
       </c>
       <c r="C188" s="5">
@@ -6694,10 +6712,10 @@
       </c>
     </row>
     <row r="189" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A189" s="16">
+      <c r="A189" s="17">
         <v>167</v>
       </c>
-      <c r="B189" s="16">
+      <c r="B189" s="17">
         <v>2</v>
       </c>
       <c r="C189" s="5">
@@ -6705,10 +6723,10 @@
       </c>
     </row>
     <row r="190" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A190" s="16">
+      <c r="A190" s="17">
         <v>168</v>
       </c>
-      <c r="B190" s="16">
+      <c r="B190" s="17">
         <v>2</v>
       </c>
       <c r="C190" s="5">
@@ -6716,10 +6734,10 @@
       </c>
     </row>
     <row r="191" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A191" s="16">
+      <c r="A191" s="17">
         <v>169</v>
       </c>
-      <c r="B191" s="16">
+      <c r="B191" s="17">
         <v>2</v>
       </c>
       <c r="C191" s="5">
@@ -6727,10 +6745,10 @@
       </c>
     </row>
     <row r="192" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A192" s="16">
+      <c r="A192" s="17">
         <v>170</v>
       </c>
-      <c r="B192" s="16">
+      <c r="B192" s="17">
         <v>2</v>
       </c>
       <c r="C192" s="5">
@@ -6738,10 +6756,10 @@
       </c>
     </row>
     <row r="193" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A193" s="16">
+      <c r="A193" s="17">
         <v>171</v>
       </c>
-      <c r="B193" s="16">
+      <c r="B193" s="17">
         <v>2</v>
       </c>
       <c r="C193" s="5">
@@ -6749,10 +6767,10 @@
       </c>
     </row>
     <row r="194" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A194" s="16">
+      <c r="A194" s="17">
         <v>172</v>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="17">
         <v>2</v>
       </c>
       <c r="C194" s="5">
@@ -6760,10 +6778,10 @@
       </c>
     </row>
     <row r="195" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A195" s="16">
+      <c r="A195" s="17">
         <v>173</v>
       </c>
-      <c r="B195" s="16">
+      <c r="B195" s="17">
         <v>2</v>
       </c>
       <c r="C195" s="5">
@@ -6771,10 +6789,10 @@
       </c>
     </row>
     <row r="196" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A196" s="16">
+      <c r="A196" s="17">
         <v>174</v>
       </c>
-      <c r="B196" s="16">
+      <c r="B196" s="17">
         <v>2</v>
       </c>
       <c r="C196" s="5">
@@ -6782,10 +6800,10 @@
       </c>
     </row>
     <row r="197" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A197" s="16">
+      <c r="A197" s="17">
         <v>175</v>
       </c>
-      <c r="B197" s="16">
+      <c r="B197" s="17">
         <v>2</v>
       </c>
       <c r="C197" s="5">
@@ -6793,10 +6811,10 @@
       </c>
     </row>
     <row r="198" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A198" s="16">
+      <c r="A198" s="17">
         <v>176</v>
       </c>
-      <c r="B198" s="16">
+      <c r="B198" s="17">
         <v>2</v>
       </c>
       <c r="C198" s="5">
@@ -6804,10 +6822,10 @@
       </c>
     </row>
     <row r="199" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A199" s="16">
+      <c r="A199" s="17">
         <v>177</v>
       </c>
-      <c r="B199" s="16">
+      <c r="B199" s="17">
         <v>2</v>
       </c>
       <c r="C199" s="5">
@@ -6815,10 +6833,10 @@
       </c>
     </row>
     <row r="200" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A200" s="16">
+      <c r="A200" s="17">
         <v>178</v>
       </c>
-      <c r="B200" s="16">
+      <c r="B200" s="17">
         <v>2</v>
       </c>
       <c r="C200" s="5">
@@ -6826,10 +6844,10 @@
       </c>
     </row>
     <row r="201" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A201" s="16">
+      <c r="A201" s="17">
         <v>179</v>
       </c>
-      <c r="B201" s="16">
+      <c r="B201" s="17">
         <v>2</v>
       </c>
       <c r="C201" s="5">
@@ -6837,10 +6855,10 @@
       </c>
     </row>
     <row r="202" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A202" s="16">
+      <c r="A202" s="17">
         <v>180</v>
       </c>
-      <c r="B202" s="16">
+      <c r="B202" s="17">
         <v>2</v>
       </c>
       <c r="C202" s="5">
@@ -6848,10 +6866,10 @@
       </c>
     </row>
     <row r="203" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A203" s="16">
+      <c r="A203" s="17">
         <v>181</v>
       </c>
-      <c r="B203" s="16">
+      <c r="B203" s="17">
         <v>2</v>
       </c>
       <c r="C203" s="5">
@@ -6859,10 +6877,10 @@
       </c>
     </row>
     <row r="204" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A204" s="16">
+      <c r="A204" s="17">
         <v>182</v>
       </c>
-      <c r="B204" s="16">
+      <c r="B204" s="17">
         <v>2</v>
       </c>
       <c r="C204" s="5">
@@ -6870,10 +6888,10 @@
       </c>
     </row>
     <row r="205" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A205" s="16">
+      <c r="A205" s="17">
         <v>183</v>
       </c>
-      <c r="B205" s="16">
+      <c r="B205" s="17">
         <v>2</v>
       </c>
       <c r="C205" s="5">
@@ -6881,10 +6899,10 @@
       </c>
     </row>
     <row r="206" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A206" s="16">
+      <c r="A206" s="17">
         <v>184</v>
       </c>
-      <c r="B206" s="16">
+      <c r="B206" s="17">
         <v>2</v>
       </c>
       <c r="C206" s="5">
@@ -6892,10 +6910,10 @@
       </c>
     </row>
     <row r="207" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A207" s="16">
+      <c r="A207" s="17">
         <v>185</v>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="17">
         <v>2</v>
       </c>
       <c r="C207" s="5">
@@ -6903,10 +6921,10 @@
       </c>
     </row>
     <row r="208" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A208" s="16">
+      <c r="A208" s="17">
         <v>186</v>
       </c>
-      <c r="B208" s="16">
+      <c r="B208" s="17">
         <v>2</v>
       </c>
       <c r="C208" s="5">
@@ -6914,10 +6932,10 @@
       </c>
     </row>
     <row r="209" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A209" s="16">
+      <c r="A209" s="17">
         <v>187</v>
       </c>
-      <c r="B209" s="16">
+      <c r="B209" s="17">
         <v>2</v>
       </c>
       <c r="C209" s="5">
@@ -6925,10 +6943,10 @@
       </c>
     </row>
     <row r="210" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A210" s="16">
+      <c r="A210" s="17">
         <v>188</v>
       </c>
-      <c r="B210" s="16">
+      <c r="B210" s="17">
         <v>2</v>
       </c>
       <c r="C210" s="5">
@@ -6936,10 +6954,10 @@
       </c>
     </row>
     <row r="211" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A211" s="16">
+      <c r="A211" s="17">
         <v>189</v>
       </c>
-      <c r="B211" s="16">
+      <c r="B211" s="17">
         <v>2</v>
       </c>
       <c r="C211" s="5">
@@ -6947,10 +6965,10 @@
       </c>
     </row>
     <row r="212" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A212" s="16">
+      <c r="A212" s="17">
         <v>190</v>
       </c>
-      <c r="B212" s="16">
+      <c r="B212" s="17">
         <v>2</v>
       </c>
       <c r="C212" s="5">
@@ -6958,10 +6976,10 @@
       </c>
     </row>
     <row r="213" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A213" s="16">
+      <c r="A213" s="17">
         <v>191</v>
       </c>
-      <c r="B213" s="16">
+      <c r="B213" s="17">
         <v>2</v>
       </c>
       <c r="C213" s="5">
@@ -6969,10 +6987,10 @@
       </c>
     </row>
     <row r="214" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A214" s="16">
+      <c r="A214" s="17">
         <v>192</v>
       </c>
-      <c r="B214" s="16">
+      <c r="B214" s="17">
         <v>2</v>
       </c>
       <c r="C214" s="5">
@@ -6980,10 +6998,10 @@
       </c>
     </row>
     <row r="215" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A215" s="16">
+      <c r="A215" s="17">
         <v>193</v>
       </c>
-      <c r="B215" s="16">
+      <c r="B215" s="17">
         <v>2</v>
       </c>
       <c r="C215" s="5">
@@ -6991,10 +7009,10 @@
       </c>
     </row>
     <row r="216" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A216" s="16">
+      <c r="A216" s="17">
         <v>194</v>
       </c>
-      <c r="B216" s="16">
+      <c r="B216" s="17">
         <v>2</v>
       </c>
       <c r="C216" s="5">
@@ -7002,10 +7020,10 @@
       </c>
     </row>
     <row r="217" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A217" s="16">
+      <c r="A217" s="17">
         <v>195</v>
       </c>
-      <c r="B217" s="16">
+      <c r="B217" s="17">
         <v>2</v>
       </c>
       <c r="C217" s="5">
@@ -7013,10 +7031,10 @@
       </c>
     </row>
     <row r="218" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A218" s="16">
+      <c r="A218" s="17">
         <v>196</v>
       </c>
-      <c r="B218" s="16">
+      <c r="B218" s="17">
         <v>2</v>
       </c>
       <c r="C218" s="5">
@@ -7024,10 +7042,10 @@
       </c>
     </row>
     <row r="219" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A219" s="16">
+      <c r="A219" s="17">
         <v>197</v>
       </c>
-      <c r="B219" s="16">
+      <c r="B219" s="17">
         <v>2</v>
       </c>
       <c r="C219" s="5">
@@ -7035,10 +7053,10 @@
       </c>
     </row>
     <row r="220" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A220" s="16">
+      <c r="A220" s="17">
         <v>198</v>
       </c>
-      <c r="B220" s="16">
+      <c r="B220" s="17">
         <v>2</v>
       </c>
       <c r="C220" s="5">
@@ -7046,10 +7064,10 @@
       </c>
     </row>
     <row r="221" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A221" s="16">
+      <c r="A221" s="17">
         <v>199</v>
       </c>
-      <c r="B221" s="16">
+      <c r="B221" s="17">
         <v>2</v>
       </c>
       <c r="C221" s="5">
@@ -7057,10 +7075,10 @@
       </c>
     </row>
     <row r="222" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A222" s="16">
+      <c r="A222" s="17">
         <v>200</v>
       </c>
-      <c r="B222" s="16">
+      <c r="B222" s="17">
         <v>2</v>
       </c>
       <c r="C222" s="5">
@@ -7068,10 +7086,10 @@
       </c>
     </row>
     <row r="223" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A223" s="16">
+      <c r="A223" s="17">
         <v>201</v>
       </c>
-      <c r="B223" s="16">
+      <c r="B223" s="17">
         <v>2</v>
       </c>
       <c r="C223" s="5">
@@ -7079,10 +7097,10 @@
       </c>
     </row>
     <row r="224" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A224" s="16">
+      <c r="A224" s="17">
         <v>202</v>
       </c>
-      <c r="B224" s="16">
+      <c r="B224" s="17">
         <v>2</v>
       </c>
       <c r="C224" s="5">
@@ -7090,10 +7108,10 @@
       </c>
     </row>
     <row r="225" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A225" s="16">
+      <c r="A225" s="17">
         <v>203</v>
       </c>
-      <c r="B225" s="16">
+      <c r="B225" s="17">
         <v>2</v>
       </c>
       <c r="C225" s="5">
@@ -7101,10 +7119,10 @@
       </c>
     </row>
     <row r="226" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A226" s="16">
+      <c r="A226" s="17">
         <v>204</v>
       </c>
-      <c r="B226" s="16">
+      <c r="B226" s="17">
         <v>2</v>
       </c>
       <c r="C226" s="5">
@@ -7112,10 +7130,10 @@
       </c>
     </row>
     <row r="227" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A227" s="16">
+      <c r="A227" s="17">
         <v>205</v>
       </c>
-      <c r="B227" s="16">
+      <c r="B227" s="17">
         <v>2</v>
       </c>
       <c r="C227" s="5">
@@ -7123,10 +7141,10 @@
       </c>
     </row>
     <row r="228" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A228" s="16">
+      <c r="A228" s="17">
         <v>206</v>
       </c>
-      <c r="B228" s="16">
+      <c r="B228" s="17">
         <v>2</v>
       </c>
       <c r="C228" s="5">
@@ -7134,10 +7152,10 @@
       </c>
     </row>
     <row r="229" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A229" s="16">
+      <c r="A229" s="17">
         <v>207</v>
       </c>
-      <c r="B229" s="16">
+      <c r="B229" s="17">
         <v>2</v>
       </c>
       <c r="C229" s="5">
@@ -7145,10 +7163,10 @@
       </c>
     </row>
     <row r="230" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A230" s="16">
+      <c r="A230" s="17">
         <v>208</v>
       </c>
-      <c r="B230" s="16">
+      <c r="B230" s="17">
         <v>2</v>
       </c>
       <c r="C230" s="5">
@@ -7156,10 +7174,10 @@
       </c>
     </row>
     <row r="231" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A231" s="16">
+      <c r="A231" s="17">
         <v>209</v>
       </c>
-      <c r="B231" s="16">
+      <c r="B231" s="17">
         <v>2</v>
       </c>
       <c r="C231" s="5">
@@ -7167,10 +7185,10 @@
       </c>
     </row>
     <row r="232" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A232" s="16">
+      <c r="A232" s="17">
         <v>210</v>
       </c>
-      <c r="B232" s="16">
+      <c r="B232" s="17">
         <v>2</v>
       </c>
       <c r="C232" s="5">
@@ -7178,10 +7196,10 @@
       </c>
     </row>
     <row r="233" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A233" s="16">
+      <c r="A233" s="17">
         <v>211</v>
       </c>
-      <c r="B233" s="16">
+      <c r="B233" s="17">
         <v>2</v>
       </c>
       <c r="C233" s="5">
@@ -7189,10 +7207,10 @@
       </c>
     </row>
     <row r="234" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A234" s="16">
+      <c r="A234" s="17">
         <v>212</v>
       </c>
-      <c r="B234" s="16">
+      <c r="B234" s="17">
         <v>2</v>
       </c>
       <c r="C234" s="5">
@@ -7200,10 +7218,10 @@
       </c>
     </row>
     <row r="235" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A235" s="16">
+      <c r="A235" s="17">
         <v>213</v>
       </c>
-      <c r="B235" s="16">
+      <c r="B235" s="17">
         <v>2</v>
       </c>
       <c r="C235" s="5">
@@ -7211,10 +7229,10 @@
       </c>
     </row>
     <row r="236" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A236" s="16">
+      <c r="A236" s="17">
         <v>214</v>
       </c>
-      <c r="B236" s="16">
+      <c r="B236" s="17">
         <v>2</v>
       </c>
       <c r="C236" s="5">
@@ -7222,10 +7240,10 @@
       </c>
     </row>
     <row r="237" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A237" s="16">
+      <c r="A237" s="17">
         <v>215</v>
       </c>
-      <c r="B237" s="16">
+      <c r="B237" s="17">
         <v>2</v>
       </c>
       <c r="C237" s="5">
@@ -7233,10 +7251,10 @@
       </c>
     </row>
     <row r="238" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A238" s="16">
+      <c r="A238" s="17">
         <v>216</v>
       </c>
-      <c r="B238" s="16">
+      <c r="B238" s="17">
         <v>2</v>
       </c>
       <c r="C238" s="5">
@@ -7244,10 +7262,10 @@
       </c>
     </row>
     <row r="239" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A239" s="16">
+      <c r="A239" s="17">
         <v>217</v>
       </c>
-      <c r="B239" s="16">
+      <c r="B239" s="17">
         <v>2</v>
       </c>
       <c r="C239" s="5">
@@ -7255,10 +7273,10 @@
       </c>
     </row>
     <row r="240" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A240" s="16">
+      <c r="A240" s="17">
         <v>218</v>
       </c>
-      <c r="B240" s="16">
+      <c r="B240" s="17">
         <v>2</v>
       </c>
       <c r="C240" s="5">
@@ -7266,10 +7284,10 @@
       </c>
     </row>
     <row r="241" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A241" s="16">
+      <c r="A241" s="17">
         <v>219</v>
       </c>
-      <c r="B241" s="16">
+      <c r="B241" s="17">
         <v>2</v>
       </c>
       <c r="C241" s="5">
@@ -7277,10 +7295,10 @@
       </c>
     </row>
     <row r="242" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A242" s="16">
+      <c r="A242" s="17">
         <v>220</v>
       </c>
-      <c r="B242" s="16">
+      <c r="B242" s="17">
         <v>2</v>
       </c>
       <c r="C242" s="5">
@@ -7288,10 +7306,10 @@
       </c>
     </row>
     <row r="243" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A243" s="16">
+      <c r="A243" s="17">
         <v>221</v>
       </c>
-      <c r="B243" s="16">
+      <c r="B243" s="17">
         <v>2</v>
       </c>
       <c r="C243" s="5">
@@ -7299,10 +7317,10 @@
       </c>
     </row>
     <row r="244" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A244" s="16">
+      <c r="A244" s="17">
         <v>222</v>
       </c>
-      <c r="B244" s="16">
+      <c r="B244" s="17">
         <v>2</v>
       </c>
       <c r="C244" s="5">
@@ -7310,10 +7328,10 @@
       </c>
     </row>
     <row r="245" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A245" s="16">
+      <c r="A245" s="17">
         <v>223</v>
       </c>
-      <c r="B245" s="16">
+      <c r="B245" s="17">
         <v>2</v>
       </c>
       <c r="C245" s="5">
@@ -7321,10 +7339,10 @@
       </c>
     </row>
     <row r="246" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A246" s="16">
+      <c r="A246" s="17">
         <v>224</v>
       </c>
-      <c r="B246" s="16">
+      <c r="B246" s="17">
         <v>2</v>
       </c>
       <c r="C246" s="5">
@@ -7332,10 +7350,10 @@
       </c>
     </row>
     <row r="247" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A247" s="16">
+      <c r="A247" s="17">
         <v>225</v>
       </c>
-      <c r="B247" s="16">
+      <c r="B247" s="17">
         <v>2</v>
       </c>
       <c r="C247" s="5">
@@ -7343,10 +7361,10 @@
       </c>
     </row>
     <row r="248" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A248" s="16">
+      <c r="A248" s="17">
         <v>226</v>
       </c>
-      <c r="B248" s="16">
+      <c r="B248" s="17">
         <v>2</v>
       </c>
       <c r="C248" s="5">
@@ -7354,10 +7372,10 @@
       </c>
     </row>
     <row r="249" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A249" s="16">
+      <c r="A249" s="17">
         <v>227</v>
       </c>
-      <c r="B249" s="16">
+      <c r="B249" s="17">
         <v>2</v>
       </c>
       <c r="C249" s="5">
@@ -7365,10 +7383,10 @@
       </c>
     </row>
     <row r="250" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A250" s="16">
+      <c r="A250" s="17">
         <v>228</v>
       </c>
-      <c r="B250" s="16">
+      <c r="B250" s="17">
         <v>2</v>
       </c>
       <c r="C250" s="5">
@@ -7376,10 +7394,10 @@
       </c>
     </row>
     <row r="251" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A251" s="16">
+      <c r="A251" s="17">
         <v>229</v>
       </c>
-      <c r="B251" s="16">
+      <c r="B251" s="17">
         <v>2</v>
       </c>
       <c r="C251" s="5">
@@ -7387,10 +7405,10 @@
       </c>
     </row>
     <row r="252" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A252" s="16">
+      <c r="A252" s="17">
         <v>230</v>
       </c>
-      <c r="B252" s="16">
+      <c r="B252" s="17">
         <v>2</v>
       </c>
       <c r="C252" s="5">
@@ -7398,10 +7416,10 @@
       </c>
     </row>
     <row r="253" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A253" s="16">
+      <c r="A253" s="17">
         <v>231</v>
       </c>
-      <c r="B253" s="16">
+      <c r="B253" s="17">
         <v>2</v>
       </c>
       <c r="C253" s="5">
@@ -7409,10 +7427,10 @@
       </c>
     </row>
     <row r="254" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A254" s="16">
+      <c r="A254" s="17">
         <v>232</v>
       </c>
-      <c r="B254" s="16">
+      <c r="B254" s="17">
         <v>2</v>
       </c>
       <c r="C254" s="5">
@@ -7420,10 +7438,10 @@
       </c>
     </row>
     <row r="255" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A255" s="16">
+      <c r="A255" s="17">
         <v>233</v>
       </c>
-      <c r="B255" s="16">
+      <c r="B255" s="17">
         <v>2</v>
       </c>
       <c r="C255" s="5">
@@ -7431,10 +7449,10 @@
       </c>
     </row>
     <row r="256" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A256" s="16">
+      <c r="A256" s="17">
         <v>234</v>
       </c>
-      <c r="B256" s="16">
+      <c r="B256" s="17">
         <v>2</v>
       </c>
       <c r="C256" s="5">
@@ -7442,10 +7460,10 @@
       </c>
     </row>
     <row r="257" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A257" s="16">
+      <c r="A257" s="17">
         <v>235</v>
       </c>
-      <c r="B257" s="16">
+      <c r="B257" s="17">
         <v>2</v>
       </c>
       <c r="C257" s="5">
@@ -7453,10 +7471,10 @@
       </c>
     </row>
     <row r="258" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A258" s="16">
+      <c r="A258" s="17">
         <v>236</v>
       </c>
-      <c r="B258" s="16">
+      <c r="B258" s="17">
         <v>2</v>
       </c>
       <c r="C258" s="5">
@@ -7464,10 +7482,10 @@
       </c>
     </row>
     <row r="259" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A259" s="16">
+      <c r="A259" s="17">
         <v>237</v>
       </c>
-      <c r="B259" s="16">
+      <c r="B259" s="17">
         <v>2</v>
       </c>
       <c r="C259" s="5">
@@ -7475,10 +7493,10 @@
       </c>
     </row>
     <row r="260" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A260" s="16">
+      <c r="A260" s="17">
         <v>238</v>
       </c>
-      <c r="B260" s="16">
+      <c r="B260" s="17">
         <v>2</v>
       </c>
       <c r="C260" s="5">
@@ -7486,10 +7504,10 @@
       </c>
     </row>
     <row r="261" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A261" s="16">
+      <c r="A261" s="17">
         <v>239</v>
       </c>
-      <c r="B261" s="16">
+      <c r="B261" s="17">
         <v>2</v>
       </c>
       <c r="C261" s="5">
@@ -7497,10 +7515,10 @@
       </c>
     </row>
     <row r="262" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A262" s="16">
+      <c r="A262" s="17">
         <v>240</v>
       </c>
-      <c r="B262" s="16">
+      <c r="B262" s="17">
         <v>2</v>
       </c>
       <c r="C262" s="5">
@@ -7508,10 +7526,10 @@
       </c>
     </row>
     <row r="263" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A263" s="16">
+      <c r="A263" s="17">
         <v>241</v>
       </c>
-      <c r="B263" s="16">
+      <c r="B263" s="17">
         <v>2</v>
       </c>
       <c r="C263" s="5">
@@ -7519,10 +7537,10 @@
       </c>
     </row>
     <row r="264" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A264" s="16">
+      <c r="A264" s="17">
         <v>242</v>
       </c>
-      <c r="B264" s="16">
+      <c r="B264" s="17">
         <v>2</v>
       </c>
       <c r="C264" s="5">
@@ -7530,10 +7548,10 @@
       </c>
     </row>
     <row r="265" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A265" s="16">
+      <c r="A265" s="17">
         <v>243</v>
       </c>
-      <c r="B265" s="16">
+      <c r="B265" s="17">
         <v>2</v>
       </c>
       <c r="C265" s="5">
@@ -7541,10 +7559,10 @@
       </c>
     </row>
     <row r="266" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A266" s="16">
+      <c r="A266" s="17">
         <v>244</v>
       </c>
-      <c r="B266" s="16">
+      <c r="B266" s="17">
         <v>2</v>
       </c>
       <c r="C266" s="5">
@@ -7552,10 +7570,10 @@
       </c>
     </row>
     <row r="267" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A267" s="16">
+      <c r="A267" s="17">
         <v>245</v>
       </c>
-      <c r="B267" s="16">
+      <c r="B267" s="17">
         <v>2</v>
       </c>
       <c r="C267" s="5">
@@ -7563,10 +7581,10 @@
       </c>
     </row>
     <row r="268" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A268" s="16">
+      <c r="A268" s="17">
         <v>246</v>
       </c>
-      <c r="B268" s="16">
+      <c r="B268" s="17">
         <v>2</v>
       </c>
       <c r="C268" s="5">
@@ -7574,10 +7592,10 @@
       </c>
     </row>
     <row r="269" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A269" s="16">
+      <c r="A269" s="17">
         <v>247</v>
       </c>
-      <c r="B269" s="16">
+      <c r="B269" s="17">
         <v>2</v>
       </c>
       <c r="C269" s="5">
@@ -7585,10 +7603,10 @@
       </c>
     </row>
     <row r="270" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A270" s="16">
+      <c r="A270" s="17">
         <v>248</v>
       </c>
-      <c r="B270" s="16">
+      <c r="B270" s="17">
         <v>2</v>
       </c>
       <c r="C270" s="5">
@@ -7596,10 +7614,10 @@
       </c>
     </row>
     <row r="271" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A271" s="16">
+      <c r="A271" s="17">
         <v>249</v>
       </c>
-      <c r="B271" s="16">
+      <c r="B271" s="17">
         <v>2</v>
       </c>
       <c r="C271" s="5">
@@ -7607,10 +7625,10 @@
       </c>
     </row>
     <row r="272" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A272" s="16">
+      <c r="A272" s="17">
         <v>250</v>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="17">
         <v>2</v>
       </c>
       <c r="C272" s="5">
@@ -7618,10 +7636,10 @@
       </c>
     </row>
     <row r="273" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A273" s="16">
+      <c r="A273" s="17">
         <v>251</v>
       </c>
-      <c r="B273" s="16">
+      <c r="B273" s="17">
         <v>2</v>
       </c>
       <c r="C273" s="5">
@@ -7629,10 +7647,10 @@
       </c>
     </row>
     <row r="274" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A274" s="16">
+      <c r="A274" s="17">
         <v>252</v>
       </c>
-      <c r="B274" s="16">
+      <c r="B274" s="17">
         <v>2</v>
       </c>
       <c r="C274" s="5">
@@ -7640,10 +7658,10 @@
       </c>
     </row>
     <row r="275" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A275" s="16">
+      <c r="A275" s="17">
         <v>253</v>
       </c>
-      <c r="B275" s="16">
+      <c r="B275" s="17">
         <v>2</v>
       </c>
       <c r="C275" s="5">
@@ -7651,10 +7669,10 @@
       </c>
     </row>
     <row r="276" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A276" s="16">
+      <c r="A276" s="17">
         <v>254</v>
       </c>
-      <c r="B276" s="16">
+      <c r="B276" s="17">
         <v>2</v>
       </c>
       <c r="C276" s="5">
@@ -7662,10 +7680,10 @@
       </c>
     </row>
     <row r="277" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A277" s="16">
+      <c r="A277" s="17">
         <v>255</v>
       </c>
-      <c r="B277" s="16">
+      <c r="B277" s="17">
         <v>2</v>
       </c>
       <c r="C277" s="5">
@@ -7673,10 +7691,10 @@
       </c>
     </row>
     <row r="278" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A278" s="16">
+      <c r="A278" s="17">
         <v>256</v>
       </c>
-      <c r="B278" s="16">
+      <c r="B278" s="17">
         <v>2</v>
       </c>
       <c r="C278" s="5">
@@ -7684,10 +7702,10 @@
       </c>
     </row>
     <row r="279" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A279" s="16">
+      <c r="A279" s="17">
         <v>257</v>
       </c>
-      <c r="B279" s="16">
+      <c r="B279" s="17">
         <v>2</v>
       </c>
       <c r="C279" s="5">
@@ -7695,10 +7713,10 @@
       </c>
     </row>
     <row r="280" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A280" s="16">
+      <c r="A280" s="17">
         <v>258</v>
       </c>
-      <c r="B280" s="16">
+      <c r="B280" s="17">
         <v>2</v>
       </c>
       <c r="C280" s="5">
@@ -7706,10 +7724,10 @@
       </c>
     </row>
     <row r="281" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A281" s="16">
+      <c r="A281" s="17">
         <v>259</v>
       </c>
-      <c r="B281" s="16">
+      <c r="B281" s="17">
         <v>2</v>
       </c>
       <c r="C281" s="5">
@@ -7717,10 +7735,10 @@
       </c>
     </row>
     <row r="282" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A282" s="16">
+      <c r="A282" s="17">
         <v>260</v>
       </c>
-      <c r="B282" s="16">
+      <c r="B282" s="17">
         <v>2</v>
       </c>
       <c r="C282" s="5">
@@ -7728,10 +7746,10 @@
       </c>
     </row>
     <row r="283" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A283" s="16">
+      <c r="A283" s="17">
         <v>261</v>
       </c>
-      <c r="B283" s="16">
+      <c r="B283" s="17">
         <v>2</v>
       </c>
       <c r="C283" s="5">
@@ -7739,10 +7757,10 @@
       </c>
     </row>
     <row r="284" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A284" s="16">
+      <c r="A284" s="17">
         <v>262</v>
       </c>
-      <c r="B284" s="16">
+      <c r="B284" s="17">
         <v>2</v>
       </c>
       <c r="C284" s="5">
@@ -7750,10 +7768,10 @@
       </c>
     </row>
     <row r="285" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A285" s="16">
+      <c r="A285" s="17">
         <v>263</v>
       </c>
-      <c r="B285" s="16">
+      <c r="B285" s="17">
         <v>2</v>
       </c>
       <c r="C285" s="5">
@@ -7761,10 +7779,10 @@
       </c>
     </row>
     <row r="286" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A286" s="16">
+      <c r="A286" s="17">
         <v>264</v>
       </c>
-      <c r="B286" s="16">
+      <c r="B286" s="17">
         <v>2</v>
       </c>
       <c r="C286" s="5">
@@ -7772,10 +7790,10 @@
       </c>
     </row>
     <row r="287" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A287" s="16">
+      <c r="A287" s="17">
         <v>265</v>
       </c>
-      <c r="B287" s="16">
+      <c r="B287" s="17">
         <v>2</v>
       </c>
       <c r="C287" s="5">
@@ -7783,10 +7801,10 @@
       </c>
     </row>
     <row r="288" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A288" s="16">
+      <c r="A288" s="17">
         <v>266</v>
       </c>
-      <c r="B288" s="16">
+      <c r="B288" s="17">
         <v>2</v>
       </c>
       <c r="C288" s="5">
@@ -7794,10 +7812,10 @@
       </c>
     </row>
     <row r="289" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A289" s="16">
+      <c r="A289" s="17">
         <v>267</v>
       </c>
-      <c r="B289" s="16">
+      <c r="B289" s="17">
         <v>2</v>
       </c>
       <c r="C289" s="5">
@@ -7805,10 +7823,10 @@
       </c>
     </row>
     <row r="290" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A290" s="16">
+      <c r="A290" s="17">
         <v>268</v>
       </c>
-      <c r="B290" s="16">
+      <c r="B290" s="17">
         <v>2</v>
       </c>
       <c r="C290" s="5">
@@ -7816,10 +7834,10 @@
       </c>
     </row>
     <row r="291" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A291" s="16">
+      <c r="A291" s="17">
         <v>269</v>
       </c>
-      <c r="B291" s="16">
+      <c r="B291" s="17">
         <v>2</v>
       </c>
       <c r="C291" s="5">
@@ -7827,10 +7845,10 @@
       </c>
     </row>
     <row r="292" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A292" s="16">
+      <c r="A292" s="17">
         <v>270</v>
       </c>
-      <c r="B292" s="16">
+      <c r="B292" s="17">
         <v>2</v>
       </c>
       <c r="C292" s="5">
@@ -7838,10 +7856,10 @@
       </c>
     </row>
     <row r="293" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A293" s="16">
+      <c r="A293" s="17">
         <v>271</v>
       </c>
-      <c r="B293" s="16">
+      <c r="B293" s="17">
         <v>2</v>
       </c>
       <c r="C293" s="5">
@@ -7849,10 +7867,10 @@
       </c>
     </row>
     <row r="294" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A294" s="16">
+      <c r="A294" s="17">
         <v>272</v>
       </c>
-      <c r="B294" s="16">
+      <c r="B294" s="17">
         <v>2</v>
       </c>
       <c r="C294" s="5">
@@ -7860,10 +7878,10 @@
       </c>
     </row>
     <row r="295" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A295" s="16">
+      <c r="A295" s="17">
         <v>273</v>
       </c>
-      <c r="B295" s="16">
+      <c r="B295" s="17">
         <v>2</v>
       </c>
       <c r="C295" s="5">
@@ -7871,10 +7889,10 @@
       </c>
     </row>
     <row r="296" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A296" s="16">
+      <c r="A296" s="17">
         <v>274</v>
       </c>
-      <c r="B296" s="16">
+      <c r="B296" s="17">
         <v>2</v>
       </c>
       <c r="C296" s="5">
@@ -7882,10 +7900,10 @@
       </c>
     </row>
     <row r="297" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A297" s="16">
+      <c r="A297" s="17">
         <v>275</v>
       </c>
-      <c r="B297" s="16">
+      <c r="B297" s="17">
         <v>2</v>
       </c>
       <c r="C297" s="5">
@@ -7893,10 +7911,10 @@
       </c>
     </row>
     <row r="298" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A298" s="16">
+      <c r="A298" s="17">
         <v>276</v>
       </c>
-      <c r="B298" s="16">
+      <c r="B298" s="17">
         <v>2</v>
       </c>
       <c r="C298" s="5">
@@ -7904,10 +7922,10 @@
       </c>
     </row>
     <row r="299" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A299" s="16">
+      <c r="A299" s="17">
         <v>277</v>
       </c>
-      <c r="B299" s="16">
+      <c r="B299" s="17">
         <v>2</v>
       </c>
       <c r="C299" s="5">
@@ -7915,10 +7933,10 @@
       </c>
     </row>
     <row r="300" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A300" s="16">
+      <c r="A300" s="17">
         <v>278</v>
       </c>
-      <c r="B300" s="16">
+      <c r="B300" s="17">
         <v>2</v>
       </c>
       <c r="C300" s="5">
@@ -7926,10 +7944,10 @@
       </c>
     </row>
     <row r="301" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A301" s="16">
+      <c r="A301" s="17">
         <v>279</v>
       </c>
-      <c r="B301" s="16">
+      <c r="B301" s="17">
         <v>2</v>
       </c>
       <c r="C301" s="5">
@@ -7937,10 +7955,10 @@
       </c>
     </row>
     <row r="302" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A302" s="16">
+      <c r="A302" s="17">
         <v>280</v>
       </c>
-      <c r="B302" s="16">
+      <c r="B302" s="17">
         <v>2</v>
       </c>
       <c r="C302" s="5">
@@ -7948,10 +7966,10 @@
       </c>
     </row>
     <row r="303" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A303" s="16">
+      <c r="A303" s="17">
         <v>281</v>
       </c>
-      <c r="B303" s="16">
+      <c r="B303" s="17">
         <v>2</v>
       </c>
       <c r="C303" s="5">
@@ -7959,10 +7977,10 @@
       </c>
     </row>
     <row r="304" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A304" s="16">
+      <c r="A304" s="17">
         <v>282</v>
       </c>
-      <c r="B304" s="16">
+      <c r="B304" s="17">
         <v>2</v>
       </c>
       <c r="C304" s="5">
@@ -7970,98 +7988,98 @@
       </c>
     </row>
     <row r="305" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A305" s="16">
+      <c r="A305" s="17">
         <v>283</v>
       </c>
-      <c r="B305" s="16">
+      <c r="B305" s="17">
         <v>2</v>
       </c>
       <c r="C305" s="5">
         <v>2111</v>
       </c>
     </row>
-    <row r="306" ht="15.5" spans="1:3">
-      <c r="A306" s="16">
+    <row r="306" ht="15.75" spans="1:3">
+      <c r="A306" s="17">
         <v>284</v>
       </c>
-      <c r="B306" s="16">
+      <c r="B306" s="17">
         <v>2</v>
       </c>
       <c r="C306" s="5">
         <v>22</v>
       </c>
     </row>
-    <row r="307" ht="15.5" spans="1:3">
-      <c r="A307" s="16">
+    <row r="307" ht="15.75" spans="1:3">
+      <c r="A307" s="17">
         <v>285</v>
       </c>
-      <c r="B307" s="16">
+      <c r="B307" s="17">
         <v>2</v>
       </c>
       <c r="C307" s="5">
         <v>2201</v>
       </c>
     </row>
-    <row r="308" ht="15.5" spans="1:3">
-      <c r="A308" s="16">
+    <row r="308" ht="15.75" spans="1:3">
+      <c r="A308" s="17">
         <v>286</v>
       </c>
-      <c r="B308" s="16">
+      <c r="B308" s="17">
         <v>2</v>
       </c>
       <c r="C308" s="5">
         <v>2202</v>
       </c>
     </row>
-    <row r="309" ht="15.5" spans="1:3">
-      <c r="A309" s="16">
+    <row r="309" ht="15.75" spans="1:3">
+      <c r="A309" s="17">
         <v>287</v>
       </c>
-      <c r="B309" s="16">
+      <c r="B309" s="17">
         <v>2</v>
       </c>
       <c r="C309" s="5">
         <v>23</v>
       </c>
     </row>
-    <row r="310" ht="15.5" spans="1:3">
-      <c r="A310" s="16">
+    <row r="310" ht="15.75" spans="1:3">
+      <c r="A310" s="17">
         <v>288</v>
       </c>
-      <c r="B310" s="16">
+      <c r="B310" s="17">
         <v>2</v>
       </c>
       <c r="C310" s="5">
         <v>2301</v>
       </c>
     </row>
-    <row r="311" ht="15.5" spans="1:3">
-      <c r="A311" s="16">
+    <row r="311" ht="15.75" spans="1:3">
+      <c r="A311" s="17">
         <v>289</v>
       </c>
-      <c r="B311" s="16">
+      <c r="B311" s="17">
         <v>2</v>
       </c>
       <c r="C311" s="5">
         <v>2302</v>
       </c>
     </row>
-    <row r="312" ht="15.5" spans="1:3">
-      <c r="A312" s="16">
+    <row r="312" ht="15.75" spans="1:3">
+      <c r="A312" s="17">
         <v>290</v>
       </c>
-      <c r="B312" s="16">
+      <c r="B312" s="17">
         <v>2</v>
       </c>
       <c r="C312" s="5">
         <v>2303</v>
       </c>
     </row>
-    <row r="313" ht="15.5" spans="1:3">
-      <c r="A313" s="16">
+    <row r="313" ht="15.75" spans="1:3">
+      <c r="A313" s="17">
         <v>291</v>
       </c>
-      <c r="B313" s="16">
+      <c r="B313" s="17">
         <v>2</v>
       </c>
       <c r="C313" s="5">
@@ -8078,8 +8096,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J348"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:J349"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.6333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -8091,7 +8109,7 @@
     <col min="10" max="10" width="17.825" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:10">
+    <row r="1" ht="23.25" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -15570,118 +15588,116 @@
       </c>
       <c r="J270" s="6"/>
     </row>
-    <row r="271" spans="10:10">
+    <row r="271" spans="1:10">
+      <c r="A271" s="5">
+        <v>1405</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C271" s="5">
+        <v>14</v>
+      </c>
+      <c r="D271" s="5">
+        <v>1405</v>
+      </c>
+      <c r="E271" s="5"/>
+      <c r="F271" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H271" s="2"/>
+      <c r="I271" s="2"/>
       <c r="J271" s="6"/>
     </row>
-    <row r="272" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A272" s="5">
-        <v>15</v>
-      </c>
-      <c r="B272" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="C272" s="5">
-        <v>1</v>
-      </c>
-      <c r="D272" s="5">
-        <v>15</v>
-      </c>
-      <c r="E272" s="5"/>
-      <c r="F272" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G272" s="6"/>
-      <c r="H272" s="6"/>
-      <c r="I272" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="J272" s="6"/>
+    <row r="272" spans="8:10">
+      <c r="H272" s="1"/>
+      <c r="I272" s="1"/>
+      <c r="J272" s="14"/>
     </row>
     <row r="273" ht="20.1" customHeight="1" spans="1:10">
       <c r="A273" s="5">
-        <v>1501</v>
+        <v>15</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C273" s="5">
+        <v>1</v>
+      </c>
+      <c r="D273" s="5">
         <v>15</v>
-      </c>
-      <c r="D273" s="5">
-        <v>1501</v>
       </c>
       <c r="E273" s="5"/>
       <c r="F273" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G273" s="6" t="s">
-        <v>309</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G273" s="6"/>
       <c r="H273" s="6"/>
       <c r="I273" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J273" s="6"/>
     </row>
     <row r="274" ht="20.1" customHeight="1" spans="1:10">
       <c r="A274" s="5">
-        <v>150101</v>
+        <v>1501</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>310</v>
       </c>
       <c r="C274" s="5">
+        <v>15</v>
+      </c>
+      <c r="D274" s="5">
         <v>1501</v>
-      </c>
-      <c r="D274" s="5">
-        <v>150101</v>
       </c>
       <c r="E274" s="5"/>
       <c r="F274" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G274" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="H274" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="H274" s="6"/>
       <c r="I274" s="6" t="s">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="J274" s="6"/>
     </row>
     <row r="275" ht="20.1" customHeight="1" spans="1:10">
       <c r="A275" s="5">
-        <v>150102</v>
+        <v>150101</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C275" s="5">
         <v>1501</v>
       </c>
       <c r="D275" s="5">
-        <v>150102</v>
+        <v>150101</v>
       </c>
       <c r="E275" s="5"/>
       <c r="F275" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G275" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H275" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J275" s="6"/>
     </row>
     <row r="276" ht="20.1" customHeight="1" spans="1:10">
       <c r="A276" s="5">
-        <v>150103</v>
+        <v>150102</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>312</v>
@@ -15690,332 +15706,334 @@
         <v>1501</v>
       </c>
       <c r="D276" s="5">
-        <v>150103</v>
+        <v>150102</v>
       </c>
       <c r="E276" s="5"/>
       <c r="F276" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G276" s="6" t="s">
         <v>313</v>
       </c>
       <c r="H276" s="6" t="s">
-        <v>297</v>
+        <v>61</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>297</v>
+        <v>61</v>
       </c>
       <c r="J276" s="6"/>
     </row>
     <row r="277" ht="20.1" customHeight="1" spans="1:10">
       <c r="A277" s="5">
-        <v>150104</v>
+        <v>150103</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C277" s="5">
         <v>1501</v>
       </c>
       <c r="D277" s="5">
-        <v>150104</v>
+        <v>150103</v>
       </c>
       <c r="E277" s="5"/>
       <c r="F277" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G277" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H277" s="6" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="J277" s="6"/>
     </row>
     <row r="278" ht="20.1" customHeight="1" spans="1:10">
       <c r="A278" s="5">
-        <v>150105</v>
+        <v>150104</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C278" s="5">
         <v>1501</v>
       </c>
       <c r="D278" s="5">
-        <v>150105</v>
+        <v>150104</v>
       </c>
       <c r="E278" s="5"/>
       <c r="F278" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H278" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J278" s="6"/>
     </row>
     <row r="279" ht="20.1" customHeight="1" spans="1:10">
       <c r="A279" s="5">
-        <v>150106</v>
+        <v>150105</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C279" s="5">
         <v>1501</v>
       </c>
       <c r="D279" s="5">
-        <v>150106</v>
+        <v>150105</v>
       </c>
       <c r="E279" s="5"/>
       <c r="F279" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G279" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H279" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J279" s="6"/>
     </row>
     <row r="280" ht="20.1" customHeight="1" spans="1:10">
       <c r="A280" s="5">
-        <v>150107</v>
+        <v>150106</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C280" s="5">
         <v>1501</v>
       </c>
       <c r="D280" s="5">
-        <v>150107</v>
+        <v>150106</v>
       </c>
       <c r="E280" s="5"/>
       <c r="F280" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J280" s="6"/>
     </row>
     <row r="281" ht="20.1" customHeight="1" spans="1:10">
       <c r="A281" s="5">
-        <v>150108</v>
+        <v>150107</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C281" s="5">
         <v>1501</v>
       </c>
       <c r="D281" s="5">
-        <v>150108</v>
+        <v>150107</v>
       </c>
       <c r="E281" s="5"/>
       <c r="F281" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G281" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H281" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J281" s="6"/>
     </row>
     <row r="282" ht="20.1" customHeight="1" spans="1:10">
       <c r="A282" s="5">
-        <v>150109</v>
+        <v>150108</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C282" s="5">
         <v>1501</v>
       </c>
       <c r="D282" s="5">
-        <v>150109</v>
+        <v>150108</v>
       </c>
       <c r="E282" s="5"/>
       <c r="F282" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G282" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>64</v>
+        <v>320</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>64</v>
+        <v>320</v>
       </c>
       <c r="J282" s="6"/>
     </row>
     <row r="283" ht="20.1" customHeight="1" spans="1:10">
       <c r="A283" s="5">
-        <v>150110</v>
+        <v>150109</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C283" s="5">
         <v>1501</v>
       </c>
       <c r="D283" s="5">
-        <v>150110</v>
+        <v>150109</v>
       </c>
       <c r="E283" s="5"/>
       <c r="F283" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G283" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H283" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J283" s="6"/>
     </row>
     <row r="284" ht="20.1" customHeight="1" spans="1:10">
       <c r="A284" s="5">
-        <v>150111</v>
+        <v>150110</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C284" s="5">
         <v>1501</v>
       </c>
       <c r="D284" s="5">
-        <v>150111</v>
+        <v>150110</v>
       </c>
       <c r="E284" s="5"/>
       <c r="F284" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J284" s="6"/>
     </row>
     <row r="285" ht="20.1" customHeight="1" spans="1:10">
       <c r="A285" s="5">
-        <v>150112</v>
+        <v>150111</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C285" s="5">
         <v>1501</v>
       </c>
       <c r="D285" s="5">
-        <v>150112</v>
+        <v>150111</v>
       </c>
       <c r="E285" s="5"/>
       <c r="F285" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G285" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H285" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J285" s="6"/>
     </row>
     <row r="286" ht="20.1" customHeight="1" spans="1:10">
       <c r="A286" s="5">
-        <v>150113</v>
+        <v>150112</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C286" s="5">
         <v>1501</v>
       </c>
       <c r="D286" s="5">
-        <v>150113</v>
+        <v>150112</v>
       </c>
       <c r="E286" s="5"/>
       <c r="F286" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G286" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H286" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J286" s="6"/>
     </row>
     <row r="287" ht="20.1" customHeight="1" spans="1:10">
       <c r="A287" s="5">
-        <v>1502</v>
+        <v>150113</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C287" s="5">
-        <v>15</v>
+        <v>1501</v>
       </c>
       <c r="D287" s="5">
-        <v>1502</v>
+        <v>150113</v>
       </c>
       <c r="E287" s="5"/>
       <c r="F287" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G287" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="H287" s="6"/>
+      <c r="H287" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I287" s="6" t="s">
-        <v>321</v>
+        <v>65</v>
       </c>
       <c r="J287" s="6"/>
     </row>
     <row r="288" ht="20.1" customHeight="1" spans="1:10">
       <c r="A288" s="5">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>323</v>
@@ -16024,7 +16042,7 @@
         <v>15</v>
       </c>
       <c r="D288" s="5">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E288" s="5"/>
       <c r="F288" s="5" t="s">
@@ -16040,150 +16058,148 @@
       <c r="J288" s="6"/>
     </row>
     <row r="289" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A289" s="7">
+      <c r="A289" s="5">
+        <v>1503</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C289" s="5">
+        <v>15</v>
+      </c>
+      <c r="D289" s="5">
+        <v>1503</v>
+      </c>
+      <c r="E289" s="5"/>
+      <c r="F289" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G289" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H289" s="6"/>
+      <c r="I289" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="J289" s="6"/>
+    </row>
+    <row r="290" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A290" s="7">
         <v>1504</v>
       </c>
-      <c r="B289" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="C289" s="7">
+      <c r="B290" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C290" s="7">
         <v>15</v>
       </c>
-      <c r="D289" s="7">
+      <c r="D290" s="7">
         <v>1504</v>
       </c>
-      <c r="E289" s="7"/>
-      <c r="F289" s="7" t="s">
+      <c r="E290" s="7"/>
+      <c r="F290" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G289" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H289" s="8"/>
-      <c r="I289" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="J289" s="6"/>
-    </row>
-    <row r="290" s="1" customFormat="1" ht="11" customHeight="1" spans="1:10">
-      <c r="A290" s="9"/>
-      <c r="B290" s="10"/>
-      <c r="C290" s="11"/>
-      <c r="D290" s="11"/>
-      <c r="E290" s="11"/>
-      <c r="F290" s="11"/>
-      <c r="G290" s="10"/>
-      <c r="H290" s="10"/>
-      <c r="I290" s="14"/>
+      <c r="G290" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="H290" s="8"/>
+      <c r="I290" s="8" t="s">
+        <v>327</v>
+      </c>
       <c r="J290" s="6"/>
     </row>
-    <row r="291" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A291" s="12">
+    <row r="291" s="1" customFormat="1" ht="11" customHeight="1" spans="1:10">
+      <c r="A291" s="9"/>
+      <c r="B291" s="10"/>
+      <c r="C291" s="11"/>
+      <c r="D291" s="11"/>
+      <c r="E291" s="11"/>
+      <c r="F291" s="11"/>
+      <c r="G291" s="10"/>
+      <c r="H291" s="10"/>
+      <c r="I291" s="15"/>
+      <c r="J291" s="6"/>
+    </row>
+    <row r="292" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A292" s="12">
         <v>16</v>
       </c>
-      <c r="B291" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="C291" s="12">
+      <c r="B292" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C292" s="12">
         <v>1</v>
       </c>
-      <c r="D291" s="12">
+      <c r="D292" s="12">
         <v>16</v>
       </c>
-      <c r="E291" s="12"/>
-      <c r="F291" s="12" t="s">
+      <c r="E292" s="12"/>
+      <c r="F292" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G291" s="13"/>
-      <c r="H291" s="13"/>
-      <c r="I291" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="J291" s="6"/>
-    </row>
-    <row r="292" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A292" s="5">
-        <v>1601</v>
-      </c>
-      <c r="B292" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C292" s="5">
-        <v>16</v>
-      </c>
-      <c r="D292" s="5">
-        <v>1601</v>
-      </c>
-      <c r="E292" s="5"/>
-      <c r="F292" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G292" s="6" t="s">
+      <c r="G292" s="13"/>
+      <c r="H292" s="13"/>
+      <c r="I292" s="13" t="s">
         <v>329</v>
-      </c>
-      <c r="H292" s="6"/>
-      <c r="I292" s="6" t="s">
-        <v>328</v>
       </c>
       <c r="J292" s="6"/>
     </row>
     <row r="293" ht="20.1" customHeight="1" spans="1:10">
       <c r="A293" s="5">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>144</v>
+        <v>330</v>
       </c>
       <c r="C293" s="5">
         <v>16</v>
       </c>
       <c r="D293" s="5">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="E293" s="5"/>
       <c r="F293" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G293" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H293" s="6"/>
       <c r="I293" s="6" t="s">
-        <v>144</v>
+        <v>330</v>
       </c>
       <c r="J293" s="6"/>
     </row>
     <row r="294" ht="20.1" customHeight="1" spans="1:10">
       <c r="A294" s="5">
-        <v>160201</v>
+        <v>1602</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C294" s="5">
+        <v>16</v>
+      </c>
+      <c r="D294" s="5">
         <v>1602</v>
-      </c>
-      <c r="D294" s="5">
-        <v>160201</v>
       </c>
       <c r="E294" s="5"/>
       <c r="F294" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G294" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H294" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="H294" s="6"/>
       <c r="I294" s="6" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="J294" s="6"/>
     </row>
     <row r="295" ht="20.1" customHeight="1" spans="1:10">
       <c r="A295" s="5">
-        <v>160202</v>
+        <v>160201</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>146</v>
@@ -16192,54 +16208,54 @@
         <v>1602</v>
       </c>
       <c r="D295" s="5">
-        <v>160202</v>
+        <v>160201</v>
       </c>
       <c r="E295" s="5"/>
       <c r="F295" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G295" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H295" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J295" s="6"/>
     </row>
     <row r="296" ht="20.1" customHeight="1" spans="1:10">
       <c r="A296" s="5">
-        <v>160203</v>
+        <v>160202</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C296" s="5">
         <v>1602</v>
       </c>
       <c r="D296" s="5">
-        <v>160203</v>
+        <v>160202</v>
       </c>
       <c r="E296" s="5"/>
       <c r="F296" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G296" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H296" s="6" t="s">
-        <v>333</v>
+        <v>61</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>333</v>
+        <v>61</v>
       </c>
       <c r="J296" s="6"/>
     </row>
     <row r="297" ht="20.1" customHeight="1" spans="1:10">
       <c r="A297" s="5">
-        <v>160204</v>
+        <v>160203</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>148</v>
@@ -16248,26 +16264,26 @@
         <v>1602</v>
       </c>
       <c r="D297" s="5">
-        <v>160204</v>
+        <v>160203</v>
       </c>
       <c r="E297" s="5"/>
       <c r="F297" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G297" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H297" s="6" t="s">
-        <v>64</v>
+        <v>335</v>
       </c>
       <c r="I297" s="6" t="s">
-        <v>64</v>
+        <v>335</v>
       </c>
       <c r="J297" s="6"/>
     </row>
     <row r="298" ht="20.1" customHeight="1" spans="1:10">
       <c r="A298" s="5">
-        <v>160205</v>
+        <v>160204</v>
       </c>
       <c r="B298" s="6" t="s">
         <v>148</v>
@@ -16276,54 +16292,54 @@
         <v>1602</v>
       </c>
       <c r="D298" s="5">
-        <v>160205</v>
+        <v>160204</v>
       </c>
       <c r="E298" s="5"/>
       <c r="F298" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G298" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H298" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J298" s="6"/>
     </row>
     <row r="299" ht="20.1" customHeight="1" spans="1:10">
       <c r="A299" s="5">
-        <v>160206</v>
+        <v>160205</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C299" s="5">
         <v>1602</v>
       </c>
       <c r="D299" s="5">
-        <v>160206</v>
+        <v>160205</v>
       </c>
       <c r="E299" s="5"/>
       <c r="F299" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>334</v>
       </c>
       <c r="H299" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J299" s="6"/>
     </row>
     <row r="300" ht="20.1" customHeight="1" spans="1:10">
       <c r="A300" s="5">
-        <v>160207</v>
+        <v>160206</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>150</v>
@@ -16332,26 +16348,26 @@
         <v>1602</v>
       </c>
       <c r="D300" s="5">
-        <v>160207</v>
+        <v>160206</v>
       </c>
       <c r="E300" s="5"/>
       <c r="F300" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G300" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H300" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I300" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J300" s="6"/>
     </row>
     <row r="301" ht="20.1" customHeight="1" spans="1:10">
       <c r="A301" s="5">
-        <v>160208</v>
+        <v>160207</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>150</v>
@@ -16360,136 +16376,136 @@
         <v>1602</v>
       </c>
       <c r="D301" s="5">
-        <v>160208</v>
+        <v>160207</v>
       </c>
       <c r="E301" s="5"/>
       <c r="F301" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G301" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H301" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J301" s="6"/>
     </row>
     <row r="302" ht="20.1" customHeight="1" spans="1:10">
       <c r="A302" s="5">
-        <v>1603</v>
+        <v>160208</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>335</v>
+        <v>150</v>
       </c>
       <c r="C302" s="5">
-        <v>16</v>
+        <v>1602</v>
       </c>
       <c r="D302" s="5">
-        <v>1603</v>
+        <v>160208</v>
       </c>
       <c r="E302" s="5"/>
       <c r="F302" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G302" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="H302" s="6"/>
+      <c r="H302" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I302" s="6" t="s">
-        <v>335</v>
+        <v>65</v>
       </c>
       <c r="J302" s="6"/>
     </row>
     <row r="303" ht="20.1" customHeight="1" spans="1:10">
       <c r="A303" s="5">
-        <v>160301</v>
+        <v>1603</v>
       </c>
       <c r="B303" s="6" t="s">
         <v>337</v>
       </c>
       <c r="C303" s="5">
+        <v>16</v>
+      </c>
+      <c r="D303" s="5">
         <v>1603</v>
-      </c>
-      <c r="D303" s="5">
-        <v>160301</v>
       </c>
       <c r="E303" s="5"/>
       <c r="F303" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G303" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="H303" s="6" t="s">
-        <v>156</v>
-      </c>
+      <c r="H303" s="6"/>
       <c r="I303" s="6" t="s">
-        <v>156</v>
+        <v>337</v>
       </c>
       <c r="J303" s="6"/>
     </row>
     <row r="304" ht="20.1" customHeight="1" spans="1:10">
       <c r="A304" s="5">
-        <v>160302</v>
+        <v>160301</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C304" s="5">
         <v>1603</v>
       </c>
       <c r="D304" s="5">
-        <v>160302</v>
+        <v>160301</v>
       </c>
       <c r="E304" s="5"/>
       <c r="F304" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G304" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H304" s="6" t="s">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="I304" s="6" t="s">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="J304" s="6"/>
     </row>
     <row r="305" ht="20.1" customHeight="1" spans="1:10">
       <c r="A305" s="5">
-        <v>160303</v>
+        <v>160302</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C305" s="5">
         <v>1603</v>
       </c>
       <c r="D305" s="5">
-        <v>160303</v>
+        <v>160302</v>
       </c>
       <c r="E305" s="5"/>
       <c r="F305" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G305" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H305" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J305" s="6"/>
     </row>
     <row r="306" ht="20.1" customHeight="1" spans="1:10">
       <c r="A306" s="5">
-        <v>160304</v>
+        <v>160303</v>
       </c>
       <c r="B306" s="6" t="s">
         <v>339</v>
@@ -16498,7 +16514,7 @@
         <v>1603</v>
       </c>
       <c r="D306" s="5">
-        <v>160304</v>
+        <v>160303</v>
       </c>
       <c r="E306" s="5"/>
       <c r="F306" s="5" t="s">
@@ -16508,261 +16524,264 @@
         <v>340</v>
       </c>
       <c r="H306" s="6" t="s">
-        <v>341</v>
+        <v>61</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>341</v>
+        <v>61</v>
       </c>
       <c r="J306" s="6"/>
     </row>
     <row r="307" ht="20.1" customHeight="1" spans="1:10">
       <c r="A307" s="5">
-        <v>160305</v>
+        <v>160304</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C307" s="5">
         <v>1603</v>
       </c>
       <c r="D307" s="5">
-        <v>160305</v>
+        <v>160304</v>
       </c>
       <c r="E307" s="5"/>
       <c r="F307" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G307" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H307" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J307" s="6"/>
     </row>
     <row r="308" ht="20.1" customHeight="1" spans="1:10">
       <c r="A308" s="5">
-        <v>160306</v>
+        <v>160305</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C308" s="5">
         <v>1603</v>
       </c>
       <c r="D308" s="5">
-        <v>160306</v>
+        <v>160305</v>
       </c>
       <c r="E308" s="5"/>
       <c r="F308" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G308" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H308" s="6" t="s">
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="I308" s="6" t="s">
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="J308" s="6"/>
     </row>
     <row r="309" ht="20.1" customHeight="1" spans="1:10">
       <c r="A309" s="5">
-        <v>160307</v>
+        <v>160306</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C309" s="5">
         <v>1603</v>
       </c>
       <c r="D309" s="5">
-        <v>160307</v>
+        <v>160306</v>
       </c>
       <c r="E309" s="5"/>
       <c r="F309" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G309" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H309" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I309" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J309" s="6"/>
     </row>
     <row r="310" ht="20.1" customHeight="1" spans="1:10">
       <c r="A310" s="5">
-        <v>160308</v>
+        <v>160307</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C310" s="5">
         <v>1603</v>
       </c>
       <c r="D310" s="5">
-        <v>160308</v>
+        <v>160307</v>
       </c>
       <c r="E310" s="5"/>
       <c r="F310" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G310" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H310" s="6" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="J310" s="6"/>
     </row>
     <row r="311" ht="20.1" customHeight="1" spans="1:10">
       <c r="A311" s="5">
-        <v>160309</v>
+        <v>160308</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C311" s="5">
         <v>1603</v>
       </c>
       <c r="D311" s="5">
-        <v>160309</v>
+        <v>160308</v>
       </c>
       <c r="E311" s="5"/>
       <c r="F311" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G311" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H311" s="6" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="J311" s="6"/>
     </row>
     <row r="312" ht="20.1" customHeight="1" spans="1:10">
       <c r="A312" s="5">
-        <v>160310</v>
+        <v>160309</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C312" s="5">
         <v>1603</v>
       </c>
       <c r="D312" s="5">
-        <v>160310</v>
+        <v>160309</v>
       </c>
       <c r="E312" s="5"/>
       <c r="F312" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G312" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H312" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J312" s="6"/>
     </row>
     <row r="313" ht="20.1" customHeight="1" spans="1:10">
       <c r="A313" s="5">
-        <v>1608</v>
+        <v>160310</v>
       </c>
       <c r="B313" s="6" t="s">
         <v>345</v>
       </c>
       <c r="C313" s="5">
-        <v>16</v>
+        <v>1603</v>
       </c>
       <c r="D313" s="5">
-        <v>1608</v>
+        <v>160310</v>
       </c>
       <c r="E313" s="5"/>
       <c r="F313" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G313" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="H313" s="6"/>
+      <c r="H313" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="I313" s="6" t="s">
-        <v>345</v>
+        <v>65</v>
       </c>
       <c r="J313" s="6"/>
     </row>
     <row r="314" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A314" s="7">
+      <c r="A314" s="5">
+        <v>1608</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C314" s="5">
+        <v>16</v>
+      </c>
+      <c r="D314" s="5">
+        <v>1608</v>
+      </c>
+      <c r="E314" s="5"/>
+      <c r="F314" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G314" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H314" s="6"/>
+      <c r="I314" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="J314" s="6"/>
+    </row>
+    <row r="315" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A315" s="7">
         <v>1604</v>
       </c>
-      <c r="B314" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="C314" s="7">
+      <c r="B315" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C315" s="7">
         <v>16</v>
       </c>
-      <c r="D314" s="7">
+      <c r="D315" s="7">
         <v>1604</v>
       </c>
-      <c r="E314" s="7"/>
-      <c r="F314" s="7" t="s">
+      <c r="E315" s="7"/>
+      <c r="F315" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G314" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="H314" s="8"/>
-      <c r="I314" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="J314" s="6"/>
-    </row>
-    <row r="315" s="2" customFormat="1" spans="1:10">
-      <c r="A315" s="5">
+      <c r="G315" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="H315" s="8"/>
+      <c r="I315" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="J315" s="6"/>
+    </row>
+    <row r="316" s="2" customFormat="1" spans="1:10">
+      <c r="A316" s="5">
         <v>1605</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C315" s="5">
-        <v>16</v>
-      </c>
-      <c r="D315" s="5">
-        <v>1605</v>
-      </c>
-      <c r="E315" s="5"/>
-      <c r="F315" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G315" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="I315" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="J315" s="6"/>
-    </row>
-    <row r="316" customFormat="1" spans="1:10">
-      <c r="A316" s="5">
-        <v>1606</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>351</v>
@@ -16771,16 +16790,15 @@
         <v>16</v>
       </c>
       <c r="D316" s="5">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E316" s="5"/>
       <c r="F316" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G316" s="2" t="s">
+      <c r="G316" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="H316" s="2"/>
       <c r="I316" s="2" t="s">
         <v>351</v>
       </c>
@@ -16788,7 +16806,7 @@
     </row>
     <row r="317" customFormat="1" spans="1:10">
       <c r="A317" s="5">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>353</v>
@@ -16797,7 +16815,7 @@
         <v>16</v>
       </c>
       <c r="D317" s="5">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E317" s="5"/>
       <c r="F317" s="5" t="s">
@@ -16812,42 +16830,44 @@
       </c>
       <c r="J317" s="6"/>
     </row>
-    <row r="318" ht="20.1" customHeight="1" spans="1:10">
+    <row r="318" customFormat="1" spans="1:10">
       <c r="A318" s="5">
-        <v>2</v>
-      </c>
-      <c r="B318" s="6" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>355</v>
       </c>
       <c r="C318" s="5">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="D318" s="5">
-        <v>2</v>
+        <v>1607</v>
       </c>
       <c r="E318" s="5"/>
       <c r="F318" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G318" s="6"/>
-      <c r="H318" s="6"/>
-      <c r="I318" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G318" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="H318" s="2"/>
+      <c r="I318" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J318" s="6"/>
     </row>
     <row r="319" ht="20.1" customHeight="1" spans="1:10">
       <c r="A319" s="5">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C319" s="5">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D319" s="5">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E319" s="5"/>
       <c r="F319" s="5" t="s">
@@ -16856,39 +16876,37 @@
       <c r="G319" s="6"/>
       <c r="H319" s="6"/>
       <c r="I319" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J319" s="6"/>
     </row>
     <row r="320" ht="20.1" customHeight="1" spans="1:10">
       <c r="A320" s="5">
-        <v>2110</v>
+        <v>21</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C320" s="5">
+        <v>2</v>
+      </c>
+      <c r="D320" s="5">
         <v>21</v>
-      </c>
-      <c r="D320" s="5">
-        <v>2110</v>
       </c>
       <c r="E320" s="5"/>
       <c r="F320" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G320" s="6" t="s">
-        <v>358</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G320" s="6"/>
       <c r="H320" s="6"/>
       <c r="I320" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J320" s="6"/>
     </row>
     <row r="321" ht="20.1" customHeight="1" spans="1:10">
       <c r="A321" s="5">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B321" s="6" t="s">
         <v>359</v>
@@ -16897,7 +16915,7 @@
         <v>21</v>
       </c>
       <c r="D321" s="5">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="E321" s="5"/>
       <c r="F321" s="5" t="s">
@@ -16914,22 +16932,24 @@
     </row>
     <row r="322" ht="20.1" customHeight="1" spans="1:10">
       <c r="A322" s="5">
-        <v>22</v>
+        <v>2111</v>
       </c>
       <c r="B322" s="6" t="s">
         <v>361</v>
       </c>
       <c r="C322" s="5">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D322" s="5">
-        <v>22</v>
+        <v>2111</v>
       </c>
       <c r="E322" s="5"/>
       <c r="F322" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G322" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G322" s="6" t="s">
+        <v>362</v>
+      </c>
       <c r="H322" s="6"/>
       <c r="I322" s="6" t="s">
         <v>361</v>
@@ -16938,33 +16958,31 @@
     </row>
     <row r="323" ht="20.1" customHeight="1" spans="1:10">
       <c r="A323" s="5">
-        <v>2201</v>
+        <v>22</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C323" s="5">
+        <v>2</v>
+      </c>
+      <c r="D323" s="5">
         <v>22</v>
-      </c>
-      <c r="D323" s="5">
-        <v>2201</v>
       </c>
       <c r="E323" s="5"/>
       <c r="F323" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G323" s="6" t="s">
-        <v>363</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G323" s="6"/>
       <c r="H323" s="6"/>
       <c r="I323" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J323" s="6"/>
     </row>
     <row r="324" ht="20.1" customHeight="1" spans="1:10">
       <c r="A324" s="5">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B324" s="6" t="s">
         <v>364</v>
@@ -16973,7 +16991,7 @@
         <v>22</v>
       </c>
       <c r="D324" s="5">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="E324" s="5"/>
       <c r="F324" s="5" t="s">
@@ -16990,7 +17008,7 @@
     </row>
     <row r="325" ht="20.1" customHeight="1" spans="1:10">
       <c r="A325" s="5">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B325" s="6" t="s">
         <v>366</v>
@@ -16999,7 +17017,7 @@
         <v>22</v>
       </c>
       <c r="D325" s="5">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="E325" s="5"/>
       <c r="F325" s="5" t="s">
@@ -17016,22 +17034,24 @@
     </row>
     <row r="326" ht="20.1" customHeight="1" spans="1:10">
       <c r="A326" s="5">
-        <v>23</v>
+        <v>2203</v>
       </c>
       <c r="B326" s="6" t="s">
         <v>368</v>
       </c>
       <c r="C326" s="5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D326" s="5">
-        <v>23</v>
+        <v>2203</v>
       </c>
       <c r="E326" s="5"/>
       <c r="F326" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G326" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G326" s="6" t="s">
+        <v>369</v>
+      </c>
       <c r="H326" s="6"/>
       <c r="I326" s="6" t="s">
         <v>368</v>
@@ -17040,48 +17060,48 @@
     </row>
     <row r="327" ht="20.1" customHeight="1" spans="1:10">
       <c r="A327" s="5">
-        <v>2301</v>
+        <v>23</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C327" s="5">
+        <v>2</v>
+      </c>
+      <c r="D327" s="5">
         <v>23</v>
-      </c>
-      <c r="D327" s="5">
-        <v>2301</v>
       </c>
       <c r="E327" s="5"/>
       <c r="F327" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G327" s="6" t="s">
-        <v>370</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G327" s="6"/>
       <c r="H327" s="6"/>
       <c r="I327" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J327" s="6"/>
     </row>
     <row r="328" ht="20.1" customHeight="1" spans="1:10">
       <c r="A328" s="5">
-        <v>2302</v>
-      </c>
-      <c r="B328" s="15" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B328" s="6" t="s">
         <v>371</v>
       </c>
       <c r="C328" s="5">
         <v>23</v>
       </c>
       <c r="D328" s="5">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="E328" s="5"/>
       <c r="F328" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G328" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="G328" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="H328" s="6"/>
       <c r="I328" s="6" t="s">
         <v>371</v>
@@ -17090,109 +17110,107 @@
     </row>
     <row r="329" ht="20.1" customHeight="1" spans="1:10">
       <c r="A329" s="5">
-        <v>23021</v>
-      </c>
-      <c r="B329" s="15" t="s">
-        <v>372</v>
+        <v>2302</v>
+      </c>
+      <c r="B329" s="16" t="s">
+        <v>373</v>
       </c>
       <c r="C329" s="5">
+        <v>23</v>
+      </c>
+      <c r="D329" s="5">
         <v>2302</v>
-      </c>
-      <c r="D329" s="5">
-        <v>23021</v>
       </c>
       <c r="E329" s="5"/>
       <c r="F329" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G329" s="15" t="s">
-        <v>373</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G329" s="16"/>
       <c r="H329" s="6"/>
       <c r="I329" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J329" s="6"/>
     </row>
     <row r="330" ht="20.1" customHeight="1" spans="1:10">
       <c r="A330" s="5">
-        <v>23022</v>
-      </c>
-      <c r="B330" s="15" t="s">
-        <v>375</v>
+        <v>23021</v>
+      </c>
+      <c r="B330" s="16" t="s">
+        <v>374</v>
       </c>
       <c r="C330" s="5">
         <v>2302</v>
       </c>
       <c r="D330" s="5">
-        <v>23022</v>
+        <v>23021</v>
       </c>
       <c r="E330" s="5"/>
       <c r="F330" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G330" s="15" t="s">
-        <v>376</v>
+      <c r="G330" s="16" t="s">
+        <v>375</v>
       </c>
       <c r="H330" s="6"/>
       <c r="I330" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J330" s="6"/>
     </row>
     <row r="331" ht="20.1" customHeight="1" spans="1:10">
       <c r="A331" s="5">
-        <v>2303</v>
-      </c>
-      <c r="B331" s="6" t="s">
-        <v>307</v>
+        <v>23022</v>
+      </c>
+      <c r="B331" s="16" t="s">
+        <v>377</v>
       </c>
       <c r="C331" s="5">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D331" s="5">
-        <v>2303</v>
+        <v>23022</v>
       </c>
       <c r="E331" s="5"/>
       <c r="F331" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G331" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G331" s="16" t="s">
+        <v>378</v>
+      </c>
       <c r="H331" s="6"/>
       <c r="I331" s="6" t="s">
-        <v>307</v>
+        <v>379</v>
       </c>
       <c r="J331" s="6"/>
     </row>
     <row r="332" ht="20.1" customHeight="1" spans="1:10">
       <c r="A332" s="5">
-        <v>23031</v>
+        <v>2303</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="C332" s="5">
+        <v>23</v>
+      </c>
+      <c r="D332" s="5">
         <v>2303</v>
-      </c>
-      <c r="D332" s="5">
-        <v>23031</v>
       </c>
       <c r="E332" s="5"/>
       <c r="F332" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G332" s="6" t="s">
-        <v>379</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G332" s="6"/>
       <c r="H332" s="6"/>
       <c r="I332" s="6" t="s">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="J332" s="6"/>
     </row>
     <row r="333" ht="20.1" customHeight="1" spans="1:10">
       <c r="A333" s="5">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B333" s="6" t="s">
         <v>380</v>
@@ -17201,7 +17219,7 @@
         <v>2303</v>
       </c>
       <c r="D333" s="5">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="E333" s="5"/>
       <c r="F333" s="5" t="s">
@@ -17218,7 +17236,7 @@
     </row>
     <row r="334" ht="20.1" customHeight="1" spans="1:10">
       <c r="A334" s="5">
-        <v>23033</v>
+        <v>23032</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>382</v>
@@ -17227,7 +17245,7 @@
         <v>2303</v>
       </c>
       <c r="D334" s="5">
-        <v>23033</v>
+        <v>23032</v>
       </c>
       <c r="E334" s="5"/>
       <c r="F334" s="5" t="s">
@@ -17244,7 +17262,7 @@
     </row>
     <row r="335" ht="20.1" customHeight="1" spans="1:10">
       <c r="A335" s="5">
-        <v>23034</v>
+        <v>23033</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>384</v>
@@ -17253,7 +17271,7 @@
         <v>2303</v>
       </c>
       <c r="D335" s="5">
-        <v>23034</v>
+        <v>23033</v>
       </c>
       <c r="E335" s="5"/>
       <c r="F335" s="5" t="s">
@@ -17268,59 +17286,59 @@
       </c>
       <c r="J335" s="6"/>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" ht="20.1" customHeight="1" spans="1:10">
       <c r="A336" s="5">
-        <v>2304</v>
+        <v>23034</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>386</v>
       </c>
       <c r="C336" s="5">
-        <v>23</v>
+        <v>2303</v>
       </c>
       <c r="D336" s="5">
-        <v>2304</v>
+        <v>23034</v>
       </c>
       <c r="E336" s="5"/>
       <c r="F336" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G336" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G336" s="6" t="s">
+        <v>387</v>
+      </c>
       <c r="H336" s="6"/>
       <c r="I336" s="6" t="s">
         <v>386</v>
       </c>
       <c r="J336" s="6"/>
     </row>
-    <row r="337" ht="20.1" customHeight="1" spans="1:10">
+    <row r="337" spans="1:10">
       <c r="A337" s="5">
-        <v>23041</v>
+        <v>2304</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C337" s="5">
+        <v>23</v>
+      </c>
+      <c r="D337" s="5">
         <v>2304</v>
-      </c>
-      <c r="D337" s="5">
-        <v>23041</v>
       </c>
       <c r="E337" s="5"/>
       <c r="F337" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G337" s="6" t="s">
-        <v>388</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G337" s="6"/>
       <c r="H337" s="6"/>
       <c r="I337" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J337" s="6"/>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" ht="20.1" customHeight="1" spans="1:10">
       <c r="A338" s="5">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>389</v>
@@ -17329,7 +17347,7 @@
         <v>2304</v>
       </c>
       <c r="D338" s="5">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="E338" s="5"/>
       <c r="F338" s="5" t="s">
@@ -17346,7 +17364,7 @@
     </row>
     <row r="339" spans="1:10">
       <c r="A339" s="5">
-        <v>23043</v>
+        <v>23042</v>
       </c>
       <c r="B339" s="6" t="s">
         <v>391</v>
@@ -17355,7 +17373,7 @@
         <v>2304</v>
       </c>
       <c r="D339" s="5">
-        <v>23043</v>
+        <v>23042</v>
       </c>
       <c r="E339" s="5"/>
       <c r="F339" s="5" t="s">
@@ -17366,89 +17384,89 @@
       </c>
       <c r="H339" s="6"/>
       <c r="I339" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="J339" s="6"/>
+    </row>
+    <row r="340" spans="1:10">
+      <c r="A340" s="5">
+        <v>23043</v>
+      </c>
+      <c r="B340" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="J339" s="6"/>
-    </row>
-    <row r="340" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A340" s="5">
-        <v>23044</v>
-      </c>
-      <c r="B340" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="C340" s="5">
         <v>2304</v>
       </c>
       <c r="D340" s="5">
-        <v>23044</v>
+        <v>23043</v>
       </c>
       <c r="E340" s="5"/>
       <c r="F340" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G340" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H340" s="6"/>
       <c r="I340" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J340" s="6"/>
+    </row>
+    <row r="341" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A341" s="5">
+        <v>23044</v>
+      </c>
+      <c r="B341" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="J340" s="6"/>
-    </row>
-    <row r="341" spans="1:10">
-      <c r="A341" s="5">
-        <v>2305</v>
-      </c>
-      <c r="B341" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="C341" s="5">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D341" s="5">
-        <v>2305</v>
+        <v>23044</v>
       </c>
       <c r="E341" s="5"/>
       <c r="F341" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G341" s="5"/>
-      <c r="H341" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G341" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="H341" s="6"/>
       <c r="I341" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J341" s="6"/>
     </row>
     <row r="342" spans="1:10">
       <c r="A342" s="5">
-        <v>23051</v>
+        <v>2305</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C342" s="5">
+        <v>23</v>
+      </c>
+      <c r="D342" s="5">
         <v>2305</v>
-      </c>
-      <c r="D342" s="5">
-        <v>23051</v>
       </c>
       <c r="E342" s="5"/>
       <c r="F342" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G342" s="6" t="s">
-        <v>399</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G342" s="5"/>
       <c r="H342" s="5"/>
       <c r="I342" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J342" s="6"/>
     </row>
     <row r="343" spans="1:10">
       <c r="A343" s="5">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>400</v>
@@ -17457,7 +17475,7 @@
         <v>2305</v>
       </c>
       <c r="D343" s="5">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="E343" s="5"/>
       <c r="F343" s="5" t="s">
@@ -17466,7 +17484,7 @@
       <c r="G343" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="H343" s="6"/>
+      <c r="H343" s="5"/>
       <c r="I343" s="6" t="s">
         <v>400</v>
       </c>
@@ -17474,22 +17492,24 @@
     </row>
     <row r="344" spans="1:10">
       <c r="A344" s="5">
-        <v>24</v>
+        <v>23052</v>
       </c>
       <c r="B344" s="6" t="s">
         <v>402</v>
       </c>
       <c r="C344" s="5">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D344" s="5">
-        <v>24</v>
+        <v>23052</v>
       </c>
       <c r="E344" s="5"/>
       <c r="F344" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G344" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G344" s="6" t="s">
+        <v>403</v>
+      </c>
       <c r="H344" s="6"/>
       <c r="I344" s="6" t="s">
         <v>402</v>
@@ -17498,83 +17518,81 @@
     </row>
     <row r="345" spans="1:10">
       <c r="A345" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C345" s="5">
         <v>2</v>
       </c>
       <c r="D345" s="5">
-        <v>25</v>
-      </c>
-      <c r="E345" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="E345" s="5"/>
       <c r="F345" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
       <c r="I345" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J345" s="6"/>
     </row>
     <row r="346" spans="1:10">
       <c r="A346" s="5">
-        <v>2501</v>
+        <v>25</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C346" s="5">
+        <v>2</v>
+      </c>
+      <c r="D346" s="5">
         <v>25</v>
-      </c>
-      <c r="D346" s="5">
-        <v>2501</v>
       </c>
       <c r="E346" s="6"/>
       <c r="F346" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G346" s="6" t="s">
-        <v>405</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G346" s="6"/>
       <c r="H346" s="6"/>
       <c r="I346" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J346" s="6"/>
     </row>
     <row r="347" spans="1:10">
       <c r="A347" s="5">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C347" s="5">
         <v>25</v>
       </c>
       <c r="D347" s="5">
-        <v>2502</v>
-      </c>
-      <c r="E347" s="5"/>
+        <v>2501</v>
+      </c>
+      <c r="E347" s="6"/>
       <c r="F347" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G347" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="H347" s="6"/>
+      <c r="I347" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="H347" s="5"/>
-      <c r="I347" s="6" t="s">
-        <v>407</v>
-      </c>
       <c r="J347" s="6"/>
     </row>
-    <row r="348" s="2" customFormat="1" spans="1:10">
+    <row r="348" spans="1:10">
       <c r="A348" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B348" s="6" t="s">
         <v>409</v>
@@ -17583,17 +17601,43 @@
         <v>25</v>
       </c>
       <c r="D348" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="E348" s="5"/>
       <c r="F348" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G348" s="6"/>
-      <c r="I348" s="2" t="s">
+      <c r="G348" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="H348" s="5"/>
+      <c r="I348" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="J348" s="2" t="b">
+      <c r="J348" s="6"/>
+    </row>
+    <row r="349" s="2" customFormat="1" spans="1:10">
+      <c r="A349" s="5">
+        <v>2503</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="C349" s="5">
+        <v>25</v>
+      </c>
+      <c r="D349" s="5">
+        <v>2503</v>
+      </c>
+      <c r="E349" s="5"/>
+      <c r="F349" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G349" s="6"/>
+      <c r="I349" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J349" s="2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="414">
   <si>
     <t>Id</t>
   </si>
@@ -1302,6 +1302,12 @@
   </si>
   <si>
     <t>Help</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.ApplicationAboutWindowViewModel</t>
   </si>
   <si>
     <t>Management</t>
@@ -2075,7 +2081,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2126,6 +2132,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2635,525 +2644,525 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="18">
         <v>666666</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="19">
         <v>1</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="19">
         <v>666666</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="20" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="18">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <v>1</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="21" t="s">
+      <c r="E4" s="19"/>
+      <c r="F4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="19">
         <v>111111</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3188,172 +3197,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="18">
         <v>1</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19">
+        <v>2</v>
+      </c>
+      <c r="C3" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="18">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <v>3</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3383,172 +3392,172 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="18">
         <v>1</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19">
+        <v>2</v>
+      </c>
+      <c r="C3" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="18">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <v>3</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3587,340 +3596,340 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>-1</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="18">
         <v>0</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="18">
         <v>1</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="19">
         <v>-1</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="19">
         <v>1</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="19">
         <v>3</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="18">
+      <c r="A4" s="19">
         <v>21</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="18">
-        <v>2</v>
-      </c>
-      <c r="D4" s="18">
+      <c r="C4" s="19">
+        <v>2</v>
+      </c>
+      <c r="D4" s="19">
         <v>21</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="19">
         <v>3</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="18">
+      <c r="A5" s="19">
         <v>211</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <v>21</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <v>211</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <v>1</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>212</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <v>21</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <v>212</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <v>3</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="18">
+      <c r="A7" s="19">
         <v>22</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="18">
-        <v>2</v>
-      </c>
-      <c r="D7" s="18">
+      <c r="C7" s="19">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19">
         <v>22</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <v>3</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="18">
+      <c r="A8" s="19">
         <v>221</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <v>22</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <v>221</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <v>3</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="18">
+      <c r="A9" s="19">
         <v>222</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <v>22</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <v>222</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <v>3</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3956,234 +3965,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="18">
         <v>0</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="18">
         <v>1</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4221,234 +4230,234 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="18">
         <v>0</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="18">
         <v>1</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4478,154 +4487,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4655,10 +4664,10 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="18">
         <v>2</v>
       </c>
       <c r="C2" s="5">
@@ -4666,10 +4675,10 @@
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18">
         <v>2</v>
       </c>
       <c r="C3" s="5">
@@ -4677,10 +4686,10 @@
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="17">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="18">
         <v>2</v>
       </c>
       <c r="C4" s="5">
@@ -4688,10 +4697,10 @@
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="17">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="18">
         <v>2</v>
       </c>
       <c r="C5" s="5">
@@ -4699,10 +4708,10 @@
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <v>2</v>
       </c>
       <c r="C6" s="5">
@@ -4710,10 +4719,10 @@
       </c>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="17">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <v>2</v>
       </c>
       <c r="C7" s="5">
@@ -4721,10 +4730,10 @@
       </c>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="17">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <v>2</v>
       </c>
       <c r="C8" s="5">
@@ -4732,10 +4741,10 @@
       </c>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="18">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="18">
         <v>2</v>
       </c>
       <c r="C9" s="5">
@@ -4743,10 +4752,10 @@
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="17">
+      <c r="A10" s="18">
         <v>9</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <v>2</v>
       </c>
       <c r="C10" s="5">
@@ -4754,10 +4763,10 @@
       </c>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="17">
+      <c r="A11" s="18">
         <v>10</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="18">
         <v>2</v>
       </c>
       <c r="C11" s="5">
@@ -4765,10 +4774,10 @@
       </c>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="18">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="18">
         <v>2</v>
       </c>
       <c r="C12" s="5">
@@ -4776,10 +4785,10 @@
       </c>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="17">
+      <c r="A13" s="18">
         <v>12</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="18">
         <v>2</v>
       </c>
       <c r="C13" s="5">
@@ -4787,10 +4796,10 @@
       </c>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="17">
+      <c r="A14" s="18">
         <v>13</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="18">
         <v>2</v>
       </c>
       <c r="C14" s="5">
@@ -4798,10 +4807,10 @@
       </c>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="18">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="18">
         <v>2</v>
       </c>
       <c r="C15" s="5">
@@ -4809,10 +4818,10 @@
       </c>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="17">
+      <c r="A16" s="18">
         <v>15</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="18">
         <v>2</v>
       </c>
       <c r="C16" s="5">
@@ -4820,10 +4829,10 @@
       </c>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="17">
+      <c r="A17" s="18">
         <v>16</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="18">
         <v>2</v>
       </c>
       <c r="C17" s="5">
@@ -4831,10 +4840,10 @@
       </c>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="18">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="18">
         <v>2</v>
       </c>
       <c r="C18" s="5">
@@ -4842,10 +4851,10 @@
       </c>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="17">
+      <c r="A19" s="18">
         <v>18</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="18">
         <v>2</v>
       </c>
       <c r="C19" s="5">
@@ -4853,10 +4862,10 @@
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="17">
+      <c r="A20" s="18">
         <v>19</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="18">
         <v>2</v>
       </c>
       <c r="C20" s="5">
@@ -4864,10 +4873,10 @@
       </c>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="18">
+      <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="18">
         <v>2</v>
       </c>
       <c r="C21" s="5">
@@ -4875,10 +4884,10 @@
       </c>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="17">
+      <c r="A22" s="18">
         <v>21</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="18">
         <v>2</v>
       </c>
       <c r="C22" s="5">
@@ -4886,10 +4895,10 @@
       </c>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="17">
+      <c r="A23" s="18">
         <v>22</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="18">
         <v>2</v>
       </c>
       <c r="C23" s="5">
@@ -4897,10 +4906,10 @@
       </c>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="18">
+      <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="18">
         <v>2</v>
       </c>
       <c r="C24" s="5">
@@ -4908,10 +4917,10 @@
       </c>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="17">
+      <c r="A25" s="18">
         <v>24</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="18">
         <v>2</v>
       </c>
       <c r="C25" s="5">
@@ -4919,10 +4928,10 @@
       </c>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="17">
+      <c r="A26" s="18">
         <v>25</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="18">
         <v>2</v>
       </c>
       <c r="C26" s="5">
@@ -4930,10 +4939,10 @@
       </c>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="18">
+      <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="18">
         <v>2</v>
       </c>
       <c r="C27" s="5">
@@ -4941,10 +4950,10 @@
       </c>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="17">
+      <c r="A28" s="18">
         <v>27</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="18">
         <v>2</v>
       </c>
       <c r="C28" s="5">
@@ -4952,10 +4961,10 @@
       </c>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="17">
+      <c r="A29" s="18">
         <v>28</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="18">
         <v>2</v>
       </c>
       <c r="C29" s="5">
@@ -4963,10 +4972,10 @@
       </c>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="18">
+      <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="18">
         <v>2</v>
       </c>
       <c r="C30" s="5">
@@ -4974,10 +4983,10 @@
       </c>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="17">
+      <c r="A31" s="18">
         <v>30</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="18">
         <v>2</v>
       </c>
       <c r="C31" s="5">
@@ -4985,10 +4994,10 @@
       </c>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A32" s="17">
+      <c r="A32" s="18">
         <v>31</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="18">
         <v>2</v>
       </c>
       <c r="C32" s="5">
@@ -4996,10 +5005,10 @@
       </c>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A33" s="18">
+      <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="18">
         <v>2</v>
       </c>
       <c r="C33" s="5">
@@ -5007,10 +5016,10 @@
       </c>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A34" s="17">
+      <c r="A34" s="18">
         <v>33</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="18">
         <v>2</v>
       </c>
       <c r="C34" s="5">
@@ -5018,10 +5027,10 @@
       </c>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A35" s="17">
+      <c r="A35" s="18">
         <v>34</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="18">
         <v>2</v>
       </c>
       <c r="C35" s="5">
@@ -5029,10 +5038,10 @@
       </c>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A36" s="18">
+      <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="18">
         <v>2</v>
       </c>
       <c r="C36" s="5">
@@ -5040,10 +5049,10 @@
       </c>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A37" s="17">
+      <c r="A37" s="18">
         <v>36</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="18">
         <v>2</v>
       </c>
       <c r="C37" s="5">
@@ -5051,10 +5060,10 @@
       </c>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A38" s="17">
+      <c r="A38" s="18">
         <v>37</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="18">
         <v>2</v>
       </c>
       <c r="C38" s="5">
@@ -5062,10 +5071,10 @@
       </c>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A39" s="18">
+      <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="18">
         <v>2</v>
       </c>
       <c r="C39" s="5">
@@ -5073,10 +5082,10 @@
       </c>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A40" s="17">
+      <c r="A40" s="18">
         <v>39</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="18">
         <v>2</v>
       </c>
       <c r="C40" s="5">
@@ -5084,10 +5093,10 @@
       </c>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A41" s="17">
+      <c r="A41" s="18">
         <v>40</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="18">
         <v>2</v>
       </c>
       <c r="C41" s="5">
@@ -5095,10 +5104,10 @@
       </c>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A42" s="18">
+      <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="18">
         <v>2</v>
       </c>
       <c r="C42" s="5">
@@ -5106,10 +5115,10 @@
       </c>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A43" s="17">
+      <c r="A43" s="18">
         <v>42</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="18">
         <v>2</v>
       </c>
       <c r="C43" s="5">
@@ -5117,10 +5126,10 @@
       </c>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A44" s="17">
+      <c r="A44" s="18">
         <v>43</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="18">
         <v>2</v>
       </c>
       <c r="C44" s="5">
@@ -5128,10 +5137,10 @@
       </c>
     </row>
     <row r="45" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A45" s="18">
+      <c r="A45" s="19">
         <v>44</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="18">
         <v>2</v>
       </c>
       <c r="C45" s="5">
@@ -5139,10 +5148,10 @@
       </c>
     </row>
     <row r="46" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A46" s="17">
+      <c r="A46" s="18">
         <v>45</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="18">
         <v>2</v>
       </c>
       <c r="C46" s="5">
@@ -5150,10 +5159,10 @@
       </c>
     </row>
     <row r="47" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A47" s="17">
+      <c r="A47" s="18">
         <v>46</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="18">
         <v>2</v>
       </c>
       <c r="C47" s="5">
@@ -5161,10 +5170,10 @@
       </c>
     </row>
     <row r="48" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A48" s="18">
+      <c r="A48" s="19">
         <v>47</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="18">
         <v>2</v>
       </c>
       <c r="C48" s="5">
@@ -5172,10 +5181,10 @@
       </c>
     </row>
     <row r="49" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A49" s="17">
+      <c r="A49" s="18">
         <v>48</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="18">
         <v>2</v>
       </c>
       <c r="C49" s="5">
@@ -5183,10 +5192,10 @@
       </c>
     </row>
     <row r="50" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A50" s="17">
+      <c r="A50" s="18">
         <v>49</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="18">
         <v>2</v>
       </c>
       <c r="C50" s="5">
@@ -5194,10 +5203,10 @@
       </c>
     </row>
     <row r="51" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A51" s="18">
+      <c r="A51" s="19">
         <v>50</v>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="18">
         <v>2</v>
       </c>
       <c r="C51" s="5">
@@ -5205,10 +5214,10 @@
       </c>
     </row>
     <row r="52" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A52" s="17">
+      <c r="A52" s="18">
         <v>51</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="18">
         <v>2</v>
       </c>
       <c r="C52" s="5">
@@ -5216,10 +5225,10 @@
       </c>
     </row>
     <row r="53" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A53" s="17">
+      <c r="A53" s="18">
         <v>52</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="18">
         <v>2</v>
       </c>
       <c r="C53" s="5">
@@ -5227,10 +5236,10 @@
       </c>
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A54" s="18">
+      <c r="A54" s="19">
         <v>53</v>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="18">
         <v>2</v>
       </c>
       <c r="C54" s="5">
@@ -5238,10 +5247,10 @@
       </c>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A55" s="17">
+      <c r="A55" s="18">
         <v>54</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="18">
         <v>2</v>
       </c>
       <c r="C55" s="5">
@@ -5249,10 +5258,10 @@
       </c>
     </row>
     <row r="56" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A56" s="17">
+      <c r="A56" s="18">
         <v>55</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="18">
         <v>2</v>
       </c>
       <c r="C56" s="5">
@@ -5260,10 +5269,10 @@
       </c>
     </row>
     <row r="57" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A57" s="18">
+      <c r="A57" s="19">
         <v>56</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="18">
         <v>2</v>
       </c>
       <c r="C57" s="5">
@@ -5271,10 +5280,10 @@
       </c>
     </row>
     <row r="58" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A58" s="17">
+      <c r="A58" s="18">
         <v>57</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="18">
         <v>2</v>
       </c>
       <c r="C58" s="5">
@@ -5282,10 +5291,10 @@
       </c>
     </row>
     <row r="59" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A59" s="17">
-        <v>58</v>
-      </c>
-      <c r="B59" s="17">
+      <c r="A59" s="18">
+        <v>58</v>
+      </c>
+      <c r="B59" s="18">
         <v>2</v>
       </c>
       <c r="C59" s="5">
@@ -5293,10 +5302,10 @@
       </c>
     </row>
     <row r="60" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A60" s="17">
+      <c r="A60" s="18">
         <v>59</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B60" s="18">
         <v>2</v>
       </c>
       <c r="C60" s="5">
@@ -5304,10 +5313,10 @@
       </c>
     </row>
     <row r="61" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A61" s="17">
+      <c r="A61" s="18">
         <v>60</v>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="18">
         <v>2</v>
       </c>
       <c r="C61" s="5">
@@ -5315,10 +5324,10 @@
       </c>
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A62" s="17">
+      <c r="A62" s="18">
         <v>61</v>
       </c>
-      <c r="B62" s="17">
+      <c r="B62" s="18">
         <v>2</v>
       </c>
       <c r="C62" s="5">
@@ -5326,10 +5335,10 @@
       </c>
     </row>
     <row r="63" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A63" s="17">
+      <c r="A63" s="18">
         <v>62</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="18">
         <v>2</v>
       </c>
       <c r="C63" s="5">
@@ -5337,10 +5346,10 @@
       </c>
     </row>
     <row r="64" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A64" s="17">
+      <c r="A64" s="18">
         <v>63</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="18">
         <v>2</v>
       </c>
       <c r="C64" s="5">
@@ -5348,10 +5357,10 @@
       </c>
     </row>
     <row r="65" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A65" s="17">
+      <c r="A65" s="18">
         <v>64</v>
       </c>
-      <c r="B65" s="17">
+      <c r="B65" s="18">
         <v>2</v>
       </c>
       <c r="C65" s="5">
@@ -5359,10 +5368,10 @@
       </c>
     </row>
     <row r="66" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A66" s="17">
+      <c r="A66" s="18">
         <v>65</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="18">
         <v>2</v>
       </c>
       <c r="C66" s="5">
@@ -5370,10 +5379,10 @@
       </c>
     </row>
     <row r="67" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A67" s="17">
+      <c r="A67" s="18">
         <v>66</v>
       </c>
-      <c r="B67" s="17">
+      <c r="B67" s="18">
         <v>2</v>
       </c>
       <c r="C67" s="5">
@@ -5381,10 +5390,10 @@
       </c>
     </row>
     <row r="68" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A68" s="17">
+      <c r="A68" s="18">
         <v>67</v>
       </c>
-      <c r="B68" s="17">
+      <c r="B68" s="18">
         <v>2</v>
       </c>
       <c r="C68" s="5">
@@ -5392,10 +5401,10 @@
       </c>
     </row>
     <row r="69" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A69" s="17">
+      <c r="A69" s="18">
         <v>68</v>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="18">
         <v>2</v>
       </c>
       <c r="C69" s="5">
@@ -5403,10 +5412,10 @@
       </c>
     </row>
     <row r="70" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A70" s="17">
+      <c r="A70" s="18">
         <v>69</v>
       </c>
-      <c r="B70" s="17">
+      <c r="B70" s="18">
         <v>2</v>
       </c>
       <c r="C70" s="5">
@@ -5414,10 +5423,10 @@
       </c>
     </row>
     <row r="71" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A71" s="17">
+      <c r="A71" s="18">
         <v>70</v>
       </c>
-      <c r="B71" s="17">
+      <c r="B71" s="18">
         <v>2</v>
       </c>
       <c r="C71" s="5">
@@ -5425,10 +5434,10 @@
       </c>
     </row>
     <row r="72" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A72" s="17">
+      <c r="A72" s="18">
         <v>71</v>
       </c>
-      <c r="B72" s="17">
+      <c r="B72" s="18">
         <v>2</v>
       </c>
       <c r="C72" s="5">
@@ -5436,10 +5445,10 @@
       </c>
     </row>
     <row r="73" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A73" s="17">
+      <c r="A73" s="18">
         <v>72</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="18">
         <v>2</v>
       </c>
       <c r="C73" s="5">
@@ -5447,10 +5456,10 @@
       </c>
     </row>
     <row r="74" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A74" s="17">
+      <c r="A74" s="18">
         <v>73</v>
       </c>
-      <c r="B74" s="17">
+      <c r="B74" s="18">
         <v>2</v>
       </c>
       <c r="C74" s="5">
@@ -5458,10 +5467,10 @@
       </c>
     </row>
     <row r="75" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A75" s="17">
+      <c r="A75" s="18">
         <v>74</v>
       </c>
-      <c r="B75" s="17">
+      <c r="B75" s="18">
         <v>2</v>
       </c>
       <c r="C75" s="5">
@@ -5469,10 +5478,10 @@
       </c>
     </row>
     <row r="76" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A76" s="17">
+      <c r="A76" s="18">
         <v>75</v>
       </c>
-      <c r="B76" s="17">
+      <c r="B76" s="18">
         <v>2</v>
       </c>
       <c r="C76" s="5">
@@ -5480,10 +5489,10 @@
       </c>
     </row>
     <row r="77" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A77" s="17">
+      <c r="A77" s="18">
         <v>76</v>
       </c>
-      <c r="B77" s="17">
+      <c r="B77" s="18">
         <v>2</v>
       </c>
       <c r="C77" s="5">
@@ -5491,10 +5500,10 @@
       </c>
     </row>
     <row r="78" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A78" s="17">
+      <c r="A78" s="18">
         <v>77</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="18">
         <v>2</v>
       </c>
       <c r="C78" s="5">
@@ -5502,10 +5511,10 @@
       </c>
     </row>
     <row r="79" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A79" s="17">
+      <c r="A79" s="18">
         <v>78</v>
       </c>
-      <c r="B79" s="17">
+      <c r="B79" s="18">
         <v>2</v>
       </c>
       <c r="C79" s="5">
@@ -5513,10 +5522,10 @@
       </c>
     </row>
     <row r="80" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A80" s="17">
+      <c r="A80" s="18">
         <v>79</v>
       </c>
-      <c r="B80" s="17">
+      <c r="B80" s="18">
         <v>2</v>
       </c>
       <c r="C80" s="5">
@@ -5524,10 +5533,10 @@
       </c>
     </row>
     <row r="81" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A81" s="17">
+      <c r="A81" s="18">
         <v>80</v>
       </c>
-      <c r="B81" s="17">
+      <c r="B81" s="18">
         <v>2</v>
       </c>
       <c r="C81" s="5">
@@ -5535,10 +5544,10 @@
       </c>
     </row>
     <row r="82" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A82" s="17">
+      <c r="A82" s="18">
         <v>81</v>
       </c>
-      <c r="B82" s="17">
+      <c r="B82" s="18">
         <v>2</v>
       </c>
       <c r="C82" s="5">
@@ -5546,10 +5555,10 @@
       </c>
     </row>
     <row r="83" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A83" s="17">
+      <c r="A83" s="18">
         <v>82</v>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="18">
         <v>2</v>
       </c>
       <c r="C83" s="5">
@@ -5557,10 +5566,10 @@
       </c>
     </row>
     <row r="84" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A84" s="17">
+      <c r="A84" s="18">
         <v>83</v>
       </c>
-      <c r="B84" s="17">
+      <c r="B84" s="18">
         <v>2</v>
       </c>
       <c r="C84" s="5">
@@ -5568,10 +5577,10 @@
       </c>
     </row>
     <row r="85" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A85" s="17">
+      <c r="A85" s="18">
         <v>84</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="18">
         <v>2</v>
       </c>
       <c r="C85" s="5">
@@ -5579,10 +5588,10 @@
       </c>
     </row>
     <row r="86" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A86" s="17">
+      <c r="A86" s="18">
         <v>85</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B86" s="18">
         <v>2</v>
       </c>
       <c r="C86" s="5">
@@ -5590,10 +5599,10 @@
       </c>
     </row>
     <row r="87" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A87" s="17">
+      <c r="A87" s="18">
         <v>86</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B87" s="18">
         <v>2</v>
       </c>
       <c r="C87" s="5">
@@ -5601,10 +5610,10 @@
       </c>
     </row>
     <row r="88" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A88" s="17">
+      <c r="A88" s="18">
         <v>87</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B88" s="18">
         <v>2</v>
       </c>
       <c r="C88" s="5">
@@ -5612,10 +5621,10 @@
       </c>
     </row>
     <row r="89" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A89" s="17">
+      <c r="A89" s="18">
         <v>88</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B89" s="18">
         <v>2</v>
       </c>
       <c r="C89" s="5">
@@ -5623,10 +5632,10 @@
       </c>
     </row>
     <row r="90" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A90" s="17">
+      <c r="A90" s="18">
         <v>89</v>
       </c>
-      <c r="B90" s="17">
+      <c r="B90" s="18">
         <v>2</v>
       </c>
       <c r="C90" s="5">
@@ -5634,10 +5643,10 @@
       </c>
     </row>
     <row r="91" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A91" s="17">
+      <c r="A91" s="18">
         <v>90</v>
       </c>
-      <c r="B91" s="17">
+      <c r="B91" s="18">
         <v>2</v>
       </c>
       <c r="C91" s="5">
@@ -5645,10 +5654,10 @@
       </c>
     </row>
     <row r="92" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A92" s="17">
+      <c r="A92" s="18">
         <v>91</v>
       </c>
-      <c r="B92" s="17">
+      <c r="B92" s="18">
         <v>2</v>
       </c>
       <c r="C92" s="5">
@@ -5656,10 +5665,10 @@
       </c>
     </row>
     <row r="93" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A93" s="17">
+      <c r="A93" s="18">
         <v>92</v>
       </c>
-      <c r="B93" s="17">
+      <c r="B93" s="18">
         <v>2</v>
       </c>
       <c r="C93" s="5">
@@ -5667,10 +5676,10 @@
       </c>
     </row>
     <row r="94" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A94" s="17">
+      <c r="A94" s="18">
         <v>93</v>
       </c>
-      <c r="B94" s="17">
+      <c r="B94" s="18">
         <v>2</v>
       </c>
       <c r="C94" s="5">
@@ -5678,10 +5687,10 @@
       </c>
     </row>
     <row r="95" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A95" s="17">
+      <c r="A95" s="18">
         <v>94</v>
       </c>
-      <c r="B95" s="17">
+      <c r="B95" s="18">
         <v>2</v>
       </c>
       <c r="C95" s="5">
@@ -5689,10 +5698,10 @@
       </c>
     </row>
     <row r="96" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A96" s="17">
+      <c r="A96" s="18">
         <v>95</v>
       </c>
-      <c r="B96" s="17">
+      <c r="B96" s="18">
         <v>2</v>
       </c>
       <c r="C96" s="5">
@@ -5700,10 +5709,10 @@
       </c>
     </row>
     <row r="97" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A97" s="17">
+      <c r="A97" s="18">
         <v>96</v>
       </c>
-      <c r="B97" s="17">
+      <c r="B97" s="18">
         <v>2</v>
       </c>
       <c r="C97" s="5">
@@ -5711,10 +5720,10 @@
       </c>
     </row>
     <row r="98" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A98" s="17">
+      <c r="A98" s="18">
         <v>97</v>
       </c>
-      <c r="B98" s="17">
+      <c r="B98" s="18">
         <v>2</v>
       </c>
       <c r="C98" s="5">
@@ -5722,10 +5731,10 @@
       </c>
     </row>
     <row r="99" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A99" s="17">
+      <c r="A99" s="18">
         <v>98</v>
       </c>
-      <c r="B99" s="17">
+      <c r="B99" s="18">
         <v>2</v>
       </c>
       <c r="C99" s="5">
@@ -5733,10 +5742,10 @@
       </c>
     </row>
     <row r="100" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A100" s="17">
+      <c r="A100" s="18">
         <v>99</v>
       </c>
-      <c r="B100" s="17">
+      <c r="B100" s="18">
         <v>2</v>
       </c>
       <c r="C100" s="5">
@@ -5744,10 +5753,10 @@
       </c>
     </row>
     <row r="101" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A101" s="17">
+      <c r="A101" s="18">
         <v>100</v>
       </c>
-      <c r="B101" s="17">
+      <c r="B101" s="18">
         <v>2</v>
       </c>
       <c r="C101" s="5">
@@ -5755,10 +5764,10 @@
       </c>
     </row>
     <row r="102" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A102" s="17">
+      <c r="A102" s="18">
         <v>101</v>
       </c>
-      <c r="B102" s="17">
+      <c r="B102" s="18">
         <v>2</v>
       </c>
       <c r="C102" s="5">
@@ -5766,10 +5775,10 @@
       </c>
     </row>
     <row r="103" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A103" s="17">
+      <c r="A103" s="18">
         <v>102</v>
       </c>
-      <c r="B103" s="17">
+      <c r="B103" s="18">
         <v>2</v>
       </c>
       <c r="C103" s="5">
@@ -5777,10 +5786,10 @@
       </c>
     </row>
     <row r="104" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A104" s="17">
+      <c r="A104" s="18">
         <v>103</v>
       </c>
-      <c r="B104" s="17">
+      <c r="B104" s="18">
         <v>2</v>
       </c>
       <c r="C104" s="5">
@@ -5788,10 +5797,10 @@
       </c>
     </row>
     <row r="105" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A105" s="17">
+      <c r="A105" s="18">
         <v>104</v>
       </c>
-      <c r="B105" s="17">
+      <c r="B105" s="18">
         <v>2</v>
       </c>
       <c r="C105" s="5">
@@ -5799,10 +5808,10 @@
       </c>
     </row>
     <row r="106" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A106" s="17">
+      <c r="A106" s="18">
         <v>105</v>
       </c>
-      <c r="B106" s="17">
+      <c r="B106" s="18">
         <v>2</v>
       </c>
       <c r="C106" s="5">
@@ -5810,10 +5819,10 @@
       </c>
     </row>
     <row r="107" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A107" s="17">
+      <c r="A107" s="18">
         <v>106</v>
       </c>
-      <c r="B107" s="17">
+      <c r="B107" s="18">
         <v>2</v>
       </c>
       <c r="C107" s="5">
@@ -5821,10 +5830,10 @@
       </c>
     </row>
     <row r="108" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A108" s="17">
+      <c r="A108" s="18">
         <v>107</v>
       </c>
-      <c r="B108" s="17">
+      <c r="B108" s="18">
         <v>2</v>
       </c>
       <c r="C108" s="5">
@@ -5832,10 +5841,10 @@
       </c>
     </row>
     <row r="109" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A109" s="17">
+      <c r="A109" s="18">
         <v>108</v>
       </c>
-      <c r="B109" s="17">
+      <c r="B109" s="18">
         <v>2</v>
       </c>
       <c r="C109" s="5">
@@ -5843,10 +5852,10 @@
       </c>
     </row>
     <row r="110" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A110" s="17">
+      <c r="A110" s="18">
         <v>109</v>
       </c>
-      <c r="B110" s="17">
+      <c r="B110" s="18">
         <v>2</v>
       </c>
       <c r="C110" s="5">
@@ -5854,10 +5863,10 @@
       </c>
     </row>
     <row r="111" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A111" s="17">
+      <c r="A111" s="18">
         <v>110</v>
       </c>
-      <c r="B111" s="17">
+      <c r="B111" s="18">
         <v>2</v>
       </c>
       <c r="C111" s="5">
@@ -5865,10 +5874,10 @@
       </c>
     </row>
     <row r="112" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A112" s="17">
+      <c r="A112" s="18">
         <v>111</v>
       </c>
-      <c r="B112" s="17">
+      <c r="B112" s="18">
         <v>2</v>
       </c>
       <c r="C112" s="5">
@@ -5876,10 +5885,10 @@
       </c>
     </row>
     <row r="113" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A113" s="17">
+      <c r="A113" s="18">
         <v>112</v>
       </c>
-      <c r="B113" s="17">
+      <c r="B113" s="18">
         <v>2</v>
       </c>
       <c r="C113" s="5">
@@ -5887,10 +5896,10 @@
       </c>
     </row>
     <row r="114" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A114" s="17">
+      <c r="A114" s="18">
         <v>113</v>
       </c>
-      <c r="B114" s="17">
+      <c r="B114" s="18">
         <v>2</v>
       </c>
       <c r="C114" s="5">
@@ -5898,10 +5907,10 @@
       </c>
     </row>
     <row r="115" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A115" s="17">
+      <c r="A115" s="18">
         <v>114</v>
       </c>
-      <c r="B115" s="17">
+      <c r="B115" s="18">
         <v>2</v>
       </c>
       <c r="C115" s="5">
@@ -5909,10 +5918,10 @@
       </c>
     </row>
     <row r="116" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A116" s="17">
+      <c r="A116" s="18">
         <v>115</v>
       </c>
-      <c r="B116" s="17">
+      <c r="B116" s="18">
         <v>2</v>
       </c>
       <c r="C116" s="5">
@@ -5920,10 +5929,10 @@
       </c>
     </row>
     <row r="117" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A117" s="17">
+      <c r="A117" s="18">
         <v>116</v>
       </c>
-      <c r="B117" s="17">
+      <c r="B117" s="18">
         <v>2</v>
       </c>
       <c r="C117" s="5">
@@ -5931,10 +5940,10 @@
       </c>
     </row>
     <row r="118" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A118" s="17">
+      <c r="A118" s="18">
         <v>117</v>
       </c>
-      <c r="B118" s="17">
+      <c r="B118" s="18">
         <v>2</v>
       </c>
       <c r="C118" s="5">
@@ -5942,10 +5951,10 @@
       </c>
     </row>
     <row r="119" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A119" s="17">
+      <c r="A119" s="18">
         <v>118</v>
       </c>
-      <c r="B119" s="17">
+      <c r="B119" s="18">
         <v>2</v>
       </c>
       <c r="C119" s="5">
@@ -5953,10 +5962,10 @@
       </c>
     </row>
     <row r="120" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A120" s="17">
+      <c r="A120" s="18">
         <v>119</v>
       </c>
-      <c r="B120" s="17">
+      <c r="B120" s="18">
         <v>2</v>
       </c>
       <c r="C120" s="5">
@@ -5964,10 +5973,10 @@
       </c>
     </row>
     <row r="121" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A121" s="17">
+      <c r="A121" s="18">
         <v>120</v>
       </c>
-      <c r="B121" s="17">
+      <c r="B121" s="18">
         <v>2</v>
       </c>
       <c r="C121" s="5">
@@ -5975,10 +5984,10 @@
       </c>
     </row>
     <row r="122" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A122" s="17">
+      <c r="A122" s="18">
         <v>121</v>
       </c>
-      <c r="B122" s="17">
+      <c r="B122" s="18">
         <v>2</v>
       </c>
       <c r="C122" s="5">
@@ -5986,10 +5995,10 @@
       </c>
     </row>
     <row r="123" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A123" s="17">
+      <c r="A123" s="18">
         <v>122</v>
       </c>
-      <c r="B123" s="17">
+      <c r="B123" s="18">
         <v>2</v>
       </c>
       <c r="C123" s="5">
@@ -5997,10 +6006,10 @@
       </c>
     </row>
     <row r="124" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A124" s="17">
+      <c r="A124" s="18">
         <v>123</v>
       </c>
-      <c r="B124" s="17">
+      <c r="B124" s="18">
         <v>2</v>
       </c>
       <c r="C124" s="5">
@@ -6008,10 +6017,10 @@
       </c>
     </row>
     <row r="125" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A125" s="17">
+      <c r="A125" s="18">
         <v>124</v>
       </c>
-      <c r="B125" s="17">
+      <c r="B125" s="18">
         <v>2</v>
       </c>
       <c r="C125" s="5">
@@ -6019,10 +6028,10 @@
       </c>
     </row>
     <row r="126" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A126" s="17">
+      <c r="A126" s="18">
         <v>125</v>
       </c>
-      <c r="B126" s="17">
+      <c r="B126" s="18">
         <v>2</v>
       </c>
       <c r="C126" s="5">
@@ -6030,10 +6039,10 @@
       </c>
     </row>
     <row r="127" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A127" s="17">
+      <c r="A127" s="18">
         <v>126</v>
       </c>
-      <c r="B127" s="17">
+      <c r="B127" s="18">
         <v>2</v>
       </c>
       <c r="C127" s="5">
@@ -6041,10 +6050,10 @@
       </c>
     </row>
     <row r="128" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A128" s="17">
+      <c r="A128" s="18">
         <v>127</v>
       </c>
-      <c r="B128" s="17">
+      <c r="B128" s="18">
         <v>2</v>
       </c>
       <c r="C128" s="5">
@@ -6052,10 +6061,10 @@
       </c>
     </row>
     <row r="129" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A129" s="17">
+      <c r="A129" s="18">
         <v>128</v>
       </c>
-      <c r="B129" s="17">
+      <c r="B129" s="18">
         <v>2</v>
       </c>
       <c r="C129" s="5">
@@ -6063,10 +6072,10 @@
       </c>
     </row>
     <row r="130" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A130" s="17">
+      <c r="A130" s="18">
         <v>129</v>
       </c>
-      <c r="B130" s="17">
+      <c r="B130" s="18">
         <v>2</v>
       </c>
       <c r="C130" s="5">
@@ -6074,10 +6083,10 @@
       </c>
     </row>
     <row r="131" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A131" s="17">
+      <c r="A131" s="18">
         <v>130</v>
       </c>
-      <c r="B131" s="17">
+      <c r="B131" s="18">
         <v>2</v>
       </c>
       <c r="C131" s="5">
@@ -6085,10 +6094,10 @@
       </c>
     </row>
     <row r="132" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A132" s="17">
+      <c r="A132" s="18">
         <v>131</v>
       </c>
-      <c r="B132" s="17">
+      <c r="B132" s="18">
         <v>2</v>
       </c>
       <c r="C132" s="5">
@@ -6096,10 +6105,10 @@
       </c>
     </row>
     <row r="133" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A133" s="17">
+      <c r="A133" s="18">
         <v>132</v>
       </c>
-      <c r="B133" s="17">
+      <c r="B133" s="18">
         <v>2</v>
       </c>
       <c r="C133" s="5">
@@ -6107,10 +6116,10 @@
       </c>
     </row>
     <row r="134" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A134" s="17">
+      <c r="A134" s="18">
         <v>133</v>
       </c>
-      <c r="B134" s="17">
+      <c r="B134" s="18">
         <v>2</v>
       </c>
       <c r="C134" s="5">
@@ -6118,10 +6127,10 @@
       </c>
     </row>
     <row r="135" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A135" s="17">
+      <c r="A135" s="18">
         <v>134</v>
       </c>
-      <c r="B135" s="17">
+      <c r="B135" s="18">
         <v>2</v>
       </c>
       <c r="C135" s="5">
@@ -6129,10 +6138,10 @@
       </c>
     </row>
     <row r="136" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A136" s="17">
+      <c r="A136" s="18">
         <v>135</v>
       </c>
-      <c r="B136" s="17">
+      <c r="B136" s="18">
         <v>2</v>
       </c>
       <c r="C136" s="5">
@@ -6140,10 +6149,10 @@
       </c>
     </row>
     <row r="137" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A137" s="17">
+      <c r="A137" s="18">
         <v>136</v>
       </c>
-      <c r="B137" s="17">
+      <c r="B137" s="18">
         <v>2</v>
       </c>
       <c r="C137" s="5">
@@ -6151,10 +6160,10 @@
       </c>
     </row>
     <row r="138" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A138" s="17">
+      <c r="A138" s="18">
         <v>137</v>
       </c>
-      <c r="B138" s="17">
+      <c r="B138" s="18">
         <v>2</v>
       </c>
       <c r="C138" s="5">
@@ -6162,10 +6171,10 @@
       </c>
     </row>
     <row r="139" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A139" s="17">
+      <c r="A139" s="18">
         <v>138</v>
       </c>
-      <c r="B139" s="17">
+      <c r="B139" s="18">
         <v>2</v>
       </c>
       <c r="C139" s="5">
@@ -6173,10 +6182,10 @@
       </c>
     </row>
     <row r="140" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A140" s="17">
+      <c r="A140" s="18">
         <v>139</v>
       </c>
-      <c r="B140" s="17">
+      <c r="B140" s="18">
         <v>2</v>
       </c>
       <c r="C140" s="5">
@@ -6184,10 +6193,10 @@
       </c>
     </row>
     <row r="141" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A141" s="17">
+      <c r="A141" s="18">
         <v>140</v>
       </c>
-      <c r="B141" s="17">
+      <c r="B141" s="18">
         <v>2</v>
       </c>
       <c r="C141" s="5">
@@ -6195,10 +6204,10 @@
       </c>
     </row>
     <row r="142" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A142" s="17">
+      <c r="A142" s="18">
         <v>141</v>
       </c>
-      <c r="B142" s="17">
+      <c r="B142" s="18">
         <v>2</v>
       </c>
       <c r="C142" s="5">
@@ -6206,10 +6215,10 @@
       </c>
     </row>
     <row r="143" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A143" s="17">
+      <c r="A143" s="18">
         <v>142</v>
       </c>
-      <c r="B143" s="17">
+      <c r="B143" s="18">
         <v>2</v>
       </c>
       <c r="C143" s="5">
@@ -6217,10 +6226,10 @@
       </c>
     </row>
     <row r="144" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A144" s="17">
+      <c r="A144" s="18">
         <v>122</v>
       </c>
-      <c r="B144" s="17">
+      <c r="B144" s="18">
         <v>2</v>
       </c>
       <c r="C144" s="5">
@@ -6228,10 +6237,10 @@
       </c>
     </row>
     <row r="145" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A145" s="17">
+      <c r="A145" s="18">
         <v>123</v>
       </c>
-      <c r="B145" s="17">
+      <c r="B145" s="18">
         <v>2</v>
       </c>
       <c r="C145" s="5">
@@ -6239,10 +6248,10 @@
       </c>
     </row>
     <row r="146" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A146" s="17">
+      <c r="A146" s="18">
         <v>124</v>
       </c>
-      <c r="B146" s="17">
+      <c r="B146" s="18">
         <v>2</v>
       </c>
       <c r="C146" s="5">
@@ -6250,10 +6259,10 @@
       </c>
     </row>
     <row r="147" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A147" s="17">
+      <c r="A147" s="18">
         <v>125</v>
       </c>
-      <c r="B147" s="17">
+      <c r="B147" s="18">
         <v>2</v>
       </c>
       <c r="C147" s="5">
@@ -6261,10 +6270,10 @@
       </c>
     </row>
     <row r="148" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A148" s="17">
+      <c r="A148" s="18">
         <v>126</v>
       </c>
-      <c r="B148" s="17">
+      <c r="B148" s="18">
         <v>2</v>
       </c>
       <c r="C148" s="5">
@@ -6272,10 +6281,10 @@
       </c>
     </row>
     <row r="149" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A149" s="17">
+      <c r="A149" s="18">
         <v>127</v>
       </c>
-      <c r="B149" s="17">
+      <c r="B149" s="18">
         <v>2</v>
       </c>
       <c r="C149" s="5">
@@ -6283,10 +6292,10 @@
       </c>
     </row>
     <row r="150" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A150" s="17">
+      <c r="A150" s="18">
         <v>128</v>
       </c>
-      <c r="B150" s="17">
+      <c r="B150" s="18">
         <v>2</v>
       </c>
       <c r="C150" s="5">
@@ -6294,10 +6303,10 @@
       </c>
     </row>
     <row r="151" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A151" s="17">
+      <c r="A151" s="18">
         <v>129</v>
       </c>
-      <c r="B151" s="17">
+      <c r="B151" s="18">
         <v>2</v>
       </c>
       <c r="C151" s="5">
@@ -6305,10 +6314,10 @@
       </c>
     </row>
     <row r="152" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A152" s="17">
+      <c r="A152" s="18">
         <v>130</v>
       </c>
-      <c r="B152" s="17">
+      <c r="B152" s="18">
         <v>2</v>
       </c>
       <c r="C152" s="5">
@@ -6316,10 +6325,10 @@
       </c>
     </row>
     <row r="153" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A153" s="17">
+      <c r="A153" s="18">
         <v>131</v>
       </c>
-      <c r="B153" s="17">
+      <c r="B153" s="18">
         <v>2</v>
       </c>
       <c r="C153" s="5">
@@ -6327,10 +6336,10 @@
       </c>
     </row>
     <row r="154" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A154" s="17">
+      <c r="A154" s="18">
         <v>132</v>
       </c>
-      <c r="B154" s="17">
+      <c r="B154" s="18">
         <v>2</v>
       </c>
       <c r="C154" s="5">
@@ -6338,10 +6347,10 @@
       </c>
     </row>
     <row r="155" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A155" s="17">
+      <c r="A155" s="18">
         <v>133</v>
       </c>
-      <c r="B155" s="17">
+      <c r="B155" s="18">
         <v>2</v>
       </c>
       <c r="C155" s="5">
@@ -6349,10 +6358,10 @@
       </c>
     </row>
     <row r="156" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A156" s="17">
+      <c r="A156" s="18">
         <v>134</v>
       </c>
-      <c r="B156" s="17">
+      <c r="B156" s="18">
         <v>2</v>
       </c>
       <c r="C156" s="5">
@@ -6360,10 +6369,10 @@
       </c>
     </row>
     <row r="157" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A157" s="17">
+      <c r="A157" s="18">
         <v>135</v>
       </c>
-      <c r="B157" s="17">
+      <c r="B157" s="18">
         <v>2</v>
       </c>
       <c r="C157" s="5">
@@ -6371,10 +6380,10 @@
       </c>
     </row>
     <row r="158" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A158" s="17">
+      <c r="A158" s="18">
         <v>136</v>
       </c>
-      <c r="B158" s="17">
+      <c r="B158" s="18">
         <v>2</v>
       </c>
       <c r="C158" s="5">
@@ -6382,10 +6391,10 @@
       </c>
     </row>
     <row r="159" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A159" s="17">
+      <c r="A159" s="18">
         <v>137</v>
       </c>
-      <c r="B159" s="17">
+      <c r="B159" s="18">
         <v>2</v>
       </c>
       <c r="C159" s="5">
@@ -6393,10 +6402,10 @@
       </c>
     </row>
     <row r="160" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A160" s="17">
+      <c r="A160" s="18">
         <v>138</v>
       </c>
-      <c r="B160" s="17">
+      <c r="B160" s="18">
         <v>2</v>
       </c>
       <c r="C160" s="5">
@@ -6404,10 +6413,10 @@
       </c>
     </row>
     <row r="161" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A161" s="17">
+      <c r="A161" s="18">
         <v>139</v>
       </c>
-      <c r="B161" s="17">
+      <c r="B161" s="18">
         <v>2</v>
       </c>
       <c r="C161" s="5">
@@ -6415,10 +6424,10 @@
       </c>
     </row>
     <row r="162" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A162" s="17">
+      <c r="A162" s="18">
         <v>140</v>
       </c>
-      <c r="B162" s="17">
+      <c r="B162" s="18">
         <v>2</v>
       </c>
       <c r="C162" s="5">
@@ -6426,10 +6435,10 @@
       </c>
     </row>
     <row r="163" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A163" s="17">
+      <c r="A163" s="18">
         <v>141</v>
       </c>
-      <c r="B163" s="17">
+      <c r="B163" s="18">
         <v>2</v>
       </c>
       <c r="C163" s="5">
@@ -6437,10 +6446,10 @@
       </c>
     </row>
     <row r="164" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A164" s="17">
+      <c r="A164" s="18">
         <v>142</v>
       </c>
-      <c r="B164" s="17">
+      <c r="B164" s="18">
         <v>2</v>
       </c>
       <c r="C164" s="5">
@@ -6448,10 +6457,10 @@
       </c>
     </row>
     <row r="165" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A165" s="17">
+      <c r="A165" s="18">
         <v>143</v>
       </c>
-      <c r="B165" s="17">
+      <c r="B165" s="18">
         <v>2</v>
       </c>
       <c r="C165" s="5">
@@ -6459,10 +6468,10 @@
       </c>
     </row>
     <row r="166" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A166" s="17">
+      <c r="A166" s="18">
         <v>144</v>
       </c>
-      <c r="B166" s="17">
+      <c r="B166" s="18">
         <v>2</v>
       </c>
       <c r="C166" s="5">
@@ -6470,10 +6479,10 @@
       </c>
     </row>
     <row r="167" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A167" s="17">
+      <c r="A167" s="18">
         <v>145</v>
       </c>
-      <c r="B167" s="17">
+      <c r="B167" s="18">
         <v>2</v>
       </c>
       <c r="C167" s="5">
@@ -6481,10 +6490,10 @@
       </c>
     </row>
     <row r="168" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A168" s="17">
+      <c r="A168" s="18">
         <v>146</v>
       </c>
-      <c r="B168" s="17">
+      <c r="B168" s="18">
         <v>2</v>
       </c>
       <c r="C168" s="5">
@@ -6492,10 +6501,10 @@
       </c>
     </row>
     <row r="169" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A169" s="17">
+      <c r="A169" s="18">
         <v>147</v>
       </c>
-      <c r="B169" s="17">
+      <c r="B169" s="18">
         <v>2</v>
       </c>
       <c r="C169" s="5">
@@ -6503,10 +6512,10 @@
       </c>
     </row>
     <row r="170" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A170" s="17">
+      <c r="A170" s="18">
         <v>148</v>
       </c>
-      <c r="B170" s="17">
+      <c r="B170" s="18">
         <v>2</v>
       </c>
       <c r="C170" s="5">
@@ -6514,10 +6523,10 @@
       </c>
     </row>
     <row r="171" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A171" s="17">
+      <c r="A171" s="18">
         <v>149</v>
       </c>
-      <c r="B171" s="17">
+      <c r="B171" s="18">
         <v>2</v>
       </c>
       <c r="C171" s="5">
@@ -6525,10 +6534,10 @@
       </c>
     </row>
     <row r="172" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A172" s="17">
+      <c r="A172" s="18">
         <v>150</v>
       </c>
-      <c r="B172" s="17">
+      <c r="B172" s="18">
         <v>2</v>
       </c>
       <c r="C172" s="5">
@@ -6536,10 +6545,10 @@
       </c>
     </row>
     <row r="173" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A173" s="17">
+      <c r="A173" s="18">
         <v>151</v>
       </c>
-      <c r="B173" s="17">
+      <c r="B173" s="18">
         <v>2</v>
       </c>
       <c r="C173" s="5">
@@ -6547,10 +6556,10 @@
       </c>
     </row>
     <row r="174" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A174" s="17">
+      <c r="A174" s="18">
         <v>152</v>
       </c>
-      <c r="B174" s="17">
+      <c r="B174" s="18">
         <v>2</v>
       </c>
       <c r="C174" s="5">
@@ -6558,10 +6567,10 @@
       </c>
     </row>
     <row r="175" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A175" s="17">
+      <c r="A175" s="18">
         <v>153</v>
       </c>
-      <c r="B175" s="17">
+      <c r="B175" s="18">
         <v>2</v>
       </c>
       <c r="C175" s="5">
@@ -6569,10 +6578,10 @@
       </c>
     </row>
     <row r="176" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A176" s="17">
+      <c r="A176" s="18">
         <v>154</v>
       </c>
-      <c r="B176" s="17">
+      <c r="B176" s="18">
         <v>2</v>
       </c>
       <c r="C176" s="5">
@@ -6580,10 +6589,10 @@
       </c>
     </row>
     <row r="177" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A177" s="17">
+      <c r="A177" s="18">
         <v>155</v>
       </c>
-      <c r="B177" s="17">
+      <c r="B177" s="18">
         <v>2</v>
       </c>
       <c r="C177" s="5">
@@ -6591,10 +6600,10 @@
       </c>
     </row>
     <row r="178" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A178" s="17">
+      <c r="A178" s="18">
         <v>156</v>
       </c>
-      <c r="B178" s="17">
+      <c r="B178" s="18">
         <v>2</v>
       </c>
       <c r="C178" s="5">
@@ -6602,10 +6611,10 @@
       </c>
     </row>
     <row r="179" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A179" s="17">
+      <c r="A179" s="18">
         <v>157</v>
       </c>
-      <c r="B179" s="17">
+      <c r="B179" s="18">
         <v>2</v>
       </c>
       <c r="C179" s="5">
@@ -6613,10 +6622,10 @@
       </c>
     </row>
     <row r="180" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A180" s="17">
+      <c r="A180" s="18">
         <v>158</v>
       </c>
-      <c r="B180" s="17">
+      <c r="B180" s="18">
         <v>2</v>
       </c>
       <c r="C180" s="5">
@@ -6624,10 +6633,10 @@
       </c>
     </row>
     <row r="181" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A181" s="17">
+      <c r="A181" s="18">
         <v>159</v>
       </c>
-      <c r="B181" s="17">
+      <c r="B181" s="18">
         <v>2</v>
       </c>
       <c r="C181" s="5">
@@ -6635,10 +6644,10 @@
       </c>
     </row>
     <row r="182" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A182" s="17">
+      <c r="A182" s="18">
         <v>160</v>
       </c>
-      <c r="B182" s="17">
+      <c r="B182" s="18">
         <v>2</v>
       </c>
       <c r="C182" s="5">
@@ -6646,10 +6655,10 @@
       </c>
     </row>
     <row r="183" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A183" s="17">
+      <c r="A183" s="18">
         <v>161</v>
       </c>
-      <c r="B183" s="17">
+      <c r="B183" s="18">
         <v>2</v>
       </c>
       <c r="C183" s="5">
@@ -6657,10 +6666,10 @@
       </c>
     </row>
     <row r="184" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A184" s="17">
+      <c r="A184" s="18">
         <v>162</v>
       </c>
-      <c r="B184" s="17">
+      <c r="B184" s="18">
         <v>2</v>
       </c>
       <c r="C184" s="5">
@@ -6668,10 +6677,10 @@
       </c>
     </row>
     <row r="185" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A185" s="17">
+      <c r="A185" s="18">
         <v>163</v>
       </c>
-      <c r="B185" s="17">
+      <c r="B185" s="18">
         <v>2</v>
       </c>
       <c r="C185" s="5">
@@ -6679,10 +6688,10 @@
       </c>
     </row>
     <row r="186" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A186" s="17">
+      <c r="A186" s="18">
         <v>164</v>
       </c>
-      <c r="B186" s="17">
+      <c r="B186" s="18">
         <v>2</v>
       </c>
       <c r="C186" s="5">
@@ -6690,10 +6699,10 @@
       </c>
     </row>
     <row r="187" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A187" s="17">
+      <c r="A187" s="18">
         <v>165</v>
       </c>
-      <c r="B187" s="17">
+      <c r="B187" s="18">
         <v>2</v>
       </c>
       <c r="C187" s="5">
@@ -6701,10 +6710,10 @@
       </c>
     </row>
     <row r="188" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A188" s="17">
+      <c r="A188" s="18">
         <v>166</v>
       </c>
-      <c r="B188" s="17">
+      <c r="B188" s="18">
         <v>2</v>
       </c>
       <c r="C188" s="5">
@@ -6712,10 +6721,10 @@
       </c>
     </row>
     <row r="189" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A189" s="17">
+      <c r="A189" s="18">
         <v>167</v>
       </c>
-      <c r="B189" s="17">
+      <c r="B189" s="18">
         <v>2</v>
       </c>
       <c r="C189" s="5">
@@ -6723,10 +6732,10 @@
       </c>
     </row>
     <row r="190" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A190" s="17">
+      <c r="A190" s="18">
         <v>168</v>
       </c>
-      <c r="B190" s="17">
+      <c r="B190" s="18">
         <v>2</v>
       </c>
       <c r="C190" s="5">
@@ -6734,10 +6743,10 @@
       </c>
     </row>
     <row r="191" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A191" s="17">
+      <c r="A191" s="18">
         <v>169</v>
       </c>
-      <c r="B191" s="17">
+      <c r="B191" s="18">
         <v>2</v>
       </c>
       <c r="C191" s="5">
@@ -6745,10 +6754,10 @@
       </c>
     </row>
     <row r="192" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A192" s="17">
+      <c r="A192" s="18">
         <v>170</v>
       </c>
-      <c r="B192" s="17">
+      <c r="B192" s="18">
         <v>2</v>
       </c>
       <c r="C192" s="5">
@@ -6756,10 +6765,10 @@
       </c>
     </row>
     <row r="193" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A193" s="17">
+      <c r="A193" s="18">
         <v>171</v>
       </c>
-      <c r="B193" s="17">
+      <c r="B193" s="18">
         <v>2</v>
       </c>
       <c r="C193" s="5">
@@ -6767,10 +6776,10 @@
       </c>
     </row>
     <row r="194" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A194" s="17">
+      <c r="A194" s="18">
         <v>172</v>
       </c>
-      <c r="B194" s="17">
+      <c r="B194" s="18">
         <v>2</v>
       </c>
       <c r="C194" s="5">
@@ -6778,10 +6787,10 @@
       </c>
     </row>
     <row r="195" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A195" s="17">
+      <c r="A195" s="18">
         <v>173</v>
       </c>
-      <c r="B195" s="17">
+      <c r="B195" s="18">
         <v>2</v>
       </c>
       <c r="C195" s="5">
@@ -6789,10 +6798,10 @@
       </c>
     </row>
     <row r="196" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A196" s="17">
+      <c r="A196" s="18">
         <v>174</v>
       </c>
-      <c r="B196" s="17">
+      <c r="B196" s="18">
         <v>2</v>
       </c>
       <c r="C196" s="5">
@@ -6800,10 +6809,10 @@
       </c>
     </row>
     <row r="197" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A197" s="17">
+      <c r="A197" s="18">
         <v>175</v>
       </c>
-      <c r="B197" s="17">
+      <c r="B197" s="18">
         <v>2</v>
       </c>
       <c r="C197" s="5">
@@ -6811,10 +6820,10 @@
       </c>
     </row>
     <row r="198" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A198" s="17">
+      <c r="A198" s="18">
         <v>176</v>
       </c>
-      <c r="B198" s="17">
+      <c r="B198" s="18">
         <v>2</v>
       </c>
       <c r="C198" s="5">
@@ -6822,10 +6831,10 @@
       </c>
     </row>
     <row r="199" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A199" s="17">
+      <c r="A199" s="18">
         <v>177</v>
       </c>
-      <c r="B199" s="17">
+      <c r="B199" s="18">
         <v>2</v>
       </c>
       <c r="C199" s="5">
@@ -6833,10 +6842,10 @@
       </c>
     </row>
     <row r="200" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A200" s="17">
+      <c r="A200" s="18">
         <v>178</v>
       </c>
-      <c r="B200" s="17">
+      <c r="B200" s="18">
         <v>2</v>
       </c>
       <c r="C200" s="5">
@@ -6844,10 +6853,10 @@
       </c>
     </row>
     <row r="201" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A201" s="17">
+      <c r="A201" s="18">
         <v>179</v>
       </c>
-      <c r="B201" s="17">
+      <c r="B201" s="18">
         <v>2</v>
       </c>
       <c r="C201" s="5">
@@ -6855,10 +6864,10 @@
       </c>
     </row>
     <row r="202" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A202" s="17">
+      <c r="A202" s="18">
         <v>180</v>
       </c>
-      <c r="B202" s="17">
+      <c r="B202" s="18">
         <v>2</v>
       </c>
       <c r="C202" s="5">
@@ -6866,10 +6875,10 @@
       </c>
     </row>
     <row r="203" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A203" s="17">
+      <c r="A203" s="18">
         <v>181</v>
       </c>
-      <c r="B203" s="17">
+      <c r="B203" s="18">
         <v>2</v>
       </c>
       <c r="C203" s="5">
@@ -6877,10 +6886,10 @@
       </c>
     </row>
     <row r="204" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A204" s="17">
+      <c r="A204" s="18">
         <v>182</v>
       </c>
-      <c r="B204" s="17">
+      <c r="B204" s="18">
         <v>2</v>
       </c>
       <c r="C204" s="5">
@@ -6888,10 +6897,10 @@
       </c>
     </row>
     <row r="205" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A205" s="17">
+      <c r="A205" s="18">
         <v>183</v>
       </c>
-      <c r="B205" s="17">
+      <c r="B205" s="18">
         <v>2</v>
       </c>
       <c r="C205" s="5">
@@ -6899,10 +6908,10 @@
       </c>
     </row>
     <row r="206" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A206" s="17">
+      <c r="A206" s="18">
         <v>184</v>
       </c>
-      <c r="B206" s="17">
+      <c r="B206" s="18">
         <v>2</v>
       </c>
       <c r="C206" s="5">
@@ -6910,10 +6919,10 @@
       </c>
     </row>
     <row r="207" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A207" s="17">
+      <c r="A207" s="18">
         <v>185</v>
       </c>
-      <c r="B207" s="17">
+      <c r="B207" s="18">
         <v>2</v>
       </c>
       <c r="C207" s="5">
@@ -6921,10 +6930,10 @@
       </c>
     </row>
     <row r="208" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A208" s="17">
+      <c r="A208" s="18">
         <v>186</v>
       </c>
-      <c r="B208" s="17">
+      <c r="B208" s="18">
         <v>2</v>
       </c>
       <c r="C208" s="5">
@@ -6932,10 +6941,10 @@
       </c>
     </row>
     <row r="209" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A209" s="17">
+      <c r="A209" s="18">
         <v>187</v>
       </c>
-      <c r="B209" s="17">
+      <c r="B209" s="18">
         <v>2</v>
       </c>
       <c r="C209" s="5">
@@ -6943,10 +6952,10 @@
       </c>
     </row>
     <row r="210" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A210" s="17">
+      <c r="A210" s="18">
         <v>188</v>
       </c>
-      <c r="B210" s="17">
+      <c r="B210" s="18">
         <v>2</v>
       </c>
       <c r="C210" s="5">
@@ -6954,10 +6963,10 @@
       </c>
     </row>
     <row r="211" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A211" s="17">
+      <c r="A211" s="18">
         <v>189</v>
       </c>
-      <c r="B211" s="17">
+      <c r="B211" s="18">
         <v>2</v>
       </c>
       <c r="C211" s="5">
@@ -6965,10 +6974,10 @@
       </c>
     </row>
     <row r="212" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A212" s="17">
+      <c r="A212" s="18">
         <v>190</v>
       </c>
-      <c r="B212" s="17">
+      <c r="B212" s="18">
         <v>2</v>
       </c>
       <c r="C212" s="5">
@@ -6976,10 +6985,10 @@
       </c>
     </row>
     <row r="213" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A213" s="17">
+      <c r="A213" s="18">
         <v>191</v>
       </c>
-      <c r="B213" s="17">
+      <c r="B213" s="18">
         <v>2</v>
       </c>
       <c r="C213" s="5">
@@ -6987,10 +6996,10 @@
       </c>
     </row>
     <row r="214" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A214" s="17">
+      <c r="A214" s="18">
         <v>192</v>
       </c>
-      <c r="B214" s="17">
+      <c r="B214" s="18">
         <v>2</v>
       </c>
       <c r="C214" s="5">
@@ -6998,10 +7007,10 @@
       </c>
     </row>
     <row r="215" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A215" s="17">
+      <c r="A215" s="18">
         <v>193</v>
       </c>
-      <c r="B215" s="17">
+      <c r="B215" s="18">
         <v>2</v>
       </c>
       <c r="C215" s="5">
@@ -7009,10 +7018,10 @@
       </c>
     </row>
     <row r="216" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A216" s="17">
+      <c r="A216" s="18">
         <v>194</v>
       </c>
-      <c r="B216" s="17">
+      <c r="B216" s="18">
         <v>2</v>
       </c>
       <c r="C216" s="5">
@@ -7020,10 +7029,10 @@
       </c>
     </row>
     <row r="217" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A217" s="17">
+      <c r="A217" s="18">
         <v>195</v>
       </c>
-      <c r="B217" s="17">
+      <c r="B217" s="18">
         <v>2</v>
       </c>
       <c r="C217" s="5">
@@ -7031,10 +7040,10 @@
       </c>
     </row>
     <row r="218" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A218" s="17">
+      <c r="A218" s="18">
         <v>196</v>
       </c>
-      <c r="B218" s="17">
+      <c r="B218" s="18">
         <v>2</v>
       </c>
       <c r="C218" s="5">
@@ -7042,10 +7051,10 @@
       </c>
     </row>
     <row r="219" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A219" s="17">
+      <c r="A219" s="18">
         <v>197</v>
       </c>
-      <c r="B219" s="17">
+      <c r="B219" s="18">
         <v>2</v>
       </c>
       <c r="C219" s="5">
@@ -7053,10 +7062,10 @@
       </c>
     </row>
     <row r="220" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A220" s="17">
+      <c r="A220" s="18">
         <v>198</v>
       </c>
-      <c r="B220" s="17">
+      <c r="B220" s="18">
         <v>2</v>
       </c>
       <c r="C220" s="5">
@@ -7064,10 +7073,10 @@
       </c>
     </row>
     <row r="221" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A221" s="17">
+      <c r="A221" s="18">
         <v>199</v>
       </c>
-      <c r="B221" s="17">
+      <c r="B221" s="18">
         <v>2</v>
       </c>
       <c r="C221" s="5">
@@ -7075,10 +7084,10 @@
       </c>
     </row>
     <row r="222" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A222" s="17">
+      <c r="A222" s="18">
         <v>200</v>
       </c>
-      <c r="B222" s="17">
+      <c r="B222" s="18">
         <v>2</v>
       </c>
       <c r="C222" s="5">
@@ -7086,10 +7095,10 @@
       </c>
     </row>
     <row r="223" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A223" s="17">
+      <c r="A223" s="18">
         <v>201</v>
       </c>
-      <c r="B223" s="17">
+      <c r="B223" s="18">
         <v>2</v>
       </c>
       <c r="C223" s="5">
@@ -7097,10 +7106,10 @@
       </c>
     </row>
     <row r="224" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A224" s="17">
+      <c r="A224" s="18">
         <v>202</v>
       </c>
-      <c r="B224" s="17">
+      <c r="B224" s="18">
         <v>2</v>
       </c>
       <c r="C224" s="5">
@@ -7108,10 +7117,10 @@
       </c>
     </row>
     <row r="225" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A225" s="17">
+      <c r="A225" s="18">
         <v>203</v>
       </c>
-      <c r="B225" s="17">
+      <c r="B225" s="18">
         <v>2</v>
       </c>
       <c r="C225" s="5">
@@ -7119,10 +7128,10 @@
       </c>
     </row>
     <row r="226" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A226" s="17">
+      <c r="A226" s="18">
         <v>204</v>
       </c>
-      <c r="B226" s="17">
+      <c r="B226" s="18">
         <v>2</v>
       </c>
       <c r="C226" s="5">
@@ -7130,10 +7139,10 @@
       </c>
     </row>
     <row r="227" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A227" s="17">
+      <c r="A227" s="18">
         <v>205</v>
       </c>
-      <c r="B227" s="17">
+      <c r="B227" s="18">
         <v>2</v>
       </c>
       <c r="C227" s="5">
@@ -7141,10 +7150,10 @@
       </c>
     </row>
     <row r="228" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A228" s="17">
+      <c r="A228" s="18">
         <v>206</v>
       </c>
-      <c r="B228" s="17">
+      <c r="B228" s="18">
         <v>2</v>
       </c>
       <c r="C228" s="5">
@@ -7152,10 +7161,10 @@
       </c>
     </row>
     <row r="229" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A229" s="17">
+      <c r="A229" s="18">
         <v>207</v>
       </c>
-      <c r="B229" s="17">
+      <c r="B229" s="18">
         <v>2</v>
       </c>
       <c r="C229" s="5">
@@ -7163,10 +7172,10 @@
       </c>
     </row>
     <row r="230" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A230" s="17">
+      <c r="A230" s="18">
         <v>208</v>
       </c>
-      <c r="B230" s="17">
+      <c r="B230" s="18">
         <v>2</v>
       </c>
       <c r="C230" s="5">
@@ -7174,10 +7183,10 @@
       </c>
     </row>
     <row r="231" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A231" s="17">
+      <c r="A231" s="18">
         <v>209</v>
       </c>
-      <c r="B231" s="17">
+      <c r="B231" s="18">
         <v>2</v>
       </c>
       <c r="C231" s="5">
@@ -7185,10 +7194,10 @@
       </c>
     </row>
     <row r="232" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A232" s="17">
+      <c r="A232" s="18">
         <v>210</v>
       </c>
-      <c r="B232" s="17">
+      <c r="B232" s="18">
         <v>2</v>
       </c>
       <c r="C232" s="5">
@@ -7196,10 +7205,10 @@
       </c>
     </row>
     <row r="233" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A233" s="17">
+      <c r="A233" s="18">
         <v>211</v>
       </c>
-      <c r="B233" s="17">
+      <c r="B233" s="18">
         <v>2</v>
       </c>
       <c r="C233" s="5">
@@ -7207,10 +7216,10 @@
       </c>
     </row>
     <row r="234" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A234" s="17">
+      <c r="A234" s="18">
         <v>212</v>
       </c>
-      <c r="B234" s="17">
+      <c r="B234" s="18">
         <v>2</v>
       </c>
       <c r="C234" s="5">
@@ -7218,10 +7227,10 @@
       </c>
     </row>
     <row r="235" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A235" s="17">
+      <c r="A235" s="18">
         <v>213</v>
       </c>
-      <c r="B235" s="17">
+      <c r="B235" s="18">
         <v>2</v>
       </c>
       <c r="C235" s="5">
@@ -7229,10 +7238,10 @@
       </c>
     </row>
     <row r="236" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A236" s="17">
+      <c r="A236" s="18">
         <v>214</v>
       </c>
-      <c r="B236" s="17">
+      <c r="B236" s="18">
         <v>2</v>
       </c>
       <c r="C236" s="5">
@@ -7240,10 +7249,10 @@
       </c>
     </row>
     <row r="237" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A237" s="17">
+      <c r="A237" s="18">
         <v>215</v>
       </c>
-      <c r="B237" s="17">
+      <c r="B237" s="18">
         <v>2</v>
       </c>
       <c r="C237" s="5">
@@ -7251,10 +7260,10 @@
       </c>
     </row>
     <row r="238" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A238" s="17">
+      <c r="A238" s="18">
         <v>216</v>
       </c>
-      <c r="B238" s="17">
+      <c r="B238" s="18">
         <v>2</v>
       </c>
       <c r="C238" s="5">
@@ -7262,10 +7271,10 @@
       </c>
     </row>
     <row r="239" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A239" s="17">
+      <c r="A239" s="18">
         <v>217</v>
       </c>
-      <c r="B239" s="17">
+      <c r="B239" s="18">
         <v>2</v>
       </c>
       <c r="C239" s="5">
@@ -7273,10 +7282,10 @@
       </c>
     </row>
     <row r="240" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A240" s="17">
+      <c r="A240" s="18">
         <v>218</v>
       </c>
-      <c r="B240" s="17">
+      <c r="B240" s="18">
         <v>2</v>
       </c>
       <c r="C240" s="5">
@@ -7284,10 +7293,10 @@
       </c>
     </row>
     <row r="241" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A241" s="17">
+      <c r="A241" s="18">
         <v>219</v>
       </c>
-      <c r="B241" s="17">
+      <c r="B241" s="18">
         <v>2</v>
       </c>
       <c r="C241" s="5">
@@ -7295,10 +7304,10 @@
       </c>
     </row>
     <row r="242" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A242" s="17">
+      <c r="A242" s="18">
         <v>220</v>
       </c>
-      <c r="B242" s="17">
+      <c r="B242" s="18">
         <v>2</v>
       </c>
       <c r="C242" s="5">
@@ -7306,10 +7315,10 @@
       </c>
     </row>
     <row r="243" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A243" s="17">
+      <c r="A243" s="18">
         <v>221</v>
       </c>
-      <c r="B243" s="17">
+      <c r="B243" s="18">
         <v>2</v>
       </c>
       <c r="C243" s="5">
@@ -7317,10 +7326,10 @@
       </c>
     </row>
     <row r="244" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A244" s="17">
+      <c r="A244" s="18">
         <v>222</v>
       </c>
-      <c r="B244" s="17">
+      <c r="B244" s="18">
         <v>2</v>
       </c>
       <c r="C244" s="5">
@@ -7328,10 +7337,10 @@
       </c>
     </row>
     <row r="245" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A245" s="17">
+      <c r="A245" s="18">
         <v>223</v>
       </c>
-      <c r="B245" s="17">
+      <c r="B245" s="18">
         <v>2</v>
       </c>
       <c r="C245" s="5">
@@ -7339,10 +7348,10 @@
       </c>
     </row>
     <row r="246" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A246" s="17">
+      <c r="A246" s="18">
         <v>224</v>
       </c>
-      <c r="B246" s="17">
+      <c r="B246" s="18">
         <v>2</v>
       </c>
       <c r="C246" s="5">
@@ -7350,10 +7359,10 @@
       </c>
     </row>
     <row r="247" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A247" s="17">
+      <c r="A247" s="18">
         <v>225</v>
       </c>
-      <c r="B247" s="17">
+      <c r="B247" s="18">
         <v>2</v>
       </c>
       <c r="C247" s="5">
@@ -7361,10 +7370,10 @@
       </c>
     </row>
     <row r="248" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A248" s="17">
+      <c r="A248" s="18">
         <v>226</v>
       </c>
-      <c r="B248" s="17">
+      <c r="B248" s="18">
         <v>2</v>
       </c>
       <c r="C248" s="5">
@@ -7372,10 +7381,10 @@
       </c>
     </row>
     <row r="249" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A249" s="17">
+      <c r="A249" s="18">
         <v>227</v>
       </c>
-      <c r="B249" s="17">
+      <c r="B249" s="18">
         <v>2</v>
       </c>
       <c r="C249" s="5">
@@ -7383,10 +7392,10 @@
       </c>
     </row>
     <row r="250" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A250" s="17">
+      <c r="A250" s="18">
         <v>228</v>
       </c>
-      <c r="B250" s="17">
+      <c r="B250" s="18">
         <v>2</v>
       </c>
       <c r="C250" s="5">
@@ -7394,10 +7403,10 @@
       </c>
     </row>
     <row r="251" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A251" s="17">
+      <c r="A251" s="18">
         <v>229</v>
       </c>
-      <c r="B251" s="17">
+      <c r="B251" s="18">
         <v>2</v>
       </c>
       <c r="C251" s="5">
@@ -7405,10 +7414,10 @@
       </c>
     </row>
     <row r="252" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A252" s="17">
+      <c r="A252" s="18">
         <v>230</v>
       </c>
-      <c r="B252" s="17">
+      <c r="B252" s="18">
         <v>2</v>
       </c>
       <c r="C252" s="5">
@@ -7416,10 +7425,10 @@
       </c>
     </row>
     <row r="253" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A253" s="17">
+      <c r="A253" s="18">
         <v>231</v>
       </c>
-      <c r="B253" s="17">
+      <c r="B253" s="18">
         <v>2</v>
       </c>
       <c r="C253" s="5">
@@ -7427,10 +7436,10 @@
       </c>
     </row>
     <row r="254" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A254" s="17">
+      <c r="A254" s="18">
         <v>232</v>
       </c>
-      <c r="B254" s="17">
+      <c r="B254" s="18">
         <v>2</v>
       </c>
       <c r="C254" s="5">
@@ -7438,10 +7447,10 @@
       </c>
     </row>
     <row r="255" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A255" s="17">
+      <c r="A255" s="18">
         <v>233</v>
       </c>
-      <c r="B255" s="17">
+      <c r="B255" s="18">
         <v>2</v>
       </c>
       <c r="C255" s="5">
@@ -7449,10 +7458,10 @@
       </c>
     </row>
     <row r="256" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A256" s="17">
+      <c r="A256" s="18">
         <v>234</v>
       </c>
-      <c r="B256" s="17">
+      <c r="B256" s="18">
         <v>2</v>
       </c>
       <c r="C256" s="5">
@@ -7460,10 +7469,10 @@
       </c>
     </row>
     <row r="257" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A257" s="17">
+      <c r="A257" s="18">
         <v>235</v>
       </c>
-      <c r="B257" s="17">
+      <c r="B257" s="18">
         <v>2</v>
       </c>
       <c r="C257" s="5">
@@ -7471,10 +7480,10 @@
       </c>
     </row>
     <row r="258" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A258" s="17">
+      <c r="A258" s="18">
         <v>236</v>
       </c>
-      <c r="B258" s="17">
+      <c r="B258" s="18">
         <v>2</v>
       </c>
       <c r="C258" s="5">
@@ -7482,10 +7491,10 @@
       </c>
     </row>
     <row r="259" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A259" s="17">
+      <c r="A259" s="18">
         <v>237</v>
       </c>
-      <c r="B259" s="17">
+      <c r="B259" s="18">
         <v>2</v>
       </c>
       <c r="C259" s="5">
@@ -7493,10 +7502,10 @@
       </c>
     </row>
     <row r="260" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A260" s="17">
+      <c r="A260" s="18">
         <v>238</v>
       </c>
-      <c r="B260" s="17">
+      <c r="B260" s="18">
         <v>2</v>
       </c>
       <c r="C260" s="5">
@@ -7504,10 +7513,10 @@
       </c>
     </row>
     <row r="261" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A261" s="17">
+      <c r="A261" s="18">
         <v>239</v>
       </c>
-      <c r="B261" s="17">
+      <c r="B261" s="18">
         <v>2</v>
       </c>
       <c r="C261" s="5">
@@ -7515,10 +7524,10 @@
       </c>
     </row>
     <row r="262" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A262" s="17">
+      <c r="A262" s="18">
         <v>240</v>
       </c>
-      <c r="B262" s="17">
+      <c r="B262" s="18">
         <v>2</v>
       </c>
       <c r="C262" s="5">
@@ -7526,10 +7535,10 @@
       </c>
     </row>
     <row r="263" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A263" s="17">
+      <c r="A263" s="18">
         <v>241</v>
       </c>
-      <c r="B263" s="17">
+      <c r="B263" s="18">
         <v>2</v>
       </c>
       <c r="C263" s="5">
@@ -7537,10 +7546,10 @@
       </c>
     </row>
     <row r="264" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A264" s="17">
+      <c r="A264" s="18">
         <v>242</v>
       </c>
-      <c r="B264" s="17">
+      <c r="B264" s="18">
         <v>2</v>
       </c>
       <c r="C264" s="5">
@@ -7548,10 +7557,10 @@
       </c>
     </row>
     <row r="265" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A265" s="17">
+      <c r="A265" s="18">
         <v>243</v>
       </c>
-      <c r="B265" s="17">
+      <c r="B265" s="18">
         <v>2</v>
       </c>
       <c r="C265" s="5">
@@ -7559,10 +7568,10 @@
       </c>
     </row>
     <row r="266" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A266" s="17">
+      <c r="A266" s="18">
         <v>244</v>
       </c>
-      <c r="B266" s="17">
+      <c r="B266" s="18">
         <v>2</v>
       </c>
       <c r="C266" s="5">
@@ -7570,10 +7579,10 @@
       </c>
     </row>
     <row r="267" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A267" s="17">
+      <c r="A267" s="18">
         <v>245</v>
       </c>
-      <c r="B267" s="17">
+      <c r="B267" s="18">
         <v>2</v>
       </c>
       <c r="C267" s="5">
@@ -7581,10 +7590,10 @@
       </c>
     </row>
     <row r="268" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A268" s="17">
+      <c r="A268" s="18">
         <v>246</v>
       </c>
-      <c r="B268" s="17">
+      <c r="B268" s="18">
         <v>2</v>
       </c>
       <c r="C268" s="5">
@@ -7592,10 +7601,10 @@
       </c>
     </row>
     <row r="269" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A269" s="17">
+      <c r="A269" s="18">
         <v>247</v>
       </c>
-      <c r="B269" s="17">
+      <c r="B269" s="18">
         <v>2</v>
       </c>
       <c r="C269" s="5">
@@ -7603,10 +7612,10 @@
       </c>
     </row>
     <row r="270" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A270" s="17">
+      <c r="A270" s="18">
         <v>248</v>
       </c>
-      <c r="B270" s="17">
+      <c r="B270" s="18">
         <v>2</v>
       </c>
       <c r="C270" s="5">
@@ -7614,10 +7623,10 @@
       </c>
     </row>
     <row r="271" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A271" s="17">
+      <c r="A271" s="18">
         <v>249</v>
       </c>
-      <c r="B271" s="17">
+      <c r="B271" s="18">
         <v>2</v>
       </c>
       <c r="C271" s="5">
@@ -7625,10 +7634,10 @@
       </c>
     </row>
     <row r="272" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A272" s="17">
+      <c r="A272" s="18">
         <v>250</v>
       </c>
-      <c r="B272" s="17">
+      <c r="B272" s="18">
         <v>2</v>
       </c>
       <c r="C272" s="5">
@@ -7636,10 +7645,10 @@
       </c>
     </row>
     <row r="273" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A273" s="17">
+      <c r="A273" s="18">
         <v>251</v>
       </c>
-      <c r="B273" s="17">
+      <c r="B273" s="18">
         <v>2</v>
       </c>
       <c r="C273" s="5">
@@ -7647,10 +7656,10 @@
       </c>
     </row>
     <row r="274" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A274" s="17">
+      <c r="A274" s="18">
         <v>252</v>
       </c>
-      <c r="B274" s="17">
+      <c r="B274" s="18">
         <v>2</v>
       </c>
       <c r="C274" s="5">
@@ -7658,10 +7667,10 @@
       </c>
     </row>
     <row r="275" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A275" s="17">
+      <c r="A275" s="18">
         <v>253</v>
       </c>
-      <c r="B275" s="17">
+      <c r="B275" s="18">
         <v>2</v>
       </c>
       <c r="C275" s="5">
@@ -7669,10 +7678,10 @@
       </c>
     </row>
     <row r="276" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A276" s="17">
+      <c r="A276" s="18">
         <v>254</v>
       </c>
-      <c r="B276" s="17">
+      <c r="B276" s="18">
         <v>2</v>
       </c>
       <c r="C276" s="5">
@@ -7680,10 +7689,10 @@
       </c>
     </row>
     <row r="277" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A277" s="17">
+      <c r="A277" s="18">
         <v>255</v>
       </c>
-      <c r="B277" s="17">
+      <c r="B277" s="18">
         <v>2</v>
       </c>
       <c r="C277" s="5">
@@ -7691,10 +7700,10 @@
       </c>
     </row>
     <row r="278" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A278" s="17">
+      <c r="A278" s="18">
         <v>256</v>
       </c>
-      <c r="B278" s="17">
+      <c r="B278" s="18">
         <v>2</v>
       </c>
       <c r="C278" s="5">
@@ -7702,10 +7711,10 @@
       </c>
     </row>
     <row r="279" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A279" s="17">
+      <c r="A279" s="18">
         <v>257</v>
       </c>
-      <c r="B279" s="17">
+      <c r="B279" s="18">
         <v>2</v>
       </c>
       <c r="C279" s="5">
@@ -7713,10 +7722,10 @@
       </c>
     </row>
     <row r="280" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A280" s="17">
+      <c r="A280" s="18">
         <v>258</v>
       </c>
-      <c r="B280" s="17">
+      <c r="B280" s="18">
         <v>2</v>
       </c>
       <c r="C280" s="5">
@@ -7724,10 +7733,10 @@
       </c>
     </row>
     <row r="281" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A281" s="17">
+      <c r="A281" s="18">
         <v>259</v>
       </c>
-      <c r="B281" s="17">
+      <c r="B281" s="18">
         <v>2</v>
       </c>
       <c r="C281" s="5">
@@ -7735,10 +7744,10 @@
       </c>
     </row>
     <row r="282" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A282" s="17">
+      <c r="A282" s="18">
         <v>260</v>
       </c>
-      <c r="B282" s="17">
+      <c r="B282" s="18">
         <v>2</v>
       </c>
       <c r="C282" s="5">
@@ -7746,10 +7755,10 @@
       </c>
     </row>
     <row r="283" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A283" s="17">
+      <c r="A283" s="18">
         <v>261</v>
       </c>
-      <c r="B283" s="17">
+      <c r="B283" s="18">
         <v>2</v>
       </c>
       <c r="C283" s="5">
@@ -7757,10 +7766,10 @@
       </c>
     </row>
     <row r="284" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A284" s="17">
+      <c r="A284" s="18">
         <v>262</v>
       </c>
-      <c r="B284" s="17">
+      <c r="B284" s="18">
         <v>2</v>
       </c>
       <c r="C284" s="5">
@@ -7768,10 +7777,10 @@
       </c>
     </row>
     <row r="285" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A285" s="17">
+      <c r="A285" s="18">
         <v>263</v>
       </c>
-      <c r="B285" s="17">
+      <c r="B285" s="18">
         <v>2</v>
       </c>
       <c r="C285" s="5">
@@ -7779,10 +7788,10 @@
       </c>
     </row>
     <row r="286" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A286" s="17">
+      <c r="A286" s="18">
         <v>264</v>
       </c>
-      <c r="B286" s="17">
+      <c r="B286" s="18">
         <v>2</v>
       </c>
       <c r="C286" s="5">
@@ -7790,10 +7799,10 @@
       </c>
     </row>
     <row r="287" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A287" s="17">
+      <c r="A287" s="18">
         <v>265</v>
       </c>
-      <c r="B287" s="17">
+      <c r="B287" s="18">
         <v>2</v>
       </c>
       <c r="C287" s="5">
@@ -7801,10 +7810,10 @@
       </c>
     </row>
     <row r="288" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A288" s="17">
+      <c r="A288" s="18">
         <v>266</v>
       </c>
-      <c r="B288" s="17">
+      <c r="B288" s="18">
         <v>2</v>
       </c>
       <c r="C288" s="5">
@@ -7812,10 +7821,10 @@
       </c>
     </row>
     <row r="289" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A289" s="17">
+      <c r="A289" s="18">
         <v>267</v>
       </c>
-      <c r="B289" s="17">
+      <c r="B289" s="18">
         <v>2</v>
       </c>
       <c r="C289" s="5">
@@ -7823,10 +7832,10 @@
       </c>
     </row>
     <row r="290" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A290" s="17">
+      <c r="A290" s="18">
         <v>268</v>
       </c>
-      <c r="B290" s="17">
+      <c r="B290" s="18">
         <v>2</v>
       </c>
       <c r="C290" s="5">
@@ -7834,10 +7843,10 @@
       </c>
     </row>
     <row r="291" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A291" s="17">
+      <c r="A291" s="18">
         <v>269</v>
       </c>
-      <c r="B291" s="17">
+      <c r="B291" s="18">
         <v>2</v>
       </c>
       <c r="C291" s="5">
@@ -7845,10 +7854,10 @@
       </c>
     </row>
     <row r="292" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A292" s="17">
+      <c r="A292" s="18">
         <v>270</v>
       </c>
-      <c r="B292" s="17">
+      <c r="B292" s="18">
         <v>2</v>
       </c>
       <c r="C292" s="5">
@@ -7856,10 +7865,10 @@
       </c>
     </row>
     <row r="293" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A293" s="17">
+      <c r="A293" s="18">
         <v>271</v>
       </c>
-      <c r="B293" s="17">
+      <c r="B293" s="18">
         <v>2</v>
       </c>
       <c r="C293" s="5">
@@ -7867,10 +7876,10 @@
       </c>
     </row>
     <row r="294" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A294" s="17">
+      <c r="A294" s="18">
         <v>272</v>
       </c>
-      <c r="B294" s="17">
+      <c r="B294" s="18">
         <v>2</v>
       </c>
       <c r="C294" s="5">
@@ -7878,10 +7887,10 @@
       </c>
     </row>
     <row r="295" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A295" s="17">
+      <c r="A295" s="18">
         <v>273</v>
       </c>
-      <c r="B295" s="17">
+      <c r="B295" s="18">
         <v>2</v>
       </c>
       <c r="C295" s="5">
@@ -7889,10 +7898,10 @@
       </c>
     </row>
     <row r="296" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A296" s="17">
+      <c r="A296" s="18">
         <v>274</v>
       </c>
-      <c r="B296" s="17">
+      <c r="B296" s="18">
         <v>2</v>
       </c>
       <c r="C296" s="5">
@@ -7900,10 +7909,10 @@
       </c>
     </row>
     <row r="297" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A297" s="17">
+      <c r="A297" s="18">
         <v>275</v>
       </c>
-      <c r="B297" s="17">
+      <c r="B297" s="18">
         <v>2</v>
       </c>
       <c r="C297" s="5">
@@ -7911,10 +7920,10 @@
       </c>
     </row>
     <row r="298" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A298" s="17">
+      <c r="A298" s="18">
         <v>276</v>
       </c>
-      <c r="B298" s="17">
+      <c r="B298" s="18">
         <v>2</v>
       </c>
       <c r="C298" s="5">
@@ -7922,10 +7931,10 @@
       </c>
     </row>
     <row r="299" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A299" s="17">
+      <c r="A299" s="18">
         <v>277</v>
       </c>
-      <c r="B299" s="17">
+      <c r="B299" s="18">
         <v>2</v>
       </c>
       <c r="C299" s="5">
@@ -7933,10 +7942,10 @@
       </c>
     </row>
     <row r="300" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A300" s="17">
+      <c r="A300" s="18">
         <v>278</v>
       </c>
-      <c r="B300" s="17">
+      <c r="B300" s="18">
         <v>2</v>
       </c>
       <c r="C300" s="5">
@@ -7944,10 +7953,10 @@
       </c>
     </row>
     <row r="301" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A301" s="17">
+      <c r="A301" s="18">
         <v>279</v>
       </c>
-      <c r="B301" s="17">
+      <c r="B301" s="18">
         <v>2</v>
       </c>
       <c r="C301" s="5">
@@ -7955,10 +7964,10 @@
       </c>
     </row>
     <row r="302" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A302" s="17">
+      <c r="A302" s="18">
         <v>280</v>
       </c>
-      <c r="B302" s="17">
+      <c r="B302" s="18">
         <v>2</v>
       </c>
       <c r="C302" s="5">
@@ -7966,10 +7975,10 @@
       </c>
     </row>
     <row r="303" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A303" s="17">
+      <c r="A303" s="18">
         <v>281</v>
       </c>
-      <c r="B303" s="17">
+      <c r="B303" s="18">
         <v>2</v>
       </c>
       <c r="C303" s="5">
@@ -7977,10 +7986,10 @@
       </c>
     </row>
     <row r="304" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A304" s="17">
+      <c r="A304" s="18">
         <v>282</v>
       </c>
-      <c r="B304" s="17">
+      <c r="B304" s="18">
         <v>2</v>
       </c>
       <c r="C304" s="5">
@@ -7988,10 +7997,10 @@
       </c>
     </row>
     <row r="305" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A305" s="17">
+      <c r="A305" s="18">
         <v>283</v>
       </c>
-      <c r="B305" s="17">
+      <c r="B305" s="18">
         <v>2</v>
       </c>
       <c r="C305" s="5">
@@ -7999,10 +8008,10 @@
       </c>
     </row>
     <row r="306" ht="15.75" spans="1:3">
-      <c r="A306" s="17">
+      <c r="A306" s="18">
         <v>284</v>
       </c>
-      <c r="B306" s="17">
+      <c r="B306" s="18">
         <v>2</v>
       </c>
       <c r="C306" s="5">
@@ -8010,10 +8019,10 @@
       </c>
     </row>
     <row r="307" ht="15.75" spans="1:3">
-      <c r="A307" s="17">
+      <c r="A307" s="18">
         <v>285</v>
       </c>
-      <c r="B307" s="17">
+      <c r="B307" s="18">
         <v>2</v>
       </c>
       <c r="C307" s="5">
@@ -8021,10 +8030,10 @@
       </c>
     </row>
     <row r="308" ht="15.75" spans="1:3">
-      <c r="A308" s="17">
+      <c r="A308" s="18">
         <v>286</v>
       </c>
-      <c r="B308" s="17">
+      <c r="B308" s="18">
         <v>2</v>
       </c>
       <c r="C308" s="5">
@@ -8032,10 +8041,10 @@
       </c>
     </row>
     <row r="309" ht="15.75" spans="1:3">
-      <c r="A309" s="17">
+      <c r="A309" s="18">
         <v>287</v>
       </c>
-      <c r="B309" s="17">
+      <c r="B309" s="18">
         <v>2</v>
       </c>
       <c r="C309" s="5">
@@ -8043,10 +8052,10 @@
       </c>
     </row>
     <row r="310" ht="15.75" spans="1:3">
-      <c r="A310" s="17">
+      <c r="A310" s="18">
         <v>288</v>
       </c>
-      <c r="B310" s="17">
+      <c r="B310" s="18">
         <v>2</v>
       </c>
       <c r="C310" s="5">
@@ -8054,10 +8063,10 @@
       </c>
     </row>
     <row r="311" ht="15.75" spans="1:3">
-      <c r="A311" s="17">
+      <c r="A311" s="18">
         <v>289</v>
       </c>
-      <c r="B311" s="17">
+      <c r="B311" s="18">
         <v>2</v>
       </c>
       <c r="C311" s="5">
@@ -8065,10 +8074,10 @@
       </c>
     </row>
     <row r="312" ht="15.75" spans="1:3">
-      <c r="A312" s="17">
+      <c r="A312" s="18">
         <v>290</v>
       </c>
-      <c r="B312" s="17">
+      <c r="B312" s="18">
         <v>2</v>
       </c>
       <c r="C312" s="5">
@@ -8076,10 +8085,10 @@
       </c>
     </row>
     <row r="313" ht="15.75" spans="1:3">
-      <c r="A313" s="17">
+      <c r="A313" s="18">
         <v>291</v>
       </c>
-      <c r="B313" s="17">
+      <c r="B313" s="18">
         <v>2</v>
       </c>
       <c r="C313" s="5">
@@ -8096,7 +8105,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J349"/>
+  <dimension ref="A1:Z350"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.6333333333333" style="3" customWidth="1"/>
@@ -17542,22 +17551,24 @@
     </row>
     <row r="346" spans="1:10">
       <c r="A346" s="5">
-        <v>25</v>
+        <v>2401</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>405</v>
       </c>
       <c r="C346" s="5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D346" s="5">
-        <v>25</v>
+        <v>2401</v>
       </c>
       <c r="E346" s="6"/>
       <c r="F346" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G346" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="G346" s="6" t="s">
+        <v>406</v>
+      </c>
       <c r="H346" s="6"/>
       <c r="I346" s="6" t="s">
         <v>405</v>
@@ -17566,59 +17577,57 @@
     </row>
     <row r="347" spans="1:10">
       <c r="A347" s="5">
-        <v>2501</v>
+        <v>25</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C347" s="5">
+        <v>2</v>
+      </c>
+      <c r="D347" s="5">
         <v>25</v>
-      </c>
-      <c r="D347" s="5">
-        <v>2501</v>
       </c>
       <c r="E347" s="6"/>
       <c r="F347" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G347" s="6" t="s">
-        <v>407</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G347" s="6"/>
       <c r="H347" s="6"/>
       <c r="I347" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J347" s="6"/>
     </row>
     <row r="348" spans="1:10">
       <c r="A348" s="5">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C348" s="5">
         <v>25</v>
       </c>
       <c r="D348" s="5">
-        <v>2502</v>
-      </c>
-      <c r="E348" s="5"/>
+        <v>2501</v>
+      </c>
+      <c r="E348" s="6"/>
       <c r="F348" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G348" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="H348" s="6"/>
+      <c r="I348" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="H348" s="5"/>
-      <c r="I348" s="6" t="s">
-        <v>409</v>
-      </c>
       <c r="J348" s="6"/>
     </row>
-    <row r="349" s="2" customFormat="1" spans="1:10">
+    <row r="349" spans="1:10">
       <c r="A349" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B349" s="6" t="s">
         <v>411</v>
@@ -17627,19 +17636,61 @@
         <v>25</v>
       </c>
       <c r="D349" s="5">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="E349" s="5"/>
       <c r="F349" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G349" s="6"/>
-      <c r="I349" s="2" t="s">
+      <c r="G349" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="H349" s="5"/>
+      <c r="I349" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="J349" s="2" t="b">
+      <c r="J349" s="6"/>
+    </row>
+    <row r="350" s="2" customFormat="1" spans="1:26">
+      <c r="A350" s="5">
+        <v>2503</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C350" s="5">
+        <v>25</v>
+      </c>
+      <c r="D350" s="5">
+        <v>2503</v>
+      </c>
+      <c r="E350" s="5"/>
+      <c r="F350" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G350" s="6"/>
+      <c r="I350" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J350" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="K350" s="1"/>
+      <c r="L350" s="1"/>
+      <c r="M350" s="1"/>
+      <c r="N350" s="1"/>
+      <c r="O350" s="1"/>
+      <c r="P350" s="1"/>
+      <c r="Q350" s="1"/>
+      <c r="R350" s="1"/>
+      <c r="S350" s="1"/>
+      <c r="T350" s="1"/>
+      <c r="U350" s="1"/>
+      <c r="V350" s="1"/>
+      <c r="W350" s="1"/>
+      <c r="X350" s="1"/>
+      <c r="Y350" s="1"/>
+      <c r="Z350" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1C4695-97F3-4BE5-B037-8D20615BD428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB62FEA-4B82-4628-85F6-180992696C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="421">
   <si>
     <t>Id</t>
   </si>
@@ -1358,6 +1358,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collection</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Collection.CollectionFocusAlignOpticsFocusWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collection Focus Align Optics Focus</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -7518,7 +7530,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z352"/>
+  <dimension ref="A1:Z354"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -16912,12 +16924,12 @@
       </c>
       <c r="J343" s="5"/>
     </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="4">
         <v>2305</v>
       </c>
-      <c r="B344" s="5" t="s">
-        <v>391</v>
+      <c r="B344" s="22" t="s">
+        <v>418</v>
       </c>
       <c r="C344" s="4">
         <v>23</v>
@@ -16929,19 +16941,19 @@
       <c r="F344" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G344" s="4"/>
-      <c r="H344" s="4"/>
-      <c r="I344" s="5" t="s">
-        <v>391</v>
+      <c r="G344" s="5"/>
+      <c r="H344" s="5"/>
+      <c r="I344" s="22" t="s">
+        <v>418</v>
       </c>
       <c r="J344" s="5"/>
     </row>
-    <row r="345" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="4">
         <v>23051</v>
       </c>
-      <c r="B345" s="5" t="s">
-        <v>392</v>
+      <c r="B345" s="22" t="s">
+        <v>420</v>
       </c>
       <c r="C345" s="4">
         <v>2305</v>
@@ -16953,94 +16965,94 @@
       <c r="F345" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G345" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="H345" s="4"/>
-      <c r="I345" s="5" t="s">
-        <v>392</v>
+      <c r="G345" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="H345" s="5"/>
+      <c r="I345" s="22" t="s">
+        <v>420</v>
       </c>
       <c r="J345" s="5"/>
     </row>
     <row r="346" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A346" s="4">
-        <v>23052</v>
+        <v>2306</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C346" s="4">
-        <v>2305</v>
+        <v>23</v>
       </c>
       <c r="D346" s="4">
-        <v>23052</v>
+        <v>2306</v>
       </c>
       <c r="E346" s="4"/>
       <c r="F346" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G346" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="H346" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G346" s="4"/>
+      <c r="H346" s="4"/>
       <c r="I346" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J346" s="5"/>
     </row>
     <row r="347" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A347" s="4">
-        <v>24</v>
+        <v>23061</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C347" s="4">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D347" s="4">
-        <v>24</v>
+        <v>23061</v>
       </c>
       <c r="E347" s="4"/>
       <c r="F347" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G347" s="5"/>
-      <c r="H347" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G347" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="H347" s="4"/>
       <c r="I347" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J347" s="5"/>
     </row>
     <row r="348" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A348" s="4">
-        <v>2401</v>
+        <v>23062</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C348" s="4">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="D348" s="4">
-        <v>2401</v>
-      </c>
-      <c r="E348" s="5"/>
+        <v>23062</v>
+      </c>
+      <c r="E348" s="4"/>
       <c r="F348" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G348" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H348" s="5"/>
       <c r="I348" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J348" s="5"/>
     </row>
     <row r="349" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A349" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B349" s="5" t="s">
         <v>399</v>
@@ -17049,7 +17061,7 @@
         <v>2</v>
       </c>
       <c r="D349" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E349" s="5"/>
       <c r="F349" s="4" t="s">
@@ -17064,16 +17076,16 @@
     </row>
     <row r="350" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A350" s="4">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B350" s="5" t="s">
         <v>400</v>
       </c>
       <c r="C350" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D350" s="4">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="E350" s="5"/>
       <c r="F350" s="4" t="s">
@@ -17090,16 +17102,16 @@
     </row>
     <row r="351" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A351" s="4">
-        <v>2502</v>
+        <v>2402</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>403</v>
       </c>
       <c r="C351" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D351" s="4">
-        <v>2502</v>
+        <v>2402</v>
       </c>
       <c r="E351" s="4"/>
       <c r="F351" s="4" t="s">
@@ -17116,16 +17128,16 @@
     </row>
     <row r="352" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A352" s="4">
-        <v>2503</v>
+        <v>2403</v>
       </c>
       <c r="B352" s="5" t="s">
         <v>405</v>
       </c>
       <c r="C352" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D352" s="4">
-        <v>2503</v>
+        <v>2403</v>
       </c>
       <c r="E352" s="4"/>
       <c r="F352" s="4" t="s">
@@ -17155,6 +17167,56 @@
       <c r="Y352"/>
       <c r="Z352" s="15"/>
     </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A353" s="4">
+        <v>25</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C353" s="4">
+        <v>2</v>
+      </c>
+      <c r="D353" s="4">
+        <v>25</v>
+      </c>
+      <c r="E353" s="4"/>
+      <c r="F353" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G353" s="5"/>
+      <c r="H353" s="5"/>
+      <c r="I353" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="J353" s="5"/>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A354" s="4">
+        <v>2501</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C354" s="4">
+        <v>25</v>
+      </c>
+      <c r="D354" s="4">
+        <v>2501</v>
+      </c>
+      <c r="E354" s="5"/>
+      <c r="F354" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G354" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="H354" s="5"/>
+      <c r="I354" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="J354" s="5"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB62FEA-4B82-4628-85F6-180992696C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A511B13B-D0A6-4B2F-8BA9-FB19EA2BF3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16796,12 +16796,12 @@
       </c>
       <c r="J338" s="5"/>
     </row>
-    <row r="339" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4">
         <v>2304</v>
       </c>
-      <c r="B339" s="5" t="s">
-        <v>380</v>
+      <c r="B339" s="22" t="s">
+        <v>418</v>
       </c>
       <c r="C339" s="4">
         <v>23</v>
@@ -16815,8 +16815,8 @@
       </c>
       <c r="G339" s="5"/>
       <c r="H339" s="5"/>
-      <c r="I339" s="5" t="s">
-        <v>380</v>
+      <c r="I339" s="22" t="s">
+        <v>418</v>
       </c>
       <c r="J339" s="5"/>
     </row>
@@ -16824,8 +16824,8 @@
       <c r="A340" s="4">
         <v>23041</v>
       </c>
-      <c r="B340" s="5" t="s">
-        <v>381</v>
+      <c r="B340" s="22" t="s">
+        <v>420</v>
       </c>
       <c r="C340" s="4">
         <v>2304</v>
@@ -16837,140 +16837,140 @@
       <c r="F340" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G340" s="5" t="s">
-        <v>382</v>
+      <c r="G340" s="22" t="s">
+        <v>419</v>
       </c>
       <c r="H340" s="5"/>
-      <c r="I340" s="5" t="s">
-        <v>381</v>
+      <c r="I340" s="22" t="s">
+        <v>420</v>
       </c>
       <c r="J340" s="5"/>
     </row>
     <row r="341" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A341" s="4">
-        <v>23042</v>
+        <v>2305</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C341" s="4">
-        <v>2304</v>
+        <v>23</v>
       </c>
       <c r="D341" s="4">
-        <v>23042</v>
+        <v>2305</v>
       </c>
       <c r="E341" s="4"/>
       <c r="F341" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G341" s="5" t="s">
-        <v>384</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G341" s="5"/>
       <c r="H341" s="5"/>
       <c r="I341" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J341" s="5"/>
     </row>
-    <row r="342" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4">
-        <v>23043</v>
+        <v>23051</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C342" s="4">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D342" s="4">
-        <v>23043</v>
+        <v>23051</v>
       </c>
       <c r="E342" s="4"/>
       <c r="F342" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G342" s="5" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H342" s="5"/>
       <c r="I342" s="5" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="J342" s="5"/>
     </row>
-    <row r="343" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>23044</v>
+        <v>23052</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C343" s="4">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D343" s="4">
-        <v>23044</v>
+        <v>23052</v>
       </c>
       <c r="E343" s="4"/>
       <c r="F343" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G343" s="5" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H343" s="5"/>
       <c r="I343" s="5" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="J343" s="5"/>
     </row>
-    <row r="344" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A344" s="4">
+        <v>23053</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C344" s="4">
         <v>2305</v>
       </c>
-      <c r="B344" s="22" t="s">
-        <v>418</v>
-      </c>
-      <c r="C344" s="4">
-        <v>23</v>
-      </c>
       <c r="D344" s="4">
-        <v>2305</v>
+        <v>23053</v>
       </c>
       <c r="E344" s="4"/>
       <c r="F344" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G344" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G344" s="5" t="s">
+        <v>386</v>
+      </c>
       <c r="H344" s="5"/>
-      <c r="I344" s="22" t="s">
-        <v>418</v>
+      <c r="I344" s="5" t="s">
+        <v>387</v>
       </c>
       <c r="J344" s="5"/>
     </row>
     <row r="345" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="4">
-        <v>23051</v>
-      </c>
-      <c r="B345" s="22" t="s">
-        <v>420</v>
+        <v>23054</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>388</v>
       </c>
       <c r="C345" s="4">
         <v>2305</v>
       </c>
       <c r="D345" s="4">
-        <v>23051</v>
+        <v>23054</v>
       </c>
       <c r="E345" s="4"/>
       <c r="F345" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G345" s="22" t="s">
-        <v>419</v>
+      <c r="G345" s="5" t="s">
+        <v>389</v>
       </c>
       <c r="H345" s="5"/>
-      <c r="I345" s="22" t="s">
-        <v>420</v>
+      <c r="I345" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="J345" s="5"/>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A511B13B-D0A6-4B2F-8BA9-FB19EA2BF3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA3E741-22F5-4E0A-8B1A-BD5D49CA2BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="406">
   <si>
     <t>Id</t>
   </si>
@@ -769,24 +769,6 @@
     <t>CugaCalibration.ViewModels.Chuck.ChuckRotateScaleCalibrationViewModel</t>
   </si>
   <si>
-    <t>Bright Stage Map</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Chuck.ChuckBrightFieldStageMapCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step0</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step0View</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step1View</t>
-  </si>
-  <si>
     <t>RowNumberNumeric</t>
   </si>
   <si>
@@ -797,33 +779,6 @@
   </si>
   <si>
     <t>RowCellHeightNumeric</t>
-  </si>
-  <si>
-    <t>WaferDiameterNumeric</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step2View</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step3</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step3View</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Review</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Review</t>
-  </si>
-  <si>
-    <t>Dark Stage Map</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Chuck.ChuckDarkFieldStageMapCalibrationViewModel</t>
   </si>
   <si>
     <t>Chuck Auto Focus</t>
@@ -7530,7 +7485,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z354"/>
+  <dimension ref="A1:Z334"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -13165,378 +13120,370 @@
     </row>
     <row r="203" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C203" s="4">
         <v>13</v>
       </c>
       <c r="D203" s="4">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H203" s="5"/>
       <c r="I203" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J203" s="5"/>
     </row>
-    <row r="204" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
-        <v>130601</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>244</v>
+        <v>1309</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C204" s="4">
-        <v>1306</v>
+        <v>13</v>
       </c>
       <c r="D204" s="4">
-        <v>130601</v>
+        <v>1309</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G204" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="H204" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I204" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="J204" s="5"/>
     </row>
     <row r="205" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
-        <v>130602</v>
+        <v>14</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C205" s="4">
-        <v>1306</v>
+        <v>1</v>
       </c>
       <c r="D205" s="4">
-        <v>130602</v>
+        <v>14</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G205" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="H205" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
       <c r="I205" s="5" t="s">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="J205" s="5"/>
     </row>
     <row r="206" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
-        <v>130603</v>
+        <v>1401</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C206" s="4">
-        <v>1306</v>
+        <v>14</v>
       </c>
       <c r="D206" s="4">
-        <v>130603</v>
+        <v>1401</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="H206" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="H206" s="5"/>
       <c r="I206" s="5" t="s">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="J206" s="5"/>
     </row>
     <row r="207" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
-        <v>130604</v>
+        <v>140101</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C207" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D207" s="4">
-        <v>130604</v>
+        <v>140101</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="J207" s="5"/>
     </row>
     <row r="208" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
-        <v>130605</v>
+        <v>140102</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C208" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D208" s="4">
-        <v>130605</v>
+        <v>140102</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>249</v>
+        <v>61</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>249</v>
+        <v>61</v>
       </c>
       <c r="J208" s="5"/>
     </row>
     <row r="209" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
-        <v>130606</v>
+        <v>140103</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C209" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D209" s="4">
-        <v>130606</v>
+        <v>140103</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="J209" s="5"/>
     </row>
     <row r="210" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
-        <v>130607</v>
+        <v>140104</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C210" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D210" s="4">
-        <v>130607</v>
+        <v>140104</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="J210" s="5"/>
     </row>
     <row r="211" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>130608</v>
+        <v>140105</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C211" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D211" s="4">
-        <v>130608</v>
+        <v>140105</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="J211" s="5"/>
     </row>
     <row r="212" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
-        <v>130609</v>
+        <v>140106</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C212" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D212" s="4">
-        <v>130609</v>
+        <v>140106</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="J212" s="5"/>
     </row>
     <row r="213" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
-        <v>130610</v>
+        <v>140107</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C213" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D213" s="4">
-        <v>130610</v>
+        <v>140107</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="J213" s="5"/>
     </row>
     <row r="214" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
-        <v>130611</v>
+        <v>140108</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C214" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D214" s="4">
-        <v>130611</v>
+        <v>140108</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="I214" s="5" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="J214" s="5"/>
     </row>
     <row r="215" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
-        <v>130612</v>
+        <v>140109</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C215" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D215" s="4">
-        <v>130612</v>
+        <v>140109</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>61</v>
+        <v>263</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>61</v>
+        <v>263</v>
       </c>
       <c r="J215" s="5"/>
     </row>
     <row r="216" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
-        <v>130613</v>
+        <v>140110</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>255</v>
       </c>
       <c r="C216" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D216" s="4">
-        <v>130613</v>
+        <v>140110</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
@@ -13555,16 +13502,16 @@
     </row>
     <row r="217" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
-        <v>130614</v>
+        <v>140111</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>255</v>
       </c>
       <c r="C217" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D217" s="4">
-        <v>130614</v>
+        <v>140111</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4" t="s">
@@ -13583,656 +13530,691 @@
     </row>
     <row r="218" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
-        <v>130615</v>
+        <v>140112</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C218" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D218" s="4">
-        <v>130615</v>
+        <v>140112</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="I218" s="5" t="s">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="J218" s="5"/>
     </row>
     <row r="219" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
-        <v>130616</v>
+        <v>140113</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C219" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D219" s="4">
-        <v>130616</v>
+        <v>140113</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I219" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J219" s="5"/>
     </row>
     <row r="220" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
-        <v>130617</v>
+        <v>1402</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C220" s="4">
-        <v>1306</v>
+        <v>14</v>
       </c>
       <c r="D220" s="4">
-        <v>130617</v>
+        <v>1402</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="H220" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="H220" s="5"/>
       <c r="I220" s="5" t="s">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="J220" s="5"/>
     </row>
     <row r="221" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
-        <v>1307</v>
+        <v>140201</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C221" s="4">
-        <v>13</v>
+        <v>1402</v>
       </c>
       <c r="D221" s="4">
-        <v>1307</v>
+        <v>140201</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="H221" s="5"/>
+        <v>269</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="I221" s="5" t="s">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="J221" s="5"/>
     </row>
     <row r="222" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>1308</v>
+        <v>140202</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C222" s="4">
-        <v>13</v>
+        <v>1402</v>
       </c>
       <c r="D222" s="4">
-        <v>1308</v>
+        <v>140202</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="H222" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="H222" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="I222" s="5" t="s">
-        <v>261</v>
+        <v>69</v>
       </c>
       <c r="J222" s="5"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
-        <v>1309</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>263</v>
+        <v>140203</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="C223" s="4">
-        <v>13</v>
+        <v>1402</v>
       </c>
       <c r="D223" s="4">
-        <v>1309</v>
+        <v>140203</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="H223" s="1"/>
-      <c r="I223" s="1" t="s">
-        <v>263</v>
+        <v>58</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H223" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I223" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="J223" s="5"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="4">
+        <v>140204</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C224" s="4">
+        <v>1402</v>
+      </c>
+      <c r="D224" s="4">
+        <v>140204</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H224" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I224" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="J224" s="5"/>
     </row>
     <row r="225" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
-        <v>14</v>
+        <v>140205</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C225" s="4">
-        <v>1</v>
+        <v>1402</v>
       </c>
       <c r="D225" s="4">
-        <v>14</v>
+        <v>140205</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G225" s="5"/>
-      <c r="H225" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H225" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="I225" s="5" t="s">
-        <v>265</v>
+        <v>69</v>
       </c>
       <c r="J225" s="5"/>
     </row>
     <row r="226" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
-        <v>1401</v>
+        <v>140206</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C226" s="4">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="D226" s="4">
-        <v>1401</v>
+        <v>140206</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="H226" s="5"/>
+        <v>273</v>
+      </c>
+      <c r="H226" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="I226" s="5" t="s">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c r="J226" s="5"/>
     </row>
     <row r="227" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
-        <v>140101</v>
+        <v>140207</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C227" s="4">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D227" s="4">
-        <v>140101</v>
+        <v>140207</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J227" s="5"/>
     </row>
     <row r="228" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
-        <v>140102</v>
+        <v>140208</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C228" s="4">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D228" s="4">
-        <v>140102</v>
+        <v>140208</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I228" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J228" s="5"/>
     </row>
     <row r="229" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
-        <v>140103</v>
+        <v>1403</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C229" s="4">
-        <v>1401</v>
+        <v>14</v>
       </c>
       <c r="D229" s="4">
-        <v>140103</v>
+        <v>1403</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="H229" s="5" t="s">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J229" s="5"/>
     </row>
     <row r="230" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
-        <v>140104</v>
+        <v>140301</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C230" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D230" s="4">
-        <v>140104</v>
+        <v>140301</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="J230" s="5"/>
     </row>
     <row r="231" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
-        <v>140105</v>
+        <v>140302</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C231" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D231" s="4">
-        <v>140105</v>
+        <v>140302</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="I231" s="5" t="s">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="J231" s="5"/>
     </row>
     <row r="232" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
-        <v>140106</v>
+        <v>140303</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C232" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D232" s="4">
-        <v>140106</v>
+        <v>140303</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I232" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J232" s="5"/>
     </row>
     <row r="233" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>140107</v>
+        <v>140304</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C233" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D233" s="4">
-        <v>140107</v>
+        <v>140304</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J233" s="5"/>
     </row>
     <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
-        <v>140108</v>
+        <v>140305</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C234" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D234" s="4">
-        <v>140108</v>
+        <v>140305</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="I234" s="5" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="J234" s="5"/>
     </row>
     <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
-        <v>140109</v>
+        <v>140306</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C235" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D235" s="4">
-        <v>140109</v>
+        <v>140306</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="I235" s="5" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="J235" s="5"/>
     </row>
     <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
-        <v>140110</v>
+        <v>140307</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C236" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D236" s="4">
-        <v>140110</v>
+        <v>140307</v>
       </c>
       <c r="E236" s="4"/>
       <c r="F236" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="I236" s="5" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="J236" s="5"/>
     </row>
     <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
-        <v>140111</v>
+        <v>140308</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C237" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D237" s="4">
-        <v>140111</v>
+        <v>140308</v>
       </c>
       <c r="E237" s="4"/>
       <c r="F237" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="I237" s="5" t="s">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="J237" s="5"/>
     </row>
     <row r="238" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
-        <v>140112</v>
+        <v>140309</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C238" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D238" s="4">
-        <v>140112</v>
+        <v>140309</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H238" s="5" t="s">
-        <v>64</v>
+        <v>282</v>
       </c>
       <c r="I238" s="5" t="s">
-        <v>64</v>
+        <v>282</v>
       </c>
       <c r="J238" s="5"/>
     </row>
     <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
-        <v>140113</v>
+        <v>140310</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C239" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D239" s="4">
-        <v>140113</v>
+        <v>140310</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>65</v>
+        <v>283</v>
       </c>
       <c r="I239" s="5" t="s">
-        <v>65</v>
+        <v>283</v>
       </c>
       <c r="J239" s="5"/>
     </row>
     <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>1402</v>
+        <v>140311</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C240" s="4">
-        <v>14</v>
+        <v>1403</v>
       </c>
       <c r="D240" s="4">
-        <v>1402</v>
+        <v>140311</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="H240" s="5"/>
+        <v>279</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="I240" s="5" t="s">
-        <v>281</v>
+        <v>64</v>
       </c>
       <c r="J240" s="5"/>
     </row>
     <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
-        <v>140201</v>
+        <v>140312</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C241" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D241" s="4">
-        <v>140201</v>
+        <v>140312</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I241" s="5" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J241" s="5"/>
     </row>
     <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
-        <v>140202</v>
+        <v>140313</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C242" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D242" s="4">
-        <v>140202</v>
+        <v>140313</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>69</v>
@@ -14244,23 +14226,23 @@
     </row>
     <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
-        <v>140203</v>
+        <v>140314</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C243" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D243" s="4">
-        <v>140203</v>
+        <v>140314</v>
       </c>
       <c r="E243" s="4"/>
       <c r="F243" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>64</v>
@@ -14272,23 +14254,23 @@
     </row>
     <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>140204</v>
+        <v>140315</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C244" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D244" s="4">
-        <v>140204</v>
+        <v>140315</v>
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H244" s="5" t="s">
         <v>65</v>
@@ -14300,51 +14282,49 @@
     </row>
     <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
-        <v>140205</v>
+        <v>1404</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C245" s="4">
-        <v>1402</v>
+        <v>14</v>
       </c>
       <c r="D245" s="4">
-        <v>140205</v>
+        <v>1404</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="H245" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="H245" s="5"/>
       <c r="I245" s="5" t="s">
-        <v>69</v>
+        <v>286</v>
       </c>
       <c r="J245" s="5"/>
     </row>
     <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>140206</v>
+        <v>140401</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C246" s="4">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D246" s="4">
-        <v>140206</v>
+        <v>140401</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>90</v>
@@ -14356,23 +14336,23 @@
     </row>
     <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>140207</v>
+        <v>140402</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C247" s="4">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D247" s="4">
-        <v>140207</v>
+        <v>140402</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>64</v>
@@ -14384,23 +14364,23 @@
     </row>
     <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
-        <v>140208</v>
+        <v>140403</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C248" s="4">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D248" s="4">
-        <v>140208</v>
+        <v>140403</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>65</v>
@@ -14412,378 +14392,345 @@
     </row>
     <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>1403</v>
+        <v>140404</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C249" s="4">
-        <v>14</v>
+        <v>1404</v>
       </c>
       <c r="D249" s="4">
-        <v>1403</v>
+        <v>140404</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="H249" s="5"/>
+        <v>291</v>
+      </c>
+      <c r="H249" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="I249" s="5" t="s">
-        <v>289</v>
+        <v>64</v>
       </c>
       <c r="J249" s="5"/>
     </row>
     <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
-        <v>140301</v>
+        <v>140405</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C250" s="4">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="D250" s="4">
-        <v>140301</v>
+        <v>140405</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G250" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H250" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I250" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J250" s="5"/>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A251" s="4">
+        <v>1405</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H250" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I250" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J250" s="5"/>
-    </row>
-    <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="4">
-        <v>140302</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>291</v>
-      </c>
       <c r="C251" s="4">
-        <v>1403</v>
+        <v>14</v>
       </c>
       <c r="D251" s="4">
-        <v>140302</v>
+        <v>1405</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G251" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H251" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I251" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
       <c r="J251" s="5"/>
     </row>
-    <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="4">
-        <v>140303</v>
-      </c>
-      <c r="B252" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C252" s="4">
-        <v>1403</v>
-      </c>
-      <c r="D252" s="4">
-        <v>140303</v>
-      </c>
-      <c r="E252" s="4"/>
-      <c r="F252" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G252" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="H252" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="I252" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="J252" s="5"/>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J252" s="13"/>
     </row>
     <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>140304</v>
+        <v>15</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C253" s="4">
-        <v>1403</v>
+        <v>1</v>
       </c>
       <c r="D253" s="4">
-        <v>140304</v>
+        <v>15</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G253" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G253" s="5"/>
+      <c r="H253" s="5"/>
+      <c r="I253" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I253" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="J253" s="5"/>
     </row>
     <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
-        <v>140305</v>
+        <v>1501</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C254" s="4">
-        <v>1403</v>
+        <v>15</v>
       </c>
       <c r="D254" s="4">
-        <v>140305</v>
+        <v>1501</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="H254" s="5" t="s">
-        <v>248</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="H254" s="5"/>
       <c r="I254" s="5" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="J254" s="5"/>
     </row>
     <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>140306</v>
+        <v>150101</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C255" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D255" s="4">
-        <v>140306</v>
+        <v>150101</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>249</v>
+        <v>60</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>249</v>
+        <v>60</v>
       </c>
       <c r="J255" s="5"/>
     </row>
     <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>140307</v>
+        <v>150102</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C256" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D256" s="4">
-        <v>140307</v>
+        <v>150102</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="I256" s="5" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="J256" s="5"/>
     </row>
     <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
-        <v>140308</v>
+        <v>150103</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C257" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D257" s="4">
-        <v>140308</v>
+        <v>150103</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="I257" s="5" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="J257" s="5"/>
     </row>
     <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>140309</v>
+        <v>150104</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C258" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D258" s="4">
-        <v>140309</v>
+        <v>150104</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I258" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J258" s="5"/>
     </row>
     <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>140310</v>
+        <v>150105</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C259" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D259" s="4">
-        <v>140310</v>
+        <v>150105</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I259" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J259" s="5"/>
     </row>
     <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>140311</v>
+        <v>150106</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C260" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D260" s="4">
-        <v>140311</v>
+        <v>150106</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>64</v>
+        <v>303</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>64</v>
+        <v>303</v>
       </c>
       <c r="J260" s="5"/>
     </row>
     <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
-        <v>140312</v>
+        <v>150107</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C261" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D261" s="4">
-        <v>140312</v>
+        <v>150107</v>
       </c>
       <c r="E261" s="4"/>
       <c r="F261" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>65</v>
+        <v>304</v>
       </c>
       <c r="I261" s="5" t="s">
-        <v>65</v>
+        <v>304</v>
       </c>
       <c r="J261" s="5"/>
     </row>
     <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>140313</v>
+        <v>150108</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C262" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D262" s="4">
-        <v>140313</v>
+        <v>150108</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
@@ -14793,25 +14740,25 @@
         <v>300</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>69</v>
+        <v>305</v>
       </c>
       <c r="I262" s="5" t="s">
-        <v>69</v>
+        <v>305</v>
       </c>
       <c r="J262" s="5"/>
     </row>
     <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
-        <v>140314</v>
+        <v>150109</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C263" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D263" s="4">
-        <v>140314</v>
+        <v>150109</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="4" t="s">
@@ -14830,16 +14777,16 @@
     </row>
     <row r="264" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
-        <v>140315</v>
+        <v>150110</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C264" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D264" s="4">
-        <v>140315</v>
+        <v>150110</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="4" t="s">
@@ -14858,266 +14805,273 @@
     </row>
     <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>1404</v>
+        <v>150111</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C265" s="4">
-        <v>14</v>
+        <v>1501</v>
       </c>
       <c r="D265" s="4">
-        <v>1404</v>
+        <v>150111</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G265" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="H265" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H265" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="I265" s="5" t="s">
-        <v>301</v>
+        <v>69</v>
       </c>
       <c r="J265" s="5"/>
     </row>
     <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>140401</v>
+        <v>150112</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C266" s="4">
-        <v>1404</v>
+        <v>1501</v>
       </c>
       <c r="D266" s="4">
-        <v>140401</v>
+        <v>150112</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G266" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H266" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="I266" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="J266" s="5"/>
     </row>
     <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>140402</v>
+        <v>150113</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C267" s="4">
-        <v>1404</v>
+        <v>1501</v>
       </c>
       <c r="D267" s="4">
-        <v>140402</v>
+        <v>150113</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J267" s="5"/>
     </row>
     <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
-        <v>140403</v>
+        <v>1502</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C268" s="4">
-        <v>1404</v>
+        <v>15</v>
       </c>
       <c r="D268" s="4">
-        <v>140403</v>
+        <v>1502</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="H268" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="J268" s="5"/>
     </row>
     <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>140404</v>
+        <v>1503</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C269" s="4">
-        <v>1404</v>
+        <v>15</v>
       </c>
       <c r="D269" s="4">
-        <v>140404</v>
+        <v>1503</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G269" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H269" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>64</v>
+        <v>310</v>
       </c>
       <c r="J269" s="5"/>
     </row>
     <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="4">
-        <v>140405</v>
-      </c>
-      <c r="B270" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C270" s="4">
-        <v>1404</v>
-      </c>
-      <c r="D270" s="4">
-        <v>140405</v>
-      </c>
-      <c r="E270" s="4"/>
-      <c r="F270" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G270" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H270" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I270" s="5" t="s">
-        <v>65</v>
+      <c r="A270" s="6">
+        <v>1504</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C270" s="6">
+        <v>15</v>
+      </c>
+      <c r="D270" s="6">
+        <v>1504</v>
+      </c>
+      <c r="E270" s="6"/>
+      <c r="F270" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G270" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H270" s="7"/>
+      <c r="I270" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="J270" s="5"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A271" s="4">
-        <v>1405</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C271" s="4">
-        <v>14</v>
-      </c>
-      <c r="D271" s="4">
-        <v>1405</v>
-      </c>
-      <c r="E271" s="4"/>
-      <c r="F271" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G271" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="H271" s="1"/>
-      <c r="I271" s="1"/>
+    <row r="271" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="8"/>
+      <c r="B271" s="9"/>
+      <c r="C271" s="10"/>
+      <c r="D271" s="10"/>
+      <c r="E271" s="10"/>
+      <c r="F271" s="10"/>
+      <c r="G271" s="9"/>
+      <c r="H271" s="9"/>
+      <c r="I271" s="14"/>
       <c r="J271" s="5"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J272" s="13"/>
+    <row r="272" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="11">
+        <v>16</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C272" s="11">
+        <v>1</v>
+      </c>
+      <c r="D272" s="11">
+        <v>16</v>
+      </c>
+      <c r="E272" s="11"/>
+      <c r="F272" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G272" s="12"/>
+      <c r="H272" s="12"/>
+      <c r="I272" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="J272" s="5"/>
     </row>
     <row r="273" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>15</v>
+        <v>1601</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C273" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D273" s="4">
-        <v>15</v>
+        <v>1601</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G273" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>316</v>
+      </c>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="J273" s="5"/>
     </row>
     <row r="274" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="C274" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D274" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="J274" s="5"/>
     </row>
     <row r="275" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
-        <v>150101</v>
+        <v>160201</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>312</v>
+        <v>146</v>
       </c>
       <c r="C275" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D275" s="4">
-        <v>150101</v>
+        <v>160201</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H275" s="5" t="s">
         <v>60</v>
@@ -15129,23 +15083,23 @@
     </row>
     <row r="276" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
-        <v>150102</v>
+        <v>160202</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>312</v>
+        <v>146</v>
       </c>
       <c r="C276" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D276" s="4">
-        <v>150102</v>
+        <v>160202</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H276" s="5" t="s">
         <v>61</v>
@@ -15157,1149 +15111,1127 @@
     </row>
     <row r="277" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>150103</v>
+        <v>160203</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="C277" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D277" s="4">
-        <v>150103</v>
+        <v>160203</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H277" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="I277" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="J277" s="5"/>
     </row>
     <row r="278" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>150104</v>
+        <v>160204</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="C278" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D278" s="4">
-        <v>150104</v>
+        <v>160204</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>316</v>
+        <v>64</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>316</v>
+        <v>64</v>
       </c>
       <c r="J278" s="5"/>
     </row>
     <row r="279" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
-        <v>150105</v>
+        <v>160205</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="C279" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D279" s="4">
-        <v>150105</v>
+        <v>160205</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>317</v>
+        <v>65</v>
       </c>
       <c r="I279" s="5" t="s">
-        <v>317</v>
+        <v>65</v>
       </c>
       <c r="J279" s="5"/>
     </row>
     <row r="280" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
-        <v>150106</v>
+        <v>160206</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="C280" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D280" s="4">
-        <v>150106</v>
+        <v>160206</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G280" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H280" s="5" t="s">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="I280" s="5" t="s">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="J280" s="5"/>
     </row>
     <row r="281" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
-        <v>150107</v>
+        <v>160207</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="C281" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D281" s="4">
-        <v>150107</v>
+        <v>160207</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H281" s="5" t="s">
-        <v>319</v>
+        <v>64</v>
       </c>
       <c r="I281" s="5" t="s">
-        <v>319</v>
+        <v>64</v>
       </c>
       <c r="J281" s="5"/>
     </row>
     <row r="282" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
-        <v>150108</v>
+        <v>160208</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="C282" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D282" s="4">
-        <v>150108</v>
+        <v>160208</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G282" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H282" s="5" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="I282" s="5" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="J282" s="5"/>
     </row>
     <row r="283" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
-        <v>150109</v>
+        <v>1603</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C283" s="4">
-        <v>1501</v>
+        <v>16</v>
       </c>
       <c r="D283" s="4">
-        <v>150109</v>
+        <v>1603</v>
       </c>
       <c r="E283" s="4"/>
       <c r="F283" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G283" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H283" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="H283" s="5"/>
       <c r="I283" s="5" t="s">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="J283" s="5"/>
     </row>
     <row r="284" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
-        <v>150110</v>
+        <v>160301</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C284" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D284" s="4">
-        <v>150110</v>
+        <v>160301</v>
       </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G284" s="5" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="H284" s="5" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="I284" s="5" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="J284" s="5"/>
     </row>
     <row r="285" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
-        <v>150111</v>
+        <v>160302</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C285" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D285" s="4">
-        <v>150111</v>
+        <v>160302</v>
       </c>
       <c r="E285" s="4"/>
       <c r="F285" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G285" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="J285" s="5"/>
     </row>
     <row r="286" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
-        <v>150112</v>
+        <v>160303</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C286" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D286" s="4">
-        <v>150112</v>
+        <v>160303</v>
       </c>
       <c r="E286" s="4"/>
       <c r="F286" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H286" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I286" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J286" s="5"/>
     </row>
     <row r="287" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
-        <v>150113</v>
+        <v>160304</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C287" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D287" s="4">
-        <v>150113</v>
+        <v>160304</v>
       </c>
       <c r="E287" s="4"/>
       <c r="F287" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H287" s="5" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="I287" s="5" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="J287" s="5"/>
     </row>
     <row r="288" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>1502</v>
+        <v>160305</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C288" s="4">
-        <v>15</v>
+        <v>1603</v>
       </c>
       <c r="D288" s="4">
-        <v>1502</v>
+        <v>160305</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="H288" s="5"/>
+        <v>327</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>329</v>
+      </c>
       <c r="I288" s="5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="J288" s="5"/>
     </row>
     <row r="289" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
-        <v>1503</v>
+        <v>160306</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C289" s="4">
-        <v>15</v>
+        <v>1603</v>
       </c>
       <c r="D289" s="4">
-        <v>1503</v>
+        <v>160306</v>
       </c>
       <c r="E289" s="4"/>
       <c r="F289" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G289" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H289" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I289" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J289" s="5"/>
+    </row>
+    <row r="290" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="4">
+        <v>160307</v>
+      </c>
+      <c r="B290" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="H289" s="5"/>
-      <c r="I289" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="J289" s="5"/>
-    </row>
-    <row r="290" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="6">
-        <v>1504</v>
-      </c>
-      <c r="B290" s="7" t="s">
+      <c r="C290" s="4">
+        <v>1603</v>
+      </c>
+      <c r="D290" s="4">
+        <v>160307</v>
+      </c>
+      <c r="E290" s="4"/>
+      <c r="F290" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G290" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C290" s="6">
-        <v>15</v>
-      </c>
-      <c r="D290" s="6">
-        <v>1504</v>
-      </c>
-      <c r="E290" s="6"/>
-      <c r="F290" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G290" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="H290" s="7"/>
-      <c r="I290" s="7" t="s">
-        <v>327</v>
+      <c r="H290" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I290" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="J290" s="5"/>
     </row>
-    <row r="291" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="8"/>
-      <c r="B291" s="9"/>
-      <c r="C291" s="10"/>
-      <c r="D291" s="10"/>
-      <c r="E291" s="10"/>
-      <c r="F291" s="10"/>
-      <c r="G291" s="9"/>
-      <c r="H291" s="9"/>
-      <c r="I291" s="14"/>
+    <row r="291" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="4">
+        <v>160308</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C291" s="4">
+        <v>1603</v>
+      </c>
+      <c r="D291" s="4">
+        <v>160308</v>
+      </c>
+      <c r="E291" s="4"/>
+      <c r="F291" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G291" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H291" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I291" s="5" t="s">
+        <v>161</v>
+      </c>
       <c r="J291" s="5"/>
     </row>
     <row r="292" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="11">
-        <v>16</v>
-      </c>
-      <c r="B292" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C292" s="11">
-        <v>1</v>
-      </c>
-      <c r="D292" s="11">
-        <v>16</v>
-      </c>
-      <c r="E292" s="11"/>
-      <c r="F292" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G292" s="12"/>
-      <c r="H292" s="12"/>
-      <c r="I292" s="12" t="s">
-        <v>329</v>
+      <c r="A292" s="4">
+        <v>160309</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C292" s="4">
+        <v>1603</v>
+      </c>
+      <c r="D292" s="4">
+        <v>160309</v>
+      </c>
+      <c r="E292" s="4"/>
+      <c r="F292" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G292" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H292" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I292" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="J292" s="5"/>
     </row>
     <row r="293" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>1601</v>
+        <v>160310</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>330</v>
       </c>
       <c r="C293" s="4">
-        <v>16</v>
+        <v>1603</v>
       </c>
       <c r="D293" s="4">
-        <v>1601</v>
+        <v>160310</v>
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G293" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="H293" s="5"/>
+      <c r="H293" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="I293" s="5" t="s">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="J293" s="5"/>
     </row>
     <row r="294" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>144</v>
+        <v>332</v>
       </c>
       <c r="C294" s="4">
         <v>16</v>
       </c>
       <c r="D294" s="4">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G294" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H294" s="5"/>
       <c r="I294" s="5" t="s">
-        <v>144</v>
+        <v>332</v>
       </c>
       <c r="J294" s="5"/>
     </row>
     <row r="295" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="4">
-        <v>160201</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C295" s="4">
-        <v>1602</v>
-      </c>
-      <c r="D295" s="4">
-        <v>160201</v>
-      </c>
-      <c r="E295" s="4"/>
-      <c r="F295" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G295" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="H295" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I295" s="5" t="s">
-        <v>60</v>
+      <c r="A295" s="6">
+        <v>1604</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C295" s="6">
+        <v>16</v>
+      </c>
+      <c r="D295" s="6">
+        <v>1604</v>
+      </c>
+      <c r="E295" s="6"/>
+      <c r="F295" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G295" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H295" s="7"/>
+      <c r="I295" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="J295" s="5"/>
     </row>
-    <row r="296" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
-        <v>160202</v>
-      </c>
-      <c r="B296" s="5" t="s">
-        <v>146</v>
+        <v>1605</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="C296" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D296" s="4">
-        <v>160202</v>
+        <v>1605</v>
       </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G296" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="H296" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I296" s="5" t="s">
-        <v>61</v>
+        <v>337</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="J296" s="5"/>
     </row>
-    <row r="297" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
-        <v>160203</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>148</v>
+        <v>1606</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="C297" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D297" s="4">
-        <v>160203</v>
+        <v>1606</v>
       </c>
       <c r="E297" s="4"/>
       <c r="F297" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G297" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H297" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="I297" s="5" t="s">
-        <v>335</v>
+        <v>55</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H297" s="1"/>
+      <c r="I297" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="J297" s="5"/>
     </row>
-    <row r="298" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
-        <v>160204</v>
-      </c>
-      <c r="B298" s="5" t="s">
-        <v>148</v>
+        <v>1607</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="C298" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D298" s="4">
-        <v>160204</v>
+        <v>1607</v>
       </c>
       <c r="E298" s="4"/>
       <c r="F298" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G298" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H298" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I298" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H298" s="1"/>
+      <c r="I298" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="J298" s="5"/>
     </row>
     <row r="299" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>160205</v>
+        <v>2</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>148</v>
+        <v>342</v>
       </c>
       <c r="C299" s="4">
-        <v>1602</v>
+        <v>-1</v>
       </c>
       <c r="D299" s="4">
-        <v>160205</v>
+        <v>2</v>
       </c>
       <c r="E299" s="4"/>
       <c r="F299" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G299" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H299" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G299" s="5"/>
+      <c r="H299" s="5"/>
       <c r="I299" s="5" t="s">
-        <v>65</v>
+        <v>342</v>
       </c>
       <c r="J299" s="5"/>
     </row>
     <row r="300" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
-        <v>160206</v>
+        <v>21</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>150</v>
+        <v>343</v>
       </c>
       <c r="C300" s="4">
-        <v>1602</v>
+        <v>2</v>
       </c>
       <c r="D300" s="4">
-        <v>160206</v>
+        <v>21</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G300" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="H300" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G300" s="5"/>
+      <c r="H300" s="5"/>
       <c r="I300" s="5" t="s">
-        <v>69</v>
+        <v>343</v>
       </c>
       <c r="J300" s="5"/>
     </row>
     <row r="301" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
-        <v>160207</v>
+        <v>2110</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>150</v>
+        <v>344</v>
       </c>
       <c r="C301" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D301" s="4">
-        <v>160207</v>
+        <v>2110</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G301" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="H301" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="H301" s="5"/>
       <c r="I301" s="5" t="s">
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="J301" s="5"/>
     </row>
     <row r="302" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
-        <v>160208</v>
+        <v>2111</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>150</v>
+        <v>346</v>
       </c>
       <c r="C302" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D302" s="4">
-        <v>160208</v>
+        <v>2111</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G302" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="H302" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
-        <v>65</v>
+        <v>346</v>
       </c>
       <c r="J302" s="5"/>
     </row>
     <row r="303" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C303" s="4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D303" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G303" s="5" t="s">
-        <v>338</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G303" s="5"/>
       <c r="H303" s="5"/>
       <c r="I303" s="5" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="J303" s="5"/>
     </row>
     <row r="304" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>160301</v>
+        <v>2201</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C304" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D304" s="4">
-        <v>160301</v>
+        <v>2201</v>
       </c>
       <c r="E304" s="4"/>
       <c r="F304" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G304" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H304" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="H304" s="5"/>
       <c r="I304" s="5" t="s">
-        <v>156</v>
+        <v>349</v>
       </c>
       <c r="J304" s="5"/>
     </row>
     <row r="305" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
-        <v>160302</v>
+        <v>2202</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C305" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D305" s="4">
-        <v>160302</v>
+        <v>2202</v>
       </c>
       <c r="E305" s="4"/>
       <c r="F305" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G305" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H305" s="5" t="s">
-        <v>60</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="H305" s="5"/>
       <c r="I305" s="5" t="s">
-        <v>60</v>
+        <v>351</v>
       </c>
       <c r="J305" s="5"/>
     </row>
     <row r="306" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
-        <v>160303</v>
+        <v>2203</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C306" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D306" s="4">
-        <v>160303</v>
+        <v>2203</v>
       </c>
       <c r="E306" s="4"/>
       <c r="F306" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G306" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H306" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="H306" s="5"/>
       <c r="I306" s="5" t="s">
-        <v>61</v>
+        <v>353</v>
       </c>
       <c r="J306" s="5"/>
     </row>
     <row r="307" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
-        <v>160304</v>
+        <v>23</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C307" s="4">
-        <v>1603</v>
+        <v>2</v>
       </c>
       <c r="D307" s="4">
-        <v>160304</v>
+        <v>23</v>
       </c>
       <c r="E307" s="4"/>
       <c r="F307" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G307" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H307" s="5" t="s">
-        <v>343</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G307" s="5"/>
+      <c r="H307" s="5"/>
       <c r="I307" s="5" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="J307" s="5"/>
     </row>
     <row r="308" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
-        <v>160305</v>
+        <v>2301</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="C308" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D308" s="4">
-        <v>160305</v>
+        <v>2301</v>
       </c>
       <c r="E308" s="4"/>
       <c r="F308" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G308" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H308" s="5" t="s">
-        <v>344</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="H308" s="5"/>
       <c r="I308" s="5" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="J308" s="5"/>
     </row>
     <row r="309" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
-        <v>160306</v>
+        <v>2302</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="C309" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D309" s="4">
-        <v>160306</v>
+        <v>2302</v>
       </c>
       <c r="E309" s="4"/>
       <c r="F309" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G309" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H309" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G309" s="5"/>
+      <c r="H309" s="5"/>
       <c r="I309" s="5" t="s">
-        <v>64</v>
+        <v>358</v>
       </c>
       <c r="J309" s="5"/>
     </row>
     <row r="310" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>160307</v>
+        <v>23021</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C310" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D310" s="4">
-        <v>160307</v>
+        <v>23021</v>
       </c>
       <c r="E310" s="4"/>
       <c r="F310" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G310" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H310" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="H310" s="5"/>
       <c r="I310" s="5" t="s">
-        <v>65</v>
+        <v>361</v>
       </c>
       <c r="J310" s="5"/>
     </row>
     <row r="311" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>160308</v>
+        <v>23022</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="C311" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D311" s="4">
-        <v>160308</v>
+        <v>23022</v>
       </c>
       <c r="E311" s="4"/>
       <c r="F311" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G311" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H311" s="5" t="s">
-        <v>161</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="H311" s="5"/>
       <c r="I311" s="5" t="s">
-        <v>161</v>
+        <v>364</v>
       </c>
       <c r="J311" s="5"/>
     </row>
     <row r="312" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
-        <v>160309</v>
+        <v>2303</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="C312" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D312" s="4">
-        <v>160309</v>
+        <v>2303</v>
       </c>
       <c r="E312" s="4"/>
       <c r="F312" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G312" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H312" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G312" s="5"/>
+      <c r="H312" s="5"/>
       <c r="I312" s="5" t="s">
-        <v>64</v>
+        <v>294</v>
       </c>
       <c r="J312" s="5"/>
     </row>
     <row r="313" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
-        <v>160310</v>
-      </c>
-      <c r="B313" s="5" t="s">
-        <v>345</v>
+        <v>23031</v>
+      </c>
+      <c r="B313" s="22" t="s">
+        <v>391</v>
       </c>
       <c r="C313" s="4">
-        <v>1603</v>
+        <v>2303</v>
       </c>
       <c r="D313" s="4">
-        <v>160310</v>
+        <v>23031</v>
       </c>
       <c r="E313" s="4"/>
       <c r="F313" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G313" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H313" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I313" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="G313" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="H313" s="5"/>
+      <c r="I313" s="22" t="s">
+        <v>391</v>
       </c>
       <c r="J313" s="5"/>
     </row>
     <row r="314" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
-        <v>1608</v>
-      </c>
-      <c r="B314" s="5" t="s">
-        <v>347</v>
+        <v>23032</v>
+      </c>
+      <c r="B314" s="22" t="s">
+        <v>393</v>
       </c>
       <c r="C314" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D314" s="4">
-        <v>1608</v>
+        <v>23032</v>
       </c>
       <c r="E314" s="4"/>
       <c r="F314" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G314" s="5" t="s">
-        <v>348</v>
+      <c r="G314" s="22" t="s">
+        <v>394</v>
       </c>
       <c r="H314" s="5"/>
-      <c r="I314" s="5" t="s">
-        <v>347</v>
+      <c r="I314" s="22" t="s">
+        <v>393</v>
       </c>
       <c r="J314" s="5"/>
     </row>
     <row r="315" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="6">
-        <v>1604</v>
-      </c>
-      <c r="B315" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C315" s="6">
-        <v>16</v>
-      </c>
-      <c r="D315" s="6">
-        <v>1604</v>
-      </c>
-      <c r="E315" s="6"/>
-      <c r="F315" s="6" t="s">
+      <c r="A315" s="4">
+        <v>23033</v>
+      </c>
+      <c r="B315" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="C315" s="4">
+        <v>2303</v>
+      </c>
+      <c r="D315" s="4">
+        <v>23033</v>
+      </c>
+      <c r="E315" s="4"/>
+      <c r="F315" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G315" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H315" s="7"/>
-      <c r="I315" s="7" t="s">
-        <v>349</v>
+      <c r="G315" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="H315" s="5"/>
+      <c r="I315" s="22" t="s">
+        <v>395</v>
       </c>
       <c r="J315" s="5"/>
     </row>
-    <row r="316" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>1605</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>351</v>
+        <v>23034</v>
+      </c>
+      <c r="B316" s="22" t="s">
+        <v>397</v>
       </c>
       <c r="C316" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D316" s="4">
-        <v>1605</v>
+        <v>23034</v>
       </c>
       <c r="E316" s="4"/>
       <c r="F316" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G316" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="I316" s="1" t="s">
-        <v>351</v>
+      <c r="G316" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="H316" s="5"/>
+      <c r="I316" s="22" t="s">
+        <v>397</v>
       </c>
       <c r="J316" s="5"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>1606</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>353</v>
+        <v>23035</v>
+      </c>
+      <c r="B317" s="22" t="s">
+        <v>399</v>
       </c>
       <c r="C317" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D317" s="4">
-        <v>1606</v>
+        <v>23035</v>
       </c>
       <c r="E317" s="4"/>
       <c r="F317" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G317" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H317" s="1"/>
-      <c r="I317" s="1" t="s">
-        <v>353</v>
+      <c r="G317" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="H317" s="5"/>
+      <c r="I317" s="22" t="s">
+        <v>399</v>
       </c>
       <c r="J317" s="5"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>1607</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>355</v>
+        <v>23036</v>
+      </c>
+      <c r="B318" s="22" t="s">
+        <v>401</v>
       </c>
       <c r="C318" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D318" s="4">
-        <v>1607</v>
+        <v>23036</v>
       </c>
       <c r="E318" s="4"/>
       <c r="F318" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G318" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="H318" s="1"/>
-      <c r="I318" s="1" t="s">
-        <v>355</v>
+      <c r="G318" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="H318" s="5"/>
+      <c r="I318" s="22" t="s">
+        <v>401</v>
       </c>
       <c r="J318" s="5"/>
     </row>
     <row r="319" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>2</v>
-      </c>
-      <c r="B319" s="5" t="s">
-        <v>357</v>
+        <v>2304</v>
+      </c>
+      <c r="B319" s="22" t="s">
+        <v>403</v>
       </c>
       <c r="C319" s="4">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="D319" s="4">
-        <v>2</v>
+        <v>2304</v>
       </c>
       <c r="E319" s="4"/>
       <c r="F319" s="4" t="s">
@@ -16307,915 +16239,407 @@
       </c>
       <c r="G319" s="5"/>
       <c r="H319" s="5"/>
-      <c r="I319" s="5" t="s">
-        <v>357</v>
+      <c r="I319" s="22" t="s">
+        <v>403</v>
       </c>
       <c r="J319" s="5"/>
     </row>
     <row r="320" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>21</v>
-      </c>
-      <c r="B320" s="5" t="s">
-        <v>358</v>
+        <v>23041</v>
+      </c>
+      <c r="B320" s="22" t="s">
+        <v>405</v>
       </c>
       <c r="C320" s="4">
-        <v>2</v>
+        <v>2304</v>
       </c>
       <c r="D320" s="4">
-        <v>21</v>
+        <v>23041</v>
       </c>
       <c r="E320" s="4"/>
       <c r="F320" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G320" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G320" s="22" t="s">
+        <v>404</v>
+      </c>
       <c r="H320" s="5"/>
-      <c r="I320" s="5" t="s">
-        <v>358</v>
+      <c r="I320" s="22" t="s">
+        <v>405</v>
       </c>
       <c r="J320" s="5"/>
     </row>
-    <row r="321" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>2110</v>
+        <v>2305</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C321" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D321" s="4">
-        <v>2110</v>
+        <v>2305</v>
       </c>
       <c r="E321" s="4"/>
       <c r="F321" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G321" s="5" t="s">
-        <v>360</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G321" s="5"/>
       <c r="H321" s="5"/>
       <c r="I321" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J321" s="5"/>
     </row>
-    <row r="322" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>2111</v>
+        <v>23051</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C322" s="4">
-        <v>21</v>
+        <v>2305</v>
       </c>
       <c r="D322" s="4">
-        <v>2111</v>
+        <v>23051</v>
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G322" s="5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H322" s="5"/>
       <c r="I322" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J322" s="5"/>
     </row>
-    <row r="323" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>22</v>
+        <v>23052</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C323" s="4">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D323" s="4">
-        <v>22</v>
+        <v>23052</v>
       </c>
       <c r="E323" s="4"/>
       <c r="F323" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G323" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G323" s="5" t="s">
+        <v>369</v>
+      </c>
       <c r="H323" s="5"/>
       <c r="I323" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J323" s="5"/>
     </row>
-    <row r="324" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>2201</v>
+        <v>23053</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C324" s="4">
-        <v>22</v>
+        <v>2305</v>
       </c>
       <c r="D324" s="4">
-        <v>2201</v>
+        <v>23053</v>
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G324" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H324" s="5"/>
       <c r="I324" s="5" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="J324" s="5"/>
     </row>
-    <row r="325" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>2202</v>
+        <v>23054</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C325" s="4">
-        <v>22</v>
+        <v>2305</v>
       </c>
       <c r="D325" s="4">
-        <v>2202</v>
+        <v>23054</v>
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G325" s="5" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="H325" s="5"/>
       <c r="I325" s="5" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="J325" s="5"/>
     </row>
-    <row r="326" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>2203</v>
+        <v>2306</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C326" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D326" s="4">
-        <v>2203</v>
+        <v>2306</v>
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G326" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="H326" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G326" s="4"/>
+      <c r="H326" s="4"/>
       <c r="I326" s="5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="J326" s="5"/>
     </row>
-    <row r="327" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>23</v>
+        <v>23061</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C327" s="4">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D327" s="4">
-        <v>23</v>
+        <v>23061</v>
       </c>
       <c r="E327" s="4"/>
       <c r="F327" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G327" s="5"/>
-      <c r="H327" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G327" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H327" s="4"/>
       <c r="I327" s="5" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="J327" s="5"/>
     </row>
-    <row r="328" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>2301</v>
+        <v>23062</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C328" s="4">
-        <v>23</v>
+        <v>2306</v>
       </c>
       <c r="D328" s="4">
-        <v>2301</v>
+        <v>23062</v>
       </c>
       <c r="E328" s="4"/>
       <c r="F328" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G328" s="5" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H328" s="5"/>
       <c r="I328" s="5" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="J328" s="5"/>
     </row>
-    <row r="329" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C329" s="4">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D329" s="4">
-        <v>2302</v>
-      </c>
-      <c r="E329" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E329" s="5"/>
       <c r="F329" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G329" s="5"/>
       <c r="H329" s="5"/>
       <c r="I329" s="5" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J329" s="5"/>
     </row>
-    <row r="330" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>23021</v>
+        <v>2401</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C330" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="D330" s="4">
-        <v>23021</v>
-      </c>
-      <c r="E330" s="4"/>
+        <v>2401</v>
+      </c>
+      <c r="E330" s="5"/>
       <c r="F330" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G330" s="5" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H330" s="5"/>
       <c r="I330" s="5" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="J330" s="5"/>
     </row>
-    <row r="331" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
-        <v>23022</v>
+        <v>2402</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C331" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="D331" s="4">
-        <v>23022</v>
+        <v>2402</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G331" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="H331" s="5"/>
+        <v>389</v>
+      </c>
+      <c r="H331" s="4"/>
       <c r="I331" s="5" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="J331" s="5"/>
     </row>
-    <row r="332" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>2303</v>
+        <v>2403</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>309</v>
+        <v>390</v>
       </c>
       <c r="C332" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D332" s="4">
-        <v>2303</v>
+        <v>2403</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G332" s="5"/>
-      <c r="H332" s="5"/>
-      <c r="I332" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="J332" s="5"/>
-    </row>
-    <row r="333" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I332" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J332" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K332"/>
+      <c r="L332"/>
+      <c r="M332"/>
+      <c r="N332"/>
+      <c r="O332"/>
+      <c r="P332"/>
+      <c r="Q332"/>
+      <c r="R332"/>
+      <c r="S332"/>
+      <c r="T332"/>
+      <c r="U332"/>
+      <c r="V332"/>
+      <c r="W332"/>
+      <c r="X332"/>
+      <c r="Y332"/>
+      <c r="Z332" s="15"/>
+    </row>
+    <row r="333" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
-        <v>23031</v>
-      </c>
-      <c r="B333" s="22" t="s">
-        <v>406</v>
+        <v>25</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="C333" s="4">
-        <v>2303</v>
+        <v>2</v>
       </c>
       <c r="D333" s="4">
-        <v>23031</v>
+        <v>25</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G333" s="22" t="s">
-        <v>407</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G333" s="5"/>
       <c r="H333" s="5"/>
-      <c r="I333" s="22" t="s">
-        <v>406</v>
+      <c r="I333" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="J333" s="5"/>
     </row>
-    <row r="334" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
-        <v>23032</v>
-      </c>
-      <c r="B334" s="22" t="s">
-        <v>408</v>
+        <v>2501</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="C334" s="4">
-        <v>2303</v>
+        <v>25</v>
       </c>
       <c r="D334" s="4">
-        <v>23032</v>
-      </c>
-      <c r="E334" s="4"/>
+        <v>2501</v>
+      </c>
+      <c r="E334" s="5"/>
       <c r="F334" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G334" s="22" t="s">
-        <v>409</v>
+      <c r="G334" s="5" t="s">
+        <v>383</v>
       </c>
       <c r="H334" s="5"/>
-      <c r="I334" s="22" t="s">
-        <v>408</v>
+      <c r="I334" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="J334" s="5"/>
-    </row>
-    <row r="335" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A335" s="4">
-        <v>23033</v>
-      </c>
-      <c r="B335" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="C335" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D335" s="4">
-        <v>23033</v>
-      </c>
-      <c r="E335" s="4"/>
-      <c r="F335" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G335" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="H335" s="5"/>
-      <c r="I335" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="J335" s="5"/>
-    </row>
-    <row r="336" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A336" s="4">
-        <v>23034</v>
-      </c>
-      <c r="B336" s="22" t="s">
-        <v>412</v>
-      </c>
-      <c r="C336" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D336" s="4">
-        <v>23034</v>
-      </c>
-      <c r="E336" s="4"/>
-      <c r="F336" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G336" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="H336" s="5"/>
-      <c r="I336" s="22" t="s">
-        <v>412</v>
-      </c>
-      <c r="J336" s="5"/>
-    </row>
-    <row r="337" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A337" s="4">
-        <v>23035</v>
-      </c>
-      <c r="B337" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="C337" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D337" s="4">
-        <v>23035</v>
-      </c>
-      <c r="E337" s="4"/>
-      <c r="F337" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G337" s="22" t="s">
-        <v>415</v>
-      </c>
-      <c r="H337" s="5"/>
-      <c r="I337" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="J337" s="5"/>
-    </row>
-    <row r="338" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A338" s="4">
-        <v>23036</v>
-      </c>
-      <c r="B338" s="22" t="s">
-        <v>416</v>
-      </c>
-      <c r="C338" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D338" s="4">
-        <v>23036</v>
-      </c>
-      <c r="E338" s="4"/>
-      <c r="F338" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G338" s="22" t="s">
-        <v>417</v>
-      </c>
-      <c r="H338" s="5"/>
-      <c r="I338" s="22" t="s">
-        <v>416</v>
-      </c>
-      <c r="J338" s="5"/>
-    </row>
-    <row r="339" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A339" s="4">
-        <v>2304</v>
-      </c>
-      <c r="B339" s="22" t="s">
-        <v>418</v>
-      </c>
-      <c r="C339" s="4">
-        <v>23</v>
-      </c>
-      <c r="D339" s="4">
-        <v>2304</v>
-      </c>
-      <c r="E339" s="4"/>
-      <c r="F339" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G339" s="5"/>
-      <c r="H339" s="5"/>
-      <c r="I339" s="22" t="s">
-        <v>418</v>
-      </c>
-      <c r="J339" s="5"/>
-    </row>
-    <row r="340" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A340" s="4">
-        <v>23041</v>
-      </c>
-      <c r="B340" s="22" t="s">
-        <v>420</v>
-      </c>
-      <c r="C340" s="4">
-        <v>2304</v>
-      </c>
-      <c r="D340" s="4">
-        <v>23041</v>
-      </c>
-      <c r="E340" s="4"/>
-      <c r="F340" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G340" s="22" t="s">
-        <v>419</v>
-      </c>
-      <c r="H340" s="5"/>
-      <c r="I340" s="22" t="s">
-        <v>420</v>
-      </c>
-      <c r="J340" s="5"/>
-    </row>
-    <row r="341" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A341" s="4">
-        <v>2305</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="C341" s="4">
-        <v>23</v>
-      </c>
-      <c r="D341" s="4">
-        <v>2305</v>
-      </c>
-      <c r="E341" s="4"/>
-      <c r="F341" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G341" s="5"/>
-      <c r="H341" s="5"/>
-      <c r="I341" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="J341" s="5"/>
-    </row>
-    <row r="342" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A342" s="4">
-        <v>23051</v>
-      </c>
-      <c r="B342" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C342" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D342" s="4">
-        <v>23051</v>
-      </c>
-      <c r="E342" s="4"/>
-      <c r="F342" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G342" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="H342" s="5"/>
-      <c r="I342" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="J342" s="5"/>
-    </row>
-    <row r="343" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A343" s="4">
-        <v>23052</v>
-      </c>
-      <c r="B343" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C343" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D343" s="4">
-        <v>23052</v>
-      </c>
-      <c r="E343" s="4"/>
-      <c r="F343" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G343" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="H343" s="5"/>
-      <c r="I343" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="J343" s="5"/>
-    </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A344" s="4">
-        <v>23053</v>
-      </c>
-      <c r="B344" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C344" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D344" s="4">
-        <v>23053</v>
-      </c>
-      <c r="E344" s="4"/>
-      <c r="F344" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G344" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="H344" s="5"/>
-      <c r="I344" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="J344" s="5"/>
-    </row>
-    <row r="345" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A345" s="4">
-        <v>23054</v>
-      </c>
-      <c r="B345" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C345" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D345" s="4">
-        <v>23054</v>
-      </c>
-      <c r="E345" s="4"/>
-      <c r="F345" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G345" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="H345" s="5"/>
-      <c r="I345" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="J345" s="5"/>
-    </row>
-    <row r="346" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A346" s="4">
-        <v>2306</v>
-      </c>
-      <c r="B346" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C346" s="4">
-        <v>23</v>
-      </c>
-      <c r="D346" s="4">
-        <v>2306</v>
-      </c>
-      <c r="E346" s="4"/>
-      <c r="F346" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G346" s="4"/>
-      <c r="H346" s="4"/>
-      <c r="I346" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="J346" s="5"/>
-    </row>
-    <row r="347" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A347" s="4">
-        <v>23061</v>
-      </c>
-      <c r="B347" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C347" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D347" s="4">
-        <v>23061</v>
-      </c>
-      <c r="E347" s="4"/>
-      <c r="F347" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G347" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="H347" s="4"/>
-      <c r="I347" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="J347" s="5"/>
-    </row>
-    <row r="348" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A348" s="4">
-        <v>23062</v>
-      </c>
-      <c r="B348" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="C348" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D348" s="4">
-        <v>23062</v>
-      </c>
-      <c r="E348" s="4"/>
-      <c r="F348" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G348" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="H348" s="5"/>
-      <c r="I348" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="J348" s="5"/>
-    </row>
-    <row r="349" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A349" s="4">
-        <v>24</v>
-      </c>
-      <c r="B349" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C349" s="4">
-        <v>2</v>
-      </c>
-      <c r="D349" s="4">
-        <v>24</v>
-      </c>
-      <c r="E349" s="5"/>
-      <c r="F349" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G349" s="5"/>
-      <c r="H349" s="5"/>
-      <c r="I349" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="J349" s="5"/>
-    </row>
-    <row r="350" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A350" s="4">
-        <v>2401</v>
-      </c>
-      <c r="B350" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C350" s="4">
-        <v>24</v>
-      </c>
-      <c r="D350" s="4">
-        <v>2401</v>
-      </c>
-      <c r="E350" s="5"/>
-      <c r="F350" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G350" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="H350" s="5"/>
-      <c r="I350" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="J350" s="5"/>
-    </row>
-    <row r="351" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A351" s="4">
-        <v>2402</v>
-      </c>
-      <c r="B351" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C351" s="4">
-        <v>24</v>
-      </c>
-      <c r="D351" s="4">
-        <v>2402</v>
-      </c>
-      <c r="E351" s="4"/>
-      <c r="F351" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G351" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="H351" s="4"/>
-      <c r="I351" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="J351" s="5"/>
-    </row>
-    <row r="352" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A352" s="4">
-        <v>2403</v>
-      </c>
-      <c r="B352" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="C352" s="4">
-        <v>24</v>
-      </c>
-      <c r="D352" s="4">
-        <v>2403</v>
-      </c>
-      <c r="E352" s="4"/>
-      <c r="F352" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G352" s="5"/>
-      <c r="I352" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="J352" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K352"/>
-      <c r="L352"/>
-      <c r="M352"/>
-      <c r="N352"/>
-      <c r="O352"/>
-      <c r="P352"/>
-      <c r="Q352"/>
-      <c r="R352"/>
-      <c r="S352"/>
-      <c r="T352"/>
-      <c r="U352"/>
-      <c r="V352"/>
-      <c r="W352"/>
-      <c r="X352"/>
-      <c r="Y352"/>
-      <c r="Z352" s="15"/>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A353" s="4">
-        <v>25</v>
-      </c>
-      <c r="B353" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="C353" s="4">
-        <v>2</v>
-      </c>
-      <c r="D353" s="4">
-        <v>25</v>
-      </c>
-      <c r="E353" s="4"/>
-      <c r="F353" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G353" s="5"/>
-      <c r="H353" s="5"/>
-      <c r="I353" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="J353" s="5"/>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A354" s="4">
-        <v>2501</v>
-      </c>
-      <c r="B354" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C354" s="4">
-        <v>25</v>
-      </c>
-      <c r="D354" s="4">
-        <v>2501</v>
-      </c>
-      <c r="E354" s="5"/>
-      <c r="F354" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G354" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="H354" s="5"/>
-      <c r="I354" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="J354" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1C4695-97F3-4BE5-B037-8D20615BD428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA3E741-22F5-4E0A-8B1A-BD5D49CA2BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="406">
   <si>
     <t>Id</t>
   </si>
@@ -769,24 +769,6 @@
     <t>CugaCalibration.ViewModels.Chuck.ChuckRotateScaleCalibrationViewModel</t>
   </si>
   <si>
-    <t>Bright Stage Map</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Chuck.ChuckBrightFieldStageMapCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step0</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step0View</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step1View</t>
-  </si>
-  <si>
     <t>RowNumberNumeric</t>
   </si>
   <si>
@@ -797,33 +779,6 @@
   </si>
   <si>
     <t>RowCellHeightNumeric</t>
-  </si>
-  <si>
-    <t>WaferDiameterNumeric</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step2View</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Step3</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Step3View</t>
-  </si>
-  <si>
-    <t>Bright Stage Map-Review</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Chuck.BrightFieldStageMap.Children.Review</t>
-  </si>
-  <si>
-    <t>Dark Stage Map</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Chuck.ChuckDarkFieldStageMapCalibrationViewModel</t>
   </si>
   <si>
     <t>Chuck Auto Focus</t>
@@ -1358,6 +1313,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collection</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Collection.CollectionFocusAlignOpticsFocusWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collection Focus Align Optics Focus</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -7518,7 +7485,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z352"/>
+  <dimension ref="A1:Z334"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -13153,378 +13120,370 @@
     </row>
     <row r="203" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C203" s="4">
         <v>13</v>
       </c>
       <c r="D203" s="4">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H203" s="5"/>
       <c r="I203" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J203" s="5"/>
     </row>
-    <row r="204" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
-        <v>130601</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>244</v>
+        <v>1309</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C204" s="4">
-        <v>1306</v>
+        <v>13</v>
       </c>
       <c r="D204" s="4">
-        <v>130601</v>
+        <v>1309</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G204" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="H204" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I204" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="J204" s="5"/>
     </row>
     <row r="205" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
-        <v>130602</v>
+        <v>14</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C205" s="4">
-        <v>1306</v>
+        <v>1</v>
       </c>
       <c r="D205" s="4">
-        <v>130602</v>
+        <v>14</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G205" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="H205" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
       <c r="I205" s="5" t="s">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="J205" s="5"/>
     </row>
     <row r="206" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
-        <v>130603</v>
+        <v>1401</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C206" s="4">
-        <v>1306</v>
+        <v>14</v>
       </c>
       <c r="D206" s="4">
-        <v>130603</v>
+        <v>1401</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="H206" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="H206" s="5"/>
       <c r="I206" s="5" t="s">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="J206" s="5"/>
     </row>
     <row r="207" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
-        <v>130604</v>
+        <v>140101</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C207" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D207" s="4">
-        <v>130604</v>
+        <v>140101</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="J207" s="5"/>
     </row>
     <row r="208" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
-        <v>130605</v>
+        <v>140102</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C208" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D208" s="4">
-        <v>130605</v>
+        <v>140102</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>249</v>
+        <v>61</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>249</v>
+        <v>61</v>
       </c>
       <c r="J208" s="5"/>
     </row>
     <row r="209" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
-        <v>130606</v>
+        <v>140103</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C209" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D209" s="4">
-        <v>130606</v>
+        <v>140103</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="J209" s="5"/>
     </row>
     <row r="210" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
-        <v>130607</v>
+        <v>140104</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C210" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D210" s="4">
-        <v>130607</v>
+        <v>140104</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="J210" s="5"/>
     </row>
     <row r="211" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>130608</v>
+        <v>140105</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C211" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D211" s="4">
-        <v>130608</v>
+        <v>140105</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="J211" s="5"/>
     </row>
     <row r="212" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
-        <v>130609</v>
+        <v>140106</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C212" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D212" s="4">
-        <v>130609</v>
+        <v>140106</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="J212" s="5"/>
     </row>
     <row r="213" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
-        <v>130610</v>
+        <v>140107</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C213" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D213" s="4">
-        <v>130610</v>
+        <v>140107</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="J213" s="5"/>
     </row>
     <row r="214" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
-        <v>130611</v>
+        <v>140108</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C214" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D214" s="4">
-        <v>130611</v>
+        <v>140108</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="I214" s="5" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="J214" s="5"/>
     </row>
     <row r="215" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
-        <v>130612</v>
+        <v>140109</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C215" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D215" s="4">
-        <v>130612</v>
+        <v>140109</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>61</v>
+        <v>263</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>61</v>
+        <v>263</v>
       </c>
       <c r="J215" s="5"/>
     </row>
     <row r="216" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
-        <v>130613</v>
+        <v>140110</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>255</v>
       </c>
       <c r="C216" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D216" s="4">
-        <v>130613</v>
+        <v>140110</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
@@ -13543,16 +13502,16 @@
     </row>
     <row r="217" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
-        <v>130614</v>
+        <v>140111</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>255</v>
       </c>
       <c r="C217" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D217" s="4">
-        <v>130614</v>
+        <v>140111</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4" t="s">
@@ -13571,656 +13530,691 @@
     </row>
     <row r="218" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
-        <v>130615</v>
+        <v>140112</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C218" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D218" s="4">
-        <v>130615</v>
+        <v>140112</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="I218" s="5" t="s">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="J218" s="5"/>
     </row>
     <row r="219" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
-        <v>130616</v>
+        <v>140113</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C219" s="4">
-        <v>1306</v>
+        <v>1401</v>
       </c>
       <c r="D219" s="4">
-        <v>130616</v>
+        <v>140113</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I219" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J219" s="5"/>
     </row>
     <row r="220" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
-        <v>130617</v>
+        <v>1402</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C220" s="4">
-        <v>1306</v>
+        <v>14</v>
       </c>
       <c r="D220" s="4">
-        <v>130617</v>
+        <v>1402</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="H220" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="H220" s="5"/>
       <c r="I220" s="5" t="s">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="J220" s="5"/>
     </row>
     <row r="221" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
-        <v>1307</v>
+        <v>140201</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C221" s="4">
-        <v>13</v>
+        <v>1402</v>
       </c>
       <c r="D221" s="4">
-        <v>1307</v>
+        <v>140201</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="H221" s="5"/>
+        <v>269</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="I221" s="5" t="s">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="J221" s="5"/>
     </row>
     <row r="222" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>1308</v>
+        <v>140202</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C222" s="4">
-        <v>13</v>
+        <v>1402</v>
       </c>
       <c r="D222" s="4">
-        <v>1308</v>
+        <v>140202</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="H222" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="H222" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="I222" s="5" t="s">
-        <v>261</v>
+        <v>69</v>
       </c>
       <c r="J222" s="5"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
-        <v>1309</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>263</v>
+        <v>140203</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="C223" s="4">
-        <v>13</v>
+        <v>1402</v>
       </c>
       <c r="D223" s="4">
-        <v>1309</v>
+        <v>140203</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="H223" s="1"/>
-      <c r="I223" s="1" t="s">
-        <v>263</v>
+        <v>58</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H223" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I223" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="J223" s="5"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="4">
+        <v>140204</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C224" s="4">
+        <v>1402</v>
+      </c>
+      <c r="D224" s="4">
+        <v>140204</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H224" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I224" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="J224" s="5"/>
     </row>
     <row r="225" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
-        <v>14</v>
+        <v>140205</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C225" s="4">
-        <v>1</v>
+        <v>1402</v>
       </c>
       <c r="D225" s="4">
-        <v>14</v>
+        <v>140205</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G225" s="5"/>
-      <c r="H225" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H225" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="I225" s="5" t="s">
-        <v>265</v>
+        <v>69</v>
       </c>
       <c r="J225" s="5"/>
     </row>
     <row r="226" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
-        <v>1401</v>
+        <v>140206</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C226" s="4">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="D226" s="4">
-        <v>1401</v>
+        <v>140206</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="H226" s="5"/>
+        <v>273</v>
+      </c>
+      <c r="H226" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="I226" s="5" t="s">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c r="J226" s="5"/>
     </row>
     <row r="227" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
-        <v>140101</v>
+        <v>140207</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C227" s="4">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D227" s="4">
-        <v>140101</v>
+        <v>140207</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J227" s="5"/>
     </row>
     <row r="228" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
-        <v>140102</v>
+        <v>140208</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C228" s="4">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D228" s="4">
-        <v>140102</v>
+        <v>140208</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I228" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J228" s="5"/>
     </row>
     <row r="229" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
-        <v>140103</v>
+        <v>1403</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C229" s="4">
-        <v>1401</v>
+        <v>14</v>
       </c>
       <c r="D229" s="4">
-        <v>140103</v>
+        <v>1403</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="H229" s="5" t="s">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J229" s="5"/>
     </row>
     <row r="230" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
-        <v>140104</v>
+        <v>140301</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C230" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D230" s="4">
-        <v>140104</v>
+        <v>140301</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="J230" s="5"/>
     </row>
     <row r="231" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
-        <v>140105</v>
+        <v>140302</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C231" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D231" s="4">
-        <v>140105</v>
+        <v>140302</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="I231" s="5" t="s">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="J231" s="5"/>
     </row>
     <row r="232" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
-        <v>140106</v>
+        <v>140303</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C232" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D232" s="4">
-        <v>140106</v>
+        <v>140303</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I232" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J232" s="5"/>
     </row>
     <row r="233" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>140107</v>
+        <v>140304</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C233" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D233" s="4">
-        <v>140107</v>
+        <v>140304</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J233" s="5"/>
     </row>
     <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
-        <v>140108</v>
+        <v>140305</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C234" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D234" s="4">
-        <v>140108</v>
+        <v>140305</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="I234" s="5" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="J234" s="5"/>
     </row>
     <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
-        <v>140109</v>
+        <v>140306</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C235" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D235" s="4">
-        <v>140109</v>
+        <v>140306</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="I235" s="5" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="J235" s="5"/>
     </row>
     <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
-        <v>140110</v>
+        <v>140307</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C236" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D236" s="4">
-        <v>140110</v>
+        <v>140307</v>
       </c>
       <c r="E236" s="4"/>
       <c r="F236" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="I236" s="5" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="J236" s="5"/>
     </row>
     <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
-        <v>140111</v>
+        <v>140308</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C237" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D237" s="4">
-        <v>140111</v>
+        <v>140308</v>
       </c>
       <c r="E237" s="4"/>
       <c r="F237" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="I237" s="5" t="s">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="J237" s="5"/>
     </row>
     <row r="238" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
-        <v>140112</v>
+        <v>140309</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C238" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D238" s="4">
-        <v>140112</v>
+        <v>140309</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H238" s="5" t="s">
-        <v>64</v>
+        <v>282</v>
       </c>
       <c r="I238" s="5" t="s">
-        <v>64</v>
+        <v>282</v>
       </c>
       <c r="J238" s="5"/>
     </row>
     <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
-        <v>140113</v>
+        <v>140310</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C239" s="4">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D239" s="4">
-        <v>140113</v>
+        <v>140310</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>65</v>
+        <v>283</v>
       </c>
       <c r="I239" s="5" t="s">
-        <v>65</v>
+        <v>283</v>
       </c>
       <c r="J239" s="5"/>
     </row>
     <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>1402</v>
+        <v>140311</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C240" s="4">
-        <v>14</v>
+        <v>1403</v>
       </c>
       <c r="D240" s="4">
-        <v>1402</v>
+        <v>140311</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="H240" s="5"/>
+        <v>279</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="I240" s="5" t="s">
-        <v>281</v>
+        <v>64</v>
       </c>
       <c r="J240" s="5"/>
     </row>
     <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
-        <v>140201</v>
+        <v>140312</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C241" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D241" s="4">
-        <v>140201</v>
+        <v>140312</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I241" s="5" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J241" s="5"/>
     </row>
     <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
-        <v>140202</v>
+        <v>140313</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C242" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D242" s="4">
-        <v>140202</v>
+        <v>140313</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>69</v>
@@ -14232,23 +14226,23 @@
     </row>
     <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
-        <v>140203</v>
+        <v>140314</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C243" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D243" s="4">
-        <v>140203</v>
+        <v>140314</v>
       </c>
       <c r="E243" s="4"/>
       <c r="F243" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>64</v>
@@ -14260,23 +14254,23 @@
     </row>
     <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>140204</v>
+        <v>140315</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C244" s="4">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D244" s="4">
-        <v>140204</v>
+        <v>140315</v>
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H244" s="5" t="s">
         <v>65</v>
@@ -14288,51 +14282,49 @@
     </row>
     <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
-        <v>140205</v>
+        <v>1404</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C245" s="4">
-        <v>1402</v>
+        <v>14</v>
       </c>
       <c r="D245" s="4">
-        <v>140205</v>
+        <v>1404</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="H245" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="H245" s="5"/>
       <c r="I245" s="5" t="s">
-        <v>69</v>
+        <v>286</v>
       </c>
       <c r="J245" s="5"/>
     </row>
     <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>140206</v>
+        <v>140401</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C246" s="4">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D246" s="4">
-        <v>140206</v>
+        <v>140401</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>90</v>
@@ -14344,23 +14336,23 @@
     </row>
     <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>140207</v>
+        <v>140402</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C247" s="4">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D247" s="4">
-        <v>140207</v>
+        <v>140402</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>64</v>
@@ -14372,23 +14364,23 @@
     </row>
     <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
-        <v>140208</v>
+        <v>140403</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C248" s="4">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D248" s="4">
-        <v>140208</v>
+        <v>140403</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>65</v>
@@ -14400,378 +14392,345 @@
     </row>
     <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>1403</v>
+        <v>140404</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C249" s="4">
-        <v>14</v>
+        <v>1404</v>
       </c>
       <c r="D249" s="4">
-        <v>1403</v>
+        <v>140404</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="H249" s="5"/>
+        <v>291</v>
+      </c>
+      <c r="H249" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="I249" s="5" t="s">
-        <v>289</v>
+        <v>64</v>
       </c>
       <c r="J249" s="5"/>
     </row>
     <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
-        <v>140301</v>
+        <v>140405</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C250" s="4">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="D250" s="4">
-        <v>140301</v>
+        <v>140405</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G250" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H250" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I250" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J250" s="5"/>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A251" s="4">
+        <v>1405</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H250" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I250" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J250" s="5"/>
-    </row>
-    <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="4">
-        <v>140302</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>291</v>
-      </c>
       <c r="C251" s="4">
-        <v>1403</v>
+        <v>14</v>
       </c>
       <c r="D251" s="4">
-        <v>140302</v>
+        <v>1405</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G251" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H251" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I251" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
       <c r="J251" s="5"/>
     </row>
-    <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="4">
-        <v>140303</v>
-      </c>
-      <c r="B252" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C252" s="4">
-        <v>1403</v>
-      </c>
-      <c r="D252" s="4">
-        <v>140303</v>
-      </c>
-      <c r="E252" s="4"/>
-      <c r="F252" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G252" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="H252" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="I252" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="J252" s="5"/>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J252" s="13"/>
     </row>
     <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>140304</v>
+        <v>15</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C253" s="4">
-        <v>1403</v>
+        <v>1</v>
       </c>
       <c r="D253" s="4">
-        <v>140304</v>
+        <v>15</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G253" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G253" s="5"/>
+      <c r="H253" s="5"/>
+      <c r="I253" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I253" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="J253" s="5"/>
     </row>
     <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
-        <v>140305</v>
+        <v>1501</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C254" s="4">
-        <v>1403</v>
+        <v>15</v>
       </c>
       <c r="D254" s="4">
-        <v>140305</v>
+        <v>1501</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="H254" s="5" t="s">
-        <v>248</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="H254" s="5"/>
       <c r="I254" s="5" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="J254" s="5"/>
     </row>
     <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>140306</v>
+        <v>150101</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C255" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D255" s="4">
-        <v>140306</v>
+        <v>150101</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>249</v>
+        <v>60</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>249</v>
+        <v>60</v>
       </c>
       <c r="J255" s="5"/>
     </row>
     <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>140307</v>
+        <v>150102</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C256" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D256" s="4">
-        <v>140307</v>
+        <v>150102</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="I256" s="5" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="J256" s="5"/>
     </row>
     <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
-        <v>140308</v>
+        <v>150103</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C257" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D257" s="4">
-        <v>140308</v>
+        <v>150103</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="I257" s="5" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="J257" s="5"/>
     </row>
     <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>140309</v>
+        <v>150104</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C258" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D258" s="4">
-        <v>140309</v>
+        <v>150104</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I258" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J258" s="5"/>
     </row>
     <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>140310</v>
+        <v>150105</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C259" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D259" s="4">
-        <v>140310</v>
+        <v>150105</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I259" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J259" s="5"/>
     </row>
     <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>140311</v>
+        <v>150106</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C260" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D260" s="4">
-        <v>140311</v>
+        <v>150106</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>64</v>
+        <v>303</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>64</v>
+        <v>303</v>
       </c>
       <c r="J260" s="5"/>
     </row>
     <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
-        <v>140312</v>
+        <v>150107</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C261" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D261" s="4">
-        <v>140312</v>
+        <v>150107</v>
       </c>
       <c r="E261" s="4"/>
       <c r="F261" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>65</v>
+        <v>304</v>
       </c>
       <c r="I261" s="5" t="s">
-        <v>65</v>
+        <v>304</v>
       </c>
       <c r="J261" s="5"/>
     </row>
     <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>140313</v>
+        <v>150108</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C262" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D262" s="4">
-        <v>140313</v>
+        <v>150108</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
@@ -14781,25 +14740,25 @@
         <v>300</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>69</v>
+        <v>305</v>
       </c>
       <c r="I262" s="5" t="s">
-        <v>69</v>
+        <v>305</v>
       </c>
       <c r="J262" s="5"/>
     </row>
     <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
-        <v>140314</v>
+        <v>150109</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C263" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D263" s="4">
-        <v>140314</v>
+        <v>150109</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="4" t="s">
@@ -14818,16 +14777,16 @@
     </row>
     <row r="264" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
-        <v>140315</v>
+        <v>150110</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C264" s="4">
-        <v>1403</v>
+        <v>1501</v>
       </c>
       <c r="D264" s="4">
-        <v>140315</v>
+        <v>150110</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="4" t="s">
@@ -14846,266 +14805,273 @@
     </row>
     <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>1404</v>
+        <v>150111</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C265" s="4">
-        <v>14</v>
+        <v>1501</v>
       </c>
       <c r="D265" s="4">
-        <v>1404</v>
+        <v>150111</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G265" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="H265" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H265" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="I265" s="5" t="s">
-        <v>301</v>
+        <v>69</v>
       </c>
       <c r="J265" s="5"/>
     </row>
     <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>140401</v>
+        <v>150112</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C266" s="4">
-        <v>1404</v>
+        <v>1501</v>
       </c>
       <c r="D266" s="4">
-        <v>140401</v>
+        <v>150112</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G266" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H266" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="I266" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="J266" s="5"/>
     </row>
     <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>140402</v>
+        <v>150113</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C267" s="4">
-        <v>1404</v>
+        <v>1501</v>
       </c>
       <c r="D267" s="4">
-        <v>140402</v>
+        <v>150113</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J267" s="5"/>
     </row>
     <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
-        <v>140403</v>
+        <v>1502</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C268" s="4">
-        <v>1404</v>
+        <v>15</v>
       </c>
       <c r="D268" s="4">
-        <v>140403</v>
+        <v>1502</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="H268" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="J268" s="5"/>
     </row>
     <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>140404</v>
+        <v>1503</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C269" s="4">
-        <v>1404</v>
+        <v>15</v>
       </c>
       <c r="D269" s="4">
-        <v>140404</v>
+        <v>1503</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G269" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H269" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>64</v>
+        <v>310</v>
       </c>
       <c r="J269" s="5"/>
     </row>
     <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="4">
-        <v>140405</v>
-      </c>
-      <c r="B270" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C270" s="4">
-        <v>1404</v>
-      </c>
-      <c r="D270" s="4">
-        <v>140405</v>
-      </c>
-      <c r="E270" s="4"/>
-      <c r="F270" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G270" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H270" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I270" s="5" t="s">
-        <v>65</v>
+      <c r="A270" s="6">
+        <v>1504</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C270" s="6">
+        <v>15</v>
+      </c>
+      <c r="D270" s="6">
+        <v>1504</v>
+      </c>
+      <c r="E270" s="6"/>
+      <c r="F270" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G270" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H270" s="7"/>
+      <c r="I270" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="J270" s="5"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A271" s="4">
-        <v>1405</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C271" s="4">
-        <v>14</v>
-      </c>
-      <c r="D271" s="4">
-        <v>1405</v>
-      </c>
-      <c r="E271" s="4"/>
-      <c r="F271" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G271" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="H271" s="1"/>
-      <c r="I271" s="1"/>
+    <row r="271" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="8"/>
+      <c r="B271" s="9"/>
+      <c r="C271" s="10"/>
+      <c r="D271" s="10"/>
+      <c r="E271" s="10"/>
+      <c r="F271" s="10"/>
+      <c r="G271" s="9"/>
+      <c r="H271" s="9"/>
+      <c r="I271" s="14"/>
       <c r="J271" s="5"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J272" s="13"/>
+    <row r="272" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="11">
+        <v>16</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C272" s="11">
+        <v>1</v>
+      </c>
+      <c r="D272" s="11">
+        <v>16</v>
+      </c>
+      <c r="E272" s="11"/>
+      <c r="F272" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G272" s="12"/>
+      <c r="H272" s="12"/>
+      <c r="I272" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="J272" s="5"/>
     </row>
     <row r="273" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>15</v>
+        <v>1601</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C273" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D273" s="4">
-        <v>15</v>
+        <v>1601</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G273" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>316</v>
+      </c>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="J273" s="5"/>
     </row>
     <row r="274" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="C274" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D274" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="J274" s="5"/>
     </row>
     <row r="275" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
-        <v>150101</v>
+        <v>160201</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>312</v>
+        <v>146</v>
       </c>
       <c r="C275" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D275" s="4">
-        <v>150101</v>
+        <v>160201</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H275" s="5" t="s">
         <v>60</v>
@@ -15117,23 +15083,23 @@
     </row>
     <row r="276" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
-        <v>150102</v>
+        <v>160202</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>312</v>
+        <v>146</v>
       </c>
       <c r="C276" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D276" s="4">
-        <v>150102</v>
+        <v>160202</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H276" s="5" t="s">
         <v>61</v>
@@ -15145,1149 +15111,1127 @@
     </row>
     <row r="277" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>150103</v>
+        <v>160203</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="C277" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D277" s="4">
-        <v>150103</v>
+        <v>160203</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H277" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="I277" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="J277" s="5"/>
     </row>
     <row r="278" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>150104</v>
+        <v>160204</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="C278" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D278" s="4">
-        <v>150104</v>
+        <v>160204</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>316</v>
+        <v>64</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>316</v>
+        <v>64</v>
       </c>
       <c r="J278" s="5"/>
     </row>
     <row r="279" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
-        <v>150105</v>
+        <v>160205</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="C279" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D279" s="4">
-        <v>150105</v>
+        <v>160205</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>317</v>
+        <v>65</v>
       </c>
       <c r="I279" s="5" t="s">
-        <v>317</v>
+        <v>65</v>
       </c>
       <c r="J279" s="5"/>
     </row>
     <row r="280" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
-        <v>150106</v>
+        <v>160206</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="C280" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D280" s="4">
-        <v>150106</v>
+        <v>160206</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G280" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H280" s="5" t="s">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="I280" s="5" t="s">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="J280" s="5"/>
     </row>
     <row r="281" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
-        <v>150107</v>
+        <v>160207</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="C281" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D281" s="4">
-        <v>150107</v>
+        <v>160207</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H281" s="5" t="s">
-        <v>319</v>
+        <v>64</v>
       </c>
       <c r="I281" s="5" t="s">
-        <v>319</v>
+        <v>64</v>
       </c>
       <c r="J281" s="5"/>
     </row>
     <row r="282" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
-        <v>150108</v>
+        <v>160208</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="C282" s="4">
-        <v>1501</v>
+        <v>1602</v>
       </c>
       <c r="D282" s="4">
-        <v>150108</v>
+        <v>160208</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G282" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H282" s="5" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="I282" s="5" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="J282" s="5"/>
     </row>
     <row r="283" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
-        <v>150109</v>
+        <v>1603</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C283" s="4">
-        <v>1501</v>
+        <v>16</v>
       </c>
       <c r="D283" s="4">
-        <v>150109</v>
+        <v>1603</v>
       </c>
       <c r="E283" s="4"/>
       <c r="F283" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G283" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H283" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="H283" s="5"/>
       <c r="I283" s="5" t="s">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="J283" s="5"/>
     </row>
     <row r="284" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
-        <v>150110</v>
+        <v>160301</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C284" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D284" s="4">
-        <v>150110</v>
+        <v>160301</v>
       </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G284" s="5" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="H284" s="5" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="I284" s="5" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="J284" s="5"/>
     </row>
     <row r="285" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
-        <v>150111</v>
+        <v>160302</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C285" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D285" s="4">
-        <v>150111</v>
+        <v>160302</v>
       </c>
       <c r="E285" s="4"/>
       <c r="F285" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G285" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="J285" s="5"/>
     </row>
     <row r="286" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
-        <v>150112</v>
+        <v>160303</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C286" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D286" s="4">
-        <v>150112</v>
+        <v>160303</v>
       </c>
       <c r="E286" s="4"/>
       <c r="F286" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H286" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I286" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J286" s="5"/>
     </row>
     <row r="287" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
-        <v>150113</v>
+        <v>160304</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C287" s="4">
-        <v>1501</v>
+        <v>1603</v>
       </c>
       <c r="D287" s="4">
-        <v>150113</v>
+        <v>160304</v>
       </c>
       <c r="E287" s="4"/>
       <c r="F287" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H287" s="5" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="I287" s="5" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="J287" s="5"/>
     </row>
     <row r="288" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>1502</v>
+        <v>160305</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C288" s="4">
-        <v>15</v>
+        <v>1603</v>
       </c>
       <c r="D288" s="4">
-        <v>1502</v>
+        <v>160305</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="H288" s="5"/>
+        <v>327</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>329</v>
+      </c>
       <c r="I288" s="5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="J288" s="5"/>
     </row>
     <row r="289" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
-        <v>1503</v>
+        <v>160306</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C289" s="4">
-        <v>15</v>
+        <v>1603</v>
       </c>
       <c r="D289" s="4">
-        <v>1503</v>
+        <v>160306</v>
       </c>
       <c r="E289" s="4"/>
       <c r="F289" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G289" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H289" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I289" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J289" s="5"/>
+    </row>
+    <row r="290" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="4">
+        <v>160307</v>
+      </c>
+      <c r="B290" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="H289" s="5"/>
-      <c r="I289" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="J289" s="5"/>
-    </row>
-    <row r="290" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="6">
-        <v>1504</v>
-      </c>
-      <c r="B290" s="7" t="s">
+      <c r="C290" s="4">
+        <v>1603</v>
+      </c>
+      <c r="D290" s="4">
+        <v>160307</v>
+      </c>
+      <c r="E290" s="4"/>
+      <c r="F290" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G290" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C290" s="6">
-        <v>15</v>
-      </c>
-      <c r="D290" s="6">
-        <v>1504</v>
-      </c>
-      <c r="E290" s="6"/>
-      <c r="F290" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G290" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="H290" s="7"/>
-      <c r="I290" s="7" t="s">
-        <v>327</v>
+      <c r="H290" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I290" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="J290" s="5"/>
     </row>
-    <row r="291" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="8"/>
-      <c r="B291" s="9"/>
-      <c r="C291" s="10"/>
-      <c r="D291" s="10"/>
-      <c r="E291" s="10"/>
-      <c r="F291" s="10"/>
-      <c r="G291" s="9"/>
-      <c r="H291" s="9"/>
-      <c r="I291" s="14"/>
+    <row r="291" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="4">
+        <v>160308</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C291" s="4">
+        <v>1603</v>
+      </c>
+      <c r="D291" s="4">
+        <v>160308</v>
+      </c>
+      <c r="E291" s="4"/>
+      <c r="F291" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G291" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H291" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I291" s="5" t="s">
+        <v>161</v>
+      </c>
       <c r="J291" s="5"/>
     </row>
     <row r="292" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="11">
-        <v>16</v>
-      </c>
-      <c r="B292" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C292" s="11">
-        <v>1</v>
-      </c>
-      <c r="D292" s="11">
-        <v>16</v>
-      </c>
-      <c r="E292" s="11"/>
-      <c r="F292" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G292" s="12"/>
-      <c r="H292" s="12"/>
-      <c r="I292" s="12" t="s">
-        <v>329</v>
+      <c r="A292" s="4">
+        <v>160309</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C292" s="4">
+        <v>1603</v>
+      </c>
+      <c r="D292" s="4">
+        <v>160309</v>
+      </c>
+      <c r="E292" s="4"/>
+      <c r="F292" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G292" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H292" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I292" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="J292" s="5"/>
     </row>
     <row r="293" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>1601</v>
+        <v>160310</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>330</v>
       </c>
       <c r="C293" s="4">
-        <v>16</v>
+        <v>1603</v>
       </c>
       <c r="D293" s="4">
-        <v>1601</v>
+        <v>160310</v>
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G293" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="H293" s="5"/>
+      <c r="H293" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="I293" s="5" t="s">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="J293" s="5"/>
     </row>
     <row r="294" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>144</v>
+        <v>332</v>
       </c>
       <c r="C294" s="4">
         <v>16</v>
       </c>
       <c r="D294" s="4">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G294" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H294" s="5"/>
       <c r="I294" s="5" t="s">
-        <v>144</v>
+        <v>332</v>
       </c>
       <c r="J294" s="5"/>
     </row>
     <row r="295" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="4">
-        <v>160201</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C295" s="4">
-        <v>1602</v>
-      </c>
-      <c r="D295" s="4">
-        <v>160201</v>
-      </c>
-      <c r="E295" s="4"/>
-      <c r="F295" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G295" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="H295" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I295" s="5" t="s">
-        <v>60</v>
+      <c r="A295" s="6">
+        <v>1604</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C295" s="6">
+        <v>16</v>
+      </c>
+      <c r="D295" s="6">
+        <v>1604</v>
+      </c>
+      <c r="E295" s="6"/>
+      <c r="F295" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G295" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H295" s="7"/>
+      <c r="I295" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="J295" s="5"/>
     </row>
-    <row r="296" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
-        <v>160202</v>
-      </c>
-      <c r="B296" s="5" t="s">
-        <v>146</v>
+        <v>1605</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="C296" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D296" s="4">
-        <v>160202</v>
+        <v>1605</v>
       </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G296" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="H296" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I296" s="5" t="s">
-        <v>61</v>
+        <v>337</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="J296" s="5"/>
     </row>
-    <row r="297" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
-        <v>160203</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>148</v>
+        <v>1606</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="C297" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D297" s="4">
-        <v>160203</v>
+        <v>1606</v>
       </c>
       <c r="E297" s="4"/>
       <c r="F297" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G297" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H297" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="I297" s="5" t="s">
-        <v>335</v>
+        <v>55</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H297" s="1"/>
+      <c r="I297" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="J297" s="5"/>
     </row>
-    <row r="298" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
-        <v>160204</v>
-      </c>
-      <c r="B298" s="5" t="s">
-        <v>148</v>
+        <v>1607</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="C298" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D298" s="4">
-        <v>160204</v>
+        <v>1607</v>
       </c>
       <c r="E298" s="4"/>
       <c r="F298" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G298" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H298" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I298" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H298" s="1"/>
+      <c r="I298" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="J298" s="5"/>
     </row>
     <row r="299" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>160205</v>
+        <v>2</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>148</v>
+        <v>342</v>
       </c>
       <c r="C299" s="4">
-        <v>1602</v>
+        <v>-1</v>
       </c>
       <c r="D299" s="4">
-        <v>160205</v>
+        <v>2</v>
       </c>
       <c r="E299" s="4"/>
       <c r="F299" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G299" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H299" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G299" s="5"/>
+      <c r="H299" s="5"/>
       <c r="I299" s="5" t="s">
-        <v>65</v>
+        <v>342</v>
       </c>
       <c r="J299" s="5"/>
     </row>
     <row r="300" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
-        <v>160206</v>
+        <v>21</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>150</v>
+        <v>343</v>
       </c>
       <c r="C300" s="4">
-        <v>1602</v>
+        <v>2</v>
       </c>
       <c r="D300" s="4">
-        <v>160206</v>
+        <v>21</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G300" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="H300" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G300" s="5"/>
+      <c r="H300" s="5"/>
       <c r="I300" s="5" t="s">
-        <v>69</v>
+        <v>343</v>
       </c>
       <c r="J300" s="5"/>
     </row>
     <row r="301" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
-        <v>160207</v>
+        <v>2110</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>150</v>
+        <v>344</v>
       </c>
       <c r="C301" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D301" s="4">
-        <v>160207</v>
+        <v>2110</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G301" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="H301" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="H301" s="5"/>
       <c r="I301" s="5" t="s">
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="J301" s="5"/>
     </row>
     <row r="302" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
-        <v>160208</v>
+        <v>2111</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>150</v>
+        <v>346</v>
       </c>
       <c r="C302" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D302" s="4">
-        <v>160208</v>
+        <v>2111</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G302" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="H302" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
-        <v>65</v>
+        <v>346</v>
       </c>
       <c r="J302" s="5"/>
     </row>
     <row r="303" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C303" s="4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D303" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G303" s="5" t="s">
-        <v>338</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G303" s="5"/>
       <c r="H303" s="5"/>
       <c r="I303" s="5" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="J303" s="5"/>
     </row>
     <row r="304" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>160301</v>
+        <v>2201</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C304" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D304" s="4">
-        <v>160301</v>
+        <v>2201</v>
       </c>
       <c r="E304" s="4"/>
       <c r="F304" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G304" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H304" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="H304" s="5"/>
       <c r="I304" s="5" t="s">
-        <v>156</v>
+        <v>349</v>
       </c>
       <c r="J304" s="5"/>
     </row>
     <row r="305" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
-        <v>160302</v>
+        <v>2202</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C305" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D305" s="4">
-        <v>160302</v>
+        <v>2202</v>
       </c>
       <c r="E305" s="4"/>
       <c r="F305" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G305" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H305" s="5" t="s">
-        <v>60</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="H305" s="5"/>
       <c r="I305" s="5" t="s">
-        <v>60</v>
+        <v>351</v>
       </c>
       <c r="J305" s="5"/>
     </row>
     <row r="306" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
-        <v>160303</v>
+        <v>2203</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C306" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D306" s="4">
-        <v>160303</v>
+        <v>2203</v>
       </c>
       <c r="E306" s="4"/>
       <c r="F306" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G306" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H306" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="H306" s="5"/>
       <c r="I306" s="5" t="s">
-        <v>61</v>
+        <v>353</v>
       </c>
       <c r="J306" s="5"/>
     </row>
     <row r="307" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
-        <v>160304</v>
+        <v>23</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C307" s="4">
-        <v>1603</v>
+        <v>2</v>
       </c>
       <c r="D307" s="4">
-        <v>160304</v>
+        <v>23</v>
       </c>
       <c r="E307" s="4"/>
       <c r="F307" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G307" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H307" s="5" t="s">
-        <v>343</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G307" s="5"/>
+      <c r="H307" s="5"/>
       <c r="I307" s="5" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="J307" s="5"/>
     </row>
     <row r="308" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
-        <v>160305</v>
+        <v>2301</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="C308" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D308" s="4">
-        <v>160305</v>
+        <v>2301</v>
       </c>
       <c r="E308" s="4"/>
       <c r="F308" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G308" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H308" s="5" t="s">
-        <v>344</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="H308" s="5"/>
       <c r="I308" s="5" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="J308" s="5"/>
     </row>
     <row r="309" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
-        <v>160306</v>
+        <v>2302</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="C309" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D309" s="4">
-        <v>160306</v>
+        <v>2302</v>
       </c>
       <c r="E309" s="4"/>
       <c r="F309" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G309" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H309" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G309" s="5"/>
+      <c r="H309" s="5"/>
       <c r="I309" s="5" t="s">
-        <v>64</v>
+        <v>358</v>
       </c>
       <c r="J309" s="5"/>
     </row>
     <row r="310" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>160307</v>
+        <v>23021</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C310" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D310" s="4">
-        <v>160307</v>
+        <v>23021</v>
       </c>
       <c r="E310" s="4"/>
       <c r="F310" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G310" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H310" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="H310" s="5"/>
       <c r="I310" s="5" t="s">
-        <v>65</v>
+        <v>361</v>
       </c>
       <c r="J310" s="5"/>
     </row>
     <row r="311" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>160308</v>
+        <v>23022</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="C311" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D311" s="4">
-        <v>160308</v>
+        <v>23022</v>
       </c>
       <c r="E311" s="4"/>
       <c r="F311" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G311" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H311" s="5" t="s">
-        <v>161</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="H311" s="5"/>
       <c r="I311" s="5" t="s">
-        <v>161</v>
+        <v>364</v>
       </c>
       <c r="J311" s="5"/>
     </row>
     <row r="312" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
-        <v>160309</v>
+        <v>2303</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="C312" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D312" s="4">
-        <v>160309</v>
+        <v>2303</v>
       </c>
       <c r="E312" s="4"/>
       <c r="F312" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G312" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H312" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G312" s="5"/>
+      <c r="H312" s="5"/>
       <c r="I312" s="5" t="s">
-        <v>64</v>
+        <v>294</v>
       </c>
       <c r="J312" s="5"/>
     </row>
     <row r="313" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
-        <v>160310</v>
-      </c>
-      <c r="B313" s="5" t="s">
-        <v>345</v>
+        <v>23031</v>
+      </c>
+      <c r="B313" s="22" t="s">
+        <v>391</v>
       </c>
       <c r="C313" s="4">
-        <v>1603</v>
+        <v>2303</v>
       </c>
       <c r="D313" s="4">
-        <v>160310</v>
+        <v>23031</v>
       </c>
       <c r="E313" s="4"/>
       <c r="F313" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G313" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H313" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I313" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="G313" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="H313" s="5"/>
+      <c r="I313" s="22" t="s">
+        <v>391</v>
       </c>
       <c r="J313" s="5"/>
     </row>
     <row r="314" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
-        <v>1608</v>
-      </c>
-      <c r="B314" s="5" t="s">
-        <v>347</v>
+        <v>23032</v>
+      </c>
+      <c r="B314" s="22" t="s">
+        <v>393</v>
       </c>
       <c r="C314" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D314" s="4">
-        <v>1608</v>
+        <v>23032</v>
       </c>
       <c r="E314" s="4"/>
       <c r="F314" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G314" s="5" t="s">
-        <v>348</v>
+      <c r="G314" s="22" t="s">
+        <v>394</v>
       </c>
       <c r="H314" s="5"/>
-      <c r="I314" s="5" t="s">
-        <v>347</v>
+      <c r="I314" s="22" t="s">
+        <v>393</v>
       </c>
       <c r="J314" s="5"/>
     </row>
     <row r="315" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="6">
-        <v>1604</v>
-      </c>
-      <c r="B315" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C315" s="6">
-        <v>16</v>
-      </c>
-      <c r="D315" s="6">
-        <v>1604</v>
-      </c>
-      <c r="E315" s="6"/>
-      <c r="F315" s="6" t="s">
+      <c r="A315" s="4">
+        <v>23033</v>
+      </c>
+      <c r="B315" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="C315" s="4">
+        <v>2303</v>
+      </c>
+      <c r="D315" s="4">
+        <v>23033</v>
+      </c>
+      <c r="E315" s="4"/>
+      <c r="F315" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G315" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H315" s="7"/>
-      <c r="I315" s="7" t="s">
-        <v>349</v>
+      <c r="G315" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="H315" s="5"/>
+      <c r="I315" s="22" t="s">
+        <v>395</v>
       </c>
       <c r="J315" s="5"/>
     </row>
-    <row r="316" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>1605</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>351</v>
+        <v>23034</v>
+      </c>
+      <c r="B316" s="22" t="s">
+        <v>397</v>
       </c>
       <c r="C316" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D316" s="4">
-        <v>1605</v>
+        <v>23034</v>
       </c>
       <c r="E316" s="4"/>
       <c r="F316" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G316" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="I316" s="1" t="s">
-        <v>351</v>
+      <c r="G316" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="H316" s="5"/>
+      <c r="I316" s="22" t="s">
+        <v>397</v>
       </c>
       <c r="J316" s="5"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>1606</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>353</v>
+        <v>23035</v>
+      </c>
+      <c r="B317" s="22" t="s">
+        <v>399</v>
       </c>
       <c r="C317" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D317" s="4">
-        <v>1606</v>
+        <v>23035</v>
       </c>
       <c r="E317" s="4"/>
       <c r="F317" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G317" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H317" s="1"/>
-      <c r="I317" s="1" t="s">
-        <v>353</v>
+      <c r="G317" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="H317" s="5"/>
+      <c r="I317" s="22" t="s">
+        <v>399</v>
       </c>
       <c r="J317" s="5"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>1607</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>355</v>
+        <v>23036</v>
+      </c>
+      <c r="B318" s="22" t="s">
+        <v>401</v>
       </c>
       <c r="C318" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D318" s="4">
-        <v>1607</v>
+        <v>23036</v>
       </c>
       <c r="E318" s="4"/>
       <c r="F318" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G318" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="H318" s="1"/>
-      <c r="I318" s="1" t="s">
-        <v>355</v>
+      <c r="G318" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="H318" s="5"/>
+      <c r="I318" s="22" t="s">
+        <v>401</v>
       </c>
       <c r="J318" s="5"/>
     </row>
     <row r="319" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>2</v>
-      </c>
-      <c r="B319" s="5" t="s">
-        <v>357</v>
+        <v>2304</v>
+      </c>
+      <c r="B319" s="22" t="s">
+        <v>403</v>
       </c>
       <c r="C319" s="4">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="D319" s="4">
-        <v>2</v>
+        <v>2304</v>
       </c>
       <c r="E319" s="4"/>
       <c r="F319" s="4" t="s">
@@ -16295,865 +16239,407 @@
       </c>
       <c r="G319" s="5"/>
       <c r="H319" s="5"/>
-      <c r="I319" s="5" t="s">
-        <v>357</v>
+      <c r="I319" s="22" t="s">
+        <v>403</v>
       </c>
       <c r="J319" s="5"/>
     </row>
     <row r="320" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>21</v>
-      </c>
-      <c r="B320" s="5" t="s">
-        <v>358</v>
+        <v>23041</v>
+      </c>
+      <c r="B320" s="22" t="s">
+        <v>405</v>
       </c>
       <c r="C320" s="4">
-        <v>2</v>
+        <v>2304</v>
       </c>
       <c r="D320" s="4">
-        <v>21</v>
+        <v>23041</v>
       </c>
       <c r="E320" s="4"/>
       <c r="F320" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G320" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G320" s="22" t="s">
+        <v>404</v>
+      </c>
       <c r="H320" s="5"/>
-      <c r="I320" s="5" t="s">
-        <v>358</v>
+      <c r="I320" s="22" t="s">
+        <v>405</v>
       </c>
       <c r="J320" s="5"/>
     </row>
-    <row r="321" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>2110</v>
+        <v>2305</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C321" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D321" s="4">
-        <v>2110</v>
+        <v>2305</v>
       </c>
       <c r="E321" s="4"/>
       <c r="F321" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G321" s="5" t="s">
-        <v>360</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G321" s="5"/>
       <c r="H321" s="5"/>
       <c r="I321" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J321" s="5"/>
     </row>
-    <row r="322" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>2111</v>
+        <v>23051</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C322" s="4">
-        <v>21</v>
+        <v>2305</v>
       </c>
       <c r="D322" s="4">
-        <v>2111</v>
+        <v>23051</v>
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G322" s="5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H322" s="5"/>
       <c r="I322" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J322" s="5"/>
     </row>
-    <row r="323" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>22</v>
+        <v>23052</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C323" s="4">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D323" s="4">
-        <v>22</v>
+        <v>23052</v>
       </c>
       <c r="E323" s="4"/>
       <c r="F323" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G323" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G323" s="5" t="s">
+        <v>369</v>
+      </c>
       <c r="H323" s="5"/>
       <c r="I323" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J323" s="5"/>
     </row>
-    <row r="324" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>2201</v>
+        <v>23053</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C324" s="4">
-        <v>22</v>
+        <v>2305</v>
       </c>
       <c r="D324" s="4">
-        <v>2201</v>
+        <v>23053</v>
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G324" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H324" s="5"/>
       <c r="I324" s="5" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="J324" s="5"/>
     </row>
-    <row r="325" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>2202</v>
+        <v>23054</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C325" s="4">
-        <v>22</v>
+        <v>2305</v>
       </c>
       <c r="D325" s="4">
-        <v>2202</v>
+        <v>23054</v>
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G325" s="5" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="H325" s="5"/>
       <c r="I325" s="5" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="J325" s="5"/>
     </row>
-    <row r="326" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>2203</v>
+        <v>2306</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C326" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D326" s="4">
-        <v>2203</v>
+        <v>2306</v>
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G326" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="H326" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G326" s="4"/>
+      <c r="H326" s="4"/>
       <c r="I326" s="5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="J326" s="5"/>
     </row>
-    <row r="327" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>23</v>
+        <v>23061</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C327" s="4">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D327" s="4">
-        <v>23</v>
+        <v>23061</v>
       </c>
       <c r="E327" s="4"/>
       <c r="F327" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G327" s="5"/>
-      <c r="H327" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G327" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H327" s="4"/>
       <c r="I327" s="5" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="J327" s="5"/>
     </row>
-    <row r="328" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>2301</v>
+        <v>23062</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C328" s="4">
-        <v>23</v>
+        <v>2306</v>
       </c>
       <c r="D328" s="4">
-        <v>2301</v>
+        <v>23062</v>
       </c>
       <c r="E328" s="4"/>
       <c r="F328" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G328" s="5" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H328" s="5"/>
       <c r="I328" s="5" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="J328" s="5"/>
     </row>
-    <row r="329" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C329" s="4">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D329" s="4">
-        <v>2302</v>
-      </c>
-      <c r="E329" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E329" s="5"/>
       <c r="F329" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G329" s="5"/>
       <c r="H329" s="5"/>
       <c r="I329" s="5" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J329" s="5"/>
     </row>
-    <row r="330" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>23021</v>
+        <v>2401</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C330" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="D330" s="4">
-        <v>23021</v>
-      </c>
-      <c r="E330" s="4"/>
+        <v>2401</v>
+      </c>
+      <c r="E330" s="5"/>
       <c r="F330" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G330" s="5" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H330" s="5"/>
       <c r="I330" s="5" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="J330" s="5"/>
     </row>
-    <row r="331" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
-        <v>23022</v>
+        <v>2402</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C331" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="D331" s="4">
-        <v>23022</v>
+        <v>2402</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G331" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="H331" s="5"/>
+        <v>389</v>
+      </c>
+      <c r="H331" s="4"/>
       <c r="I331" s="5" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="J331" s="5"/>
     </row>
-    <row r="332" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>2303</v>
+        <v>2403</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>309</v>
+        <v>390</v>
       </c>
       <c r="C332" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D332" s="4">
-        <v>2303</v>
+        <v>2403</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G332" s="5"/>
-      <c r="H332" s="5"/>
-      <c r="I332" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="J332" s="5"/>
-    </row>
-    <row r="333" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I332" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J332" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K332"/>
+      <c r="L332"/>
+      <c r="M332"/>
+      <c r="N332"/>
+      <c r="O332"/>
+      <c r="P332"/>
+      <c r="Q332"/>
+      <c r="R332"/>
+      <c r="S332"/>
+      <c r="T332"/>
+      <c r="U332"/>
+      <c r="V332"/>
+      <c r="W332"/>
+      <c r="X332"/>
+      <c r="Y332"/>
+      <c r="Z332" s="15"/>
+    </row>
+    <row r="333" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
-        <v>23031</v>
-      </c>
-      <c r="B333" s="22" t="s">
-        <v>406</v>
+        <v>25</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="C333" s="4">
-        <v>2303</v>
+        <v>2</v>
       </c>
       <c r="D333" s="4">
-        <v>23031</v>
+        <v>25</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G333" s="22" t="s">
-        <v>407</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G333" s="5"/>
       <c r="H333" s="5"/>
-      <c r="I333" s="22" t="s">
-        <v>406</v>
+      <c r="I333" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="J333" s="5"/>
     </row>
-    <row r="334" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
-        <v>23032</v>
-      </c>
-      <c r="B334" s="22" t="s">
-        <v>408</v>
+        <v>2501</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="C334" s="4">
-        <v>2303</v>
+        <v>25</v>
       </c>
       <c r="D334" s="4">
-        <v>23032</v>
-      </c>
-      <c r="E334" s="4"/>
+        <v>2501</v>
+      </c>
+      <c r="E334" s="5"/>
       <c r="F334" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G334" s="22" t="s">
-        <v>409</v>
+      <c r="G334" s="5" t="s">
+        <v>383</v>
       </c>
       <c r="H334" s="5"/>
-      <c r="I334" s="22" t="s">
-        <v>408</v>
+      <c r="I334" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="J334" s="5"/>
-    </row>
-    <row r="335" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A335" s="4">
-        <v>23033</v>
-      </c>
-      <c r="B335" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="C335" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D335" s="4">
-        <v>23033</v>
-      </c>
-      <c r="E335" s="4"/>
-      <c r="F335" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G335" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="H335" s="5"/>
-      <c r="I335" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="J335" s="5"/>
-    </row>
-    <row r="336" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A336" s="4">
-        <v>23034</v>
-      </c>
-      <c r="B336" s="22" t="s">
-        <v>412</v>
-      </c>
-      <c r="C336" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D336" s="4">
-        <v>23034</v>
-      </c>
-      <c r="E336" s="4"/>
-      <c r="F336" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G336" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="H336" s="5"/>
-      <c r="I336" s="22" t="s">
-        <v>412</v>
-      </c>
-      <c r="J336" s="5"/>
-    </row>
-    <row r="337" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A337" s="4">
-        <v>23035</v>
-      </c>
-      <c r="B337" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="C337" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D337" s="4">
-        <v>23035</v>
-      </c>
-      <c r="E337" s="4"/>
-      <c r="F337" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G337" s="22" t="s">
-        <v>415</v>
-      </c>
-      <c r="H337" s="5"/>
-      <c r="I337" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="J337" s="5"/>
-    </row>
-    <row r="338" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A338" s="4">
-        <v>23036</v>
-      </c>
-      <c r="B338" s="22" t="s">
-        <v>416</v>
-      </c>
-      <c r="C338" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D338" s="4">
-        <v>23036</v>
-      </c>
-      <c r="E338" s="4"/>
-      <c r="F338" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G338" s="22" t="s">
-        <v>417</v>
-      </c>
-      <c r="H338" s="5"/>
-      <c r="I338" s="22" t="s">
-        <v>416</v>
-      </c>
-      <c r="J338" s="5"/>
-    </row>
-    <row r="339" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A339" s="4">
-        <v>2304</v>
-      </c>
-      <c r="B339" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="C339" s="4">
-        <v>23</v>
-      </c>
-      <c r="D339" s="4">
-        <v>2304</v>
-      </c>
-      <c r="E339" s="4"/>
-      <c r="F339" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G339" s="5"/>
-      <c r="H339" s="5"/>
-      <c r="I339" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="J339" s="5"/>
-    </row>
-    <row r="340" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A340" s="4">
-        <v>23041</v>
-      </c>
-      <c r="B340" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C340" s="4">
-        <v>2304</v>
-      </c>
-      <c r="D340" s="4">
-        <v>23041</v>
-      </c>
-      <c r="E340" s="4"/>
-      <c r="F340" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G340" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="H340" s="5"/>
-      <c r="I340" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="J340" s="5"/>
-    </row>
-    <row r="341" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A341" s="4">
-        <v>23042</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C341" s="4">
-        <v>2304</v>
-      </c>
-      <c r="D341" s="4">
-        <v>23042</v>
-      </c>
-      <c r="E341" s="4"/>
-      <c r="F341" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G341" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="H341" s="5"/>
-      <c r="I341" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="J341" s="5"/>
-    </row>
-    <row r="342" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A342" s="4">
-        <v>23043</v>
-      </c>
-      <c r="B342" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C342" s="4">
-        <v>2304</v>
-      </c>
-      <c r="D342" s="4">
-        <v>23043</v>
-      </c>
-      <c r="E342" s="4"/>
-      <c r="F342" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G342" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="H342" s="5"/>
-      <c r="I342" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="J342" s="5"/>
-    </row>
-    <row r="343" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A343" s="4">
-        <v>23044</v>
-      </c>
-      <c r="B343" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C343" s="4">
-        <v>2304</v>
-      </c>
-      <c r="D343" s="4">
-        <v>23044</v>
-      </c>
-      <c r="E343" s="4"/>
-      <c r="F343" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G343" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="H343" s="5"/>
-      <c r="I343" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="J343" s="5"/>
-    </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A344" s="4">
-        <v>2305</v>
-      </c>
-      <c r="B344" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C344" s="4">
-        <v>23</v>
-      </c>
-      <c r="D344" s="4">
-        <v>2305</v>
-      </c>
-      <c r="E344" s="4"/>
-      <c r="F344" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G344" s="4"/>
-      <c r="H344" s="4"/>
-      <c r="I344" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="J344" s="5"/>
-    </row>
-    <row r="345" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A345" s="4">
-        <v>23051</v>
-      </c>
-      <c r="B345" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C345" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D345" s="4">
-        <v>23051</v>
-      </c>
-      <c r="E345" s="4"/>
-      <c r="F345" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G345" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="H345" s="4"/>
-      <c r="I345" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="J345" s="5"/>
-    </row>
-    <row r="346" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A346" s="4">
-        <v>23052</v>
-      </c>
-      <c r="B346" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="C346" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D346" s="4">
-        <v>23052</v>
-      </c>
-      <c r="E346" s="4"/>
-      <c r="F346" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G346" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="H346" s="5"/>
-      <c r="I346" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="J346" s="5"/>
-    </row>
-    <row r="347" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A347" s="4">
-        <v>24</v>
-      </c>
-      <c r="B347" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="C347" s="4">
-        <v>2</v>
-      </c>
-      <c r="D347" s="4">
-        <v>24</v>
-      </c>
-      <c r="E347" s="4"/>
-      <c r="F347" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G347" s="5"/>
-      <c r="H347" s="5"/>
-      <c r="I347" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="J347" s="5"/>
-    </row>
-    <row r="348" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A348" s="4">
-        <v>2401</v>
-      </c>
-      <c r="B348" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C348" s="4">
-        <v>24</v>
-      </c>
-      <c r="D348" s="4">
-        <v>2401</v>
-      </c>
-      <c r="E348" s="5"/>
-      <c r="F348" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G348" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="H348" s="5"/>
-      <c r="I348" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="J348" s="5"/>
-    </row>
-    <row r="349" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A349" s="4">
-        <v>25</v>
-      </c>
-      <c r="B349" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C349" s="4">
-        <v>2</v>
-      </c>
-      <c r="D349" s="4">
-        <v>25</v>
-      </c>
-      <c r="E349" s="5"/>
-      <c r="F349" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G349" s="5"/>
-      <c r="H349" s="5"/>
-      <c r="I349" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="J349" s="5"/>
-    </row>
-    <row r="350" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A350" s="4">
-        <v>2501</v>
-      </c>
-      <c r="B350" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C350" s="4">
-        <v>25</v>
-      </c>
-      <c r="D350" s="4">
-        <v>2501</v>
-      </c>
-      <c r="E350" s="5"/>
-      <c r="F350" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G350" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="H350" s="5"/>
-      <c r="I350" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="J350" s="5"/>
-    </row>
-    <row r="351" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A351" s="4">
-        <v>2502</v>
-      </c>
-      <c r="B351" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C351" s="4">
-        <v>25</v>
-      </c>
-      <c r="D351" s="4">
-        <v>2502</v>
-      </c>
-      <c r="E351" s="4"/>
-      <c r="F351" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G351" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="H351" s="4"/>
-      <c r="I351" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="J351" s="5"/>
-    </row>
-    <row r="352" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A352" s="4">
-        <v>2503</v>
-      </c>
-      <c r="B352" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="C352" s="4">
-        <v>25</v>
-      </c>
-      <c r="D352" s="4">
-        <v>2503</v>
-      </c>
-      <c r="E352" s="4"/>
-      <c r="F352" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G352" s="5"/>
-      <c r="I352" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="J352" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K352"/>
-      <c r="L352"/>
-      <c r="M352"/>
-      <c r="N352"/>
-      <c r="O352"/>
-      <c r="P352"/>
-      <c r="Q352"/>
-      <c r="R352"/>
-      <c r="S352"/>
-      <c r="T352"/>
-      <c r="U352"/>
-      <c r="V352"/>
-      <c r="W352"/>
-      <c r="X352"/>
-      <c r="Y352"/>
-      <c r="Z352" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBEDD11-C117-4774-A5EF-A3F25123B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4759B9FC-5E48-472A-ABA4-80E3520D16AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -871,9 +871,6 @@
     <t>Aod Alignment</t>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserPrescanChirpAodAlignmentCalibrationViewModel</t>
-  </si>
-  <si>
     <t>XY Astigmatism</t>
   </si>
   <si>
@@ -1232,15 +1229,19 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserAODDelayViewModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>CugaCalibration.ViewModels.Laser.LaserAttenuatorViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserOpticalPowerMeterViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Laser.LaserPrescanChirpAodAlignmentCalibrationViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.AOD.AODDelayViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -13778,7 +13779,7 @@
         <v>55</v>
       </c>
       <c r="G229" s="23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
@@ -13804,7 +13805,7 @@
         <v>55</v>
       </c>
       <c r="G230" s="23" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5" t="s">
@@ -13844,7 +13845,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C233" s="4">
         <v>1</v>
@@ -13868,7 +13869,7 @@
         <v>1501</v>
       </c>
       <c r="B234" s="23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
@@ -13881,11 +13882,11 @@
         <v>55</v>
       </c>
       <c r="G234" s="23" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H234" s="5"/>
       <c r="I234" s="23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J234" s="5"/>
     </row>
@@ -13894,7 +13895,7 @@
         <v>1502</v>
       </c>
       <c r="B235" s="23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C235" s="4">
         <v>15</v>
@@ -13906,8 +13907,8 @@
       <c r="F235" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G235" s="5" t="s">
-        <v>276</v>
+      <c r="G235" s="23" t="s">
+        <v>379</v>
       </c>
       <c r="H235" s="5"/>
       <c r="I235" s="5" t="s">
@@ -13920,7 +13921,7 @@
         <v>1503</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C236" s="4">
         <v>15</v>
@@ -13933,11 +13934,11 @@
         <v>55</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H236" s="5"/>
       <c r="I236" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J236" s="5"/>
     </row>
@@ -13946,7 +13947,7 @@
         <v>1504</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C237" s="7">
         <v>15</v>
@@ -13959,11 +13960,11 @@
         <v>55</v>
       </c>
       <c r="G237" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H237" s="8"/>
       <c r="I237" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J237" s="5"/>
     </row>
@@ -13984,7 +13985,7 @@
         <v>16</v>
       </c>
       <c r="B239" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C239" s="12">
         <v>1</v>
@@ -13999,7 +14000,7 @@
       <c r="G239" s="13"/>
       <c r="H239" s="13"/>
       <c r="I239" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J239" s="5"/>
     </row>
@@ -14008,7 +14009,7 @@
         <v>1601</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C240" s="4">
         <v>16</v>
@@ -14021,11 +14022,11 @@
         <v>55</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H240" s="5"/>
       <c r="I240" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J240" s="5"/>
     </row>
@@ -14047,7 +14048,7 @@
         <v>55</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H241" s="5"/>
       <c r="I241" s="5" t="s">
@@ -14073,7 +14074,7 @@
         <v>58</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>60</v>
@@ -14101,7 +14102,7 @@
         <v>58</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>61</v>
@@ -14129,13 +14130,13 @@
         <v>68</v>
       </c>
       <c r="G244" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H244" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="H244" s="5" t="s">
-        <v>287</v>
-      </c>
       <c r="I244" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J244" s="5"/>
     </row>
@@ -14157,7 +14158,7 @@
         <v>58</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H245" s="5" t="s">
         <v>64</v>
@@ -14185,7 +14186,7 @@
         <v>58</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>65</v>
@@ -14213,7 +14214,7 @@
         <v>68</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>69</v>
@@ -14241,7 +14242,7 @@
         <v>58</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>64</v>
@@ -14269,7 +14270,7 @@
         <v>58</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H249" s="5" t="s">
         <v>65</v>
@@ -14284,7 +14285,7 @@
         <v>1603</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C250" s="4">
         <v>16</v>
@@ -14297,11 +14298,11 @@
         <v>55</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H250" s="5"/>
       <c r="I250" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J250" s="5"/>
     </row>
@@ -14310,7 +14311,7 @@
         <v>160301</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C251" s="4">
         <v>1603</v>
@@ -14323,7 +14324,7 @@
         <v>58</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>156</v>
@@ -14338,7 +14339,7 @@
         <v>160302</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C252" s="4">
         <v>1603</v>
@@ -14351,7 +14352,7 @@
         <v>58</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H252" s="5" t="s">
         <v>60</v>
@@ -14366,7 +14367,7 @@
         <v>160303</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C253" s="4">
         <v>1603</v>
@@ -14379,7 +14380,7 @@
         <v>58</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H253" s="5" t="s">
         <v>61</v>
@@ -14394,7 +14395,7 @@
         <v>160304</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C254" s="4">
         <v>1603</v>
@@ -14407,13 +14408,13 @@
         <v>58</v>
       </c>
       <c r="G254" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="H254" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="H254" s="5" t="s">
-        <v>295</v>
-      </c>
       <c r="I254" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J254" s="5"/>
     </row>
@@ -14422,7 +14423,7 @@
         <v>160305</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C255" s="4">
         <v>1603</v>
@@ -14435,13 +14436,13 @@
         <v>58</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J255" s="5"/>
     </row>
@@ -14450,7 +14451,7 @@
         <v>160306</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C256" s="4">
         <v>1603</v>
@@ -14463,7 +14464,7 @@
         <v>58</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H256" s="5" t="s">
         <v>64</v>
@@ -14478,7 +14479,7 @@
         <v>160307</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C257" s="4">
         <v>1603</v>
@@ -14491,7 +14492,7 @@
         <v>58</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H257" s="5" t="s">
         <v>65</v>
@@ -14506,7 +14507,7 @@
         <v>160308</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C258" s="4">
         <v>1603</v>
@@ -14519,7 +14520,7 @@
         <v>68</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H258" s="5" t="s">
         <v>161</v>
@@ -14534,7 +14535,7 @@
         <v>160309</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C259" s="4">
         <v>1603</v>
@@ -14547,7 +14548,7 @@
         <v>58</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H259" s="5" t="s">
         <v>64</v>
@@ -14562,7 +14563,7 @@
         <v>160310</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C260" s="4">
         <v>1603</v>
@@ -14575,7 +14576,7 @@
         <v>58</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H260" s="5" t="s">
         <v>65</v>
@@ -14590,7 +14591,7 @@
         <v>1604</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C261" s="4">
         <v>16</v>
@@ -14603,11 +14604,11 @@
         <v>55</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H261" s="5"/>
       <c r="I261" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J261" s="5"/>
     </row>
@@ -14616,7 +14617,7 @@
         <v>1608</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C262" s="4">
         <v>16</v>
@@ -14629,11 +14630,11 @@
         <v>55</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H262" s="5"/>
       <c r="I262" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J262" s="5"/>
     </row>
@@ -14642,7 +14643,7 @@
         <v>1604</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C263" s="7">
         <v>16</v>
@@ -14655,11 +14656,11 @@
         <v>55</v>
       </c>
       <c r="G263" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H263" s="8"/>
       <c r="I263" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J263" s="5"/>
     </row>
@@ -14668,7 +14669,7 @@
         <v>1605</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C264" s="4">
         <v>16</v>
@@ -14681,10 +14682,10 @@
         <v>55</v>
       </c>
       <c r="G264" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J264" s="5"/>
     </row>
@@ -14693,7 +14694,7 @@
         <v>1606</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C265" s="4">
         <v>16</v>
@@ -14706,11 +14707,11 @@
         <v>55</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J265" s="5"/>
     </row>
@@ -14719,7 +14720,7 @@
         <v>1607</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C266" s="4">
         <v>16</v>
@@ -14732,11 +14733,11 @@
         <v>55</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H266" s="1"/>
       <c r="I266" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J266" s="5"/>
     </row>
@@ -14745,7 +14746,7 @@
         <v>2</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C267" s="4">
         <v>-1</v>
@@ -14760,7 +14761,7 @@
       <c r="G267" s="5"/>
       <c r="H267" s="5"/>
       <c r="I267" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J267" s="5"/>
     </row>
@@ -14769,7 +14770,7 @@
         <v>21</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C268" s="4">
         <v>2</v>
@@ -14784,7 +14785,7 @@
       <c r="G268" s="5"/>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J268" s="5"/>
     </row>
@@ -14793,7 +14794,7 @@
         <v>2110</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C269" s="4">
         <v>21</v>
@@ -14806,11 +14807,11 @@
         <v>55</v>
       </c>
       <c r="G269" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J269" s="5"/>
     </row>
@@ -14819,7 +14820,7 @@
         <v>2111</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C270" s="4">
         <v>21</v>
@@ -14832,11 +14833,11 @@
         <v>55</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J270" s="5"/>
     </row>
@@ -14845,7 +14846,7 @@
         <v>22</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C271" s="4">
         <v>2</v>
@@ -14860,7 +14861,7 @@
       <c r="G271" s="5"/>
       <c r="H271" s="5"/>
       <c r="I271" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J271" s="5"/>
     </row>
@@ -14869,7 +14870,7 @@
         <v>2201</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C272" s="4">
         <v>22</v>
@@ -14882,11 +14883,11 @@
         <v>55</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H272" s="5"/>
       <c r="I272" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J272" s="5"/>
     </row>
@@ -14895,7 +14896,7 @@
         <v>2202</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C273" s="4">
         <v>22</v>
@@ -14908,11 +14909,11 @@
         <v>55</v>
       </c>
       <c r="G273" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J273" s="5"/>
     </row>
@@ -14921,7 +14922,7 @@
         <v>2203</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C274" s="4">
         <v>22</v>
@@ -14934,11 +14935,11 @@
         <v>55</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J274" s="5"/>
     </row>
@@ -14947,7 +14948,7 @@
         <v>23</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C275" s="4">
         <v>2</v>
@@ -14962,7 +14963,7 @@
       <c r="G275" s="5"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J275" s="5"/>
     </row>
@@ -14971,7 +14972,7 @@
         <v>2301</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C276" s="4">
         <v>23</v>
@@ -14984,11 +14985,11 @@
         <v>55</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H276" s="5"/>
       <c r="I276" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J276" s="5"/>
     </row>
@@ -14997,7 +14998,7 @@
         <v>2302</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C277" s="4">
         <v>23</v>
@@ -15012,7 +15013,7 @@
       <c r="G277" s="5"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J277" s="5"/>
     </row>
@@ -15021,7 +15022,7 @@
         <v>23021</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C278" s="4">
         <v>2302</v>
@@ -15034,11 +15035,11 @@
         <v>55</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H278" s="5"/>
       <c r="I278" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J278" s="5"/>
     </row>
@@ -15047,7 +15048,7 @@
         <v>23022</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C279" s="4">
         <v>2302</v>
@@ -15060,11 +15061,11 @@
         <v>55</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H279" s="5"/>
       <c r="I279" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J279" s="5"/>
     </row>
@@ -15097,7 +15098,7 @@
         <v>23031</v>
       </c>
       <c r="B281" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C281" s="4">
         <v>2303</v>
@@ -15110,11 +15111,11 @@
         <v>55</v>
       </c>
       <c r="G281" s="14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H281" s="5"/>
       <c r="I281" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J281" s="5"/>
     </row>
@@ -15123,7 +15124,7 @@
         <v>23032</v>
       </c>
       <c r="B282" s="14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C282" s="4">
         <v>2303</v>
@@ -15136,11 +15137,11 @@
         <v>55</v>
       </c>
       <c r="G282" s="14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H282" s="5"/>
       <c r="I282" s="14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J282" s="5"/>
     </row>
@@ -15149,7 +15150,7 @@
         <v>23033</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C283" s="4">
         <v>2303</v>
@@ -15162,11 +15163,11 @@
         <v>55</v>
       </c>
       <c r="G283" s="14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H283" s="5"/>
       <c r="I283" s="14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J283" s="5"/>
     </row>
@@ -15175,7 +15176,7 @@
         <v>23034</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C284" s="4">
         <v>2303</v>
@@ -15188,11 +15189,11 @@
         <v>55</v>
       </c>
       <c r="G284" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H284" s="5"/>
       <c r="I284" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J284" s="5"/>
     </row>
@@ -15201,7 +15202,7 @@
         <v>23035</v>
       </c>
       <c r="B285" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C285" s="4">
         <v>2303</v>
@@ -15214,11 +15215,11 @@
         <v>55</v>
       </c>
       <c r="G285" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H285" s="5"/>
       <c r="I285" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J285" s="5"/>
     </row>
@@ -15227,7 +15228,7 @@
         <v>23036</v>
       </c>
       <c r="B286" s="14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C286" s="4">
         <v>2303</v>
@@ -15240,11 +15241,11 @@
         <v>55</v>
       </c>
       <c r="G286" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H286" s="5"/>
       <c r="I286" s="14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J286" s="5"/>
     </row>
@@ -15253,7 +15254,7 @@
         <v>2304</v>
       </c>
       <c r="B287" s="14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C287" s="4">
         <v>23</v>
@@ -15268,7 +15269,7 @@
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
       <c r="I287" s="14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J287" s="5"/>
     </row>
@@ -15277,7 +15278,7 @@
         <v>23041</v>
       </c>
       <c r="B288" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C288" s="4">
         <v>2304</v>
@@ -15290,11 +15291,11 @@
         <v>55</v>
       </c>
       <c r="G288" s="14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H288" s="5"/>
       <c r="I288" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J288" s="5"/>
     </row>
@@ -15303,7 +15304,7 @@
         <v>2305</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C289" s="4">
         <v>23</v>
@@ -15318,7 +15319,7 @@
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
       <c r="I289" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J289" s="5"/>
     </row>
@@ -15327,7 +15328,7 @@
         <v>23051</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C290" s="4">
         <v>2305</v>
@@ -15340,11 +15341,11 @@
         <v>55</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H290" s="5"/>
       <c r="I290" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J290" s="5"/>
     </row>
@@ -15353,7 +15354,7 @@
         <v>23052</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C291" s="4">
         <v>2305</v>
@@ -15366,11 +15367,11 @@
         <v>55</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H291" s="5"/>
       <c r="I291" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J291" s="5"/>
     </row>
@@ -15379,7 +15380,7 @@
         <v>23053</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C292" s="4">
         <v>2305</v>
@@ -15392,11 +15393,11 @@
         <v>55</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H292" s="5"/>
       <c r="I292" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J292" s="5"/>
     </row>
@@ -15405,7 +15406,7 @@
         <v>23054</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C293" s="4">
         <v>2305</v>
@@ -15418,11 +15419,11 @@
         <v>55</v>
       </c>
       <c r="G293" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H293" s="5"/>
       <c r="I293" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J293" s="5"/>
     </row>
@@ -15431,7 +15432,7 @@
         <v>2306</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C294" s="4">
         <v>23</v>
@@ -15446,7 +15447,7 @@
       <c r="G294" s="4"/>
       <c r="H294" s="4"/>
       <c r="I294" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J294" s="5"/>
     </row>
@@ -15455,7 +15456,7 @@
         <v>23061</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C295" s="4">
         <v>2306</v>
@@ -15468,11 +15469,11 @@
         <v>55</v>
       </c>
       <c r="G295" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H295" s="4"/>
       <c r="I295" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J295" s="5"/>
     </row>
@@ -15481,7 +15482,7 @@
         <v>23062</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C296" s="4">
         <v>2306</v>
@@ -15494,11 +15495,11 @@
         <v>55</v>
       </c>
       <c r="G296" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H296" s="5"/>
       <c r="I296" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J296" s="5"/>
     </row>
@@ -15507,7 +15508,7 @@
         <v>24</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C297" s="4">
         <v>2</v>
@@ -15522,7 +15523,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J297" s="5"/>
     </row>
@@ -15531,7 +15532,7 @@
         <v>2401</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C298" s="4">
         <v>24</v>
@@ -15544,11 +15545,11 @@
         <v>55</v>
       </c>
       <c r="G298" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H298" s="5"/>
       <c r="I298" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J298" s="5"/>
     </row>
@@ -15557,7 +15558,7 @@
         <v>2402</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C299" s="4">
         <v>24</v>
@@ -15570,11 +15571,11 @@
         <v>55</v>
       </c>
       <c r="G299" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H299" s="4"/>
       <c r="I299" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J299" s="5"/>
     </row>
@@ -15583,7 +15584,7 @@
         <v>2403</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C300" s="4">
         <v>24</v>
@@ -15597,7 +15598,7 @@
       </c>
       <c r="G300" s="5"/>
       <c r="I300" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J300" s="1" t="b">
         <v>1</v>
@@ -15624,7 +15625,7 @@
         <v>25</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C301" s="4">
         <v>2</v>
@@ -15639,7 +15640,7 @@
       <c r="G301" s="5"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J301" s="5"/>
     </row>
@@ -15648,7 +15649,7 @@
         <v>2501</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C302" s="4">
         <v>25</v>
@@ -15661,11 +15662,11 @@
         <v>55</v>
       </c>
       <c r="G302" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J302" s="5"/>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Calibration_Chj\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4759B9FC-5E48-472A-ABA4-80E3520D16AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0EFC8E-BF32-442B-B538-730891BFD9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -32,16 +32,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="383">
   <si>
     <t>Id</t>
   </si>
@@ -1032,6 +1033,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>CugaCalibration.ViewModels.Common.Windows.Tools.Alignment.AlignmentWindow</t>
@@ -1041,6 +1043,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>BrightField</t>
@@ -1050,6 +1053,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ViewModel</t>
@@ -1064,6 +1068,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dark</t>
@@ -1073,6 +1078,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Field</t>
@@ -1082,6 +1088,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Alignment</t>
@@ -1178,9 +1185,6 @@
     <t>ADS Diagnosis</t>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Diagnosis.AdsDiagnosisWindowViewModel</t>
-  </si>
-  <si>
     <t>RTFC Diagnosis</t>
   </si>
   <si>
@@ -1242,6 +1246,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.AOD.AODDelayViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADS XY Move Diagnosis</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Diagnosis.AdsDiagnosisWindowViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Diagnosis.AdsXYMoveDiagnosisWindowViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1261,18 +1277,21 @@
       <sz val="18"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1280,6 +1299,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1287,6 +1307,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1294,6 +1315,7 @@
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -7412,7 +7434,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z302"/>
+  <dimension ref="A1:Z303"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -13779,7 +13801,7 @@
         <v>55</v>
       </c>
       <c r="G229" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
@@ -13805,7 +13827,7 @@
         <v>55</v>
       </c>
       <c r="G230" s="23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5" t="s">
@@ -13845,7 +13867,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="23" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C233" s="4">
         <v>1</v>
@@ -13869,7 +13891,7 @@
         <v>1501</v>
       </c>
       <c r="B234" s="23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
@@ -13882,11 +13904,11 @@
         <v>55</v>
       </c>
       <c r="G234" s="23" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H234" s="5"/>
       <c r="I234" s="23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J234" s="5"/>
     </row>
@@ -13895,7 +13917,7 @@
         <v>1502</v>
       </c>
       <c r="B235" s="23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C235" s="4">
         <v>15</v>
@@ -13908,7 +13930,7 @@
         <v>55</v>
       </c>
       <c r="G235" s="23" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H235" s="5"/>
       <c r="I235" s="5" t="s">
@@ -15468,8 +15490,8 @@
       <c r="F295" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G295" s="5" t="s">
-        <v>361</v>
+      <c r="G295" s="14" t="s">
+        <v>381</v>
       </c>
       <c r="H295" s="4"/>
       <c r="I295" s="5" t="s">
@@ -15482,7 +15504,7 @@
         <v>23062</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C296" s="4">
         <v>2306</v>
@@ -15495,180 +15517,206 @@
         <v>55</v>
       </c>
       <c r="G296" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H296" s="5"/>
       <c r="I296" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J296" s="5"/>
     </row>
     <row r="297" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
-        <v>24</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>364</v>
+        <v>23063</v>
+      </c>
+      <c r="B297" s="14" t="s">
+        <v>380</v>
       </c>
       <c r="C297" s="4">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D297" s="4">
-        <v>24</v>
-      </c>
-      <c r="E297" s="5"/>
+        <v>23063</v>
+      </c>
+      <c r="E297" s="4"/>
       <c r="F297" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G297" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G297" s="14" t="s">
+        <v>382</v>
+      </c>
       <c r="H297" s="5"/>
-      <c r="I297" s="5" t="s">
-        <v>364</v>
+      <c r="I297" s="14" t="s">
+        <v>380</v>
       </c>
       <c r="J297" s="5"/>
     </row>
     <row r="298" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
-        <v>2401</v>
+        <v>24</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C298" s="4">
+        <v>2</v>
+      </c>
+      <c r="D298" s="4">
         <v>24</v>
-      </c>
-      <c r="D298" s="4">
-        <v>2401</v>
       </c>
       <c r="E298" s="5"/>
       <c r="F298" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G298" s="5" t="s">
-        <v>366</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G298" s="5"/>
       <c r="H298" s="5"/>
       <c r="I298" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J298" s="5"/>
     </row>
     <row r="299" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C299" s="4">
         <v>24</v>
       </c>
       <c r="D299" s="4">
-        <v>2402</v>
-      </c>
-      <c r="E299" s="4"/>
+        <v>2401</v>
+      </c>
+      <c r="E299" s="5"/>
       <c r="F299" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G299" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="H299" s="4"/>
+        <v>365</v>
+      </c>
+      <c r="H299" s="5"/>
       <c r="I299" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J299" s="5"/>
     </row>
-    <row r="300" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C300" s="4">
         <v>24</v>
       </c>
       <c r="D300" s="4">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G300" s="5"/>
-      <c r="I300" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="J300" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K300"/>
-      <c r="L300"/>
-      <c r="M300"/>
-      <c r="N300"/>
-      <c r="O300"/>
-      <c r="P300"/>
-      <c r="Q300"/>
-      <c r="R300"/>
-      <c r="S300"/>
-      <c r="T300"/>
-      <c r="U300"/>
-      <c r="V300"/>
-      <c r="W300"/>
-      <c r="X300"/>
-      <c r="Y300"/>
-      <c r="Z300" s="16"/>
-    </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="G300" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="H300" s="4"/>
+      <c r="I300" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="J300" s="5"/>
+    </row>
+    <row r="301" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
-        <v>25</v>
+        <v>2403</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C301" s="4">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D301" s="4">
-        <v>25</v>
+        <v>2403</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G301" s="5"/>
-      <c r="H301" s="5"/>
-      <c r="I301" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="J301" s="5"/>
+      <c r="I301" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="J301" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K301"/>
+      <c r="L301"/>
+      <c r="M301"/>
+      <c r="N301"/>
+      <c r="O301"/>
+      <c r="P301"/>
+      <c r="Q301"/>
+      <c r="R301"/>
+      <c r="S301"/>
+      <c r="T301"/>
+      <c r="U301"/>
+      <c r="V301"/>
+      <c r="W301"/>
+      <c r="X301"/>
+      <c r="Y301"/>
+      <c r="Z301" s="16"/>
     </row>
     <row r="302" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
-        <v>2501</v>
+        <v>25</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C302" s="4">
+        <v>2</v>
+      </c>
+      <c r="D302" s="4">
         <v>25</v>
       </c>
-      <c r="D302" s="4">
-        <v>2501</v>
-      </c>
-      <c r="E302" s="5"/>
+      <c r="E302" s="4"/>
       <c r="F302" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G302" s="5" t="s">
-        <v>373</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G302" s="5"/>
       <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="J302" s="5"/>
+    </row>
+    <row r="303" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A303" s="4">
+        <v>2501</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C303" s="4">
+        <v>25</v>
+      </c>
+      <c r="D303" s="4">
+        <v>2501</v>
+      </c>
+      <c r="E303" s="5"/>
+      <c r="F303" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G303" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="J302" s="5"/>
+      <c r="H303" s="5"/>
+      <c r="I303" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="J303" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Calibration_Chj\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0EFC8E-BF32-442B-B538-730891BFD9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41666820-1823-471A-9A6C-A960EEE2BE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,17 +32,16 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="383">
   <si>
     <t>Id</t>
   </si>
@@ -1033,7 +1032,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>CugaCalibration.ViewModels.Common.Windows.Tools.Alignment.AlignmentWindow</t>
@@ -1043,7 +1041,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>BrightField</t>
@@ -1053,7 +1050,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ViewModel</t>
@@ -1068,7 +1064,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dark</t>
@@ -1078,7 +1073,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Field</t>
@@ -1088,7 +1082,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Alignment</t>
@@ -1161,15 +1154,6 @@
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.GrabbingDarkImagePointToPointWindowViewModel</t>
   </si>
   <si>
-    <t>Gain Illumination Dark Image</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.GranIlluminationDarkImageWindowViewModel</t>
-  </si>
-  <si>
-    <t>Gran Illumination Dark Image</t>
-  </si>
-  <si>
     <t>Create Dark Image Template</t>
   </si>
   <si>
@@ -1249,15 +1233,27 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Diagnosis.AdsDiagnosisWindowViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>ADS XY Move Diagnosis</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Diagnosis.AdsDiagnosisWindowViewModel</t>
+    <t>CugaCalibration.ViewModels.Common.Windows.Diagnosis.AdsXYMoveDiagnosisWindowViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Diagnosis.AdsXYMoveDiagnosisWindowViewModel</t>
+    <t>Optics</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Optics.OpticsObjectiveYAngleWindowViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Objective Y Angle</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1277,21 +1273,18 @@
       <sz val="18"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1299,7 +1292,6 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1307,7 +1299,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1315,7 +1306,6 @@
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1346,7 +1336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1370,15 +1360,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1389,30 +1370,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1458,11 +1415,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1482,6 +1439,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1490,31 +1450,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1523,7 +1465,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
@@ -1981,525 +1923,525 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="12">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="12">
         <v>666666</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="13">
         <v>1</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="13"/>
+      <c r="F3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="13">
         <v>666666</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="13">
         <v>1</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="21" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="13">
         <v>111111</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
     </row>
     <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
     </row>
     <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
     </row>
     <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
     </row>
     <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
     </row>
     <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
     </row>
     <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
     </row>
     <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
     </row>
     <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
     </row>
     <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
     </row>
     <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
     </row>
     <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
     </row>
     <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
     </row>
     <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
     </row>
     <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
     </row>
     <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
     </row>
     <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
     </row>
     <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
     </row>
     <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
     </row>
     <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2533,172 +2475,172 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="13">
         <v>3</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2727,172 +2669,172 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="13">
         <v>3</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2930,340 +2872,340 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="12">
         <v>-1</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="12">
         <v>0</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="12">
         <v>1</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="13">
         <v>-1</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="13">
         <v>3</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+      <c r="A4" s="13">
         <v>21</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="18">
-        <v>2</v>
-      </c>
-      <c r="D4" s="18">
+      <c r="C4" s="13">
+        <v>2</v>
+      </c>
+      <c r="D4" s="13">
         <v>21</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="13">
         <v>3</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="13" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18">
+      <c r="A5" s="13">
         <v>211</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="13">
         <v>21</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="13">
         <v>211</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="13">
         <v>212</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="13">
         <v>21</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="13">
         <v>212</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="13">
         <v>3</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
+      <c r="A7" s="13">
         <v>22</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="18">
-        <v>2</v>
-      </c>
-      <c r="D7" s="18">
+      <c r="C7" s="13">
+        <v>2</v>
+      </c>
+      <c r="D7" s="13">
         <v>22</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="13">
         <v>3</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="13">
         <v>221</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="13">
         <v>22</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="13">
         <v>221</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="13">
         <v>3</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
+      <c r="A9" s="13">
         <v>222</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="13">
         <v>22</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="13">
         <v>222</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="13">
         <v>3</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
     </row>
     <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
     </row>
     <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
     </row>
     <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
     </row>
     <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
     </row>
     <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3298,234 +3240,234 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="12">
         <v>0</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="12">
         <v>1</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3562,234 +3504,234 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="12">
         <v>0</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="12">
         <v>1</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3818,154 +3760,154 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3994,10 +3936,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="12">
         <v>2</v>
       </c>
       <c r="C2" s="4">
@@ -4005,10 +3947,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12">
         <v>2</v>
       </c>
       <c r="C3" s="4">
@@ -4016,10 +3958,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="12">
         <v>2</v>
       </c>
       <c r="C4" s="4">
@@ -4027,10 +3969,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="12">
         <v>2</v>
       </c>
       <c r="C5" s="4">
@@ -4038,10 +3980,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="12">
         <v>2</v>
       </c>
       <c r="C6" s="4">
@@ -4049,10 +3991,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="12">
         <v>2</v>
       </c>
       <c r="C7" s="4">
@@ -4060,10 +4002,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="12">
         <v>2</v>
       </c>
       <c r="C8" s="4">
@@ -4071,10 +4013,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="12">
         <v>2</v>
       </c>
       <c r="C9" s="4">
@@ -4082,10 +4024,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17">
+      <c r="A10" s="12">
         <v>9</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="12">
         <v>2</v>
       </c>
       <c r="C10" s="4">
@@ -4093,10 +4035,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="17">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="12">
         <v>2</v>
       </c>
       <c r="C11" s="4">
@@ -4104,10 +4046,10 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="12">
         <v>2</v>
       </c>
       <c r="C12" s="4">
@@ -4115,10 +4057,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="17">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="12">
         <v>2</v>
       </c>
       <c r="C13" s="4">
@@ -4126,10 +4068,10 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="17">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="12">
         <v>2</v>
       </c>
       <c r="C14" s="4">
@@ -4137,10 +4079,10 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="12">
         <v>2</v>
       </c>
       <c r="C15" s="4">
@@ -4148,10 +4090,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="17">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="12">
         <v>2</v>
       </c>
       <c r="C16" s="4">
@@ -4159,10 +4101,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="17">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="12">
         <v>2</v>
       </c>
       <c r="C17" s="4">
@@ -4170,10 +4112,10 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="12">
         <v>2</v>
       </c>
       <c r="C18" s="4">
@@ -4181,10 +4123,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17">
+      <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="12">
         <v>2</v>
       </c>
       <c r="C19" s="4">
@@ -4192,10 +4134,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="17">
+      <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="12">
         <v>2</v>
       </c>
       <c r="C20" s="4">
@@ -4203,10 +4145,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="12">
         <v>2</v>
       </c>
       <c r="C21" s="4">
@@ -4214,10 +4156,10 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="17">
+      <c r="A22" s="12">
         <v>21</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="12">
         <v>2</v>
       </c>
       <c r="C22" s="4">
@@ -4225,10 +4167,10 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17">
+      <c r="A23" s="12">
         <v>22</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="12">
         <v>2</v>
       </c>
       <c r="C23" s="4">
@@ -4236,10 +4178,10 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18">
+      <c r="A24" s="13">
         <v>23</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="12">
         <v>2</v>
       </c>
       <c r="C24" s="4">
@@ -4247,10 +4189,10 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="17">
+      <c r="A25" s="12">
         <v>24</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="12">
         <v>2</v>
       </c>
       <c r="C25" s="4">
@@ -4258,10 +4200,10 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="17">
+      <c r="A26" s="12">
         <v>25</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="12">
         <v>2</v>
       </c>
       <c r="C26" s="4">
@@ -4269,10 +4211,10 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+      <c r="A27" s="13">
         <v>26</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="12">
         <v>2</v>
       </c>
       <c r="C27" s="4">
@@ -4280,10 +4222,10 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="17">
+      <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="12">
         <v>2</v>
       </c>
       <c r="C28" s="4">
@@ -4291,10 +4233,10 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="17">
+      <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="12">
         <v>2</v>
       </c>
       <c r="C29" s="4">
@@ -4302,10 +4244,10 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18">
+      <c r="A30" s="13">
         <v>29</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="12">
         <v>2</v>
       </c>
       <c r="C30" s="4">
@@ -4313,10 +4255,10 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17">
+      <c r="A31" s="12">
         <v>30</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="12">
         <v>2</v>
       </c>
       <c r="C31" s="4">
@@ -4324,10 +4266,10 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="17">
+      <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="12">
         <v>2</v>
       </c>
       <c r="C32" s="4">
@@ -4335,10 +4277,10 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="18">
+      <c r="A33" s="13">
         <v>32</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="12">
         <v>2</v>
       </c>
       <c r="C33" s="4">
@@ -4346,10 +4288,10 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="17">
+      <c r="A34" s="12">
         <v>33</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="12">
         <v>2</v>
       </c>
       <c r="C34" s="4">
@@ -4357,10 +4299,10 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="17">
+      <c r="A35" s="12">
         <v>34</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="12">
         <v>2</v>
       </c>
       <c r="C35" s="4">
@@ -4368,10 +4310,10 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="18">
+      <c r="A36" s="13">
         <v>35</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="12">
         <v>2</v>
       </c>
       <c r="C36" s="4">
@@ -4379,10 +4321,10 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="17">
+      <c r="A37" s="12">
         <v>36</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="12">
         <v>2</v>
       </c>
       <c r="C37" s="4">
@@ -4390,10 +4332,10 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="17">
+      <c r="A38" s="12">
         <v>37</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="12">
         <v>2</v>
       </c>
       <c r="C38" s="4">
@@ -4401,10 +4343,10 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="18">
+      <c r="A39" s="13">
         <v>38</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="12">
         <v>2</v>
       </c>
       <c r="C39" s="4">
@@ -4412,10 +4354,10 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="17">
+      <c r="A40" s="12">
         <v>39</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="12">
         <v>2</v>
       </c>
       <c r="C40" s="4">
@@ -4423,10 +4365,10 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="17">
+      <c r="A41" s="12">
         <v>40</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="12">
         <v>2</v>
       </c>
       <c r="C41" s="4">
@@ -4434,10 +4376,10 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="18">
+      <c r="A42" s="13">
         <v>41</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="12">
         <v>2</v>
       </c>
       <c r="C42" s="4">
@@ -4445,10 +4387,10 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="17">
+      <c r="A43" s="12">
         <v>42</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="12">
         <v>2</v>
       </c>
       <c r="C43" s="4">
@@ -4456,10 +4398,10 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="17">
+      <c r="A44" s="12">
         <v>43</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="12">
         <v>2</v>
       </c>
       <c r="C44" s="4">
@@ -4467,10 +4409,10 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="18">
+      <c r="A45" s="13">
         <v>44</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="12">
         <v>2</v>
       </c>
       <c r="C45" s="4">
@@ -4478,10 +4420,10 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="17">
+      <c r="A46" s="12">
         <v>45</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="12">
         <v>2</v>
       </c>
       <c r="C46" s="4">
@@ -4489,10 +4431,10 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="17">
+      <c r="A47" s="12">
         <v>46</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="12">
         <v>2</v>
       </c>
       <c r="C47" s="4">
@@ -4500,10 +4442,10 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="18">
+      <c r="A48" s="13">
         <v>47</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="12">
         <v>2</v>
       </c>
       <c r="C48" s="4">
@@ -4511,10 +4453,10 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="17">
+      <c r="A49" s="12">
         <v>48</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="12">
         <v>2</v>
       </c>
       <c r="C49" s="4">
@@ -4522,10 +4464,10 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="17">
+      <c r="A50" s="12">
         <v>49</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="12">
         <v>2</v>
       </c>
       <c r="C50" s="4">
@@ -4533,10 +4475,10 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="18">
+      <c r="A51" s="13">
         <v>50</v>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="12">
         <v>2</v>
       </c>
       <c r="C51" s="4">
@@ -4544,10 +4486,10 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="17">
+      <c r="A52" s="12">
         <v>51</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="12">
         <v>2</v>
       </c>
       <c r="C52" s="4">
@@ -4555,10 +4497,10 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="17">
+      <c r="A53" s="12">
         <v>52</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="12">
         <v>2</v>
       </c>
       <c r="C53" s="4">
@@ -4566,10 +4508,10 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="18">
+      <c r="A54" s="13">
         <v>53</v>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="12">
         <v>2</v>
       </c>
       <c r="C54" s="4">
@@ -4577,10 +4519,10 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="17">
+      <c r="A55" s="12">
         <v>54</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="12">
         <v>2</v>
       </c>
       <c r="C55" s="4">
@@ -4588,10 +4530,10 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="17">
+      <c r="A56" s="12">
         <v>55</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="12">
         <v>2</v>
       </c>
       <c r="C56" s="4">
@@ -4599,10 +4541,10 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="18">
+      <c r="A57" s="13">
         <v>56</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="12">
         <v>2</v>
       </c>
       <c r="C57" s="4">
@@ -4610,10 +4552,10 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="17">
+      <c r="A58" s="12">
         <v>57</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="12">
         <v>2</v>
       </c>
       <c r="C58" s="4">
@@ -4621,10 +4563,10 @@
       </c>
     </row>
     <row r="59" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="17">
-        <v>58</v>
-      </c>
-      <c r="B59" s="17">
+      <c r="A59" s="12">
+        <v>58</v>
+      </c>
+      <c r="B59" s="12">
         <v>2</v>
       </c>
       <c r="C59" s="4">
@@ -4632,10 +4574,10 @@
       </c>
     </row>
     <row r="60" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="17">
+      <c r="A60" s="12">
         <v>59</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B60" s="12">
         <v>2</v>
       </c>
       <c r="C60" s="4">
@@ -4643,10 +4585,10 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="17">
+      <c r="A61" s="12">
         <v>60</v>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="12">
         <v>2</v>
       </c>
       <c r="C61" s="4">
@@ -4654,10 +4596,10 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="17">
+      <c r="A62" s="12">
         <v>61</v>
       </c>
-      <c r="B62" s="17">
+      <c r="B62" s="12">
         <v>2</v>
       </c>
       <c r="C62" s="4">
@@ -4665,10 +4607,10 @@
       </c>
     </row>
     <row r="63" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="17">
+      <c r="A63" s="12">
         <v>62</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="12">
         <v>2</v>
       </c>
       <c r="C63" s="4">
@@ -4676,10 +4618,10 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="17">
+      <c r="A64" s="12">
         <v>63</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="12">
         <v>2</v>
       </c>
       <c r="C64" s="4">
@@ -4687,10 +4629,10 @@
       </c>
     </row>
     <row r="65" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="17">
+      <c r="A65" s="12">
         <v>64</v>
       </c>
-      <c r="B65" s="17">
+      <c r="B65" s="12">
         <v>2</v>
       </c>
       <c r="C65" s="4">
@@ -4698,10 +4640,10 @@
       </c>
     </row>
     <row r="66" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="17">
+      <c r="A66" s="12">
         <v>65</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="12">
         <v>2</v>
       </c>
       <c r="C66" s="4">
@@ -4709,10 +4651,10 @@
       </c>
     </row>
     <row r="67" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="17">
+      <c r="A67" s="12">
         <v>66</v>
       </c>
-      <c r="B67" s="17">
+      <c r="B67" s="12">
         <v>2</v>
       </c>
       <c r="C67" s="4">
@@ -4720,10 +4662,10 @@
       </c>
     </row>
     <row r="68" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="17">
+      <c r="A68" s="12">
         <v>67</v>
       </c>
-      <c r="B68" s="17">
+      <c r="B68" s="12">
         <v>2</v>
       </c>
       <c r="C68" s="4">
@@ -4731,10 +4673,10 @@
       </c>
     </row>
     <row r="69" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="17">
+      <c r="A69" s="12">
         <v>68</v>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="12">
         <v>2</v>
       </c>
       <c r="C69" s="4">
@@ -4742,10 +4684,10 @@
       </c>
     </row>
     <row r="70" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="17">
+      <c r="A70" s="12">
         <v>69</v>
       </c>
-      <c r="B70" s="17">
+      <c r="B70" s="12">
         <v>2</v>
       </c>
       <c r="C70" s="4">
@@ -4753,10 +4695,10 @@
       </c>
     </row>
     <row r="71" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="17">
+      <c r="A71" s="12">
         <v>70</v>
       </c>
-      <c r="B71" s="17">
+      <c r="B71" s="12">
         <v>2</v>
       </c>
       <c r="C71" s="4">
@@ -4764,10 +4706,10 @@
       </c>
     </row>
     <row r="72" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="17">
+      <c r="A72" s="12">
         <v>71</v>
       </c>
-      <c r="B72" s="17">
+      <c r="B72" s="12">
         <v>2</v>
       </c>
       <c r="C72" s="4">
@@ -4775,10 +4717,10 @@
       </c>
     </row>
     <row r="73" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="17">
+      <c r="A73" s="12">
         <v>72</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="12">
         <v>2</v>
       </c>
       <c r="C73" s="4">
@@ -4786,10 +4728,10 @@
       </c>
     </row>
     <row r="74" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="17">
+      <c r="A74" s="12">
         <v>73</v>
       </c>
-      <c r="B74" s="17">
+      <c r="B74" s="12">
         <v>2</v>
       </c>
       <c r="C74" s="4">
@@ -4797,10 +4739,10 @@
       </c>
     </row>
     <row r="75" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="17">
+      <c r="A75" s="12">
         <v>74</v>
       </c>
-      <c r="B75" s="17">
+      <c r="B75" s="12">
         <v>2</v>
       </c>
       <c r="C75" s="4">
@@ -4808,10 +4750,10 @@
       </c>
     </row>
     <row r="76" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="17">
+      <c r="A76" s="12">
         <v>75</v>
       </c>
-      <c r="B76" s="17">
+      <c r="B76" s="12">
         <v>2</v>
       </c>
       <c r="C76" s="4">
@@ -4819,10 +4761,10 @@
       </c>
     </row>
     <row r="77" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="17">
+      <c r="A77" s="12">
         <v>76</v>
       </c>
-      <c r="B77" s="17">
+      <c r="B77" s="12">
         <v>2</v>
       </c>
       <c r="C77" s="4">
@@ -4830,10 +4772,10 @@
       </c>
     </row>
     <row r="78" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="17">
+      <c r="A78" s="12">
         <v>77</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="12">
         <v>2</v>
       </c>
       <c r="C78" s="4">
@@ -4841,10 +4783,10 @@
       </c>
     </row>
     <row r="79" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="17">
+      <c r="A79" s="12">
         <v>78</v>
       </c>
-      <c r="B79" s="17">
+      <c r="B79" s="12">
         <v>2</v>
       </c>
       <c r="C79" s="4">
@@ -4852,10 +4794,10 @@
       </c>
     </row>
     <row r="80" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="17">
+      <c r="A80" s="12">
         <v>79</v>
       </c>
-      <c r="B80" s="17">
+      <c r="B80" s="12">
         <v>2</v>
       </c>
       <c r="C80" s="4">
@@ -4863,10 +4805,10 @@
       </c>
     </row>
     <row r="81" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="17">
+      <c r="A81" s="12">
         <v>80</v>
       </c>
-      <c r="B81" s="17">
+      <c r="B81" s="12">
         <v>2</v>
       </c>
       <c r="C81" s="4">
@@ -4874,10 +4816,10 @@
       </c>
     </row>
     <row r="82" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="17">
+      <c r="A82" s="12">
         <v>81</v>
       </c>
-      <c r="B82" s="17">
+      <c r="B82" s="12">
         <v>2</v>
       </c>
       <c r="C82" s="4">
@@ -4885,10 +4827,10 @@
       </c>
     </row>
     <row r="83" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="17">
+      <c r="A83" s="12">
         <v>82</v>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="12">
         <v>2</v>
       </c>
       <c r="C83" s="4">
@@ -4896,10 +4838,10 @@
       </c>
     </row>
     <row r="84" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="17">
+      <c r="A84" s="12">
         <v>83</v>
       </c>
-      <c r="B84" s="17">
+      <c r="B84" s="12">
         <v>2</v>
       </c>
       <c r="C84" s="4">
@@ -4907,10 +4849,10 @@
       </c>
     </row>
     <row r="85" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="17">
+      <c r="A85" s="12">
         <v>84</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="12">
         <v>2</v>
       </c>
       <c r="C85" s="4">
@@ -4918,10 +4860,10 @@
       </c>
     </row>
     <row r="86" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="17">
+      <c r="A86" s="12">
         <v>85</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B86" s="12">
         <v>2</v>
       </c>
       <c r="C86" s="4">
@@ -4929,10 +4871,10 @@
       </c>
     </row>
     <row r="87" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="17">
+      <c r="A87" s="12">
         <v>86</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B87" s="12">
         <v>2</v>
       </c>
       <c r="C87" s="4">
@@ -4940,10 +4882,10 @@
       </c>
     </row>
     <row r="88" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="17">
+      <c r="A88" s="12">
         <v>87</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B88" s="12">
         <v>2</v>
       </c>
       <c r="C88" s="4">
@@ -4951,10 +4893,10 @@
       </c>
     </row>
     <row r="89" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="17">
+      <c r="A89" s="12">
         <v>88</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B89" s="12">
         <v>2</v>
       </c>
       <c r="C89" s="4">
@@ -4962,10 +4904,10 @@
       </c>
     </row>
     <row r="90" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="17">
+      <c r="A90" s="12">
         <v>89</v>
       </c>
-      <c r="B90" s="17">
+      <c r="B90" s="12">
         <v>2</v>
       </c>
       <c r="C90" s="4">
@@ -4973,10 +4915,10 @@
       </c>
     </row>
     <row r="91" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="17">
+      <c r="A91" s="12">
         <v>90</v>
       </c>
-      <c r="B91" s="17">
+      <c r="B91" s="12">
         <v>2</v>
       </c>
       <c r="C91" s="4">
@@ -4984,10 +4926,10 @@
       </c>
     </row>
     <row r="92" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="17">
+      <c r="A92" s="12">
         <v>91</v>
       </c>
-      <c r="B92" s="17">
+      <c r="B92" s="12">
         <v>2</v>
       </c>
       <c r="C92" s="4">
@@ -4995,10 +4937,10 @@
       </c>
     </row>
     <row r="93" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="17">
+      <c r="A93" s="12">
         <v>92</v>
       </c>
-      <c r="B93" s="17">
+      <c r="B93" s="12">
         <v>2</v>
       </c>
       <c r="C93" s="4">
@@ -5006,10 +4948,10 @@
       </c>
     </row>
     <row r="94" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="17">
+      <c r="A94" s="12">
         <v>93</v>
       </c>
-      <c r="B94" s="17">
+      <c r="B94" s="12">
         <v>2</v>
       </c>
       <c r="C94" s="4">
@@ -5017,10 +4959,10 @@
       </c>
     </row>
     <row r="95" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="17">
+      <c r="A95" s="12">
         <v>94</v>
       </c>
-      <c r="B95" s="17">
+      <c r="B95" s="12">
         <v>2</v>
       </c>
       <c r="C95" s="4">
@@ -5028,10 +4970,10 @@
       </c>
     </row>
     <row r="96" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="17">
+      <c r="A96" s="12">
         <v>95</v>
       </c>
-      <c r="B96" s="17">
+      <c r="B96" s="12">
         <v>2</v>
       </c>
       <c r="C96" s="4">
@@ -5039,10 +4981,10 @@
       </c>
     </row>
     <row r="97" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="17">
+      <c r="A97" s="12">
         <v>96</v>
       </c>
-      <c r="B97" s="17">
+      <c r="B97" s="12">
         <v>2</v>
       </c>
       <c r="C97" s="4">
@@ -5050,10 +4992,10 @@
       </c>
     </row>
     <row r="98" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="17">
+      <c r="A98" s="12">
         <v>97</v>
       </c>
-      <c r="B98" s="17">
+      <c r="B98" s="12">
         <v>2</v>
       </c>
       <c r="C98" s="4">
@@ -5061,10 +5003,10 @@
       </c>
     </row>
     <row r="99" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="17">
+      <c r="A99" s="12">
         <v>98</v>
       </c>
-      <c r="B99" s="17">
+      <c r="B99" s="12">
         <v>2</v>
       </c>
       <c r="C99" s="4">
@@ -5072,10 +5014,10 @@
       </c>
     </row>
     <row r="100" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="17">
+      <c r="A100" s="12">
         <v>99</v>
       </c>
-      <c r="B100" s="17">
+      <c r="B100" s="12">
         <v>2</v>
       </c>
       <c r="C100" s="4">
@@ -5083,10 +5025,10 @@
       </c>
     </row>
     <row r="101" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="17">
+      <c r="A101" s="12">
         <v>100</v>
       </c>
-      <c r="B101" s="17">
+      <c r="B101" s="12">
         <v>2</v>
       </c>
       <c r="C101" s="4">
@@ -5094,10 +5036,10 @@
       </c>
     </row>
     <row r="102" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="17">
+      <c r="A102" s="12">
         <v>101</v>
       </c>
-      <c r="B102" s="17">
+      <c r="B102" s="12">
         <v>2</v>
       </c>
       <c r="C102" s="4">
@@ -5105,10 +5047,10 @@
       </c>
     </row>
     <row r="103" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="17">
+      <c r="A103" s="12">
         <v>102</v>
       </c>
-      <c r="B103" s="17">
+      <c r="B103" s="12">
         <v>2</v>
       </c>
       <c r="C103" s="4">
@@ -5116,10 +5058,10 @@
       </c>
     </row>
     <row r="104" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="17">
+      <c r="A104" s="12">
         <v>103</v>
       </c>
-      <c r="B104" s="17">
+      <c r="B104" s="12">
         <v>2</v>
       </c>
       <c r="C104" s="4">
@@ -5127,10 +5069,10 @@
       </c>
     </row>
     <row r="105" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="17">
+      <c r="A105" s="12">
         <v>104</v>
       </c>
-      <c r="B105" s="17">
+      <c r="B105" s="12">
         <v>2</v>
       </c>
       <c r="C105" s="4">
@@ -5138,10 +5080,10 @@
       </c>
     </row>
     <row r="106" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="17">
+      <c r="A106" s="12">
         <v>105</v>
       </c>
-      <c r="B106" s="17">
+      <c r="B106" s="12">
         <v>2</v>
       </c>
       <c r="C106" s="4">
@@ -5149,10 +5091,10 @@
       </c>
     </row>
     <row r="107" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="17">
+      <c r="A107" s="12">
         <v>106</v>
       </c>
-      <c r="B107" s="17">
+      <c r="B107" s="12">
         <v>2</v>
       </c>
       <c r="C107" s="4">
@@ -5160,10 +5102,10 @@
       </c>
     </row>
     <row r="108" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="17">
+      <c r="A108" s="12">
         <v>107</v>
       </c>
-      <c r="B108" s="17">
+      <c r="B108" s="12">
         <v>2</v>
       </c>
       <c r="C108" s="4">
@@ -5171,10 +5113,10 @@
       </c>
     </row>
     <row r="109" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="17">
+      <c r="A109" s="12">
         <v>108</v>
       </c>
-      <c r="B109" s="17">
+      <c r="B109" s="12">
         <v>2</v>
       </c>
       <c r="C109" s="4">
@@ -5182,10 +5124,10 @@
       </c>
     </row>
     <row r="110" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="17">
+      <c r="A110" s="12">
         <v>109</v>
       </c>
-      <c r="B110" s="17">
+      <c r="B110" s="12">
         <v>2</v>
       </c>
       <c r="C110" s="4">
@@ -5193,10 +5135,10 @@
       </c>
     </row>
     <row r="111" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="17">
+      <c r="A111" s="12">
         <v>110</v>
       </c>
-      <c r="B111" s="17">
+      <c r="B111" s="12">
         <v>2</v>
       </c>
       <c r="C111" s="4">
@@ -5204,10 +5146,10 @@
       </c>
     </row>
     <row r="112" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="17">
+      <c r="A112" s="12">
         <v>111</v>
       </c>
-      <c r="B112" s="17">
+      <c r="B112" s="12">
         <v>2</v>
       </c>
       <c r="C112" s="4">
@@ -5215,10 +5157,10 @@
       </c>
     </row>
     <row r="113" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="17">
+      <c r="A113" s="12">
         <v>112</v>
       </c>
-      <c r="B113" s="17">
+      <c r="B113" s="12">
         <v>2</v>
       </c>
       <c r="C113" s="4">
@@ -5226,10 +5168,10 @@
       </c>
     </row>
     <row r="114" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="17">
+      <c r="A114" s="12">
         <v>113</v>
       </c>
-      <c r="B114" s="17">
+      <c r="B114" s="12">
         <v>2</v>
       </c>
       <c r="C114" s="4">
@@ -5237,10 +5179,10 @@
       </c>
     </row>
     <row r="115" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="17">
+      <c r="A115" s="12">
         <v>114</v>
       </c>
-      <c r="B115" s="17">
+      <c r="B115" s="12">
         <v>2</v>
       </c>
       <c r="C115" s="4">
@@ -5248,10 +5190,10 @@
       </c>
     </row>
     <row r="116" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="17">
+      <c r="A116" s="12">
         <v>115</v>
       </c>
-      <c r="B116" s="17">
+      <c r="B116" s="12">
         <v>2</v>
       </c>
       <c r="C116" s="4">
@@ -5259,10 +5201,10 @@
       </c>
     </row>
     <row r="117" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="17">
+      <c r="A117" s="12">
         <v>116</v>
       </c>
-      <c r="B117" s="17">
+      <c r="B117" s="12">
         <v>2</v>
       </c>
       <c r="C117" s="4">
@@ -5270,10 +5212,10 @@
       </c>
     </row>
     <row r="118" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="17">
+      <c r="A118" s="12">
         <v>117</v>
       </c>
-      <c r="B118" s="17">
+      <c r="B118" s="12">
         <v>2</v>
       </c>
       <c r="C118" s="4">
@@ -5281,10 +5223,10 @@
       </c>
     </row>
     <row r="119" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="17">
+      <c r="A119" s="12">
         <v>118</v>
       </c>
-      <c r="B119" s="17">
+      <c r="B119" s="12">
         <v>2</v>
       </c>
       <c r="C119" s="4">
@@ -5292,10 +5234,10 @@
       </c>
     </row>
     <row r="120" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="17">
+      <c r="A120" s="12">
         <v>119</v>
       </c>
-      <c r="B120" s="17">
+      <c r="B120" s="12">
         <v>2</v>
       </c>
       <c r="C120" s="4">
@@ -5303,10 +5245,10 @@
       </c>
     </row>
     <row r="121" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="17">
+      <c r="A121" s="12">
         <v>120</v>
       </c>
-      <c r="B121" s="17">
+      <c r="B121" s="12">
         <v>2</v>
       </c>
       <c r="C121" s="4">
@@ -5314,10 +5256,10 @@
       </c>
     </row>
     <row r="122" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="17">
+      <c r="A122" s="12">
         <v>121</v>
       </c>
-      <c r="B122" s="17">
+      <c r="B122" s="12">
         <v>2</v>
       </c>
       <c r="C122" s="4">
@@ -5325,10 +5267,10 @@
       </c>
     </row>
     <row r="123" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="17">
+      <c r="A123" s="12">
         <v>122</v>
       </c>
-      <c r="B123" s="17">
+      <c r="B123" s="12">
         <v>2</v>
       </c>
       <c r="C123" s="4">
@@ -5336,10 +5278,10 @@
       </c>
     </row>
     <row r="124" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="17">
+      <c r="A124" s="12">
         <v>123</v>
       </c>
-      <c r="B124" s="17">
+      <c r="B124" s="12">
         <v>2</v>
       </c>
       <c r="C124" s="4">
@@ -5347,10 +5289,10 @@
       </c>
     </row>
     <row r="125" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="17">
+      <c r="A125" s="12">
         <v>124</v>
       </c>
-      <c r="B125" s="17">
+      <c r="B125" s="12">
         <v>2</v>
       </c>
       <c r="C125" s="4">
@@ -5358,10 +5300,10 @@
       </c>
     </row>
     <row r="126" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="17">
+      <c r="A126" s="12">
         <v>125</v>
       </c>
-      <c r="B126" s="17">
+      <c r="B126" s="12">
         <v>2</v>
       </c>
       <c r="C126" s="4">
@@ -5369,10 +5311,10 @@
       </c>
     </row>
     <row r="127" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="17">
+      <c r="A127" s="12">
         <v>126</v>
       </c>
-      <c r="B127" s="17">
+      <c r="B127" s="12">
         <v>2</v>
       </c>
       <c r="C127" s="4">
@@ -5380,10 +5322,10 @@
       </c>
     </row>
     <row r="128" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="17">
+      <c r="A128" s="12">
         <v>127</v>
       </c>
-      <c r="B128" s="17">
+      <c r="B128" s="12">
         <v>2</v>
       </c>
       <c r="C128" s="4">
@@ -5391,10 +5333,10 @@
       </c>
     </row>
     <row r="129" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="17">
+      <c r="A129" s="12">
         <v>128</v>
       </c>
-      <c r="B129" s="17">
+      <c r="B129" s="12">
         <v>2</v>
       </c>
       <c r="C129" s="4">
@@ -5402,10 +5344,10 @@
       </c>
     </row>
     <row r="130" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="17">
+      <c r="A130" s="12">
         <v>129</v>
       </c>
-      <c r="B130" s="17">
+      <c r="B130" s="12">
         <v>2</v>
       </c>
       <c r="C130" s="4">
@@ -5413,10 +5355,10 @@
       </c>
     </row>
     <row r="131" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="17">
+      <c r="A131" s="12">
         <v>130</v>
       </c>
-      <c r="B131" s="17">
+      <c r="B131" s="12">
         <v>2</v>
       </c>
       <c r="C131" s="4">
@@ -5424,10 +5366,10 @@
       </c>
     </row>
     <row r="132" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="17">
+      <c r="A132" s="12">
         <v>131</v>
       </c>
-      <c r="B132" s="17">
+      <c r="B132" s="12">
         <v>2</v>
       </c>
       <c r="C132" s="4">
@@ -5435,10 +5377,10 @@
       </c>
     </row>
     <row r="133" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="17">
+      <c r="A133" s="12">
         <v>132</v>
       </c>
-      <c r="B133" s="17">
+      <c r="B133" s="12">
         <v>2</v>
       </c>
       <c r="C133" s="4">
@@ -5446,10 +5388,10 @@
       </c>
     </row>
     <row r="134" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="17">
+      <c r="A134" s="12">
         <v>133</v>
       </c>
-      <c r="B134" s="17">
+      <c r="B134" s="12">
         <v>2</v>
       </c>
       <c r="C134" s="4">
@@ -5457,10 +5399,10 @@
       </c>
     </row>
     <row r="135" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="17">
+      <c r="A135" s="12">
         <v>134</v>
       </c>
-      <c r="B135" s="17">
+      <c r="B135" s="12">
         <v>2</v>
       </c>
       <c r="C135" s="4">
@@ -5468,10 +5410,10 @@
       </c>
     </row>
     <row r="136" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="17">
+      <c r="A136" s="12">
         <v>135</v>
       </c>
-      <c r="B136" s="17">
+      <c r="B136" s="12">
         <v>2</v>
       </c>
       <c r="C136" s="4">
@@ -5479,10 +5421,10 @@
       </c>
     </row>
     <row r="137" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="17">
+      <c r="A137" s="12">
         <v>136</v>
       </c>
-      <c r="B137" s="17">
+      <c r="B137" s="12">
         <v>2</v>
       </c>
       <c r="C137" s="4">
@@ -5490,10 +5432,10 @@
       </c>
     </row>
     <row r="138" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="17">
+      <c r="A138" s="12">
         <v>137</v>
       </c>
-      <c r="B138" s="17">
+      <c r="B138" s="12">
         <v>2</v>
       </c>
       <c r="C138" s="4">
@@ -5501,10 +5443,10 @@
       </c>
     </row>
     <row r="139" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="17">
+      <c r="A139" s="12">
         <v>138</v>
       </c>
-      <c r="B139" s="17">
+      <c r="B139" s="12">
         <v>2</v>
       </c>
       <c r="C139" s="4">
@@ -5512,10 +5454,10 @@
       </c>
     </row>
     <row r="140" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="17">
+      <c r="A140" s="12">
         <v>139</v>
       </c>
-      <c r="B140" s="17">
+      <c r="B140" s="12">
         <v>2</v>
       </c>
       <c r="C140" s="4">
@@ -5523,10 +5465,10 @@
       </c>
     </row>
     <row r="141" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="17">
+      <c r="A141" s="12">
         <v>140</v>
       </c>
-      <c r="B141" s="17">
+      <c r="B141" s="12">
         <v>2</v>
       </c>
       <c r="C141" s="4">
@@ -5534,10 +5476,10 @@
       </c>
     </row>
     <row r="142" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="17">
+      <c r="A142" s="12">
         <v>141</v>
       </c>
-      <c r="B142" s="17">
+      <c r="B142" s="12">
         <v>2</v>
       </c>
       <c r="C142" s="4">
@@ -5545,10 +5487,10 @@
       </c>
     </row>
     <row r="143" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="17">
+      <c r="A143" s="12">
         <v>142</v>
       </c>
-      <c r="B143" s="17">
+      <c r="B143" s="12">
         <v>2</v>
       </c>
       <c r="C143" s="4">
@@ -5556,10 +5498,10 @@
       </c>
     </row>
     <row r="144" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="17">
+      <c r="A144" s="12">
         <v>122</v>
       </c>
-      <c r="B144" s="17">
+      <c r="B144" s="12">
         <v>2</v>
       </c>
       <c r="C144" s="4">
@@ -5567,10 +5509,10 @@
       </c>
     </row>
     <row r="145" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="17">
+      <c r="A145" s="12">
         <v>123</v>
       </c>
-      <c r="B145" s="17">
+      <c r="B145" s="12">
         <v>2</v>
       </c>
       <c r="C145" s="4">
@@ -5578,10 +5520,10 @@
       </c>
     </row>
     <row r="146" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="17">
+      <c r="A146" s="12">
         <v>124</v>
       </c>
-      <c r="B146" s="17">
+      <c r="B146" s="12">
         <v>2</v>
       </c>
       <c r="C146" s="4">
@@ -5589,10 +5531,10 @@
       </c>
     </row>
     <row r="147" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="17">
+      <c r="A147" s="12">
         <v>125</v>
       </c>
-      <c r="B147" s="17">
+      <c r="B147" s="12">
         <v>2</v>
       </c>
       <c r="C147" s="4">
@@ -5600,10 +5542,10 @@
       </c>
     </row>
     <row r="148" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="17">
+      <c r="A148" s="12">
         <v>126</v>
       </c>
-      <c r="B148" s="17">
+      <c r="B148" s="12">
         <v>2</v>
       </c>
       <c r="C148" s="4">
@@ -5611,10 +5553,10 @@
       </c>
     </row>
     <row r="149" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="17">
+      <c r="A149" s="12">
         <v>127</v>
       </c>
-      <c r="B149" s="17">
+      <c r="B149" s="12">
         <v>2</v>
       </c>
       <c r="C149" s="4">
@@ -5622,10 +5564,10 @@
       </c>
     </row>
     <row r="150" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="17">
+      <c r="A150" s="12">
         <v>128</v>
       </c>
-      <c r="B150" s="17">
+      <c r="B150" s="12">
         <v>2</v>
       </c>
       <c r="C150" s="4">
@@ -5633,10 +5575,10 @@
       </c>
     </row>
     <row r="151" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="17">
+      <c r="A151" s="12">
         <v>129</v>
       </c>
-      <c r="B151" s="17">
+      <c r="B151" s="12">
         <v>2</v>
       </c>
       <c r="C151" s="4">
@@ -5644,10 +5586,10 @@
       </c>
     </row>
     <row r="152" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="17">
+      <c r="A152" s="12">
         <v>130</v>
       </c>
-      <c r="B152" s="17">
+      <c r="B152" s="12">
         <v>2</v>
       </c>
       <c r="C152" s="4">
@@ -5655,10 +5597,10 @@
       </c>
     </row>
     <row r="153" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="17">
+      <c r="A153" s="12">
         <v>131</v>
       </c>
-      <c r="B153" s="17">
+      <c r="B153" s="12">
         <v>2</v>
       </c>
       <c r="C153" s="4">
@@ -5666,10 +5608,10 @@
       </c>
     </row>
     <row r="154" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="17">
+      <c r="A154" s="12">
         <v>132</v>
       </c>
-      <c r="B154" s="17">
+      <c r="B154" s="12">
         <v>2</v>
       </c>
       <c r="C154" s="4">
@@ -5677,10 +5619,10 @@
       </c>
     </row>
     <row r="155" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="17">
+      <c r="A155" s="12">
         <v>133</v>
       </c>
-      <c r="B155" s="17">
+      <c r="B155" s="12">
         <v>2</v>
       </c>
       <c r="C155" s="4">
@@ -5688,10 +5630,10 @@
       </c>
     </row>
     <row r="156" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="17">
+      <c r="A156" s="12">
         <v>134</v>
       </c>
-      <c r="B156" s="17">
+      <c r="B156" s="12">
         <v>2</v>
       </c>
       <c r="C156" s="4">
@@ -5699,10 +5641,10 @@
       </c>
     </row>
     <row r="157" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="17">
+      <c r="A157" s="12">
         <v>135</v>
       </c>
-      <c r="B157" s="17">
+      <c r="B157" s="12">
         <v>2</v>
       </c>
       <c r="C157" s="4">
@@ -5710,10 +5652,10 @@
       </c>
     </row>
     <row r="158" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="17">
+      <c r="A158" s="12">
         <v>136</v>
       </c>
-      <c r="B158" s="17">
+      <c r="B158" s="12">
         <v>2</v>
       </c>
       <c r="C158" s="4">
@@ -5721,10 +5663,10 @@
       </c>
     </row>
     <row r="159" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="17">
+      <c r="A159" s="12">
         <v>137</v>
       </c>
-      <c r="B159" s="17">
+      <c r="B159" s="12">
         <v>2</v>
       </c>
       <c r="C159" s="4">
@@ -5732,10 +5674,10 @@
       </c>
     </row>
     <row r="160" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="17">
+      <c r="A160" s="12">
         <v>138</v>
       </c>
-      <c r="B160" s="17">
+      <c r="B160" s="12">
         <v>2</v>
       </c>
       <c r="C160" s="4">
@@ -5743,10 +5685,10 @@
       </c>
     </row>
     <row r="161" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="17">
+      <c r="A161" s="12">
         <v>139</v>
       </c>
-      <c r="B161" s="17">
+      <c r="B161" s="12">
         <v>2</v>
       </c>
       <c r="C161" s="4">
@@ -5754,10 +5696,10 @@
       </c>
     </row>
     <row r="162" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="17">
+      <c r="A162" s="12">
         <v>140</v>
       </c>
-      <c r="B162" s="17">
+      <c r="B162" s="12">
         <v>2</v>
       </c>
       <c r="C162" s="4">
@@ -5765,10 +5707,10 @@
       </c>
     </row>
     <row r="163" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="17">
+      <c r="A163" s="12">
         <v>141</v>
       </c>
-      <c r="B163" s="17">
+      <c r="B163" s="12">
         <v>2</v>
       </c>
       <c r="C163" s="4">
@@ -5776,10 +5718,10 @@
       </c>
     </row>
     <row r="164" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="17">
+      <c r="A164" s="12">
         <v>142</v>
       </c>
-      <c r="B164" s="17">
+      <c r="B164" s="12">
         <v>2</v>
       </c>
       <c r="C164" s="4">
@@ -5787,10 +5729,10 @@
       </c>
     </row>
     <row r="165" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="17">
+      <c r="A165" s="12">
         <v>143</v>
       </c>
-      <c r="B165" s="17">
+      <c r="B165" s="12">
         <v>2</v>
       </c>
       <c r="C165" s="4">
@@ -5798,10 +5740,10 @@
       </c>
     </row>
     <row r="166" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="17">
+      <c r="A166" s="12">
         <v>144</v>
       </c>
-      <c r="B166" s="17">
+      <c r="B166" s="12">
         <v>2</v>
       </c>
       <c r="C166" s="4">
@@ -5809,10 +5751,10 @@
       </c>
     </row>
     <row r="167" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="17">
+      <c r="A167" s="12">
         <v>145</v>
       </c>
-      <c r="B167" s="17">
+      <c r="B167" s="12">
         <v>2</v>
       </c>
       <c r="C167" s="4">
@@ -5820,10 +5762,10 @@
       </c>
     </row>
     <row r="168" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="17">
+      <c r="A168" s="12">
         <v>146</v>
       </c>
-      <c r="B168" s="17">
+      <c r="B168" s="12">
         <v>2</v>
       </c>
       <c r="C168" s="4">
@@ -5831,10 +5773,10 @@
       </c>
     </row>
     <row r="169" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="17">
+      <c r="A169" s="12">
         <v>147</v>
       </c>
-      <c r="B169" s="17">
+      <c r="B169" s="12">
         <v>2</v>
       </c>
       <c r="C169" s="4">
@@ -5842,10 +5784,10 @@
       </c>
     </row>
     <row r="170" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="17">
+      <c r="A170" s="12">
         <v>148</v>
       </c>
-      <c r="B170" s="17">
+      <c r="B170" s="12">
         <v>2</v>
       </c>
       <c r="C170" s="4">
@@ -5853,10 +5795,10 @@
       </c>
     </row>
     <row r="171" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="17">
+      <c r="A171" s="12">
         <v>149</v>
       </c>
-      <c r="B171" s="17">
+      <c r="B171" s="12">
         <v>2</v>
       </c>
       <c r="C171" s="4">
@@ -5864,10 +5806,10 @@
       </c>
     </row>
     <row r="172" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="17">
+      <c r="A172" s="12">
         <v>150</v>
       </c>
-      <c r="B172" s="17">
+      <c r="B172" s="12">
         <v>2</v>
       </c>
       <c r="C172" s="4">
@@ -5875,10 +5817,10 @@
       </c>
     </row>
     <row r="173" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="17">
+      <c r="A173" s="12">
         <v>151</v>
       </c>
-      <c r="B173" s="17">
+      <c r="B173" s="12">
         <v>2</v>
       </c>
       <c r="C173" s="4">
@@ -5886,10 +5828,10 @@
       </c>
     </row>
     <row r="174" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="17">
+      <c r="A174" s="12">
         <v>152</v>
       </c>
-      <c r="B174" s="17">
+      <c r="B174" s="12">
         <v>2</v>
       </c>
       <c r="C174" s="4">
@@ -5897,10 +5839,10 @@
       </c>
     </row>
     <row r="175" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="17">
+      <c r="A175" s="12">
         <v>153</v>
       </c>
-      <c r="B175" s="17">
+      <c r="B175" s="12">
         <v>2</v>
       </c>
       <c r="C175" s="4">
@@ -5908,10 +5850,10 @@
       </c>
     </row>
     <row r="176" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="17">
+      <c r="A176" s="12">
         <v>154</v>
       </c>
-      <c r="B176" s="17">
+      <c r="B176" s="12">
         <v>2</v>
       </c>
       <c r="C176" s="4">
@@ -5919,10 +5861,10 @@
       </c>
     </row>
     <row r="177" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="17">
+      <c r="A177" s="12">
         <v>155</v>
       </c>
-      <c r="B177" s="17">
+      <c r="B177" s="12">
         <v>2</v>
       </c>
       <c r="C177" s="4">
@@ -5930,10 +5872,10 @@
       </c>
     </row>
     <row r="178" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="17">
+      <c r="A178" s="12">
         <v>156</v>
       </c>
-      <c r="B178" s="17">
+      <c r="B178" s="12">
         <v>2</v>
       </c>
       <c r="C178" s="4">
@@ -5941,10 +5883,10 @@
       </c>
     </row>
     <row r="179" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="17">
+      <c r="A179" s="12">
         <v>157</v>
       </c>
-      <c r="B179" s="17">
+      <c r="B179" s="12">
         <v>2</v>
       </c>
       <c r="C179" s="4">
@@ -5952,10 +5894,10 @@
       </c>
     </row>
     <row r="180" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="17">
+      <c r="A180" s="12">
         <v>158</v>
       </c>
-      <c r="B180" s="17">
+      <c r="B180" s="12">
         <v>2</v>
       </c>
       <c r="C180" s="4">
@@ -5963,10 +5905,10 @@
       </c>
     </row>
     <row r="181" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="17">
+      <c r="A181" s="12">
         <v>159</v>
       </c>
-      <c r="B181" s="17">
+      <c r="B181" s="12">
         <v>2</v>
       </c>
       <c r="C181" s="4">
@@ -5974,10 +5916,10 @@
       </c>
     </row>
     <row r="182" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="17">
+      <c r="A182" s="12">
         <v>160</v>
       </c>
-      <c r="B182" s="17">
+      <c r="B182" s="12">
         <v>2</v>
       </c>
       <c r="C182" s="4">
@@ -5985,10 +5927,10 @@
       </c>
     </row>
     <row r="183" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="17">
+      <c r="A183" s="12">
         <v>161</v>
       </c>
-      <c r="B183" s="17">
+      <c r="B183" s="12">
         <v>2</v>
       </c>
       <c r="C183" s="4">
@@ -5996,10 +5938,10 @@
       </c>
     </row>
     <row r="184" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="17">
+      <c r="A184" s="12">
         <v>162</v>
       </c>
-      <c r="B184" s="17">
+      <c r="B184" s="12">
         <v>2</v>
       </c>
       <c r="C184" s="4">
@@ -6007,10 +5949,10 @@
       </c>
     </row>
     <row r="185" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="17">
+      <c r="A185" s="12">
         <v>163</v>
       </c>
-      <c r="B185" s="17">
+      <c r="B185" s="12">
         <v>2</v>
       </c>
       <c r="C185" s="4">
@@ -6018,10 +5960,10 @@
       </c>
     </row>
     <row r="186" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="17">
+      <c r="A186" s="12">
         <v>164</v>
       </c>
-      <c r="B186" s="17">
+      <c r="B186" s="12">
         <v>2</v>
       </c>
       <c r="C186" s="4">
@@ -6029,10 +5971,10 @@
       </c>
     </row>
     <row r="187" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="17">
+      <c r="A187" s="12">
         <v>165</v>
       </c>
-      <c r="B187" s="17">
+      <c r="B187" s="12">
         <v>2</v>
       </c>
       <c r="C187" s="4">
@@ -6040,10 +5982,10 @@
       </c>
     </row>
     <row r="188" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="17">
+      <c r="A188" s="12">
         <v>166</v>
       </c>
-      <c r="B188" s="17">
+      <c r="B188" s="12">
         <v>2</v>
       </c>
       <c r="C188" s="4">
@@ -6051,10 +5993,10 @@
       </c>
     </row>
     <row r="189" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="17">
+      <c r="A189" s="12">
         <v>167</v>
       </c>
-      <c r="B189" s="17">
+      <c r="B189" s="12">
         <v>2</v>
       </c>
       <c r="C189" s="4">
@@ -6062,10 +6004,10 @@
       </c>
     </row>
     <row r="190" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="17">
+      <c r="A190" s="12">
         <v>168</v>
       </c>
-      <c r="B190" s="17">
+      <c r="B190" s="12">
         <v>2</v>
       </c>
       <c r="C190" s="4">
@@ -6073,10 +6015,10 @@
       </c>
     </row>
     <row r="191" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="17">
+      <c r="A191" s="12">
         <v>169</v>
       </c>
-      <c r="B191" s="17">
+      <c r="B191" s="12">
         <v>2</v>
       </c>
       <c r="C191" s="4">
@@ -6084,10 +6026,10 @@
       </c>
     </row>
     <row r="192" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="17">
+      <c r="A192" s="12">
         <v>170</v>
       </c>
-      <c r="B192" s="17">
+      <c r="B192" s="12">
         <v>2</v>
       </c>
       <c r="C192" s="4">
@@ -6095,10 +6037,10 @@
       </c>
     </row>
     <row r="193" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="17">
+      <c r="A193" s="12">
         <v>171</v>
       </c>
-      <c r="B193" s="17">
+      <c r="B193" s="12">
         <v>2</v>
       </c>
       <c r="C193" s="4">
@@ -6106,10 +6048,10 @@
       </c>
     </row>
     <row r="194" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="17">
+      <c r="A194" s="12">
         <v>172</v>
       </c>
-      <c r="B194" s="17">
+      <c r="B194" s="12">
         <v>2</v>
       </c>
       <c r="C194" s="4">
@@ -6117,10 +6059,10 @@
       </c>
     </row>
     <row r="195" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="17">
+      <c r="A195" s="12">
         <v>173</v>
       </c>
-      <c r="B195" s="17">
+      <c r="B195" s="12">
         <v>2</v>
       </c>
       <c r="C195" s="4">
@@ -6128,10 +6070,10 @@
       </c>
     </row>
     <row r="196" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="17">
+      <c r="A196" s="12">
         <v>174</v>
       </c>
-      <c r="B196" s="17">
+      <c r="B196" s="12">
         <v>2</v>
       </c>
       <c r="C196" s="4">
@@ -6139,10 +6081,10 @@
       </c>
     </row>
     <row r="197" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="17">
+      <c r="A197" s="12">
         <v>175</v>
       </c>
-      <c r="B197" s="17">
+      <c r="B197" s="12">
         <v>2</v>
       </c>
       <c r="C197" s="4">
@@ -6150,10 +6092,10 @@
       </c>
     </row>
     <row r="198" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="17">
+      <c r="A198" s="12">
         <v>176</v>
       </c>
-      <c r="B198" s="17">
+      <c r="B198" s="12">
         <v>2</v>
       </c>
       <c r="C198" s="4">
@@ -6161,10 +6103,10 @@
       </c>
     </row>
     <row r="199" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="17">
+      <c r="A199" s="12">
         <v>177</v>
       </c>
-      <c r="B199" s="17">
+      <c r="B199" s="12">
         <v>2</v>
       </c>
       <c r="C199" s="4">
@@ -6172,10 +6114,10 @@
       </c>
     </row>
     <row r="200" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="17">
+      <c r="A200" s="12">
         <v>178</v>
       </c>
-      <c r="B200" s="17">
+      <c r="B200" s="12">
         <v>2</v>
       </c>
       <c r="C200" s="4">
@@ -6183,10 +6125,10 @@
       </c>
     </row>
     <row r="201" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="17">
+      <c r="A201" s="12">
         <v>179</v>
       </c>
-      <c r="B201" s="17">
+      <c r="B201" s="12">
         <v>2</v>
       </c>
       <c r="C201" s="4">
@@ -6194,10 +6136,10 @@
       </c>
     </row>
     <row r="202" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="17">
+      <c r="A202" s="12">
         <v>180</v>
       </c>
-      <c r="B202" s="17">
+      <c r="B202" s="12">
         <v>2</v>
       </c>
       <c r="C202" s="4">
@@ -6205,10 +6147,10 @@
       </c>
     </row>
     <row r="203" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="17">
+      <c r="A203" s="12">
         <v>181</v>
       </c>
-      <c r="B203" s="17">
+      <c r="B203" s="12">
         <v>2</v>
       </c>
       <c r="C203" s="4">
@@ -6216,10 +6158,10 @@
       </c>
     </row>
     <row r="204" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="17">
+      <c r="A204" s="12">
         <v>182</v>
       </c>
-      <c r="B204" s="17">
+      <c r="B204" s="12">
         <v>2</v>
       </c>
       <c r="C204" s="4">
@@ -6227,10 +6169,10 @@
       </c>
     </row>
     <row r="205" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="17">
+      <c r="A205" s="12">
         <v>183</v>
       </c>
-      <c r="B205" s="17">
+      <c r="B205" s="12">
         <v>2</v>
       </c>
       <c r="C205" s="4">
@@ -6238,10 +6180,10 @@
       </c>
     </row>
     <row r="206" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="17">
+      <c r="A206" s="12">
         <v>184</v>
       </c>
-      <c r="B206" s="17">
+      <c r="B206" s="12">
         <v>2</v>
       </c>
       <c r="C206" s="4">
@@ -6249,10 +6191,10 @@
       </c>
     </row>
     <row r="207" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="17">
+      <c r="A207" s="12">
         <v>185</v>
       </c>
-      <c r="B207" s="17">
+      <c r="B207" s="12">
         <v>2</v>
       </c>
       <c r="C207" s="4">
@@ -6260,10 +6202,10 @@
       </c>
     </row>
     <row r="208" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="17">
+      <c r="A208" s="12">
         <v>186</v>
       </c>
-      <c r="B208" s="17">
+      <c r="B208" s="12">
         <v>2</v>
       </c>
       <c r="C208" s="4">
@@ -6271,10 +6213,10 @@
       </c>
     </row>
     <row r="209" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="17">
+      <c r="A209" s="12">
         <v>187</v>
       </c>
-      <c r="B209" s="17">
+      <c r="B209" s="12">
         <v>2</v>
       </c>
       <c r="C209" s="4">
@@ -6282,10 +6224,10 @@
       </c>
     </row>
     <row r="210" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="17">
+      <c r="A210" s="12">
         <v>188</v>
       </c>
-      <c r="B210" s="17">
+      <c r="B210" s="12">
         <v>2</v>
       </c>
       <c r="C210" s="4">
@@ -6293,10 +6235,10 @@
       </c>
     </row>
     <row r="211" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="17">
+      <c r="A211" s="12">
         <v>189</v>
       </c>
-      <c r="B211" s="17">
+      <c r="B211" s="12">
         <v>2</v>
       </c>
       <c r="C211" s="4">
@@ -6304,10 +6246,10 @@
       </c>
     </row>
     <row r="212" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="17">
+      <c r="A212" s="12">
         <v>190</v>
       </c>
-      <c r="B212" s="17">
+      <c r="B212" s="12">
         <v>2</v>
       </c>
       <c r="C212" s="4">
@@ -6315,10 +6257,10 @@
       </c>
     </row>
     <row r="213" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="17">
+      <c r="A213" s="12">
         <v>191</v>
       </c>
-      <c r="B213" s="17">
+      <c r="B213" s="12">
         <v>2</v>
       </c>
       <c r="C213" s="4">
@@ -6326,10 +6268,10 @@
       </c>
     </row>
     <row r="214" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="17">
+      <c r="A214" s="12">
         <v>192</v>
       </c>
-      <c r="B214" s="17">
+      <c r="B214" s="12">
         <v>2</v>
       </c>
       <c r="C214" s="4">
@@ -6337,10 +6279,10 @@
       </c>
     </row>
     <row r="215" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="17">
+      <c r="A215" s="12">
         <v>193</v>
       </c>
-      <c r="B215" s="17">
+      <c r="B215" s="12">
         <v>2</v>
       </c>
       <c r="C215" s="4">
@@ -6348,10 +6290,10 @@
       </c>
     </row>
     <row r="216" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="17">
+      <c r="A216" s="12">
         <v>194</v>
       </c>
-      <c r="B216" s="17">
+      <c r="B216" s="12">
         <v>2</v>
       </c>
       <c r="C216" s="4">
@@ -6359,10 +6301,10 @@
       </c>
     </row>
     <row r="217" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="17">
+      <c r="A217" s="12">
         <v>195</v>
       </c>
-      <c r="B217" s="17">
+      <c r="B217" s="12">
         <v>2</v>
       </c>
       <c r="C217" s="4">
@@ -6370,10 +6312,10 @@
       </c>
     </row>
     <row r="218" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="17">
+      <c r="A218" s="12">
         <v>196</v>
       </c>
-      <c r="B218" s="17">
+      <c r="B218" s="12">
         <v>2</v>
       </c>
       <c r="C218" s="4">
@@ -6381,10 +6323,10 @@
       </c>
     </row>
     <row r="219" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="17">
+      <c r="A219" s="12">
         <v>197</v>
       </c>
-      <c r="B219" s="17">
+      <c r="B219" s="12">
         <v>2</v>
       </c>
       <c r="C219" s="4">
@@ -6392,10 +6334,10 @@
       </c>
     </row>
     <row r="220" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="17">
+      <c r="A220" s="12">
         <v>198</v>
       </c>
-      <c r="B220" s="17">
+      <c r="B220" s="12">
         <v>2</v>
       </c>
       <c r="C220" s="4">
@@ -6403,10 +6345,10 @@
       </c>
     </row>
     <row r="221" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="17">
+      <c r="A221" s="12">
         <v>199</v>
       </c>
-      <c r="B221" s="17">
+      <c r="B221" s="12">
         <v>2</v>
       </c>
       <c r="C221" s="4">
@@ -6414,10 +6356,10 @@
       </c>
     </row>
     <row r="222" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="17">
+      <c r="A222" s="12">
         <v>200</v>
       </c>
-      <c r="B222" s="17">
+      <c r="B222" s="12">
         <v>2</v>
       </c>
       <c r="C222" s="4">
@@ -6425,10 +6367,10 @@
       </c>
     </row>
     <row r="223" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="17">
+      <c r="A223" s="12">
         <v>201</v>
       </c>
-      <c r="B223" s="17">
+      <c r="B223" s="12">
         <v>2</v>
       </c>
       <c r="C223" s="4">
@@ -6436,10 +6378,10 @@
       </c>
     </row>
     <row r="224" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="17">
+      <c r="A224" s="12">
         <v>202</v>
       </c>
-      <c r="B224" s="17">
+      <c r="B224" s="12">
         <v>2</v>
       </c>
       <c r="C224" s="4">
@@ -6447,10 +6389,10 @@
       </c>
     </row>
     <row r="225" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="17">
+      <c r="A225" s="12">
         <v>203</v>
       </c>
-      <c r="B225" s="17">
+      <c r="B225" s="12">
         <v>2</v>
       </c>
       <c r="C225" s="4">
@@ -6458,10 +6400,10 @@
       </c>
     </row>
     <row r="226" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="17">
+      <c r="A226" s="12">
         <v>204</v>
       </c>
-      <c r="B226" s="17">
+      <c r="B226" s="12">
         <v>2</v>
       </c>
       <c r="C226" s="4">
@@ -6469,10 +6411,10 @@
       </c>
     </row>
     <row r="227" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="17">
+      <c r="A227" s="12">
         <v>205</v>
       </c>
-      <c r="B227" s="17">
+      <c r="B227" s="12">
         <v>2</v>
       </c>
       <c r="C227" s="4">
@@ -6480,10 +6422,10 @@
       </c>
     </row>
     <row r="228" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="17">
+      <c r="A228" s="12">
         <v>206</v>
       </c>
-      <c r="B228" s="17">
+      <c r="B228" s="12">
         <v>2</v>
       </c>
       <c r="C228" s="4">
@@ -6491,10 +6433,10 @@
       </c>
     </row>
     <row r="229" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="17">
+      <c r="A229" s="12">
         <v>207</v>
       </c>
-      <c r="B229" s="17">
+      <c r="B229" s="12">
         <v>2</v>
       </c>
       <c r="C229" s="4">
@@ -6502,10 +6444,10 @@
       </c>
     </row>
     <row r="230" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="17">
+      <c r="A230" s="12">
         <v>208</v>
       </c>
-      <c r="B230" s="17">
+      <c r="B230" s="12">
         <v>2</v>
       </c>
       <c r="C230" s="4">
@@ -6513,10 +6455,10 @@
       </c>
     </row>
     <row r="231" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="17">
+      <c r="A231" s="12">
         <v>209</v>
       </c>
-      <c r="B231" s="17">
+      <c r="B231" s="12">
         <v>2</v>
       </c>
       <c r="C231" s="4">
@@ -6524,10 +6466,10 @@
       </c>
     </row>
     <row r="232" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="17">
+      <c r="A232" s="12">
         <v>210</v>
       </c>
-      <c r="B232" s="17">
+      <c r="B232" s="12">
         <v>2</v>
       </c>
       <c r="C232" s="4">
@@ -6535,10 +6477,10 @@
       </c>
     </row>
     <row r="233" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="17">
+      <c r="A233" s="12">
         <v>211</v>
       </c>
-      <c r="B233" s="17">
+      <c r="B233" s="12">
         <v>2</v>
       </c>
       <c r="C233" s="4">
@@ -6546,10 +6488,10 @@
       </c>
     </row>
     <row r="234" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="17">
+      <c r="A234" s="12">
         <v>212</v>
       </c>
-      <c r="B234" s="17">
+      <c r="B234" s="12">
         <v>2</v>
       </c>
       <c r="C234" s="4">
@@ -6557,10 +6499,10 @@
       </c>
     </row>
     <row r="235" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="17">
+      <c r="A235" s="12">
         <v>213</v>
       </c>
-      <c r="B235" s="17">
+      <c r="B235" s="12">
         <v>2</v>
       </c>
       <c r="C235" s="4">
@@ -6568,10 +6510,10 @@
       </c>
     </row>
     <row r="236" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="17">
+      <c r="A236" s="12">
         <v>214</v>
       </c>
-      <c r="B236" s="17">
+      <c r="B236" s="12">
         <v>2</v>
       </c>
       <c r="C236" s="4">
@@ -6579,10 +6521,10 @@
       </c>
     </row>
     <row r="237" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="17">
+      <c r="A237" s="12">
         <v>215</v>
       </c>
-      <c r="B237" s="17">
+      <c r="B237" s="12">
         <v>2</v>
       </c>
       <c r="C237" s="4">
@@ -6590,10 +6532,10 @@
       </c>
     </row>
     <row r="238" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="17">
+      <c r="A238" s="12">
         <v>216</v>
       </c>
-      <c r="B238" s="17">
+      <c r="B238" s="12">
         <v>2</v>
       </c>
       <c r="C238" s="4">
@@ -6601,10 +6543,10 @@
       </c>
     </row>
     <row r="239" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="17">
+      <c r="A239" s="12">
         <v>217</v>
       </c>
-      <c r="B239" s="17">
+      <c r="B239" s="12">
         <v>2</v>
       </c>
       <c r="C239" s="4">
@@ -6612,10 +6554,10 @@
       </c>
     </row>
     <row r="240" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="17">
+      <c r="A240" s="12">
         <v>218</v>
       </c>
-      <c r="B240" s="17">
+      <c r="B240" s="12">
         <v>2</v>
       </c>
       <c r="C240" s="4">
@@ -6623,10 +6565,10 @@
       </c>
     </row>
     <row r="241" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="17">
+      <c r="A241" s="12">
         <v>219</v>
       </c>
-      <c r="B241" s="17">
+      <c r="B241" s="12">
         <v>2</v>
       </c>
       <c r="C241" s="4">
@@ -6634,10 +6576,10 @@
       </c>
     </row>
     <row r="242" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="17">
+      <c r="A242" s="12">
         <v>220</v>
       </c>
-      <c r="B242" s="17">
+      <c r="B242" s="12">
         <v>2</v>
       </c>
       <c r="C242" s="4">
@@ -6645,10 +6587,10 @@
       </c>
     </row>
     <row r="243" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="17">
+      <c r="A243" s="12">
         <v>221</v>
       </c>
-      <c r="B243" s="17">
+      <c r="B243" s="12">
         <v>2</v>
       </c>
       <c r="C243" s="4">
@@ -6656,10 +6598,10 @@
       </c>
     </row>
     <row r="244" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="17">
+      <c r="A244" s="12">
         <v>222</v>
       </c>
-      <c r="B244" s="17">
+      <c r="B244" s="12">
         <v>2</v>
       </c>
       <c r="C244" s="4">
@@ -6667,10 +6609,10 @@
       </c>
     </row>
     <row r="245" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="17">
+      <c r="A245" s="12">
         <v>223</v>
       </c>
-      <c r="B245" s="17">
+      <c r="B245" s="12">
         <v>2</v>
       </c>
       <c r="C245" s="4">
@@ -6678,10 +6620,10 @@
       </c>
     </row>
     <row r="246" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="17">
+      <c r="A246" s="12">
         <v>224</v>
       </c>
-      <c r="B246" s="17">
+      <c r="B246" s="12">
         <v>2</v>
       </c>
       <c r="C246" s="4">
@@ -6689,10 +6631,10 @@
       </c>
     </row>
     <row r="247" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="17">
+      <c r="A247" s="12">
         <v>225</v>
       </c>
-      <c r="B247" s="17">
+      <c r="B247" s="12">
         <v>2</v>
       </c>
       <c r="C247" s="4">
@@ -6700,10 +6642,10 @@
       </c>
     </row>
     <row r="248" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="17">
+      <c r="A248" s="12">
         <v>226</v>
       </c>
-      <c r="B248" s="17">
+      <c r="B248" s="12">
         <v>2</v>
       </c>
       <c r="C248" s="4">
@@ -6711,10 +6653,10 @@
       </c>
     </row>
     <row r="249" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A249" s="17">
+      <c r="A249" s="12">
         <v>227</v>
       </c>
-      <c r="B249" s="17">
+      <c r="B249" s="12">
         <v>2</v>
       </c>
       <c r="C249" s="4">
@@ -6722,10 +6664,10 @@
       </c>
     </row>
     <row r="250" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="17">
+      <c r="A250" s="12">
         <v>228</v>
       </c>
-      <c r="B250" s="17">
+      <c r="B250" s="12">
         <v>2</v>
       </c>
       <c r="C250" s="4">
@@ -6733,10 +6675,10 @@
       </c>
     </row>
     <row r="251" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="17">
+      <c r="A251" s="12">
         <v>229</v>
       </c>
-      <c r="B251" s="17">
+      <c r="B251" s="12">
         <v>2</v>
       </c>
       <c r="C251" s="4">
@@ -6744,10 +6686,10 @@
       </c>
     </row>
     <row r="252" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="17">
+      <c r="A252" s="12">
         <v>230</v>
       </c>
-      <c r="B252" s="17">
+      <c r="B252" s="12">
         <v>2</v>
       </c>
       <c r="C252" s="4">
@@ -6755,10 +6697,10 @@
       </c>
     </row>
     <row r="253" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="17">
+      <c r="A253" s="12">
         <v>231</v>
       </c>
-      <c r="B253" s="17">
+      <c r="B253" s="12">
         <v>2</v>
       </c>
       <c r="C253" s="4">
@@ -6766,10 +6708,10 @@
       </c>
     </row>
     <row r="254" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="17">
+      <c r="A254" s="12">
         <v>232</v>
       </c>
-      <c r="B254" s="17">
+      <c r="B254" s="12">
         <v>2</v>
       </c>
       <c r="C254" s="4">
@@ -6777,10 +6719,10 @@
       </c>
     </row>
     <row r="255" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="17">
+      <c r="A255" s="12">
         <v>233</v>
       </c>
-      <c r="B255" s="17">
+      <c r="B255" s="12">
         <v>2</v>
       </c>
       <c r="C255" s="4">
@@ -6788,10 +6730,10 @@
       </c>
     </row>
     <row r="256" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A256" s="17">
+      <c r="A256" s="12">
         <v>234</v>
       </c>
-      <c r="B256" s="17">
+      <c r="B256" s="12">
         <v>2</v>
       </c>
       <c r="C256" s="4">
@@ -6799,10 +6741,10 @@
       </c>
     </row>
     <row r="257" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="17">
+      <c r="A257" s="12">
         <v>235</v>
       </c>
-      <c r="B257" s="17">
+      <c r="B257" s="12">
         <v>2</v>
       </c>
       <c r="C257" s="4">
@@ -6810,10 +6752,10 @@
       </c>
     </row>
     <row r="258" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="17">
+      <c r="A258" s="12">
         <v>236</v>
       </c>
-      <c r="B258" s="17">
+      <c r="B258" s="12">
         <v>2</v>
       </c>
       <c r="C258" s="4">
@@ -6821,10 +6763,10 @@
       </c>
     </row>
     <row r="259" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="17">
+      <c r="A259" s="12">
         <v>237</v>
       </c>
-      <c r="B259" s="17">
+      <c r="B259" s="12">
         <v>2</v>
       </c>
       <c r="C259" s="4">
@@ -6832,10 +6774,10 @@
       </c>
     </row>
     <row r="260" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="17">
+      <c r="A260" s="12">
         <v>238</v>
       </c>
-      <c r="B260" s="17">
+      <c r="B260" s="12">
         <v>2</v>
       </c>
       <c r="C260" s="4">
@@ -6843,10 +6785,10 @@
       </c>
     </row>
     <row r="261" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="17">
+      <c r="A261" s="12">
         <v>239</v>
       </c>
-      <c r="B261" s="17">
+      <c r="B261" s="12">
         <v>2</v>
       </c>
       <c r="C261" s="4">
@@ -6854,10 +6796,10 @@
       </c>
     </row>
     <row r="262" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="17">
+      <c r="A262" s="12">
         <v>240</v>
       </c>
-      <c r="B262" s="17">
+      <c r="B262" s="12">
         <v>2</v>
       </c>
       <c r="C262" s="4">
@@ -6865,10 +6807,10 @@
       </c>
     </row>
     <row r="263" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="17">
+      <c r="A263" s="12">
         <v>241</v>
       </c>
-      <c r="B263" s="17">
+      <c r="B263" s="12">
         <v>2</v>
       </c>
       <c r="C263" s="4">
@@ -6876,10 +6818,10 @@
       </c>
     </row>
     <row r="264" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="17">
+      <c r="A264" s="12">
         <v>242</v>
       </c>
-      <c r="B264" s="17">
+      <c r="B264" s="12">
         <v>2</v>
       </c>
       <c r="C264" s="4">
@@ -6887,10 +6829,10 @@
       </c>
     </row>
     <row r="265" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="17">
+      <c r="A265" s="12">
         <v>243</v>
       </c>
-      <c r="B265" s="17">
+      <c r="B265" s="12">
         <v>2</v>
       </c>
       <c r="C265" s="4">
@@ -6898,10 +6840,10 @@
       </c>
     </row>
     <row r="266" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="17">
+      <c r="A266" s="12">
         <v>244</v>
       </c>
-      <c r="B266" s="17">
+      <c r="B266" s="12">
         <v>2</v>
       </c>
       <c r="C266" s="4">
@@ -6909,10 +6851,10 @@
       </c>
     </row>
     <row r="267" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="17">
+      <c r="A267" s="12">
         <v>245</v>
       </c>
-      <c r="B267" s="17">
+      <c r="B267" s="12">
         <v>2</v>
       </c>
       <c r="C267" s="4">
@@ -6920,10 +6862,10 @@
       </c>
     </row>
     <row r="268" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="17">
+      <c r="A268" s="12">
         <v>246</v>
       </c>
-      <c r="B268" s="17">
+      <c r="B268" s="12">
         <v>2</v>
       </c>
       <c r="C268" s="4">
@@ -6931,10 +6873,10 @@
       </c>
     </row>
     <row r="269" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="17">
+      <c r="A269" s="12">
         <v>247</v>
       </c>
-      <c r="B269" s="17">
+      <c r="B269" s="12">
         <v>2</v>
       </c>
       <c r="C269" s="4">
@@ -6942,10 +6884,10 @@
       </c>
     </row>
     <row r="270" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="17">
+      <c r="A270" s="12">
         <v>248</v>
       </c>
-      <c r="B270" s="17">
+      <c r="B270" s="12">
         <v>2</v>
       </c>
       <c r="C270" s="4">
@@ -6953,10 +6895,10 @@
       </c>
     </row>
     <row r="271" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="17">
+      <c r="A271" s="12">
         <v>249</v>
       </c>
-      <c r="B271" s="17">
+      <c r="B271" s="12">
         <v>2</v>
       </c>
       <c r="C271" s="4">
@@ -6964,10 +6906,10 @@
       </c>
     </row>
     <row r="272" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="17">
+      <c r="A272" s="12">
         <v>250</v>
       </c>
-      <c r="B272" s="17">
+      <c r="B272" s="12">
         <v>2</v>
       </c>
       <c r="C272" s="4">
@@ -6975,10 +6917,10 @@
       </c>
     </row>
     <row r="273" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="17">
+      <c r="A273" s="12">
         <v>251</v>
       </c>
-      <c r="B273" s="17">
+      <c r="B273" s="12">
         <v>2</v>
       </c>
       <c r="C273" s="4">
@@ -6986,10 +6928,10 @@
       </c>
     </row>
     <row r="274" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="17">
+      <c r="A274" s="12">
         <v>252</v>
       </c>
-      <c r="B274" s="17">
+      <c r="B274" s="12">
         <v>2</v>
       </c>
       <c r="C274" s="4">
@@ -6997,10 +6939,10 @@
       </c>
     </row>
     <row r="275" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="17">
+      <c r="A275" s="12">
         <v>253</v>
       </c>
-      <c r="B275" s="17">
+      <c r="B275" s="12">
         <v>2</v>
       </c>
       <c r="C275" s="4">
@@ -7008,10 +6950,10 @@
       </c>
     </row>
     <row r="276" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="17">
+      <c r="A276" s="12">
         <v>254</v>
       </c>
-      <c r="B276" s="17">
+      <c r="B276" s="12">
         <v>2</v>
       </c>
       <c r="C276" s="4">
@@ -7019,10 +6961,10 @@
       </c>
     </row>
     <row r="277" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="17">
+      <c r="A277" s="12">
         <v>255</v>
       </c>
-      <c r="B277" s="17">
+      <c r="B277" s="12">
         <v>2</v>
       </c>
       <c r="C277" s="4">
@@ -7030,10 +6972,10 @@
       </c>
     </row>
     <row r="278" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="17">
+      <c r="A278" s="12">
         <v>256</v>
       </c>
-      <c r="B278" s="17">
+      <c r="B278" s="12">
         <v>2</v>
       </c>
       <c r="C278" s="4">
@@ -7041,10 +6983,10 @@
       </c>
     </row>
     <row r="279" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="17">
+      <c r="A279" s="12">
         <v>257</v>
       </c>
-      <c r="B279" s="17">
+      <c r="B279" s="12">
         <v>2</v>
       </c>
       <c r="C279" s="4">
@@ -7052,10 +6994,10 @@
       </c>
     </row>
     <row r="280" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="17">
+      <c r="A280" s="12">
         <v>258</v>
       </c>
-      <c r="B280" s="17">
+      <c r="B280" s="12">
         <v>2</v>
       </c>
       <c r="C280" s="4">
@@ -7063,10 +7005,10 @@
       </c>
     </row>
     <row r="281" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="17">
+      <c r="A281" s="12">
         <v>259</v>
       </c>
-      <c r="B281" s="17">
+      <c r="B281" s="12">
         <v>2</v>
       </c>
       <c r="C281" s="4">
@@ -7074,10 +7016,10 @@
       </c>
     </row>
     <row r="282" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="17">
+      <c r="A282" s="12">
         <v>260</v>
       </c>
-      <c r="B282" s="17">
+      <c r="B282" s="12">
         <v>2</v>
       </c>
       <c r="C282" s="4">
@@ -7085,10 +7027,10 @@
       </c>
     </row>
     <row r="283" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="17">
+      <c r="A283" s="12">
         <v>261</v>
       </c>
-      <c r="B283" s="17">
+      <c r="B283" s="12">
         <v>2</v>
       </c>
       <c r="C283" s="4">
@@ -7096,10 +7038,10 @@
       </c>
     </row>
     <row r="284" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="17">
+      <c r="A284" s="12">
         <v>262</v>
       </c>
-      <c r="B284" s="17">
+      <c r="B284" s="12">
         <v>2</v>
       </c>
       <c r="C284" s="4">
@@ -7107,10 +7049,10 @@
       </c>
     </row>
     <row r="285" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="17">
+      <c r="A285" s="12">
         <v>263</v>
       </c>
-      <c r="B285" s="17">
+      <c r="B285" s="12">
         <v>2</v>
       </c>
       <c r="C285" s="4">
@@ -7118,10 +7060,10 @@
       </c>
     </row>
     <row r="286" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="17">
+      <c r="A286" s="12">
         <v>264</v>
       </c>
-      <c r="B286" s="17">
+      <c r="B286" s="12">
         <v>2</v>
       </c>
       <c r="C286" s="4">
@@ -7129,10 +7071,10 @@
       </c>
     </row>
     <row r="287" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="17">
+      <c r="A287" s="12">
         <v>265</v>
       </c>
-      <c r="B287" s="17">
+      <c r="B287" s="12">
         <v>2</v>
       </c>
       <c r="C287" s="4">
@@ -7140,10 +7082,10 @@
       </c>
     </row>
     <row r="288" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="17">
+      <c r="A288" s="12">
         <v>266</v>
       </c>
-      <c r="B288" s="17">
+      <c r="B288" s="12">
         <v>2</v>
       </c>
       <c r="C288" s="4">
@@ -7151,10 +7093,10 @@
       </c>
     </row>
     <row r="289" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="17">
+      <c r="A289" s="12">
         <v>267</v>
       </c>
-      <c r="B289" s="17">
+      <c r="B289" s="12">
         <v>2</v>
       </c>
       <c r="C289" s="4">
@@ -7162,10 +7104,10 @@
       </c>
     </row>
     <row r="290" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="17">
+      <c r="A290" s="12">
         <v>268</v>
       </c>
-      <c r="B290" s="17">
+      <c r="B290" s="12">
         <v>2</v>
       </c>
       <c r="C290" s="4">
@@ -7173,10 +7115,10 @@
       </c>
     </row>
     <row r="291" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="17">
+      <c r="A291" s="12">
         <v>269</v>
       </c>
-      <c r="B291" s="17">
+      <c r="B291" s="12">
         <v>2</v>
       </c>
       <c r="C291" s="4">
@@ -7184,10 +7126,10 @@
       </c>
     </row>
     <row r="292" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="17">
+      <c r="A292" s="12">
         <v>270</v>
       </c>
-      <c r="B292" s="17">
+      <c r="B292" s="12">
         <v>2</v>
       </c>
       <c r="C292" s="4">
@@ -7195,10 +7137,10 @@
       </c>
     </row>
     <row r="293" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="17">
+      <c r="A293" s="12">
         <v>271</v>
       </c>
-      <c r="B293" s="17">
+      <c r="B293" s="12">
         <v>2</v>
       </c>
       <c r="C293" s="4">
@@ -7206,10 +7148,10 @@
       </c>
     </row>
     <row r="294" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="17">
+      <c r="A294" s="12">
         <v>272</v>
       </c>
-      <c r="B294" s="17">
+      <c r="B294" s="12">
         <v>2</v>
       </c>
       <c r="C294" s="4">
@@ -7217,10 +7159,10 @@
       </c>
     </row>
     <row r="295" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="17">
+      <c r="A295" s="12">
         <v>273</v>
       </c>
-      <c r="B295" s="17">
+      <c r="B295" s="12">
         <v>2</v>
       </c>
       <c r="C295" s="4">
@@ -7228,10 +7170,10 @@
       </c>
     </row>
     <row r="296" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="17">
+      <c r="A296" s="12">
         <v>274</v>
       </c>
-      <c r="B296" s="17">
+      <c r="B296" s="12">
         <v>2</v>
       </c>
       <c r="C296" s="4">
@@ -7239,10 +7181,10 @@
       </c>
     </row>
     <row r="297" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="17">
+      <c r="A297" s="12">
         <v>275</v>
       </c>
-      <c r="B297" s="17">
+      <c r="B297" s="12">
         <v>2</v>
       </c>
       <c r="C297" s="4">
@@ -7250,10 +7192,10 @@
       </c>
     </row>
     <row r="298" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="17">
+      <c r="A298" s="12">
         <v>276</v>
       </c>
-      <c r="B298" s="17">
+      <c r="B298" s="12">
         <v>2</v>
       </c>
       <c r="C298" s="4">
@@ -7261,10 +7203,10 @@
       </c>
     </row>
     <row r="299" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="17">
+      <c r="A299" s="12">
         <v>277</v>
       </c>
-      <c r="B299" s="17">
+      <c r="B299" s="12">
         <v>2</v>
       </c>
       <c r="C299" s="4">
@@ -7272,10 +7214,10 @@
       </c>
     </row>
     <row r="300" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="17">
+      <c r="A300" s="12">
         <v>278</v>
       </c>
-      <c r="B300" s="17">
+      <c r="B300" s="12">
         <v>2</v>
       </c>
       <c r="C300" s="4">
@@ -7283,10 +7225,10 @@
       </c>
     </row>
     <row r="301" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="17">
+      <c r="A301" s="12">
         <v>279</v>
       </c>
-      <c r="B301" s="17">
+      <c r="B301" s="12">
         <v>2</v>
       </c>
       <c r="C301" s="4">
@@ -7294,10 +7236,10 @@
       </c>
     </row>
     <row r="302" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="17">
+      <c r="A302" s="12">
         <v>280</v>
       </c>
-      <c r="B302" s="17">
+      <c r="B302" s="12">
         <v>2</v>
       </c>
       <c r="C302" s="4">
@@ -7305,10 +7247,10 @@
       </c>
     </row>
     <row r="303" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="17">
+      <c r="A303" s="12">
         <v>281</v>
       </c>
-      <c r="B303" s="17">
+      <c r="B303" s="12">
         <v>2</v>
       </c>
       <c r="C303" s="4">
@@ -7316,10 +7258,10 @@
       </c>
     </row>
     <row r="304" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A304" s="17">
+      <c r="A304" s="12">
         <v>282</v>
       </c>
-      <c r="B304" s="17">
+      <c r="B304" s="12">
         <v>2</v>
       </c>
       <c r="C304" s="4">
@@ -7327,10 +7269,10 @@
       </c>
     </row>
     <row r="305" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="17">
+      <c r="A305" s="12">
         <v>283</v>
       </c>
-      <c r="B305" s="17">
+      <c r="B305" s="12">
         <v>2</v>
       </c>
       <c r="C305" s="4">
@@ -7338,10 +7280,10 @@
       </c>
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A306" s="17">
+      <c r="A306" s="12">
         <v>284</v>
       </c>
-      <c r="B306" s="17">
+      <c r="B306" s="12">
         <v>2</v>
       </c>
       <c r="C306" s="4">
@@ -7349,10 +7291,10 @@
       </c>
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A307" s="17">
+      <c r="A307" s="12">
         <v>285</v>
       </c>
-      <c r="B307" s="17">
+      <c r="B307" s="12">
         <v>2</v>
       </c>
       <c r="C307" s="4">
@@ -7360,10 +7302,10 @@
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A308" s="17">
+      <c r="A308" s="12">
         <v>286</v>
       </c>
-      <c r="B308" s="17">
+      <c r="B308" s="12">
         <v>2</v>
       </c>
       <c r="C308" s="4">
@@ -7371,10 +7313,10 @@
       </c>
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A309" s="17">
+      <c r="A309" s="12">
         <v>287</v>
       </c>
-      <c r="B309" s="17">
+      <c r="B309" s="12">
         <v>2</v>
       </c>
       <c r="C309" s="4">
@@ -7382,10 +7324,10 @@
       </c>
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A310" s="17">
+      <c r="A310" s="12">
         <v>288</v>
       </c>
-      <c r="B310" s="17">
+      <c r="B310" s="12">
         <v>2</v>
       </c>
       <c r="C310" s="4">
@@ -7393,10 +7335,10 @@
       </c>
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A311" s="17">
+      <c r="A311" s="12">
         <v>289</v>
       </c>
-      <c r="B311" s="17">
+      <c r="B311" s="12">
         <v>2</v>
       </c>
       <c r="C311" s="4">
@@ -7404,10 +7346,10 @@
       </c>
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A312" s="17">
+      <c r="A312" s="12">
         <v>290</v>
       </c>
-      <c r="B312" s="17">
+      <c r="B312" s="12">
         <v>2</v>
       </c>
       <c r="C312" s="4">
@@ -7415,10 +7357,10 @@
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A313" s="17">
+      <c r="A313" s="12">
         <v>291</v>
       </c>
-      <c r="B313" s="17">
+      <c r="B313" s="12">
         <v>2</v>
       </c>
       <c r="C313" s="4">
@@ -7434,7 +7376,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z303"/>
+  <dimension ref="A1:Z302"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -13800,8 +13742,8 @@
       <c r="F229" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G229" s="23" t="s">
-        <v>377</v>
+      <c r="G229" s="18" t="s">
+        <v>374</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
@@ -13826,8 +13768,8 @@
       <c r="F230" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G230" s="23" t="s">
-        <v>376</v>
+      <c r="G230" s="18" t="s">
+        <v>373</v>
       </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5" t="s">
@@ -13859,284 +13801,325 @@
       <c r="I231" s="1"/>
       <c r="J231" s="5"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J232" s="6"/>
+    <row r="232" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="4">
+        <v>15</v>
+      </c>
+      <c r="B232" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="C232" s="4">
+        <v>1</v>
+      </c>
+      <c r="D232" s="4">
+        <v>15</v>
+      </c>
+      <c r="E232" s="4"/>
+      <c r="F232" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G232" s="5"/>
+      <c r="H232" s="5"/>
+      <c r="I232" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="J232" s="5"/>
     </row>
     <row r="233" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B233" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C233" s="4">
         <v>15</v>
       </c>
-      <c r="B233" s="23" t="s">
-        <v>373</v>
-      </c>
-      <c r="C233" s="4">
-        <v>1</v>
-      </c>
       <c r="D233" s="4">
-        <v>15</v>
+        <v>1501</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G233" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G233" s="18" t="s">
+        <v>376</v>
+      </c>
       <c r="H233" s="5"/>
-      <c r="I233" s="5" t="s">
-        <v>274</v>
+      <c r="I233" s="18" t="s">
+        <v>371</v>
       </c>
       <c r="J233" s="5"/>
     </row>
     <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
-        <v>1501</v>
-      </c>
-      <c r="B234" s="23" t="s">
-        <v>374</v>
+        <v>1502</v>
+      </c>
+      <c r="B234" s="18" t="s">
+        <v>372</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
       </c>
       <c r="D234" s="4">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G234" s="23" t="s">
-        <v>379</v>
+      <c r="G234" s="18" t="s">
+        <v>375</v>
       </c>
       <c r="H234" s="5"/>
-      <c r="I234" s="23" t="s">
-        <v>374</v>
+      <c r="I234" s="5" t="s">
+        <v>275</v>
       </c>
       <c r="J234" s="5"/>
     </row>
     <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
-        <v>1502</v>
-      </c>
-      <c r="B235" s="23" t="s">
-        <v>375</v>
+        <v>1503</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="C235" s="4">
         <v>15</v>
       </c>
       <c r="D235" s="4">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G235" s="23" t="s">
-        <v>378</v>
+      <c r="G235" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="H235" s="5"/>
       <c r="I235" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J235" s="5"/>
     </row>
     <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="4">
-        <v>1503</v>
-      </c>
-      <c r="B236" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C236" s="4">
+      <c r="A236" s="6">
+        <v>1504</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="C236" s="6">
         <v>15</v>
       </c>
-      <c r="D236" s="4">
-        <v>1503</v>
-      </c>
-      <c r="E236" s="4"/>
-      <c r="F236" s="4" t="s">
+      <c r="D236" s="6">
+        <v>1504</v>
+      </c>
+      <c r="E236" s="6"/>
+      <c r="F236" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G236" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="H236" s="5"/>
-      <c r="I236" s="5" t="s">
-        <v>276</v>
+      <c r="G236" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H236" s="7"/>
+      <c r="I236" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="J236" s="5"/>
     </row>
     <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="7">
-        <v>1504</v>
-      </c>
-      <c r="B237" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="C237" s="7">
-        <v>15</v>
-      </c>
-      <c r="D237" s="7">
-        <v>1504</v>
-      </c>
-      <c r="E237" s="7"/>
-      <c r="F237" s="7" t="s">
+      <c r="A237" s="8">
+        <v>16</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C237" s="8">
+        <v>1</v>
+      </c>
+      <c r="D237" s="8">
+        <v>16</v>
+      </c>
+      <c r="E237" s="8"/>
+      <c r="F237" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G237" s="9"/>
+      <c r="H237" s="9"/>
+      <c r="I237" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="J237" s="5"/>
+    </row>
+    <row r="238" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="4">
+        <v>1601</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C238" s="4">
+        <v>16</v>
+      </c>
+      <c r="D238" s="4">
+        <v>1601</v>
+      </c>
+      <c r="E238" s="4"/>
+      <c r="F238" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G237" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="H237" s="8"/>
-      <c r="I237" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="J237" s="5"/>
-    </row>
-    <row r="238" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="9"/>
-      <c r="B238" s="10"/>
-      <c r="C238" s="11"/>
-      <c r="D238" s="11"/>
-      <c r="E238" s="11"/>
-      <c r="F238" s="11"/>
-      <c r="G238" s="10"/>
-      <c r="H238" s="10"/>
-      <c r="I238" s="15"/>
+      <c r="G238" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="H238" s="5"/>
+      <c r="I238" s="5" t="s">
+        <v>281</v>
+      </c>
       <c r="J238" s="5"/>
     </row>
     <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="12">
+      <c r="A239" s="4">
+        <v>1602</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C239" s="4">
         <v>16</v>
       </c>
-      <c r="B239" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="C239" s="12">
-        <v>1</v>
-      </c>
-      <c r="D239" s="12">
-        <v>16</v>
-      </c>
-      <c r="E239" s="12"/>
-      <c r="F239" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G239" s="13"/>
-      <c r="H239" s="13"/>
-      <c r="I239" s="13" t="s">
-        <v>280</v>
+      <c r="D239" s="4">
+        <v>1602</v>
+      </c>
+      <c r="E239" s="4"/>
+      <c r="F239" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H239" s="5"/>
+      <c r="I239" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="J239" s="5"/>
     </row>
     <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>1601</v>
+        <v>160201</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>281</v>
+        <v>146</v>
       </c>
       <c r="C240" s="4">
-        <v>16</v>
+        <v>1602</v>
       </c>
       <c r="D240" s="4">
-        <v>1601</v>
+        <v>160201</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="H240" s="5"/>
+        <v>284</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="I240" s="5" t="s">
-        <v>281</v>
+        <v>60</v>
       </c>
       <c r="J240" s="5"/>
     </row>
     <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
+        <v>160202</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C241" s="4">
         <v>1602</v>
       </c>
-      <c r="B241" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C241" s="4">
-        <v>16</v>
-      </c>
       <c r="D241" s="4">
-        <v>1602</v>
+        <v>160202</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H241" s="5"/>
+        <v>284</v>
+      </c>
+      <c r="H241" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="I241" s="5" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="J241" s="5"/>
     </row>
     <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
-        <v>160201</v>
+        <v>160203</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C242" s="4">
         <v>1602</v>
       </c>
       <c r="D242" s="4">
-        <v>160201</v>
+        <v>160203</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H242" s="5" t="s">
-        <v>60</v>
+        <v>286</v>
       </c>
       <c r="I242" s="5" t="s">
-        <v>60</v>
+        <v>286</v>
       </c>
       <c r="J242" s="5"/>
     </row>
     <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
-        <v>160202</v>
+        <v>160204</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C243" s="4">
         <v>1602</v>
       </c>
       <c r="D243" s="4">
-        <v>160202</v>
+        <v>160204</v>
       </c>
       <c r="E243" s="4"/>
       <c r="F243" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H243" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I243" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J243" s="5"/>
     </row>
     <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>160203</v>
+        <v>160205</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>148</v>
@@ -14145,82 +14128,82 @@
         <v>1602</v>
       </c>
       <c r="D244" s="4">
-        <v>160203</v>
+        <v>160205</v>
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>285</v>
       </c>
       <c r="H244" s="5" t="s">
-        <v>286</v>
+        <v>65</v>
       </c>
       <c r="I244" s="5" t="s">
-        <v>286</v>
+        <v>65</v>
       </c>
       <c r="J244" s="5"/>
     </row>
     <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
-        <v>160204</v>
+        <v>160206</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C245" s="4">
         <v>1602</v>
       </c>
       <c r="D245" s="4">
-        <v>160204</v>
+        <v>160206</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I245" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J245" s="5"/>
     </row>
     <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>160205</v>
+        <v>160207</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C246" s="4">
         <v>1602</v>
       </c>
       <c r="D246" s="4">
-        <v>160205</v>
+        <v>160207</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I246" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J246" s="5"/>
     </row>
     <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>160206</v>
+        <v>160208</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>150</v>
@@ -14229,108 +14212,108 @@
         <v>1602</v>
       </c>
       <c r="D247" s="4">
-        <v>160206</v>
+        <v>160208</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G247" s="5" t="s">
         <v>287</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I247" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J247" s="5"/>
     </row>
     <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
-        <v>160207</v>
+        <v>1603</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="C248" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D248" s="4">
-        <v>160207</v>
+        <v>1603</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="H248" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="H248" s="5"/>
       <c r="I248" s="5" t="s">
-        <v>64</v>
+        <v>288</v>
       </c>
       <c r="J248" s="5"/>
     </row>
     <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>160208</v>
+        <v>160301</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="C249" s="4">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="D249" s="4">
-        <v>160208</v>
+        <v>160301</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="I249" s="5" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="J249" s="5"/>
     </row>
     <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
+        <v>160302</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C250" s="4">
         <v>1603</v>
       </c>
-      <c r="B250" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C250" s="4">
-        <v>16</v>
-      </c>
       <c r="D250" s="4">
-        <v>1603</v>
+        <v>160302</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H250" s="5"/>
+        <v>291</v>
+      </c>
+      <c r="H250" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="I250" s="5" t="s">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="J250" s="5"/>
     </row>
     <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
-        <v>160301</v>
+        <v>160303</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>290</v>
@@ -14339,7 +14322,7 @@
         <v>1603</v>
       </c>
       <c r="D251" s="4">
-        <v>160301</v>
+        <v>160303</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="4" t="s">
@@ -14349,72 +14332,72 @@
         <v>291</v>
       </c>
       <c r="H251" s="5" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="I251" s="5" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="J251" s="5"/>
     </row>
     <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
-        <v>160302</v>
+        <v>160304</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C252" s="4">
         <v>1603</v>
       </c>
       <c r="D252" s="4">
-        <v>160302</v>
+        <v>160304</v>
       </c>
       <c r="E252" s="4"/>
       <c r="F252" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>60</v>
+        <v>294</v>
       </c>
       <c r="I252" s="5" t="s">
-        <v>60</v>
+        <v>294</v>
       </c>
       <c r="J252" s="5"/>
     </row>
     <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>160303</v>
+        <v>160305</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C253" s="4">
         <v>1603</v>
       </c>
       <c r="D253" s="4">
-        <v>160303</v>
+        <v>160305</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H253" s="5" t="s">
-        <v>61</v>
+        <v>295</v>
       </c>
       <c r="I253" s="5" t="s">
-        <v>61</v>
+        <v>295</v>
       </c>
       <c r="J253" s="5"/>
     </row>
     <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
-        <v>160304</v>
+        <v>160306</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>292</v>
@@ -14423,7 +14406,7 @@
         <v>1603</v>
       </c>
       <c r="D254" s="4">
-        <v>160304</v>
+        <v>160306</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
@@ -14433,16 +14416,16 @@
         <v>293</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>294</v>
+        <v>64</v>
       </c>
       <c r="I254" s="5" t="s">
-        <v>294</v>
+        <v>64</v>
       </c>
       <c r="J254" s="5"/>
     </row>
     <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>160305</v>
+        <v>160307</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>292</v>
@@ -14451,7 +14434,7 @@
         <v>1603</v>
       </c>
       <c r="D255" s="4">
-        <v>160305</v>
+        <v>160307</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="4" t="s">
@@ -14461,72 +14444,72 @@
         <v>293</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>295</v>
+        <v>65</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>295</v>
+        <v>65</v>
       </c>
       <c r="J255" s="5"/>
     </row>
     <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>160306</v>
+        <v>160308</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C256" s="4">
         <v>1603</v>
       </c>
       <c r="D256" s="4">
-        <v>160306</v>
+        <v>160308</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="I256" s="5" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="J256" s="5"/>
     </row>
     <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
-        <v>160307</v>
+        <v>160309</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C257" s="4">
         <v>1603</v>
       </c>
       <c r="D257" s="4">
-        <v>160307</v>
+        <v>160309</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I257" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J257" s="5"/>
     </row>
     <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>160308</v>
+        <v>160310</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>296</v>
@@ -14535,448 +14518,442 @@
         <v>1603</v>
       </c>
       <c r="D258" s="4">
-        <v>160308</v>
+        <v>160310</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G258" s="5" t="s">
         <v>297</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="I258" s="5" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="J258" s="5"/>
     </row>
     <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>160309</v>
+        <v>1604</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C259" s="4">
-        <v>1603</v>
+        <v>16</v>
       </c>
       <c r="D259" s="4">
-        <v>160309</v>
+        <v>1604</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="H259" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="H259" s="5"/>
       <c r="I259" s="5" t="s">
-        <v>64</v>
+        <v>298</v>
       </c>
       <c r="J259" s="5"/>
     </row>
     <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>160310</v>
+        <v>1608</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C260" s="4">
-        <v>1603</v>
+        <v>16</v>
       </c>
       <c r="D260" s="4">
-        <v>160310</v>
+        <v>1608</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="H260" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="H260" s="5"/>
       <c r="I260" s="5" t="s">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="J260" s="5"/>
     </row>
     <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="4">
+      <c r="A261" s="6">
         <v>1604</v>
       </c>
-      <c r="B261" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C261" s="4">
+      <c r="B261" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="C261" s="6">
         <v>16</v>
       </c>
-      <c r="D261" s="4">
+      <c r="D261" s="6">
         <v>1604</v>
       </c>
-      <c r="E261" s="4"/>
-      <c r="F261" s="4" t="s">
+      <c r="E261" s="6"/>
+      <c r="F261" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G261" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="H261" s="5"/>
-      <c r="I261" s="5" t="s">
-        <v>298</v>
+      <c r="G261" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="H261" s="7"/>
+      <c r="I261" s="7" t="s">
+        <v>302</v>
       </c>
       <c r="J261" s="5"/>
     </row>
-    <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>1608</v>
-      </c>
-      <c r="B262" s="5" t="s">
-        <v>300</v>
+        <v>1605</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="C262" s="4">
         <v>16</v>
       </c>
       <c r="D262" s="4">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="H262" s="5"/>
-      <c r="I262" s="5" t="s">
-        <v>300</v>
+        <v>305</v>
+      </c>
+      <c r="I262" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="J262" s="5"/>
     </row>
-    <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="7">
-        <v>1604</v>
-      </c>
-      <c r="B263" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C263" s="7">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A263" s="4">
+        <v>1606</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C263" s="4">
         <v>16</v>
       </c>
-      <c r="D263" s="7">
-        <v>1604</v>
-      </c>
-      <c r="E263" s="7"/>
-      <c r="F263" s="7" t="s">
+      <c r="D263" s="4">
+        <v>1606</v>
+      </c>
+      <c r="E263" s="4"/>
+      <c r="F263" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G263" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="H263" s="8"/>
-      <c r="I263" s="8" t="s">
-        <v>302</v>
+      <c r="G263" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="J263" s="5"/>
     </row>
-    <row r="264" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C264" s="4">
         <v>16</v>
       </c>
       <c r="D264" s="4">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G264" s="5" t="s">
-        <v>305</v>
-      </c>
+      <c r="G264" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H264" s="1"/>
       <c r="I264" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="J264" s="5"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>1606</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>306</v>
+        <v>2</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="C265" s="4">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="D265" s="4">
-        <v>1606</v>
+        <v>2</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G265" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H265" s="1"/>
-      <c r="I265" s="1" t="s">
-        <v>306</v>
+        <v>52</v>
+      </c>
+      <c r="G265" s="5"/>
+      <c r="H265" s="5"/>
+      <c r="I265" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="J265" s="5"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>1607</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>308</v>
+        <v>21</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>311</v>
       </c>
       <c r="C266" s="4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D266" s="4">
-        <v>1607</v>
+        <v>21</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="H266" s="1"/>
-      <c r="I266" s="1" t="s">
-        <v>308</v>
+        <v>52</v>
+      </c>
+      <c r="G266" s="5"/>
+      <c r="H266" s="5"/>
+      <c r="I266" s="5" t="s">
+        <v>311</v>
       </c>
       <c r="J266" s="5"/>
     </row>
     <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>2</v>
+        <v>2110</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C267" s="4">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="D267" s="4">
-        <v>2</v>
+        <v>2110</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G267" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G267" s="5" t="s">
+        <v>313</v>
+      </c>
       <c r="H267" s="5"/>
       <c r="I267" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J267" s="5"/>
     </row>
     <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
+        <v>2111</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C268" s="4">
         <v>21</v>
       </c>
-      <c r="B268" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C268" s="4">
-        <v>2</v>
-      </c>
       <c r="D268" s="4">
-        <v>21</v>
+        <v>2111</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G268" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>315</v>
+      </c>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J268" s="5"/>
     </row>
     <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>2110</v>
+        <v>22</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C269" s="4">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D269" s="4">
-        <v>2110</v>
+        <v>22</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G269" s="5" t="s">
-        <v>313</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="J269" s="5"/>
     </row>
     <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
-        <v>2111</v>
+        <v>2201</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C270" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D270" s="4">
-        <v>2111</v>
+        <v>2201</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J270" s="5"/>
     </row>
     <row r="271" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
+        <v>2202</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C271" s="4">
         <v>22</v>
       </c>
-      <c r="B271" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C271" s="4">
-        <v>2</v>
-      </c>
       <c r="D271" s="4">
-        <v>22</v>
+        <v>2202</v>
       </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G271" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G271" s="5" t="s">
+        <v>320</v>
+      </c>
       <c r="H271" s="5"/>
       <c r="I271" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J271" s="5"/>
     </row>
     <row r="272" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C272" s="4">
         <v>22</v>
       </c>
       <c r="D272" s="4">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H272" s="5"/>
       <c r="I272" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J272" s="5"/>
     </row>
     <row r="273" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>2202</v>
+        <v>23</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C273" s="4">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D273" s="4">
-        <v>2202</v>
+        <v>23</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G273" s="5" t="s">
-        <v>320</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G273" s="5"/>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J273" s="5"/>
     </row>
     <row r="274" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>2203</v>
+        <v>2301</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C274" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D274" s="4">
-        <v>2203</v>
+        <v>2301</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J274" s="5"/>
     </row>
     <row r="275" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
+        <v>2302</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C275" s="4">
         <v>23</v>
       </c>
-      <c r="B275" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C275" s="4">
-        <v>2</v>
-      </c>
       <c r="D275" s="4">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="4" t="s">
@@ -14985,304 +14962,304 @@
       <c r="G275" s="5"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J275" s="5"/>
     </row>
     <row r="276" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
-        <v>2301</v>
+        <v>23021</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C276" s="4">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D276" s="4">
-        <v>2301</v>
+        <v>23021</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H276" s="5"/>
       <c r="I276" s="5" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="J276" s="5"/>
     </row>
     <row r="277" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
+        <v>23022</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C277" s="4">
         <v>2302</v>
       </c>
-      <c r="B277" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="C277" s="4">
-        <v>23</v>
-      </c>
       <c r="D277" s="4">
-        <v>2302</v>
+        <v>23022</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G277" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G277" s="5" t="s">
+        <v>331</v>
+      </c>
       <c r="H277" s="5"/>
       <c r="I277" s="5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="J277" s="5"/>
     </row>
     <row r="278" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>23021</v>
+        <v>2303</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="C278" s="4">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D278" s="4">
-        <v>23021</v>
+        <v>2303</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G278" s="5" t="s">
-        <v>328</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G278" s="5"/>
       <c r="H278" s="5"/>
       <c r="I278" s="5" t="s">
-        <v>329</v>
+        <v>274</v>
       </c>
       <c r="J278" s="5"/>
     </row>
     <row r="279" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
-        <v>23022</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>330</v>
+        <v>23031</v>
+      </c>
+      <c r="B279" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="C279" s="4">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="D279" s="4">
-        <v>23022</v>
+        <v>23031</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G279" s="5" t="s">
-        <v>331</v>
+      <c r="G279" s="10" t="s">
+        <v>334</v>
       </c>
       <c r="H279" s="5"/>
-      <c r="I279" s="5" t="s">
-        <v>332</v>
+      <c r="I279" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="J279" s="5"/>
     </row>
     <row r="280" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
+        <v>23032</v>
+      </c>
+      <c r="B280" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C280" s="4">
         <v>2303</v>
       </c>
-      <c r="B280" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C280" s="4">
-        <v>23</v>
-      </c>
       <c r="D280" s="4">
-        <v>2303</v>
+        <v>23032</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G280" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G280" s="10" t="s">
+        <v>336</v>
+      </c>
       <c r="H280" s="5"/>
-      <c r="I280" s="5" t="s">
-        <v>274</v>
+      <c r="I280" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="J280" s="5"/>
     </row>
     <row r="281" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
-        <v>23031</v>
-      </c>
-      <c r="B281" s="14" t="s">
-        <v>333</v>
+        <v>23033</v>
+      </c>
+      <c r="B281" s="10" t="s">
+        <v>337</v>
       </c>
       <c r="C281" s="4">
         <v>2303</v>
       </c>
       <c r="D281" s="4">
-        <v>23031</v>
+        <v>23033</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G281" s="14" t="s">
-        <v>334</v>
+      <c r="G281" s="10" t="s">
+        <v>338</v>
       </c>
       <c r="H281" s="5"/>
-      <c r="I281" s="14" t="s">
-        <v>333</v>
+      <c r="I281" s="10" t="s">
+        <v>337</v>
       </c>
       <c r="J281" s="5"/>
     </row>
     <row r="282" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
-        <v>23032</v>
-      </c>
-      <c r="B282" s="14" t="s">
-        <v>335</v>
+        <v>23034</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>339</v>
       </c>
       <c r="C282" s="4">
         <v>2303</v>
       </c>
       <c r="D282" s="4">
-        <v>23032</v>
+        <v>23034</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G282" s="14" t="s">
-        <v>336</v>
+      <c r="G282" s="10" t="s">
+        <v>340</v>
       </c>
       <c r="H282" s="5"/>
-      <c r="I282" s="14" t="s">
-        <v>335</v>
+      <c r="I282" s="10" t="s">
+        <v>339</v>
       </c>
       <c r="J282" s="5"/>
     </row>
     <row r="283" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
-        <v>23033</v>
-      </c>
-      <c r="B283" s="14" t="s">
-        <v>337</v>
+        <v>23035</v>
+      </c>
+      <c r="B283" s="10" t="s">
+        <v>341</v>
       </c>
       <c r="C283" s="4">
         <v>2303</v>
       </c>
       <c r="D283" s="4">
-        <v>23033</v>
+        <v>23035</v>
       </c>
       <c r="E283" s="4"/>
       <c r="F283" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G283" s="14" t="s">
-        <v>338</v>
+      <c r="G283" s="10" t="s">
+        <v>342</v>
       </c>
       <c r="H283" s="5"/>
-      <c r="I283" s="14" t="s">
-        <v>337</v>
+      <c r="I283" s="10" t="s">
+        <v>341</v>
       </c>
       <c r="J283" s="5"/>
     </row>
     <row r="284" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
-        <v>23034</v>
-      </c>
-      <c r="B284" s="14" t="s">
-        <v>339</v>
+        <v>23036</v>
+      </c>
+      <c r="B284" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="C284" s="4">
         <v>2303</v>
       </c>
       <c r="D284" s="4">
-        <v>23034</v>
+        <v>23036</v>
       </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G284" s="14" t="s">
-        <v>340</v>
+      <c r="G284" s="10" t="s">
+        <v>344</v>
       </c>
       <c r="H284" s="5"/>
-      <c r="I284" s="14" t="s">
-        <v>339</v>
+      <c r="I284" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="J284" s="5"/>
     </row>
     <row r="285" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
-        <v>23035</v>
-      </c>
-      <c r="B285" s="14" t="s">
-        <v>341</v>
+        <v>2304</v>
+      </c>
+      <c r="B285" s="10" t="s">
+        <v>345</v>
       </c>
       <c r="C285" s="4">
-        <v>2303</v>
+        <v>23</v>
       </c>
       <c r="D285" s="4">
-        <v>23035</v>
+        <v>2304</v>
       </c>
       <c r="E285" s="4"/>
       <c r="F285" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G285" s="14" t="s">
-        <v>342</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G285" s="5"/>
       <c r="H285" s="5"/>
-      <c r="I285" s="14" t="s">
-        <v>341</v>
+      <c r="I285" s="10" t="s">
+        <v>345</v>
       </c>
       <c r="J285" s="5"/>
     </row>
     <row r="286" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
-        <v>23036</v>
-      </c>
-      <c r="B286" s="14" t="s">
-        <v>343</v>
+        <v>23041</v>
+      </c>
+      <c r="B286" s="10" t="s">
+        <v>346</v>
       </c>
       <c r="C286" s="4">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="D286" s="4">
-        <v>23036</v>
+        <v>23041</v>
       </c>
       <c r="E286" s="4"/>
       <c r="F286" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G286" s="14" t="s">
-        <v>344</v>
+      <c r="G286" s="10" t="s">
+        <v>347</v>
       </c>
       <c r="H286" s="5"/>
-      <c r="I286" s="14" t="s">
-        <v>343</v>
+      <c r="I286" s="10" t="s">
+        <v>346</v>
       </c>
       <c r="J286" s="5"/>
     </row>
     <row r="287" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
-        <v>2304</v>
-      </c>
-      <c r="B287" s="14" t="s">
-        <v>345</v>
+        <v>2305</v>
+      </c>
+      <c r="B287" s="18" t="s">
+        <v>380</v>
       </c>
       <c r="C287" s="4">
         <v>23</v>
       </c>
       <c r="D287" s="4">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="E287" s="4"/>
       <c r="F287" s="4" t="s">
@@ -15290,40 +15267,40 @@
       </c>
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
-      <c r="I287" s="14" t="s">
-        <v>345</v>
+      <c r="I287" s="18" t="s">
+        <v>380</v>
       </c>
       <c r="J287" s="5"/>
     </row>
     <row r="288" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>23041</v>
-      </c>
-      <c r="B288" s="14" t="s">
-        <v>346</v>
+        <v>23051</v>
+      </c>
+      <c r="B288" s="18" t="s">
+        <v>382</v>
       </c>
       <c r="C288" s="4">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D288" s="4">
-        <v>23041</v>
+        <v>23051</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G288" s="14" t="s">
-        <v>347</v>
+      <c r="G288" s="18" t="s">
+        <v>381</v>
       </c>
       <c r="H288" s="5"/>
-      <c r="I288" s="14" t="s">
-        <v>346</v>
+      <c r="I288" s="18" t="s">
+        <v>382</v>
       </c>
       <c r="J288" s="5"/>
     </row>
     <row r="289" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>348</v>
@@ -15332,7 +15309,7 @@
         <v>23</v>
       </c>
       <c r="D289" s="4">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="E289" s="4"/>
       <c r="F289" s="4" t="s">
@@ -15347,16 +15324,16 @@
     </row>
     <row r="290" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
-        <v>23051</v>
+        <v>23061</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>349</v>
       </c>
       <c r="C290" s="4">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="D290" s="4">
-        <v>23051</v>
+        <v>23061</v>
       </c>
       <c r="E290" s="4"/>
       <c r="F290" s="4" t="s">
@@ -15373,16 +15350,16 @@
     </row>
     <row r="291" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
-        <v>23052</v>
+        <v>23062</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>351</v>
       </c>
       <c r="C291" s="4">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="D291" s="4">
-        <v>23052</v>
+        <v>23062</v>
       </c>
       <c r="E291" s="4"/>
       <c r="F291" s="4" t="s">
@@ -15397,18 +15374,18 @@
       </c>
       <c r="J291" s="5"/>
     </row>
-    <row r="292" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
-        <v>23053</v>
+        <v>23063</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>353</v>
       </c>
       <c r="C292" s="4">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="D292" s="4">
-        <v>23053</v>
+        <v>23063</v>
       </c>
       <c r="E292" s="4"/>
       <c r="F292" s="4" t="s">
@@ -15423,152 +15400,152 @@
       </c>
       <c r="J292" s="5"/>
     </row>
-    <row r="293" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>23054</v>
+        <v>2307</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>356</v>
       </c>
       <c r="C293" s="4">
-        <v>2305</v>
+        <v>23</v>
       </c>
       <c r="D293" s="4">
-        <v>23054</v>
+        <v>2307</v>
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G293" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="H293" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G293" s="4"/>
+      <c r="H293" s="4"/>
       <c r="I293" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J293" s="5"/>
     </row>
     <row r="294" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
-        <v>2306</v>
+        <v>23071</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C294" s="4">
-        <v>23</v>
+        <v>2307</v>
       </c>
       <c r="D294" s="4">
-        <v>2306</v>
+        <v>23071</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G294" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="G294" s="18" t="s">
+        <v>377</v>
+      </c>
       <c r="H294" s="4"/>
       <c r="I294" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J294" s="5"/>
     </row>
     <row r="295" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
-        <v>23061</v>
+        <v>23072</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C295" s="4">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="D295" s="4">
-        <v>23061</v>
+        <v>23072</v>
       </c>
       <c r="E295" s="4"/>
       <c r="F295" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G295" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="H295" s="4"/>
+      <c r="G295" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="H295" s="5"/>
       <c r="I295" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J295" s="5"/>
     </row>
     <row r="296" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
-        <v>23062</v>
-      </c>
-      <c r="B296" s="5" t="s">
-        <v>361</v>
+        <v>23073</v>
+      </c>
+      <c r="B296" s="18" t="s">
+        <v>378</v>
       </c>
       <c r="C296" s="4">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="D296" s="4">
-        <v>23062</v>
+        <v>23073</v>
       </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G296" s="5" t="s">
-        <v>362</v>
+      <c r="G296" s="18" t="s">
+        <v>379</v>
       </c>
       <c r="H296" s="5"/>
-      <c r="I296" s="5" t="s">
-        <v>361</v>
+      <c r="I296" s="18" t="s">
+        <v>378</v>
       </c>
       <c r="J296" s="5"/>
     </row>
     <row r="297" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
-        <v>23063</v>
-      </c>
-      <c r="B297" s="14" t="s">
-        <v>380</v>
+        <v>24</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>360</v>
       </c>
       <c r="C297" s="4">
-        <v>2306</v>
+        <v>2</v>
       </c>
       <c r="D297" s="4">
-        <v>23063</v>
-      </c>
-      <c r="E297" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E297" s="5"/>
       <c r="F297" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G297" s="14" t="s">
-        <v>382</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G297" s="5"/>
       <c r="H297" s="5"/>
-      <c r="I297" s="14" t="s">
-        <v>380</v>
+      <c r="I297" s="5" t="s">
+        <v>360</v>
       </c>
       <c r="J297" s="5"/>
     </row>
     <row r="298" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
+        <v>2401</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C298" s="4">
         <v>24</v>
       </c>
-      <c r="B298" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C298" s="4">
-        <v>2</v>
-      </c>
       <c r="D298" s="4">
-        <v>24</v>
+        <v>2401</v>
       </c>
       <c r="E298" s="5"/>
       <c r="F298" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G298" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G298" s="5" t="s">
+        <v>362</v>
+      </c>
       <c r="H298" s="5"/>
       <c r="I298" s="5" t="s">
         <v>363</v>
@@ -15577,7 +15554,7 @@
     </row>
     <row r="299" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>364</v>
@@ -15586,137 +15563,111 @@
         <v>24</v>
       </c>
       <c r="D299" s="4">
-        <v>2401</v>
-      </c>
-      <c r="E299" s="5"/>
+        <v>2402</v>
+      </c>
+      <c r="E299" s="4"/>
       <c r="F299" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G299" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="H299" s="5"/>
+      <c r="H299" s="4"/>
       <c r="I299" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="J299" s="5"/>
+    </row>
+    <row r="300" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="4">
+        <v>2403</v>
+      </c>
+      <c r="B300" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="J299" s="5"/>
-    </row>
-    <row r="300" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A300" s="4">
-        <v>2402</v>
-      </c>
-      <c r="B300" s="5" t="s">
-        <v>367</v>
       </c>
       <c r="C300" s="4">
         <v>24</v>
       </c>
       <c r="D300" s="4">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G300" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="H300" s="4"/>
-      <c r="I300" s="5" t="s">
+      <c r="G300" s="5"/>
+      <c r="I300" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J300" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K300"/>
+      <c r="L300"/>
+      <c r="M300"/>
+      <c r="N300"/>
+      <c r="O300"/>
+      <c r="P300"/>
+      <c r="Q300"/>
+      <c r="R300"/>
+      <c r="S300"/>
+      <c r="T300"/>
+      <c r="U300"/>
+      <c r="V300"/>
+      <c r="W300"/>
+      <c r="X300"/>
+      <c r="Y300"/>
+      <c r="Z300" s="11"/>
+    </row>
+    <row r="301" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A301" s="4">
+        <v>25</v>
+      </c>
+      <c r="B301" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="J300" s="5"/>
-    </row>
-    <row r="301" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="4">
-        <v>2403</v>
-      </c>
-      <c r="B301" s="5" t="s">
-        <v>369</v>
-      </c>
       <c r="C301" s="4">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D301" s="4">
-        <v>2403</v>
+        <v>25</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G301" s="5"/>
-      <c r="I301" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="J301" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K301"/>
-      <c r="L301"/>
-      <c r="M301"/>
-      <c r="N301"/>
-      <c r="O301"/>
-      <c r="P301"/>
-      <c r="Q301"/>
-      <c r="R301"/>
-      <c r="S301"/>
-      <c r="T301"/>
-      <c r="U301"/>
-      <c r="V301"/>
-      <c r="W301"/>
-      <c r="X301"/>
-      <c r="Y301"/>
-      <c r="Z301" s="16"/>
+      <c r="H301" s="5"/>
+      <c r="I301" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="J301" s="5"/>
     </row>
     <row r="302" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
+        <v>2501</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C302" s="4">
         <v>25</v>
       </c>
-      <c r="B302" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="C302" s="4">
-        <v>2</v>
-      </c>
       <c r="D302" s="4">
-        <v>25</v>
-      </c>
-      <c r="E302" s="4"/>
+        <v>2501</v>
+      </c>
+      <c r="E302" s="5"/>
       <c r="F302" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G302" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G302" s="5" t="s">
+        <v>369</v>
+      </c>
       <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J302" s="5"/>
-    </row>
-    <row r="303" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A303" s="4">
-        <v>2501</v>
-      </c>
-      <c r="B303" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C303" s="4">
-        <v>25</v>
-      </c>
-      <c r="D303" s="4">
-        <v>2501</v>
-      </c>
-      <c r="E303" s="5"/>
-      <c r="F303" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G303" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="H303" s="5"/>
-      <c r="I303" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="J303" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41666820-1823-471A-9A6C-A960EEE2BE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5F378-1409-453B-BCAA-9308093ACBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="382">
   <si>
     <t>Id</t>
   </si>
@@ -868,9 +868,6 @@
     <t>AOD</t>
   </si>
   <si>
-    <t>Aod Alignment</t>
-  </si>
-  <si>
     <t>XY Astigmatism</t>
   </si>
   <si>
@@ -878,9 +875,6 @@
   </si>
   <si>
     <t>Illumination Profile</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserIlluminationProfileCalibrationViewModel</t>
   </si>
   <si>
     <t>CIB</t>
@@ -1225,10 +1219,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserPrescanChirpAodAlignmentCalibrationViewModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>CugaCalibration.ViewModels.AOD.AODDelayViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1254,6 +1244,14 @@
   </si>
   <si>
     <t>Objective Y Angle</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Laser.LaserIlluminationProfileCalibrationViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.AOD.AODAlignmentViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1419,7 +1417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1475,6 +1473,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -13743,7 +13744,7 @@
         <v>55</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
@@ -13769,7 +13770,7 @@
         <v>55</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5" t="s">
@@ -13806,7 +13807,7 @@
         <v>15</v>
       </c>
       <c r="B232" s="18" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C232" s="4">
         <v>1</v>
@@ -13830,7 +13831,7 @@
         <v>1501</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C233" s="4">
         <v>15</v>
@@ -13843,11 +13844,11 @@
         <v>55</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H233" s="5"/>
       <c r="I233" s="18" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J233" s="5"/>
     </row>
@@ -13856,7 +13857,7 @@
         <v>1502</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
@@ -13869,11 +13870,11 @@
         <v>55</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H234" s="5"/>
-      <c r="I234" s="5" t="s">
-        <v>275</v>
+      <c r="I234" s="18" t="s">
+        <v>370</v>
       </c>
       <c r="J234" s="5"/>
     </row>
@@ -13882,7 +13883,7 @@
         <v>1503</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C235" s="4">
         <v>15</v>
@@ -13895,11 +13896,11 @@
         <v>55</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H235" s="5"/>
       <c r="I235" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J235" s="5"/>
     </row>
@@ -13908,7 +13909,7 @@
         <v>1504</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C236" s="6">
         <v>15</v>
@@ -13920,12 +13921,12 @@
       <c r="F236" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G236" s="7" t="s">
-        <v>279</v>
+      <c r="G236" s="19" t="s">
+        <v>380</v>
       </c>
       <c r="H236" s="7"/>
       <c r="I236" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J236" s="5"/>
     </row>
@@ -13934,7 +13935,7 @@
         <v>16</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C237" s="8">
         <v>1</v>
@@ -13949,7 +13950,7 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J237" s="5"/>
     </row>
@@ -13958,7 +13959,7 @@
         <v>1601</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C238" s="4">
         <v>16</v>
@@ -13971,11 +13972,11 @@
         <v>55</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H238" s="5"/>
       <c r="I238" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J238" s="5"/>
     </row>
@@ -13997,7 +13998,7 @@
         <v>55</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H239" s="5"/>
       <c r="I239" s="5" t="s">
@@ -14023,7 +14024,7 @@
         <v>58</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H240" s="5" t="s">
         <v>60</v>
@@ -14051,7 +14052,7 @@
         <v>58</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>61</v>
@@ -14079,13 +14080,13 @@
         <v>68</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H242" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I242" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J242" s="5"/>
     </row>
@@ -14107,7 +14108,7 @@
         <v>58</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>64</v>
@@ -14135,7 +14136,7 @@
         <v>58</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H244" s="5" t="s">
         <v>65</v>
@@ -14163,7 +14164,7 @@
         <v>68</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H245" s="5" t="s">
         <v>69</v>
@@ -14191,7 +14192,7 @@
         <v>58</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>64</v>
@@ -14219,7 +14220,7 @@
         <v>58</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>65</v>
@@ -14234,7 +14235,7 @@
         <v>1603</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C248" s="4">
         <v>16</v>
@@ -14247,11 +14248,11 @@
         <v>55</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H248" s="5"/>
       <c r="I248" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J248" s="5"/>
     </row>
@@ -14260,7 +14261,7 @@
         <v>160301</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C249" s="4">
         <v>1603</v>
@@ -14273,7 +14274,7 @@
         <v>58</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H249" s="5" t="s">
         <v>156</v>
@@ -14288,7 +14289,7 @@
         <v>160302</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C250" s="4">
         <v>1603</v>
@@ -14301,7 +14302,7 @@
         <v>58</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H250" s="5" t="s">
         <v>60</v>
@@ -14316,7 +14317,7 @@
         <v>160303</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C251" s="4">
         <v>1603</v>
@@ -14329,7 +14330,7 @@
         <v>58</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>61</v>
@@ -14344,7 +14345,7 @@
         <v>160304</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C252" s="4">
         <v>1603</v>
@@ -14357,13 +14358,13 @@
         <v>58</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I252" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J252" s="5"/>
     </row>
@@ -14372,7 +14373,7 @@
         <v>160305</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C253" s="4">
         <v>1603</v>
@@ -14385,13 +14386,13 @@
         <v>58</v>
       </c>
       <c r="G253" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H253" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="H253" s="5" t="s">
-        <v>295</v>
-      </c>
       <c r="I253" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J253" s="5"/>
     </row>
@@ -14400,7 +14401,7 @@
         <v>160306</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C254" s="4">
         <v>1603</v>
@@ -14413,7 +14414,7 @@
         <v>58</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H254" s="5" t="s">
         <v>64</v>
@@ -14428,7 +14429,7 @@
         <v>160307</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C255" s="4">
         <v>1603</v>
@@ -14441,7 +14442,7 @@
         <v>58</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H255" s="5" t="s">
         <v>65</v>
@@ -14456,7 +14457,7 @@
         <v>160308</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C256" s="4">
         <v>1603</v>
@@ -14469,7 +14470,7 @@
         <v>68</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H256" s="5" t="s">
         <v>161</v>
@@ -14484,7 +14485,7 @@
         <v>160309</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C257" s="4">
         <v>1603</v>
@@ -14497,7 +14498,7 @@
         <v>58</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H257" s="5" t="s">
         <v>64</v>
@@ -14512,7 +14513,7 @@
         <v>160310</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C258" s="4">
         <v>1603</v>
@@ -14525,7 +14526,7 @@
         <v>58</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H258" s="5" t="s">
         <v>65</v>
@@ -14540,7 +14541,7 @@
         <v>1604</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C259" s="4">
         <v>16</v>
@@ -14553,11 +14554,11 @@
         <v>55</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H259" s="5"/>
       <c r="I259" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J259" s="5"/>
     </row>
@@ -14566,7 +14567,7 @@
         <v>1608</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C260" s="4">
         <v>16</v>
@@ -14579,11 +14580,11 @@
         <v>55</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H260" s="5"/>
       <c r="I260" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J260" s="5"/>
     </row>
@@ -14592,7 +14593,7 @@
         <v>1604</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C261" s="6">
         <v>16</v>
@@ -14605,11 +14606,11 @@
         <v>55</v>
       </c>
       <c r="G261" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H261" s="7"/>
       <c r="I261" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J261" s="5"/>
     </row>
@@ -14618,7 +14619,7 @@
         <v>1605</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C262" s="4">
         <v>16</v>
@@ -14631,10 +14632,10 @@
         <v>55</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J262" s="5"/>
     </row>
@@ -14643,7 +14644,7 @@
         <v>1606</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C263" s="4">
         <v>16</v>
@@ -14656,11 +14657,11 @@
         <v>55</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J263" s="5"/>
     </row>
@@ -14669,7 +14670,7 @@
         <v>1607</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C264" s="4">
         <v>16</v>
@@ -14682,11 +14683,11 @@
         <v>55</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J264" s="5"/>
     </row>
@@ -14695,7 +14696,7 @@
         <v>2</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C265" s="4">
         <v>-1</v>
@@ -14710,7 +14711,7 @@
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
       <c r="I265" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J265" s="5"/>
     </row>
@@ -14719,7 +14720,7 @@
         <v>21</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C266" s="4">
         <v>2</v>
@@ -14734,7 +14735,7 @@
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J266" s="5"/>
     </row>
@@ -14743,7 +14744,7 @@
         <v>2110</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C267" s="4">
         <v>21</v>
@@ -14756,11 +14757,11 @@
         <v>55</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H267" s="5"/>
       <c r="I267" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J267" s="5"/>
     </row>
@@ -14769,7 +14770,7 @@
         <v>2111</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C268" s="4">
         <v>21</v>
@@ -14782,11 +14783,11 @@
         <v>55</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J268" s="5"/>
     </row>
@@ -14795,7 +14796,7 @@
         <v>22</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C269" s="4">
         <v>2</v>
@@ -14810,7 +14811,7 @@
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J269" s="5"/>
     </row>
@@ -14819,7 +14820,7 @@
         <v>2201</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C270" s="4">
         <v>22</v>
@@ -14832,11 +14833,11 @@
         <v>55</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J270" s="5"/>
     </row>
@@ -14845,7 +14846,7 @@
         <v>2202</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C271" s="4">
         <v>22</v>
@@ -14858,11 +14859,11 @@
         <v>55</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H271" s="5"/>
       <c r="I271" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J271" s="5"/>
     </row>
@@ -14871,7 +14872,7 @@
         <v>2203</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C272" s="4">
         <v>22</v>
@@ -14884,11 +14885,11 @@
         <v>55</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H272" s="5"/>
       <c r="I272" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J272" s="5"/>
     </row>
@@ -14897,7 +14898,7 @@
         <v>23</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C273" s="4">
         <v>2</v>
@@ -14912,7 +14913,7 @@
       <c r="G273" s="5"/>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J273" s="5"/>
     </row>
@@ -14921,7 +14922,7 @@
         <v>2301</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C274" s="4">
         <v>23</v>
@@ -14934,11 +14935,11 @@
         <v>55</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J274" s="5"/>
     </row>
@@ -14947,7 +14948,7 @@
         <v>2302</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C275" s="4">
         <v>23</v>
@@ -14962,7 +14963,7 @@
       <c r="G275" s="5"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J275" s="5"/>
     </row>
@@ -14971,7 +14972,7 @@
         <v>23021</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C276" s="4">
         <v>2302</v>
@@ -14984,11 +14985,11 @@
         <v>55</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H276" s="5"/>
       <c r="I276" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J276" s="5"/>
     </row>
@@ -14997,7 +14998,7 @@
         <v>23022</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C277" s="4">
         <v>2302</v>
@@ -15010,11 +15011,11 @@
         <v>55</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H277" s="5"/>
       <c r="I277" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J277" s="5"/>
     </row>
@@ -15047,7 +15048,7 @@
         <v>23031</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C279" s="4">
         <v>2303</v>
@@ -15060,11 +15061,11 @@
         <v>55</v>
       </c>
       <c r="G279" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H279" s="5"/>
       <c r="I279" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J279" s="5"/>
     </row>
@@ -15073,7 +15074,7 @@
         <v>23032</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C280" s="4">
         <v>2303</v>
@@ -15086,11 +15087,11 @@
         <v>55</v>
       </c>
       <c r="G280" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H280" s="5"/>
       <c r="I280" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J280" s="5"/>
     </row>
@@ -15099,7 +15100,7 @@
         <v>23033</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C281" s="4">
         <v>2303</v>
@@ -15112,11 +15113,11 @@
         <v>55</v>
       </c>
       <c r="G281" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H281" s="5"/>
       <c r="I281" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J281" s="5"/>
     </row>
@@ -15125,7 +15126,7 @@
         <v>23034</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C282" s="4">
         <v>2303</v>
@@ -15138,11 +15139,11 @@
         <v>55</v>
       </c>
       <c r="G282" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H282" s="5"/>
       <c r="I282" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J282" s="5"/>
     </row>
@@ -15151,7 +15152,7 @@
         <v>23035</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C283" s="4">
         <v>2303</v>
@@ -15164,11 +15165,11 @@
         <v>55</v>
       </c>
       <c r="G283" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H283" s="5"/>
       <c r="I283" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J283" s="5"/>
     </row>
@@ -15177,7 +15178,7 @@
         <v>23036</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C284" s="4">
         <v>2303</v>
@@ -15190,11 +15191,11 @@
         <v>55</v>
       </c>
       <c r="G284" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H284" s="5"/>
       <c r="I284" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J284" s="5"/>
     </row>
@@ -15203,7 +15204,7 @@
         <v>2304</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C285" s="4">
         <v>23</v>
@@ -15218,7 +15219,7 @@
       <c r="G285" s="5"/>
       <c r="H285" s="5"/>
       <c r="I285" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J285" s="5"/>
     </row>
@@ -15227,7 +15228,7 @@
         <v>23041</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C286" s="4">
         <v>2304</v>
@@ -15240,11 +15241,11 @@
         <v>55</v>
       </c>
       <c r="G286" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H286" s="5"/>
       <c r="I286" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J286" s="5"/>
     </row>
@@ -15253,7 +15254,7 @@
         <v>2305</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C287" s="4">
         <v>23</v>
@@ -15268,7 +15269,7 @@
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
       <c r="I287" s="18" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J287" s="5"/>
     </row>
@@ -15277,7 +15278,7 @@
         <v>23051</v>
       </c>
       <c r="B288" s="18" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C288" s="4">
         <v>2305</v>
@@ -15290,11 +15291,11 @@
         <v>55</v>
       </c>
       <c r="G288" s="18" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H288" s="5"/>
       <c r="I288" s="18" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="J288" s="5"/>
     </row>
@@ -15303,7 +15304,7 @@
         <v>2306</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C289" s="4">
         <v>23</v>
@@ -15318,7 +15319,7 @@
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
       <c r="I289" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J289" s="5"/>
     </row>
@@ -15327,7 +15328,7 @@
         <v>23061</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C290" s="4">
         <v>2306</v>
@@ -15340,11 +15341,11 @@
         <v>55</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H290" s="5"/>
       <c r="I290" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J290" s="5"/>
     </row>
@@ -15353,7 +15354,7 @@
         <v>23062</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C291" s="4">
         <v>2306</v>
@@ -15366,11 +15367,11 @@
         <v>55</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H291" s="5"/>
       <c r="I291" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J291" s="5"/>
     </row>
@@ -15379,7 +15380,7 @@
         <v>23063</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C292" s="4">
         <v>2306</v>
@@ -15392,11 +15393,11 @@
         <v>55</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H292" s="5"/>
       <c r="I292" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J292" s="5"/>
     </row>
@@ -15405,7 +15406,7 @@
         <v>2307</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C293" s="4">
         <v>23</v>
@@ -15420,7 +15421,7 @@
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
       <c r="I293" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J293" s="5"/>
     </row>
@@ -15429,7 +15430,7 @@
         <v>23071</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C294" s="4">
         <v>2307</v>
@@ -15442,11 +15443,11 @@
         <v>55</v>
       </c>
       <c r="G294" s="18" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H294" s="4"/>
       <c r="I294" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J294" s="5"/>
     </row>
@@ -15455,7 +15456,7 @@
         <v>23072</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C295" s="4">
         <v>2307</v>
@@ -15468,11 +15469,11 @@
         <v>55</v>
       </c>
       <c r="G295" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H295" s="5"/>
       <c r="I295" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J295" s="5"/>
     </row>
@@ -15481,7 +15482,7 @@
         <v>23073</v>
       </c>
       <c r="B296" s="18" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C296" s="4">
         <v>2307</v>
@@ -15494,11 +15495,11 @@
         <v>55</v>
       </c>
       <c r="G296" s="18" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H296" s="5"/>
       <c r="I296" s="18" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J296" s="5"/>
     </row>
@@ -15507,7 +15508,7 @@
         <v>24</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C297" s="4">
         <v>2</v>
@@ -15522,7 +15523,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J297" s="5"/>
     </row>
@@ -15531,7 +15532,7 @@
         <v>2401</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C298" s="4">
         <v>24</v>
@@ -15544,11 +15545,11 @@
         <v>55</v>
       </c>
       <c r="G298" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H298" s="5"/>
       <c r="I298" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J298" s="5"/>
     </row>
@@ -15557,7 +15558,7 @@
         <v>2402</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C299" s="4">
         <v>24</v>
@@ -15570,11 +15571,11 @@
         <v>55</v>
       </c>
       <c r="G299" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H299" s="4"/>
       <c r="I299" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J299" s="5"/>
     </row>
@@ -15583,7 +15584,7 @@
         <v>2403</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C300" s="4">
         <v>24</v>
@@ -15597,7 +15598,7 @@
       </c>
       <c r="G300" s="5"/>
       <c r="I300" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J300" s="1" t="b">
         <v>1</v>
@@ -15624,7 +15625,7 @@
         <v>25</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C301" s="4">
         <v>2</v>
@@ -15639,7 +15640,7 @@
       <c r="G301" s="5"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J301" s="5"/>
     </row>
@@ -15648,7 +15649,7 @@
         <v>2501</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C302" s="4">
         <v>25</v>
@@ -15661,11 +15662,11 @@
         <v>55</v>
       </c>
       <c r="G302" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J302" s="5"/>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5F378-1409-453B-BCAA-9308093ACBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB6171D-6CD2-4645-99C6-FA518E4FC4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -943,12 +943,6 @@
     <t>CugaCalibration.ViewModels.Laser.LaserPmtAgcDelayCalibrationViewModel</t>
   </si>
   <si>
-    <t>Pmt Gain</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserPmtGainCalibrationViewModel</t>
-  </si>
-  <si>
     <t>X Pixel Size</t>
   </si>
   <si>
@@ -1026,6 +1020,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>CugaCalibration.ViewModels.Common.Windows.Tools.Alignment.AlignmentWindow</t>
@@ -1035,6 +1030,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>BrightField</t>
@@ -1044,6 +1040,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ViewModel</t>
@@ -1058,6 +1055,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dark</t>
@@ -1067,6 +1065,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Field</t>
@@ -1076,6 +1075,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Alignment</t>
@@ -1252,6 +1252,14 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.AOD.AODAlignmentViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMD</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.CIB.CIBMMDViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1271,18 +1279,21 @@
       <sz val="18"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1290,6 +1301,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1297,6 +1309,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1304,6 +1317,7 @@
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1417,7 +1431,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1476,6 +1490,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -13744,7 +13761,7 @@
         <v>55</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
@@ -13770,7 +13787,7 @@
         <v>55</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5" t="s">
@@ -13807,7 +13824,7 @@
         <v>15</v>
       </c>
       <c r="B232" s="18" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C232" s="4">
         <v>1</v>
@@ -13831,7 +13848,7 @@
         <v>1501</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C233" s="4">
         <v>15</v>
@@ -13844,11 +13861,11 @@
         <v>55</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H233" s="5"/>
       <c r="I233" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J233" s="5"/>
     </row>
@@ -13857,7 +13874,7 @@
         <v>1502</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
@@ -13870,11 +13887,11 @@
         <v>55</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H234" s="5"/>
       <c r="I234" s="18" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J234" s="5"/>
     </row>
@@ -13922,7 +13939,7 @@
         <v>55</v>
       </c>
       <c r="G236" s="19" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H236" s="7"/>
       <c r="I236" s="7" t="s">
@@ -14592,8 +14609,8 @@
       <c r="A261" s="6">
         <v>1604</v>
       </c>
-      <c r="B261" s="7" t="s">
-        <v>300</v>
+      <c r="B261" s="20" t="s">
+        <v>380</v>
       </c>
       <c r="C261" s="6">
         <v>16</v>
@@ -14605,12 +14622,12 @@
       <c r="F261" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G261" s="7" t="s">
-        <v>301</v>
+      <c r="G261" s="20" t="s">
+        <v>381</v>
       </c>
       <c r="H261" s="7"/>
-      <c r="I261" s="7" t="s">
-        <v>300</v>
+      <c r="I261" s="20" t="s">
+        <v>380</v>
       </c>
       <c r="J261" s="5"/>
     </row>
@@ -14619,7 +14636,7 @@
         <v>1605</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C262" s="4">
         <v>16</v>
@@ -14632,10 +14649,10 @@
         <v>55</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J262" s="5"/>
     </row>
@@ -14644,7 +14661,7 @@
         <v>1606</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C263" s="4">
         <v>16</v>
@@ -14657,11 +14674,11 @@
         <v>55</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J263" s="5"/>
     </row>
@@ -14670,7 +14687,7 @@
         <v>1607</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C264" s="4">
         <v>16</v>
@@ -14683,11 +14700,11 @@
         <v>55</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J264" s="5"/>
     </row>
@@ -14696,7 +14713,7 @@
         <v>2</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C265" s="4">
         <v>-1</v>
@@ -14711,7 +14728,7 @@
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
       <c r="I265" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J265" s="5"/>
     </row>
@@ -14720,7 +14737,7 @@
         <v>21</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C266" s="4">
         <v>2</v>
@@ -14735,7 +14752,7 @@
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J266" s="5"/>
     </row>
@@ -14744,7 +14761,7 @@
         <v>2110</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C267" s="4">
         <v>21</v>
@@ -14757,11 +14774,11 @@
         <v>55</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H267" s="5"/>
       <c r="I267" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J267" s="5"/>
     </row>
@@ -14770,7 +14787,7 @@
         <v>2111</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C268" s="4">
         <v>21</v>
@@ -14783,11 +14800,11 @@
         <v>55</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J268" s="5"/>
     </row>
@@ -14796,7 +14813,7 @@
         <v>22</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C269" s="4">
         <v>2</v>
@@ -14811,7 +14828,7 @@
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J269" s="5"/>
     </row>
@@ -14820,7 +14837,7 @@
         <v>2201</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C270" s="4">
         <v>22</v>
@@ -14833,11 +14850,11 @@
         <v>55</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J270" s="5"/>
     </row>
@@ -14846,7 +14863,7 @@
         <v>2202</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C271" s="4">
         <v>22</v>
@@ -14859,11 +14876,11 @@
         <v>55</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H271" s="5"/>
       <c r="I271" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J271" s="5"/>
     </row>
@@ -14872,7 +14889,7 @@
         <v>2203</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C272" s="4">
         <v>22</v>
@@ -14885,11 +14902,11 @@
         <v>55</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H272" s="5"/>
       <c r="I272" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J272" s="5"/>
     </row>
@@ -14898,7 +14915,7 @@
         <v>23</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C273" s="4">
         <v>2</v>
@@ -14913,7 +14930,7 @@
       <c r="G273" s="5"/>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J273" s="5"/>
     </row>
@@ -14922,7 +14939,7 @@
         <v>2301</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C274" s="4">
         <v>23</v>
@@ -14935,11 +14952,11 @@
         <v>55</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J274" s="5"/>
     </row>
@@ -14948,7 +14965,7 @@
         <v>2302</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C275" s="4">
         <v>23</v>
@@ -14963,7 +14980,7 @@
       <c r="G275" s="5"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J275" s="5"/>
     </row>
@@ -14972,7 +14989,7 @@
         <v>23021</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C276" s="4">
         <v>2302</v>
@@ -14985,11 +15002,11 @@
         <v>55</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H276" s="5"/>
       <c r="I276" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J276" s="5"/>
     </row>
@@ -14998,7 +15015,7 @@
         <v>23022</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C277" s="4">
         <v>2302</v>
@@ -15011,11 +15028,11 @@
         <v>55</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H277" s="5"/>
       <c r="I277" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J277" s="5"/>
     </row>
@@ -15048,7 +15065,7 @@
         <v>23031</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C279" s="4">
         <v>2303</v>
@@ -15061,11 +15078,11 @@
         <v>55</v>
       </c>
       <c r="G279" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H279" s="5"/>
       <c r="I279" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J279" s="5"/>
     </row>
@@ -15074,7 +15091,7 @@
         <v>23032</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C280" s="4">
         <v>2303</v>
@@ -15087,11 +15104,11 @@
         <v>55</v>
       </c>
       <c r="G280" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H280" s="5"/>
       <c r="I280" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J280" s="5"/>
     </row>
@@ -15100,7 +15117,7 @@
         <v>23033</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C281" s="4">
         <v>2303</v>
@@ -15113,11 +15130,11 @@
         <v>55</v>
       </c>
       <c r="G281" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H281" s="5"/>
       <c r="I281" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J281" s="5"/>
     </row>
@@ -15126,7 +15143,7 @@
         <v>23034</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C282" s="4">
         <v>2303</v>
@@ -15139,11 +15156,11 @@
         <v>55</v>
       </c>
       <c r="G282" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H282" s="5"/>
       <c r="I282" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J282" s="5"/>
     </row>
@@ -15152,7 +15169,7 @@
         <v>23035</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C283" s="4">
         <v>2303</v>
@@ -15165,11 +15182,11 @@
         <v>55</v>
       </c>
       <c r="G283" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H283" s="5"/>
       <c r="I283" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J283" s="5"/>
     </row>
@@ -15178,7 +15195,7 @@
         <v>23036</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C284" s="4">
         <v>2303</v>
@@ -15191,11 +15208,11 @@
         <v>55</v>
       </c>
       <c r="G284" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H284" s="5"/>
       <c r="I284" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J284" s="5"/>
     </row>
@@ -15204,7 +15221,7 @@
         <v>2304</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C285" s="4">
         <v>23</v>
@@ -15219,7 +15236,7 @@
       <c r="G285" s="5"/>
       <c r="H285" s="5"/>
       <c r="I285" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J285" s="5"/>
     </row>
@@ -15228,7 +15245,7 @@
         <v>23041</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C286" s="4">
         <v>2304</v>
@@ -15241,11 +15258,11 @@
         <v>55</v>
       </c>
       <c r="G286" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H286" s="5"/>
       <c r="I286" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J286" s="5"/>
     </row>
@@ -15254,7 +15271,7 @@
         <v>2305</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C287" s="4">
         <v>23</v>
@@ -15269,7 +15286,7 @@
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
       <c r="I287" s="18" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J287" s="5"/>
     </row>
@@ -15278,7 +15295,7 @@
         <v>23051</v>
       </c>
       <c r="B288" s="18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C288" s="4">
         <v>2305</v>
@@ -15291,11 +15308,11 @@
         <v>55</v>
       </c>
       <c r="G288" s="18" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H288" s="5"/>
       <c r="I288" s="18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J288" s="5"/>
     </row>
@@ -15304,7 +15321,7 @@
         <v>2306</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C289" s="4">
         <v>23</v>
@@ -15319,7 +15336,7 @@
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
       <c r="I289" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J289" s="5"/>
     </row>
@@ -15328,7 +15345,7 @@
         <v>23061</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C290" s="4">
         <v>2306</v>
@@ -15341,11 +15358,11 @@
         <v>55</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H290" s="5"/>
       <c r="I290" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J290" s="5"/>
     </row>
@@ -15354,7 +15371,7 @@
         <v>23062</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C291" s="4">
         <v>2306</v>
@@ -15367,11 +15384,11 @@
         <v>55</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H291" s="5"/>
       <c r="I291" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J291" s="5"/>
     </row>
@@ -15380,7 +15397,7 @@
         <v>23063</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C292" s="4">
         <v>2306</v>
@@ -15393,11 +15410,11 @@
         <v>55</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H292" s="5"/>
       <c r="I292" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J292" s="5"/>
     </row>
@@ -15406,7 +15423,7 @@
         <v>2307</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C293" s="4">
         <v>23</v>
@@ -15421,7 +15438,7 @@
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
       <c r="I293" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J293" s="5"/>
     </row>
@@ -15430,7 +15447,7 @@
         <v>23071</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C294" s="4">
         <v>2307</v>
@@ -15443,11 +15460,11 @@
         <v>55</v>
       </c>
       <c r="G294" s="18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H294" s="4"/>
       <c r="I294" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J294" s="5"/>
     </row>
@@ -15456,7 +15473,7 @@
         <v>23072</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C295" s="4">
         <v>2307</v>
@@ -15469,11 +15486,11 @@
         <v>55</v>
       </c>
       <c r="G295" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H295" s="5"/>
       <c r="I295" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J295" s="5"/>
     </row>
@@ -15482,7 +15499,7 @@
         <v>23073</v>
       </c>
       <c r="B296" s="18" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C296" s="4">
         <v>2307</v>
@@ -15495,11 +15512,11 @@
         <v>55</v>
       </c>
       <c r="G296" s="18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H296" s="5"/>
       <c r="I296" s="18" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J296" s="5"/>
     </row>
@@ -15508,7 +15525,7 @@
         <v>24</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C297" s="4">
         <v>2</v>
@@ -15523,7 +15540,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J297" s="5"/>
     </row>
@@ -15532,7 +15549,7 @@
         <v>2401</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C298" s="4">
         <v>24</v>
@@ -15545,11 +15562,11 @@
         <v>55</v>
       </c>
       <c r="G298" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H298" s="5"/>
       <c r="I298" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J298" s="5"/>
     </row>
@@ -15558,7 +15575,7 @@
         <v>2402</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C299" s="4">
         <v>24</v>
@@ -15571,11 +15588,11 @@
         <v>55</v>
       </c>
       <c r="G299" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H299" s="4"/>
       <c r="I299" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J299" s="5"/>
     </row>
@@ -15584,7 +15601,7 @@
         <v>2403</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C300" s="4">
         <v>24</v>
@@ -15598,7 +15615,7 @@
       </c>
       <c r="G300" s="5"/>
       <c r="I300" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J300" s="1" t="b">
         <v>1</v>
@@ -15625,7 +15642,7 @@
         <v>25</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C301" s="4">
         <v>2</v>
@@ -15640,7 +15657,7 @@
       <c r="G301" s="5"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J301" s="5"/>
     </row>
@@ -15649,7 +15666,7 @@
         <v>2501</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C302" s="4">
         <v>25</v>
@@ -15662,11 +15679,11 @@
         <v>55</v>
       </c>
       <c r="G302" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J302" s="5"/>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB6171D-6CD2-4645-99C6-FA518E4FC4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7FCA20-B239-4E45-97DF-59511898C34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="365">
   <si>
     <t>Id</t>
   </si>
@@ -889,76 +889,22 @@
     <t>CugaCalibration.ViewModels.Laser.LaserPixelSizeCalibrationViewModel</t>
   </si>
   <si>
-    <t>CugaCalibration.Views.Laser.PixelSize.Children.Step1View</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.PixelSize.Children.Step2View</t>
-  </si>
-  <si>
-    <t>XWidthPixelNumeric</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.PixelSize.Children.Review</t>
-  </si>
-  <si>
     <t>Line Centricity</t>
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserLineCentricityCalibrationViewModel</t>
   </si>
   <si>
-    <t>Line Centricity-Step1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.LineCentricity.Children.Step1View</t>
-  </si>
-  <si>
-    <t>Line Centricity-Step2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.LineCentricity.Children.Step2View</t>
-  </si>
-  <si>
-    <t>PathTextBox</t>
-  </si>
-  <si>
-    <t>ChangeButton</t>
-  </si>
-  <si>
-    <t>Line Centricity-Review</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.LineCentricity.Children.Review</t>
-  </si>
-  <si>
     <t>Line Orientation Offset</t>
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserLineOrientationOffsetCalibrationViewModel</t>
   </si>
   <si>
-    <t>Pmt Agc Delay</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserPmtAgcDelayCalibrationViewModel</t>
-  </si>
-  <si>
     <t>X Pixel Size</t>
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserXPixelSizeCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>Focus Shift</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserFocusShiftCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>RTFC</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserRtfcCalibrationViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -1260,6 +1206,10 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.CIB.CIBMMDViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y Pixel Size</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -7394,7 +7344,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z302"/>
+  <dimension ref="A1:Z281"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -13761,7 +13711,7 @@
         <v>55</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
@@ -13787,7 +13737,7 @@
         <v>55</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5" t="s">
@@ -13824,7 +13774,7 @@
         <v>15</v>
       </c>
       <c r="B232" s="18" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="C232" s="4">
         <v>1</v>
@@ -13848,7 +13798,7 @@
         <v>1501</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C233" s="4">
         <v>15</v>
@@ -13861,11 +13811,11 @@
         <v>55</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="H233" s="5"/>
       <c r="I233" s="18" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="J233" s="5"/>
     </row>
@@ -13874,7 +13824,7 @@
         <v>1502</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
@@ -13887,11 +13837,11 @@
         <v>55</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="H234" s="5"/>
       <c r="I234" s="18" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="J234" s="5"/>
     </row>
@@ -13939,7 +13889,7 @@
         <v>55</v>
       </c>
       <c r="G236" s="19" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="H236" s="7"/>
       <c r="I236" s="7" t="s">
@@ -13975,8 +13925,8 @@
       <c r="A238" s="4">
         <v>1601</v>
       </c>
-      <c r="B238" s="5" t="s">
-        <v>279</v>
+      <c r="B238" s="10" t="s">
+        <v>364</v>
       </c>
       <c r="C238" s="4">
         <v>16</v>
@@ -13989,20 +13939,20 @@
         <v>55</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H238" s="5"/>
-      <c r="I238" s="5" t="s">
-        <v>279</v>
+      <c r="I238" s="10" t="s">
+        <v>364</v>
       </c>
       <c r="J238" s="5"/>
     </row>
-    <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>1602</v>
       </c>
-      <c r="B239" s="5" t="s">
-        <v>144</v>
+      <c r="B239" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="C239" s="4">
         <v>16</v>
@@ -14015,735 +13965,687 @@
         <v>55</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="H239" s="5"/>
-      <c r="I239" s="5" t="s">
-        <v>144</v>
+        <v>287</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="J239" s="5"/>
     </row>
     <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>160201</v>
+        <v>1603</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="C240" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D240" s="4">
-        <v>160201</v>
+        <v>1603</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G240" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H240" s="5"/>
+      <c r="I240" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="H240" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I240" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="J240" s="5"/>
     </row>
     <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
-        <v>160202</v>
+        <v>1604</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>146</v>
+        <v>284</v>
       </c>
       <c r="C241" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D241" s="4">
-        <v>160202</v>
+        <v>1604</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="H241" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="H241" s="5"/>
       <c r="I241" s="5" t="s">
-        <v>61</v>
+        <v>284</v>
       </c>
       <c r="J241" s="5"/>
     </row>
     <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
-        <v>160203</v>
+        <v>1605</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="C242" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D242" s="4">
-        <v>160203</v>
+        <v>1605</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H242" s="5" t="s">
-        <v>284</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="H242" s="5"/>
       <c r="I242" s="5" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="J242" s="5"/>
     </row>
     <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="4">
-        <v>160204</v>
-      </c>
-      <c r="B243" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C243" s="4">
-        <v>1602</v>
-      </c>
-      <c r="D243" s="4">
-        <v>160204</v>
-      </c>
-      <c r="E243" s="4"/>
-      <c r="F243" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G243" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H243" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I243" s="5" t="s">
-        <v>64</v>
+      <c r="A243" s="6">
+        <v>1606</v>
+      </c>
+      <c r="B243" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="C243" s="6">
+        <v>16</v>
+      </c>
+      <c r="D243" s="6">
+        <v>1607</v>
+      </c>
+      <c r="E243" s="6"/>
+      <c r="F243" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G243" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="H243" s="7"/>
+      <c r="I243" s="20" t="s">
+        <v>362</v>
       </c>
       <c r="J243" s="5"/>
     </row>
     <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>160205</v>
+        <v>2</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="C244" s="4">
-        <v>1602</v>
+        <v>-1</v>
       </c>
       <c r="D244" s="4">
-        <v>160205</v>
+        <v>2</v>
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G244" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H244" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G244" s="5"/>
+      <c r="H244" s="5"/>
       <c r="I244" s="5" t="s">
-        <v>65</v>
+        <v>288</v>
       </c>
       <c r="J244" s="5"/>
     </row>
     <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
-        <v>160206</v>
+        <v>21</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>150</v>
+        <v>289</v>
       </c>
       <c r="C245" s="4">
-        <v>1602</v>
+        <v>2</v>
       </c>
       <c r="D245" s="4">
-        <v>160206</v>
+        <v>21</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G245" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H245" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G245" s="5"/>
+      <c r="H245" s="5"/>
       <c r="I245" s="5" t="s">
-        <v>69</v>
+        <v>289</v>
       </c>
       <c r="J245" s="5"/>
     </row>
     <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>160207</v>
+        <v>2110</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="C246" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D246" s="4">
-        <v>160207</v>
+        <v>2110</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H246" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="H246" s="5"/>
       <c r="I246" s="5" t="s">
-        <v>64</v>
+        <v>290</v>
       </c>
       <c r="J246" s="5"/>
     </row>
     <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>160208</v>
+        <v>2111</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>150</v>
+        <v>292</v>
       </c>
       <c r="C247" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D247" s="4">
-        <v>160208</v>
+        <v>2111</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H247" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="H247" s="5"/>
       <c r="I247" s="5" t="s">
-        <v>65</v>
+        <v>292</v>
       </c>
       <c r="J247" s="5"/>
     </row>
     <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C248" s="4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D248" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G248" s="5" t="s">
-        <v>287</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G248" s="5"/>
       <c r="H248" s="5"/>
       <c r="I248" s="5" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="J248" s="5"/>
     </row>
     <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>160301</v>
+        <v>2201</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C249" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D249" s="4">
-        <v>160301</v>
+        <v>2201</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H249" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="H249" s="5"/>
       <c r="I249" s="5" t="s">
-        <v>156</v>
+        <v>295</v>
       </c>
       <c r="J249" s="5"/>
     </row>
     <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
-        <v>160302</v>
+        <v>2202</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C250" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D250" s="4">
-        <v>160302</v>
+        <v>2202</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H250" s="5" t="s">
-        <v>60</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="H250" s="5"/>
       <c r="I250" s="5" t="s">
-        <v>60</v>
+        <v>297</v>
       </c>
       <c r="J250" s="5"/>
     </row>
     <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
-        <v>160303</v>
+        <v>2203</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C251" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D251" s="4">
-        <v>160303</v>
+        <v>2203</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H251" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="H251" s="5"/>
       <c r="I251" s="5" t="s">
-        <v>61</v>
+        <v>299</v>
       </c>
       <c r="J251" s="5"/>
     </row>
     <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
-        <v>160304</v>
+        <v>23</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C252" s="4">
-        <v>1603</v>
+        <v>2</v>
       </c>
       <c r="D252" s="4">
-        <v>160304</v>
+        <v>23</v>
       </c>
       <c r="E252" s="4"/>
       <c r="F252" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G252" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H252" s="5" t="s">
-        <v>292</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G252" s="5"/>
+      <c r="H252" s="5"/>
       <c r="I252" s="5" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="J252" s="5"/>
     </row>
     <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>160305</v>
+        <v>2301</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C253" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D253" s="4">
-        <v>160305</v>
+        <v>2301</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>293</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="H253" s="5"/>
       <c r="I253" s="5" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="J253" s="5"/>
     </row>
     <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
-        <v>160306</v>
+        <v>2302</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C254" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D254" s="4">
-        <v>160306</v>
+        <v>2302</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G254" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H254" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G254" s="5"/>
+      <c r="H254" s="5"/>
       <c r="I254" s="5" t="s">
-        <v>64</v>
+        <v>304</v>
       </c>
       <c r="J254" s="5"/>
     </row>
     <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>160307</v>
+        <v>23021</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C255" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D255" s="4">
-        <v>160307</v>
+        <v>23021</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H255" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="H255" s="5"/>
       <c r="I255" s="5" t="s">
-        <v>65</v>
+        <v>307</v>
       </c>
       <c r="J255" s="5"/>
     </row>
     <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>160308</v>
+        <v>23022</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C256" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D256" s="4">
-        <v>160308</v>
+        <v>23022</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H256" s="5" t="s">
-        <v>161</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H256" s="5"/>
       <c r="I256" s="5" t="s">
-        <v>161</v>
+        <v>310</v>
       </c>
       <c r="J256" s="5"/>
     </row>
     <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
-        <v>160309</v>
+        <v>2303</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="C257" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D257" s="4">
-        <v>160309</v>
+        <v>2303</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G257" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H257" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G257" s="5"/>
+      <c r="H257" s="5"/>
       <c r="I257" s="5" t="s">
-        <v>64</v>
+        <v>274</v>
       </c>
       <c r="J257" s="5"/>
     </row>
     <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>160310</v>
-      </c>
-      <c r="B258" s="5" t="s">
-        <v>294</v>
+        <v>23031</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="C258" s="4">
-        <v>1603</v>
+        <v>2303</v>
       </c>
       <c r="D258" s="4">
-        <v>160310</v>
+        <v>23031</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G258" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H258" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I258" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="G258" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="H258" s="5"/>
+      <c r="I258" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="J258" s="5"/>
     </row>
     <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>1604</v>
-      </c>
-      <c r="B259" s="5" t="s">
-        <v>296</v>
+        <v>23032</v>
+      </c>
+      <c r="B259" s="10" t="s">
+        <v>313</v>
       </c>
       <c r="C259" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D259" s="4">
-        <v>1604</v>
+        <v>23032</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G259" s="5" t="s">
-        <v>297</v>
+      <c r="G259" s="10" t="s">
+        <v>314</v>
       </c>
       <c r="H259" s="5"/>
-      <c r="I259" s="5" t="s">
-        <v>296</v>
+      <c r="I259" s="10" t="s">
+        <v>313</v>
       </c>
       <c r="J259" s="5"/>
     </row>
     <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>1608</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>298</v>
+        <v>23033</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="C260" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D260" s="4">
-        <v>1608</v>
+        <v>23033</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G260" s="5" t="s">
-        <v>299</v>
+      <c r="G260" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="H260" s="5"/>
-      <c r="I260" s="5" t="s">
-        <v>298</v>
+      <c r="I260" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="J260" s="5"/>
     </row>
     <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="6">
-        <v>1604</v>
-      </c>
-      <c r="B261" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="C261" s="6">
-        <v>16</v>
-      </c>
-      <c r="D261" s="6">
-        <v>1604</v>
-      </c>
-      <c r="E261" s="6"/>
-      <c r="F261" s="6" t="s">
+      <c r="A261" s="4">
+        <v>23034</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C261" s="4">
+        <v>2303</v>
+      </c>
+      <c r="D261" s="4">
+        <v>23034</v>
+      </c>
+      <c r="E261" s="4"/>
+      <c r="F261" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G261" s="20" t="s">
-        <v>381</v>
-      </c>
-      <c r="H261" s="7"/>
-      <c r="I261" s="20" t="s">
-        <v>380</v>
+      <c r="G261" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H261" s="5"/>
+      <c r="I261" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="J261" s="5"/>
     </row>
-    <row r="262" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>1605</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>300</v>
+        <v>23035</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>319</v>
       </c>
       <c r="C262" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D262" s="4">
-        <v>1605</v>
+        <v>23035</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G262" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="I262" s="1" t="s">
-        <v>300</v>
+      <c r="G262" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="H262" s="5"/>
+      <c r="I262" s="10" t="s">
+        <v>319</v>
       </c>
       <c r="J262" s="5"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
-        <v>1606</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>302</v>
+        <v>23036</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="C263" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D263" s="4">
-        <v>1606</v>
+        <v>23036</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G263" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="H263" s="1"/>
-      <c r="I263" s="1" t="s">
-        <v>302</v>
+      <c r="G263" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H263" s="5"/>
+      <c r="I263" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="J263" s="5"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
-        <v>1607</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>304</v>
+        <v>2304</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="C264" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D264" s="4">
-        <v>1607</v>
+        <v>2304</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G264" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="H264" s="1"/>
-      <c r="I264" s="1" t="s">
-        <v>304</v>
+        <v>52</v>
+      </c>
+      <c r="G264" s="5"/>
+      <c r="H264" s="5"/>
+      <c r="I264" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="J264" s="5"/>
     </row>
     <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>2</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>306</v>
+        <v>23041</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>324</v>
       </c>
       <c r="C265" s="4">
-        <v>-1</v>
+        <v>2304</v>
       </c>
       <c r="D265" s="4">
-        <v>2</v>
+        <v>23041</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G265" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G265" s="10" t="s">
+        <v>325</v>
+      </c>
       <c r="H265" s="5"/>
-      <c r="I265" s="5" t="s">
-        <v>306</v>
+      <c r="I265" s="10" t="s">
+        <v>324</v>
       </c>
       <c r="J265" s="5"/>
     </row>
     <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>21</v>
-      </c>
-      <c r="B266" s="5" t="s">
-        <v>307</v>
+        <v>2305</v>
+      </c>
+      <c r="B266" s="18" t="s">
+        <v>357</v>
       </c>
       <c r="C266" s="4">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D266" s="4">
-        <v>21</v>
+        <v>2305</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="4" t="s">
@@ -14751,941 +14653,407 @@
       </c>
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
-      <c r="I266" s="5" t="s">
-        <v>307</v>
+      <c r="I266" s="18" t="s">
+        <v>357</v>
       </c>
       <c r="J266" s="5"/>
     </row>
     <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>2110</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>308</v>
+        <v>23051</v>
+      </c>
+      <c r="B267" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="C267" s="4">
-        <v>21</v>
+        <v>2305</v>
       </c>
       <c r="D267" s="4">
-        <v>2110</v>
+        <v>23051</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G267" s="5" t="s">
-        <v>309</v>
+      <c r="G267" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="H267" s="5"/>
-      <c r="I267" s="5" t="s">
-        <v>308</v>
+      <c r="I267" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="J267" s="5"/>
     </row>
-    <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
-        <v>2111</v>
+        <v>2306</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="C268" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D268" s="4">
-        <v>2111</v>
+        <v>2306</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G268" s="5" t="s">
-        <v>311</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G268" s="5"/>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="J268" s="5"/>
     </row>
     <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>22</v>
+        <v>23061</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C269" s="4">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D269" s="4">
-        <v>22</v>
+        <v>23061</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G269" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G269" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J269" s="5"/>
     </row>
-    <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
-        <v>2201</v>
+        <v>23062</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C270" s="4">
-        <v>22</v>
+        <v>2306</v>
       </c>
       <c r="D270" s="4">
-        <v>2201</v>
+        <v>23062</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="J270" s="5"/>
     </row>
     <row r="271" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
-        <v>2202</v>
+        <v>23063</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C271" s="4">
-        <v>22</v>
+        <v>2306</v>
       </c>
       <c r="D271" s="4">
-        <v>2202</v>
+        <v>23063</v>
       </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="H271" s="5"/>
       <c r="I271" s="5" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="J271" s="5"/>
     </row>
-    <row r="272" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
-        <v>2203</v>
+        <v>2307</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="C272" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D272" s="4">
-        <v>2203</v>
+        <v>2307</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G272" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H272" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G272" s="4"/>
+      <c r="H272" s="4"/>
       <c r="I272" s="5" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="J272" s="5"/>
     </row>
-    <row r="273" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>23</v>
+        <v>23071</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="C273" s="4">
-        <v>2</v>
+        <v>2307</v>
       </c>
       <c r="D273" s="4">
-        <v>23</v>
+        <v>23071</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G273" s="5"/>
-      <c r="H273" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G273" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="H273" s="4"/>
       <c r="I273" s="5" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="J273" s="5"/>
     </row>
-    <row r="274" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>2301</v>
+        <v>23072</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="C274" s="4">
-        <v>23</v>
+        <v>2307</v>
       </c>
       <c r="D274" s="4">
-        <v>2301</v>
+        <v>23072</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="J274" s="5"/>
     </row>
-    <row r="275" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
-        <v>2302</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>322</v>
+        <v>23073</v>
+      </c>
+      <c r="B275" s="18" t="s">
+        <v>355</v>
       </c>
       <c r="C275" s="4">
-        <v>23</v>
+        <v>2307</v>
       </c>
       <c r="D275" s="4">
-        <v>2302</v>
+        <v>23073</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G275" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="H275" s="5"/>
+      <c r="I275" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="J275" s="5"/>
+    </row>
+    <row r="276" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A276" s="4">
+        <v>24</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C276" s="4">
+        <v>2</v>
+      </c>
+      <c r="D276" s="4">
+        <v>24</v>
+      </c>
+      <c r="E276" s="5"/>
+      <c r="F276" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G275" s="5"/>
-      <c r="H275" s="5"/>
-      <c r="I275" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="J275" s="5"/>
-    </row>
-    <row r="276" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="4">
-        <v>23021</v>
-      </c>
-      <c r="B276" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C276" s="4">
-        <v>2302</v>
-      </c>
-      <c r="D276" s="4">
-        <v>23021</v>
-      </c>
-      <c r="E276" s="4"/>
-      <c r="F276" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G276" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="G276" s="5"/>
       <c r="H276" s="5"/>
       <c r="I276" s="5" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="J276" s="5"/>
     </row>
-    <row r="277" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>23022</v>
+        <v>2401</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C277" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="D277" s="4">
-        <v>23022</v>
-      </c>
-      <c r="E277" s="4"/>
+        <v>2401</v>
+      </c>
+      <c r="E277" s="5"/>
       <c r="F277" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="H277" s="5"/>
       <c r="I277" s="5" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="J277" s="5"/>
     </row>
-    <row r="278" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>2303</v>
+        <v>2402</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="C278" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D278" s="4">
-        <v>2303</v>
+        <v>2402</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G278" s="5"/>
-      <c r="H278" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="H278" s="4"/>
       <c r="I278" s="5" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="J278" s="5"/>
     </row>
-    <row r="279" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
-        <v>23031</v>
-      </c>
-      <c r="B279" s="10" t="s">
-        <v>329</v>
+        <v>2403</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="C279" s="4">
-        <v>2303</v>
+        <v>24</v>
       </c>
       <c r="D279" s="4">
-        <v>23031</v>
+        <v>2403</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G279" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="H279" s="5"/>
-      <c r="I279" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="J279" s="5"/>
-    </row>
-    <row r="280" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G279" s="5"/>
+      <c r="I279" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J279" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K279"/>
+      <c r="L279"/>
+      <c r="M279"/>
+      <c r="N279"/>
+      <c r="O279"/>
+      <c r="P279"/>
+      <c r="Q279"/>
+      <c r="R279"/>
+      <c r="S279"/>
+      <c r="T279"/>
+      <c r="U279"/>
+      <c r="V279"/>
+      <c r="W279"/>
+      <c r="X279"/>
+      <c r="Y279"/>
+      <c r="Z279" s="11"/>
+    </row>
+    <row r="280" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
-        <v>23032</v>
-      </c>
-      <c r="B280" s="10" t="s">
-        <v>331</v>
+        <v>25</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="C280" s="4">
-        <v>2303</v>
+        <v>2</v>
       </c>
       <c r="D280" s="4">
-        <v>23032</v>
+        <v>25</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G280" s="10" t="s">
-        <v>332</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G280" s="5"/>
       <c r="H280" s="5"/>
-      <c r="I280" s="10" t="s">
-        <v>331</v>
+      <c r="I280" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="J280" s="5"/>
     </row>
-    <row r="281" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
-        <v>23033</v>
-      </c>
-      <c r="B281" s="10" t="s">
-        <v>333</v>
+        <v>2501</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>346</v>
       </c>
       <c r="C281" s="4">
-        <v>2303</v>
+        <v>25</v>
       </c>
       <c r="D281" s="4">
-        <v>23033</v>
-      </c>
-      <c r="E281" s="4"/>
+        <v>2501</v>
+      </c>
+      <c r="E281" s="5"/>
       <c r="F281" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G281" s="10" t="s">
-        <v>334</v>
+      <c r="G281" s="5" t="s">
+        <v>347</v>
       </c>
       <c r="H281" s="5"/>
-      <c r="I281" s="10" t="s">
-        <v>333</v>
+      <c r="I281" s="5" t="s">
+        <v>346</v>
       </c>
       <c r="J281" s="5"/>
-    </row>
-    <row r="282" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="4">
-        <v>23034</v>
-      </c>
-      <c r="B282" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="C282" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D282" s="4">
-        <v>23034</v>
-      </c>
-      <c r="E282" s="4"/>
-      <c r="F282" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G282" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="H282" s="5"/>
-      <c r="I282" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J282" s="5"/>
-    </row>
-    <row r="283" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="4">
-        <v>23035</v>
-      </c>
-      <c r="B283" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C283" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D283" s="4">
-        <v>23035</v>
-      </c>
-      <c r="E283" s="4"/>
-      <c r="F283" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G283" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="H283" s="5"/>
-      <c r="I283" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="J283" s="5"/>
-    </row>
-    <row r="284" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="4">
-        <v>23036</v>
-      </c>
-      <c r="B284" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="C284" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D284" s="4">
-        <v>23036</v>
-      </c>
-      <c r="E284" s="4"/>
-      <c r="F284" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G284" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="H284" s="5"/>
-      <c r="I284" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="J284" s="5"/>
-    </row>
-    <row r="285" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="4">
-        <v>2304</v>
-      </c>
-      <c r="B285" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="C285" s="4">
-        <v>23</v>
-      </c>
-      <c r="D285" s="4">
-        <v>2304</v>
-      </c>
-      <c r="E285" s="4"/>
-      <c r="F285" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G285" s="5"/>
-      <c r="H285" s="5"/>
-      <c r="I285" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="J285" s="5"/>
-    </row>
-    <row r="286" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="4">
-        <v>23041</v>
-      </c>
-      <c r="B286" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="C286" s="4">
-        <v>2304</v>
-      </c>
-      <c r="D286" s="4">
-        <v>23041</v>
-      </c>
-      <c r="E286" s="4"/>
-      <c r="F286" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G286" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="H286" s="5"/>
-      <c r="I286" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="J286" s="5"/>
-    </row>
-    <row r="287" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="4">
-        <v>2305</v>
-      </c>
-      <c r="B287" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="C287" s="4">
-        <v>23</v>
-      </c>
-      <c r="D287" s="4">
-        <v>2305</v>
-      </c>
-      <c r="E287" s="4"/>
-      <c r="F287" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G287" s="5"/>
-      <c r="H287" s="5"/>
-      <c r="I287" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="J287" s="5"/>
-    </row>
-    <row r="288" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="4">
-        <v>23051</v>
-      </c>
-      <c r="B288" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="C288" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D288" s="4">
-        <v>23051</v>
-      </c>
-      <c r="E288" s="4"/>
-      <c r="F288" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G288" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="H288" s="5"/>
-      <c r="I288" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="J288" s="5"/>
-    </row>
-    <row r="289" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A289" s="4">
-        <v>2306</v>
-      </c>
-      <c r="B289" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C289" s="4">
-        <v>23</v>
-      </c>
-      <c r="D289" s="4">
-        <v>2306</v>
-      </c>
-      <c r="E289" s="4"/>
-      <c r="F289" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G289" s="5"/>
-      <c r="H289" s="5"/>
-      <c r="I289" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="J289" s="5"/>
-    </row>
-    <row r="290" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="4">
-        <v>23061</v>
-      </c>
-      <c r="B290" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C290" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D290" s="4">
-        <v>23061</v>
-      </c>
-      <c r="E290" s="4"/>
-      <c r="F290" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G290" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H290" s="5"/>
-      <c r="I290" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="J290" s="5"/>
-    </row>
-    <row r="291" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A291" s="4">
-        <v>23062</v>
-      </c>
-      <c r="B291" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C291" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D291" s="4">
-        <v>23062</v>
-      </c>
-      <c r="E291" s="4"/>
-      <c r="F291" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G291" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H291" s="5"/>
-      <c r="I291" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J291" s="5"/>
-    </row>
-    <row r="292" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="4">
-        <v>23063</v>
-      </c>
-      <c r="B292" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C292" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D292" s="4">
-        <v>23063</v>
-      </c>
-      <c r="E292" s="4"/>
-      <c r="F292" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G292" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="H292" s="5"/>
-      <c r="I292" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="J292" s="5"/>
-    </row>
-    <row r="293" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A293" s="4">
-        <v>2307</v>
-      </c>
-      <c r="B293" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C293" s="4">
-        <v>23</v>
-      </c>
-      <c r="D293" s="4">
-        <v>2307</v>
-      </c>
-      <c r="E293" s="4"/>
-      <c r="F293" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G293" s="4"/>
-      <c r="H293" s="4"/>
-      <c r="I293" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="J293" s="5"/>
-    </row>
-    <row r="294" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A294" s="4">
-        <v>23071</v>
-      </c>
-      <c r="B294" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="C294" s="4">
-        <v>2307</v>
-      </c>
-      <c r="D294" s="4">
-        <v>23071</v>
-      </c>
-      <c r="E294" s="4"/>
-      <c r="F294" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G294" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="H294" s="4"/>
-      <c r="I294" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="J294" s="5"/>
-    </row>
-    <row r="295" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A295" s="4">
-        <v>23072</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="C295" s="4">
-        <v>2307</v>
-      </c>
-      <c r="D295" s="4">
-        <v>23072</v>
-      </c>
-      <c r="E295" s="4"/>
-      <c r="F295" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G295" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="H295" s="5"/>
-      <c r="I295" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="J295" s="5"/>
-    </row>
-    <row r="296" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A296" s="4">
-        <v>23073</v>
-      </c>
-      <c r="B296" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="C296" s="4">
-        <v>2307</v>
-      </c>
-      <c r="D296" s="4">
-        <v>23073</v>
-      </c>
-      <c r="E296" s="4"/>
-      <c r="F296" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G296" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="H296" s="5"/>
-      <c r="I296" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="J296" s="5"/>
-    </row>
-    <row r="297" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A297" s="4">
-        <v>24</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C297" s="4">
-        <v>2</v>
-      </c>
-      <c r="D297" s="4">
-        <v>24</v>
-      </c>
-      <c r="E297" s="5"/>
-      <c r="F297" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G297" s="5"/>
-      <c r="H297" s="5"/>
-      <c r="I297" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="J297" s="5"/>
-    </row>
-    <row r="298" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A298" s="4">
-        <v>2401</v>
-      </c>
-      <c r="B298" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="C298" s="4">
-        <v>24</v>
-      </c>
-      <c r="D298" s="4">
-        <v>2401</v>
-      </c>
-      <c r="E298" s="5"/>
-      <c r="F298" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G298" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="H298" s="5"/>
-      <c r="I298" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="J298" s="5"/>
-    </row>
-    <row r="299" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A299" s="4">
-        <v>2402</v>
-      </c>
-      <c r="B299" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C299" s="4">
-        <v>24</v>
-      </c>
-      <c r="D299" s="4">
-        <v>2402</v>
-      </c>
-      <c r="E299" s="4"/>
-      <c r="F299" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G299" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="H299" s="4"/>
-      <c r="I299" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="J299" s="5"/>
-    </row>
-    <row r="300" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="4">
-        <v>2403</v>
-      </c>
-      <c r="B300" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C300" s="4">
-        <v>24</v>
-      </c>
-      <c r="D300" s="4">
-        <v>2403</v>
-      </c>
-      <c r="E300" s="4"/>
-      <c r="F300" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G300" s="5"/>
-      <c r="I300" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="J300" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K300"/>
-      <c r="L300"/>
-      <c r="M300"/>
-      <c r="N300"/>
-      <c r="O300"/>
-      <c r="P300"/>
-      <c r="Q300"/>
-      <c r="R300"/>
-      <c r="S300"/>
-      <c r="T300"/>
-      <c r="U300"/>
-      <c r="V300"/>
-      <c r="W300"/>
-      <c r="X300"/>
-      <c r="Y300"/>
-      <c r="Z300" s="11"/>
-    </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A301" s="4">
-        <v>25</v>
-      </c>
-      <c r="B301" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C301" s="4">
-        <v>2</v>
-      </c>
-      <c r="D301" s="4">
-        <v>25</v>
-      </c>
-      <c r="E301" s="4"/>
-      <c r="F301" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G301" s="5"/>
-      <c r="H301" s="5"/>
-      <c r="I301" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="J301" s="5"/>
-    </row>
-    <row r="302" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A302" s="4">
-        <v>2501</v>
-      </c>
-      <c r="B302" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C302" s="4">
-        <v>25</v>
-      </c>
-      <c r="D302" s="4">
-        <v>2501</v>
-      </c>
-      <c r="E302" s="5"/>
-      <c r="F302" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G302" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="H302" s="5"/>
-      <c r="I302" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="J302" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7FCA20-B239-4E45-97DF-59511898C34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBCFBDF-83BB-4B51-AFE0-FAB6142E625E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="363">
   <si>
     <t>Id</t>
   </si>
@@ -767,12 +767,6 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Chuck.ChuckRotateScaleCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>Chuck Auto Focus</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Chuck.ChuckAutoFocusCalibrationViewModel</t>
   </si>
   <si>
     <t>Stage Map</t>
@@ -7344,7 +7338,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z281"/>
+  <dimension ref="A1:Z280"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -12977,139 +12971,141 @@
       </c>
       <c r="J202" s="5"/>
     </row>
-    <row r="203" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
-        <v>1308</v>
-      </c>
-      <c r="B203" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C203" s="4">
         <v>13</v>
       </c>
       <c r="D203" s="4">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G203" s="5" t="s">
+      <c r="G203" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H203" s="5"/>
-      <c r="I203" s="5" t="s">
+      <c r="H203" s="1"/>
+      <c r="I203" s="1" t="s">
         <v>242</v>
       </c>
       <c r="J203" s="5"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
-        <v>1309</v>
-      </c>
-      <c r="B204" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B204" s="5" t="s">
         <v>244</v>
       </c>
       <c r="C204" s="4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D204" s="4">
-        <v>1309</v>
+        <v>14</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="H204" s="1"/>
-      <c r="I204" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G204" s="5"/>
+      <c r="H204" s="5"/>
+      <c r="I204" s="5" t="s">
         <v>244</v>
       </c>
       <c r="J204" s="5"/>
     </row>
     <row r="205" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
+        <v>1401</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C205" s="4">
         <v>14</v>
       </c>
-      <c r="B205" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C205" s="4">
-        <v>1</v>
-      </c>
       <c r="D205" s="4">
-        <v>14</v>
+        <v>1401</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G205" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>246</v>
+      </c>
       <c r="H205" s="5"/>
       <c r="I205" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J205" s="5"/>
     </row>
     <row r="206" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
-        <v>1401</v>
+        <v>140101</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>247</v>
       </c>
       <c r="C206" s="4">
-        <v>14</v>
+        <v>1401</v>
       </c>
       <c r="D206" s="4">
-        <v>1401</v>
+        <v>140101</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G206" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="H206" s="5"/>
+      <c r="H206" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="I206" s="5" t="s">
-        <v>247</v>
+        <v>60</v>
       </c>
       <c r="J206" s="5"/>
     </row>
     <row r="207" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
-        <v>140101</v>
+        <v>140102</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C207" s="4">
         <v>1401</v>
       </c>
       <c r="D207" s="4">
-        <v>140101</v>
+        <v>140102</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J207" s="5"/>
     </row>
     <row r="208" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
-        <v>140102</v>
+        <v>140103</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>249</v>
@@ -13118,360 +13114,360 @@
         <v>1401</v>
       </c>
       <c r="D208" s="4">
-        <v>140102</v>
+        <v>140103</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>250</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="J208" s="5"/>
     </row>
     <row r="209" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
-        <v>140103</v>
+        <v>140104</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C209" s="4">
         <v>1401</v>
       </c>
       <c r="D209" s="4">
-        <v>140103</v>
+        <v>140104</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G209" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H209" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="H209" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="I209" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J209" s="5"/>
     </row>
     <row r="210" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
-        <v>140104</v>
+        <v>140105</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C210" s="4">
         <v>1401</v>
       </c>
       <c r="D210" s="4">
-        <v>140104</v>
+        <v>140105</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J210" s="5"/>
     </row>
     <row r="211" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>140105</v>
+        <v>140106</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C211" s="4">
         <v>1401</v>
       </c>
       <c r="D211" s="4">
-        <v>140105</v>
+        <v>140106</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J211" s="5"/>
     </row>
     <row r="212" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
-        <v>140106</v>
+        <v>140107</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C212" s="4">
         <v>1401</v>
       </c>
       <c r="D212" s="4">
-        <v>140106</v>
+        <v>140107</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J212" s="5"/>
     </row>
     <row r="213" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
-        <v>140107</v>
+        <v>140108</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C213" s="4">
         <v>1401</v>
       </c>
       <c r="D213" s="4">
-        <v>140107</v>
+        <v>140108</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J213" s="5"/>
     </row>
     <row r="214" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
-        <v>140108</v>
+        <v>140109</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C214" s="4">
         <v>1401</v>
       </c>
       <c r="D214" s="4">
-        <v>140108</v>
+        <v>140109</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I214" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J214" s="5"/>
     </row>
     <row r="215" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
-        <v>140109</v>
+        <v>140110</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C215" s="4">
         <v>1401</v>
       </c>
       <c r="D215" s="4">
-        <v>140109</v>
+        <v>140110</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>259</v>
+        <v>64</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>259</v>
+        <v>64</v>
       </c>
       <c r="J215" s="5"/>
     </row>
     <row r="216" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
-        <v>140110</v>
+        <v>140111</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C216" s="4">
         <v>1401</v>
       </c>
       <c r="D216" s="4">
-        <v>140110</v>
+        <v>140111</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I216" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J216" s="5"/>
     </row>
     <row r="217" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
-        <v>140111</v>
+        <v>140112</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C217" s="4">
         <v>1401</v>
       </c>
       <c r="D217" s="4">
-        <v>140111</v>
+        <v>140112</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I217" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J217" s="5"/>
     </row>
     <row r="218" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
-        <v>140112</v>
+        <v>140113</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C218" s="4">
         <v>1401</v>
       </c>
       <c r="D218" s="4">
-        <v>140112</v>
+        <v>140113</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I218" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J218" s="5"/>
     </row>
     <row r="219" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
-        <v>140113</v>
+        <v>1402</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>260</v>
       </c>
       <c r="C219" s="4">
-        <v>1401</v>
+        <v>14</v>
       </c>
       <c r="D219" s="4">
-        <v>140113</v>
+        <v>1402</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="H219" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="H219" s="5"/>
       <c r="I219" s="5" t="s">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="J219" s="5"/>
     </row>
     <row r="220" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
-        <v>1402</v>
+        <v>140201</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>262</v>
       </c>
       <c r="C220" s="4">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="D220" s="4">
-        <v>1402</v>
+        <v>140201</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="H220" s="5"/>
+      <c r="H220" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="I220" s="5" t="s">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="J220" s="5"/>
     </row>
     <row r="221" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
-        <v>140201</v>
+        <v>140202</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>264</v>
@@ -13480,7 +13476,7 @@
         <v>1402</v>
       </c>
       <c r="D221" s="4">
-        <v>140201</v>
+        <v>140202</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4" t="s">
@@ -13490,72 +13486,72 @@
         <v>265</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="J221" s="5"/>
     </row>
     <row r="222" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>140202</v>
+        <v>140203</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C222" s="4">
         <v>1402</v>
       </c>
       <c r="D222" s="4">
-        <v>140202</v>
+        <v>140203</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="J222" s="5"/>
     </row>
     <row r="223" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
-        <v>140203</v>
+        <v>140204</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C223" s="4">
         <v>1402</v>
       </c>
       <c r="D223" s="4">
-        <v>140203</v>
+        <v>140204</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I223" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J223" s="5"/>
     </row>
     <row r="224" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
-        <v>140204</v>
+        <v>140205</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>266</v>
@@ -13564,417 +13560,415 @@
         <v>1402</v>
       </c>
       <c r="D224" s="4">
-        <v>140204</v>
+        <v>140205</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G224" s="5" t="s">
         <v>267</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I224" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J224" s="5"/>
     </row>
     <row r="225" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
-        <v>140205</v>
+        <v>140206</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C225" s="4">
         <v>1402</v>
       </c>
       <c r="D225" s="4">
-        <v>140205</v>
+        <v>140206</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I225" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J225" s="5"/>
     </row>
     <row r="226" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
-        <v>140206</v>
+        <v>140207</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C226" s="4">
         <v>1402</v>
       </c>
       <c r="D226" s="4">
-        <v>140206</v>
+        <v>140207</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="J226" s="5"/>
     </row>
     <row r="227" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
-        <v>140207</v>
+        <v>140208</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C227" s="4">
         <v>1402</v>
       </c>
       <c r="D227" s="4">
-        <v>140207</v>
+        <v>140208</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J227" s="5"/>
     </row>
     <row r="228" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
-        <v>140208</v>
+        <v>1403</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>268</v>
       </c>
       <c r="C228" s="4">
-        <v>1402</v>
+        <v>14</v>
       </c>
       <c r="D228" s="4">
-        <v>140208</v>
+        <v>1403</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G228" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="H228" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G228" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="H228" s="5"/>
       <c r="I228" s="5" t="s">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="J228" s="5"/>
     </row>
     <row r="229" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C229" s="4">
         <v>14</v>
       </c>
       <c r="D229" s="4">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J229" s="5"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A230" s="4">
+        <v>1405</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="J229" s="5"/>
-    </row>
-    <row r="230" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="4">
-        <v>1404</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="C230" s="4">
         <v>14</v>
       </c>
       <c r="D230" s="4">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G230" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="H230" s="5"/>
-      <c r="I230" s="5" t="s">
+      <c r="G230" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
       <c r="J230" s="5"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
-        <v>1405</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>272</v>
+        <v>15</v>
+      </c>
+      <c r="B231" s="18" t="s">
+        <v>346</v>
       </c>
       <c r="C231" s="4">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D231" s="4">
-        <v>1405</v>
+        <v>15</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H231" s="1"/>
-      <c r="I231" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="G231" s="5"/>
+      <c r="H231" s="5"/>
+      <c r="I231" s="5" t="s">
+        <v>272</v>
+      </c>
       <c r="J231" s="5"/>
     </row>
     <row r="232" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B232" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="C232" s="4">
         <v>15</v>
       </c>
-      <c r="B232" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="C232" s="4">
-        <v>1</v>
-      </c>
       <c r="D232" s="4">
-        <v>15</v>
+        <v>1501</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G232" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G232" s="18" t="s">
+        <v>351</v>
+      </c>
       <c r="H232" s="5"/>
-      <c r="I232" s="5" t="s">
-        <v>274</v>
+      <c r="I232" s="18" t="s">
+        <v>347</v>
       </c>
       <c r="J232" s="5"/>
     </row>
     <row r="233" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C233" s="4">
         <v>15</v>
       </c>
       <c r="D233" s="4">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H233" s="5"/>
       <c r="I233" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J233" s="5"/>
     </row>
     <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
-        <v>1502</v>
-      </c>
-      <c r="B234" s="18" t="s">
-        <v>350</v>
+        <v>1503</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
       </c>
       <c r="D234" s="4">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G234" s="18" t="s">
-        <v>361</v>
+      <c r="G234" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="H234" s="5"/>
-      <c r="I234" s="18" t="s">
-        <v>350</v>
+      <c r="I234" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="J234" s="5"/>
     </row>
     <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="4">
-        <v>1503</v>
-      </c>
-      <c r="B235" s="5" t="s">
+      <c r="A235" s="6">
+        <v>1504</v>
+      </c>
+      <c r="B235" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C235" s="4">
+      <c r="C235" s="6">
         <v>15</v>
       </c>
-      <c r="D235" s="4">
-        <v>1503</v>
-      </c>
-      <c r="E235" s="4"/>
-      <c r="F235" s="4" t="s">
+      <c r="D235" s="6">
+        <v>1504</v>
+      </c>
+      <c r="E235" s="6"/>
+      <c r="F235" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G235" s="5" t="s">
+      <c r="G235" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="H235" s="7"/>
+      <c r="I235" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="J235" s="5"/>
+    </row>
+    <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="8">
+        <v>16</v>
+      </c>
+      <c r="B236" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H235" s="5"/>
-      <c r="I235" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="J235" s="5"/>
-    </row>
-    <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="6">
-        <v>1504</v>
-      </c>
-      <c r="B236" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C236" s="6">
-        <v>15</v>
-      </c>
-      <c r="D236" s="6">
-        <v>1504</v>
-      </c>
-      <c r="E236" s="6"/>
-      <c r="F236" s="6" t="s">
+      <c r="C236" s="8">
+        <v>1</v>
+      </c>
+      <c r="D236" s="8">
+        <v>16</v>
+      </c>
+      <c r="E236" s="8"/>
+      <c r="F236" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G236" s="9"/>
+      <c r="H236" s="9"/>
+      <c r="I236" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="J236" s="5"/>
+    </row>
+    <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="4">
+        <v>1601</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C237" s="4">
+        <v>16</v>
+      </c>
+      <c r="D237" s="4">
+        <v>1601</v>
+      </c>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G236" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="H236" s="7"/>
-      <c r="I236" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="J236" s="5"/>
-    </row>
-    <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="8">
-        <v>16</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C237" s="8">
-        <v>1</v>
-      </c>
-      <c r="D237" s="8">
-        <v>16</v>
-      </c>
-      <c r="E237" s="8"/>
-      <c r="F237" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G237" s="9"/>
-      <c r="H237" s="9"/>
-      <c r="I237" s="9" t="s">
-        <v>278</v>
+      <c r="G237" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H237" s="5"/>
+      <c r="I237" s="10" t="s">
+        <v>362</v>
       </c>
       <c r="J237" s="5"/>
     </row>
-    <row r="238" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
-        <v>1601</v>
-      </c>
-      <c r="B238" s="10" t="s">
-        <v>364</v>
+        <v>1602</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="C238" s="4">
         <v>16</v>
       </c>
       <c r="D238" s="4">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="H238" s="5"/>
-      <c r="I238" s="10" t="s">
-        <v>364</v>
+        <v>285</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="J238" s="5"/>
     </row>
-    <row r="239" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
-        <v>1602</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>286</v>
+        <v>1603</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="C239" s="4">
         <v>16</v>
       </c>
       <c r="D239" s="4">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I239" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
+      </c>
+      <c r="H239" s="5"/>
+      <c r="I239" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="J239" s="5"/>
     </row>
     <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>282</v>
@@ -13983,7 +13977,7 @@
         <v>16</v>
       </c>
       <c r="D240" s="4">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
@@ -14000,94 +13994,92 @@
     </row>
     <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C241" s="4">
         <v>16</v>
       </c>
       <c r="D241" s="4">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="H241" s="5"/>
       <c r="I241" s="5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="J241" s="5"/>
     </row>
     <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="4">
-        <v>1605</v>
-      </c>
-      <c r="B242" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C242" s="4">
+      <c r="A242" s="6">
+        <v>1606</v>
+      </c>
+      <c r="B242" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="C242" s="6">
         <v>16</v>
       </c>
-      <c r="D242" s="4">
-        <v>1605</v>
-      </c>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4" t="s">
+      <c r="D242" s="6">
+        <v>1607</v>
+      </c>
+      <c r="E242" s="6"/>
+      <c r="F242" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G242" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="H242" s="5"/>
-      <c r="I242" s="5" t="s">
-        <v>279</v>
+      <c r="G242" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="H242" s="7"/>
+      <c r="I242" s="20" t="s">
+        <v>360</v>
       </c>
       <c r="J242" s="5"/>
     </row>
     <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="6">
-        <v>1606</v>
-      </c>
-      <c r="B243" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="C243" s="6">
-        <v>16</v>
-      </c>
-      <c r="D243" s="6">
-        <v>1607</v>
-      </c>
-      <c r="E243" s="6"/>
-      <c r="F243" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G243" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="H243" s="7"/>
-      <c r="I243" s="20" t="s">
-        <v>362</v>
+      <c r="A243" s="4">
+        <v>2</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C243" s="4">
+        <v>-1</v>
+      </c>
+      <c r="D243" s="4">
+        <v>2</v>
+      </c>
+      <c r="E243" s="4"/>
+      <c r="F243" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G243" s="5"/>
+      <c r="H243" s="5"/>
+      <c r="I243" s="5" t="s">
+        <v>286</v>
       </c>
       <c r="J243" s="5"/>
     </row>
     <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C244" s="4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="D244" s="4">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4" t="s">
@@ -14096,37 +14088,39 @@
       <c r="G244" s="5"/>
       <c r="H244" s="5"/>
       <c r="I244" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J244" s="5"/>
     </row>
     <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
+        <v>2110</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C245" s="4">
         <v>21</v>
       </c>
-      <c r="B245" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C245" s="4">
-        <v>2</v>
-      </c>
       <c r="D245" s="4">
-        <v>21</v>
+        <v>2110</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G245" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>289</v>
+      </c>
       <c r="H245" s="5"/>
       <c r="I245" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J245" s="5"/>
     </row>
     <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>290</v>
@@ -14135,7 +14129,7 @@
         <v>21</v>
       </c>
       <c r="D246" s="4">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="4" t="s">
@@ -14152,24 +14146,22 @@
     </row>
     <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>2111</v>
+        <v>22</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>292</v>
       </c>
       <c r="C247" s="4">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D247" s="4">
-        <v>2111</v>
+        <v>22</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G247" s="5" t="s">
-        <v>293</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G247" s="5"/>
       <c r="H247" s="5"/>
       <c r="I247" s="5" t="s">
         <v>292</v>
@@ -14178,31 +14170,33 @@
     </row>
     <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
+        <v>2201</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C248" s="4">
         <v>22</v>
       </c>
-      <c r="B248" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C248" s="4">
-        <v>2</v>
-      </c>
       <c r="D248" s="4">
-        <v>22</v>
+        <v>2201</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G248" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G248" s="5" t="s">
+        <v>294</v>
+      </c>
       <c r="H248" s="5"/>
       <c r="I248" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J248" s="5"/>
     </row>
     <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>295</v>
@@ -14211,7 +14205,7 @@
         <v>22</v>
       </c>
       <c r="D249" s="4">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4" t="s">
@@ -14228,7 +14222,7 @@
     </row>
     <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>297</v>
@@ -14237,7 +14231,7 @@
         <v>22</v>
       </c>
       <c r="D250" s="4">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4" t="s">
@@ -14254,24 +14248,22 @@
     </row>
     <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
-        <v>2203</v>
+        <v>23</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C251" s="4">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D251" s="4">
-        <v>2203</v>
+        <v>23</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G251" s="5" t="s">
-        <v>300</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G251" s="5"/>
       <c r="H251" s="5"/>
       <c r="I251" s="5" t="s">
         <v>299</v>
@@ -14280,31 +14272,33 @@
     </row>
     <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
+        <v>2301</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C252" s="4">
         <v>23</v>
       </c>
-      <c r="B252" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C252" s="4">
-        <v>2</v>
-      </c>
       <c r="D252" s="4">
-        <v>23</v>
+        <v>2301</v>
       </c>
       <c r="E252" s="4"/>
       <c r="F252" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G252" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G252" s="5" t="s">
+        <v>301</v>
+      </c>
       <c r="H252" s="5"/>
       <c r="I252" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J252" s="5"/>
     </row>
     <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>302</v>
@@ -14313,15 +14307,13 @@
         <v>23</v>
       </c>
       <c r="D253" s="4">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G253" s="5" t="s">
-        <v>303</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G253" s="5"/>
       <c r="H253" s="5"/>
       <c r="I253" s="5" t="s">
         <v>302</v>
@@ -14330,107 +14322,109 @@
     </row>
     <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
+        <v>23021</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C254" s="4">
         <v>2302</v>
       </c>
-      <c r="B254" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C254" s="4">
-        <v>23</v>
-      </c>
       <c r="D254" s="4">
-        <v>2302</v>
+        <v>23021</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G254" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G254" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="H254" s="5"/>
       <c r="I254" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J254" s="5"/>
     </row>
     <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>23021</v>
+        <v>23022</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C255" s="4">
         <v>2302</v>
       </c>
       <c r="D255" s="4">
-        <v>23021</v>
+        <v>23022</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H255" s="5"/>
       <c r="I255" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J255" s="5"/>
     </row>
     <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>23022</v>
+        <v>2303</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="C256" s="4">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D256" s="4">
-        <v>23022</v>
+        <v>2303</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G256" s="5" t="s">
-        <v>309</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G256" s="5"/>
       <c r="H256" s="5"/>
       <c r="I256" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="J256" s="5"/>
     </row>
     <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
+        <v>23031</v>
+      </c>
+      <c r="B257" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C257" s="4">
         <v>2303</v>
       </c>
-      <c r="B257" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C257" s="4">
-        <v>23</v>
-      </c>
       <c r="D257" s="4">
-        <v>2303</v>
+        <v>23031</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G257" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G257" s="10" t="s">
+        <v>310</v>
+      </c>
       <c r="H257" s="5"/>
-      <c r="I257" s="5" t="s">
-        <v>274</v>
+      <c r="I257" s="10" t="s">
+        <v>309</v>
       </c>
       <c r="J257" s="5"/>
     </row>
     <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>23031</v>
+        <v>23032</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>311</v>
@@ -14439,7 +14433,7 @@
         <v>2303</v>
       </c>
       <c r="D258" s="4">
-        <v>23031</v>
+        <v>23032</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="4" t="s">
@@ -14456,7 +14450,7 @@
     </row>
     <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>23032</v>
+        <v>23033</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>313</v>
@@ -14465,7 +14459,7 @@
         <v>2303</v>
       </c>
       <c r="D259" s="4">
-        <v>23032</v>
+        <v>23033</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="4" t="s">
@@ -14482,7 +14476,7 @@
     </row>
     <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>23033</v>
+        <v>23034</v>
       </c>
       <c r="B260" s="10" t="s">
         <v>315</v>
@@ -14491,7 +14485,7 @@
         <v>2303</v>
       </c>
       <c r="D260" s="4">
-        <v>23033</v>
+        <v>23034</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="4" t="s">
@@ -14508,7 +14502,7 @@
     </row>
     <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
-        <v>23034</v>
+        <v>23035</v>
       </c>
       <c r="B261" s="10" t="s">
         <v>317</v>
@@ -14517,7 +14511,7 @@
         <v>2303</v>
       </c>
       <c r="D261" s="4">
-        <v>23034</v>
+        <v>23035</v>
       </c>
       <c r="E261" s="4"/>
       <c r="F261" s="4" t="s">
@@ -14534,7 +14528,7 @@
     </row>
     <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>23035</v>
+        <v>23036</v>
       </c>
       <c r="B262" s="10" t="s">
         <v>319</v>
@@ -14543,7 +14537,7 @@
         <v>2303</v>
       </c>
       <c r="D262" s="4">
-        <v>23035</v>
+        <v>23036</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
@@ -14560,24 +14554,22 @@
     </row>
     <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
-        <v>23036</v>
+        <v>2304</v>
       </c>
       <c r="B263" s="10" t="s">
         <v>321</v>
       </c>
       <c r="C263" s="4">
-        <v>2303</v>
+        <v>23</v>
       </c>
       <c r="D263" s="4">
-        <v>23036</v>
+        <v>2304</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G263" s="10" t="s">
-        <v>322</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G263" s="5"/>
       <c r="H263" s="5"/>
       <c r="I263" s="10" t="s">
         <v>321</v>
@@ -14586,131 +14578,133 @@
     </row>
     <row r="264" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
+        <v>23041</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C264" s="4">
         <v>2304</v>
       </c>
-      <c r="B264" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="C264" s="4">
-        <v>23</v>
-      </c>
       <c r="D264" s="4">
-        <v>2304</v>
+        <v>23041</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G264" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G264" s="10" t="s">
+        <v>323</v>
+      </c>
       <c r="H264" s="5"/>
       <c r="I264" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J264" s="5"/>
     </row>
     <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>23041</v>
-      </c>
-      <c r="B265" s="10" t="s">
-        <v>324</v>
+        <v>2305</v>
+      </c>
+      <c r="B265" s="18" t="s">
+        <v>355</v>
       </c>
       <c r="C265" s="4">
-        <v>2304</v>
+        <v>23</v>
       </c>
       <c r="D265" s="4">
-        <v>23041</v>
+        <v>2305</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G265" s="10" t="s">
-        <v>325</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G265" s="5"/>
       <c r="H265" s="5"/>
-      <c r="I265" s="10" t="s">
-        <v>324</v>
+      <c r="I265" s="18" t="s">
+        <v>355</v>
       </c>
       <c r="J265" s="5"/>
     </row>
     <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>2305</v>
+        <v>23051</v>
       </c>
       <c r="B266" s="18" t="s">
         <v>357</v>
       </c>
       <c r="C266" s="4">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D266" s="4">
-        <v>2305</v>
+        <v>23051</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G266" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G266" s="18" t="s">
+        <v>356</v>
+      </c>
       <c r="H266" s="5"/>
       <c r="I266" s="18" t="s">
         <v>357</v>
       </c>
       <c r="J266" s="5"/>
     </row>
-    <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>23051</v>
-      </c>
-      <c r="B267" s="18" t="s">
-        <v>359</v>
+        <v>2306</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="C267" s="4">
-        <v>2305</v>
+        <v>23</v>
       </c>
       <c r="D267" s="4">
-        <v>23051</v>
+        <v>2306</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G267" s="18" t="s">
-        <v>358</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G267" s="5"/>
       <c r="H267" s="5"/>
-      <c r="I267" s="18" t="s">
-        <v>359</v>
+      <c r="I267" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="J267" s="5"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
+        <v>23061</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C268" s="4">
         <v>2306</v>
       </c>
-      <c r="B268" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="C268" s="4">
-        <v>23</v>
-      </c>
       <c r="D268" s="4">
-        <v>2306</v>
+        <v>23061</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G268" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>326</v>
+      </c>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J268" s="5"/>
     </row>
-    <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>23061</v>
+        <v>23062</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>327</v>
@@ -14719,7 +14713,7 @@
         <v>2306</v>
       </c>
       <c r="D269" s="4">
-        <v>23061</v>
+        <v>23062</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4" t="s">
@@ -14734,9 +14728,9 @@
       </c>
       <c r="J269" s="5"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
-        <v>23062</v>
+        <v>23063</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>329</v>
@@ -14745,7 +14739,7 @@
         <v>2306</v>
       </c>
       <c r="D270" s="4">
-        <v>23062</v>
+        <v>23063</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="4" t="s">
@@ -14756,191 +14750,191 @@
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J270" s="5"/>
     </row>
-    <row r="271" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
-        <v>23063</v>
+        <v>2307</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C271" s="4">
-        <v>2306</v>
+        <v>23</v>
       </c>
       <c r="D271" s="4">
-        <v>23063</v>
+        <v>2307</v>
       </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G271" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G271" s="4"/>
+      <c r="H271" s="4"/>
+      <c r="I271" s="5" t="s">
         <v>332</v>
-      </c>
-      <c r="H271" s="5"/>
-      <c r="I271" s="5" t="s">
-        <v>333</v>
       </c>
       <c r="J271" s="5"/>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
+        <v>23071</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C272" s="4">
         <v>2307</v>
       </c>
-      <c r="B272" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C272" s="4">
-        <v>23</v>
-      </c>
       <c r="D272" s="4">
-        <v>2307</v>
+        <v>23071</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G272" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="G272" s="18" t="s">
+        <v>352</v>
+      </c>
       <c r="H272" s="4"/>
       <c r="I272" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J272" s="5"/>
     </row>
     <row r="273" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>23071</v>
+        <v>23072</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C273" s="4">
         <v>2307</v>
       </c>
       <c r="D273" s="4">
-        <v>23071</v>
+        <v>23072</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G273" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="H273" s="4"/>
+      <c r="G273" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J273" s="5"/>
     </row>
     <row r="274" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>23072</v>
-      </c>
-      <c r="B274" s="5" t="s">
-        <v>336</v>
+        <v>23073</v>
+      </c>
+      <c r="B274" s="18" t="s">
+        <v>353</v>
       </c>
       <c r="C274" s="4">
         <v>2307</v>
       </c>
       <c r="D274" s="4">
-        <v>23072</v>
+        <v>23073</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G274" s="5" t="s">
-        <v>337</v>
+      <c r="G274" s="18" t="s">
+        <v>354</v>
       </c>
       <c r="H274" s="5"/>
-      <c r="I274" s="5" t="s">
-        <v>336</v>
+      <c r="I274" s="18" t="s">
+        <v>353</v>
       </c>
       <c r="J274" s="5"/>
     </row>
     <row r="275" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
-        <v>23073</v>
-      </c>
-      <c r="B275" s="18" t="s">
-        <v>355</v>
+        <v>24</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="C275" s="4">
-        <v>2307</v>
+        <v>2</v>
       </c>
       <c r="D275" s="4">
-        <v>23073</v>
-      </c>
-      <c r="E275" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E275" s="5"/>
       <c r="F275" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G275" s="18" t="s">
-        <v>356</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G275" s="5"/>
       <c r="H275" s="5"/>
-      <c r="I275" s="18" t="s">
-        <v>355</v>
+      <c r="I275" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="J275" s="5"/>
     </row>
     <row r="276" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
+        <v>2401</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C276" s="4">
         <v>24</v>
       </c>
-      <c r="B276" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="C276" s="4">
-        <v>2</v>
-      </c>
       <c r="D276" s="4">
-        <v>24</v>
+        <v>2401</v>
       </c>
       <c r="E276" s="5"/>
       <c r="F276" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G276" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G276" s="5" t="s">
+        <v>338</v>
+      </c>
       <c r="H276" s="5"/>
       <c r="I276" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J276" s="5"/>
     </row>
     <row r="277" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C277" s="4">
         <v>24</v>
       </c>
       <c r="D277" s="4">
-        <v>2401</v>
-      </c>
-      <c r="E277" s="5"/>
+        <v>2402</v>
+      </c>
+      <c r="E277" s="4"/>
       <c r="F277" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G277" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="H277" s="4"/>
+      <c r="I277" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H277" s="5"/>
-      <c r="I277" s="5" t="s">
-        <v>341</v>
-      </c>
       <c r="J277" s="5"/>
     </row>
-    <row r="278" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="B278" s="5" t="s">
         <v>342</v>
@@ -14949,111 +14943,85 @@
         <v>24</v>
       </c>
       <c r="D278" s="4">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G278" s="5" t="s">
+      <c r="G278" s="5"/>
+      <c r="I278" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="J278" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K278"/>
+      <c r="L278"/>
+      <c r="M278"/>
+      <c r="N278"/>
+      <c r="O278"/>
+      <c r="P278"/>
+      <c r="Q278"/>
+      <c r="R278"/>
+      <c r="S278"/>
+      <c r="T278"/>
+      <c r="U278"/>
+      <c r="V278"/>
+      <c r="W278"/>
+      <c r="X278"/>
+      <c r="Y278"/>
+      <c r="Z278" s="11"/>
+    </row>
+    <row r="279" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A279" s="4">
+        <v>25</v>
+      </c>
+      <c r="B279" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H278" s="4"/>
-      <c r="I278" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="J278" s="5"/>
-    </row>
-    <row r="279" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="4">
-        <v>2403</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>344</v>
-      </c>
       <c r="C279" s="4">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D279" s="4">
-        <v>2403</v>
+        <v>25</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G279" s="5"/>
-      <c r="I279" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="J279" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K279"/>
-      <c r="L279"/>
-      <c r="M279"/>
-      <c r="N279"/>
-      <c r="O279"/>
-      <c r="P279"/>
-      <c r="Q279"/>
-      <c r="R279"/>
-      <c r="S279"/>
-      <c r="T279"/>
-      <c r="U279"/>
-      <c r="V279"/>
-      <c r="W279"/>
-      <c r="X279"/>
-      <c r="Y279"/>
-      <c r="Z279" s="11"/>
+      <c r="H279" s="5"/>
+      <c r="I279" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="J279" s="5"/>
     </row>
     <row r="280" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
+        <v>2501</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C280" s="4">
         <v>25</v>
       </c>
-      <c r="B280" s="5" t="s">
+      <c r="D280" s="4">
+        <v>2501</v>
+      </c>
+      <c r="E280" s="5"/>
+      <c r="F280" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G280" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="C280" s="4">
-        <v>2</v>
-      </c>
-      <c r="D280" s="4">
-        <v>25</v>
-      </c>
-      <c r="E280" s="4"/>
-      <c r="F280" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G280" s="5"/>
       <c r="H280" s="5"/>
       <c r="I280" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J280" s="5"/>
-    </row>
-    <row r="281" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A281" s="4">
-        <v>2501</v>
-      </c>
-      <c r="B281" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C281" s="4">
-        <v>25</v>
-      </c>
-      <c r="D281" s="4">
-        <v>2501</v>
-      </c>
-      <c r="E281" s="5"/>
-      <c r="F281" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G281" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="H281" s="5"/>
-      <c r="I281" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J281" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5F378-1409-453B-BCAA-9308093ACBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBCFBDF-83BB-4B51-AFE0-FAB6142E625E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="363">
   <si>
     <t>Id</t>
   </si>
@@ -769,12 +769,6 @@
     <t>CugaCalibration.ViewModels.Chuck.ChuckRotateScaleCalibrationViewModel</t>
   </si>
   <si>
-    <t>Chuck Auto Focus</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Chuck.ChuckAutoFocusCalibrationViewModel</t>
-  </si>
-  <si>
     <t>Stage Map</t>
   </si>
   <si>
@@ -889,82 +883,22 @@
     <t>CugaCalibration.ViewModels.Laser.LaserPixelSizeCalibrationViewModel</t>
   </si>
   <si>
-    <t>CugaCalibration.Views.Laser.PixelSize.Children.Step1View</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.PixelSize.Children.Step2View</t>
-  </si>
-  <si>
-    <t>XWidthPixelNumeric</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.PixelSize.Children.Review</t>
-  </si>
-  <si>
     <t>Line Centricity</t>
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserLineCentricityCalibrationViewModel</t>
   </si>
   <si>
-    <t>Line Centricity-Step1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.LineCentricity.Children.Step1View</t>
-  </si>
-  <si>
-    <t>Line Centricity-Step2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.LineCentricity.Children.Step2View</t>
-  </si>
-  <si>
-    <t>PathTextBox</t>
-  </si>
-  <si>
-    <t>ChangeButton</t>
-  </si>
-  <si>
-    <t>Line Centricity-Review</t>
-  </si>
-  <si>
-    <t>CugaCalibration.Views.Laser.LineCentricity.Children.Review</t>
-  </si>
-  <si>
     <t>Line Orientation Offset</t>
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserLineOrientationOffsetCalibrationViewModel</t>
   </si>
   <si>
-    <t>Pmt Agc Delay</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserPmtAgcDelayCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>Pmt Gain</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserPmtGainCalibrationViewModel</t>
-  </si>
-  <si>
     <t>X Pixel Size</t>
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Laser.LaserXPixelSizeCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>Focus Shift</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserFocusShiftCalibrationViewModel</t>
-  </si>
-  <si>
-    <t>RTFC</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Laser.LaserRtfcCalibrationViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -1026,6 +960,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>CugaCalibration.ViewModels.Common.Windows.Tools.Alignment.AlignmentWindow</t>
@@ -1035,6 +970,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>BrightField</t>
@@ -1044,6 +980,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ViewModel</t>
@@ -1058,6 +995,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dark</t>
@@ -1067,6 +1005,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Field</t>
@@ -1076,6 +1015,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Alignment</t>
@@ -1252,6 +1192,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.AOD.AODAlignmentViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMD</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.CIB.CIBMMDViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y Pixel Size</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1271,18 +1223,21 @@
       <sz val="18"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1290,6 +1245,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1297,6 +1253,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1304,6 +1261,7 @@
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1417,7 +1375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1476,6 +1434,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7377,7 +7338,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z302"/>
+  <dimension ref="A1:Z280"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -13010,139 +12971,141 @@
       </c>
       <c r="J202" s="5"/>
     </row>
-    <row r="203" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
-        <v>1308</v>
-      </c>
-      <c r="B203" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C203" s="4">
         <v>13</v>
       </c>
       <c r="D203" s="4">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G203" s="5" t="s">
+      <c r="G203" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H203" s="5"/>
-      <c r="I203" s="5" t="s">
+      <c r="H203" s="1"/>
+      <c r="I203" s="1" t="s">
         <v>242</v>
       </c>
       <c r="J203" s="5"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
-        <v>1309</v>
-      </c>
-      <c r="B204" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B204" s="5" t="s">
         <v>244</v>
       </c>
       <c r="C204" s="4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D204" s="4">
-        <v>1309</v>
+        <v>14</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="H204" s="1"/>
-      <c r="I204" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G204" s="5"/>
+      <c r="H204" s="5"/>
+      <c r="I204" s="5" t="s">
         <v>244</v>
       </c>
       <c r="J204" s="5"/>
     </row>
     <row r="205" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
+        <v>1401</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C205" s="4">
         <v>14</v>
       </c>
-      <c r="B205" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C205" s="4">
-        <v>1</v>
-      </c>
       <c r="D205" s="4">
-        <v>14</v>
+        <v>1401</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G205" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>246</v>
+      </c>
       <c r="H205" s="5"/>
       <c r="I205" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J205" s="5"/>
     </row>
     <row r="206" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
-        <v>1401</v>
+        <v>140101</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>247</v>
       </c>
       <c r="C206" s="4">
-        <v>14</v>
+        <v>1401</v>
       </c>
       <c r="D206" s="4">
-        <v>1401</v>
+        <v>140101</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G206" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="H206" s="5"/>
+      <c r="H206" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="I206" s="5" t="s">
-        <v>247</v>
+        <v>60</v>
       </c>
       <c r="J206" s="5"/>
     </row>
     <row r="207" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
-        <v>140101</v>
+        <v>140102</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C207" s="4">
         <v>1401</v>
       </c>
       <c r="D207" s="4">
-        <v>140101</v>
+        <v>140102</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J207" s="5"/>
     </row>
     <row r="208" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
-        <v>140102</v>
+        <v>140103</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>249</v>
@@ -13151,360 +13114,360 @@
         <v>1401</v>
       </c>
       <c r="D208" s="4">
-        <v>140102</v>
+        <v>140103</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>250</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="J208" s="5"/>
     </row>
     <row r="209" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
-        <v>140103</v>
+        <v>140104</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C209" s="4">
         <v>1401</v>
       </c>
       <c r="D209" s="4">
-        <v>140103</v>
+        <v>140104</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G209" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H209" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="H209" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="I209" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J209" s="5"/>
     </row>
     <row r="210" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
-        <v>140104</v>
+        <v>140105</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C210" s="4">
         <v>1401</v>
       </c>
       <c r="D210" s="4">
-        <v>140104</v>
+        <v>140105</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J210" s="5"/>
     </row>
     <row r="211" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>140105</v>
+        <v>140106</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C211" s="4">
         <v>1401</v>
       </c>
       <c r="D211" s="4">
-        <v>140105</v>
+        <v>140106</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J211" s="5"/>
     </row>
     <row r="212" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
-        <v>140106</v>
+        <v>140107</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C212" s="4">
         <v>1401</v>
       </c>
       <c r="D212" s="4">
-        <v>140106</v>
+        <v>140107</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J212" s="5"/>
     </row>
     <row r="213" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
-        <v>140107</v>
+        <v>140108</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C213" s="4">
         <v>1401</v>
       </c>
       <c r="D213" s="4">
-        <v>140107</v>
+        <v>140108</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J213" s="5"/>
     </row>
     <row r="214" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
-        <v>140108</v>
+        <v>140109</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C214" s="4">
         <v>1401</v>
       </c>
       <c r="D214" s="4">
-        <v>140108</v>
+        <v>140109</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I214" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J214" s="5"/>
     </row>
     <row r="215" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
-        <v>140109</v>
+        <v>140110</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C215" s="4">
         <v>1401</v>
       </c>
       <c r="D215" s="4">
-        <v>140109</v>
+        <v>140110</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>259</v>
+        <v>64</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>259</v>
+        <v>64</v>
       </c>
       <c r="J215" s="5"/>
     </row>
     <row r="216" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
-        <v>140110</v>
+        <v>140111</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C216" s="4">
         <v>1401</v>
       </c>
       <c r="D216" s="4">
-        <v>140110</v>
+        <v>140111</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I216" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J216" s="5"/>
     </row>
     <row r="217" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
-        <v>140111</v>
+        <v>140112</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C217" s="4">
         <v>1401</v>
       </c>
       <c r="D217" s="4">
-        <v>140111</v>
+        <v>140112</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I217" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J217" s="5"/>
     </row>
     <row r="218" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
-        <v>140112</v>
+        <v>140113</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C218" s="4">
         <v>1401</v>
       </c>
       <c r="D218" s="4">
-        <v>140112</v>
+        <v>140113</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I218" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J218" s="5"/>
     </row>
     <row r="219" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
-        <v>140113</v>
+        <v>1402</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>260</v>
       </c>
       <c r="C219" s="4">
-        <v>1401</v>
+        <v>14</v>
       </c>
       <c r="D219" s="4">
-        <v>140113</v>
+        <v>1402</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="H219" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="H219" s="5"/>
       <c r="I219" s="5" t="s">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="J219" s="5"/>
     </row>
     <row r="220" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
-        <v>1402</v>
+        <v>140201</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>262</v>
       </c>
       <c r="C220" s="4">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="D220" s="4">
-        <v>1402</v>
+        <v>140201</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="H220" s="5"/>
+      <c r="H220" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="I220" s="5" t="s">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="J220" s="5"/>
     </row>
     <row r="221" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
-        <v>140201</v>
+        <v>140202</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>264</v>
@@ -13513,7 +13476,7 @@
         <v>1402</v>
       </c>
       <c r="D221" s="4">
-        <v>140201</v>
+        <v>140202</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4" t="s">
@@ -13523,72 +13486,72 @@
         <v>265</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="J221" s="5"/>
     </row>
     <row r="222" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>140202</v>
+        <v>140203</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C222" s="4">
         <v>1402</v>
       </c>
       <c r="D222" s="4">
-        <v>140202</v>
+        <v>140203</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="J222" s="5"/>
     </row>
     <row r="223" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
-        <v>140203</v>
+        <v>140204</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C223" s="4">
         <v>1402</v>
       </c>
       <c r="D223" s="4">
-        <v>140203</v>
+        <v>140204</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I223" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J223" s="5"/>
     </row>
     <row r="224" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
-        <v>140204</v>
+        <v>140205</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>266</v>
@@ -13597,401 +13560,398 @@
         <v>1402</v>
       </c>
       <c r="D224" s="4">
-        <v>140204</v>
+        <v>140205</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G224" s="5" t="s">
         <v>267</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I224" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J224" s="5"/>
     </row>
     <row r="225" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
-        <v>140205</v>
+        <v>140206</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C225" s="4">
         <v>1402</v>
       </c>
       <c r="D225" s="4">
-        <v>140205</v>
+        <v>140206</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I225" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J225" s="5"/>
     </row>
     <row r="226" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
-        <v>140206</v>
+        <v>140207</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C226" s="4">
         <v>1402</v>
       </c>
       <c r="D226" s="4">
-        <v>140206</v>
+        <v>140207</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="J226" s="5"/>
     </row>
     <row r="227" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
-        <v>140207</v>
+        <v>140208</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C227" s="4">
         <v>1402</v>
       </c>
       <c r="D227" s="4">
-        <v>140207</v>
+        <v>140208</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J227" s="5"/>
     </row>
     <row r="228" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
-        <v>140208</v>
+        <v>1403</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>268</v>
       </c>
       <c r="C228" s="4">
-        <v>1402</v>
+        <v>14</v>
       </c>
       <c r="D228" s="4">
-        <v>140208</v>
+        <v>1403</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G228" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="H228" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G228" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="H228" s="5"/>
       <c r="I228" s="5" t="s">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="J228" s="5"/>
     </row>
     <row r="229" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C229" s="4">
         <v>14</v>
       </c>
       <c r="D229" s="4">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J229" s="5"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A230" s="4">
+        <v>1405</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="J229" s="5"/>
-    </row>
-    <row r="230" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="4">
-        <v>1404</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="C230" s="4">
         <v>14</v>
       </c>
       <c r="D230" s="4">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G230" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="H230" s="5"/>
-      <c r="I230" s="5" t="s">
+      <c r="G230" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
       <c r="J230" s="5"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
-        <v>1405</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>272</v>
+        <v>15</v>
+      </c>
+      <c r="B231" s="18" t="s">
+        <v>346</v>
       </c>
       <c r="C231" s="4">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D231" s="4">
-        <v>1405</v>
+        <v>15</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H231" s="1"/>
-      <c r="I231" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="G231" s="5"/>
+      <c r="H231" s="5"/>
+      <c r="I231" s="5" t="s">
+        <v>272</v>
+      </c>
       <c r="J231" s="5"/>
     </row>
     <row r="232" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B232" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="C232" s="4">
         <v>15</v>
       </c>
-      <c r="B232" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="C232" s="4">
-        <v>1</v>
-      </c>
       <c r="D232" s="4">
-        <v>15</v>
+        <v>1501</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G232" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G232" s="18" t="s">
+        <v>351</v>
+      </c>
       <c r="H232" s="5"/>
-      <c r="I232" s="5" t="s">
-        <v>274</v>
+      <c r="I232" s="18" t="s">
+        <v>347</v>
       </c>
       <c r="J232" s="5"/>
     </row>
     <row r="233" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="C233" s="4">
         <v>15</v>
       </c>
       <c r="D233" s="4">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="H233" s="5"/>
       <c r="I233" s="18" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="J233" s="5"/>
     </row>
     <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
-        <v>1502</v>
-      </c>
-      <c r="B234" s="18" t="s">
-        <v>370</v>
+        <v>1503</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="C234" s="4">
         <v>15</v>
       </c>
       <c r="D234" s="4">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G234" s="18" t="s">
-        <v>381</v>
+      <c r="G234" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="H234" s="5"/>
-      <c r="I234" s="18" t="s">
-        <v>370</v>
+      <c r="I234" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="J234" s="5"/>
     </row>
     <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="4">
-        <v>1503</v>
-      </c>
-      <c r="B235" s="5" t="s">
+      <c r="A235" s="6">
+        <v>1504</v>
+      </c>
+      <c r="B235" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C235" s="4">
+      <c r="C235" s="6">
         <v>15</v>
       </c>
-      <c r="D235" s="4">
-        <v>1503</v>
-      </c>
-      <c r="E235" s="4"/>
-      <c r="F235" s="4" t="s">
+      <c r="D235" s="6">
+        <v>1504</v>
+      </c>
+      <c r="E235" s="6"/>
+      <c r="F235" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G235" s="5" t="s">
+      <c r="G235" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="H235" s="7"/>
+      <c r="I235" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="J235" s="5"/>
+    </row>
+    <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="8">
+        <v>16</v>
+      </c>
+      <c r="B236" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H235" s="5"/>
-      <c r="I235" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="J235" s="5"/>
-    </row>
-    <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="6">
-        <v>1504</v>
-      </c>
-      <c r="B236" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C236" s="6">
-        <v>15</v>
-      </c>
-      <c r="D236" s="6">
-        <v>1504</v>
-      </c>
-      <c r="E236" s="6"/>
-      <c r="F236" s="6" t="s">
+      <c r="C236" s="8">
+        <v>1</v>
+      </c>
+      <c r="D236" s="8">
+        <v>16</v>
+      </c>
+      <c r="E236" s="8"/>
+      <c r="F236" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G236" s="9"/>
+      <c r="H236" s="9"/>
+      <c r="I236" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="J236" s="5"/>
+    </row>
+    <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="4">
+        <v>1601</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C237" s="4">
+        <v>16</v>
+      </c>
+      <c r="D237" s="4">
+        <v>1601</v>
+      </c>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G236" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="H236" s="7"/>
-      <c r="I236" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="J236" s="5"/>
-    </row>
-    <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="8">
-        <v>16</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C237" s="8">
-        <v>1</v>
-      </c>
-      <c r="D237" s="8">
-        <v>16</v>
-      </c>
-      <c r="E237" s="8"/>
-      <c r="F237" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G237" s="9"/>
-      <c r="H237" s="9"/>
-      <c r="I237" s="9" t="s">
-        <v>278</v>
+      <c r="G237" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H237" s="5"/>
+      <c r="I237" s="10" t="s">
+        <v>362</v>
       </c>
       <c r="J237" s="5"/>
     </row>
-    <row r="238" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
-        <v>1601</v>
-      </c>
-      <c r="B238" s="5" t="s">
-        <v>279</v>
+        <v>1602</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="C238" s="4">
         <v>16</v>
       </c>
       <c r="D238" s="4">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="H238" s="5"/>
-      <c r="I238" s="5" t="s">
-        <v>279</v>
+        <v>285</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="J238" s="5"/>
     </row>
     <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>144</v>
+        <v>280</v>
       </c>
       <c r="C239" s="4">
         <v>16</v>
       </c>
       <c r="D239" s="4">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="4" t="s">
@@ -14002,707 +13962,658 @@
       </c>
       <c r="H239" s="5"/>
       <c r="I239" s="5" t="s">
-        <v>144</v>
+        <v>280</v>
       </c>
       <c r="J239" s="5"/>
     </row>
     <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>160201</v>
+        <v>1604</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="C240" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D240" s="4">
-        <v>160201</v>
+        <v>1604</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G240" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H240" s="5"/>
+      <c r="I240" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="H240" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I240" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="J240" s="5"/>
     </row>
     <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
-        <v>160202</v>
+        <v>1605</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>146</v>
+        <v>277</v>
       </c>
       <c r="C241" s="4">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="D241" s="4">
-        <v>160202</v>
+        <v>1605</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="H241" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="H241" s="5"/>
       <c r="I241" s="5" t="s">
-        <v>61</v>
+        <v>277</v>
       </c>
       <c r="J241" s="5"/>
     </row>
     <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="4">
-        <v>160203</v>
-      </c>
-      <c r="B242" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C242" s="4">
-        <v>1602</v>
-      </c>
-      <c r="D242" s="4">
-        <v>160203</v>
-      </c>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G242" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H242" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="I242" s="5" t="s">
-        <v>284</v>
+      <c r="A242" s="6">
+        <v>1606</v>
+      </c>
+      <c r="B242" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="C242" s="6">
+        <v>16</v>
+      </c>
+      <c r="D242" s="6">
+        <v>1607</v>
+      </c>
+      <c r="E242" s="6"/>
+      <c r="F242" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G242" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="H242" s="7"/>
+      <c r="I242" s="20" t="s">
+        <v>360</v>
       </c>
       <c r="J242" s="5"/>
     </row>
     <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
-        <v>160204</v>
+        <v>2</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>148</v>
+        <v>286</v>
       </c>
       <c r="C243" s="4">
-        <v>1602</v>
+        <v>-1</v>
       </c>
       <c r="D243" s="4">
-        <v>160204</v>
+        <v>2</v>
       </c>
       <c r="E243" s="4"/>
       <c r="F243" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G243" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H243" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G243" s="5"/>
+      <c r="H243" s="5"/>
       <c r="I243" s="5" t="s">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="J243" s="5"/>
     </row>
     <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>160205</v>
+        <v>21</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>148</v>
+        <v>287</v>
       </c>
       <c r="C244" s="4">
-        <v>1602</v>
+        <v>2</v>
       </c>
       <c r="D244" s="4">
-        <v>160205</v>
+        <v>21</v>
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G244" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H244" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G244" s="5"/>
+      <c r="H244" s="5"/>
       <c r="I244" s="5" t="s">
-        <v>65</v>
+        <v>287</v>
       </c>
       <c r="J244" s="5"/>
     </row>
     <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
-        <v>160206</v>
+        <v>2110</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="C245" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D245" s="4">
-        <v>160206</v>
+        <v>2110</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H245" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="H245" s="5"/>
       <c r="I245" s="5" t="s">
-        <v>69</v>
+        <v>288</v>
       </c>
       <c r="J245" s="5"/>
     </row>
     <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>160207</v>
+        <v>2111</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="C246" s="4">
-        <v>1602</v>
+        <v>21</v>
       </c>
       <c r="D246" s="4">
-        <v>160207</v>
+        <v>2111</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H246" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="H246" s="5"/>
       <c r="I246" s="5" t="s">
-        <v>64</v>
+        <v>290</v>
       </c>
       <c r="J246" s="5"/>
     </row>
     <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>160208</v>
+        <v>22</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>150</v>
+        <v>292</v>
       </c>
       <c r="C247" s="4">
-        <v>1602</v>
+        <v>2</v>
       </c>
       <c r="D247" s="4">
-        <v>160208</v>
+        <v>22</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G247" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H247" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G247" s="5"/>
+      <c r="H247" s="5"/>
       <c r="I247" s="5" t="s">
-        <v>65</v>
+        <v>292</v>
       </c>
       <c r="J247" s="5"/>
     </row>
     <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
-        <v>1603</v>
+        <v>2201</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C248" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D248" s="4">
-        <v>1603</v>
+        <v>2201</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="H248" s="5"/>
       <c r="I248" s="5" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="J248" s="5"/>
     </row>
     <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>160301</v>
+        <v>2202</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C249" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D249" s="4">
-        <v>160301</v>
+        <v>2202</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H249" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="H249" s="5"/>
       <c r="I249" s="5" t="s">
-        <v>156</v>
+        <v>295</v>
       </c>
       <c r="J249" s="5"/>
     </row>
     <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
-        <v>160302</v>
+        <v>2203</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C250" s="4">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="D250" s="4">
-        <v>160302</v>
+        <v>2203</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H250" s="5" t="s">
-        <v>60</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="H250" s="5"/>
       <c r="I250" s="5" t="s">
-        <v>60</v>
+        <v>297</v>
       </c>
       <c r="J250" s="5"/>
     </row>
     <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
-        <v>160303</v>
+        <v>23</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C251" s="4">
-        <v>1603</v>
+        <v>2</v>
       </c>
       <c r="D251" s="4">
-        <v>160303</v>
+        <v>23</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G251" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H251" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G251" s="5"/>
+      <c r="H251" s="5"/>
       <c r="I251" s="5" t="s">
-        <v>61</v>
+        <v>299</v>
       </c>
       <c r="J251" s="5"/>
     </row>
     <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
-        <v>160304</v>
+        <v>2301</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C252" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D252" s="4">
-        <v>160304</v>
+        <v>2301</v>
       </c>
       <c r="E252" s="4"/>
       <c r="F252" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H252" s="5" t="s">
-        <v>292</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="H252" s="5"/>
       <c r="I252" s="5" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="J252" s="5"/>
     </row>
     <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>160305</v>
+        <v>2302</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C253" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D253" s="4">
-        <v>160305</v>
+        <v>2302</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G253" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>293</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G253" s="5"/>
+      <c r="H253" s="5"/>
       <c r="I253" s="5" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="J253" s="5"/>
     </row>
     <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
-        <v>160306</v>
+        <v>23021</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C254" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D254" s="4">
-        <v>160306</v>
+        <v>23021</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H254" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="H254" s="5"/>
       <c r="I254" s="5" t="s">
-        <v>64</v>
+        <v>305</v>
       </c>
       <c r="J254" s="5"/>
     </row>
     <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>160307</v>
+        <v>23022</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="C255" s="4">
-        <v>1603</v>
+        <v>2302</v>
       </c>
       <c r="D255" s="4">
-        <v>160307</v>
+        <v>23022</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H255" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="H255" s="5"/>
       <c r="I255" s="5" t="s">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="J255" s="5"/>
     </row>
     <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>160308</v>
+        <v>2303</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="C256" s="4">
-        <v>1603</v>
+        <v>23</v>
       </c>
       <c r="D256" s="4">
-        <v>160308</v>
+        <v>2303</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G256" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H256" s="5" t="s">
-        <v>161</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G256" s="5"/>
+      <c r="H256" s="5"/>
       <c r="I256" s="5" t="s">
-        <v>161</v>
+        <v>272</v>
       </c>
       <c r="J256" s="5"/>
     </row>
     <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
-        <v>160309</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>294</v>
+        <v>23031</v>
+      </c>
+      <c r="B257" s="10" t="s">
+        <v>309</v>
       </c>
       <c r="C257" s="4">
-        <v>1603</v>
+        <v>2303</v>
       </c>
       <c r="D257" s="4">
-        <v>160309</v>
+        <v>23031</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G257" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H257" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I257" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="G257" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="H257" s="5"/>
+      <c r="I257" s="10" t="s">
+        <v>309</v>
       </c>
       <c r="J257" s="5"/>
     </row>
     <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>160310</v>
-      </c>
-      <c r="B258" s="5" t="s">
-        <v>294</v>
+        <v>23032</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="C258" s="4">
-        <v>1603</v>
+        <v>2303</v>
       </c>
       <c r="D258" s="4">
-        <v>160310</v>
+        <v>23032</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G258" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H258" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I258" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="G258" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="H258" s="5"/>
+      <c r="I258" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="J258" s="5"/>
     </row>
     <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>1604</v>
-      </c>
-      <c r="B259" s="5" t="s">
-        <v>296</v>
+        <v>23033</v>
+      </c>
+      <c r="B259" s="10" t="s">
+        <v>313</v>
       </c>
       <c r="C259" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D259" s="4">
-        <v>1604</v>
+        <v>23033</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G259" s="5" t="s">
-        <v>297</v>
+      <c r="G259" s="10" t="s">
+        <v>314</v>
       </c>
       <c r="H259" s="5"/>
-      <c r="I259" s="5" t="s">
-        <v>296</v>
+      <c r="I259" s="10" t="s">
+        <v>313</v>
       </c>
       <c r="J259" s="5"/>
     </row>
     <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>1608</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>298</v>
+        <v>23034</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="C260" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D260" s="4">
-        <v>1608</v>
+        <v>23034</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G260" s="5" t="s">
-        <v>299</v>
+      <c r="G260" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="H260" s="5"/>
-      <c r="I260" s="5" t="s">
-        <v>298</v>
+      <c r="I260" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="J260" s="5"/>
     </row>
     <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="6">
-        <v>1604</v>
-      </c>
-      <c r="B261" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C261" s="6">
-        <v>16</v>
-      </c>
-      <c r="D261" s="6">
-        <v>1604</v>
-      </c>
-      <c r="E261" s="6"/>
-      <c r="F261" s="6" t="s">
+      <c r="A261" s="4">
+        <v>23035</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C261" s="4">
+        <v>2303</v>
+      </c>
+      <c r="D261" s="4">
+        <v>23035</v>
+      </c>
+      <c r="E261" s="4"/>
+      <c r="F261" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G261" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="H261" s="7"/>
-      <c r="I261" s="7" t="s">
-        <v>300</v>
+      <c r="G261" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H261" s="5"/>
+      <c r="I261" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="J261" s="5"/>
     </row>
-    <row r="262" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>1605</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>302</v>
+        <v>23036</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>319</v>
       </c>
       <c r="C262" s="4">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="D262" s="4">
-        <v>1605</v>
+        <v>23036</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G262" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="I262" s="1" t="s">
-        <v>302</v>
+      <c r="G262" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="H262" s="5"/>
+      <c r="I262" s="10" t="s">
+        <v>319</v>
       </c>
       <c r="J262" s="5"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
-        <v>1606</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>304</v>
+        <v>2304</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="C263" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D263" s="4">
-        <v>1606</v>
+        <v>2304</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G263" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="H263" s="1"/>
-      <c r="I263" s="1" t="s">
-        <v>304</v>
+        <v>52</v>
+      </c>
+      <c r="G263" s="5"/>
+      <c r="H263" s="5"/>
+      <c r="I263" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="J263" s="5"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
-        <v>1607</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>306</v>
+        <v>23041</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="C264" s="4">
-        <v>16</v>
+        <v>2304</v>
       </c>
       <c r="D264" s="4">
-        <v>1607</v>
+        <v>23041</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G264" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H264" s="1"/>
-      <c r="I264" s="1" t="s">
-        <v>306</v>
+      <c r="G264" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="H264" s="5"/>
+      <c r="I264" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="J264" s="5"/>
     </row>
     <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>2</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>308</v>
+        <v>2305</v>
+      </c>
+      <c r="B265" s="18" t="s">
+        <v>355</v>
       </c>
       <c r="C265" s="4">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="D265" s="4">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4" t="s">
@@ -14710,965 +14621,407 @@
       </c>
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
-      <c r="I265" s="5" t="s">
-        <v>308</v>
+      <c r="I265" s="18" t="s">
+        <v>355</v>
       </c>
       <c r="J265" s="5"/>
     </row>
     <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>21</v>
-      </c>
-      <c r="B266" s="5" t="s">
-        <v>309</v>
+        <v>23051</v>
+      </c>
+      <c r="B266" s="18" t="s">
+        <v>357</v>
       </c>
       <c r="C266" s="4">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D266" s="4">
-        <v>21</v>
+        <v>23051</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G266" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G266" s="18" t="s">
+        <v>356</v>
+      </c>
       <c r="H266" s="5"/>
-      <c r="I266" s="5" t="s">
-        <v>309</v>
+      <c r="I266" s="18" t="s">
+        <v>357</v>
       </c>
       <c r="J266" s="5"/>
     </row>
-    <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>2110</v>
+        <v>2306</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C267" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D267" s="4">
-        <v>2110</v>
+        <v>2306</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G267" s="5" t="s">
-        <v>311</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G267" s="5"/>
       <c r="H267" s="5"/>
       <c r="I267" s="5" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="J267" s="5"/>
     </row>
     <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
-        <v>2111</v>
+        <v>23061</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C268" s="4">
-        <v>21</v>
+        <v>2306</v>
       </c>
       <c r="D268" s="4">
-        <v>2111</v>
+        <v>23061</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="J268" s="5"/>
     </row>
-    <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>22</v>
+        <v>23062</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C269" s="4">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D269" s="4">
-        <v>22</v>
+        <v>23062</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G269" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G269" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="J269" s="5"/>
     </row>
     <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
-        <v>2201</v>
+        <v>23063</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C270" s="4">
-        <v>22</v>
+        <v>2306</v>
       </c>
       <c r="D270" s="4">
-        <v>2201</v>
+        <v>23063</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="J270" s="5"/>
     </row>
-    <row r="271" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
-        <v>2202</v>
+        <v>2307</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C271" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D271" s="4">
-        <v>2202</v>
+        <v>2307</v>
       </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G271" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H271" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G271" s="4"/>
+      <c r="H271" s="4"/>
       <c r="I271" s="5" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="J271" s="5"/>
     </row>
-    <row r="272" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
-        <v>2203</v>
+        <v>23071</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C272" s="4">
-        <v>22</v>
+        <v>2307</v>
       </c>
       <c r="D272" s="4">
-        <v>2203</v>
+        <v>23071</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G272" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H272" s="5"/>
+      <c r="G272" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="H272" s="4"/>
       <c r="I272" s="5" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="J272" s="5"/>
     </row>
-    <row r="273" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>23</v>
+        <v>23072</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="C273" s="4">
-        <v>2</v>
+        <v>2307</v>
       </c>
       <c r="D273" s="4">
-        <v>23</v>
+        <v>23072</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G273" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>335</v>
+      </c>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="J273" s="5"/>
     </row>
-    <row r="274" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>2301</v>
-      </c>
-      <c r="B274" s="5" t="s">
-        <v>322</v>
+        <v>23073</v>
+      </c>
+      <c r="B274" s="18" t="s">
+        <v>353</v>
       </c>
       <c r="C274" s="4">
-        <v>23</v>
+        <v>2307</v>
       </c>
       <c r="D274" s="4">
-        <v>2301</v>
+        <v>23073</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G274" s="5" t="s">
-        <v>323</v>
+      <c r="G274" s="18" t="s">
+        <v>354</v>
       </c>
       <c r="H274" s="5"/>
-      <c r="I274" s="5" t="s">
-        <v>322</v>
+      <c r="I274" s="18" t="s">
+        <v>353</v>
       </c>
       <c r="J274" s="5"/>
     </row>
-    <row r="275" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C275" s="4">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D275" s="4">
-        <v>2302</v>
-      </c>
-      <c r="E275" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E275" s="5"/>
       <c r="F275" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G275" s="5"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="J275" s="5"/>
     </row>
-    <row r="276" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
-        <v>23021</v>
+        <v>2401</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C276" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="D276" s="4">
-        <v>23021</v>
-      </c>
-      <c r="E276" s="4"/>
+        <v>2401</v>
+      </c>
+      <c r="E276" s="5"/>
       <c r="F276" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="H276" s="5"/>
       <c r="I276" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="J276" s="5"/>
     </row>
-    <row r="277" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>23022</v>
+        <v>2402</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C277" s="4">
-        <v>2302</v>
+        <v>24</v>
       </c>
       <c r="D277" s="4">
-        <v>23022</v>
+        <v>2402</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="H277" s="5"/>
+        <v>341</v>
+      </c>
+      <c r="H277" s="4"/>
       <c r="I277" s="5" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="J277" s="5"/>
     </row>
-    <row r="278" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>2303</v>
+        <v>2403</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="C278" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D278" s="4">
-        <v>2303</v>
+        <v>2403</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G278" s="5"/>
-      <c r="H278" s="5"/>
-      <c r="I278" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="J278" s="5"/>
-    </row>
-    <row r="279" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I278" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="J278" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K278"/>
+      <c r="L278"/>
+      <c r="M278"/>
+      <c r="N278"/>
+      <c r="O278"/>
+      <c r="P278"/>
+      <c r="Q278"/>
+      <c r="R278"/>
+      <c r="S278"/>
+      <c r="T278"/>
+      <c r="U278"/>
+      <c r="V278"/>
+      <c r="W278"/>
+      <c r="X278"/>
+      <c r="Y278"/>
+      <c r="Z278" s="11"/>
+    </row>
+    <row r="279" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
-        <v>23031</v>
-      </c>
-      <c r="B279" s="10" t="s">
-        <v>331</v>
+        <v>25</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>343</v>
       </c>
       <c r="C279" s="4">
-        <v>2303</v>
+        <v>2</v>
       </c>
       <c r="D279" s="4">
-        <v>23031</v>
+        <v>25</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G279" s="10" t="s">
-        <v>332</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G279" s="5"/>
       <c r="H279" s="5"/>
-      <c r="I279" s="10" t="s">
-        <v>331</v>
+      <c r="I279" s="5" t="s">
+        <v>343</v>
       </c>
       <c r="J279" s="5"/>
     </row>
-    <row r="280" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
-        <v>23032</v>
-      </c>
-      <c r="B280" s="10" t="s">
-        <v>333</v>
+        <v>2501</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="C280" s="4">
-        <v>2303</v>
+        <v>25</v>
       </c>
       <c r="D280" s="4">
-        <v>23032</v>
-      </c>
-      <c r="E280" s="4"/>
+        <v>2501</v>
+      </c>
+      <c r="E280" s="5"/>
       <c r="F280" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G280" s="10" t="s">
-        <v>334</v>
+      <c r="G280" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="H280" s="5"/>
-      <c r="I280" s="10" t="s">
-        <v>333</v>
+      <c r="I280" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="J280" s="5"/>
-    </row>
-    <row r="281" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="4">
-        <v>23033</v>
-      </c>
-      <c r="B281" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="C281" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D281" s="4">
-        <v>23033</v>
-      </c>
-      <c r="E281" s="4"/>
-      <c r="F281" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G281" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="H281" s="5"/>
-      <c r="I281" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J281" s="5"/>
-    </row>
-    <row r="282" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="4">
-        <v>23034</v>
-      </c>
-      <c r="B282" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C282" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D282" s="4">
-        <v>23034</v>
-      </c>
-      <c r="E282" s="4"/>
-      <c r="F282" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G282" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="H282" s="5"/>
-      <c r="I282" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="J282" s="5"/>
-    </row>
-    <row r="283" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="4">
-        <v>23035</v>
-      </c>
-      <c r="B283" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="C283" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D283" s="4">
-        <v>23035</v>
-      </c>
-      <c r="E283" s="4"/>
-      <c r="F283" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G283" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="H283" s="5"/>
-      <c r="I283" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="J283" s="5"/>
-    </row>
-    <row r="284" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="4">
-        <v>23036</v>
-      </c>
-      <c r="B284" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="C284" s="4">
-        <v>2303</v>
-      </c>
-      <c r="D284" s="4">
-        <v>23036</v>
-      </c>
-      <c r="E284" s="4"/>
-      <c r="F284" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G284" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="H284" s="5"/>
-      <c r="I284" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="J284" s="5"/>
-    </row>
-    <row r="285" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="4">
-        <v>2304</v>
-      </c>
-      <c r="B285" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="C285" s="4">
-        <v>23</v>
-      </c>
-      <c r="D285" s="4">
-        <v>2304</v>
-      </c>
-      <c r="E285" s="4"/>
-      <c r="F285" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G285" s="5"/>
-      <c r="H285" s="5"/>
-      <c r="I285" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="J285" s="5"/>
-    </row>
-    <row r="286" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="4">
-        <v>23041</v>
-      </c>
-      <c r="B286" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="C286" s="4">
-        <v>2304</v>
-      </c>
-      <c r="D286" s="4">
-        <v>23041</v>
-      </c>
-      <c r="E286" s="4"/>
-      <c r="F286" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G286" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="H286" s="5"/>
-      <c r="I286" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="J286" s="5"/>
-    </row>
-    <row r="287" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="4">
-        <v>2305</v>
-      </c>
-      <c r="B287" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="C287" s="4">
-        <v>23</v>
-      </c>
-      <c r="D287" s="4">
-        <v>2305</v>
-      </c>
-      <c r="E287" s="4"/>
-      <c r="F287" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G287" s="5"/>
-      <c r="H287" s="5"/>
-      <c r="I287" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="J287" s="5"/>
-    </row>
-    <row r="288" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="4">
-        <v>23051</v>
-      </c>
-      <c r="B288" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="C288" s="4">
-        <v>2305</v>
-      </c>
-      <c r="D288" s="4">
-        <v>23051</v>
-      </c>
-      <c r="E288" s="4"/>
-      <c r="F288" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G288" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="H288" s="5"/>
-      <c r="I288" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="J288" s="5"/>
-    </row>
-    <row r="289" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A289" s="4">
-        <v>2306</v>
-      </c>
-      <c r="B289" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C289" s="4">
-        <v>23</v>
-      </c>
-      <c r="D289" s="4">
-        <v>2306</v>
-      </c>
-      <c r="E289" s="4"/>
-      <c r="F289" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G289" s="5"/>
-      <c r="H289" s="5"/>
-      <c r="I289" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J289" s="5"/>
-    </row>
-    <row r="290" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="4">
-        <v>23061</v>
-      </c>
-      <c r="B290" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C290" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D290" s="4">
-        <v>23061</v>
-      </c>
-      <c r="E290" s="4"/>
-      <c r="F290" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G290" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H290" s="5"/>
-      <c r="I290" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J290" s="5"/>
-    </row>
-    <row r="291" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A291" s="4">
-        <v>23062</v>
-      </c>
-      <c r="B291" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C291" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D291" s="4">
-        <v>23062</v>
-      </c>
-      <c r="E291" s="4"/>
-      <c r="F291" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G291" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="H291" s="5"/>
-      <c r="I291" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="J291" s="5"/>
-    </row>
-    <row r="292" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="4">
-        <v>23063</v>
-      </c>
-      <c r="B292" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C292" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D292" s="4">
-        <v>23063</v>
-      </c>
-      <c r="E292" s="4"/>
-      <c r="F292" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G292" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="H292" s="5"/>
-      <c r="I292" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="J292" s="5"/>
-    </row>
-    <row r="293" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A293" s="4">
-        <v>2307</v>
-      </c>
-      <c r="B293" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="C293" s="4">
-        <v>23</v>
-      </c>
-      <c r="D293" s="4">
-        <v>2307</v>
-      </c>
-      <c r="E293" s="4"/>
-      <c r="F293" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G293" s="4"/>
-      <c r="H293" s="4"/>
-      <c r="I293" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="J293" s="5"/>
-    </row>
-    <row r="294" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A294" s="4">
-        <v>23071</v>
-      </c>
-      <c r="B294" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C294" s="4">
-        <v>2307</v>
-      </c>
-      <c r="D294" s="4">
-        <v>23071</v>
-      </c>
-      <c r="E294" s="4"/>
-      <c r="F294" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G294" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="H294" s="4"/>
-      <c r="I294" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="J294" s="5"/>
-    </row>
-    <row r="295" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A295" s="4">
-        <v>23072</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C295" s="4">
-        <v>2307</v>
-      </c>
-      <c r="D295" s="4">
-        <v>23072</v>
-      </c>
-      <c r="E295" s="4"/>
-      <c r="F295" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G295" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="H295" s="5"/>
-      <c r="I295" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="J295" s="5"/>
-    </row>
-    <row r="296" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A296" s="4">
-        <v>23073</v>
-      </c>
-      <c r="B296" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="C296" s="4">
-        <v>2307</v>
-      </c>
-      <c r="D296" s="4">
-        <v>23073</v>
-      </c>
-      <c r="E296" s="4"/>
-      <c r="F296" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G296" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="H296" s="5"/>
-      <c r="I296" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="J296" s="5"/>
-    </row>
-    <row r="297" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A297" s="4">
-        <v>24</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C297" s="4">
-        <v>2</v>
-      </c>
-      <c r="D297" s="4">
-        <v>24</v>
-      </c>
-      <c r="E297" s="5"/>
-      <c r="F297" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G297" s="5"/>
-      <c r="H297" s="5"/>
-      <c r="I297" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="J297" s="5"/>
-    </row>
-    <row r="298" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A298" s="4">
-        <v>2401</v>
-      </c>
-      <c r="B298" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="C298" s="4">
-        <v>24</v>
-      </c>
-      <c r="D298" s="4">
-        <v>2401</v>
-      </c>
-      <c r="E298" s="5"/>
-      <c r="F298" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G298" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="H298" s="5"/>
-      <c r="I298" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="J298" s="5"/>
-    </row>
-    <row r="299" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A299" s="4">
-        <v>2402</v>
-      </c>
-      <c r="B299" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C299" s="4">
-        <v>24</v>
-      </c>
-      <c r="D299" s="4">
-        <v>2402</v>
-      </c>
-      <c r="E299" s="4"/>
-      <c r="F299" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G299" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="H299" s="4"/>
-      <c r="I299" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="J299" s="5"/>
-    </row>
-    <row r="300" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="4">
-        <v>2403</v>
-      </c>
-      <c r="B300" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C300" s="4">
-        <v>24</v>
-      </c>
-      <c r="D300" s="4">
-        <v>2403</v>
-      </c>
-      <c r="E300" s="4"/>
-      <c r="F300" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G300" s="5"/>
-      <c r="I300" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="J300" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K300"/>
-      <c r="L300"/>
-      <c r="M300"/>
-      <c r="N300"/>
-      <c r="O300"/>
-      <c r="P300"/>
-      <c r="Q300"/>
-      <c r="R300"/>
-      <c r="S300"/>
-      <c r="T300"/>
-      <c r="U300"/>
-      <c r="V300"/>
-      <c r="W300"/>
-      <c r="X300"/>
-      <c r="Y300"/>
-      <c r="Z300" s="11"/>
-    </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A301" s="4">
-        <v>25</v>
-      </c>
-      <c r="B301" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="C301" s="4">
-        <v>2</v>
-      </c>
-      <c r="D301" s="4">
-        <v>25</v>
-      </c>
-      <c r="E301" s="4"/>
-      <c r="F301" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G301" s="5"/>
-      <c r="H301" s="5"/>
-      <c r="I301" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="J301" s="5"/>
-    </row>
-    <row r="302" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A302" s="4">
-        <v>2501</v>
-      </c>
-      <c r="B302" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="C302" s="4">
-        <v>25</v>
-      </c>
-      <c r="D302" s="4">
-        <v>2501</v>
-      </c>
-      <c r="E302" s="5"/>
-      <c r="F302" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G302" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="H302" s="5"/>
-      <c r="I302" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="J302" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E15441-717C-4095-81E3-DEF222DB177F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AF3DE6-A663-4B34-8B43-4415E0D90019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="366">
   <si>
     <t>Id</t>
   </si>
@@ -1191,6 +1191,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.PrescanAODWaveformElectrodeInitializeWindowViewModel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optics</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relay</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Optics.OpticsRelayViewModel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1272,7 +1284,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1302,33 +1314,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1351,11 +1337,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1374,22 +1360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1398,7 +1369,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
@@ -1409,6 +1380,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1856,525 +1830,525 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="6">
         <v>1</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="14" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>666666</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="7">
         <v>1</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="7">
         <v>666666</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="7">
         <v>1</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="7">
         <v>111111</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="16"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
     </row>
     <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="16"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
     </row>
     <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="16"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
     </row>
     <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="16"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
     </row>
     <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="16"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2408,172 +2382,172 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12">
-        <v>2</v>
-      </c>
-      <c r="C3" s="12">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="7">
         <v>3</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2602,172 +2576,172 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12">
-        <v>2</v>
-      </c>
-      <c r="C3" s="12">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="7">
         <v>3</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2805,340 +2779,340 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="6">
         <v>-1</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>0</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="7">
         <v>-1</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="7">
         <v>3</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="A4" s="7">
         <v>21</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="12">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="C4" s="7">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7">
         <v>21</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
+      <c r="A5" s="7">
         <v>211</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="7">
         <v>21</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="7">
         <v>211</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="7">
         <v>1</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="A6" s="7">
         <v>212</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="7">
         <v>21</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="7">
         <v>212</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="7">
         <v>3</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
+      <c r="A7" s="7">
         <v>22</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="12">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C7" s="7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7">
         <v>22</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="7">
         <v>3</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12">
+      <c r="A8" s="7">
         <v>221</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="7">
         <v>22</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="7">
         <v>221</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="7">
         <v>3</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
+      <c r="A9" s="7">
         <v>222</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="7">
         <v>22</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="7">
         <v>222</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="7">
         <v>3</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3173,234 +3147,234 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>0</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="6">
         <v>1</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3437,234 +3411,234 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>0</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="6">
         <v>1</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3693,154 +3667,154 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3869,10 +3843,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>2</v>
       </c>
       <c r="C2" s="4">
@@ -3880,10 +3854,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
         <v>2</v>
       </c>
       <c r="C3" s="4">
@@ -3891,10 +3865,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
       <c r="C4" s="4">
@@ -3902,10 +3876,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="6">
         <v>2</v>
       </c>
       <c r="C5" s="4">
@@ -3913,10 +3887,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
       <c r="C6" s="4">
@@ -3924,10 +3898,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="6">
         <v>2</v>
       </c>
       <c r="C7" s="4">
@@ -3935,10 +3909,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="6">
         <v>2</v>
       </c>
       <c r="C8" s="4">
@@ -3946,10 +3920,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="4">
@@ -3957,10 +3931,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="6">
         <v>2</v>
       </c>
       <c r="C10" s="4">
@@ -3968,10 +3942,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="6">
         <v>2</v>
       </c>
       <c r="C11" s="4">
@@ -3979,10 +3953,10 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="6">
         <v>2</v>
       </c>
       <c r="C12" s="4">
@@ -3990,10 +3964,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="6">
         <v>2</v>
       </c>
       <c r="C13" s="4">
@@ -4001,10 +3975,10 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="6">
         <v>2</v>
       </c>
       <c r="C14" s="4">
@@ -4012,10 +3986,10 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="6">
         <v>2</v>
       </c>
       <c r="C15" s="4">
@@ -4023,10 +3997,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="6">
         <v>2</v>
       </c>
       <c r="C16" s="4">
@@ -4034,10 +4008,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="6">
         <v>2</v>
       </c>
       <c r="C17" s="4">
@@ -4045,10 +4019,10 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="6">
         <v>2</v>
       </c>
       <c r="C18" s="4">
@@ -4056,10 +4030,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="6">
         <v>2</v>
       </c>
       <c r="C19" s="4">
@@ -4067,10 +4041,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="6">
         <v>2</v>
       </c>
       <c r="C20" s="4">
@@ -4078,10 +4052,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="6">
         <v>2</v>
       </c>
       <c r="C21" s="4">
@@ -4089,10 +4063,10 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="6">
         <v>2</v>
       </c>
       <c r="C22" s="4">
@@ -4100,10 +4074,10 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="6">
         <v>2</v>
       </c>
       <c r="C23" s="4">
@@ -4111,10 +4085,10 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12">
+      <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="6">
         <v>2</v>
       </c>
       <c r="C24" s="4">
@@ -4122,10 +4096,10 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="6">
         <v>2</v>
       </c>
       <c r="C25" s="4">
@@ -4133,10 +4107,10 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="6">
         <v>2</v>
       </c>
       <c r="C26" s="4">
@@ -4144,10 +4118,10 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12">
+      <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="6">
         <v>2</v>
       </c>
       <c r="C27" s="4">
@@ -4155,10 +4129,10 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11">
+      <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="6">
         <v>2</v>
       </c>
       <c r="C28" s="4">
@@ -4166,10 +4140,10 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11">
+      <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="6">
         <v>2</v>
       </c>
       <c r="C29" s="4">
@@ -4177,10 +4151,10 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12">
+      <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="6">
         <v>2</v>
       </c>
       <c r="C30" s="4">
@@ -4188,10 +4162,10 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="6">
         <v>2</v>
       </c>
       <c r="C31" s="4">
@@ -4199,10 +4173,10 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11">
+      <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="6">
         <v>2</v>
       </c>
       <c r="C32" s="4">
@@ -4210,10 +4184,10 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12">
+      <c r="A33" s="7">
         <v>32</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="6">
         <v>2</v>
       </c>
       <c r="C33" s="4">
@@ -4221,10 +4195,10 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11">
+      <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="6">
         <v>2</v>
       </c>
       <c r="C34" s="4">
@@ -4232,10 +4206,10 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="6">
         <v>2</v>
       </c>
       <c r="C35" s="4">
@@ -4243,10 +4217,10 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12">
+      <c r="A36" s="7">
         <v>35</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="6">
         <v>2</v>
       </c>
       <c r="C36" s="4">
@@ -4254,10 +4228,10 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11">
+      <c r="A37" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="6">
         <v>2</v>
       </c>
       <c r="C37" s="4">
@@ -4265,10 +4239,10 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11">
+      <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="6">
         <v>2</v>
       </c>
       <c r="C38" s="4">
@@ -4276,10 +4250,10 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12">
+      <c r="A39" s="7">
         <v>38</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="6">
         <v>2</v>
       </c>
       <c r="C39" s="4">
@@ -4287,10 +4261,10 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11">
+      <c r="A40" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="6">
         <v>2</v>
       </c>
       <c r="C40" s="4">
@@ -4298,10 +4272,10 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="11">
+      <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="6">
         <v>2</v>
       </c>
       <c r="C41" s="4">
@@ -4309,10 +4283,10 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="12">
+      <c r="A42" s="7">
         <v>41</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="6">
         <v>2</v>
       </c>
       <c r="C42" s="4">
@@ -4320,10 +4294,10 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11">
+      <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="6">
         <v>2</v>
       </c>
       <c r="C43" s="4">
@@ -4331,10 +4305,10 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="11">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="6">
         <v>2</v>
       </c>
       <c r="C44" s="4">
@@ -4342,10 +4316,10 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="12">
+      <c r="A45" s="7">
         <v>44</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="6">
         <v>2</v>
       </c>
       <c r="C45" s="4">
@@ -4353,10 +4327,10 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="11">
+      <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="6">
         <v>2</v>
       </c>
       <c r="C46" s="4">
@@ -4364,10 +4338,10 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11">
+      <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="6">
         <v>2</v>
       </c>
       <c r="C47" s="4">
@@ -4375,10 +4349,10 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="12">
+      <c r="A48" s="7">
         <v>47</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="6">
         <v>2</v>
       </c>
       <c r="C48" s="4">
@@ -4386,10 +4360,10 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11">
+      <c r="A49" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="6">
         <v>2</v>
       </c>
       <c r="C49" s="4">
@@ -4397,10 +4371,10 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="11">
+      <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="6">
         <v>2</v>
       </c>
       <c r="C50" s="4">
@@ -4408,10 +4382,10 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12">
+      <c r="A51" s="7">
         <v>50</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="6">
         <v>2</v>
       </c>
       <c r="C51" s="4">
@@ -4419,10 +4393,10 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="11">
+      <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="6">
         <v>2</v>
       </c>
       <c r="C52" s="4">
@@ -4430,10 +4404,10 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="11">
+      <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="6">
         <v>2</v>
       </c>
       <c r="C53" s="4">
@@ -4441,10 +4415,10 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="12">
+      <c r="A54" s="7">
         <v>53</v>
       </c>
-      <c r="B54" s="11">
+      <c r="B54" s="6">
         <v>2</v>
       </c>
       <c r="C54" s="4">
@@ -4452,10 +4426,10 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11">
+      <c r="A55" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="6">
         <v>2</v>
       </c>
       <c r="C55" s="4">
@@ -4463,10 +4437,10 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="11">
+      <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="6">
         <v>2</v>
       </c>
       <c r="C56" s="4">
@@ -4474,10 +4448,10 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="12">
+      <c r="A57" s="7">
         <v>56</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="6">
         <v>2</v>
       </c>
       <c r="C57" s="4">
@@ -4485,10 +4459,10 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="11">
+      <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="11">
+      <c r="B58" s="6">
         <v>2</v>
       </c>
       <c r="C58" s="4">
@@ -4496,10 +4470,10 @@
       </c>
     </row>
     <row r="59" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="11">
-        <v>58</v>
-      </c>
-      <c r="B59" s="11">
+      <c r="A59" s="6">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6">
         <v>2</v>
       </c>
       <c r="C59" s="4">
@@ -4507,10 +4481,10 @@
       </c>
     </row>
     <row r="60" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="11">
+      <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="6">
         <v>2</v>
       </c>
       <c r="C60" s="4">
@@ -4518,10 +4492,10 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="11">
+      <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="6">
         <v>2</v>
       </c>
       <c r="C61" s="4">
@@ -4529,10 +4503,10 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="11">
+      <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="6">
         <v>2</v>
       </c>
       <c r="C62" s="4">
@@ -4540,10 +4514,10 @@
       </c>
     </row>
     <row r="63" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="11">
+      <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="6">
         <v>2</v>
       </c>
       <c r="C63" s="4">
@@ -4551,10 +4525,10 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="11">
+      <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="6">
         <v>2</v>
       </c>
       <c r="C64" s="4">
@@ -4562,10 +4536,10 @@
       </c>
     </row>
     <row r="65" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="11">
+      <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="6">
         <v>2</v>
       </c>
       <c r="C65" s="4">
@@ -4573,10 +4547,10 @@
       </c>
     </row>
     <row r="66" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="11">
+      <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="6">
         <v>2</v>
       </c>
       <c r="C66" s="4">
@@ -4584,10 +4558,10 @@
       </c>
     </row>
     <row r="67" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="11">
+      <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="6">
         <v>2</v>
       </c>
       <c r="C67" s="4">
@@ -4595,10 +4569,10 @@
       </c>
     </row>
     <row r="68" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="11">
+      <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="6">
         <v>2</v>
       </c>
       <c r="C68" s="4">
@@ -4606,10 +4580,10 @@
       </c>
     </row>
     <row r="69" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="11">
+      <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="6">
         <v>2</v>
       </c>
       <c r="C69" s="4">
@@ -4617,10 +4591,10 @@
       </c>
     </row>
     <row r="70" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="11">
+      <c r="A70" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="6">
         <v>2</v>
       </c>
       <c r="C70" s="4">
@@ -4628,10 +4602,10 @@
       </c>
     </row>
     <row r="71" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="11">
+      <c r="A71" s="6">
         <v>70</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="6">
         <v>2</v>
       </c>
       <c r="C71" s="4">
@@ -4639,10 +4613,10 @@
       </c>
     </row>
     <row r="72" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="11">
+      <c r="A72" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="6">
         <v>2</v>
       </c>
       <c r="C72" s="4">
@@ -4650,10 +4624,10 @@
       </c>
     </row>
     <row r="73" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="11">
+      <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="6">
         <v>2</v>
       </c>
       <c r="C73" s="4">
@@ -4661,10 +4635,10 @@
       </c>
     </row>
     <row r="74" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="11">
+      <c r="A74" s="6">
         <v>73</v>
       </c>
-      <c r="B74" s="11">
+      <c r="B74" s="6">
         <v>2</v>
       </c>
       <c r="C74" s="4">
@@ -4672,10 +4646,10 @@
       </c>
     </row>
     <row r="75" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="11">
+      <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="6">
         <v>2</v>
       </c>
       <c r="C75" s="4">
@@ -4683,10 +4657,10 @@
       </c>
     </row>
     <row r="76" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="11">
+      <c r="A76" s="6">
         <v>75</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="6">
         <v>2</v>
       </c>
       <c r="C76" s="4">
@@ -4694,10 +4668,10 @@
       </c>
     </row>
     <row r="77" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="11">
+      <c r="A77" s="6">
         <v>76</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="6">
         <v>2</v>
       </c>
       <c r="C77" s="4">
@@ -4705,10 +4679,10 @@
       </c>
     </row>
     <row r="78" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="11">
+      <c r="A78" s="6">
         <v>77</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="6">
         <v>2</v>
       </c>
       <c r="C78" s="4">
@@ -4716,10 +4690,10 @@
       </c>
     </row>
     <row r="79" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="11">
+      <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="6">
         <v>2</v>
       </c>
       <c r="C79" s="4">
@@ -4727,10 +4701,10 @@
       </c>
     </row>
     <row r="80" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="11">
+      <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="6">
         <v>2</v>
       </c>
       <c r="C80" s="4">
@@ -4738,10 +4712,10 @@
       </c>
     </row>
     <row r="81" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="11">
+      <c r="A81" s="6">
         <v>80</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="6">
         <v>2</v>
       </c>
       <c r="C81" s="4">
@@ -4749,10 +4723,10 @@
       </c>
     </row>
     <row r="82" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="11">
+      <c r="A82" s="6">
         <v>81</v>
       </c>
-      <c r="B82" s="11">
+      <c r="B82" s="6">
         <v>2</v>
       </c>
       <c r="C82" s="4">
@@ -4760,10 +4734,10 @@
       </c>
     </row>
     <row r="83" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="11">
+      <c r="A83" s="6">
         <v>82</v>
       </c>
-      <c r="B83" s="11">
+      <c r="B83" s="6">
         <v>2</v>
       </c>
       <c r="C83" s="4">
@@ -4771,10 +4745,10 @@
       </c>
     </row>
     <row r="84" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="11">
+      <c r="A84" s="6">
         <v>83</v>
       </c>
-      <c r="B84" s="11">
+      <c r="B84" s="6">
         <v>2</v>
       </c>
       <c r="C84" s="4">
@@ -4782,10 +4756,10 @@
       </c>
     </row>
     <row r="85" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="11">
+      <c r="A85" s="6">
         <v>84</v>
       </c>
-      <c r="B85" s="11">
+      <c r="B85" s="6">
         <v>2</v>
       </c>
       <c r="C85" s="4">
@@ -4793,10 +4767,10 @@
       </c>
     </row>
     <row r="86" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="11">
+      <c r="A86" s="6">
         <v>85</v>
       </c>
-      <c r="B86" s="11">
+      <c r="B86" s="6">
         <v>2</v>
       </c>
       <c r="C86" s="4">
@@ -4804,10 +4778,10 @@
       </c>
     </row>
     <row r="87" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="11">
+      <c r="A87" s="6">
         <v>86</v>
       </c>
-      <c r="B87" s="11">
+      <c r="B87" s="6">
         <v>2</v>
       </c>
       <c r="C87" s="4">
@@ -4815,10 +4789,10 @@
       </c>
     </row>
     <row r="88" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="11">
+      <c r="A88" s="6">
         <v>87</v>
       </c>
-      <c r="B88" s="11">
+      <c r="B88" s="6">
         <v>2</v>
       </c>
       <c r="C88" s="4">
@@ -4826,10 +4800,10 @@
       </c>
     </row>
     <row r="89" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="11">
+      <c r="A89" s="6">
         <v>88</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="6">
         <v>2</v>
       </c>
       <c r="C89" s="4">
@@ -4837,10 +4811,10 @@
       </c>
     </row>
     <row r="90" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="11">
+      <c r="A90" s="6">
         <v>89</v>
       </c>
-      <c r="B90" s="11">
+      <c r="B90" s="6">
         <v>2</v>
       </c>
       <c r="C90" s="4">
@@ -4848,10 +4822,10 @@
       </c>
     </row>
     <row r="91" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="11">
+      <c r="A91" s="6">
         <v>90</v>
       </c>
-      <c r="B91" s="11">
+      <c r="B91" s="6">
         <v>2</v>
       </c>
       <c r="C91" s="4">
@@ -4859,10 +4833,10 @@
       </c>
     </row>
     <row r="92" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="11">
+      <c r="A92" s="6">
         <v>91</v>
       </c>
-      <c r="B92" s="11">
+      <c r="B92" s="6">
         <v>2</v>
       </c>
       <c r="C92" s="4">
@@ -4870,10 +4844,10 @@
       </c>
     </row>
     <row r="93" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="11">
+      <c r="A93" s="6">
         <v>92</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="6">
         <v>2</v>
       </c>
       <c r="C93" s="4">
@@ -4881,10 +4855,10 @@
       </c>
     </row>
     <row r="94" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="11">
+      <c r="A94" s="6">
         <v>93</v>
       </c>
-      <c r="B94" s="11">
+      <c r="B94" s="6">
         <v>2</v>
       </c>
       <c r="C94" s="4">
@@ -4892,10 +4866,10 @@
       </c>
     </row>
     <row r="95" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="11">
+      <c r="A95" s="6">
         <v>94</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="6">
         <v>2</v>
       </c>
       <c r="C95" s="4">
@@ -4903,10 +4877,10 @@
       </c>
     </row>
     <row r="96" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="11">
+      <c r="A96" s="6">
         <v>95</v>
       </c>
-      <c r="B96" s="11">
+      <c r="B96" s="6">
         <v>2</v>
       </c>
       <c r="C96" s="4">
@@ -4914,10 +4888,10 @@
       </c>
     </row>
     <row r="97" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="11">
+      <c r="A97" s="6">
         <v>96</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="6">
         <v>2</v>
       </c>
       <c r="C97" s="4">
@@ -4925,10 +4899,10 @@
       </c>
     </row>
     <row r="98" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="11">
+      <c r="A98" s="6">
         <v>97</v>
       </c>
-      <c r="B98" s="11">
+      <c r="B98" s="6">
         <v>2</v>
       </c>
       <c r="C98" s="4">
@@ -4936,10 +4910,10 @@
       </c>
     </row>
     <row r="99" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="11">
+      <c r="A99" s="6">
         <v>98</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="6">
         <v>2</v>
       </c>
       <c r="C99" s="4">
@@ -4947,10 +4921,10 @@
       </c>
     </row>
     <row r="100" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="11">
+      <c r="A100" s="6">
         <v>99</v>
       </c>
-      <c r="B100" s="11">
+      <c r="B100" s="6">
         <v>2</v>
       </c>
       <c r="C100" s="4">
@@ -4958,10 +4932,10 @@
       </c>
     </row>
     <row r="101" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="11">
+      <c r="A101" s="6">
         <v>100</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="6">
         <v>2</v>
       </c>
       <c r="C101" s="4">
@@ -4969,10 +4943,10 @@
       </c>
     </row>
     <row r="102" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="11">
+      <c r="A102" s="6">
         <v>101</v>
       </c>
-      <c r="B102" s="11">
+      <c r="B102" s="6">
         <v>2</v>
       </c>
       <c r="C102" s="4">
@@ -4980,10 +4954,10 @@
       </c>
     </row>
     <row r="103" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="11">
+      <c r="A103" s="6">
         <v>102</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="6">
         <v>2</v>
       </c>
       <c r="C103" s="4">
@@ -4991,10 +4965,10 @@
       </c>
     </row>
     <row r="104" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="11">
+      <c r="A104" s="6">
         <v>103</v>
       </c>
-      <c r="B104" s="11">
+      <c r="B104" s="6">
         <v>2</v>
       </c>
       <c r="C104" s="4">
@@ -5002,10 +4976,10 @@
       </c>
     </row>
     <row r="105" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="11">
+      <c r="A105" s="6">
         <v>104</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="6">
         <v>2</v>
       </c>
       <c r="C105" s="4">
@@ -5013,10 +4987,10 @@
       </c>
     </row>
     <row r="106" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="11">
+      <c r="A106" s="6">
         <v>105</v>
       </c>
-      <c r="B106" s="11">
+      <c r="B106" s="6">
         <v>2</v>
       </c>
       <c r="C106" s="4">
@@ -5024,10 +4998,10 @@
       </c>
     </row>
     <row r="107" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="11">
+      <c r="A107" s="6">
         <v>106</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="6">
         <v>2</v>
       </c>
       <c r="C107" s="4">
@@ -5035,10 +5009,10 @@
       </c>
     </row>
     <row r="108" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="11">
+      <c r="A108" s="6">
         <v>107</v>
       </c>
-      <c r="B108" s="11">
+      <c r="B108" s="6">
         <v>2</v>
       </c>
       <c r="C108" s="4">
@@ -5046,10 +5020,10 @@
       </c>
     </row>
     <row r="109" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="11">
+      <c r="A109" s="6">
         <v>108</v>
       </c>
-      <c r="B109" s="11">
+      <c r="B109" s="6">
         <v>2</v>
       </c>
       <c r="C109" s="4">
@@ -5057,10 +5031,10 @@
       </c>
     </row>
     <row r="110" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="11">
+      <c r="A110" s="6">
         <v>109</v>
       </c>
-      <c r="B110" s="11">
+      <c r="B110" s="6">
         <v>2</v>
       </c>
       <c r="C110" s="4">
@@ -5068,10 +5042,10 @@
       </c>
     </row>
     <row r="111" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="11">
+      <c r="A111" s="6">
         <v>110</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="6">
         <v>2</v>
       </c>
       <c r="C111" s="4">
@@ -5079,10 +5053,10 @@
       </c>
     </row>
     <row r="112" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="11">
+      <c r="A112" s="6">
         <v>111</v>
       </c>
-      <c r="B112" s="11">
+      <c r="B112" s="6">
         <v>2</v>
       </c>
       <c r="C112" s="4">
@@ -5090,10 +5064,10 @@
       </c>
     </row>
     <row r="113" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="11">
+      <c r="A113" s="6">
         <v>112</v>
       </c>
-      <c r="B113" s="11">
+      <c r="B113" s="6">
         <v>2</v>
       </c>
       <c r="C113" s="4">
@@ -5101,10 +5075,10 @@
       </c>
     </row>
     <row r="114" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="11">
+      <c r="A114" s="6">
         <v>113</v>
       </c>
-      <c r="B114" s="11">
+      <c r="B114" s="6">
         <v>2</v>
       </c>
       <c r="C114" s="4">
@@ -5112,10 +5086,10 @@
       </c>
     </row>
     <row r="115" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="11">
+      <c r="A115" s="6">
         <v>114</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="6">
         <v>2</v>
       </c>
       <c r="C115" s="4">
@@ -5123,10 +5097,10 @@
       </c>
     </row>
     <row r="116" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="11">
+      <c r="A116" s="6">
         <v>115</v>
       </c>
-      <c r="B116" s="11">
+      <c r="B116" s="6">
         <v>2</v>
       </c>
       <c r="C116" s="4">
@@ -5134,10 +5108,10 @@
       </c>
     </row>
     <row r="117" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="11">
+      <c r="A117" s="6">
         <v>116</v>
       </c>
-      <c r="B117" s="11">
+      <c r="B117" s="6">
         <v>2</v>
       </c>
       <c r="C117" s="4">
@@ -5145,10 +5119,10 @@
       </c>
     </row>
     <row r="118" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="11">
+      <c r="A118" s="6">
         <v>117</v>
       </c>
-      <c r="B118" s="11">
+      <c r="B118" s="6">
         <v>2</v>
       </c>
       <c r="C118" s="4">
@@ -5156,10 +5130,10 @@
       </c>
     </row>
     <row r="119" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="11">
+      <c r="A119" s="6">
         <v>118</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="6">
         <v>2</v>
       </c>
       <c r="C119" s="4">
@@ -5167,10 +5141,10 @@
       </c>
     </row>
     <row r="120" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="11">
+      <c r="A120" s="6">
         <v>119</v>
       </c>
-      <c r="B120" s="11">
+      <c r="B120" s="6">
         <v>2</v>
       </c>
       <c r="C120" s="4">
@@ -5178,10 +5152,10 @@
       </c>
     </row>
     <row r="121" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="11">
+      <c r="A121" s="6">
         <v>120</v>
       </c>
-      <c r="B121" s="11">
+      <c r="B121" s="6">
         <v>2</v>
       </c>
       <c r="C121" s="4">
@@ -5189,10 +5163,10 @@
       </c>
     </row>
     <row r="122" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="11">
+      <c r="A122" s="6">
         <v>121</v>
       </c>
-      <c r="B122" s="11">
+      <c r="B122" s="6">
         <v>2</v>
       </c>
       <c r="C122" s="4">
@@ -5200,10 +5174,10 @@
       </c>
     </row>
     <row r="123" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="11">
+      <c r="A123" s="6">
         <v>122</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B123" s="6">
         <v>2</v>
       </c>
       <c r="C123" s="4">
@@ -5211,10 +5185,10 @@
       </c>
     </row>
     <row r="124" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="11">
+      <c r="A124" s="6">
         <v>123</v>
       </c>
-      <c r="B124" s="11">
+      <c r="B124" s="6">
         <v>2</v>
       </c>
       <c r="C124" s="4">
@@ -5222,10 +5196,10 @@
       </c>
     </row>
     <row r="125" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="11">
+      <c r="A125" s="6">
         <v>124</v>
       </c>
-      <c r="B125" s="11">
+      <c r="B125" s="6">
         <v>2</v>
       </c>
       <c r="C125" s="4">
@@ -5233,10 +5207,10 @@
       </c>
     </row>
     <row r="126" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="11">
+      <c r="A126" s="6">
         <v>125</v>
       </c>
-      <c r="B126" s="11">
+      <c r="B126" s="6">
         <v>2</v>
       </c>
       <c r="C126" s="4">
@@ -5244,10 +5218,10 @@
       </c>
     </row>
     <row r="127" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="11">
+      <c r="A127" s="6">
         <v>126</v>
       </c>
-      <c r="B127" s="11">
+      <c r="B127" s="6">
         <v>2</v>
       </c>
       <c r="C127" s="4">
@@ -5255,10 +5229,10 @@
       </c>
     </row>
     <row r="128" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="11">
+      <c r="A128" s="6">
         <v>127</v>
       </c>
-      <c r="B128" s="11">
+      <c r="B128" s="6">
         <v>2</v>
       </c>
       <c r="C128" s="4">
@@ -5266,10 +5240,10 @@
       </c>
     </row>
     <row r="129" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="11">
+      <c r="A129" s="6">
         <v>128</v>
       </c>
-      <c r="B129" s="11">
+      <c r="B129" s="6">
         <v>2</v>
       </c>
       <c r="C129" s="4">
@@ -5277,10 +5251,10 @@
       </c>
     </row>
     <row r="130" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="11">
+      <c r="A130" s="6">
         <v>129</v>
       </c>
-      <c r="B130" s="11">
+      <c r="B130" s="6">
         <v>2</v>
       </c>
       <c r="C130" s="4">
@@ -5288,10 +5262,10 @@
       </c>
     </row>
     <row r="131" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="11">
+      <c r="A131" s="6">
         <v>130</v>
       </c>
-      <c r="B131" s="11">
+      <c r="B131" s="6">
         <v>2</v>
       </c>
       <c r="C131" s="4">
@@ -5299,10 +5273,10 @@
       </c>
     </row>
     <row r="132" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="11">
+      <c r="A132" s="6">
         <v>131</v>
       </c>
-      <c r="B132" s="11">
+      <c r="B132" s="6">
         <v>2</v>
       </c>
       <c r="C132" s="4">
@@ -5310,10 +5284,10 @@
       </c>
     </row>
     <row r="133" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="11">
+      <c r="A133" s="6">
         <v>132</v>
       </c>
-      <c r="B133" s="11">
+      <c r="B133" s="6">
         <v>2</v>
       </c>
       <c r="C133" s="4">
@@ -5321,10 +5295,10 @@
       </c>
     </row>
     <row r="134" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="11">
+      <c r="A134" s="6">
         <v>133</v>
       </c>
-      <c r="B134" s="11">
+      <c r="B134" s="6">
         <v>2</v>
       </c>
       <c r="C134" s="4">
@@ -5332,10 +5306,10 @@
       </c>
     </row>
     <row r="135" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="11">
+      <c r="A135" s="6">
         <v>134</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="6">
         <v>2</v>
       </c>
       <c r="C135" s="4">
@@ -5343,10 +5317,10 @@
       </c>
     </row>
     <row r="136" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="11">
+      <c r="A136" s="6">
         <v>135</v>
       </c>
-      <c r="B136" s="11">
+      <c r="B136" s="6">
         <v>2</v>
       </c>
       <c r="C136" s="4">
@@ -5354,10 +5328,10 @@
       </c>
     </row>
     <row r="137" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="11">
+      <c r="A137" s="6">
         <v>136</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="6">
         <v>2</v>
       </c>
       <c r="C137" s="4">
@@ -5365,10 +5339,10 @@
       </c>
     </row>
     <row r="138" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="11">
+      <c r="A138" s="6">
         <v>137</v>
       </c>
-      <c r="B138" s="11">
+      <c r="B138" s="6">
         <v>2</v>
       </c>
       <c r="C138" s="4">
@@ -5376,10 +5350,10 @@
       </c>
     </row>
     <row r="139" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="11">
+      <c r="A139" s="6">
         <v>138</v>
       </c>
-      <c r="B139" s="11">
+      <c r="B139" s="6">
         <v>2</v>
       </c>
       <c r="C139" s="4">
@@ -5387,10 +5361,10 @@
       </c>
     </row>
     <row r="140" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="11">
+      <c r="A140" s="6">
         <v>139</v>
       </c>
-      <c r="B140" s="11">
+      <c r="B140" s="6">
         <v>2</v>
       </c>
       <c r="C140" s="4">
@@ -5398,10 +5372,10 @@
       </c>
     </row>
     <row r="141" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="11">
+      <c r="A141" s="6">
         <v>140</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B141" s="6">
         <v>2</v>
       </c>
       <c r="C141" s="4">
@@ -5409,10 +5383,10 @@
       </c>
     </row>
     <row r="142" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="11">
+      <c r="A142" s="6">
         <v>141</v>
       </c>
-      <c r="B142" s="11">
+      <c r="B142" s="6">
         <v>2</v>
       </c>
       <c r="C142" s="4">
@@ -5420,10 +5394,10 @@
       </c>
     </row>
     <row r="143" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="11">
+      <c r="A143" s="6">
         <v>142</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="6">
         <v>2</v>
       </c>
       <c r="C143" s="4">
@@ -5431,10 +5405,10 @@
       </c>
     </row>
     <row r="144" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="11">
+      <c r="A144" s="6">
         <v>122</v>
       </c>
-      <c r="B144" s="11">
+      <c r="B144" s="6">
         <v>2</v>
       </c>
       <c r="C144" s="4">
@@ -5442,10 +5416,10 @@
       </c>
     </row>
     <row r="145" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="11">
+      <c r="A145" s="6">
         <v>123</v>
       </c>
-      <c r="B145" s="11">
+      <c r="B145" s="6">
         <v>2</v>
       </c>
       <c r="C145" s="4">
@@ -5453,10 +5427,10 @@
       </c>
     </row>
     <row r="146" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="11">
+      <c r="A146" s="6">
         <v>124</v>
       </c>
-      <c r="B146" s="11">
+      <c r="B146" s="6">
         <v>2</v>
       </c>
       <c r="C146" s="4">
@@ -5464,10 +5438,10 @@
       </c>
     </row>
     <row r="147" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="11">
+      <c r="A147" s="6">
         <v>125</v>
       </c>
-      <c r="B147" s="11">
+      <c r="B147" s="6">
         <v>2</v>
       </c>
       <c r="C147" s="4">
@@ -5475,10 +5449,10 @@
       </c>
     </row>
     <row r="148" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="11">
+      <c r="A148" s="6">
         <v>126</v>
       </c>
-      <c r="B148" s="11">
+      <c r="B148" s="6">
         <v>2</v>
       </c>
       <c r="C148" s="4">
@@ -5486,10 +5460,10 @@
       </c>
     </row>
     <row r="149" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="11">
+      <c r="A149" s="6">
         <v>127</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="6">
         <v>2</v>
       </c>
       <c r="C149" s="4">
@@ -5497,10 +5471,10 @@
       </c>
     </row>
     <row r="150" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="11">
+      <c r="A150" s="6">
         <v>128</v>
       </c>
-      <c r="B150" s="11">
+      <c r="B150" s="6">
         <v>2</v>
       </c>
       <c r="C150" s="4">
@@ -5508,10 +5482,10 @@
       </c>
     </row>
     <row r="151" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="11">
+      <c r="A151" s="6">
         <v>129</v>
       </c>
-      <c r="B151" s="11">
+      <c r="B151" s="6">
         <v>2</v>
       </c>
       <c r="C151" s="4">
@@ -5519,10 +5493,10 @@
       </c>
     </row>
     <row r="152" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="11">
+      <c r="A152" s="6">
         <v>130</v>
       </c>
-      <c r="B152" s="11">
+      <c r="B152" s="6">
         <v>2</v>
       </c>
       <c r="C152" s="4">
@@ -5530,10 +5504,10 @@
       </c>
     </row>
     <row r="153" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="11">
+      <c r="A153" s="6">
         <v>131</v>
       </c>
-      <c r="B153" s="11">
+      <c r="B153" s="6">
         <v>2</v>
       </c>
       <c r="C153" s="4">
@@ -5541,10 +5515,10 @@
       </c>
     </row>
     <row r="154" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="11">
+      <c r="A154" s="6">
         <v>132</v>
       </c>
-      <c r="B154" s="11">
+      <c r="B154" s="6">
         <v>2</v>
       </c>
       <c r="C154" s="4">
@@ -5552,10 +5526,10 @@
       </c>
     </row>
     <row r="155" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="11">
+      <c r="A155" s="6">
         <v>133</v>
       </c>
-      <c r="B155" s="11">
+      <c r="B155" s="6">
         <v>2</v>
       </c>
       <c r="C155" s="4">
@@ -5563,10 +5537,10 @@
       </c>
     </row>
     <row r="156" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="11">
+      <c r="A156" s="6">
         <v>134</v>
       </c>
-      <c r="B156" s="11">
+      <c r="B156" s="6">
         <v>2</v>
       </c>
       <c r="C156" s="4">
@@ -5574,10 +5548,10 @@
       </c>
     </row>
     <row r="157" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="11">
+      <c r="A157" s="6">
         <v>135</v>
       </c>
-      <c r="B157" s="11">
+      <c r="B157" s="6">
         <v>2</v>
       </c>
       <c r="C157" s="4">
@@ -5585,10 +5559,10 @@
       </c>
     </row>
     <row r="158" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="11">
+      <c r="A158" s="6">
         <v>136</v>
       </c>
-      <c r="B158" s="11">
+      <c r="B158" s="6">
         <v>2</v>
       </c>
       <c r="C158" s="4">
@@ -5596,10 +5570,10 @@
       </c>
     </row>
     <row r="159" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="11">
+      <c r="A159" s="6">
         <v>137</v>
       </c>
-      <c r="B159" s="11">
+      <c r="B159" s="6">
         <v>2</v>
       </c>
       <c r="C159" s="4">
@@ -5607,10 +5581,10 @@
       </c>
     </row>
     <row r="160" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="11">
+      <c r="A160" s="6">
         <v>138</v>
       </c>
-      <c r="B160" s="11">
+      <c r="B160" s="6">
         <v>2</v>
       </c>
       <c r="C160" s="4">
@@ -5618,10 +5592,10 @@
       </c>
     </row>
     <row r="161" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="11">
+      <c r="A161" s="6">
         <v>139</v>
       </c>
-      <c r="B161" s="11">
+      <c r="B161" s="6">
         <v>2</v>
       </c>
       <c r="C161" s="4">
@@ -5629,10 +5603,10 @@
       </c>
     </row>
     <row r="162" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="11">
+      <c r="A162" s="6">
         <v>140</v>
       </c>
-      <c r="B162" s="11">
+      <c r="B162" s="6">
         <v>2</v>
       </c>
       <c r="C162" s="4">
@@ -5640,10 +5614,10 @@
       </c>
     </row>
     <row r="163" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="11">
+      <c r="A163" s="6">
         <v>141</v>
       </c>
-      <c r="B163" s="11">
+      <c r="B163" s="6">
         <v>2</v>
       </c>
       <c r="C163" s="4">
@@ -5651,10 +5625,10 @@
       </c>
     </row>
     <row r="164" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="11">
+      <c r="A164" s="6">
         <v>142</v>
       </c>
-      <c r="B164" s="11">
+      <c r="B164" s="6">
         <v>2</v>
       </c>
       <c r="C164" s="4">
@@ -5662,10 +5636,10 @@
       </c>
     </row>
     <row r="165" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="11">
+      <c r="A165" s="6">
         <v>143</v>
       </c>
-      <c r="B165" s="11">
+      <c r="B165" s="6">
         <v>2</v>
       </c>
       <c r="C165" s="4">
@@ -5673,10 +5647,10 @@
       </c>
     </row>
     <row r="166" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="11">
+      <c r="A166" s="6">
         <v>144</v>
       </c>
-      <c r="B166" s="11">
+      <c r="B166" s="6">
         <v>2</v>
       </c>
       <c r="C166" s="4">
@@ -5684,10 +5658,10 @@
       </c>
     </row>
     <row r="167" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="11">
+      <c r="A167" s="6">
         <v>145</v>
       </c>
-      <c r="B167" s="11">
+      <c r="B167" s="6">
         <v>2</v>
       </c>
       <c r="C167" s="4">
@@ -5695,10 +5669,10 @@
       </c>
     </row>
     <row r="168" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="11">
+      <c r="A168" s="6">
         <v>146</v>
       </c>
-      <c r="B168" s="11">
+      <c r="B168" s="6">
         <v>2</v>
       </c>
       <c r="C168" s="4">
@@ -5706,10 +5680,10 @@
       </c>
     </row>
     <row r="169" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="11">
+      <c r="A169" s="6">
         <v>147</v>
       </c>
-      <c r="B169" s="11">
+      <c r="B169" s="6">
         <v>2</v>
       </c>
       <c r="C169" s="4">
@@ -5717,10 +5691,10 @@
       </c>
     </row>
     <row r="170" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="11">
+      <c r="A170" s="6">
         <v>148</v>
       </c>
-      <c r="B170" s="11">
+      <c r="B170" s="6">
         <v>2</v>
       </c>
       <c r="C170" s="4">
@@ -5728,10 +5702,10 @@
       </c>
     </row>
     <row r="171" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="11">
+      <c r="A171" s="6">
         <v>149</v>
       </c>
-      <c r="B171" s="11">
+      <c r="B171" s="6">
         <v>2</v>
       </c>
       <c r="C171" s="4">
@@ -5739,10 +5713,10 @@
       </c>
     </row>
     <row r="172" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="11">
+      <c r="A172" s="6">
         <v>150</v>
       </c>
-      <c r="B172" s="11">
+      <c r="B172" s="6">
         <v>2</v>
       </c>
       <c r="C172" s="4">
@@ -5750,10 +5724,10 @@
       </c>
     </row>
     <row r="173" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="11">
+      <c r="A173" s="6">
         <v>151</v>
       </c>
-      <c r="B173" s="11">
+      <c r="B173" s="6">
         <v>2</v>
       </c>
       <c r="C173" s="4">
@@ -5761,10 +5735,10 @@
       </c>
     </row>
     <row r="174" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="11">
+      <c r="A174" s="6">
         <v>152</v>
       </c>
-      <c r="B174" s="11">
+      <c r="B174" s="6">
         <v>2</v>
       </c>
       <c r="C174" s="4">
@@ -5772,10 +5746,10 @@
       </c>
     </row>
     <row r="175" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="11">
+      <c r="A175" s="6">
         <v>153</v>
       </c>
-      <c r="B175" s="11">
+      <c r="B175" s="6">
         <v>2</v>
       </c>
       <c r="C175" s="4">
@@ -5783,10 +5757,10 @@
       </c>
     </row>
     <row r="176" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="11">
+      <c r="A176" s="6">
         <v>154</v>
       </c>
-      <c r="B176" s="11">
+      <c r="B176" s="6">
         <v>2</v>
       </c>
       <c r="C176" s="4">
@@ -5794,10 +5768,10 @@
       </c>
     </row>
     <row r="177" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="11">
+      <c r="A177" s="6">
         <v>155</v>
       </c>
-      <c r="B177" s="11">
+      <c r="B177" s="6">
         <v>2</v>
       </c>
       <c r="C177" s="4">
@@ -5805,10 +5779,10 @@
       </c>
     </row>
     <row r="178" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="11">
+      <c r="A178" s="6">
         <v>156</v>
       </c>
-      <c r="B178" s="11">
+      <c r="B178" s="6">
         <v>2</v>
       </c>
       <c r="C178" s="4">
@@ -5816,10 +5790,10 @@
       </c>
     </row>
     <row r="179" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="11">
+      <c r="A179" s="6">
         <v>157</v>
       </c>
-      <c r="B179" s="11">
+      <c r="B179" s="6">
         <v>2</v>
       </c>
       <c r="C179" s="4">
@@ -5827,10 +5801,10 @@
       </c>
     </row>
     <row r="180" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="11">
+      <c r="A180" s="6">
         <v>158</v>
       </c>
-      <c r="B180" s="11">
+      <c r="B180" s="6">
         <v>2</v>
       </c>
       <c r="C180" s="4">
@@ -5838,10 +5812,10 @@
       </c>
     </row>
     <row r="181" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="11">
+      <c r="A181" s="6">
         <v>159</v>
       </c>
-      <c r="B181" s="11">
+      <c r="B181" s="6">
         <v>2</v>
       </c>
       <c r="C181" s="4">
@@ -5849,10 +5823,10 @@
       </c>
     </row>
     <row r="182" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="11">
+      <c r="A182" s="6">
         <v>160</v>
       </c>
-      <c r="B182" s="11">
+      <c r="B182" s="6">
         <v>2</v>
       </c>
       <c r="C182" s="4">
@@ -5860,10 +5834,10 @@
       </c>
     </row>
     <row r="183" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="11">
+      <c r="A183" s="6">
         <v>161</v>
       </c>
-      <c r="B183" s="11">
+      <c r="B183" s="6">
         <v>2</v>
       </c>
       <c r="C183" s="4">
@@ -5871,10 +5845,10 @@
       </c>
     </row>
     <row r="184" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="11">
+      <c r="A184" s="6">
         <v>162</v>
       </c>
-      <c r="B184" s="11">
+      <c r="B184" s="6">
         <v>2</v>
       </c>
       <c r="C184" s="4">
@@ -5882,10 +5856,10 @@
       </c>
     </row>
     <row r="185" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="11">
+      <c r="A185" s="6">
         <v>163</v>
       </c>
-      <c r="B185" s="11">
+      <c r="B185" s="6">
         <v>2</v>
       </c>
       <c r="C185" s="4">
@@ -5893,10 +5867,10 @@
       </c>
     </row>
     <row r="186" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="11">
+      <c r="A186" s="6">
         <v>164</v>
       </c>
-      <c r="B186" s="11">
+      <c r="B186" s="6">
         <v>2</v>
       </c>
       <c r="C186" s="4">
@@ -5904,10 +5878,10 @@
       </c>
     </row>
     <row r="187" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="11">
+      <c r="A187" s="6">
         <v>165</v>
       </c>
-      <c r="B187" s="11">
+      <c r="B187" s="6">
         <v>2</v>
       </c>
       <c r="C187" s="4">
@@ -5915,10 +5889,10 @@
       </c>
     </row>
     <row r="188" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="11">
+      <c r="A188" s="6">
         <v>166</v>
       </c>
-      <c r="B188" s="11">
+      <c r="B188" s="6">
         <v>2</v>
       </c>
       <c r="C188" s="4">
@@ -5926,10 +5900,10 @@
       </c>
     </row>
     <row r="189" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="11">
+      <c r="A189" s="6">
         <v>167</v>
       </c>
-      <c r="B189" s="11">
+      <c r="B189" s="6">
         <v>2</v>
       </c>
       <c r="C189" s="4">
@@ -5937,10 +5911,10 @@
       </c>
     </row>
     <row r="190" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="11">
+      <c r="A190" s="6">
         <v>168</v>
       </c>
-      <c r="B190" s="11">
+      <c r="B190" s="6">
         <v>2</v>
       </c>
       <c r="C190" s="4">
@@ -5948,10 +5922,10 @@
       </c>
     </row>
     <row r="191" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="11">
+      <c r="A191" s="6">
         <v>169</v>
       </c>
-      <c r="B191" s="11">
+      <c r="B191" s="6">
         <v>2</v>
       </c>
       <c r="C191" s="4">
@@ -5959,10 +5933,10 @@
       </c>
     </row>
     <row r="192" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="11">
+      <c r="A192" s="6">
         <v>170</v>
       </c>
-      <c r="B192" s="11">
+      <c r="B192" s="6">
         <v>2</v>
       </c>
       <c r="C192" s="4">
@@ -5970,10 +5944,10 @@
       </c>
     </row>
     <row r="193" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="11">
+      <c r="A193" s="6">
         <v>171</v>
       </c>
-      <c r="B193" s="11">
+      <c r="B193" s="6">
         <v>2</v>
       </c>
       <c r="C193" s="4">
@@ -5981,10 +5955,10 @@
       </c>
     </row>
     <row r="194" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="11">
+      <c r="A194" s="6">
         <v>172</v>
       </c>
-      <c r="B194" s="11">
+      <c r="B194" s="6">
         <v>2</v>
       </c>
       <c r="C194" s="4">
@@ -5992,10 +5966,10 @@
       </c>
     </row>
     <row r="195" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="11">
+      <c r="A195" s="6">
         <v>173</v>
       </c>
-      <c r="B195" s="11">
+      <c r="B195" s="6">
         <v>2</v>
       </c>
       <c r="C195" s="4">
@@ -6003,10 +5977,10 @@
       </c>
     </row>
     <row r="196" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="11">
+      <c r="A196" s="6">
         <v>174</v>
       </c>
-      <c r="B196" s="11">
+      <c r="B196" s="6">
         <v>2</v>
       </c>
       <c r="C196" s="4">
@@ -6014,10 +5988,10 @@
       </c>
     </row>
     <row r="197" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="11">
+      <c r="A197" s="6">
         <v>175</v>
       </c>
-      <c r="B197" s="11">
+      <c r="B197" s="6">
         <v>2</v>
       </c>
       <c r="C197" s="4">
@@ -6025,10 +5999,10 @@
       </c>
     </row>
     <row r="198" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="11">
+      <c r="A198" s="6">
         <v>176</v>
       </c>
-      <c r="B198" s="11">
+      <c r="B198" s="6">
         <v>2</v>
       </c>
       <c r="C198" s="4">
@@ -6036,10 +6010,10 @@
       </c>
     </row>
     <row r="199" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="11">
+      <c r="A199" s="6">
         <v>177</v>
       </c>
-      <c r="B199" s="11">
+      <c r="B199" s="6">
         <v>2</v>
       </c>
       <c r="C199" s="4">
@@ -6047,10 +6021,10 @@
       </c>
     </row>
     <row r="200" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="11">
+      <c r="A200" s="6">
         <v>178</v>
       </c>
-      <c r="B200" s="11">
+      <c r="B200" s="6">
         <v>2</v>
       </c>
       <c r="C200" s="4">
@@ -6058,10 +6032,10 @@
       </c>
     </row>
     <row r="201" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="11">
+      <c r="A201" s="6">
         <v>179</v>
       </c>
-      <c r="B201" s="11">
+      <c r="B201" s="6">
         <v>2</v>
       </c>
       <c r="C201" s="4">
@@ -6069,10 +6043,10 @@
       </c>
     </row>
     <row r="202" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="11">
+      <c r="A202" s="6">
         <v>180</v>
       </c>
-      <c r="B202" s="11">
+      <c r="B202" s="6">
         <v>2</v>
       </c>
       <c r="C202" s="4">
@@ -6080,10 +6054,10 @@
       </c>
     </row>
     <row r="203" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="11">
+      <c r="A203" s="6">
         <v>181</v>
       </c>
-      <c r="B203" s="11">
+      <c r="B203" s="6">
         <v>2</v>
       </c>
       <c r="C203" s="4">
@@ -6091,10 +6065,10 @@
       </c>
     </row>
     <row r="204" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="11">
+      <c r="A204" s="6">
         <v>182</v>
       </c>
-      <c r="B204" s="11">
+      <c r="B204" s="6">
         <v>2</v>
       </c>
       <c r="C204" s="4">
@@ -6102,10 +6076,10 @@
       </c>
     </row>
     <row r="205" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="11">
+      <c r="A205" s="6">
         <v>183</v>
       </c>
-      <c r="B205" s="11">
+      <c r="B205" s="6">
         <v>2</v>
       </c>
       <c r="C205" s="4">
@@ -6113,10 +6087,10 @@
       </c>
     </row>
     <row r="206" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="11">
+      <c r="A206" s="6">
         <v>184</v>
       </c>
-      <c r="B206" s="11">
+      <c r="B206" s="6">
         <v>2</v>
       </c>
       <c r="C206" s="4">
@@ -6124,10 +6098,10 @@
       </c>
     </row>
     <row r="207" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="11">
+      <c r="A207" s="6">
         <v>185</v>
       </c>
-      <c r="B207" s="11">
+      <c r="B207" s="6">
         <v>2</v>
       </c>
       <c r="C207" s="4">
@@ -6135,10 +6109,10 @@
       </c>
     </row>
     <row r="208" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="11">
+      <c r="A208" s="6">
         <v>186</v>
       </c>
-      <c r="B208" s="11">
+      <c r="B208" s="6">
         <v>2</v>
       </c>
       <c r="C208" s="4">
@@ -6146,10 +6120,10 @@
       </c>
     </row>
     <row r="209" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="11">
+      <c r="A209" s="6">
         <v>187</v>
       </c>
-      <c r="B209" s="11">
+      <c r="B209" s="6">
         <v>2</v>
       </c>
       <c r="C209" s="4">
@@ -6157,10 +6131,10 @@
       </c>
     </row>
     <row r="210" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="11">
+      <c r="A210" s="6">
         <v>188</v>
       </c>
-      <c r="B210" s="11">
+      <c r="B210" s="6">
         <v>2</v>
       </c>
       <c r="C210" s="4">
@@ -6168,10 +6142,10 @@
       </c>
     </row>
     <row r="211" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="11">
+      <c r="A211" s="6">
         <v>189</v>
       </c>
-      <c r="B211" s="11">
+      <c r="B211" s="6">
         <v>2</v>
       </c>
       <c r="C211" s="4">
@@ -6179,10 +6153,10 @@
       </c>
     </row>
     <row r="212" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="11">
+      <c r="A212" s="6">
         <v>190</v>
       </c>
-      <c r="B212" s="11">
+      <c r="B212" s="6">
         <v>2</v>
       </c>
       <c r="C212" s="4">
@@ -6190,10 +6164,10 @@
       </c>
     </row>
     <row r="213" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="11">
+      <c r="A213" s="6">
         <v>191</v>
       </c>
-      <c r="B213" s="11">
+      <c r="B213" s="6">
         <v>2</v>
       </c>
       <c r="C213" s="4">
@@ -6201,10 +6175,10 @@
       </c>
     </row>
     <row r="214" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="11">
+      <c r="A214" s="6">
         <v>192</v>
       </c>
-      <c r="B214" s="11">
+      <c r="B214" s="6">
         <v>2</v>
       </c>
       <c r="C214" s="4">
@@ -6212,10 +6186,10 @@
       </c>
     </row>
     <row r="215" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="11">
+      <c r="A215" s="6">
         <v>193</v>
       </c>
-      <c r="B215" s="11">
+      <c r="B215" s="6">
         <v>2</v>
       </c>
       <c r="C215" s="4">
@@ -6223,10 +6197,10 @@
       </c>
     </row>
     <row r="216" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="11">
+      <c r="A216" s="6">
         <v>194</v>
       </c>
-      <c r="B216" s="11">
+      <c r="B216" s="6">
         <v>2</v>
       </c>
       <c r="C216" s="4">
@@ -6234,10 +6208,10 @@
       </c>
     </row>
     <row r="217" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="11">
+      <c r="A217" s="6">
         <v>195</v>
       </c>
-      <c r="B217" s="11">
+      <c r="B217" s="6">
         <v>2</v>
       </c>
       <c r="C217" s="4">
@@ -6245,10 +6219,10 @@
       </c>
     </row>
     <row r="218" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="11">
+      <c r="A218" s="6">
         <v>196</v>
       </c>
-      <c r="B218" s="11">
+      <c r="B218" s="6">
         <v>2</v>
       </c>
       <c r="C218" s="4">
@@ -6256,10 +6230,10 @@
       </c>
     </row>
     <row r="219" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="11">
+      <c r="A219" s="6">
         <v>197</v>
       </c>
-      <c r="B219" s="11">
+      <c r="B219" s="6">
         <v>2</v>
       </c>
       <c r="C219" s="4">
@@ -6267,10 +6241,10 @@
       </c>
     </row>
     <row r="220" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="11">
+      <c r="A220" s="6">
         <v>198</v>
       </c>
-      <c r="B220" s="11">
+      <c r="B220" s="6">
         <v>2</v>
       </c>
       <c r="C220" s="4">
@@ -6278,10 +6252,10 @@
       </c>
     </row>
     <row r="221" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="11">
+      <c r="A221" s="6">
         <v>199</v>
       </c>
-      <c r="B221" s="11">
+      <c r="B221" s="6">
         <v>2</v>
       </c>
       <c r="C221" s="4">
@@ -6289,10 +6263,10 @@
       </c>
     </row>
     <row r="222" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="11">
+      <c r="A222" s="6">
         <v>200</v>
       </c>
-      <c r="B222" s="11">
+      <c r="B222" s="6">
         <v>2</v>
       </c>
       <c r="C222" s="4">
@@ -6300,10 +6274,10 @@
       </c>
     </row>
     <row r="223" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="11">
+      <c r="A223" s="6">
         <v>201</v>
       </c>
-      <c r="B223" s="11">
+      <c r="B223" s="6">
         <v>2</v>
       </c>
       <c r="C223" s="4">
@@ -6311,10 +6285,10 @@
       </c>
     </row>
     <row r="224" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="11">
+      <c r="A224" s="6">
         <v>202</v>
       </c>
-      <c r="B224" s="11">
+      <c r="B224" s="6">
         <v>2</v>
       </c>
       <c r="C224" s="4">
@@ -6322,10 +6296,10 @@
       </c>
     </row>
     <row r="225" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="11">
+      <c r="A225" s="6">
         <v>203</v>
       </c>
-      <c r="B225" s="11">
+      <c r="B225" s="6">
         <v>2</v>
       </c>
       <c r="C225" s="4">
@@ -6333,10 +6307,10 @@
       </c>
     </row>
     <row r="226" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="11">
+      <c r="A226" s="6">
         <v>204</v>
       </c>
-      <c r="B226" s="11">
+      <c r="B226" s="6">
         <v>2</v>
       </c>
       <c r="C226" s="4">
@@ -6344,10 +6318,10 @@
       </c>
     </row>
     <row r="227" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="11">
+      <c r="A227" s="6">
         <v>205</v>
       </c>
-      <c r="B227" s="11">
+      <c r="B227" s="6">
         <v>2</v>
       </c>
       <c r="C227" s="4">
@@ -6355,10 +6329,10 @@
       </c>
     </row>
     <row r="228" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="11">
+      <c r="A228" s="6">
         <v>206</v>
       </c>
-      <c r="B228" s="11">
+      <c r="B228" s="6">
         <v>2</v>
       </c>
       <c r="C228" s="4">
@@ -6366,10 +6340,10 @@
       </c>
     </row>
     <row r="229" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="11">
+      <c r="A229" s="6">
         <v>207</v>
       </c>
-      <c r="B229" s="11">
+      <c r="B229" s="6">
         <v>2</v>
       </c>
       <c r="C229" s="4">
@@ -6377,10 +6351,10 @@
       </c>
     </row>
     <row r="230" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="11">
+      <c r="A230" s="6">
         <v>208</v>
       </c>
-      <c r="B230" s="11">
+      <c r="B230" s="6">
         <v>2</v>
       </c>
       <c r="C230" s="4">
@@ -6388,10 +6362,10 @@
       </c>
     </row>
     <row r="231" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="11">
+      <c r="A231" s="6">
         <v>209</v>
       </c>
-      <c r="B231" s="11">
+      <c r="B231" s="6">
         <v>2</v>
       </c>
       <c r="C231" s="4">
@@ -6399,10 +6373,10 @@
       </c>
     </row>
     <row r="232" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="11">
+      <c r="A232" s="6">
         <v>210</v>
       </c>
-      <c r="B232" s="11">
+      <c r="B232" s="6">
         <v>2</v>
       </c>
       <c r="C232" s="4">
@@ -6410,10 +6384,10 @@
       </c>
     </row>
     <row r="233" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="11">
+      <c r="A233" s="6">
         <v>211</v>
       </c>
-      <c r="B233" s="11">
+      <c r="B233" s="6">
         <v>2</v>
       </c>
       <c r="C233" s="4">
@@ -6421,10 +6395,10 @@
       </c>
     </row>
     <row r="234" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="11">
+      <c r="A234" s="6">
         <v>212</v>
       </c>
-      <c r="B234" s="11">
+      <c r="B234" s="6">
         <v>2</v>
       </c>
       <c r="C234" s="4">
@@ -6432,10 +6406,10 @@
       </c>
     </row>
     <row r="235" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="11">
+      <c r="A235" s="6">
         <v>213</v>
       </c>
-      <c r="B235" s="11">
+      <c r="B235" s="6">
         <v>2</v>
       </c>
       <c r="C235" s="4">
@@ -6443,10 +6417,10 @@
       </c>
     </row>
     <row r="236" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="11">
+      <c r="A236" s="6">
         <v>214</v>
       </c>
-      <c r="B236" s="11">
+      <c r="B236" s="6">
         <v>2</v>
       </c>
       <c r="C236" s="4">
@@ -6454,10 +6428,10 @@
       </c>
     </row>
     <row r="237" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="11">
+      <c r="A237" s="6">
         <v>215</v>
       </c>
-      <c r="B237" s="11">
+      <c r="B237" s="6">
         <v>2</v>
       </c>
       <c r="C237" s="4">
@@ -6465,10 +6439,10 @@
       </c>
     </row>
     <row r="238" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="11">
+      <c r="A238" s="6">
         <v>216</v>
       </c>
-      <c r="B238" s="11">
+      <c r="B238" s="6">
         <v>2</v>
       </c>
       <c r="C238" s="4">
@@ -6476,10 +6450,10 @@
       </c>
     </row>
     <row r="239" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="11">
+      <c r="A239" s="6">
         <v>217</v>
       </c>
-      <c r="B239" s="11">
+      <c r="B239" s="6">
         <v>2</v>
       </c>
       <c r="C239" s="4">
@@ -6487,10 +6461,10 @@
       </c>
     </row>
     <row r="240" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="11">
+      <c r="A240" s="6">
         <v>218</v>
       </c>
-      <c r="B240" s="11">
+      <c r="B240" s="6">
         <v>2</v>
       </c>
       <c r="C240" s="4">
@@ -6498,10 +6472,10 @@
       </c>
     </row>
     <row r="241" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="11">
+      <c r="A241" s="6">
         <v>219</v>
       </c>
-      <c r="B241" s="11">
+      <c r="B241" s="6">
         <v>2</v>
       </c>
       <c r="C241" s="4">
@@ -6509,10 +6483,10 @@
       </c>
     </row>
     <row r="242" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="11">
+      <c r="A242" s="6">
         <v>220</v>
       </c>
-      <c r="B242" s="11">
+      <c r="B242" s="6">
         <v>2</v>
       </c>
       <c r="C242" s="4">
@@ -6520,10 +6494,10 @@
       </c>
     </row>
     <row r="243" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="11">
+      <c r="A243" s="6">
         <v>221</v>
       </c>
-      <c r="B243" s="11">
+      <c r="B243" s="6">
         <v>2</v>
       </c>
       <c r="C243" s="4">
@@ -6531,10 +6505,10 @@
       </c>
     </row>
     <row r="244" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="11">
+      <c r="A244" s="6">
         <v>222</v>
       </c>
-      <c r="B244" s="11">
+      <c r="B244" s="6">
         <v>2</v>
       </c>
       <c r="C244" s="4">
@@ -6542,10 +6516,10 @@
       </c>
     </row>
     <row r="245" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="11">
+      <c r="A245" s="6">
         <v>223</v>
       </c>
-      <c r="B245" s="11">
+      <c r="B245" s="6">
         <v>2</v>
       </c>
       <c r="C245" s="4">
@@ -6553,10 +6527,10 @@
       </c>
     </row>
     <row r="246" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="11">
+      <c r="A246" s="6">
         <v>224</v>
       </c>
-      <c r="B246" s="11">
+      <c r="B246" s="6">
         <v>2</v>
       </c>
       <c r="C246" s="4">
@@ -6564,10 +6538,10 @@
       </c>
     </row>
     <row r="247" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="11">
+      <c r="A247" s="6">
         <v>225</v>
       </c>
-      <c r="B247" s="11">
+      <c r="B247" s="6">
         <v>2</v>
       </c>
       <c r="C247" s="4">
@@ -6575,10 +6549,10 @@
       </c>
     </row>
     <row r="248" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="11">
+      <c r="A248" s="6">
         <v>226</v>
       </c>
-      <c r="B248" s="11">
+      <c r="B248" s="6">
         <v>2</v>
       </c>
       <c r="C248" s="4">
@@ -6586,10 +6560,10 @@
       </c>
     </row>
     <row r="249" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A249" s="11">
+      <c r="A249" s="6">
         <v>227</v>
       </c>
-      <c r="B249" s="11">
+      <c r="B249" s="6">
         <v>2</v>
       </c>
       <c r="C249" s="4">
@@ -6597,10 +6571,10 @@
       </c>
     </row>
     <row r="250" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="11">
+      <c r="A250" s="6">
         <v>228</v>
       </c>
-      <c r="B250" s="11">
+      <c r="B250" s="6">
         <v>2</v>
       </c>
       <c r="C250" s="4">
@@ -6608,10 +6582,10 @@
       </c>
     </row>
     <row r="251" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="11">
+      <c r="A251" s="6">
         <v>229</v>
       </c>
-      <c r="B251" s="11">
+      <c r="B251" s="6">
         <v>2</v>
       </c>
       <c r="C251" s="4">
@@ -6619,10 +6593,10 @@
       </c>
     </row>
     <row r="252" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="11">
+      <c r="A252" s="6">
         <v>230</v>
       </c>
-      <c r="B252" s="11">
+      <c r="B252" s="6">
         <v>2</v>
       </c>
       <c r="C252" s="4">
@@ -6630,10 +6604,10 @@
       </c>
     </row>
     <row r="253" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="11">
+      <c r="A253" s="6">
         <v>231</v>
       </c>
-      <c r="B253" s="11">
+      <c r="B253" s="6">
         <v>2</v>
       </c>
       <c r="C253" s="4">
@@ -6641,10 +6615,10 @@
       </c>
     </row>
     <row r="254" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="11">
+      <c r="A254" s="6">
         <v>232</v>
       </c>
-      <c r="B254" s="11">
+      <c r="B254" s="6">
         <v>2</v>
       </c>
       <c r="C254" s="4">
@@ -6652,10 +6626,10 @@
       </c>
     </row>
     <row r="255" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="11">
+      <c r="A255" s="6">
         <v>233</v>
       </c>
-      <c r="B255" s="11">
+      <c r="B255" s="6">
         <v>2</v>
       </c>
       <c r="C255" s="4">
@@ -6663,10 +6637,10 @@
       </c>
     </row>
     <row r="256" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A256" s="11">
+      <c r="A256" s="6">
         <v>234</v>
       </c>
-      <c r="B256" s="11">
+      <c r="B256" s="6">
         <v>2</v>
       </c>
       <c r="C256" s="4">
@@ -6674,10 +6648,10 @@
       </c>
     </row>
     <row r="257" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="11">
+      <c r="A257" s="6">
         <v>235</v>
       </c>
-      <c r="B257" s="11">
+      <c r="B257" s="6">
         <v>2</v>
       </c>
       <c r="C257" s="4">
@@ -6685,10 +6659,10 @@
       </c>
     </row>
     <row r="258" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="11">
+      <c r="A258" s="6">
         <v>236</v>
       </c>
-      <c r="B258" s="11">
+      <c r="B258" s="6">
         <v>2</v>
       </c>
       <c r="C258" s="4">
@@ -6696,10 +6670,10 @@
       </c>
     </row>
     <row r="259" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="11">
+      <c r="A259" s="6">
         <v>237</v>
       </c>
-      <c r="B259" s="11">
+      <c r="B259" s="6">
         <v>2</v>
       </c>
       <c r="C259" s="4">
@@ -6707,10 +6681,10 @@
       </c>
     </row>
     <row r="260" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="11">
+      <c r="A260" s="6">
         <v>238</v>
       </c>
-      <c r="B260" s="11">
+      <c r="B260" s="6">
         <v>2</v>
       </c>
       <c r="C260" s="4">
@@ -6718,10 +6692,10 @@
       </c>
     </row>
     <row r="261" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="11">
+      <c r="A261" s="6">
         <v>239</v>
       </c>
-      <c r="B261" s="11">
+      <c r="B261" s="6">
         <v>2</v>
       </c>
       <c r="C261" s="4">
@@ -6729,10 +6703,10 @@
       </c>
     </row>
     <row r="262" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="11">
+      <c r="A262" s="6">
         <v>240</v>
       </c>
-      <c r="B262" s="11">
+      <c r="B262" s="6">
         <v>2</v>
       </c>
       <c r="C262" s="4">
@@ -6740,10 +6714,10 @@
       </c>
     </row>
     <row r="263" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="11">
+      <c r="A263" s="6">
         <v>241</v>
       </c>
-      <c r="B263" s="11">
+      <c r="B263" s="6">
         <v>2</v>
       </c>
       <c r="C263" s="4">
@@ -6751,10 +6725,10 @@
       </c>
     </row>
     <row r="264" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="11">
+      <c r="A264" s="6">
         <v>242</v>
       </c>
-      <c r="B264" s="11">
+      <c r="B264" s="6">
         <v>2</v>
       </c>
       <c r="C264" s="4">
@@ -6762,10 +6736,10 @@
       </c>
     </row>
     <row r="265" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="11">
+      <c r="A265" s="6">
         <v>243</v>
       </c>
-      <c r="B265" s="11">
+      <c r="B265" s="6">
         <v>2</v>
       </c>
       <c r="C265" s="4">
@@ -6773,10 +6747,10 @@
       </c>
     </row>
     <row r="266" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="11">
+      <c r="A266" s="6">
         <v>244</v>
       </c>
-      <c r="B266" s="11">
+      <c r="B266" s="6">
         <v>2</v>
       </c>
       <c r="C266" s="4">
@@ -6784,10 +6758,10 @@
       </c>
     </row>
     <row r="267" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="11">
+      <c r="A267" s="6">
         <v>245</v>
       </c>
-      <c r="B267" s="11">
+      <c r="B267" s="6">
         <v>2</v>
       </c>
       <c r="C267" s="4">
@@ -6795,10 +6769,10 @@
       </c>
     </row>
     <row r="268" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="11">
+      <c r="A268" s="6">
         <v>246</v>
       </c>
-      <c r="B268" s="11">
+      <c r="B268" s="6">
         <v>2</v>
       </c>
       <c r="C268" s="4">
@@ -6806,10 +6780,10 @@
       </c>
     </row>
     <row r="269" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="11">
+      <c r="A269" s="6">
         <v>247</v>
       </c>
-      <c r="B269" s="11">
+      <c r="B269" s="6">
         <v>2</v>
       </c>
       <c r="C269" s="4">
@@ -6817,10 +6791,10 @@
       </c>
     </row>
     <row r="270" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="11">
+      <c r="A270" s="6">
         <v>248</v>
       </c>
-      <c r="B270" s="11">
+      <c r="B270" s="6">
         <v>2</v>
       </c>
       <c r="C270" s="4">
@@ -6828,10 +6802,10 @@
       </c>
     </row>
     <row r="271" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="11">
+      <c r="A271" s="6">
         <v>249</v>
       </c>
-      <c r="B271" s="11">
+      <c r="B271" s="6">
         <v>2</v>
       </c>
       <c r="C271" s="4">
@@ -6839,10 +6813,10 @@
       </c>
     </row>
     <row r="272" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="11">
+      <c r="A272" s="6">
         <v>250</v>
       </c>
-      <c r="B272" s="11">
+      <c r="B272" s="6">
         <v>2</v>
       </c>
       <c r="C272" s="4">
@@ -6850,10 +6824,10 @@
       </c>
     </row>
     <row r="273" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="11">
+      <c r="A273" s="6">
         <v>251</v>
       </c>
-      <c r="B273" s="11">
+      <c r="B273" s="6">
         <v>2</v>
       </c>
       <c r="C273" s="4">
@@ -6861,10 +6835,10 @@
       </c>
     </row>
     <row r="274" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="11">
+      <c r="A274" s="6">
         <v>252</v>
       </c>
-      <c r="B274" s="11">
+      <c r="B274" s="6">
         <v>2</v>
       </c>
       <c r="C274" s="4">
@@ -6872,10 +6846,10 @@
       </c>
     </row>
     <row r="275" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="11">
+      <c r="A275" s="6">
         <v>253</v>
       </c>
-      <c r="B275" s="11">
+      <c r="B275" s="6">
         <v>2</v>
       </c>
       <c r="C275" s="4">
@@ -6883,10 +6857,10 @@
       </c>
     </row>
     <row r="276" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="11">
+      <c r="A276" s="6">
         <v>254</v>
       </c>
-      <c r="B276" s="11">
+      <c r="B276" s="6">
         <v>2</v>
       </c>
       <c r="C276" s="4">
@@ -6894,10 +6868,10 @@
       </c>
     </row>
     <row r="277" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="11">
+      <c r="A277" s="6">
         <v>255</v>
       </c>
-      <c r="B277" s="11">
+      <c r="B277" s="6">
         <v>2</v>
       </c>
       <c r="C277" s="4">
@@ -6905,10 +6879,10 @@
       </c>
     </row>
     <row r="278" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="11">
+      <c r="A278" s="6">
         <v>256</v>
       </c>
-      <c r="B278" s="11">
+      <c r="B278" s="6">
         <v>2</v>
       </c>
       <c r="C278" s="4">
@@ -6916,10 +6890,10 @@
       </c>
     </row>
     <row r="279" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="11">
+      <c r="A279" s="6">
         <v>257</v>
       </c>
-      <c r="B279" s="11">
+      <c r="B279" s="6">
         <v>2</v>
       </c>
       <c r="C279" s="4">
@@ -6927,10 +6901,10 @@
       </c>
     </row>
     <row r="280" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="11">
+      <c r="A280" s="6">
         <v>258</v>
       </c>
-      <c r="B280" s="11">
+      <c r="B280" s="6">
         <v>2</v>
       </c>
       <c r="C280" s="4">
@@ -6938,10 +6912,10 @@
       </c>
     </row>
     <row r="281" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="11">
+      <c r="A281" s="6">
         <v>259</v>
       </c>
-      <c r="B281" s="11">
+      <c r="B281" s="6">
         <v>2</v>
       </c>
       <c r="C281" s="4">
@@ -6949,10 +6923,10 @@
       </c>
     </row>
     <row r="282" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="11">
+      <c r="A282" s="6">
         <v>260</v>
       </c>
-      <c r="B282" s="11">
+      <c r="B282" s="6">
         <v>2</v>
       </c>
       <c r="C282" s="4">
@@ -6960,10 +6934,10 @@
       </c>
     </row>
     <row r="283" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="11">
+      <c r="A283" s="6">
         <v>261</v>
       </c>
-      <c r="B283" s="11">
+      <c r="B283" s="6">
         <v>2</v>
       </c>
       <c r="C283" s="4">
@@ -6971,10 +6945,10 @@
       </c>
     </row>
     <row r="284" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="11">
+      <c r="A284" s="6">
         <v>262</v>
       </c>
-      <c r="B284" s="11">
+      <c r="B284" s="6">
         <v>2</v>
       </c>
       <c r="C284" s="4">
@@ -6982,10 +6956,10 @@
       </c>
     </row>
     <row r="285" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="11">
+      <c r="A285" s="6">
         <v>263</v>
       </c>
-      <c r="B285" s="11">
+      <c r="B285" s="6">
         <v>2</v>
       </c>
       <c r="C285" s="4">
@@ -6993,10 +6967,10 @@
       </c>
     </row>
     <row r="286" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="11">
+      <c r="A286" s="6">
         <v>264</v>
       </c>
-      <c r="B286" s="11">
+      <c r="B286" s="6">
         <v>2</v>
       </c>
       <c r="C286" s="4">
@@ -7004,10 +6978,10 @@
       </c>
     </row>
     <row r="287" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="11">
+      <c r="A287" s="6">
         <v>265</v>
       </c>
-      <c r="B287" s="11">
+      <c r="B287" s="6">
         <v>2</v>
       </c>
       <c r="C287" s="4">
@@ -7015,10 +6989,10 @@
       </c>
     </row>
     <row r="288" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="11">
+      <c r="A288" s="6">
         <v>266</v>
       </c>
-      <c r="B288" s="11">
+      <c r="B288" s="6">
         <v>2</v>
       </c>
       <c r="C288" s="4">
@@ -7026,10 +7000,10 @@
       </c>
     </row>
     <row r="289" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="11">
+      <c r="A289" s="6">
         <v>267</v>
       </c>
-      <c r="B289" s="11">
+      <c r="B289" s="6">
         <v>2</v>
       </c>
       <c r="C289" s="4">
@@ -7037,10 +7011,10 @@
       </c>
     </row>
     <row r="290" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="11">
+      <c r="A290" s="6">
         <v>268</v>
       </c>
-      <c r="B290" s="11">
+      <c r="B290" s="6">
         <v>2</v>
       </c>
       <c r="C290" s="4">
@@ -7048,10 +7022,10 @@
       </c>
     </row>
     <row r="291" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="11">
+      <c r="A291" s="6">
         <v>269</v>
       </c>
-      <c r="B291" s="11">
+      <c r="B291" s="6">
         <v>2</v>
       </c>
       <c r="C291" s="4">
@@ -7059,10 +7033,10 @@
       </c>
     </row>
     <row r="292" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="11">
+      <c r="A292" s="6">
         <v>270</v>
       </c>
-      <c r="B292" s="11">
+      <c r="B292" s="6">
         <v>2</v>
       </c>
       <c r="C292" s="4">
@@ -7070,10 +7044,10 @@
       </c>
     </row>
     <row r="293" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="11">
+      <c r="A293" s="6">
         <v>271</v>
       </c>
-      <c r="B293" s="11">
+      <c r="B293" s="6">
         <v>2</v>
       </c>
       <c r="C293" s="4">
@@ -7081,10 +7055,10 @@
       </c>
     </row>
     <row r="294" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="11">
+      <c r="A294" s="6">
         <v>272</v>
       </c>
-      <c r="B294" s="11">
+      <c r="B294" s="6">
         <v>2</v>
       </c>
       <c r="C294" s="4">
@@ -7092,10 +7066,10 @@
       </c>
     </row>
     <row r="295" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="11">
+      <c r="A295" s="6">
         <v>273</v>
       </c>
-      <c r="B295" s="11">
+      <c r="B295" s="6">
         <v>2</v>
       </c>
       <c r="C295" s="4">
@@ -7103,10 +7077,10 @@
       </c>
     </row>
     <row r="296" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="11">
+      <c r="A296" s="6">
         <v>274</v>
       </c>
-      <c r="B296" s="11">
+      <c r="B296" s="6">
         <v>2</v>
       </c>
       <c r="C296" s="4">
@@ -7114,10 +7088,10 @@
       </c>
     </row>
     <row r="297" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="11">
+      <c r="A297" s="6">
         <v>275</v>
       </c>
-      <c r="B297" s="11">
+      <c r="B297" s="6">
         <v>2</v>
       </c>
       <c r="C297" s="4">
@@ -7125,10 +7099,10 @@
       </c>
     </row>
     <row r="298" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="11">
+      <c r="A298" s="6">
         <v>276</v>
       </c>
-      <c r="B298" s="11">
+      <c r="B298" s="6">
         <v>2</v>
       </c>
       <c r="C298" s="4">
@@ -7136,10 +7110,10 @@
       </c>
     </row>
     <row r="299" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="11">
+      <c r="A299" s="6">
         <v>277</v>
       </c>
-      <c r="B299" s="11">
+      <c r="B299" s="6">
         <v>2</v>
       </c>
       <c r="C299" s="4">
@@ -7147,10 +7121,10 @@
       </c>
     </row>
     <row r="300" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="11">
+      <c r="A300" s="6">
         <v>278</v>
       </c>
-      <c r="B300" s="11">
+      <c r="B300" s="6">
         <v>2</v>
       </c>
       <c r="C300" s="4">
@@ -7158,10 +7132,10 @@
       </c>
     </row>
     <row r="301" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="11">
+      <c r="A301" s="6">
         <v>279</v>
       </c>
-      <c r="B301" s="11">
+      <c r="B301" s="6">
         <v>2</v>
       </c>
       <c r="C301" s="4">
@@ -7169,10 +7143,10 @@
       </c>
     </row>
     <row r="302" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="11">
+      <c r="A302" s="6">
         <v>280</v>
       </c>
-      <c r="B302" s="11">
+      <c r="B302" s="6">
         <v>2</v>
       </c>
       <c r="C302" s="4">
@@ -7180,10 +7154,10 @@
       </c>
     </row>
     <row r="303" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="11">
+      <c r="A303" s="6">
         <v>281</v>
       </c>
-      <c r="B303" s="11">
+      <c r="B303" s="6">
         <v>2</v>
       </c>
       <c r="C303" s="4">
@@ -7191,10 +7165,10 @@
       </c>
     </row>
     <row r="304" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A304" s="11">
+      <c r="A304" s="6">
         <v>282</v>
       </c>
-      <c r="B304" s="11">
+      <c r="B304" s="6">
         <v>2</v>
       </c>
       <c r="C304" s="4">
@@ -7202,10 +7176,10 @@
       </c>
     </row>
     <row r="305" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="11">
+      <c r="A305" s="6">
         <v>283</v>
       </c>
-      <c r="B305" s="11">
+      <c r="B305" s="6">
         <v>2</v>
       </c>
       <c r="C305" s="4">
@@ -7213,10 +7187,10 @@
       </c>
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A306" s="11">
+      <c r="A306" s="6">
         <v>284</v>
       </c>
-      <c r="B306" s="11">
+      <c r="B306" s="6">
         <v>2</v>
       </c>
       <c r="C306" s="4">
@@ -7224,10 +7198,10 @@
       </c>
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A307" s="11">
+      <c r="A307" s="6">
         <v>285</v>
       </c>
-      <c r="B307" s="11">
+      <c r="B307" s="6">
         <v>2</v>
       </c>
       <c r="C307" s="4">
@@ -7235,10 +7209,10 @@
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A308" s="11">
+      <c r="A308" s="6">
         <v>286</v>
       </c>
-      <c r="B308" s="11">
+      <c r="B308" s="6">
         <v>2</v>
       </c>
       <c r="C308" s="4">
@@ -7246,10 +7220,10 @@
       </c>
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A309" s="11">
+      <c r="A309" s="6">
         <v>287</v>
       </c>
-      <c r="B309" s="11">
+      <c r="B309" s="6">
         <v>2</v>
       </c>
       <c r="C309" s="4">
@@ -7257,10 +7231,10 @@
       </c>
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A310" s="11">
+      <c r="A310" s="6">
         <v>288</v>
       </c>
-      <c r="B310" s="11">
+      <c r="B310" s="6">
         <v>2</v>
       </c>
       <c r="C310" s="4">
@@ -7268,10 +7242,10 @@
       </c>
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A311" s="11">
+      <c r="A311" s="6">
         <v>289</v>
       </c>
-      <c r="B311" s="11">
+      <c r="B311" s="6">
         <v>2</v>
       </c>
       <c r="C311" s="4">
@@ -7279,10 +7253,10 @@
       </c>
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A312" s="11">
+      <c r="A312" s="6">
         <v>290</v>
       </c>
-      <c r="B312" s="11">
+      <c r="B312" s="6">
         <v>2</v>
       </c>
       <c r="C312" s="4">
@@ -7290,10 +7264,10 @@
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A313" s="11">
+      <c r="A313" s="6">
         <v>291</v>
       </c>
-      <c r="B313" s="11">
+      <c r="B313" s="6">
         <v>2</v>
       </c>
       <c r="C313" s="4">
@@ -7309,7 +7283,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Z281"/>
+  <dimension ref="A1:J283"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -13785,56 +13759,56 @@
       <c r="J233" s="5"/>
     </row>
     <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="6">
+      <c r="A234" s="4">
         <v>1504</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C234" s="6">
+      <c r="C234" s="4">
         <v>15</v>
       </c>
-      <c r="D234" s="6">
+      <c r="D234" s="4">
         <v>1504</v>
       </c>
-      <c r="E234" s="6"/>
-      <c r="F234" s="6" t="s">
+      <c r="E234" s="4"/>
+      <c r="F234" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G234" s="7" t="s">
+      <c r="G234" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="H234" s="7"/>
-      <c r="I234" s="7" t="s">
+      <c r="H234" s="5"/>
+      <c r="I234" s="5" t="s">
         <v>279</v>
       </c>
       <c r="J234" s="5"/>
     </row>
     <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="8">
+      <c r="A235" s="4">
         <v>16</v>
       </c>
-      <c r="B235" s="9" t="s">
+      <c r="B235" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C235" s="8">
+      <c r="C235" s="4">
         <v>1</v>
       <